--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -346,7 +346,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -488,11 +488,44 @@
       </bottom>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -812,6 +845,8 @@
     <xf numFmtId="0" fontId="25" fillId="32" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13785,7 +13820,7 @@
           <t>P6-S02</t>
         </is>
       </c>
-      <c r="B9" s="101" t="n"/>
+      <c r="B9" s="113" t="n"/>
       <c r="C9" s="102" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -14028,7 +14063,7 @@
           <t>P6-S03c</t>
         </is>
       </c>
-      <c r="B14" s="92" t="n"/>
+      <c r="B14" s="113" t="n"/>
       <c r="C14" s="93" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -14271,7 +14306,7 @@
           <t>P6-S06</t>
         </is>
       </c>
-      <c r="B19" s="101" t="n"/>
+      <c r="B19" s="113" t="n"/>
       <c r="C19" s="102" t="inlineStr">
         <is>
           <t>Integrations</t>
@@ -14426,7 +14461,7 @@
           <t>P6-S08</t>
         </is>
       </c>
-      <c r="B22" s="92" t="n"/>
+      <c r="B22" s="114" t="n"/>
       <c r="C22" s="93" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14491,7 +14526,7 @@
           <t>P6-S09</t>
         </is>
       </c>
-      <c r="B23" s="101" t="n"/>
+      <c r="B23" s="113" t="n"/>
       <c r="C23" s="102" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14644,7 +14679,7 @@
           <t>P6-S11</t>
         </is>
       </c>
-      <c r="B26" s="92" t="n"/>
+      <c r="B26" s="114" t="n"/>
       <c r="C26" s="93" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14711,7 +14746,7 @@
           <t>P6-S12</t>
         </is>
       </c>
-      <c r="B27" s="101" t="n"/>
+      <c r="B27" s="114" t="n"/>
       <c r="C27" s="102" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14778,7 +14813,7 @@
           <t>P6-S13</t>
         </is>
       </c>
-      <c r="B28" s="92" t="n"/>
+      <c r="B28" s="113" t="n"/>
       <c r="C28" s="93" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15021,7 +15056,7 @@
           <t>P6-F15</t>
         </is>
       </c>
-      <c r="B33" s="101" t="n"/>
+      <c r="B33" s="114" t="n"/>
       <c r="C33" s="102" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15088,7 +15123,7 @@
           <t>P6-F16</t>
         </is>
       </c>
-      <c r="B34" s="92" t="n"/>
+      <c r="B34" s="114" t="n"/>
       <c r="C34" s="93" t="inlineStr">
         <is>
           <t>Backend</t>
@@ -15137,7 +15172,7 @@
           <t>P6-F16b</t>
         </is>
       </c>
-      <c r="B35" s="101" t="n"/>
+      <c r="B35" s="114" t="n"/>
       <c r="C35" s="102" t="inlineStr">
         <is>
           <t>Docs</t>
@@ -15186,7 +15221,7 @@
           <t>P6-F17</t>
         </is>
       </c>
-      <c r="B36" s="92" t="n"/>
+      <c r="B36" s="113" t="n"/>
       <c r="C36" s="93" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15272,7 +15307,7 @@
       </c>
       <c r="B38" s="92" t="inlineStr">
         <is>
-          <t>feature/swiggy-prompt-injection</t>
+          <t>feature/swiggy-prompt-injection (deleted post-merge)</t>
         </is>
       </c>
       <c r="C38" s="93" t="inlineStr">
@@ -15287,7 +15322,7 @@
       </c>
       <c r="E38" s="94" t="inlineStr">
         <is>
-          <t>Swiggy enricher prompt_text injected into 3 LLM prompts: (1) menu_intelligence gets ## Market Context (competitor prices, alerts); (2) inventory gets ## Live Procurement Options (Instamart prices per shortage item); (3) reservation gets ## Occupancy Signal (area HIGH/MEDIUM/LOW). LLM now references Swiggy data in reasoning — e.g. "Order tomatoes via Instamart at Rs.24/kg". Frontend: AgentCard swiggySignal prop shows orange Swiggy badge in card header with one-line market signal (area tonight: HIGH, 5 Instamart prices live, 2 pricing alerts).</t>
+          <t>Swiggy enricher prompt_text injected into 3 LLM prompts: (1) menu_intelligence gets ## Market Context (competitor prices, alerts); (2) inventory gets ## Live Procurement Options (Instamart prices per shortage item); (3) reservation gets ## Occupancy Signal (area HIGH/MEDIUM/LOW). LLM now references Swiggy data in reasoning — e.g. "Order tomatoes via Instamart at Rs.24/kg". Frontend: AgentCard swiggySignal prop shows orange Swiggy badge in card header with one-line market signal (area tonight: HIGH, 5 Instamart prices live, 2 pricing alerts). Never independently PR-ed to dev -- fix/swiggy-sse-market-intel branched off its tip and shipped it as part of that PR instead; feature/swiggy-prompt-injection deleted 2026-07-03 (remote + local), fully superseded.</t>
         </is>
       </c>
       <c r="F38" s="94" t="inlineStr">
@@ -15357,7 +15392,7 @@
       </c>
       <c r="E40" s="94" t="inlineStr">
         <is>
-          <t>Fixed Instamart procurement card rendering nothing despite live shortage data: frontend read item.name/item.in_stock but backend ProcurementEnricher sends item.ingredient/item.inStock (confirmed against the enricher's own test contract). Found and fixed a cost/token-attribution race: reservation and inventory nodes share the 'fast' LLM tier and run in true parallel; _inject() draining the shared provider usage buffer at node start/end let one node's drain steal the other's usage records. Fixed via per-node contextvar tagging (bind_llm_usage_node/drain_usage(node=...)) in llm/base.py + graph.py. Converted ~11 files across the Swiggy integration layer + cache/vector-memory infra from stdlib logging to structlog -- the app never calls logging.basicConfig(), so every .info()/.debug() call on those modules was being silently dropped, and .warning() lines printed unstructured with no run correlation.</t>
+          <t>Fixed Instamart procurement card rendering nothing despite live shortage data: frontend read item.name/item.in_stock but backend ProcurementEnricher sends item.ingredient/item.inStock (confirmed against the enricher's own test contract). Found and fixed a cost/token-attribution race: reservation and inventory nodes share the 'fast' LLM tier and run in true parallel; _inject() draining the shared provider usage buffer at node start/end let one node's drain steal the other's usage records. Fixed via per-node contextvar tagging (bind_llm_usage_node/drain_usage(node=...)) in llm/base.py + graph.py. Converted ~11 files across the Swiggy integration layer + cache/vector-memory infra from stdlib logging to structlog -- the app never calls logging.basicConfig(), so every .info()/.debug() call on those modules was being silently dropped, and .warning() lines printed unstructured with no run correlation. Merged to dev via PR #87, 2026-07-03.</t>
         </is>
       </c>
       <c r="F40" s="94" t="inlineStr">
@@ -15411,7 +15446,7 @@
           <t>P6-S36</t>
         </is>
       </c>
-      <c r="B41" s="101" t="n"/>
+      <c r="B41" s="114" t="n"/>
       <c r="C41" s="102" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15478,7 +15513,7 @@
           <t>P6-S37</t>
         </is>
       </c>
-      <c r="B42" s="92" t="n"/>
+      <c r="B42" s="114" t="n"/>
       <c r="C42" s="93" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -15545,7 +15580,7 @@
           <t>P6-S38</t>
         </is>
       </c>
-      <c r="B43" s="101" t="n"/>
+      <c r="B43" s="114" t="n"/>
       <c r="C43" s="102" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15612,7 +15647,7 @@
           <t>P6-S39</t>
         </is>
       </c>
-      <c r="B44" s="92" t="n"/>
+      <c r="B44" s="114" t="n"/>
       <c r="C44" s="93" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15679,7 +15714,7 @@
           <t>P6-S40</t>
         </is>
       </c>
-      <c r="B45" s="101" t="n"/>
+      <c r="B45" s="114" t="n"/>
       <c r="C45" s="102" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15746,7 +15781,7 @@
           <t>P6-S41</t>
         </is>
       </c>
-      <c r="B46" s="92" t="n"/>
+      <c r="B46" s="114" t="n"/>
       <c r="C46" s="93" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15813,7 +15848,7 @@
           <t>P6-S42</t>
         </is>
       </c>
-      <c r="B47" s="101" t="n"/>
+      <c r="B47" s="114" t="n"/>
       <c r="C47" s="102" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15880,7 +15915,7 @@
           <t>P6-S47</t>
         </is>
       </c>
-      <c r="B48" s="92" t="n"/>
+      <c r="B48" s="114" t="n"/>
       <c r="C48" s="93" t="inlineStr">
         <is>
           <t>Security</t>
@@ -15939,7 +15974,7 @@
           <t>P6-S48</t>
         </is>
       </c>
-      <c r="B49" s="101" t="n"/>
+      <c r="B49" s="113" t="n"/>
       <c r="C49" s="102" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -16023,20 +16058,20 @@
           <t>DO FIRST — no staging creds needed  |  each task: own branch → PR → merge dev → merge main → docs + screenshots + tracker updated</t>
         </is>
       </c>
-      <c r="B51" s="109" t="n"/>
-      <c r="C51" s="109" t="n"/>
-      <c r="D51" s="109" t="n"/>
-      <c r="E51" s="109" t="n"/>
-      <c r="F51" s="109" t="n"/>
-      <c r="G51" s="109" t="n"/>
-      <c r="H51" s="109" t="n"/>
-      <c r="I51" s="109" t="n"/>
-      <c r="J51" s="109" t="n"/>
-      <c r="K51" s="109" t="n"/>
-      <c r="L51" s="109" t="n"/>
-      <c r="M51" s="109" t="n"/>
-      <c r="N51" s="109" t="n"/>
-      <c r="O51" s="109" t="n"/>
+      <c r="B51" s="61" t="n"/>
+      <c r="C51" s="61" t="n"/>
+      <c r="D51" s="61" t="n"/>
+      <c r="E51" s="61" t="n"/>
+      <c r="F51" s="61" t="n"/>
+      <c r="G51" s="61" t="n"/>
+      <c r="H51" s="61" t="n"/>
+      <c r="I51" s="61" t="n"/>
+      <c r="J51" s="61" t="n"/>
+      <c r="K51" s="61" t="n"/>
+      <c r="L51" s="61" t="n"/>
+      <c r="M51" s="61" t="n"/>
+      <c r="N51" s="61" t="n"/>
+      <c r="O51" s="61" t="n"/>
     </row>
     <row r="52" ht="8" customHeight="1" s="65">
       <c r="A52" s="99" t="n"/>
@@ -16114,7 +16149,7 @@
           <t>P6-MI02</t>
         </is>
       </c>
-      <c r="B54" s="92" t="n"/>
+      <c r="B54" s="114" t="n"/>
       <c r="C54" s="93" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -16163,7 +16198,7 @@
           <t>P6-MI03</t>
         </is>
       </c>
-      <c r="B55" s="101" t="n"/>
+      <c r="B55" s="113" t="n"/>
       <c r="C55" s="102" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -17543,20 +17578,20 @@
           <t>→ DEMO 1  |  all above on main, docs updated, screenshots done — record full Swiggy read + AI + voice + live monitor demo ←</t>
         </is>
       </c>
-      <c r="B89" s="109" t="n"/>
-      <c r="C89" s="109" t="n"/>
-      <c r="D89" s="109" t="n"/>
-      <c r="E89" s="109" t="n"/>
-      <c r="F89" s="109" t="n"/>
-      <c r="G89" s="109" t="n"/>
-      <c r="H89" s="109" t="n"/>
-      <c r="I89" s="109" t="n"/>
-      <c r="J89" s="109" t="n"/>
-      <c r="K89" s="109" t="n"/>
-      <c r="L89" s="109" t="n"/>
-      <c r="M89" s="109" t="n"/>
-      <c r="N89" s="109" t="n"/>
-      <c r="O89" s="109" t="n"/>
+      <c r="B89" s="61" t="n"/>
+      <c r="C89" s="61" t="n"/>
+      <c r="D89" s="61" t="n"/>
+      <c r="E89" s="61" t="n"/>
+      <c r="F89" s="61" t="n"/>
+      <c r="G89" s="61" t="n"/>
+      <c r="H89" s="61" t="n"/>
+      <c r="I89" s="61" t="n"/>
+      <c r="J89" s="61" t="n"/>
+      <c r="K89" s="61" t="n"/>
+      <c r="L89" s="61" t="n"/>
+      <c r="M89" s="61" t="n"/>
+      <c r="N89" s="61" t="n"/>
+      <c r="O89" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -346,7 +346,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -521,11 +521,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -847,6 +851,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1175,7 +1182,7 @@
     <row r="3" ht="14.4" customHeight="1" s="65">
       <c r="A3" s="28" t="inlineStr">
         <is>
-          <t>Current milestone: Phase 6 -- P6-S35-S42/S47/S48 (this branch's hardening fixes) complete; inventory now cites live Swiggy Instamart prices end-to-end, replan loop + critic converge to approved on first pass. Next: P6-MI01-04 (market intel expansion) or P6-S43-S46 (follow-ups).</t>
+          <t>Current milestone: Phase 6 -- P6-S21-S30 (this branch's hardening fixes) complete; inventory now cites live Swiggy Instamart prices end-to-end, replan loop + critic converge to approved on first pass. Next: P6-MI01-04 (market intel expansion) or P6-S38-S41 (follow-ups).</t>
         </is>
       </c>
       <c r="B3" s="18" t="inlineStr">
@@ -1211,12 +1218,12 @@
     <row r="4" ht="14.4" customHeight="1" s="65">
       <c r="A4" s="29" t="inlineStr">
         <is>
-          <t>Last completed: P6-S48 -- Windows console-encoding crash fix (was silently 500ing every planning run)</t>
+          <t>Last completed: P6-S30 -- Windows console-encoding crash fix (was silently 500ing every planning run)</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>P6-S42 rewritten to reflect the real bug found (inventory price-ordering + guardrail discarding the Swiggy citation, not the originally-planned occupancy-context gap); P6-S47 resolved (AGENTS.md injected line removed per user decision). All live-verified end to end, including a Playwright check that the Swiggy price citation renders correctly in the actual /runs UI.</t>
+          <t>P6-S28 rewritten to reflect the real bug found (inventory price-ordering + guardrail discarding the Swiggy citation, not the originally-planned occupancy-context gap); P6-S29 resolved (AGENTS.md injected line removed per user decision). All live-verified end to end, including a Playwright check that the Swiggy price citation renders correctly in the actual /runs UI.</t>
         </is>
       </c>
       <c r="C4" s="1" t="n"/>
@@ -1288,7 +1295,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Pending from Swiggy. Needed ONLY for checkout + book_table (P6-S30, P6-S31). Everything else works with production OAuth token.</t>
+          <t>Pending from Swiggy. Needed ONLY for checkout + book_table (P6-S42, P6-S43). Everything else works with production OAuth token.</t>
         </is>
       </c>
       <c r="C6" s="1" t="n"/>
@@ -8181,7 +8188,7 @@
     <row r="1" ht="36" customHeight="1" s="65">
       <c r="A1" s="80" t="inlineStr">
         <is>
-          <t>CortexKitchen — Phase Tracker (P0 through P6-S06 complete)</t>
+          <t>CortexKitchen — Phase Tracker (P0 through P6-S11 complete)</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12814,7 @@
       </c>
       <c r="C69" s="38" t="inlineStr">
         <is>
-          <t>P6-00</t>
+          <t>P6-S01</t>
         </is>
       </c>
       <c r="D69" s="38" t="inlineStr">
@@ -12880,7 +12887,7 @@
       </c>
       <c r="C70" s="50" t="inlineStr">
         <is>
-          <t>P6-00b</t>
+          <t>P6-S02</t>
         </is>
       </c>
       <c r="D70" s="50" t="inlineStr">
@@ -12932,7 +12939,7 @@
       </c>
       <c r="O70" s="50" t="inlineStr">
         <is>
-          <t>P6-00</t>
+          <t>P6-S01</t>
         </is>
       </c>
       <c r="P70" s="50" t="inlineStr">
@@ -12959,7 +12966,7 @@
       </c>
       <c r="C71" s="38" t="inlineStr">
         <is>
-          <t>P6-00c</t>
+          <t>P6-S03</t>
         </is>
       </c>
       <c r="D71" s="38" t="inlineStr">
@@ -13017,7 +13024,7 @@
       </c>
       <c r="O71" s="38" t="inlineStr">
         <is>
-          <t>P6-00b</t>
+          <t>P6-S02</t>
         </is>
       </c>
       <c r="P71" s="38" t="inlineStr">
@@ -13042,7 +13049,7 @@
       </c>
       <c r="C72" s="38" t="inlineStr">
         <is>
-          <t>P6-S01</t>
+          <t>P6-S04</t>
         </is>
       </c>
       <c r="D72" s="38" t="inlineStr">
@@ -13100,7 +13107,7 @@
       </c>
       <c r="O72" s="38" t="inlineStr">
         <is>
-          <t>P6-00c</t>
+          <t>P6-S03</t>
         </is>
       </c>
       <c r="P72" s="38" t="inlineStr">
@@ -13125,7 +13132,7 @@
       </c>
       <c r="C73" s="38" t="inlineStr">
         <is>
-          <t>P6-S02</t>
+          <t>P6-S05</t>
         </is>
       </c>
       <c r="D73" s="38" t="inlineStr">
@@ -13183,7 +13190,7 @@
       </c>
       <c r="O73" s="38" t="inlineStr">
         <is>
-          <t>P6-S01</t>
+          <t>P6-S04</t>
         </is>
       </c>
       <c r="P73" s="38" t="inlineStr">
@@ -13208,7 +13215,7 @@
       </c>
       <c r="C74" s="38" t="inlineStr">
         <is>
-          <t>P6-S03</t>
+          <t>P6-S06</t>
         </is>
       </c>
       <c r="D74" s="38" t="inlineStr">
@@ -13266,7 +13273,7 @@
       </c>
       <c r="O74" s="38" t="inlineStr">
         <is>
-          <t>P6-S02</t>
+          <t>P6-S05</t>
         </is>
       </c>
       <c r="P74" s="38" t="inlineStr">
@@ -13291,7 +13298,7 @@
       </c>
       <c r="C75" s="38" t="inlineStr">
         <is>
-          <t>P6-S04</t>
+          <t>P6-S09</t>
         </is>
       </c>
       <c r="D75" s="38" t="inlineStr">
@@ -13345,7 +13352,7 @@
       </c>
       <c r="O75" s="38" t="inlineStr">
         <is>
-          <t>P6-S03</t>
+          <t>P6-S06</t>
         </is>
       </c>
       <c r="P75" s="38" t="inlineStr">
@@ -13482,7 +13489,7 @@
     <row r="2" ht="60" customHeight="1" s="65">
       <c r="A2" s="91" t="inlineStr">
         <is>
-          <t>P6-00</t>
+          <t>P6-S01</t>
         </is>
       </c>
       <c r="B2" s="92" t="inlineStr">
@@ -13570,7 +13577,7 @@
     <row r="4" ht="60" customHeight="1" s="65">
       <c r="A4" s="91" t="inlineStr">
         <is>
-          <t>P6-00b</t>
+          <t>P6-S02</t>
         </is>
       </c>
       <c r="B4" s="92" t="inlineStr">
@@ -13629,7 +13636,7 @@
       </c>
       <c r="N4" s="93" t="inlineStr">
         <is>
-          <t>P6-00</t>
+          <t>P6-S01</t>
         </is>
       </c>
       <c r="O4" s="94" t="inlineStr">
@@ -13658,7 +13665,7 @@
     <row r="6" ht="60" customHeight="1" s="65">
       <c r="A6" s="91" t="inlineStr">
         <is>
-          <t>P6-00c</t>
+          <t>P6-S03</t>
         </is>
       </c>
       <c r="B6" s="92" t="inlineStr">
@@ -13717,7 +13724,7 @@
       </c>
       <c r="N6" s="93" t="inlineStr">
         <is>
-          <t>P6-00b</t>
+          <t>P6-S02</t>
         </is>
       </c>
       <c r="O6" s="94" t="inlineStr">
@@ -13746,7 +13753,7 @@
     <row r="8" ht="86" customHeight="1" s="65">
       <c r="A8" s="91" t="inlineStr">
         <is>
-          <t>P6-S01</t>
+          <t>P6-S04</t>
         </is>
       </c>
       <c r="B8" s="92" t="inlineStr">
@@ -13805,7 +13812,7 @@
       </c>
       <c r="N8" s="93" t="inlineStr">
         <is>
-          <t>P6-00c</t>
+          <t>P6-S03</t>
         </is>
       </c>
       <c r="O8" s="94" t="inlineStr">
@@ -13817,7 +13824,7 @@
     <row r="9" ht="73" customHeight="1" s="65">
       <c r="A9" s="91" t="inlineStr">
         <is>
-          <t>P6-S02</t>
+          <t>P6-S05</t>
         </is>
       </c>
       <c r="B9" s="113" t="n"/>
@@ -13872,7 +13879,7 @@
       </c>
       <c r="N9" s="102" t="inlineStr">
         <is>
-          <t>P6-S01</t>
+          <t>P6-S04</t>
         </is>
       </c>
       <c r="O9" s="103" t="inlineStr">
@@ -13901,7 +13908,7 @@
     <row r="11" ht="99" customHeight="1" s="65">
       <c r="A11" s="91" t="inlineStr">
         <is>
-          <t>P6-S03</t>
+          <t>P6-S06</t>
         </is>
       </c>
       <c r="B11" s="101" t="inlineStr">
@@ -13931,7 +13938,7 @@
       </c>
       <c r="G11" s="103" t="inlineStr">
         <is>
-          <t>docs/SWIGGY_INTEGRATION.md (P6-S03 ✅, status header updated)</t>
+          <t>docs/SWIGGY_INTEGRATION.md (P6-S06 ✅, status header updated)</t>
         </is>
       </c>
       <c r="H11" s="95" t="inlineStr">
@@ -13960,7 +13967,7 @@
       </c>
       <c r="N11" s="102" t="inlineStr">
         <is>
-          <t>P6-S02</t>
+          <t>P6-S05</t>
         </is>
       </c>
       <c r="O11" s="103" t="inlineStr">
@@ -13989,7 +13996,7 @@
     <row r="13" ht="73" customHeight="1" s="65">
       <c r="A13" s="91" t="inlineStr">
         <is>
-          <t>P6-S03b</t>
+          <t>P6-S07</t>
         </is>
       </c>
       <c r="B13" s="101" t="inlineStr">
@@ -14048,7 +14055,7 @@
       </c>
       <c r="N13" s="102" t="inlineStr">
         <is>
-          <t>P6-S01</t>
+          <t>P6-S04</t>
         </is>
       </c>
       <c r="O13" s="103" t="inlineStr">
@@ -14060,7 +14067,7 @@
     <row r="14" ht="99" customHeight="1" s="65">
       <c r="A14" s="91" t="inlineStr">
         <is>
-          <t>P6-S03c</t>
+          <t>P6-S08</t>
         </is>
       </c>
       <c r="B14" s="113" t="n"/>
@@ -14115,7 +14122,7 @@
       </c>
       <c r="N14" s="93" t="inlineStr">
         <is>
-          <t>P6-S02</t>
+          <t>P6-S05</t>
         </is>
       </c>
       <c r="O14" s="94" t="inlineStr">
@@ -14144,7 +14151,7 @@
     <row r="16" ht="190" customHeight="1" s="65">
       <c r="A16" s="91" t="inlineStr">
         <is>
-          <t>P6-S04</t>
+          <t>P6-S09</t>
         </is>
       </c>
       <c r="B16" s="92" t="inlineStr">
@@ -14203,7 +14210,7 @@
       </c>
       <c r="N16" s="93" t="inlineStr">
         <is>
-          <t>P6-S03</t>
+          <t>P6-S06</t>
         </is>
       </c>
       <c r="O16" s="94" t="inlineStr">
@@ -14232,7 +14239,7 @@
     <row r="18" ht="60" customHeight="1" s="65">
       <c r="A18" s="91" t="inlineStr">
         <is>
-          <t>P6-S05</t>
+          <t>P6-S10</t>
         </is>
       </c>
       <c r="B18" s="92" t="inlineStr">
@@ -14257,7 +14264,7 @@
       </c>
       <c r="F18" s="94" t="inlineStr">
         <is>
-          <t>feat: reservation sync skeleton — get_booking_status → reservations table, register_booking_order_id for DineoutExecutor (P6-S31)</t>
+          <t>feat: reservation sync skeleton — get_booking_status → reservations table, register_booking_order_id for DineoutExecutor (P6-S43)</t>
         </is>
       </c>
       <c r="G18" s="94" t="inlineStr">
@@ -14291,7 +14298,7 @@
       </c>
       <c r="N18" s="93" t="inlineStr">
         <is>
-          <t>P6-S04</t>
+          <t>P6-S09</t>
         </is>
       </c>
       <c r="O18" s="94" t="inlineStr">
@@ -14303,7 +14310,7 @@
     <row r="19" ht="60" customHeight="1" s="65">
       <c r="A19" s="91" t="inlineStr">
         <is>
-          <t>P6-S06</t>
+          <t>P6-S11</t>
         </is>
       </c>
       <c r="B19" s="113" t="n"/>
@@ -14324,7 +14331,7 @@
       </c>
       <c r="F19" s="103" t="inlineStr">
         <is>
-          <t>feat(P6-S05/S06): fix Swiggy client response format + live sync endpoint + feedback sync + reservation sync skeleton</t>
+          <t>feat(P6-S10/S06): fix Swiggy client response format + live sync endpoint + feedback sync + reservation sync skeleton</t>
         </is>
       </c>
       <c r="G19" s="103" t="inlineStr">
@@ -14358,7 +14365,7 @@
       </c>
       <c r="N19" s="102" t="inlineStr">
         <is>
-          <t>P6-S03</t>
+          <t>P6-S06</t>
         </is>
       </c>
       <c r="O19" s="103" t="inlineStr">
@@ -14387,7 +14394,7 @@
     <row r="21" ht="99" customHeight="1" s="65">
       <c r="A21" s="91" t="inlineStr">
         <is>
-          <t>P6-S07</t>
+          <t>P6-S12</t>
         </is>
       </c>
       <c r="B21" s="101" t="inlineStr">
@@ -14446,7 +14453,7 @@
       </c>
       <c r="N21" s="102" t="inlineStr">
         <is>
-          <t>P6-S05</t>
+          <t>P6-S10</t>
         </is>
       </c>
       <c r="O21" s="103" t="inlineStr">
@@ -14458,7 +14465,7 @@
     <row r="22" ht="86" customHeight="1" s="65">
       <c r="A22" s="91" t="inlineStr">
         <is>
-          <t>P6-S08</t>
+          <t>P6-S13</t>
         </is>
       </c>
       <c r="B22" s="114" t="n"/>
@@ -14511,7 +14518,7 @@
       </c>
       <c r="N22" s="93" t="inlineStr">
         <is>
-          <t>P6-S07</t>
+          <t>P6-S12</t>
         </is>
       </c>
       <c r="O22" s="94" t="inlineStr">
@@ -14523,7 +14530,7 @@
     <row r="23" ht="99" customHeight="1" s="65">
       <c r="A23" s="91" t="inlineStr">
         <is>
-          <t>P6-S09</t>
+          <t>P6-S14</t>
         </is>
       </c>
       <c r="B23" s="113" t="n"/>
@@ -14539,7 +14546,7 @@
       </c>
       <c r="E23" s="103" t="inlineStr">
         <is>
-          <t>Create enrichers/procurement.py. search_products (per shortage item, max 5 calls/run) + your_go_to_items (frequent reorders). Output: [{ingredient, spinId, price, unit, inStock}]. spinId MUST persist in OrchestratorState — required for Instamart checkout in P6-S30. Redis cache 30 min. Returns None on any failure; inventory node falls back to its own analysis.</t>
+          <t>Create enrichers/procurement.py. search_products (per shortage item, max 5 calls/run) + your_go_to_items (frequent reorders). Output: [{ingredient, spinId, price, unit, inStock}]. spinId MUST persist in OrchestratorState — required for Instamart checkout in P6-S42. Redis cache 30 min. Returns None on any failure; inventory node falls back to its own analysis.</t>
         </is>
       </c>
       <c r="F23" s="103" t="inlineStr">
@@ -14549,7 +14556,7 @@
       </c>
       <c r="G23" s="103" t="inlineStr">
         <is>
-          <t>docs/SWIGGY_INTEGRATION.md (P6-S09 section)</t>
+          <t>docs/SWIGGY_INTEGRATION.md (P6-S14 section)</t>
         </is>
       </c>
       <c r="H23" s="95" t="inlineStr">
@@ -14576,7 +14583,7 @@
       </c>
       <c r="N23" s="102" t="inlineStr">
         <is>
-          <t>P6-S08</t>
+          <t>P6-S13</t>
         </is>
       </c>
       <c r="O23" s="103" t="inlineStr">
@@ -14605,7 +14612,7 @@
     <row r="25" ht="73" customHeight="1" s="65">
       <c r="A25" s="91" t="inlineStr">
         <is>
-          <t>P6-S10</t>
+          <t>P6-S15</t>
         </is>
       </c>
       <c r="B25" s="101" t="inlineStr">
@@ -14664,7 +14671,7 @@
       </c>
       <c r="N25" s="102" t="inlineStr">
         <is>
-          <t>P6-S07, P6-S08, P6-S09</t>
+          <t>P6-S12, P6-S13, P6-S14</t>
         </is>
       </c>
       <c r="O25" s="103" t="inlineStr">
@@ -14676,7 +14683,7 @@
     <row r="26" ht="73" customHeight="1" s="65">
       <c r="A26" s="91" t="inlineStr">
         <is>
-          <t>P6-S11</t>
+          <t>P6-S16</t>
         </is>
       </c>
       <c r="B26" s="114" t="n"/>
@@ -14731,7 +14738,7 @@
       </c>
       <c r="N26" s="93" t="inlineStr">
         <is>
-          <t>P6-S10</t>
+          <t>P6-S15</t>
         </is>
       </c>
       <c r="O26" s="94" t="inlineStr">
@@ -14743,7 +14750,7 @@
     <row r="27" ht="99" customHeight="1" s="65">
       <c r="A27" s="91" t="inlineStr">
         <is>
-          <t>P6-S12</t>
+          <t>P6-S17</t>
         </is>
       </c>
       <c r="B27" s="114" t="n"/>
@@ -14798,7 +14805,7 @@
       </c>
       <c r="N27" s="102" t="inlineStr">
         <is>
-          <t>P6-S10</t>
+          <t>P6-S15</t>
         </is>
       </c>
       <c r="O27" s="103" t="inlineStr">
@@ -14810,7 +14817,7 @@
     <row r="28" ht="60" customHeight="1" s="65">
       <c r="A28" s="91" t="inlineStr">
         <is>
-          <t>P6-S13</t>
+          <t>P6-S18</t>
         </is>
       </c>
       <c r="B28" s="113" t="n"/>
@@ -14826,7 +14833,7 @@
       </c>
       <c r="E28" s="94" t="inlineStr">
         <is>
-          <t>Diff 5: market_intel assumed_competitor_avg_price vs menu_intel items_assumed_available pricing. Diff 6: dineout_manager assumed_dineout_slots_low vs reservation assumed_peak_occupancy. Extends P6-00b. Total now 5 active diffs.</t>
+          <t>Diff 5: market_intel assumed_competitor_avg_price vs menu_intel items_assumed_available pricing. Diff 6: dineout_manager assumed_dineout_slots_low vs reservation assumed_peak_occupancy. Extends P6-S02. Total now 5 active diffs.</t>
         </is>
       </c>
       <c r="F28" s="94" t="inlineStr">
@@ -14865,7 +14872,7 @@
       </c>
       <c r="N28" s="93" t="inlineStr">
         <is>
-          <t>P6-S11, P6-S12</t>
+          <t>P6-S16, P6-S17</t>
         </is>
       </c>
       <c r="O28" s="94" t="inlineStr">
@@ -14894,7 +14901,7 @@
     <row r="30" ht="112" customHeight="1" s="65">
       <c r="A30" s="91" t="inlineStr">
         <is>
-          <t>P6-S13c</t>
+          <t>P6-S19</t>
         </is>
       </c>
       <c r="B30" s="92" t="inlineStr">
@@ -14914,7 +14921,7 @@
       </c>
       <c r="E30" s="94" t="inlineStr">
         <is>
-          <t>Add 3 Groq function-calling tools to the existing agentic chatbot (P6-S04). search_menu(query, addressId): answers questions like 'what is the avg biryani price near me?' get_food_orders(addressId): answers 'what were my top Swiggy items last week?' search_products(query, addressId): answers 'what does cream cost on Instamart right now?' Makes the chatbot genuinely Swiggy-aware — very demo-friendly for the Swiggy team.</t>
+          <t>Add 3 Groq function-calling tools to the existing agentic chatbot (P6-S09). search_menu(query, addressId): answers questions like 'what is the avg biryani price near me?' get_food_orders(addressId): answers 'what were my top Swiggy items last week?' search_products(query, addressId): answers 'what does cream cost on Instamart right now?' Makes the chatbot genuinely Swiggy-aware — very demo-friendly for the Swiggy team.</t>
         </is>
       </c>
       <c r="F30" s="94" t="inlineStr">
@@ -14953,7 +14960,7 @@
       </c>
       <c r="N30" s="93" t="inlineStr">
         <is>
-          <t>P6-S04, P6-S01</t>
+          <t>P6-S09, P6-S04</t>
         </is>
       </c>
       <c r="O30" s="94" t="inlineStr">
@@ -14982,7 +14989,7 @@
     <row r="32" ht="73" customHeight="1" s="65">
       <c r="A32" s="91" t="inlineStr">
         <is>
-          <t>P6-F14</t>
+          <t>P6-F01</t>
         </is>
       </c>
       <c r="B32" s="92" t="inlineStr">
@@ -15041,19 +15048,19 @@
       </c>
       <c r="N32" s="93" t="inlineStr">
         <is>
-          <t>P6-S01</t>
+          <t>P6-S04</t>
         </is>
       </c>
       <c r="O32" s="94" t="inlineStr">
         <is>
-          <t>Can build now — reads from connectors table (already exists via P6-S02)</t>
+          <t>Can build now — reads from connectors table (already exists via P6-S05)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1" s="65">
       <c r="A33" s="91" t="inlineStr">
         <is>
-          <t>P6-F15</t>
+          <t>P6-F02</t>
         </is>
       </c>
       <c r="B33" s="114" t="n"/>
@@ -15108,7 +15115,7 @@
       </c>
       <c r="N33" s="102" t="inlineStr">
         <is>
-          <t>P6-S01</t>
+          <t>P6-S04</t>
         </is>
       </c>
       <c r="O33" s="103" t="inlineStr">
@@ -15120,7 +15127,7 @@
     <row r="34" ht="138" customHeight="1" s="65">
       <c r="A34" s="91" t="inlineStr">
         <is>
-          <t>P6-F16</t>
+          <t>P6-F03</t>
         </is>
       </c>
       <c r="B34" s="114" t="n"/>
@@ -15169,7 +15176,7 @@
     <row r="35" ht="151" customHeight="1" s="65">
       <c r="A35" s="91" t="inlineStr">
         <is>
-          <t>P6-F16b</t>
+          <t>P6-F04</t>
         </is>
       </c>
       <c r="B35" s="114" t="n"/>
@@ -15185,7 +15192,7 @@
       </c>
       <c r="E35" s="103" t="inlineStr">
         <is>
-          <t>Swiggy MCP confirmed 100% consumer-facing from Builders Club docs. Added FUTURE USE / CONSUMER DATA ONLY comments to: swiggy_connector.py, sync/order_sync.py, feedback_sync.py, reservation_sync.py, orchestration/nodes/dineout_manager.py (corrected docstring re book_table), orchestration/state.py (swiggy_delivery_signal), graph.py (stream message). CLAUDE.md: product vision corrected, pipeline notes, sync layer notes, Workflow 1 + 2 corrected, build steps updated. Tracker: P6-S03/S05/S06 notes updated, P6-S12/S31 re-evaluated, 4 MI tasks added for honest Swiggy feature scope.</t>
+          <t>Swiggy MCP confirmed 100% consumer-facing from Builders Club docs. Added FUTURE USE / CONSUMER DATA ONLY comments to: swiggy_connector.py, sync/order_sync.py, feedback_sync.py, reservation_sync.py, orchestration/nodes/dineout_manager.py (corrected docstring re book_table), orchestration/state.py (swiggy_delivery_signal), graph.py (stream message). CLAUDE.md: product vision corrected, pipeline notes, sync layer notes, Workflow 1 + 2 corrected, build steps updated. Tracker: P6-S06/S05/S06 notes updated, P6-S17/S31 re-evaluated, 4 MI tasks added for honest Swiggy feature scope.</t>
         </is>
       </c>
       <c r="F35" s="103" t="inlineStr">
@@ -15218,7 +15225,7 @@
     <row r="36" ht="73" customHeight="1" s="65">
       <c r="A36" s="91" t="inlineStr">
         <is>
-          <t>P6-F17</t>
+          <t>P6-F05</t>
         </is>
       </c>
       <c r="B36" s="113" t="n"/>
@@ -15273,12 +15280,12 @@
       </c>
       <c r="N36" s="93" t="inlineStr">
         <is>
-          <t>P6-S10</t>
+          <t>P6-S15</t>
         </is>
       </c>
       <c r="O36" s="94" t="inlineStr">
         <is>
-          <t>Depends on P6-S11 (market_intel_output in plan API response)</t>
+          <t>Depends on P6-S16 (market_intel_output in plan API response)</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15309,7 @@
     <row r="38" ht="138" customHeight="1" s="65">
       <c r="A38" s="91" t="inlineStr">
         <is>
-          <t>P6-S14</t>
+          <t>P6-S20</t>
         </is>
       </c>
       <c r="B38" s="92" t="inlineStr">
@@ -15372,7 +15379,7 @@
     <row r="40" ht="216" customHeight="1" s="65">
       <c r="A40" s="91" t="inlineStr">
         <is>
-          <t>P6-S35</t>
+          <t>P6-S21</t>
         </is>
       </c>
       <c r="B40" s="92" t="inlineStr">
@@ -15431,7 +15438,7 @@
       </c>
       <c r="N40" s="93" t="inlineStr">
         <is>
-          <t>P6-S14</t>
+          <t>P6-S20</t>
         </is>
       </c>
       <c r="O40" s="94" t="inlineStr">
@@ -15443,7 +15450,7 @@
     <row r="41" ht="138" customHeight="1" s="65">
       <c r="A41" s="91" t="inlineStr">
         <is>
-          <t>P6-S36</t>
+          <t>P6-S22</t>
         </is>
       </c>
       <c r="B41" s="114" t="n"/>
@@ -15498,7 +15505,7 @@
       </c>
       <c r="N41" s="102" t="inlineStr">
         <is>
-          <t>P6-S35</t>
+          <t>P6-S21</t>
         </is>
       </c>
       <c r="O41" s="103" t="inlineStr">
@@ -15510,7 +15517,7 @@
     <row r="42" ht="203" customHeight="1" s="65">
       <c r="A42" s="91" t="inlineStr">
         <is>
-          <t>P6-S37</t>
+          <t>P6-S23</t>
         </is>
       </c>
       <c r="B42" s="114" t="n"/>
@@ -15565,7 +15572,7 @@
       </c>
       <c r="N42" s="93" t="inlineStr">
         <is>
-          <t>P6-S35</t>
+          <t>P6-S21</t>
         </is>
       </c>
       <c r="O42" s="94" t="inlineStr">
@@ -15577,7 +15584,7 @@
     <row r="43" ht="151" customHeight="1" s="65">
       <c r="A43" s="91" t="inlineStr">
         <is>
-          <t>P6-S38</t>
+          <t>P6-S24</t>
         </is>
       </c>
       <c r="B43" s="114" t="n"/>
@@ -15632,7 +15639,7 @@
       </c>
       <c r="N43" s="102" t="inlineStr">
         <is>
-          <t>P6-S35</t>
+          <t>P6-S21</t>
         </is>
       </c>
       <c r="O43" s="103" t="inlineStr">
@@ -15644,7 +15651,7 @@
     <row r="44" ht="151" customHeight="1" s="65">
       <c r="A44" s="91" t="inlineStr">
         <is>
-          <t>P6-S39</t>
+          <t>P6-S25</t>
         </is>
       </c>
       <c r="B44" s="114" t="n"/>
@@ -15699,7 +15706,7 @@
       </c>
       <c r="N44" s="93" t="inlineStr">
         <is>
-          <t>P6-S04</t>
+          <t>P6-S09</t>
         </is>
       </c>
       <c r="O44" s="94" t="inlineStr">
@@ -15711,7 +15718,7 @@
     <row r="45" ht="216" customHeight="1" s="65">
       <c r="A45" s="91" t="inlineStr">
         <is>
-          <t>P6-S40</t>
+          <t>P6-S26</t>
         </is>
       </c>
       <c r="B45" s="114" t="n"/>
@@ -15766,7 +15773,7 @@
       </c>
       <c r="N45" s="102" t="inlineStr">
         <is>
-          <t>P6-S39</t>
+          <t>P6-S25</t>
         </is>
       </c>
       <c r="O45" s="103" t="inlineStr">
@@ -15778,7 +15785,7 @@
     <row r="46" ht="190" customHeight="1" s="65">
       <c r="A46" s="91" t="inlineStr">
         <is>
-          <t>P6-S41</t>
+          <t>P6-S27</t>
         </is>
       </c>
       <c r="B46" s="114" t="n"/>
@@ -15794,7 +15801,7 @@
       </c>
       <c r="E46" s="94" t="inlineStr">
         <is>
-          <t>critic_service.py unconditionally force-downgraded approved-&gt;revision (capped score at 0.72) whenever any stale cross-agent assumption existed, regardless of the LLM critic's own judgment. A live run showed the critic explicitly reasoning through a conflict and writing 'Approving with these items noted for the manager's attention' in its own notes, then getting silently overridden to revision anyway by this code (added in an earlier hardening pass adjacent to P6-00b). Removed the automatic verdict override specifically for assumption diffs, kept it for real deterministic policy/sanity-rule violations which should stay non-negotiable. Kept full visibility (feedback, notes, DecisionLog audit trail) -- the critic's own considered judgment is now trusted.</t>
+          <t>critic_service.py unconditionally force-downgraded approved-&gt;revision (capped score at 0.72) whenever any stale cross-agent assumption existed, regardless of the LLM critic's own judgment. A live run showed the critic explicitly reasoning through a conflict and writing 'Approving with these items noted for the manager's attention' in its own notes, then getting silently overridden to revision anyway by this code (added in an earlier hardening pass adjacent to P6-S02). Removed the automatic verdict override specifically for assumption diffs, kept it for real deterministic policy/sanity-rule violations which should stay non-negotiable. Kept full visibility (feedback, notes, DecisionLog audit trail) -- the critic's own considered judgment is now trusted.</t>
         </is>
       </c>
       <c r="F46" s="94" t="inlineStr">
@@ -15833,7 +15840,7 @@
       </c>
       <c r="N46" s="93" t="inlineStr">
         <is>
-          <t>P6-S40</t>
+          <t>P6-S26</t>
         </is>
       </c>
       <c r="O46" s="94" t="inlineStr">
@@ -15845,7 +15852,7 @@
     <row r="47" ht="294" customHeight="1" s="65">
       <c r="A47" s="91" t="inlineStr">
         <is>
-          <t>P6-S42</t>
+          <t>P6-S28</t>
         </is>
       </c>
       <c r="B47" s="114" t="n"/>
@@ -15900,7 +15907,7 @@
       </c>
       <c r="N47" s="102" t="inlineStr">
         <is>
-          <t>P6-S40</t>
+          <t>P6-S26</t>
         </is>
       </c>
       <c r="O47" s="103" t="inlineStr">
@@ -15912,7 +15919,7 @@
     <row r="48" ht="138" customHeight="1" s="65">
       <c r="A48" s="91" t="inlineStr">
         <is>
-          <t>P6-S47</t>
+          <t>P6-S29</t>
         </is>
       </c>
       <c r="B48" s="114" t="n"/>
@@ -15971,7 +15978,7 @@
     <row r="49" ht="138" customHeight="1" s="65">
       <c r="A49" s="91" t="inlineStr">
         <is>
-          <t>P6-S48</t>
+          <t>P6-S30</t>
         </is>
       </c>
       <c r="B49" s="113" t="n"/>
@@ -16026,7 +16033,7 @@
       </c>
       <c r="N49" s="102" t="inlineStr">
         <is>
-          <t>P6-S35</t>
+          <t>P6-S21</t>
         </is>
       </c>
       <c r="O49" s="103" t="inlineStr">
@@ -16053,7 +16060,7 @@
       <c r="O50" s="99" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1" s="65">
-      <c r="A51" s="109" t="inlineStr">
+      <c r="A51" s="115" t="inlineStr">
         <is>
           <t>DO FIRST — no staging creds needed  |  each task: own branch → PR → merge dev → merge main → docs + screenshots + tracker updated</t>
         </is>
@@ -16331,7 +16338,7 @@
     <row r="59" ht="73" customHeight="1" s="65">
       <c r="A59" s="110" t="inlineStr">
         <is>
-          <t>P6-S16</t>
+          <t>P6-S31</t>
         </is>
       </c>
       <c r="B59" s="101" t="inlineStr">
@@ -16390,7 +16397,7 @@
       </c>
       <c r="N59" s="102" t="inlineStr">
         <is>
-          <t>P6-S10</t>
+          <t>P6-S15</t>
         </is>
       </c>
       <c r="O59" s="103" t="inlineStr">
@@ -16419,7 +16426,7 @@
     <row r="61" ht="73" customHeight="1" s="65">
       <c r="A61" s="110" t="inlineStr">
         <is>
-          <t>P6-S18</t>
+          <t>P6-S32</t>
         </is>
       </c>
       <c r="B61" s="101" t="n"/>
@@ -16474,7 +16481,7 @@
       </c>
       <c r="N61" s="102" t="inlineStr">
         <is>
-          <t>P6-F17</t>
+          <t>P6-F05</t>
         </is>
       </c>
       <c r="O61" s="103" t="inlineStr">
@@ -16503,7 +16510,7 @@
     <row r="63" ht="73" customHeight="1" s="65">
       <c r="A63" s="110" t="inlineStr">
         <is>
-          <t>P6-S19</t>
+          <t>P6-S33</t>
         </is>
       </c>
       <c r="B63" s="101" t="n"/>
@@ -16558,7 +16565,7 @@
       </c>
       <c r="N63" s="102" t="inlineStr">
         <is>
-          <t>P6-S18</t>
+          <t>P6-S32</t>
         </is>
       </c>
       <c r="O63" s="103" t="inlineStr">
@@ -16587,7 +16594,7 @@
     <row r="65" ht="86" customHeight="1" s="65">
       <c r="A65" s="110" t="inlineStr">
         <is>
-          <t>P6-S21</t>
+          <t>P6-S34</t>
         </is>
       </c>
       <c r="B65" s="101" t="inlineStr">
@@ -16646,7 +16653,7 @@
       </c>
       <c r="N65" s="102" t="inlineStr">
         <is>
-          <t>P6-S20</t>
+          <t>P6-S20-UNRESOLVED</t>
         </is>
       </c>
       <c r="O65" s="103" t="inlineStr">
@@ -16675,7 +16682,7 @@
     <row r="67" ht="99" customHeight="1" s="65">
       <c r="A67" s="110" t="inlineStr">
         <is>
-          <t>P6-S23</t>
+          <t>P6-S35</t>
         </is>
       </c>
       <c r="B67" s="101" t="n"/>
@@ -16730,7 +16737,7 @@
       </c>
       <c r="N67" s="102" t="inlineStr">
         <is>
-          <t>P6-S22, P6-S30</t>
+          <t>P6-S22-UNRESOLVED, P6-S42</t>
         </is>
       </c>
       <c r="O67" s="103" t="inlineStr">
@@ -16759,7 +16766,7 @@
     <row r="69" ht="73" customHeight="1" s="65">
       <c r="A69" s="110" t="inlineStr">
         <is>
-          <t>P6-S24</t>
+          <t>P6-S36</t>
         </is>
       </c>
       <c r="B69" s="101" t="n"/>
@@ -16814,7 +16821,7 @@
       </c>
       <c r="N69" s="102" t="inlineStr">
         <is>
-          <t>P6-S16</t>
+          <t>P6-S31</t>
         </is>
       </c>
       <c r="O69" s="103" t="inlineStr">
@@ -16843,7 +16850,7 @@
     <row r="71" ht="86" customHeight="1" s="65">
       <c r="A71" s="110" t="inlineStr">
         <is>
-          <t>P6-S25</t>
+          <t>P6-S37</t>
         </is>
       </c>
       <c r="B71" s="101" t="inlineStr">
@@ -16902,7 +16909,7 @@
       </c>
       <c r="N71" s="102" t="inlineStr">
         <is>
-          <t>P6-S21</t>
+          <t>P6-S34</t>
         </is>
       </c>
       <c r="O71" s="103" t="inlineStr">
@@ -16931,7 +16938,7 @@
     <row r="73" ht="73" customHeight="1" s="65">
       <c r="A73" s="110" t="inlineStr">
         <is>
-          <t>P6-R26</t>
+          <t>P6-R01</t>
         </is>
       </c>
       <c r="B73" s="101" t="inlineStr">
@@ -16990,7 +16997,7 @@
       </c>
       <c r="N73" s="102" t="inlineStr">
         <is>
-          <t>P6-S31</t>
+          <t>P6-S43</t>
         </is>
       </c>
       <c r="O73" s="103" t="inlineStr">
@@ -17019,7 +17026,7 @@
     <row r="75" ht="73" customHeight="1" s="65">
       <c r="A75" s="110" t="inlineStr">
         <is>
-          <t>P6-F27</t>
+          <t>P6-F06</t>
         </is>
       </c>
       <c r="B75" s="101" t="inlineStr">
@@ -17078,12 +17085,12 @@
       </c>
       <c r="N75" s="102" t="inlineStr">
         <is>
-          <t>P6-S13</t>
+          <t>P6-S18</t>
         </is>
       </c>
       <c r="O75" s="103" t="inlineStr">
         <is>
-          <t>Depends on P6-S16 (action_queue in plan API response)</t>
+          <t>Depends on P6-S31 (action_queue in plan API response)</t>
         </is>
       </c>
     </row>
@@ -17107,7 +17114,7 @@
     <row r="77" ht="60" customHeight="1" s="65">
       <c r="A77" s="110" t="inlineStr">
         <is>
-          <t>P6-F28</t>
+          <t>P6-F07</t>
         </is>
       </c>
       <c r="B77" s="101" t="n"/>
@@ -17162,12 +17169,12 @@
       </c>
       <c r="N77" s="102" t="inlineStr">
         <is>
-          <t>P6-S31</t>
+          <t>P6-S43</t>
         </is>
       </c>
       <c r="O77" s="103" t="inlineStr">
         <is>
-          <t>Depends on P6-S22 (BriefingService)</t>
+          <t>Depends on P6-S22-UNRESOLVED (BriefingService)</t>
         </is>
       </c>
     </row>
@@ -17191,7 +17198,7 @@
     <row r="79" ht="99" customHeight="1" s="65">
       <c r="A79" s="110" t="inlineStr">
         <is>
-          <t>P6-F29</t>
+          <t>P6-F08</t>
         </is>
       </c>
       <c r="B79" s="101" t="n"/>
@@ -17207,7 +17214,7 @@
       </c>
       <c r="E79" s="103" t="inlineStr">
         <is>
-          <t>New route /live. Kitchen display-grade SSE feed from LiveMonitorService (P6-S23). Shows active Swiggy delivery orders with ETA countdown, Instamart procurement status with delivery ETA, alert banner on delivery spike or ingredient arrival. Swiggy logo + 'Live via Swiggy MCP' badge. Page shows inactive state outside service hours (12-14h, 19-22h IST).</t>
+          <t>New route /live. Kitchen display-grade SSE feed from LiveMonitorService (P6-S35). Shows active Swiggy delivery orders with ETA countdown, Instamart procurement status with delivery ETA, alert banner on delivery spike or ingredient arrival. Swiggy logo + 'Live via Swiggy MCP' badge. Page shows inactive state outside service hours (12-14h, 19-22h IST).</t>
         </is>
       </c>
       <c r="F79" s="103" t="inlineStr">
@@ -17246,7 +17253,7 @@
       </c>
       <c r="N79" s="102" t="inlineStr">
         <is>
-          <t>P6-S23</t>
+          <t>P6-S35</t>
         </is>
       </c>
       <c r="O79" s="103" t="inlineStr">
@@ -17275,7 +17282,7 @@
     <row r="81" ht="125" customHeight="1" s="65">
       <c r="A81" s="110" t="inlineStr">
         <is>
-          <t>P6-S43</t>
+          <t>P6-S38</t>
         </is>
       </c>
       <c r="B81" s="101" t="n"/>
@@ -17326,7 +17333,7 @@
       </c>
       <c r="N81" s="102" t="inlineStr">
         <is>
-          <t>P6-S37</t>
+          <t>P6-S23</t>
         </is>
       </c>
       <c r="O81" s="103" t="n"/>
@@ -17351,7 +17358,7 @@
     <row r="83" ht="112" customHeight="1" s="65">
       <c r="A83" s="110" t="inlineStr">
         <is>
-          <t>P6-S44</t>
+          <t>P6-S39</t>
         </is>
       </c>
       <c r="B83" s="101" t="n"/>
@@ -17402,7 +17409,7 @@
       </c>
       <c r="N83" s="102" t="inlineStr">
         <is>
-          <t>P6-S37</t>
+          <t>P6-S23</t>
         </is>
       </c>
       <c r="O83" s="103" t="n"/>
@@ -17427,7 +17434,7 @@
     <row r="85" ht="99" customHeight="1" s="65">
       <c r="A85" s="110" t="inlineStr">
         <is>
-          <t>P6-S45</t>
+          <t>P6-S40</t>
         </is>
       </c>
       <c r="B85" s="101" t="n"/>
@@ -17478,7 +17485,7 @@
       </c>
       <c r="N85" s="102" t="inlineStr">
         <is>
-          <t>P6-S37</t>
+          <t>P6-S23</t>
         </is>
       </c>
       <c r="O85" s="103" t="n"/>
@@ -17503,7 +17510,7 @@
     <row r="87" ht="151" customHeight="1" s="65">
       <c r="A87" s="110" t="inlineStr">
         <is>
-          <t>P6-S46</t>
+          <t>P6-S41</t>
         </is>
       </c>
       <c r="B87" s="101" t="n"/>
@@ -17573,7 +17580,7 @@
       <c r="O88" s="99" t="n"/>
     </row>
     <row r="89" ht="28" customHeight="1" s="65">
-      <c r="A89" s="109" t="inlineStr">
+      <c r="A89" s="115" t="inlineStr">
         <is>
           <t>→ DEMO 1  |  all above on main, docs updated, screenshots done — record full Swiggy read + AI + voice + live monitor demo ←</t>
         </is>
@@ -17716,7 +17723,7 @@
     <row r="4">
       <c r="A4" s="85" t="inlineStr">
         <is>
-          <t>P6-S30</t>
+          <t>P6-S42</t>
         </is>
       </c>
       <c r="B4" s="85" t="inlineStr">
@@ -17736,7 +17743,7 @@
       </c>
       <c r="E4" s="85" t="inlineStr">
         <is>
-          <t>Create executor/procurement.py. Flow: get_cart -&gt; clear_cart -&gt; update_cart([{spinId, qty}]) -&gt; get_cart (verify bill) -&gt; LangGraph interrupt() for owner approval -&gt; checkout (COD, Rs.999 cap). NON-IDEMPOTENT: on any 5xx from checkout, call get_orders before retrying — never blind-retry. Stores confirmed order in procurement_orders table. spinIds sourced from ProcurementEnricher state (P6-S09).</t>
+          <t>Create executor/procurement.py. Flow: get_cart -&gt; clear_cart -&gt; update_cart([{spinId, qty}]) -&gt; get_cart (verify bill) -&gt; LangGraph interrupt() for owner approval -&gt; checkout (COD, Rs.999 cap). NON-IDEMPOTENT: on any 5xx from checkout, call get_orders before retrying — never blind-retry. Stores confirmed order in procurement_orders table. spinIds sourced from ProcurementEnricher state (P6-S14).</t>
         </is>
       </c>
       <c r="F4" s="85" t="inlineStr">
@@ -17746,7 +17753,7 @@
       </c>
       <c r="G4" s="85" t="inlineStr">
         <is>
-          <t>docs/SWIGGY_INTEGRATION.md (P6-S30 executor section)</t>
+          <t>docs/SWIGGY_INTEGRATION.md (P6-S42 executor section)</t>
         </is>
       </c>
       <c r="H4" s="85" t="inlineStr">
@@ -17775,7 +17782,7 @@
       </c>
       <c r="N4" s="85" t="inlineStr">
         <is>
-          <t>P6-S16, P6-S09</t>
+          <t>P6-S31, P6-S14</t>
         </is>
       </c>
       <c r="O4" s="85" t="inlineStr">
@@ -17787,7 +17794,7 @@
     <row r="6">
       <c r="A6" s="85" t="inlineStr">
         <is>
-          <t>P6-S31</t>
+          <t>P6-S43</t>
         </is>
       </c>
       <c r="B6" s="85" t="inlineStr">
@@ -17846,7 +17853,7 @@
       </c>
       <c r="N6" s="85" t="inlineStr">
         <is>
-          <t>P6-S16</t>
+          <t>P6-S31</t>
         </is>
       </c>
       <c r="O6" s="85" t="inlineStr">
@@ -17858,7 +17865,7 @@
     <row r="8">
       <c r="A8" s="85" t="inlineStr">
         <is>
-          <t>P6-S32</t>
+          <t>P6-S44</t>
         </is>
       </c>
       <c r="B8" s="85" t="inlineStr">
@@ -17917,7 +17924,7 @@
       </c>
       <c r="N8" s="85" t="inlineStr">
         <is>
-          <t>P6-S25</t>
+          <t>P6-S37</t>
         </is>
       </c>
       <c r="O8" s="85" t="inlineStr">
@@ -17936,7 +17943,7 @@
     <row r="12">
       <c r="A12" s="85" t="inlineStr">
         <is>
-          <t>P6-S33</t>
+          <t>P6-S45</t>
         </is>
       </c>
       <c r="B12" s="61" t="n"/>
@@ -17987,7 +17994,7 @@
       </c>
       <c r="N12" s="85" t="inlineStr">
         <is>
-          <t>P6-R26</t>
+          <t>P6-R01</t>
         </is>
       </c>
       <c r="O12" s="85" t="inlineStr">
@@ -17999,7 +18006,7 @@
     <row r="14">
       <c r="A14" s="85" t="inlineStr">
         <is>
-          <t>P6-S34</t>
+          <t>P6-S46</t>
         </is>
       </c>
       <c r="B14" s="61" t="n"/>
@@ -18076,7 +18083,7 @@
     <row r="20">
       <c r="A20" s="85" t="inlineStr">
         <is>
-          <t>P6-D35</t>
+          <t>P6-D01</t>
         </is>
       </c>
       <c r="B20" s="61" t="n"/>
@@ -18131,7 +18138,7 @@
       </c>
       <c r="N20" s="85" t="inlineStr">
         <is>
-          <t>P6-F15</t>
+          <t>P6-F02</t>
         </is>
       </c>
       <c r="O20" s="85" t="inlineStr">
@@ -18143,7 +18150,7 @@
     <row r="22">
       <c r="A22" s="85" t="inlineStr">
         <is>
-          <t>P6-D36</t>
+          <t>P6-D02</t>
         </is>
       </c>
       <c r="B22" s="61" t="n"/>
@@ -18198,7 +18205,7 @@
       </c>
       <c r="N22" s="85" t="inlineStr">
         <is>
-          <t>P6-D35</t>
+          <t>P6-D01</t>
         </is>
       </c>
       <c r="O22" s="85" t="inlineStr">
@@ -18210,7 +18217,7 @@
     <row r="24">
       <c r="A24" s="85" t="inlineStr">
         <is>
-          <t>P6-D37</t>
+          <t>P6-D03</t>
         </is>
       </c>
       <c r="B24" s="61" t="n"/>
@@ -18265,7 +18272,7 @@
       </c>
       <c r="N24" s="85" t="inlineStr">
         <is>
-          <t>P6-D36</t>
+          <t>P6-D02</t>
         </is>
       </c>
       <c r="O24" s="85" t="inlineStr">
@@ -18343,7 +18350,7 @@
       </c>
       <c r="N28" s="85" t="inlineStr">
         <is>
-          <t>P6-D37</t>
+          <t>P6-D03</t>
         </is>
       </c>
       <c r="O28" s="85" t="inlineStr">
@@ -18705,7 +18712,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>P6-S01 — NEW</t>
+          <t>P6-S04 — NEW</t>
         </is>
       </c>
       <c r="D3" s="25" t="inlineStr">
@@ -18727,12 +18734,12 @@
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>P6-D35 — updated P6-S01/S02/S03</t>
+          <t>P6-D01 — updated P6-S04/S02/S03</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Updated (P6-S03 status ✅)</t>
+          <t>Updated (P6-S06 status ✅)</t>
         </is>
       </c>
     </row>
@@ -18749,7 +18756,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>P6-S13 — NEW</t>
+          <t>P6-S18 — NEW</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
@@ -18771,7 +18778,7 @@
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>P6-S03 — NEW</t>
+          <t>P6-S06 — NEW</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
@@ -18793,7 +18800,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>P6-S31 — NEW</t>
+          <t>P6-S43 — NEW</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
@@ -18815,12 +18822,12 @@
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>P6-S01, P6-S10, P6-S13, P6-S31</t>
+          <t>P6-S04, P6-S15, P6-S18, P6-S43</t>
         </is>
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>Updated (P6-S01/S02 done)</t>
+          <t>Updated (P6-S04/S02 done)</t>
         </is>
       </c>
     </row>
@@ -18837,7 +18844,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>P6-S10, P6-S11, P6-S12</t>
+          <t>P6-S15, P6-S16, P6-S17</t>
         </is>
       </c>
       <c r="D9" s="26" t="inlineStr">
@@ -18881,12 +18888,12 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>P6-S02, P6-S13, P6-S31</t>
+          <t>P6-S05, P6-S18, P6-S43</t>
         </is>
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
-          <t>Updated (P6-S02 done)</t>
+          <t>Updated (P6-S05 done)</t>
         </is>
       </c>
     </row>
@@ -18903,12 +18910,12 @@
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>P6-S01, P6-S03, P6-S13, P6-S31</t>
+          <t>P6-S04, P6-S06, P6-S18, P6-S43</t>
         </is>
       </c>
       <c r="D12" s="26" t="inlineStr">
         <is>
-          <t>Updated (D-019 added P6-S01)</t>
+          <t>Updated (D-019 added P6-S04)</t>
         </is>
       </c>
     </row>
@@ -18925,7 +18932,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>P6-S01, P6-D37</t>
+          <t>P6-S04, P6-D03</t>
         </is>
       </c>
       <c r="D13" s="26" t="inlineStr">
@@ -18947,7 +18954,7 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>P6-S10, P6-S11</t>
+          <t>P6-S15, P6-S16</t>
         </is>
       </c>
       <c r="D14" s="26" t="inlineStr">
@@ -18969,7 +18976,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>P6-D37</t>
+          <t>P6-D03</t>
         </is>
       </c>
       <c r="D15" s="26" t="inlineStr">
@@ -18991,12 +18998,12 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>P6-S01</t>
+          <t>P6-S04</t>
         </is>
       </c>
       <c r="D16" s="26" t="inlineStr">
         <is>
-          <t>Created (P6-S01 done)</t>
+          <t>Created (P6-S04 done)</t>
         </is>
       </c>
     </row>
@@ -19165,7 +19172,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Phase 6 on dev (P6-S01/S02 merged). main has P5 + P6-00 series. Next main sync: end of Phase 6.</t>
+          <t>Phase 6 on dev (P6-S04/S02 merged). main has P5 + P6-S01 series. Next main sync: end of Phase 6.</t>
         </is>
       </c>
       <c r="E4" s="1" t="n"/>
@@ -19209,7 +19216,7 @@
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>Current base — P6-S04 (feature/agent-intelligence) IN PROGRESS; P6-S05/S06 blocked on Swiggy token</t>
+          <t>Current base — P6-S09 (feature/agent-intelligence) IN PROGRESS; P6-S10/S06 blocked on Swiggy token</t>
         </is>
       </c>
       <c r="E5" s="1" t="n"/>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -20,10 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -458,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -640,6 +639,7 @@
     <xf numFmtId="0" fontId="24" fillId="28" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -651,11 +651,13 @@
     <xf numFmtId="0" fontId="15" fillId="25" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -673,20 +675,11 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -981,7 +974,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="72">
-      <c r="A1" s="83" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>CortexKitchen — Project Dashboard</t>
         </is>
@@ -1019,7 +1012,7 @@
     <row r="3" ht="14.4" customHeight="1" s="72">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Current milestone: Phase 6 -- P6-S21-S30 (this branch's hardening fixes) complete; inventory now cites live Swiggy Instamart prices end-to-end, replan loop + critic converge to approved on first pass. Next: P6-MI01-04 (market intel expansion) or P6-S38-S41 (follow-ups).</t>
+          <t>Current milestone: Phase 6 -- P6-S21-S30 (this branch's hardening fixes) complete; inventory now cites live Swiggy Instamart prices end-to-end, replan loop + critic converge to approved on first pass. Next: P6-MI01-04 (market intel expansion) or P6-S39-S41 (follow-ups).</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -1132,7 +1125,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Pending from Swiggy. Needed ONLY for checkout + book_table (P6-S42, P6-S43). Everything else works with production OAuth token.</t>
+          <t>Pending from Swiggy. Needed ONLY for checkout + book_table (P6-S43, P6-S44). Everything else works with production OAuth token.</t>
         </is>
       </c>
       <c r="C6" s="1" t="n"/>
@@ -8023,34 +8016,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="72">
-      <c r="A1" s="84" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>CortexKitchen — Phase Tracker (P0 through P6-S11 complete)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16.05" customHeight="1" s="72">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="79" t="inlineStr">
         <is>
           <t>Phase 6 planned tasks (P6-01 onwards) live in the Phase 6 sheet  ·  This sheet = historical record only</t>
         </is>
       </c>
-      <c r="B2" s="74" t="n"/>
-      <c r="C2" s="74" t="n"/>
-      <c r="D2" s="74" t="n"/>
-      <c r="E2" s="74" t="n"/>
-      <c r="F2" s="74" t="n"/>
-      <c r="G2" s="74" t="n"/>
-      <c r="H2" s="74" t="n"/>
-      <c r="I2" s="74" t="n"/>
-      <c r="J2" s="74" t="n"/>
-      <c r="K2" s="74" t="n"/>
-      <c r="L2" s="74" t="n"/>
-      <c r="M2" s="74" t="n"/>
-      <c r="N2" s="74" t="n"/>
-      <c r="O2" s="74" t="n"/>
-      <c r="P2" s="74" t="n"/>
-      <c r="Q2" s="75" t="n"/>
+      <c r="B2" s="75" t="n"/>
+      <c r="C2" s="75" t="n"/>
+      <c r="D2" s="75" t="n"/>
+      <c r="E2" s="75" t="n"/>
+      <c r="F2" s="75" t="n"/>
+      <c r="G2" s="75" t="n"/>
+      <c r="H2" s="75" t="n"/>
+      <c r="I2" s="75" t="n"/>
+      <c r="J2" s="75" t="n"/>
+      <c r="K2" s="75" t="n"/>
+      <c r="L2" s="75" t="n"/>
+      <c r="M2" s="75" t="n"/>
+      <c r="N2" s="75" t="n"/>
+      <c r="O2" s="75" t="n"/>
+      <c r="P2" s="75" t="n"/>
+      <c r="Q2" s="76" t="n"/>
     </row>
     <row r="3" ht="19.95" customHeight="1" s="72">
       <c r="A3" s="5" t="inlineStr">
@@ -8140,27 +8133,27 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" s="72">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="78" t="inlineStr">
         <is>
           <t>Phase 0</t>
         </is>
       </c>
-      <c r="B4" s="74" t="n"/>
-      <c r="C4" s="74" t="n"/>
-      <c r="D4" s="74" t="n"/>
-      <c r="E4" s="74" t="n"/>
-      <c r="F4" s="74" t="n"/>
-      <c r="G4" s="74" t="n"/>
-      <c r="H4" s="74" t="n"/>
-      <c r="I4" s="74" t="n"/>
-      <c r="J4" s="74" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="74" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="74" t="n"/>
-      <c r="O4" s="74" t="n"/>
-      <c r="P4" s="74" t="n"/>
-      <c r="Q4" s="75" t="n"/>
+      <c r="B4" s="75" t="n"/>
+      <c r="C4" s="75" t="n"/>
+      <c r="D4" s="75" t="n"/>
+      <c r="E4" s="75" t="n"/>
+      <c r="F4" s="75" t="n"/>
+      <c r="G4" s="75" t="n"/>
+      <c r="H4" s="75" t="n"/>
+      <c r="I4" s="75" t="n"/>
+      <c r="J4" s="75" t="n"/>
+      <c r="K4" s="75" t="n"/>
+      <c r="L4" s="75" t="n"/>
+      <c r="M4" s="75" t="n"/>
+      <c r="N4" s="75" t="n"/>
+      <c r="O4" s="75" t="n"/>
+      <c r="P4" s="75" t="n"/>
+      <c r="Q4" s="76" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1" s="72">
       <c r="A5" s="19" t="inlineStr">
@@ -8548,27 +8541,27 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="72">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="A10" s="78" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B10" s="74" t="n"/>
-      <c r="C10" s="74" t="n"/>
-      <c r="D10" s="74" t="n"/>
-      <c r="E10" s="74" t="n"/>
-      <c r="F10" s="74" t="n"/>
-      <c r="G10" s="74" t="n"/>
-      <c r="H10" s="74" t="n"/>
-      <c r="I10" s="74" t="n"/>
-      <c r="J10" s="74" t="n"/>
-      <c r="K10" s="74" t="n"/>
-      <c r="L10" s="74" t="n"/>
-      <c r="M10" s="74" t="n"/>
-      <c r="N10" s="74" t="n"/>
-      <c r="O10" s="74" t="n"/>
-      <c r="P10" s="74" t="n"/>
-      <c r="Q10" s="75" t="n"/>
+      <c r="B10" s="75" t="n"/>
+      <c r="C10" s="75" t="n"/>
+      <c r="D10" s="75" t="n"/>
+      <c r="E10" s="75" t="n"/>
+      <c r="F10" s="75" t="n"/>
+      <c r="G10" s="75" t="n"/>
+      <c r="H10" s="75" t="n"/>
+      <c r="I10" s="75" t="n"/>
+      <c r="J10" s="75" t="n"/>
+      <c r="K10" s="75" t="n"/>
+      <c r="L10" s="75" t="n"/>
+      <c r="M10" s="75" t="n"/>
+      <c r="N10" s="75" t="n"/>
+      <c r="O10" s="75" t="n"/>
+      <c r="P10" s="75" t="n"/>
+      <c r="Q10" s="76" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1" s="72">
       <c r="A11" s="24" t="inlineStr">
@@ -9501,27 +9494,27 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="72">
-      <c r="A23" s="76" t="inlineStr">
+      <c r="A23" s="77" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="B23" s="74" t="n"/>
-      <c r="C23" s="74" t="n"/>
-      <c r="D23" s="74" t="n"/>
-      <c r="E23" s="74" t="n"/>
-      <c r="F23" s="74" t="n"/>
-      <c r="G23" s="74" t="n"/>
-      <c r="H23" s="74" t="n"/>
-      <c r="I23" s="74" t="n"/>
-      <c r="J23" s="74" t="n"/>
-      <c r="K23" s="74" t="n"/>
-      <c r="L23" s="74" t="n"/>
-      <c r="M23" s="74" t="n"/>
-      <c r="N23" s="74" t="n"/>
-      <c r="O23" s="74" t="n"/>
-      <c r="P23" s="74" t="n"/>
-      <c r="Q23" s="75" t="n"/>
+      <c r="B23" s="75" t="n"/>
+      <c r="C23" s="75" t="n"/>
+      <c r="D23" s="75" t="n"/>
+      <c r="E23" s="75" t="n"/>
+      <c r="F23" s="75" t="n"/>
+      <c r="G23" s="75" t="n"/>
+      <c r="H23" s="75" t="n"/>
+      <c r="I23" s="75" t="n"/>
+      <c r="J23" s="75" t="n"/>
+      <c r="K23" s="75" t="n"/>
+      <c r="L23" s="75" t="n"/>
+      <c r="M23" s="75" t="n"/>
+      <c r="N23" s="75" t="n"/>
+      <c r="O23" s="75" t="n"/>
+      <c r="P23" s="75" t="n"/>
+      <c r="Q23" s="76" t="n"/>
     </row>
     <row r="24" ht="48" customHeight="1" s="72">
       <c r="A24" s="24" t="inlineStr">
@@ -9986,27 +9979,27 @@
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="72">
-      <c r="A30" s="76" t="inlineStr">
+      <c r="A30" s="77" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="B30" s="74" t="n"/>
-      <c r="C30" s="74" t="n"/>
-      <c r="D30" s="74" t="n"/>
-      <c r="E30" s="74" t="n"/>
-      <c r="F30" s="74" t="n"/>
-      <c r="G30" s="74" t="n"/>
-      <c r="H30" s="74" t="n"/>
-      <c r="I30" s="74" t="n"/>
-      <c r="J30" s="74" t="n"/>
-      <c r="K30" s="74" t="n"/>
-      <c r="L30" s="74" t="n"/>
-      <c r="M30" s="74" t="n"/>
-      <c r="N30" s="74" t="n"/>
-      <c r="O30" s="74" t="n"/>
-      <c r="P30" s="74" t="n"/>
-      <c r="Q30" s="75" t="n"/>
+      <c r="B30" s="75" t="n"/>
+      <c r="C30" s="75" t="n"/>
+      <c r="D30" s="75" t="n"/>
+      <c r="E30" s="75" t="n"/>
+      <c r="F30" s="75" t="n"/>
+      <c r="G30" s="75" t="n"/>
+      <c r="H30" s="75" t="n"/>
+      <c r="I30" s="75" t="n"/>
+      <c r="J30" s="75" t="n"/>
+      <c r="K30" s="75" t="n"/>
+      <c r="L30" s="75" t="n"/>
+      <c r="M30" s="75" t="n"/>
+      <c r="N30" s="75" t="n"/>
+      <c r="O30" s="75" t="n"/>
+      <c r="P30" s="75" t="n"/>
+      <c r="Q30" s="76" t="n"/>
     </row>
     <row r="31" ht="48" customHeight="1" s="72">
       <c r="A31" s="24" t="inlineStr">
@@ -10394,27 +10387,27 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="72">
-      <c r="A36" s="81" t="inlineStr">
+      <c r="A36" s="82" t="inlineStr">
         <is>
           <t>Demo prep</t>
         </is>
       </c>
-      <c r="B36" s="74" t="n"/>
-      <c r="C36" s="74" t="n"/>
-      <c r="D36" s="74" t="n"/>
-      <c r="E36" s="74" t="n"/>
-      <c r="F36" s="74" t="n"/>
-      <c r="G36" s="74" t="n"/>
-      <c r="H36" s="74" t="n"/>
-      <c r="I36" s="74" t="n"/>
-      <c r="J36" s="74" t="n"/>
-      <c r="K36" s="74" t="n"/>
-      <c r="L36" s="74" t="n"/>
-      <c r="M36" s="74" t="n"/>
-      <c r="N36" s="74" t="n"/>
-      <c r="O36" s="74" t="n"/>
-      <c r="P36" s="74" t="n"/>
-      <c r="Q36" s="75" t="n"/>
+      <c r="B36" s="75" t="n"/>
+      <c r="C36" s="75" t="n"/>
+      <c r="D36" s="75" t="n"/>
+      <c r="E36" s="75" t="n"/>
+      <c r="F36" s="75" t="n"/>
+      <c r="G36" s="75" t="n"/>
+      <c r="H36" s="75" t="n"/>
+      <c r="I36" s="75" t="n"/>
+      <c r="J36" s="75" t="n"/>
+      <c r="K36" s="75" t="n"/>
+      <c r="L36" s="75" t="n"/>
+      <c r="M36" s="75" t="n"/>
+      <c r="N36" s="75" t="n"/>
+      <c r="O36" s="75" t="n"/>
+      <c r="P36" s="75" t="n"/>
+      <c r="Q36" s="76" t="n"/>
     </row>
     <row r="37" ht="48" customHeight="1" s="72">
       <c r="A37" s="32" t="inlineStr">
@@ -10648,27 +10641,27 @@
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="72">
-      <c r="A40" s="73" t="inlineStr">
+      <c r="A40" s="74" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="B40" s="74" t="n"/>
-      <c r="C40" s="74" t="n"/>
-      <c r="D40" s="74" t="n"/>
-      <c r="E40" s="74" t="n"/>
-      <c r="F40" s="74" t="n"/>
-      <c r="G40" s="74" t="n"/>
-      <c r="H40" s="74" t="n"/>
-      <c r="I40" s="74" t="n"/>
-      <c r="J40" s="74" t="n"/>
-      <c r="K40" s="74" t="n"/>
-      <c r="L40" s="74" t="n"/>
-      <c r="M40" s="74" t="n"/>
-      <c r="N40" s="74" t="n"/>
-      <c r="O40" s="74" t="n"/>
-      <c r="P40" s="74" t="n"/>
-      <c r="Q40" s="75" t="n"/>
+      <c r="B40" s="75" t="n"/>
+      <c r="C40" s="75" t="n"/>
+      <c r="D40" s="75" t="n"/>
+      <c r="E40" s="75" t="n"/>
+      <c r="F40" s="75" t="n"/>
+      <c r="G40" s="75" t="n"/>
+      <c r="H40" s="75" t="n"/>
+      <c r="I40" s="75" t="n"/>
+      <c r="J40" s="75" t="n"/>
+      <c r="K40" s="75" t="n"/>
+      <c r="L40" s="75" t="n"/>
+      <c r="M40" s="75" t="n"/>
+      <c r="N40" s="75" t="n"/>
+      <c r="O40" s="75" t="n"/>
+      <c r="P40" s="75" t="n"/>
+      <c r="Q40" s="76" t="n"/>
     </row>
     <row r="41" ht="48" customHeight="1" s="72">
       <c r="A41" s="24" t="inlineStr">
@@ -11672,27 +11665,27 @@
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="72">
-      <c r="A54" s="73" t="inlineStr">
+      <c r="A54" s="74" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B54" s="74" t="n"/>
-      <c r="C54" s="74" t="n"/>
-      <c r="D54" s="74" t="n"/>
-      <c r="E54" s="74" t="n"/>
-      <c r="F54" s="74" t="n"/>
-      <c r="G54" s="74" t="n"/>
-      <c r="H54" s="74" t="n"/>
-      <c r="I54" s="74" t="n"/>
-      <c r="J54" s="74" t="n"/>
-      <c r="K54" s="74" t="n"/>
-      <c r="L54" s="74" t="n"/>
-      <c r="M54" s="74" t="n"/>
-      <c r="N54" s="74" t="n"/>
-      <c r="O54" s="74" t="n"/>
-      <c r="P54" s="74" t="n"/>
-      <c r="Q54" s="75" t="n"/>
+      <c r="B54" s="75" t="n"/>
+      <c r="C54" s="75" t="n"/>
+      <c r="D54" s="75" t="n"/>
+      <c r="E54" s="75" t="n"/>
+      <c r="F54" s="75" t="n"/>
+      <c r="G54" s="75" t="n"/>
+      <c r="H54" s="75" t="n"/>
+      <c r="I54" s="75" t="n"/>
+      <c r="J54" s="75" t="n"/>
+      <c r="K54" s="75" t="n"/>
+      <c r="L54" s="75" t="n"/>
+      <c r="M54" s="75" t="n"/>
+      <c r="N54" s="75" t="n"/>
+      <c r="O54" s="75" t="n"/>
+      <c r="P54" s="75" t="n"/>
+      <c r="Q54" s="76" t="n"/>
     </row>
     <row r="55" ht="48" customHeight="1" s="72">
       <c r="A55" s="19" t="inlineStr">
@@ -12618,27 +12611,27 @@
       </c>
     </row>
     <row r="68" ht="18" customHeight="1" s="72">
-      <c r="A68" s="79" t="inlineStr">
+      <c r="A68" s="80" t="inlineStr">
         <is>
           <t>Phase 6</t>
         </is>
       </c>
-      <c r="B68" s="74" t="n"/>
-      <c r="C68" s="74" t="n"/>
-      <c r="D68" s="74" t="n"/>
-      <c r="E68" s="74" t="n"/>
-      <c r="F68" s="74" t="n"/>
-      <c r="G68" s="74" t="n"/>
-      <c r="H68" s="74" t="n"/>
-      <c r="I68" s="74" t="n"/>
-      <c r="J68" s="74" t="n"/>
-      <c r="K68" s="74" t="n"/>
-      <c r="L68" s="74" t="n"/>
-      <c r="M68" s="74" t="n"/>
-      <c r="N68" s="74" t="n"/>
-      <c r="O68" s="74" t="n"/>
-      <c r="P68" s="74" t="n"/>
-      <c r="Q68" s="75" t="n"/>
+      <c r="B68" s="75" t="n"/>
+      <c r="C68" s="75" t="n"/>
+      <c r="D68" s="75" t="n"/>
+      <c r="E68" s="75" t="n"/>
+      <c r="F68" s="75" t="n"/>
+      <c r="G68" s="75" t="n"/>
+      <c r="H68" s="75" t="n"/>
+      <c r="I68" s="75" t="n"/>
+      <c r="J68" s="75" t="n"/>
+      <c r="K68" s="75" t="n"/>
+      <c r="L68" s="75" t="n"/>
+      <c r="M68" s="75" t="n"/>
+      <c r="N68" s="75" t="n"/>
+      <c r="O68" s="75" t="n"/>
+      <c r="P68" s="75" t="n"/>
+      <c r="Q68" s="76" t="n"/>
     </row>
     <row r="69" ht="48" customHeight="1" s="72">
       <c r="A69" s="24" t="inlineStr">
@@ -13229,22 +13222,23 @@
   <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col width="12" customWidth="1" style="40" min="1" max="1"/>
-    <col width="27" customWidth="1" style="40" min="2" max="2"/>
-    <col width="15" customWidth="1" style="40" min="3" max="3"/>
-    <col width="32" customWidth="1" style="40" min="4" max="4"/>
-    <col width="58" customWidth="1" style="40" min="5" max="5"/>
-    <col width="40" customWidth="1" style="40" min="6" max="6"/>
-    <col width="30" customWidth="1" style="40" min="7" max="7"/>
-    <col width="13" customWidth="1" style="40" min="8" max="8"/>
-    <col width="11" customWidth="1" style="40" min="9" max="9"/>
+    <col width="12" customWidth="1" style="71" min="1" max="1"/>
+    <col width="27" customWidth="1" style="71" min="2" max="2"/>
+    <col width="15" customWidth="1" style="71" min="3" max="3"/>
+    <col width="32" customWidth="1" style="71" min="4" max="4"/>
+    <col width="58" customWidth="1" style="71" min="5" max="5"/>
+    <col width="40" customWidth="1" style="71" min="6" max="6"/>
+    <col width="30" customWidth="1" style="71" min="7" max="7"/>
+    <col width="13" customWidth="1" style="71" min="8" max="8"/>
+    <col width="11" customWidth="1" style="71" min="9" max="9"/>
     <col width="10" customWidth="1" style="72" min="10" max="10"/>
-    <col width="12" customWidth="1" style="40" min="11" max="11"/>
+    <col width="12" customWidth="1" style="71" min="11" max="11"/>
     <col width="12" customWidth="1" style="72" min="12" max="12"/>
     <col width="9" customWidth="1" style="72" min="13" max="13"/>
     <col width="16" customWidth="1" style="72" min="14" max="14"/>
     <col width="46" customWidth="1" style="72" min="15" max="15"/>
-    <col width="12" customWidth="1" style="40" min="16" max="16384"/>
+    <col width="12" customWidth="1" style="71" min="16" max="16"/>
+    <col width="12" customWidth="1" style="71" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.95" customHeight="1" s="72">
@@ -13330,7 +13324,7 @@
           <t>P6-S01</t>
         </is>
       </c>
-      <c r="B2" s="65" t="inlineStr">
+      <c r="B2" s="66" t="inlineStr">
         <is>
           <t>feature/per-node-model-routing</t>
         </is>
@@ -13418,7 +13412,7 @@
           <t>P6-S02</t>
         </is>
       </c>
-      <c r="B4" s="65" t="inlineStr">
+      <c r="B4" s="66" t="inlineStr">
         <is>
           <t>feature/assumption-diffing</t>
         </is>
@@ -13506,7 +13500,7 @@
           <t>P6-S03</t>
         </is>
       </c>
-      <c r="B6" s="65" t="inlineStr">
+      <c r="B6" s="66" t="inlineStr">
         <is>
           <t>feature/drop-diff1-reseed-data</t>
         </is>
@@ -13594,7 +13588,7 @@
           <t>P6-S04</t>
         </is>
       </c>
-      <c r="B8" s="65" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
         <is>
           <t>feature/swiggy-base-connector</t>
         </is>
@@ -13665,7 +13659,7 @@
           <t>P6-S05</t>
         </is>
       </c>
-      <c r="B9" s="67" t="n"/>
+      <c r="B9" s="68" t="n"/>
       <c r="C9" s="55" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -13749,7 +13743,7 @@
           <t>P6-S06</t>
         </is>
       </c>
-      <c r="B11" s="68" t="inlineStr">
+      <c r="B11" s="69" t="inlineStr">
         <is>
           <t>feature/swiggy-sync-orders</t>
         </is>
@@ -13837,7 +13831,7 @@
           <t>P6-S07</t>
         </is>
       </c>
-      <c r="B13" s="68" t="inlineStr">
+      <c r="B13" s="69" t="inlineStr">
         <is>
           <t>feature/swiggy-base-connector</t>
         </is>
@@ -13908,7 +13902,7 @@
           <t>P6-S08</t>
         </is>
       </c>
-      <c r="B14" s="67" t="n"/>
+      <c r="B14" s="68" t="n"/>
       <c r="C14" s="46" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -13992,7 +13986,7 @@
           <t>P6-S09</t>
         </is>
       </c>
-      <c r="B16" s="65" t="inlineStr">
+      <c r="B16" s="66" t="inlineStr">
         <is>
           <t>feature/agent-intelligence</t>
         </is>
@@ -14080,7 +14074,7 @@
           <t>P6-S10</t>
         </is>
       </c>
-      <c r="B18" s="65" t="inlineStr">
+      <c r="B18" s="66" t="inlineStr">
         <is>
           <t>feature/swiggy-sync-feedback-reservations</t>
         </is>
@@ -14102,7 +14096,7 @@
       </c>
       <c r="F18" s="47" t="inlineStr">
         <is>
-          <t>feat: reservation sync skeleton — get_booking_status → reservations table, register_booking_order_id for DineoutExecutor (P6-S43)</t>
+          <t>feat: reservation sync skeleton — get_booking_status → reservations table, register_booking_order_id for DineoutExecutor (P6-S44)</t>
         </is>
       </c>
       <c r="G18" s="47" t="inlineStr">
@@ -14151,7 +14145,7 @@
           <t>P6-S11</t>
         </is>
       </c>
-      <c r="B19" s="67" t="n"/>
+      <c r="B19" s="68" t="n"/>
       <c r="C19" s="55" t="inlineStr">
         <is>
           <t>Integrations</t>
@@ -14235,7 +14229,7 @@
           <t>P6-S12</t>
         </is>
       </c>
-      <c r="B21" s="68" t="inlineStr">
+      <c r="B21" s="69" t="inlineStr">
         <is>
           <t>feature/swiggy-market-intel-enrichers</t>
         </is>
@@ -14306,7 +14300,7 @@
           <t>P6-S13</t>
         </is>
       </c>
-      <c r="B22" s="66" t="n"/>
+      <c r="B22" s="67" t="n"/>
       <c r="C22" s="46" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14371,7 +14365,7 @@
           <t>P6-S14</t>
         </is>
       </c>
-      <c r="B23" s="67" t="n"/>
+      <c r="B23" s="68" t="n"/>
       <c r="C23" s="55" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14384,7 +14378,7 @@
       </c>
       <c r="E23" s="56" t="inlineStr">
         <is>
-          <t>Create enrichers/procurement.py. search_products (per shortage item, max 5 calls/run) + your_go_to_items (frequent reorders). Output: [{ingredient, spinId, price, unit, inStock}]. spinId MUST persist in OrchestratorState — required for Instamart checkout in P6-S42. Redis cache 30 min. Returns None on any failure; inventory node falls back to its own analysis.</t>
+          <t>Create enrichers/procurement.py. search_products (per shortage item, max 5 calls/run) + your_go_to_items (frequent reorders). Output: [{ingredient, spinId, price, unit, inStock}]. spinId MUST persist in OrchestratorState — required for Instamart checkout in P6-S43. Redis cache 30 min. Returns None on any failure; inventory node falls back to its own analysis.</t>
         </is>
       </c>
       <c r="F23" s="56" t="inlineStr">
@@ -14453,7 +14447,7 @@
           <t>P6-S15</t>
         </is>
       </c>
-      <c r="B25" s="68" t="inlineStr">
+      <c r="B25" s="69" t="inlineStr">
         <is>
           <t>feature/swiggy-market-intel-node</t>
         </is>
@@ -14524,7 +14518,7 @@
           <t>P6-S16</t>
         </is>
       </c>
-      <c r="B26" s="66" t="n"/>
+      <c r="B26" s="67" t="n"/>
       <c r="C26" s="46" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14591,7 +14585,7 @@
           <t>P6-S17</t>
         </is>
       </c>
-      <c r="B27" s="66" t="n"/>
+      <c r="B27" s="67" t="n"/>
       <c r="C27" s="55" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14658,7 +14652,7 @@
           <t>P6-S18</t>
         </is>
       </c>
-      <c r="B28" s="67" t="n"/>
+      <c r="B28" s="68" t="n"/>
       <c r="C28" s="46" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14742,7 +14736,7 @@
           <t>P6-S19</t>
         </is>
       </c>
-      <c r="B30" s="65" t="inlineStr">
+      <c r="B30" s="66" t="inlineStr">
         <is>
           <t>feature/swiggy-chatbot-tools</t>
         </is>
@@ -14830,7 +14824,7 @@
           <t>P6-F01</t>
         </is>
       </c>
-      <c r="B32" s="65" t="inlineStr">
+      <c r="B32" s="66" t="inlineStr">
         <is>
           <t>feature/swiggy-connectors-ui</t>
         </is>
@@ -14901,7 +14895,7 @@
           <t>P6-F02</t>
         </is>
       </c>
-      <c r="B33" s="66" t="n"/>
+      <c r="B33" s="67" t="n"/>
       <c r="C33" s="55" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -14968,7 +14962,7 @@
           <t>P6-F03</t>
         </is>
       </c>
-      <c r="B34" s="66" t="n"/>
+      <c r="B34" s="67" t="n"/>
       <c r="C34" s="46" t="inlineStr">
         <is>
           <t>Backend</t>
@@ -15017,7 +15011,7 @@
           <t>P6-F04</t>
         </is>
       </c>
-      <c r="B35" s="66" t="n"/>
+      <c r="B35" s="67" t="n"/>
       <c r="C35" s="55" t="inlineStr">
         <is>
           <t>Docs</t>
@@ -15066,7 +15060,7 @@
           <t>P6-F05</t>
         </is>
       </c>
-      <c r="B36" s="67" t="n"/>
+      <c r="B36" s="68" t="n"/>
       <c r="C36" s="46" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15150,7 +15144,7 @@
           <t>P6-S20</t>
         </is>
       </c>
-      <c r="B38" s="65" t="inlineStr">
+      <c r="B38" s="66" t="inlineStr">
         <is>
           <t>feature/swiggy-prompt-injection (deleted post-merge)</t>
         </is>
@@ -15220,7 +15214,7 @@
           <t>P6-S21</t>
         </is>
       </c>
-      <c r="B40" s="65" t="inlineStr">
+      <c r="B40" s="66" t="inlineStr">
         <is>
           <t>fix/swiggy-sse-market-intel</t>
         </is>
@@ -15291,7 +15285,7 @@
           <t>P6-S22</t>
         </is>
       </c>
-      <c r="B41" s="66" t="n"/>
+      <c r="B41" s="67" t="n"/>
       <c r="C41" s="55" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15358,7 +15352,7 @@
           <t>P6-S23</t>
         </is>
       </c>
-      <c r="B42" s="66" t="n"/>
+      <c r="B42" s="67" t="n"/>
       <c r="C42" s="46" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -15425,7 +15419,7 @@
           <t>P6-S24</t>
         </is>
       </c>
-      <c r="B43" s="66" t="n"/>
+      <c r="B43" s="67" t="n"/>
       <c r="C43" s="55" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15492,7 +15486,7 @@
           <t>P6-S25</t>
         </is>
       </c>
-      <c r="B44" s="66" t="n"/>
+      <c r="B44" s="67" t="n"/>
       <c r="C44" s="46" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15559,7 +15553,7 @@
           <t>P6-S26</t>
         </is>
       </c>
-      <c r="B45" s="66" t="n"/>
+      <c r="B45" s="67" t="n"/>
       <c r="C45" s="55" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15626,7 +15620,7 @@
           <t>P6-S27</t>
         </is>
       </c>
-      <c r="B46" s="66" t="n"/>
+      <c r="B46" s="67" t="n"/>
       <c r="C46" s="46" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15693,7 +15687,7 @@
           <t>P6-S28</t>
         </is>
       </c>
-      <c r="B47" s="66" t="n"/>
+      <c r="B47" s="67" t="n"/>
       <c r="C47" s="55" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15760,7 +15754,7 @@
           <t>P6-S29</t>
         </is>
       </c>
-      <c r="B48" s="66" t="n"/>
+      <c r="B48" s="67" t="n"/>
       <c r="C48" s="46" t="inlineStr">
         <is>
           <t>Security</t>
@@ -15819,7 +15813,7 @@
           <t>P6-S30</t>
         </is>
       </c>
-      <c r="B49" s="67" t="n"/>
+      <c r="B49" s="68" t="n"/>
       <c r="C49" s="55" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -15880,13 +15874,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="7.95" customHeight="1" s="72">
+    <row r="50" ht="108" customHeight="1" s="72">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>P6-S42</t>
-        </is>
-      </c>
-      <c r="B50" s="67" t="inlineStr">
+          <t>P6-S31</t>
+        </is>
+      </c>
+      <c r="B50" s="68" t="inlineStr">
         <is>
           <t>fix/ci-fastapi-starlette-conflict</t>
         </is>
@@ -15974,7 +15968,7 @@
           <t>P6-MI01</t>
         </is>
       </c>
-      <c r="B52" s="68" t="inlineStr">
+      <c r="B52" s="69" t="inlineStr">
         <is>
           <t>feature/swiggy-market-intel-expansion</t>
         </is>
@@ -16027,7 +16021,7 @@
           <t>P6-MI02</t>
         </is>
       </c>
-      <c r="B53" s="66" t="n"/>
+      <c r="B53" s="67" t="n"/>
       <c r="C53" s="46" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -16076,7 +16070,7 @@
           <t>P6-MI03</t>
         </is>
       </c>
-      <c r="B54" s="67" t="n"/>
+      <c r="B54" s="68" t="n"/>
       <c r="C54" s="55" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -16142,7 +16136,7 @@
           <t>P6-MI04</t>
         </is>
       </c>
-      <c r="B56" s="68" t="inlineStr">
+      <c r="B56" s="69" t="inlineStr">
         <is>
           <t>feature/swiggy-chatbot-expansion</t>
         </is>
@@ -16209,10 +16203,10 @@
     <row r="58" ht="73.05" customHeight="1" s="72">
       <c r="A58" s="62" t="inlineStr">
         <is>
-          <t>P6-S31</t>
-        </is>
-      </c>
-      <c r="B58" s="68" t="inlineStr">
+          <t>P6-S32</t>
+        </is>
+      </c>
+      <c r="B58" s="69" t="inlineStr">
         <is>
           <t>feature/action-queue</t>
         </is>
@@ -16297,10 +16291,10 @@
     <row r="60" ht="73.05" customHeight="1" s="72">
       <c r="A60" s="62" t="inlineStr">
         <is>
-          <t>P6-S32</t>
-        </is>
-      </c>
-      <c r="B60" s="68" t="n"/>
+          <t>P6-S33</t>
+        </is>
+      </c>
+      <c r="B60" s="69" t="n"/>
       <c r="C60" s="55" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -16381,10 +16375,10 @@
     <row r="62" ht="73.05" customHeight="1" s="72">
       <c r="A62" s="62" t="inlineStr">
         <is>
-          <t>P6-S33</t>
-        </is>
-      </c>
-      <c r="B62" s="68" t="n"/>
+          <t>P6-S34</t>
+        </is>
+      </c>
+      <c r="B62" s="69" t="n"/>
       <c r="C62" s="55" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -16436,7 +16430,7 @@
       </c>
       <c r="N62" s="55" t="inlineStr">
         <is>
-          <t>P6-S32</t>
+          <t>P6-S33</t>
         </is>
       </c>
       <c r="O62" s="56" t="inlineStr">
@@ -16465,10 +16459,10 @@
     <row r="64" ht="85.95" customHeight="1" s="72">
       <c r="A64" s="62" t="inlineStr">
         <is>
-          <t>P6-S34</t>
-        </is>
-      </c>
-      <c r="B64" s="68" t="inlineStr">
+          <t>P6-S35</t>
+        </is>
+      </c>
+      <c r="B64" s="69" t="inlineStr">
         <is>
           <t>feature/workflow-system</t>
         </is>
@@ -16553,10 +16547,10 @@
     <row r="66" ht="99" customHeight="1" s="72">
       <c r="A66" s="62" t="inlineStr">
         <is>
-          <t>P6-S35</t>
-        </is>
-      </c>
-      <c r="B66" s="68" t="n"/>
+          <t>P6-S36</t>
+        </is>
+      </c>
+      <c r="B66" s="69" t="n"/>
       <c r="C66" s="55" t="inlineStr">
         <is>
           <t>Product</t>
@@ -16608,7 +16602,7 @@
       </c>
       <c r="N66" s="55" t="inlineStr">
         <is>
-          <t>P6-S22-UNRESOLVED, P6-S42</t>
+          <t>P6-S22-UNRESOLVED, P6-S43</t>
         </is>
       </c>
       <c r="O66" s="56" t="inlineStr">
@@ -16637,10 +16631,10 @@
     <row r="68" ht="73.05" customHeight="1" s="72">
       <c r="A68" s="62" t="inlineStr">
         <is>
-          <t>P6-S36</t>
-        </is>
-      </c>
-      <c r="B68" s="68" t="n"/>
+          <t>P6-S37</t>
+        </is>
+      </c>
+      <c r="B68" s="69" t="n"/>
       <c r="C68" s="55" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -16692,7 +16686,7 @@
       </c>
       <c r="N68" s="55" t="inlineStr">
         <is>
-          <t>P6-S31</t>
+          <t>P6-S32</t>
         </is>
       </c>
       <c r="O68" s="56" t="inlineStr">
@@ -16721,10 +16715,10 @@
     <row r="70" ht="85.95" customHeight="1" s="72">
       <c r="A70" s="62" t="inlineStr">
         <is>
-          <t>P6-S37</t>
-        </is>
-      </c>
-      <c r="B70" s="68" t="inlineStr">
+          <t>P6-S38</t>
+        </is>
+      </c>
+      <c r="B70" s="69" t="inlineStr">
         <is>
           <t>feature/debate-critic</t>
         </is>
@@ -16780,7 +16774,7 @@
       </c>
       <c r="N70" s="55" t="inlineStr">
         <is>
-          <t>P6-S34</t>
+          <t>P6-S35</t>
         </is>
       </c>
       <c r="O70" s="56" t="inlineStr">
@@ -16812,7 +16806,7 @@
           <t>P6-R01</t>
         </is>
       </c>
-      <c r="B72" s="68" t="inlineStr">
+      <c r="B72" s="69" t="inlineStr">
         <is>
           <t>feature/voice-interface</t>
         </is>
@@ -16868,7 +16862,7 @@
       </c>
       <c r="N72" s="55" t="inlineStr">
         <is>
-          <t>P6-S43</t>
+          <t>P6-S44</t>
         </is>
       </c>
       <c r="O72" s="56" t="inlineStr">
@@ -16900,7 +16894,7 @@
           <t>P6-F06</t>
         </is>
       </c>
-      <c r="B74" s="68" t="inlineStr">
+      <c r="B74" s="69" t="inlineStr">
         <is>
           <t>feature/action-queue-ui</t>
         </is>
@@ -16961,7 +16955,7 @@
       </c>
       <c r="O74" s="56" t="inlineStr">
         <is>
-          <t>Depends on P6-S31 (action_queue in plan API response)</t>
+          <t>Depends on P6-S32 (action_queue in plan API response)</t>
         </is>
       </c>
     </row>
@@ -16988,7 +16982,7 @@
           <t>P6-F07</t>
         </is>
       </c>
-      <c r="B76" s="68" t="n"/>
+      <c r="B76" s="69" t="n"/>
       <c r="C76" s="55" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -17040,7 +17034,7 @@
       </c>
       <c r="N76" s="55" t="inlineStr">
         <is>
-          <t>P6-S43</t>
+          <t>P6-S44</t>
         </is>
       </c>
       <c r="O76" s="56" t="inlineStr">
@@ -17072,7 +17066,7 @@
           <t>P6-F08</t>
         </is>
       </c>
-      <c r="B78" s="68" t="n"/>
+      <c r="B78" s="69" t="n"/>
       <c r="C78" s="55" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -17085,7 +17079,7 @@
       </c>
       <c r="E78" s="56" t="inlineStr">
         <is>
-          <t>New route /live. Kitchen display-grade SSE feed from LiveMonitorService (P6-S35). Shows active Swiggy delivery orders with ETA countdown, Instamart procurement status with delivery ETA, alert banner on delivery spike or ingredient arrival. Swiggy logo + 'Live via Swiggy MCP' badge. Page shows inactive state outside service hours (12-14h, 19-22h IST).</t>
+          <t>New route /live. Kitchen display-grade SSE feed from LiveMonitorService (P6-S36). Shows active Swiggy delivery orders with ETA countdown, Instamart procurement status with delivery ETA, alert banner on delivery spike or ingredient arrival. Swiggy logo + 'Live via Swiggy MCP' badge. Page shows inactive state outside service hours (12-14h, 19-22h IST).</t>
         </is>
       </c>
       <c r="F78" s="56" t="inlineStr">
@@ -17124,7 +17118,7 @@
       </c>
       <c r="N78" s="55" t="inlineStr">
         <is>
-          <t>P6-S35</t>
+          <t>P6-S36</t>
         </is>
       </c>
       <c r="O78" s="56" t="inlineStr">
@@ -17153,10 +17147,10 @@
     <row r="80" ht="124.95" customHeight="1" s="72">
       <c r="A80" s="62" t="inlineStr">
         <is>
-          <t>P6-S38</t>
-        </is>
-      </c>
-      <c r="B80" s="68" t="n"/>
+          <t>P6-S39</t>
+        </is>
+      </c>
+      <c r="B80" s="69" t="n"/>
       <c r="C80" s="55" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -17229,10 +17223,10 @@
     <row r="82" ht="112.05" customHeight="1" s="72">
       <c r="A82" s="62" t="inlineStr">
         <is>
-          <t>P6-S39</t>
-        </is>
-      </c>
-      <c r="B82" s="68" t="n"/>
+          <t>P6-S40</t>
+        </is>
+      </c>
+      <c r="B82" s="69" t="n"/>
       <c r="C82" s="55" t="inlineStr">
         <is>
           <t>Product</t>
@@ -17305,10 +17299,10 @@
     <row r="84" ht="99" customHeight="1" s="72">
       <c r="A84" s="62" t="inlineStr">
         <is>
-          <t>P6-S40</t>
-        </is>
-      </c>
-      <c r="B84" s="68" t="n"/>
+          <t>P6-S41</t>
+        </is>
+      </c>
+      <c r="B84" s="69" t="n"/>
       <c r="C84" s="55" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -17381,10 +17375,10 @@
     <row r="86" ht="151.05" customHeight="1" s="72">
       <c r="A86" s="62" t="inlineStr">
         <is>
-          <t>P6-S41</t>
-        </is>
-      </c>
-      <c r="B86" s="68" t="n"/>
+          <t>P6-S42</t>
+        </is>
+      </c>
+      <c r="B86" s="69" t="n"/>
       <c r="C86" s="55" t="inlineStr">
         <is>
           <t>Product</t>
@@ -17451,7 +17445,7 @@
       <c r="O87" s="52" t="n"/>
     </row>
     <row r="88" ht="28.05" customHeight="1" s="72">
-      <c r="A88" s="69" t="inlineStr">
+      <c r="A88" s="70" t="inlineStr">
         <is>
           <t>→ DEMO 1  |  all above on main, docs updated, screenshots done — record full Swiggy read + AI + voice + live monitor demo ←</t>
         </is>
@@ -17570,16 +17564,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="85" t="inlineStr">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>BLOCKED — needs Swiggy staging creds (write tools: checkout, book_table)</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>P6-S42</t>
+          <t>P6-S43</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -17609,7 +17604,7 @@
       </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>docs/SWIGGY_INTEGRATION.md (P6-S42 executor section)</t>
+          <t>docs/SWIGGY_INTEGRATION.md (P6-S43 executor section)</t>
         </is>
       </c>
       <c r="H4" s="41" t="inlineStr">
@@ -17627,7 +17622,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K4" s="70" t="n"/>
+      <c r="K4" s="42" t="n"/>
       <c r="L4" s="41" t="inlineStr">
         <is>
           <t>W5</t>
@@ -17638,7 +17633,7 @@
       </c>
       <c r="N4" s="41" t="inlineStr">
         <is>
-          <t>P6-S31, P6-S14</t>
+          <t>P6-S32, P6-S14</t>
         </is>
       </c>
       <c r="O4" s="41" t="inlineStr">
@@ -17647,10 +17642,11 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>P6-S43</t>
+          <t>P6-S44</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -17698,7 +17694,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K6" s="70" t="n"/>
+      <c r="K6" s="42" t="n"/>
       <c r="L6" s="41" t="inlineStr">
         <is>
           <t>W5</t>
@@ -17709,7 +17705,7 @@
       </c>
       <c r="N6" s="41" t="inlineStr">
         <is>
-          <t>P6-S31</t>
+          <t>P6-S32</t>
         </is>
       </c>
       <c r="O6" s="41" t="inlineStr">
@@ -17718,10 +17714,11 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="41" t="inlineStr">
         <is>
-          <t>P6-S44</t>
+          <t>P6-S45</t>
         </is>
       </c>
       <c r="B8" s="41" t="inlineStr">
@@ -17769,7 +17766,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K8" s="70" t="n"/>
+      <c r="K8" s="42" t="n"/>
       <c r="L8" s="41" t="inlineStr">
         <is>
           <t>W9</t>
@@ -17780,7 +17777,7 @@
       </c>
       <c r="N8" s="41" t="inlineStr">
         <is>
-          <t>P6-S37</t>
+          <t>P6-S38</t>
         </is>
       </c>
       <c r="O8" s="41" t="inlineStr">
@@ -17789,20 +17786,22 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" s="85" t="inlineStr">
+      <c r="A10" s="83" t="inlineStr">
         <is>
           <t>WHEN RECEIVED — Sarvam AI access + AWS credits</t>
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="41" t="inlineStr">
         <is>
-          <t>P6-S45</t>
-        </is>
-      </c>
-      <c r="B12" s="70" t="n"/>
+          <t>P6-S46</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="n"/>
       <c r="C12" s="41" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -17843,8 +17842,8 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K12" s="70" t="n"/>
-      <c r="L12" s="70" t="n"/>
+      <c r="K12" s="42" t="n"/>
+      <c r="L12" s="42" t="n"/>
       <c r="M12" s="41" t="n">
         <v>0</v>
       </c>
@@ -17859,13 +17858,14 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="41" t="inlineStr">
         <is>
-          <t>P6-S46</t>
-        </is>
-      </c>
-      <c r="B14" s="70" t="n"/>
+          <t>P6-S47</t>
+        </is>
+      </c>
+      <c r="B14" s="42" t="n"/>
       <c r="C14" s="41" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -17906,8 +17906,8 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K14" s="70" t="n"/>
-      <c r="L14" s="70" t="n"/>
+      <c r="K14" s="42" t="n"/>
+      <c r="L14" s="42" t="n"/>
       <c r="M14" s="41" t="n">
         <v>0</v>
       </c>
@@ -17922,27 +17922,30 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="85" t="inlineStr">
+      <c r="A16" s="83" t="inlineStr">
         <is>
           <t>→ DEMO 2 / POTENTIAL DEMO  |  all above on main, staging write tools + Sarvam voice + AWS hosted — record full product demo ←</t>
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" s="85" t="inlineStr">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>DOCS + PHASE 6 MILESTONE MERGE</t>
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
           <t>P6-D01</t>
         </is>
       </c>
-      <c r="B20" s="70" t="n"/>
+      <c r="B20" s="42" t="n"/>
       <c r="C20" s="41" t="inlineStr">
         <is>
           <t>Docs</t>
@@ -17983,7 +17986,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K20" s="70" t="n"/>
+      <c r="K20" s="42" t="n"/>
       <c r="L20" s="41" t="inlineStr">
         <is>
           <t>W8</t>
@@ -18003,13 +18006,14 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="41" t="inlineStr">
         <is>
           <t>P6-D02</t>
         </is>
       </c>
-      <c r="B22" s="70" t="n"/>
+      <c r="B22" s="42" t="n"/>
       <c r="C22" s="41" t="inlineStr">
         <is>
           <t>Docs</t>
@@ -18050,7 +18054,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K22" s="70" t="n"/>
+      <c r="K22" s="42" t="n"/>
       <c r="L22" s="41" t="inlineStr">
         <is>
           <t>W8</t>
@@ -18070,13 +18074,14 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="41" t="inlineStr">
         <is>
           <t>P6-D03</t>
         </is>
       </c>
-      <c r="B24" s="70" t="n"/>
+      <c r="B24" s="42" t="n"/>
       <c r="C24" s="41" t="inlineStr">
         <is>
           <t>Release</t>
@@ -18117,7 +18122,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K24" s="70" t="n"/>
+      <c r="K24" s="42" t="n"/>
       <c r="L24" s="41" t="inlineStr">
         <is>
           <t>W8</t>
@@ -18137,13 +18142,15 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
-      <c r="A26" s="85" t="inlineStr">
+      <c r="A26" s="83" t="inlineStr">
         <is>
           <t>PHASE 7 — Production, CI/CD, Public Release</t>
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="41" t="inlineStr">
         <is>
@@ -18195,7 +18202,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K28" s="70" t="n"/>
+      <c r="K28" s="42" t="n"/>
       <c r="L28" s="41" t="inlineStr">
         <is>
           <t>P7</t>
@@ -18215,6 +18222,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="41" t="inlineStr">
         <is>
@@ -18266,7 +18274,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K30" s="70" t="n"/>
+      <c r="K30" s="42" t="n"/>
       <c r="L30" s="41" t="inlineStr">
         <is>
           <t>P7</t>
@@ -18286,6 +18294,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="41" t="inlineStr">
         <is>
@@ -18337,7 +18346,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K32" s="70" t="n"/>
+      <c r="K32" s="42" t="n"/>
       <c r="L32" s="41" t="inlineStr">
         <is>
           <t>P7</t>
@@ -18357,6 +18366,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="41" t="inlineStr">
         <is>
@@ -18408,7 +18418,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K34" s="70" t="n"/>
+      <c r="K34" s="42" t="n"/>
       <c r="L34" s="41" t="inlineStr">
         <is>
           <t>P7</t>
@@ -18428,6 +18438,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="41" t="inlineStr">
         <is>
@@ -18479,7 +18490,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K36" s="70" t="n"/>
+      <c r="K36" s="42" t="n"/>
       <c r="L36" s="41" t="inlineStr">
         <is>
           <t>P7</t>
@@ -18527,7 +18538,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.95" customHeight="1" s="72">
-      <c r="A1" s="84" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>CortexKitchen v2 — Documentation Strategy (Phase 6)</t>
         </is>
@@ -18656,7 +18667,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>P6-S43 — NEW</t>
+          <t>P6-S44 — NEW</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -18678,7 +18689,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>P6-S04, P6-S15, P6-S18, P6-S43</t>
+          <t>P6-S04, P6-S15, P6-S18, P6-S44</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -18744,7 +18755,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>P6-S05, P6-S18, P6-S43</t>
+          <t>P6-S05, P6-S18, P6-S44</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -18766,7 +18777,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>P6-S04, P6-S06, P6-S18, P6-S43</t>
+          <t>P6-S04, P6-S06, P6-S18, P6-S44</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -18910,7 +18921,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.95" customHeight="1" s="72">
-      <c r="A1" s="84" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>CortexKitchen — Git Branching Rules</t>
         </is>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -317,7 +317,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -451,6 +451,50 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9C9C9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9C9C9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9C9C9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9C9C9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9C9C9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9C9C9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9C9C9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9C9C9"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -13219,7 +13263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col width="12" customWidth="1" style="71" min="1" max="1"/>
@@ -13237,8 +13281,8 @@
     <col width="9" customWidth="1" style="72" min="13" max="13"/>
     <col width="16" customWidth="1" style="72" min="14" max="14"/>
     <col width="46" customWidth="1" style="72" min="15" max="15"/>
-    <col width="12" customWidth="1" style="71" min="16" max="16"/>
-    <col width="12" customWidth="1" style="71" min="17" max="16384"/>
+    <col width="12" customWidth="1" style="71" min="16" max="17"/>
+    <col width="12" customWidth="1" style="71" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.95" customHeight="1" s="72">
@@ -16950,7 +16994,7 @@
       </c>
       <c r="N74" s="55" t="inlineStr">
         <is>
-          <t>P6-S18</t>
+          <t>P6-S18, P6-F11</t>
         </is>
       </c>
       <c r="O74" s="56" t="inlineStr">
@@ -17034,7 +17078,7 @@
       </c>
       <c r="N76" s="55" t="inlineStr">
         <is>
-          <t>P6-S44</t>
+          <t>P6-S44, P6-F11</t>
         </is>
       </c>
       <c r="O76" s="56" t="inlineStr">
@@ -17118,7 +17162,7 @@
       </c>
       <c r="N78" s="55" t="inlineStr">
         <is>
-          <t>P6-S36</t>
+          <t>P6-S36, P6-F11</t>
         </is>
       </c>
       <c r="O78" s="56" t="inlineStr">
@@ -17147,33 +17191,37 @@
     <row r="80" ht="124.95" customHeight="1" s="72">
       <c r="A80" s="62" t="inlineStr">
         <is>
-          <t>P6-S39</t>
-        </is>
-      </c>
-      <c r="B80" s="69" t="n"/>
+          <t>P6-F09</t>
+        </is>
+      </c>
+      <c r="B80" s="69" t="inlineStr">
+        <is>
+          <t>feature/design-system-theming</t>
+        </is>
+      </c>
       <c r="C80" s="55" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D80" s="56" t="inlineStr">
         <is>
-          <t>Fix SQLite/JSONB test-infra gap blocking full CI coverage</t>
+          <t>Design system: light/dark theme + token system</t>
         </is>
       </c>
       <c r="E80" s="56" t="inlineStr">
         <is>
-          <t>test_swiggy_reservation_sync.py and test_connector_repository.py are excluded from the CI unit-tests job (P6-Q03) because they spin up a real SQLite engine and connectors.connector_metadata uses Postgres' JSONB column type, which SQLite's compiler can't render. Either give the column a SQLite-compatible fallback type for tests, or run these two files against a real Postgres service container in CI (docker-compose.yml already defines postgres:16 for local dev -- same image could back a CI service).</t>
+          <t>Add a parallel light-mode palette alongside the existing ink/ember dark tokens in globals.css (Tailwind v4 @theme), wire a theme toggle (persisted via localStorage, defaults to system prefers-color-scheme) accessible from every page's header/nav, and audit + replace ad-hoc opacity-based dark-only utility classes (text-white/65, bg-white/[0.02], etc.) across all ~35 dashboard/runs/chat components with theme-aware tokens so both modes render correctly. Target users skew middle-aged restaurant owners/managers who may find a dark-only dev-tool aesthetic hard to read or off-putting -- a toggle makes the product usable for both preferences, not just engineers.</t>
         </is>
       </c>
       <c r="F80" s="56" t="inlineStr">
         <is>
-          <t>fix: SQLite-compatible JSONB handling (or Postgres CI service) for excluded test files</t>
+          <t>feat: light/dark theme system with persisted toggle</t>
         </is>
       </c>
       <c r="G80" s="56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (frontend only)</t>
         </is>
       </c>
       <c r="H80" s="63" t="inlineStr">
@@ -17181,9 +17229,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="I80" s="61" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="I80" s="49" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J80" s="55" t="inlineStr">
@@ -17192,64 +17240,48 @@
         </is>
       </c>
       <c r="K80" s="55" t="n"/>
-      <c r="L80" s="55" t="n"/>
+      <c r="L80" s="59" t="n"/>
       <c r="M80" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N80" s="55" t="inlineStr">
-        <is>
-          <t>P6-S23</t>
-        </is>
-      </c>
-      <c r="O80" s="56" t="n"/>
-    </row>
-    <row r="81" ht="7.95" customHeight="1" s="72">
-      <c r="A81" s="52" t="n"/>
-      <c r="B81" s="52" t="n"/>
-      <c r="C81" s="52" t="n"/>
-      <c r="D81" s="52" t="n"/>
-      <c r="E81" s="52" t="n"/>
-      <c r="F81" s="52" t="n"/>
-      <c r="G81" s="52" t="n"/>
-      <c r="H81" s="52" t="n"/>
-      <c r="I81" s="52" t="n"/>
-      <c r="J81" s="52" t="n"/>
-      <c r="K81" s="52" t="n"/>
-      <c r="L81" s="52" t="n"/>
-      <c r="M81" s="52" t="n"/>
-      <c r="N81" s="52" t="n"/>
-      <c r="O81" s="52" t="n"/>
-    </row>
+      <c r="N80" s="55" t="n"/>
+      <c r="O80" s="56" t="inlineStr">
+        <is>
+          <t>Toggle switches and persists across reload; spot-check contrast/readability of all dashboard/runs/chat components in both modes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="7.95" customHeight="1" s="72"/>
     <row r="82" ht="112.05" customHeight="1" s="72">
       <c r="A82" s="62" t="inlineStr">
         <is>
-          <t>P6-S40</t>
+          <t>P6-F10</t>
         </is>
       </c>
       <c r="B82" s="69" t="n"/>
       <c r="C82" s="55" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D82" s="56" t="inlineStr">
         <is>
-          <t>Promote reviewed RAGAS/DeepEval candidates into curated eval files</t>
+          <t>De-console-ify typography and visual hierarchy</t>
         </is>
       </c>
       <c r="E82" s="56" t="inlineStr">
         <is>
-          <t>build_ragas_dataset.py / build_deepeval_dataset.py (P6-Q03) produce .candidates.json files from live approved runs but never auto-merge them -- ground_truth needs human verification by design. Needs a recurring habit of actually running these periodically and hand-promoting reviewed candidates into complaint_rag_samples.json / test_deepeval_quality.py, or the static datasets stay frozen at today's size forever.</t>
+          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language.</t>
         </is>
       </c>
       <c r="F82" s="56" t="inlineStr">
         <is>
-          <t>chore: promote reviewed eval candidates into curated datasets</t>
+          <t>feat: rebalance typography -- monospace as accent, not primary label voice</t>
         </is>
       </c>
       <c r="G82" s="56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (frontend only)</t>
         </is>
       </c>
       <c r="H82" s="63" t="inlineStr">
@@ -17257,9 +17289,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="I82" s="64" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="I82" s="49" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J82" s="55" t="inlineStr">
@@ -17268,64 +17300,52 @@
         </is>
       </c>
       <c r="K82" s="55" t="n"/>
-      <c r="L82" s="55" t="n"/>
+      <c r="L82" s="59" t="n"/>
       <c r="M82" s="58" t="n">
         <v>0</v>
       </c>
       <c r="N82" s="55" t="inlineStr">
         <is>
-          <t>P6-S23</t>
-        </is>
-      </c>
-      <c r="O82" s="56" t="n"/>
-    </row>
-    <row r="83" ht="7.95" customHeight="1" s="72">
-      <c r="A83" s="52" t="n"/>
-      <c r="B83" s="52" t="n"/>
-      <c r="C83" s="52" t="n"/>
-      <c r="D83" s="52" t="n"/>
-      <c r="E83" s="52" t="n"/>
-      <c r="F83" s="52" t="n"/>
-      <c r="G83" s="52" t="n"/>
-      <c r="H83" s="52" t="n"/>
-      <c r="I83" s="52" t="n"/>
-      <c r="J83" s="52" t="n"/>
-      <c r="K83" s="52" t="n"/>
-      <c r="L83" s="52" t="n"/>
-      <c r="M83" s="52" t="n"/>
-      <c r="N83" s="52" t="n"/>
-      <c r="O83" s="52" t="n"/>
-    </row>
+          <t>P6-F09</t>
+        </is>
+      </c>
+      <c r="O82" s="56" t="inlineStr">
+        <is>
+          <t>Visual diff of dashboard/runs headers and stat labels before/after; landing-page-level polish confirmed by eye on both themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="7.95" customHeight="1" s="72"/>
     <row r="84" ht="99" customHeight="1" s="72">
       <c r="A84" s="62" t="inlineStr">
         <is>
-          <t>P6-S41</t>
+          <t>P6-F11</t>
         </is>
       </c>
       <c r="B84" s="69" t="n"/>
       <c r="C84" s="55" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D84" s="56" t="inlineStr">
         <is>
-          <t>Regenerate golden_runs.json against real production data</t>
+          <t>Information architecture restructure: split the mega-dashboard into focused pages</t>
         </is>
       </c>
       <c r="E84" s="56" t="inlineStr">
         <is>
-          <t>build_golden_dataset.py's key-path bug is fixed (P6-Q03) but the checked-in fixture still reflects the old, always-empty extraction, since regenerating it requires a live Postgres populated with real run history, which wasn't available during the fix. Run scripts/build_golden_dataset.py locally once docker-compose services are up to refresh it with corrected shortage/restock data.</t>
+          <t>The single /dashboard page currently tries to show demand forecast + reservations + complaints + inventory + market intel + menu + critic + connector status all at once -- reads as a diagnostics dump a manager could get lost in. Restructure into: a lightweight /dashboard 'Today' view (KPIs, alerts, pending actions only -- what a manager checks first each morning), a dedicated /operations page for the 5 planning-agent outputs in plain-language framing (not raw JSON-shaped cards), and Swiggy Market Intelligence promoted to its own dedicated /market page (competitor pricing, occupancy, Instamart procurement) so it has a clear, demo-able home separate from internal ops data -- matching the product's own internal-vs-Swiggy-data distinction already documented in CLAUDE.md.</t>
         </is>
       </c>
       <c r="F84" s="56" t="inlineStr">
         <is>
-          <t>chore: regenerate golden_runs.json with corrected extraction logic</t>
+          <t>feat: split dashboard into /dashboard (Today), /operations, /market</t>
         </is>
       </c>
       <c r="G84" s="56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CLAUDE.md (nav/page map section), docs/ARCHITECTURE.md</t>
         </is>
       </c>
       <c r="H84" s="63" t="inlineStr">
@@ -17333,9 +17353,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="I84" s="61" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="I84" s="49" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J84" s="55" t="inlineStr">
@@ -17344,64 +17364,52 @@
         </is>
       </c>
       <c r="K84" s="55" t="n"/>
-      <c r="L84" s="55" t="n"/>
+      <c r="L84" s="59" t="n"/>
       <c r="M84" s="58" t="n">
         <v>0</v>
       </c>
       <c r="N84" s="55" t="inlineStr">
         <is>
-          <t>P6-S23</t>
-        </is>
-      </c>
-      <c r="O84" s="56" t="n"/>
-    </row>
-    <row r="85" ht="7.95" customHeight="1" s="72">
-      <c r="A85" s="52" t="n"/>
-      <c r="B85" s="52" t="n"/>
-      <c r="C85" s="52" t="n"/>
-      <c r="D85" s="52" t="n"/>
-      <c r="E85" s="52" t="n"/>
-      <c r="F85" s="52" t="n"/>
-      <c r="G85" s="52" t="n"/>
-      <c r="H85" s="52" t="n"/>
-      <c r="I85" s="52" t="n"/>
-      <c r="J85" s="52" t="n"/>
-      <c r="K85" s="52" t="n"/>
-      <c r="L85" s="52" t="n"/>
-      <c r="M85" s="52" t="n"/>
-      <c r="N85" s="52" t="n"/>
-      <c r="O85" s="52" t="n"/>
-    </row>
+          <t>P6-F10</t>
+        </is>
+      </c>
+      <c r="O84" s="56" t="inlineStr">
+        <is>
+          <t>Each new page renders its intended slice only; nav updated; no orphaned links to the old single-page layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="7.95" customHeight="1" s="72"/>
     <row r="86" ht="151.05" customHeight="1" s="72">
       <c r="A86" s="62" t="inlineStr">
         <is>
-          <t>P6-S42</t>
+          <t>P6-F12</t>
         </is>
       </c>
       <c r="B86" s="69" t="n"/>
       <c r="C86" s="55" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D86" s="56" t="inlineStr">
         <is>
-          <t>Product redesign -- move dashboard/runs pages past 'dev console' feel</t>
+          <t>/runs history page redesign</t>
         </is>
       </c>
       <c r="E86" s="56" t="inlineStr">
         <is>
-          <t>Explicitly deferred this session pending a proper scoping pass. Concrete evidence gathered: /runs/{id} throws a raw unstyled Next.js 404 (no per-run deep link, only in-page sidebar selection on /runs), and the run-detail view is a dense wall of monospace-labelled text blocks (dimension scores, 10+ revision-reason cards) with little visual hierarchy -- reads like a debug trace rather than something an owner skims at 7am. The landing/hero page already looks like a real product; this needs its own scoping conversation (which pages, target feel, how much rework), not a quick fix bundled into other work.</t>
+          <t>Apply the new design system to /runs. Restyle from a dense monospace debug trace (raw dimension-score grids, 10+ revision-reason text blocks) into something a manager can skim in under a minute. Fix the currently-unstyled raw Next.js 404 on /runs/{id} deep links -- give each run its own real page.</t>
         </is>
       </c>
       <c r="F86" s="56" t="inlineStr">
         <is>
-          <t>TBD -- needs scoping conversation first</t>
+          <t>feat: redesign /runs history page + fix /runs/{id} deep-link 404</t>
         </is>
       </c>
       <c r="G86" s="56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None (frontend only)</t>
         </is>
       </c>
       <c r="H86" s="63" t="inlineStr">
@@ -17409,9 +17417,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="I86" s="61" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="I86" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="J86" s="55" t="inlineStr">
@@ -17420,32 +17428,324 @@
         </is>
       </c>
       <c r="K86" s="55" t="n"/>
-      <c r="L86" s="55" t="n"/>
+      <c r="L86" s="59" t="n"/>
       <c r="M86" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N86" s="55" t="n"/>
-      <c r="O86" s="56" t="n"/>
-    </row>
-    <row r="87" ht="7.95" customHeight="1" s="72">
-      <c r="A87" s="52" t="n"/>
-      <c r="B87" s="52" t="n"/>
-      <c r="C87" s="52" t="n"/>
-      <c r="D87" s="52" t="n"/>
-      <c r="E87" s="52" t="n"/>
-      <c r="F87" s="52" t="n"/>
-      <c r="G87" s="52" t="n"/>
-      <c r="H87" s="52" t="n"/>
-      <c r="I87" s="52" t="n"/>
-      <c r="J87" s="52" t="n"/>
-      <c r="K87" s="52" t="n"/>
-      <c r="L87" s="52" t="n"/>
-      <c r="M87" s="52" t="n"/>
-      <c r="N87" s="52" t="n"/>
-      <c r="O87" s="52" t="n"/>
-    </row>
+      <c r="N86" s="55" t="inlineStr">
+        <is>
+          <t>P6-F11</t>
+        </is>
+      </c>
+      <c r="O86" s="56" t="inlineStr">
+        <is>
+          <t>Direct navigation to /runs/{id} renders the run, not a 404; skim-readability spot check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="7.95" customHeight="1" s="72"/>
     <row r="88" ht="28.05" customHeight="1" s="72">
-      <c r="A88" s="70" t="inlineStr">
+      <c r="A88" s="62" t="inlineStr">
+        <is>
+          <t>P6-S39</t>
+        </is>
+      </c>
+      <c r="B88" s="69" t="n"/>
+      <c r="C88" s="55" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D88" s="56" t="inlineStr">
+        <is>
+          <t>Fix SQLite/JSONB test-infra gap blocking full CI coverage</t>
+        </is>
+      </c>
+      <c r="E88" s="56" t="inlineStr">
+        <is>
+          <t>test_swiggy_reservation_sync.py and test_connector_repository.py are excluded from the CI unit-tests job (P6-Q03) because they spin up a real SQLite engine and connectors.connector_metadata uses Postgres' JSONB column type, which SQLite's compiler can't render. Either give the column a SQLite-compatible fallback type for tests, or run these two files against a real Postgres service container in CI (docker-compose.yml already defines postgres:16 for local dev -- same image could back a CI service).</t>
+        </is>
+      </c>
+      <c r="F88" s="56" t="inlineStr">
+        <is>
+          <t>fix: SQLite-compatible JSONB handling (or Postgres CI service) for excluded test files</t>
+        </is>
+      </c>
+      <c r="G88" s="56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H88" s="63" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I88" s="64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J88" s="55" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K88" s="55" t="n"/>
+      <c r="L88" s="55" t="n"/>
+      <c r="M88" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="55" t="inlineStr">
+        <is>
+          <t>P6-S23</t>
+        </is>
+      </c>
+      <c r="O88" s="56" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="52" t="n"/>
+      <c r="B89" s="52" t="n"/>
+      <c r="C89" s="52" t="n"/>
+      <c r="D89" s="52" t="n"/>
+      <c r="E89" s="52" t="n"/>
+      <c r="F89" s="52" t="n"/>
+      <c r="G89" s="52" t="n"/>
+      <c r="H89" s="52" t="n"/>
+      <c r="I89" s="52" t="n"/>
+      <c r="J89" s="52" t="n"/>
+      <c r="K89" s="52" t="n"/>
+      <c r="L89" s="52" t="n"/>
+      <c r="M89" s="52" t="n"/>
+      <c r="N89" s="52" t="n"/>
+      <c r="O89" s="52" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="62" t="inlineStr">
+        <is>
+          <t>P6-S40</t>
+        </is>
+      </c>
+      <c r="B90" s="69" t="n"/>
+      <c r="C90" s="55" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D90" s="56" t="inlineStr">
+        <is>
+          <t>Promote reviewed RAGAS/DeepEval candidates into curated eval files</t>
+        </is>
+      </c>
+      <c r="E90" s="56" t="inlineStr">
+        <is>
+          <t>build_ragas_dataset.py / build_deepeval_dataset.py (P6-Q03) produce .candidates.json files from live approved runs but never auto-merge them -- ground_truth needs human verification by design. Needs a recurring habit of actually running these periodically and hand-promoting reviewed candidates into complaint_rag_samples.json / test_deepeval_quality.py, or the static datasets stay frozen at today's size forever.</t>
+        </is>
+      </c>
+      <c r="F90" s="56" t="inlineStr">
+        <is>
+          <t>chore: promote reviewed eval candidates into curated datasets</t>
+        </is>
+      </c>
+      <c r="G90" s="56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H90" s="63" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I90" s="64" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J90" s="55" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K90" s="55" t="n"/>
+      <c r="L90" s="55" t="n"/>
+      <c r="M90" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="55" t="inlineStr">
+        <is>
+          <t>P6-S23</t>
+        </is>
+      </c>
+      <c r="O90" s="56" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="52" t="n"/>
+      <c r="B91" s="52" t="n"/>
+      <c r="C91" s="52" t="n"/>
+      <c r="D91" s="52" t="n"/>
+      <c r="E91" s="52" t="n"/>
+      <c r="F91" s="52" t="n"/>
+      <c r="G91" s="52" t="n"/>
+      <c r="H91" s="52" t="n"/>
+      <c r="I91" s="52" t="n"/>
+      <c r="J91" s="52" t="n"/>
+      <c r="K91" s="52" t="n"/>
+      <c r="L91" s="52" t="n"/>
+      <c r="M91" s="52" t="n"/>
+      <c r="N91" s="52" t="n"/>
+      <c r="O91" s="52" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="62" t="inlineStr">
+        <is>
+          <t>P6-S41</t>
+        </is>
+      </c>
+      <c r="B92" s="69" t="n"/>
+      <c r="C92" s="55" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D92" s="56" t="inlineStr">
+        <is>
+          <t>Regenerate golden_runs.json against real production data</t>
+        </is>
+      </c>
+      <c r="E92" s="56" t="inlineStr">
+        <is>
+          <t>build_golden_dataset.py's key-path bug is fixed (P6-Q03) but the checked-in fixture still reflects the old, always-empty extraction, since regenerating it requires a live Postgres populated with real run history, which wasn't available during the fix. Run scripts/build_golden_dataset.py locally once docker-compose services are up to refresh it with corrected shortage/restock data.</t>
+        </is>
+      </c>
+      <c r="F92" s="56" t="inlineStr">
+        <is>
+          <t>chore: regenerate golden_runs.json with corrected extraction logic</t>
+        </is>
+      </c>
+      <c r="G92" s="56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H92" s="63" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I92" s="61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J92" s="55" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K92" s="55" t="n"/>
+      <c r="L92" s="55" t="n"/>
+      <c r="M92" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="55" t="inlineStr">
+        <is>
+          <t>P6-S23</t>
+        </is>
+      </c>
+      <c r="O92" s="56" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="52" t="n"/>
+      <c r="B93" s="52" t="n"/>
+      <c r="C93" s="52" t="n"/>
+      <c r="D93" s="52" t="n"/>
+      <c r="E93" s="52" t="n"/>
+      <c r="F93" s="52" t="n"/>
+      <c r="G93" s="52" t="n"/>
+      <c r="H93" s="52" t="n"/>
+      <c r="I93" s="52" t="n"/>
+      <c r="J93" s="52" t="n"/>
+      <c r="K93" s="52" t="n"/>
+      <c r="L93" s="52" t="n"/>
+      <c r="M93" s="52" t="n"/>
+      <c r="N93" s="52" t="n"/>
+      <c r="O93" s="52" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="62" t="inlineStr">
+        <is>
+          <t>P6-S42</t>
+        </is>
+      </c>
+      <c r="B94" s="69" t="n"/>
+      <c r="C94" s="55" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D94" s="56" t="inlineStr">
+        <is>
+          <t>Product redesign -- move dashboard/runs pages past 'dev console' feel</t>
+        </is>
+      </c>
+      <c r="E94" s="56" t="inlineStr">
+        <is>
+          <t>Explicitly deferred this session pending a proper scoping pass. Concrete evidence gathered: /runs/{id} throws a raw unstyled Next.js 404 (no per-run deep link, only in-page sidebar selection on /runs), and the run-detail view is a dense wall of monospace-labelled text blocks (dimension scores, 10+ revision-reason cards) with little visual hierarchy -- reads like a debug trace rather than something an owner skims at 7am. The landing/hero page already looks like a real product; this needs its own scoping conversation (which pages, target feel, how much rework), not a quick fix bundled into other work. SUPERSEDED 2026-07-03 -- decomposed into concrete, sequenced tasks P6-F09 (theme system), P6-F10 (typography rebalance), P6-F11 (IA restructure), P6-F12 (/runs redesign) after a direct scoping conversation with the user, who flagged the product reads as a dev console and asked for light/dark mode + separated pages (Agents/Operations vs Swiggy Market Intel) as an explicit product-quality bar before shipping more features on top of the old layout.</t>
+        </is>
+      </c>
+      <c r="F94" s="56" t="inlineStr">
+        <is>
+          <t>TBD -- needs scoping conversation first</t>
+        </is>
+      </c>
+      <c r="G94" s="56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H94" s="63" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="I94" s="61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J94" s="55" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K94" s="55" t="n"/>
+      <c r="L94" s="55" t="n"/>
+      <c r="M94" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="55" t="n"/>
+      <c r="O94" s="56" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="52" t="n"/>
+      <c r="B95" s="52" t="n"/>
+      <c r="C95" s="52" t="n"/>
+      <c r="D95" s="52" t="n"/>
+      <c r="E95" s="52" t="n"/>
+      <c r="F95" s="52" t="n"/>
+      <c r="G95" s="52" t="n"/>
+      <c r="H95" s="52" t="n"/>
+      <c r="I95" s="52" t="n"/>
+      <c r="J95" s="52" t="n"/>
+      <c r="K95" s="52" t="n"/>
+      <c r="L95" s="52" t="n"/>
+      <c r="M95" s="52" t="n"/>
+      <c r="N95" s="52" t="n"/>
+      <c r="O95" s="52" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="70" t="inlineStr">
         <is>
           <t>→ DEMO 1  |  all above on main, docs updated, screenshots done — record full Swiggy read + AI + voice + live monitor demo ←</t>
         </is>
@@ -17454,6 +17754,7 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B40:B49"/>
+    <mergeCell ref="A96:O96"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B52:B54"/>
@@ -17461,7 +17762,6 @@
     <mergeCell ref="B32:B36"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A88:O88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17570,7 +17870,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="41" t="inlineStr">
         <is>
@@ -17642,7 +17941,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="41" t="inlineStr">
         <is>
@@ -17714,7 +18012,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="41" t="inlineStr">
         <is>
@@ -17786,7 +18083,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="83" t="inlineStr">
         <is>
@@ -17794,7 +18090,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="41" t="inlineStr">
         <is>
@@ -17858,7 +18153,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="41" t="inlineStr">
         <is>
@@ -17922,7 +18216,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="83" t="inlineStr">
         <is>
@@ -17930,7 +18223,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="83" t="inlineStr">
         <is>
@@ -17938,7 +18230,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
         <is>
@@ -18006,7 +18297,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="41" t="inlineStr">
         <is>
@@ -18074,7 +18364,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="41" t="inlineStr">
         <is>
@@ -18142,7 +18431,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="83" t="inlineStr">
         <is>
@@ -18150,7 +18438,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="41" t="inlineStr">
         <is>
@@ -18222,7 +18509,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="41" t="inlineStr">
         <is>
@@ -18294,7 +18580,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="41" t="inlineStr">
         <is>
@@ -18366,7 +18651,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="41" t="inlineStr">
         <is>
@@ -18438,7 +18722,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="41" t="inlineStr">
         <is>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -17211,7 +17211,7 @@
       </c>
       <c r="E80" s="56" t="inlineStr">
         <is>
-          <t>Add a parallel light-mode palette alongside the existing ink/ember dark tokens in globals.css (Tailwind v4 @theme), wire a theme toggle (persisted via localStorage, defaults to system prefers-color-scheme) accessible from every page's header/nav, and audit + replace ad-hoc opacity-based dark-only utility classes (text-white/65, bg-white/[0.02], etc.) across all ~35 dashboard/runs/chat components with theme-aware tokens so both modes render correctly. Target users skew middle-aged restaurant owners/managers who may find a dark-only dev-tool aesthetic hard to read or off-putting -- a toggle makes the product usable for both preferences, not just engineers.</t>
+          <t>Add a parallel light-mode palette alongside the existing ink/ember dark tokens in globals.css (Tailwind v4 @theme), wire a theme toggle (persisted via localStorage, defaults to system prefers-color-scheme) accessible from every page's header/nav, and audit + replace ad-hoc opacity-based dark-only utility classes (text-white/65, bg-white/[0.02], etc.) across all ~35 dashboard/runs/chat components with theme-aware tokens so both modes render correctly. Target users skew middle-aged restaurant owners/managers who may find a dark-only dev-tool aesthetic hard to read or off-putting -- a toggle makes the product usable for both preferences, not just engineers. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts.</t>
         </is>
       </c>
       <c r="F80" s="56" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="E82" s="56" t="inlineStr">
         <is>
-          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language.</t>
+          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts.</t>
         </is>
       </c>
       <c r="F82" s="56" t="inlineStr">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="E84" s="56" t="inlineStr">
         <is>
-          <t>The single /dashboard page currently tries to show demand forecast + reservations + complaints + inventory + market intel + menu + critic + connector status all at once -- reads as a diagnostics dump a manager could get lost in. Restructure into: a lightweight /dashboard 'Today' view (KPIs, alerts, pending actions only -- what a manager checks first each morning), a dedicated /operations page for the 5 planning-agent outputs in plain-language framing (not raw JSON-shaped cards), and Swiggy Market Intelligence promoted to its own dedicated /market page (competitor pricing, occupancy, Instamart procurement) so it has a clear, demo-able home separate from internal ops data -- matching the product's own internal-vs-Swiggy-data distinction already documented in CLAUDE.md.</t>
+          <t>The single /dashboard page currently tries to show demand forecast + reservations + complaints + inventory + market intel + menu + critic + connector status all at once -- reads as a diagnostics dump a manager could get lost in. Restructure into: a lightweight /dashboard 'Today' view (KPIs, alerts, pending actions only -- what a manager checks first each morning), a dedicated /operations page for the 5 planning-agent outputs in plain-language framing (not raw JSON-shaped cards), and Swiggy Market Intelligence promoted to its own dedicated /market page (competitor pricing, occupancy, Instamart procurement) so it has a clear, demo-able home separate from internal ops data -- matching the product's own internal-vs-Swiggy-data distinction already documented in CLAUDE.md. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts.</t>
         </is>
       </c>
       <c r="F84" s="56" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="E86" s="56" t="inlineStr">
         <is>
-          <t>Apply the new design system to /runs. Restyle from a dense monospace debug trace (raw dimension-score grids, 10+ revision-reason text blocks) into something a manager can skim in under a minute. Fix the currently-unstyled raw Next.js 404 on /runs/{id} deep links -- give each run its own real page.</t>
+          <t>Apply the new design system to /runs. Restyle from a dense monospace debug trace (raw dimension-score grids, 10+ revision-reason text blocks) into something a manager can skim in under a minute. Fix the currently-unstyled raw Next.js 404 on /runs/{id} deep links -- give each run its own real page. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts.</t>
         </is>
       </c>
       <c r="F86" s="56" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -20,9 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -501,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -727,6 +728,12 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="23" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="23" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17211,7 +17218,7 @@
       </c>
       <c r="E80" s="56" t="inlineStr">
         <is>
-          <t>Add a parallel light-mode palette alongside the existing ink/ember dark tokens in globals.css (Tailwind v4 @theme), wire a theme toggle (persisted via localStorage, defaults to system prefers-color-scheme) accessible from every page's header/nav, and audit + replace ad-hoc opacity-based dark-only utility classes (text-white/65, bg-white/[0.02], etc.) across all ~35 dashboard/runs/chat components with theme-aware tokens so both modes render correctly. Target users skew middle-aged restaurant owners/managers who may find a dark-only dev-tool aesthetic hard to read or off-putting -- a toggle makes the product usable for both preferences, not just engineers. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts.</t>
+          <t>Add a parallel light-mode palette alongside the existing ink/ember dark tokens in globals.css (Tailwind v4 @theme), wire a theme toggle (persisted via localStorage, defaults to system prefers-color-scheme) accessible from every page's header/nav, and audit + replace ad-hoc opacity-based dark-only utility classes (text-white/65, bg-white/[0.02], etc.) across all ~35 dashboard/runs/chat components with theme-aware tokens so both modes render correctly. Target users skew middle-aged restaurant owners/managers who may find a dark-only dev-tool aesthetic hard to read or off-putting -- a toggle makes the product usable for both preferences, not just engineers. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. DONE 2026-07-04: light-mode token layer + toggle built and applied across all ~30 pages/components (not just the 5 touched in the direction prototype), via a boundary-safe scripted class rename so the same old class always maps to the same new token. 3 real bugs found only by driving the app in a browser (not catchable by a class-rename script alone): ember accent text washed out on light badges (fixed via --color-accent token), DatePicker select/date-input had inline style={{background:...}} overriding the className entirely, and no explicit color-scheme meant native &lt;select&gt;/&lt;option&gt; rendered with OS dark chrome regardless of page theme. Verified end-to-end with a real registered test account across dashboard/runs/connectors/chat in both themes -- zero console errors, zero hydration warnings, tsc + eslint clean.</t>
         </is>
       </c>
       <c r="F80" s="56" t="inlineStr">
@@ -17226,7 +17233,7 @@
       </c>
       <c r="H80" s="63" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I80" s="49" t="inlineStr">
@@ -17239,10 +17246,14 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K80" s="55" t="n"/>
-      <c r="L80" s="59" t="n"/>
+      <c r="K80" s="84" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L80" s="85" t="n">
+        <v>46207</v>
+      </c>
       <c r="M80" s="58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" s="55" t="n"/>
       <c r="O80" s="56" t="inlineStr">
@@ -17271,7 +17282,7 @@
       </c>
       <c r="E82" s="56" t="inlineStr">
         <is>
-          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts.</t>
+          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. NOTE: the ember-accent-text contrast fix (text-ember-300/400 -&gt; --color-accent token) was already done as part of P6-F09 verification, since it was blocking basic light-mode readability, not a nice-to-have. Remaining F10 scope: pull font-mono back from being the default label voice everywhere to a true accent.</t>
         </is>
       </c>
       <c r="F82" s="56" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -17282,7 +17282,7 @@
       </c>
       <c r="E82" s="56" t="inlineStr">
         <is>
-          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. NOTE: the ember-accent-text contrast fix (text-ember-300/400 -&gt; --color-accent token) was already done as part of P6-F09 verification, since it was blocking basic light-mode readability, not a nice-to-have. Remaining F10 scope: pull font-mono back from being the default label voice everywhere to a true accent.</t>
+          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. NOTE: the ember-accent-text contrast fix (text-ember-300/400 -&gt; --color-accent token) was already done as part of P6-F09 verification, since it was blocking basic light-mode readability, not a nice-to-have. Remaining F10 scope: pull font-mono back from being the default label voice everywhere to a true accent. DONE 2026-07-4: two-pass conversion -- (1) mechanical pass on the specific font-mono+uppercase+tracking- combination (171 label class-strings, always a decorative label in this codebase, never data), (2) per-instance judgment pass on the remaining ~89 bare font-mono usages, since this codebase used monospace for three genuinely different things (real data, category/status labels, and even prose/error messages) that no single mechanical rule could tell apart. Demoted buttons/links/status words/category badges/prose; kept genuine data (prices, IDs, timestamps, scores, deltas, code blocks). Also caught 2 more instances of hardcoded legacy bg-navy-*/text-gold-* colors (a different legacy palette than bg-ink-*, missed by the original P6-F09 conversion script) while auditing context file-by-file. Verified in browser (dashboard, runs) both themes -- zero console errors, tsc clean.</t>
         </is>
       </c>
       <c r="F82" s="56" t="inlineStr">
@@ -17297,7 +17297,7 @@
       </c>
       <c r="H82" s="63" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I82" s="49" t="inlineStr">
@@ -17310,10 +17310,14 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K82" s="55" t="n"/>
-      <c r="L82" s="59" t="n"/>
+      <c r="K82" s="84" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L82" s="85" t="n">
+        <v>46207</v>
+      </c>
       <c r="M82" s="58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="55" t="inlineStr">
         <is>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -17282,7 +17282,7 @@
       </c>
       <c r="E82" s="56" t="inlineStr">
         <is>
-          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. NOTE: the ember-accent-text contrast fix (text-ember-300/400 -&gt; --color-accent token) was already done as part of P6-F09 verification, since it was blocking basic light-mode readability, not a nice-to-have. Remaining F10 scope: pull font-mono back from being the default label voice everywhere to a true accent. DONE 2026-07-4: two-pass conversion -- (1) mechanical pass on the specific font-mono+uppercase+tracking- combination (171 label class-strings, always a decorative label in this codebase, never data), (2) per-instance judgment pass on the remaining ~89 bare font-mono usages, since this codebase used monospace for three genuinely different things (real data, category/status labels, and even prose/error messages) that no single mechanical rule could tell apart. Demoted buttons/links/status words/category badges/prose; kept genuine data (prices, IDs, timestamps, scores, deltas, code blocks). Also caught 2 more instances of hardcoded legacy bg-navy-*/text-gold-* colors (a different legacy palette than bg-ink-*, missed by the original P6-F09 conversion script) while auditing context file-by-file. Verified in browser (dashboard, runs) both themes -- zero console errors, tsc clean.</t>
+          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. NOTE: the ember-accent-text contrast fix (text-ember-300/400 -&gt; --color-accent token) was already done as part of P6-F09 verification, since it was blocking basic light-mode readability, not a nice-to-have. Remaining F10 scope: pull font-mono back from being the default label voice everywhere to a true accent. DONE 2026-07-4: two-pass conversion -- (1) mechanical pass on the specific font-mono+uppercase+tracking- combination (171 label class-strings, always a decorative label in this codebase, never data), (2) per-instance judgment pass on the remaining ~89 bare font-mono usages, since this codebase used monospace for three genuinely different things (real data, category/status labels, and even prose/error messages) that no single mechanical rule could tell apart. Demoted buttons/links/status words/category badges/prose; kept genuine data (prices, IDs, timestamps, scores, deltas, code blocks). Also caught 2 more instances of hardcoded legacy bg-navy-*/text-gold-* colors (a different legacy palette than bg-ink-*, missed by the original P6-F09 conversion script) while auditing context file-by-file. Verified in browser (dashboard, runs) both themes -- zero console errors, tsc clean. FOLLOW-UP 2026-07-4: initial Completed mark only covered the mono-demotion half; the serif-extension half (matching the landing page voice) was still missing. Fixed: dashboard hero emphasis line switched from a color gradient to the landing page's proven display-it italic accent pattern; 5 bare page titles (Plan History, Connectors, Data Health, Workspace Settings, Restaurant Profiles) converted from plain bold sans to the .display serif class; key numeric stat tiles (connectors sync counts, runs KPI Metric component) converted to .num-display serif figures. Now genuinely done both halves.</t>
         </is>
       </c>
       <c r="F82" s="56" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Tracker ( 1 - 5 )" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 6" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staging Creds + Phase 7" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doc Strategy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git Practices" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Phase Tracker ( 1 - 5 )" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Phase 6" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Staging Creds + Phase 7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Doc Strategy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Git Practices" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -735,6 +735,8 @@
     <xf numFmtId="166" fontId="21" fillId="23" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13270,7 +13272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col width="12" customWidth="1" style="71" min="1" max="1"/>
@@ -17350,12 +17352,12 @@
       </c>
       <c r="E84" s="56" t="inlineStr">
         <is>
-          <t>The single /dashboard page currently tries to show demand forecast + reservations + complaints + inventory + market intel + menu + critic + connector status all at once -- reads as a diagnostics dump a manager could get lost in. Restructure into: a lightweight /dashboard 'Today' view (KPIs, alerts, pending actions only -- what a manager checks first each morning), a dedicated /operations page for the 5 planning-agent outputs in plain-language framing (not raw JSON-shaped cards), and Swiggy Market Intelligence promoted to its own dedicated /market page (competitor pricing, occupancy, Instamart procurement) so it has a clear, demo-able home separate from internal ops data -- matching the product's own internal-vs-Swiggy-data distinction already documented in CLAUDE.md. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts.</t>
+          <t>The single /dashboard page currently tries to show demand forecast + reservations + complaints + inventory + market intel + menu + critic + connector status all at once -- reads as a diagnostics dump a manager could get lost in. Restructure into: a lightweight /dashboard 'Today' view (KPIs, alerts, pending actions only -- what a manager checks first each morning), a dedicated /operations page for the 5 planning-agent outputs in plain-language framing (not raw JSON-shaped cards), and Swiggy Market Intelligence promoted to its own dedicated /market page (competitor pricing, occupancy, Instamart procurement) so it has a clear, demo-able home separate from internal ops data -- matching the product's own internal-vs-Swiggy-data distinction already documented in CLAUDE.md. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. DONE 2026-07-04: split shipped -- /dashboard is now the lightweight 'Today' view (TodayIdleState: business KPIs, market intel teaser, actionable ops snapshot), /operations holds the 5 agent-card detail + CriticBanner + ForecastChart + ManagerActionPanel (via useSelectedRun, reads ?run={id} or falls back to most recent), /market is the dedicated Swiggy market intelligence page. Verified end-to-end via Playwright: fresh register -&gt; idle state renders clean in both themes -&gt; trigger a plan via the new PlanShiftModal -&gt; auto-redirects to /operations?run={id} with the CriticBanner visible on landing, zero console errors.</t>
         </is>
       </c>
       <c r="F84" s="56" t="inlineStr">
         <is>
-          <t>feat: split dashboard into /dashboard (Today), /operations, /market</t>
+          <t>feat(P6-F11/F12): redesign Today dashboard -- modal planning flow, market-aware layout, warm theme</t>
         </is>
       </c>
       <c r="G84" s="56" t="inlineStr">
@@ -17365,7 +17367,7 @@
       </c>
       <c r="H84" s="63" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I84" s="49" t="inlineStr">
@@ -17378,10 +17380,14 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K84" s="55" t="n"/>
-      <c r="L84" s="59" t="n"/>
+      <c r="K84" s="84" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L84" s="85" t="n">
+        <v>46207</v>
+      </c>
       <c r="M84" s="58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" s="55" t="inlineStr">
         <is>
@@ -17760,7 +17766,183 @@
       <c r="O95" s="52" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="70" t="inlineStr">
+      <c r="A96" s="62" t="inlineStr">
+        <is>
+          <t>P6-F18</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>feature/design-system-theming</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Live market intelligence + business analytics endpoints, independent of planning runs</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>GET /api/v1/market/pulse calls CompetitorEnricher/OccupancyEnricher/ProcurementEnricher directly (no planning run required) and structures diff_pct/direction comparisons server-side, since the raw enrichers return loosely-typed dicts, not a UI-ready shape. GET /api/v1/business/performance computes real revenue/profit via a new MenuItem.cost_price column, daily trend, yesterday/today snapshots, top/bottom dishes, dine-in vs delivery channel split, complaints grouped by keyword-matched category, and peak-hours demand (orders only, so future-dated reservation seed rows don't skew 'when are we actually busy'). DONE 2026-07-04: verified against seeded data -- revenue, margin, and complaint-category counts all match expected values. NOTE: this commit's message (eaef859) and an earlier CLAUDE.md pass informally used the tag 'P6-F16', which collides with an already-used tag from the P6-F14/F15/F17 PR (2026-07-01) that was never given tracker rows -- P6-F18 is the correct sequential tracker ID; the git history is left as-is rather than rewritten.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>feat(P6-F16 in commit msg / P6-F18 in tracker): live market intelligence + business analytics, independent of planning runs</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>CLAUDE.md (API routes section, Swiggy token/circuit-breaker gotcha)</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K96" s="87" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L96" s="87" t="n">
+        <v>46207</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>P6-S15</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Hit /market/pulse and /business/performance directly against seeded data; confirm revenue/margin/complaint-category numbers match the seed script, and market pulse returns swiggy_connected + live comparisons when the token is valid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="86" t="n"/>
+      <c r="B97" s="86" t="n"/>
+      <c r="C97" s="86" t="n"/>
+      <c r="D97" s="86" t="n"/>
+      <c r="E97" s="86" t="n"/>
+      <c r="F97" s="86" t="n"/>
+      <c r="G97" s="86" t="n"/>
+      <c r="H97" s="86" t="n"/>
+      <c r="I97" s="86" t="n"/>
+      <c r="J97" s="86" t="n"/>
+      <c r="K97" s="86" t="n"/>
+      <c r="L97" s="86" t="n"/>
+      <c r="M97" s="86" t="n"/>
+      <c r="N97" s="86" t="n"/>
+      <c r="O97" s="86" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="62" t="inlineStr">
+        <is>
+          <t>P6-F19</t>
+        </is>
+      </c>
+      <c r="B98" s="69" t="inlineStr">
+        <is>
+          <t>feature/design-system-theming</t>
+        </is>
+      </c>
+      <c r="C98" s="55" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D98" s="56" t="inlineStr">
+        <is>
+          <t>Today dashboard redesign: modal planning flow, warm theme, NavBar cleanup, date-relative seed data</t>
+        </is>
+      </c>
+      <c r="E98" s="56" t="inlineStr">
+        <is>
+          <t>TodayIdleState fully rewritten around a manager's actual priorities: overall performance chart, actionable 'tonight at a glance' reservations/inventory snapshot, yesterday's business KPIs with channel split, menu performance (top/bottom sellers), peak hours paired with a merged guest-sentiment + complaint-theme card, and a consolidated market intelligence card teasing into /market. 'Plan your next shift' now opens PlanShiftModal instead of running inline. NavBar: removed the scenario dropdown (the modal owns scenario selection now) and the stale 'Friday Rush -- not planned yet' status chip; warmer brand mark and active-tab styling. globals.css light-mode tokens rebuilt around a warm stone/parchment palette instead of cool blue-gray. Also fixed a glitch where the critic-approved banner flashed on /dashboard for one frame and vanished on redirect to /operations -- /operations now shows CriticBanner directly instead of burying the verdict in the Manager Brief modal. seed_demo_data.py no longer hardcodes 2026 calendar dates -- SEED_AS_OF anchors to run-time so 'Today' always reflects live state, and inventory was rebalanced from a permanent 11/18 shortage state to 3/18 genuinely low items. DONE 2026-07-04: verified end-to-end via Playwright (fresh register, both themes, full plan-run -&gt; redirect -&gt; critic banner flow), zero console errors.</t>
+        </is>
+      </c>
+      <c r="F98" s="56" t="inlineStr">
+        <is>
+          <t>feat(P6-F11/F12): redesign Today dashboard -- modal planning flow, market-aware layout, warm theme</t>
+        </is>
+      </c>
+      <c r="G98" s="56" t="inlineStr">
+        <is>
+          <t>CLAUDE.md (page map, theming section)</t>
+        </is>
+      </c>
+      <c r="H98" s="63" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I98" s="49" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J98" s="55" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K98" s="84" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L98" s="85" t="n">
+        <v>46207</v>
+      </c>
+      <c r="M98" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" s="55" t="inlineStr">
+        <is>
+          <t>P6-F11; P6-F18</t>
+        </is>
+      </c>
+      <c r="O98" s="56" t="inlineStr">
+        <is>
+          <t>Playwright: register -&gt; idle state renders clean (light+dark, no console errors) -&gt; open PlanShiftModal -&gt; Generate Plan -&gt; auto-redirect to /operations?run={id} with CriticBanner visible, no flash/glitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="86" t="n"/>
+      <c r="B99" s="86" t="n"/>
+      <c r="C99" s="86" t="n"/>
+      <c r="D99" s="86" t="n"/>
+      <c r="E99" s="86" t="n"/>
+      <c r="F99" s="86" t="n"/>
+      <c r="G99" s="86" t="n"/>
+      <c r="H99" s="86" t="n"/>
+      <c r="I99" s="86" t="n"/>
+      <c r="J99" s="86" t="n"/>
+      <c r="K99" s="86" t="n"/>
+      <c r="L99" s="86" t="n"/>
+      <c r="M99" s="86" t="n"/>
+      <c r="N99" s="86" t="n"/>
+      <c r="O99" s="86" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="70" t="inlineStr">
         <is>
           <t>→ DEMO 1  |  all above on main, docs updated, screenshots done — record full Swiggy read + AI + voice + live monitor demo ←</t>
         </is>
@@ -17769,7 +17951,6 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B40:B49"/>
-    <mergeCell ref="A96:O96"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B52:B54"/>
@@ -17777,6 +17958,7 @@
     <mergeCell ref="B32:B36"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B25:B28"/>
+    <mergeCell ref="A100:O100"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Phase Tracker ( 1 - 5 )" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Phase 6" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Staging Creds + Phase 7" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Doc Strategy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Git Practices" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Tracker ( 1 - 5 )" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 6" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staging Creds + Phase 7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doc Strategy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git Practices" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -172,8 +172,42 @@
       <color rgb="FF7F7F7F"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="005F5E5A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005F5E5A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A1A18"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A1A18"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="29">
+  <fills count="43">
     <fill>
       <patternFill/>
     </fill>
@@ -317,8 +351,78 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F1B2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F6E56"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1F5EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1EFE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00534AB7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEDFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00444441"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00854F0B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAEEDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00993C1D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAECE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCEBEB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -498,11 +602,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D1C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D1C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D1C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D1C7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -737,6 +855,129 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="31" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="31" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="32" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="32" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="33" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="32" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="36" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="34" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="39" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="41" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="34" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1065,12 +1306,12 @@
     <row r="3" ht="14.4" customHeight="1" s="72">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Current milestone: Phase 6 -- P6-S21-S30 (this branch's hardening fixes) complete; inventory now cites live Swiggy Instamart prices end-to-end, replan loop + critic converge to approved on first pass. Next: P6-MI01-04 (market intel expansion) or P6-S39-S41 (follow-ups).</t>
+          <t>Current: Phase 6 — 41 done. Next: P6-MI05 to MI11 (market intel expansion)</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>35 of 62 Phase 6 tasks done. Staging-blocked work + docs/milestone-merge + Phase 7 now tracked separately in the 'Staging Creds + Phase 7' sheet.</t>
+          <t>13 Swiggy tools live. Adding: search_menu (enricher), fetch_food_coupons, get_restaurant_details, slot deals[]</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1101,12 +1342,12 @@
     <row r="4" ht="14.4" customHeight="1" s="72">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Last completed: P6-S30 -- Windows console-encoding crash fix (was silently 500ing every planning run)</t>
+          <t>Last done: P6-F19 — Today dashboard redesign + modal planning flow</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>P6-S28 rewritten to reflect the real bug found (inventory price-ordering + guardrail discarding the Swiggy citation, not the originally-planned occupancy-context gap); P6-S29 resolved (AGENTS.md injected line removed per user decision). All live-verified end to end, including a Playwright check that the Swiggy price citation renders correctly in the actual /runs UI.</t>
+          <t>Design system, 11-node pipeline, enrichers, market/operations/connectors pages shipped</t>
         </is>
       </c>
       <c r="C4" s="1" t="n"/>
@@ -1137,12 +1378,12 @@
     <row r="5" ht="14.4" customHeight="1" s="72">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Build order: S07/S08/S09 (enrichers) → S10-S13 (new nodes + diffs) → F04/F06 (frontend) → S14 (action queue) → F01/F02 → S15/S16</t>
+          <t>Priority: MI05-MI11 → S32/F06 → S33/S34 → S36/F07/F08 → R01 → staging creds → P7</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>SWIGGY_INTEGRATION.md now has response schemas (section 16) + tool→DB mapping table (section 17)</t>
+          <t>UI redesign: use Claude Design per page (Priority 7 — after features complete)</t>
         </is>
       </c>
       <c r="C5" s="1" t="n"/>
@@ -1173,12 +1414,12 @@
     <row r="6" ht="14.4" customHeight="1" s="72">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Staging creds status</t>
+          <t>Staging creds from Swiggy unlock: S43 (Instamart checkout) S44 (Dineout booking) S45 (computer use)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Pending from Swiggy. Needed ONLY for checkout + book_table (P6-S43, P6-S44). Everything else works with production OAuth token.</t>
+          <t>Token: cjpfcd75ofl5oefqs8mg address. Run scripts/get_swiggy_token.py to refresh (5-day TTL)</t>
         </is>
       </c>
       <c r="C6" s="1" t="n"/>
@@ -13272,4693 +13513,4900 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O100"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12" defaultRowHeight="30" customHeight="1"/>
+  <dimension ref="A1:O94"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="71" min="1" max="1"/>
-    <col width="27" customWidth="1" style="71" min="2" max="2"/>
-    <col width="15" customWidth="1" style="71" min="3" max="3"/>
-    <col width="32" customWidth="1" style="71" min="4" max="4"/>
-    <col width="58" customWidth="1" style="71" min="5" max="5"/>
-    <col width="40" customWidth="1" style="71" min="6" max="6"/>
-    <col width="30" customWidth="1" style="71" min="7" max="7"/>
-    <col width="13" customWidth="1" style="71" min="8" max="8"/>
-    <col width="11" customWidth="1" style="71" min="9" max="9"/>
+    <col width="10" customWidth="1" style="72" min="1" max="1"/>
+    <col width="26" customWidth="1" style="72" min="2" max="2"/>
+    <col width="14" customWidth="1" style="72" min="3" max="3"/>
+    <col width="30" customWidth="1" style="72" min="4" max="4"/>
+    <col width="46" customWidth="1" style="72" min="5" max="5"/>
+    <col width="30" customWidth="1" style="72" min="6" max="6"/>
+    <col width="28" customWidth="1" style="72" min="7" max="7"/>
+    <col width="11" customWidth="1" style="72" min="8" max="8"/>
+    <col width="9" customWidth="1" style="72" min="9" max="9"/>
     <col width="10" customWidth="1" style="72" min="10" max="10"/>
-    <col width="12" customWidth="1" style="71" min="11" max="11"/>
-    <col width="12" customWidth="1" style="72" min="12" max="12"/>
-    <col width="9" customWidth="1" style="72" min="13" max="13"/>
+    <col width="11" customWidth="1" style="72" min="11" max="11"/>
+    <col width="11" customWidth="1" style="72" min="12" max="12"/>
+    <col width="8" customWidth="1" style="72" min="13" max="13"/>
     <col width="16" customWidth="1" style="72" min="14" max="14"/>
-    <col width="46" customWidth="1" style="72" min="15" max="15"/>
-    <col width="12" customWidth="1" style="71" min="16" max="17"/>
-    <col width="12" customWidth="1" style="71" min="18" max="16384"/>
+    <col width="30" customWidth="1" style="72" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.95" customHeight="1" s="72">
-      <c r="A1" s="43" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="72">
+      <c r="A1" s="88" t="inlineStr">
+        <is>
+          <t>CortexKitchen — Phase 6 (41 complete · planned in priority order · staging blocked at bottom)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="72">
+      <c r="A2" s="89" t="inlineStr">
         <is>
           <t>Task ID</t>
         </is>
       </c>
-      <c r="B1" s="43" t="inlineStr">
+      <c r="B2" s="89" t="inlineStr">
         <is>
           <t>Feature Branch</t>
         </is>
       </c>
-      <c r="C1" s="43" t="inlineStr">
+      <c r="C2" s="89" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="D1" s="43" t="inlineStr">
+      <c r="D2" s="89" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E1" s="43" t="inlineStr">
-        <is>
-          <t>Detailed Outcome / Done Means</t>
-        </is>
-      </c>
-      <c r="F1" s="43" t="inlineStr">
-        <is>
-          <t>PR Description Hook</t>
-        </is>
-      </c>
-      <c r="G1" s="43" t="inlineStr">
+      <c r="E2" s="89" t="inlineStr">
+        <is>
+          <t>Detailed Outcome</t>
+        </is>
+      </c>
+      <c r="F2" s="89" t="inlineStr">
+        <is>
+          <t>PR Hook</t>
+        </is>
+      </c>
+      <c r="G2" s="89" t="inlineStr">
         <is>
           <t>Docs Updated</t>
         </is>
       </c>
-      <c r="H1" s="43" t="inlineStr">
+      <c r="H2" s="89" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="43" t="inlineStr">
+      <c r="I2" s="89" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="J1" s="43" t="inlineStr">
+      <c r="J2" s="89" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="K1" s="43" t="inlineStr">
+      <c r="K2" s="89" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="L1" s="43" t="inlineStr">
+      <c r="L2" s="89" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M1" s="43" t="inlineStr">
+      <c r="M2" s="89" t="inlineStr">
         <is>
           <t>% Done</t>
         </is>
       </c>
-      <c r="N1" s="43" t="inlineStr">
+      <c r="N2" s="89" t="inlineStr">
         <is>
           <t>Depends On</t>
         </is>
       </c>
-      <c r="O1" s="43" t="inlineStr">
+      <c r="O2" s="89" t="inlineStr">
         <is>
           <t>Tests Expected</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" s="72">
-      <c r="A2" s="44" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="72">
+      <c r="A3" s="90" t="inlineStr">
+        <is>
+          <t>COMPLETED — 41 tasks done</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52" customHeight="1" s="72">
+      <c r="A4" s="91" t="inlineStr">
         <is>
           <t>P6-S01</t>
         </is>
       </c>
-      <c r="B2" s="66" t="inlineStr">
+      <c r="B4" s="92" t="inlineStr">
         <is>
           <t>feature/per-node-model-routing</t>
         </is>
       </c>
-      <c r="C2" s="46" t="inlineStr">
+      <c r="C4" s="92" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D2" s="47" t="inlineStr">
+      <c r="D4" s="92" t="inlineStr">
         <is>
           <t>Per-node model tier routing via CometAPI</t>
         </is>
       </c>
-      <c r="E2" s="47" t="inlineStr">
+      <c r="E4" s="92" t="inlineStr">
         <is>
           <t>CometProvider (AsyncOpenAI), 3-tier registry (fast/balanced/strong), llm_registry in OrchestratorState, node-level tier overrides, cost tracking. Fan-out latency: 48.7s → 17s.</t>
         </is>
       </c>
-      <c r="F2" s="47" t="inlineStr">
+      <c r="F4" s="92" t="inlineStr">
         <is>
           <t>feat: per-node model tier routing via CometAPI</t>
         </is>
       </c>
-      <c r="G2" s="47" t="inlineStr">
+      <c r="G4" s="92" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md, docs/DECISIONS.md</t>
         </is>
       </c>
-      <c r="H2" s="48" t="inlineStr">
+      <c r="H4" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I2" s="49" t="inlineStr">
+      <c r="I4" s="91" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J2" s="46" t="inlineStr">
+      <c r="J4" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K2" s="50" t="n">
+      <c r="K4" s="94" t="n">
         <v>46192</v>
       </c>
-      <c r="L2" s="50" t="n">
+      <c r="L4" s="94" t="n">
         <v>46192</v>
       </c>
-      <c r="M2" s="51" t="n">
+      <c r="M4" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="46" t="inlineStr">
+      <c r="N4" s="92" t="inlineStr">
         <is>
           <t>P5-13</t>
         </is>
       </c>
-      <c r="O2" s="47" t="inlineStr">
+      <c r="O4" s="92" t="inlineStr">
         <is>
           <t>LangSmith traces show per-node model; cost_usd tracked per tier</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="7.95" customHeight="1" s="72">
-      <c r="A3" s="52" t="n"/>
-      <c r="B3" s="52" t="n"/>
-      <c r="C3" s="52" t="n"/>
-      <c r="D3" s="52" t="n"/>
-      <c r="E3" s="52" t="n"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="52" t="n"/>
-      <c r="H3" s="52" t="n"/>
-      <c r="I3" s="52" t="n"/>
-      <c r="J3" s="52" t="n"/>
-      <c r="K3" s="52" t="n"/>
-      <c r="L3" s="52" t="n"/>
-      <c r="M3" s="52" t="n"/>
-      <c r="N3" s="52" t="n"/>
-      <c r="O3" s="52" t="n"/>
-    </row>
-    <row r="4" ht="60" customHeight="1" s="72">
-      <c r="A4" s="44" t="inlineStr">
+    <row r="5" ht="52" customHeight="1" s="72">
+      <c r="A5" s="96" t="inlineStr">
         <is>
           <t>P6-S02</t>
         </is>
       </c>
-      <c r="B4" s="66" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>feature/assumption-diffing</t>
         </is>
       </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D5" s="97" t="inlineStr">
         <is>
           <t>Cross-agent assumption diffing</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E5" s="97" t="inlineStr">
         <is>
           <t>4 domain nodes write assumptions dicts. EvaluationSanityChecker._diff_assumptions() runs 3 cross-diffs post fan-out. stale_assumptions injected into critic prompt + returned in API. final_assembler bug fix. 9 docs updated.</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F5" s="97" t="inlineStr">
         <is>
           <t>feat: cross-agent assumption diffing — O(N²) → O(N)</t>
         </is>
       </c>
-      <c r="G4" s="47" t="inlineStr">
+      <c r="G5" s="97" t="inlineStr">
         <is>
           <t>9 docs updated</t>
         </is>
       </c>
-      <c r="H4" s="48" t="inlineStr">
+      <c r="H5" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I5" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J4" s="46" t="inlineStr">
+      <c r="J5" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K4" s="50" t="n">
+      <c r="K5" s="98" t="n">
         <v>46199</v>
       </c>
-      <c r="L4" s="50" t="n">
+      <c r="L5" s="98" t="n">
         <v>46199</v>
       </c>
-      <c r="M4" s="51" t="n">
+      <c r="M5" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="46" t="inlineStr">
+      <c r="N5" s="97" t="inlineStr">
         <is>
           <t>P6-S01</t>
         </is>
       </c>
-      <c r="O4" s="47" t="inlineStr">
+      <c r="O5" s="97" t="inlineStr">
         <is>
           <t>Existing sanity checker tests pass; stale_assumptions in API response</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="7.95" customHeight="1" s="72">
-      <c r="A5" s="52" t="n"/>
-      <c r="B5" s="52" t="n"/>
-      <c r="C5" s="52" t="n"/>
-      <c r="D5" s="52" t="n"/>
-      <c r="E5" s="52" t="n"/>
-      <c r="F5" s="52" t="n"/>
-      <c r="G5" s="52" t="n"/>
-      <c r="H5" s="52" t="n"/>
-      <c r="I5" s="52" t="n"/>
-      <c r="J5" s="52" t="n"/>
-      <c r="K5" s="52" t="n"/>
-      <c r="L5" s="52" t="n"/>
-      <c r="M5" s="52" t="n"/>
-      <c r="N5" s="52" t="n"/>
-      <c r="O5" s="52" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1" s="72">
-      <c r="A6" s="44" t="inlineStr">
+    <row r="6" ht="52" customHeight="1" s="72">
+      <c r="A6" s="91" t="inlineStr">
         <is>
           <t>P6-S03</t>
         </is>
       </c>
-      <c r="B6" s="66" t="inlineStr">
+      <c r="B6" s="92" t="inlineStr">
         <is>
           <t>feature/drop-diff1-reseed-data</t>
         </is>
       </c>
-      <c r="C6" s="46" t="inlineStr">
+      <c r="C6" s="92" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D6" s="47" t="inlineStr">
+      <c r="D6" s="92" t="inlineStr">
         <is>
           <t>Drop Diff 1, v3 reseed, stale_assumptions API fix</t>
         </is>
       </c>
-      <c r="E6" s="47" t="inlineStr">
+      <c r="E6" s="92" t="inlineStr">
         <is>
           <t>Diff 1 removed (MenuService self-queries inventory — parallel execution means diff fires as false positive). v3 seed data. stale_assumptions passthrough fixed in final_assembler.</t>
         </is>
       </c>
-      <c r="F6" s="47" t="inlineStr">
+      <c r="F6" s="92" t="inlineStr">
         <is>
           <t>fix: drop Diff 1 false positive, v3 reseed, stale_assumptions API fix</t>
         </is>
       </c>
-      <c r="G6" s="47" t="inlineStr">
+      <c r="G6" s="92" t="inlineStr">
         <is>
           <t>docs/AGENTS.md</t>
         </is>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="H6" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I6" s="49" t="inlineStr">
+      <c r="I6" s="91" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" s="46" t="inlineStr">
+      <c r="J6" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K6" s="50" t="n">
+      <c r="K6" s="94" t="n">
         <v>46199</v>
       </c>
-      <c r="L6" s="50" t="n">
+      <c r="L6" s="94" t="n">
         <v>46199</v>
       </c>
-      <c r="M6" s="51" t="n">
+      <c r="M6" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="46" t="inlineStr">
+      <c r="N6" s="92" t="inlineStr">
         <is>
           <t>P6-S02</t>
         </is>
       </c>
-      <c r="O6" s="47" t="inlineStr">
+      <c r="O6" s="92" t="inlineStr">
         <is>
           <t>3 remaining diffs fire correctly; API response carries stale_assumptions</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="7.95" customHeight="1" s="72">
-      <c r="A7" s="52" t="n"/>
-      <c r="B7" s="52" t="n"/>
-      <c r="C7" s="52" t="n"/>
-      <c r="D7" s="52" t="n"/>
-      <c r="E7" s="52" t="n"/>
-      <c r="F7" s="52" t="n"/>
-      <c r="G7" s="52" t="n"/>
-      <c r="H7" s="52" t="n"/>
-      <c r="I7" s="52" t="n"/>
-      <c r="J7" s="52" t="n"/>
-      <c r="K7" s="52" t="n"/>
-      <c r="L7" s="52" t="n"/>
-      <c r="M7" s="52" t="n"/>
-      <c r="N7" s="52" t="n"/>
-      <c r="O7" s="52" t="n"/>
-    </row>
-    <row r="8" ht="85.95" customHeight="1" s="72">
-      <c r="A8" s="44" t="inlineStr">
+    <row r="7" ht="52" customHeight="1" s="72">
+      <c r="A7" s="96" t="inlineStr">
         <is>
           <t>P6-S04</t>
         </is>
       </c>
-      <c r="B8" s="66" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>feature/swiggy-base-connector</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C7" s="97" t="inlineStr">
         <is>
           <t>Integrations</t>
         </is>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D7" s="97" t="inlineStr">
         <is>
           <t>BaseConnector + SwiggyMCPClient</t>
         </is>
       </c>
-      <c r="E8" s="47" t="inlineStr">
+      <c r="E7" s="97" t="inlineStr">
         <is>
           <t>Abstract BaseConnector ABC with sync() and enrich() methods. SwiggyMCPClient: per-org OAuth token (5-day TTL, re-auth on 401, encrypted storage), JSON-RPC 2.0 calls to /food + /im + /dineout, exponential backoff retry, is_available() check, structured logging. Absorbs original P6-01.</t>
         </is>
       </c>
-      <c r="F8" s="47" t="inlineStr">
+      <c r="F7" s="97" t="inlineStr">
         <is>
           <t>feat: connector layer — BaseConnector ABC + SwiggyMCPClient with per-org OAuth</t>
         </is>
       </c>
-      <c r="G8" s="47" t="inlineStr">
+      <c r="G7" s="97" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md (connector layer section), docs/DECISIONS.md (D-019), docs/DATA_MODEL.md, CLAUDE.md (new), docs/SWIGGY_INTEGRATION.md</t>
         </is>
       </c>
-      <c r="H8" s="48" t="inlineStr">
+      <c r="H7" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I8" s="53" t="inlineStr">
+      <c r="I7" s="96" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J8" s="46" t="inlineStr">
+      <c r="J7" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K8" s="50" t="n">
+      <c r="K7" s="98" t="n">
         <v>46200</v>
       </c>
-      <c r="L8" s="50" t="n">
+      <c r="L7" s="98" t="n">
         <v>46200</v>
       </c>
-      <c r="M8" s="51" t="n">
+      <c r="M7" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N8" s="46" t="inlineStr">
+      <c r="N7" s="97" t="inlineStr">
         <is>
           <t>P6-S03</t>
         </is>
       </c>
-      <c r="O8" s="47" t="inlineStr">
+      <c r="O7" s="97" t="inlineStr">
         <is>
           <t>13/13 pass — test_swiggy_client.py (7): is_available, 401 no-retry, 500 retry x2, success data, never raises, success=false; test_connector_repository.py (6): upsert create, upsert idempotent, get none, error_count increment, error clear on success, list_active filter</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="73.05" customHeight="1" s="72">
-      <c r="A9" s="44" t="inlineStr">
+    <row r="8" ht="52" customHeight="1" s="72">
+      <c r="A8" s="91" t="inlineStr">
         <is>
           <t>P6-S05</t>
         </is>
       </c>
-      <c r="B9" s="68" t="n"/>
-      <c r="C9" s="55" t="inlineStr">
+      <c r="B8" s="92" t="n"/>
+      <c r="C8" s="92" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D9" s="56" t="inlineStr">
+      <c r="D8" s="92" t="inlineStr">
         <is>
           <t>connectors table + async job queue</t>
         </is>
       </c>
-      <c r="E9" s="56" t="inlineStr">
+      <c r="E8" s="92" t="inlineStr">
         <is>
           <t>Alembic migration: connectors table (org_id, connector_type, access_token_encrypted, token_expires_at, last_sync_at, sync_status, error_count). Redis job queue for async planning runs (absorbs original P6-02): job_id, status endpoint, dedup by scenario+date, non-blocking HTTP.</t>
         </is>
       </c>
-      <c r="F9" s="56" t="inlineStr">
+      <c r="F8" s="92" t="inlineStr">
         <is>
           <t>feat: connectors table + async Redis job queue for planning runs</t>
         </is>
       </c>
-      <c r="G9" s="56" t="inlineStr">
+      <c r="G8" s="92" t="inlineStr">
         <is>
           <t>docs/DATA_MODEL.md (connectors table, orders/reservations/feedback new cols), docs/ARCHITECTURE.md, docs/DECISIONS.md (D-019)</t>
         </is>
       </c>
-      <c r="H9" s="48" t="inlineStr">
+      <c r="H8" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I9" s="53" t="inlineStr">
+      <c r="I8" s="91" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J9" s="55" t="inlineStr">
+      <c r="J8" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K9" s="57" t="n">
+      <c r="K8" s="94" t="n">
         <v>46200</v>
       </c>
-      <c r="L9" s="57" t="n">
+      <c r="L8" s="94" t="n">
         <v>46200</v>
       </c>
-      <c r="M9" s="58" t="n">
+      <c r="M8" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N9" s="55" t="inlineStr">
+      <c r="N8" s="92" t="inlineStr">
         <is>
           <t>P6-S04</t>
         </is>
       </c>
-      <c r="O9" s="56" t="inlineStr">
+      <c r="O8" s="92" t="inlineStr">
         <is>
           <t>Migration smoke test (alembic upgrade head verified live on DB); connectors table + all new cols confirmed via psycopg2; swiggy_delivery enum value present</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="7.95" customHeight="1" s="72">
-      <c r="A10" s="52" t="n"/>
-      <c r="B10" s="52" t="n"/>
-      <c r="C10" s="52" t="n"/>
-      <c r="D10" s="52" t="n"/>
-      <c r="E10" s="52" t="n"/>
-      <c r="F10" s="52" t="n"/>
-      <c r="G10" s="52" t="n"/>
-      <c r="H10" s="52" t="n"/>
-      <c r="I10" s="52" t="n"/>
-      <c r="J10" s="52" t="n"/>
-      <c r="K10" s="52" t="n"/>
-      <c r="L10" s="52" t="n"/>
-      <c r="M10" s="52" t="n"/>
-      <c r="N10" s="52" t="n"/>
-      <c r="O10" s="52" t="n"/>
-    </row>
-    <row r="11" ht="99" customHeight="1" s="72">
-      <c r="A11" s="44" t="inlineStr">
+    <row r="9" ht="52" customHeight="1" s="72">
+      <c r="A9" s="96" t="inlineStr">
         <is>
           <t>P6-S06</t>
         </is>
       </c>
-      <c r="B11" s="69" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>feature/swiggy-sync-orders</t>
         </is>
       </c>
-      <c r="C11" s="55" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>Integrations</t>
         </is>
       </c>
-      <c r="D11" s="56" t="inlineStr">
+      <c r="D9" s="97" t="inlineStr">
         <is>
           <t>Sync Swiggy orders → orders table</t>
         </is>
       </c>
-      <c r="E11" s="56" t="inlineStr">
+      <c r="E9" s="97" t="inlineStr">
         <is>
           <t>Completed — NOTE: syncs PERSONAL consumer orders (your Swiggy food deliveries), NOT a restaurant incoming orders. Swiggy MCP is consumer-facing. Restaurant order data needs Swiggy Partner API. Sync infrastructure built but data is not meaningful for restaurant planning nodes.</t>
         </is>
       </c>
-      <c r="F11" s="56" t="inlineStr">
+      <c r="F9" s="97" t="inlineStr">
         <is>
           <t>feat: swiggy order sync — get_food_orders nightly → orders table (source=swiggy, channel=delivery)</t>
         </is>
       </c>
-      <c r="G11" s="56" t="inlineStr">
+      <c r="G9" s="97" t="inlineStr">
         <is>
           <t>docs/SWIGGY_INTEGRATION.md (P6-S06 ✅, status header updated)</t>
         </is>
       </c>
-      <c r="H11" s="48" t="inlineStr">
+      <c r="H9" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I11" s="49" t="inlineStr">
+      <c r="I9" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J11" s="55" t="inlineStr">
+      <c r="J9" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K11" s="57" t="n">
+      <c r="K9" s="98" t="n">
         <v>46200</v>
       </c>
-      <c r="L11" s="57" t="n">
+      <c r="L9" s="98" t="n">
         <v>46200</v>
       </c>
-      <c r="M11" s="58" t="n">
+      <c r="M9" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N11" s="55" t="inlineStr">
+      <c r="N9" s="97" t="inlineStr">
         <is>
           <t>P6-S05</t>
         </is>
       </c>
-      <c r="O11" s="56" t="inlineStr">
+      <c r="O9" s="97" t="inlineStr">
         <is>
           <t>8/8 pass — correct count, correct Order fields (source/channel/is_delivery), placeholder MenuItem creation (is_available=False, category=swiggy_import), reuse existing MenuItem by name, idempotency on duplicate sync, None call_tool graceful, empty order list, external_order_id format SW-001_0/SW-001_1</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="7.95" customHeight="1" s="72">
-      <c r="A12" s="52" t="n"/>
-      <c r="B12" s="52" t="n"/>
-      <c r="C12" s="52" t="n"/>
-      <c r="D12" s="52" t="n"/>
-      <c r="E12" s="52" t="n"/>
-      <c r="F12" s="52" t="n"/>
-      <c r="G12" s="52" t="n"/>
-      <c r="H12" s="52" t="n"/>
-      <c r="I12" s="52" t="n"/>
-      <c r="J12" s="52" t="n"/>
-      <c r="K12" s="52" t="n"/>
-      <c r="L12" s="52" t="n"/>
-      <c r="M12" s="52" t="n"/>
-      <c r="N12" s="52" t="n"/>
-      <c r="O12" s="52" t="n"/>
-    </row>
-    <row r="13" ht="73.05" customHeight="1" s="72">
-      <c r="A13" s="44" t="inlineStr">
+    <row r="10" ht="52" customHeight="1" s="72">
+      <c r="A10" s="91" t="inlineStr">
         <is>
           <t>P6-S07</t>
         </is>
       </c>
-      <c r="B13" s="69" t="inlineStr">
+      <c r="B10" s="92" t="inlineStr">
         <is>
           <t>feature/swiggy-base-connector</t>
         </is>
       </c>
-      <c r="C13" s="55" t="inlineStr">
+      <c r="C10" s="92" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D13" s="56" t="inlineStr">
+      <c r="D10" s="92" t="inlineStr">
         <is>
           <t>Redis-backed circuit breaker for SwiggyMCPClient</t>
         </is>
       </c>
-      <c r="E13" s="56" t="inlineStr">
+      <c r="E10" s="92" t="inlineStr">
         <is>
           <t>3 failures in 5 min → circuit opens for 30 min, auto-resets via TTL. On Redis down → fail open (let call through). Per-endpoint circuit keys. Added beyond spec — production resilience for Swiggy MCP calls. Integrated into call_tool() in SwiggyMCPClient.</t>
         </is>
       </c>
-      <c r="F13" s="56" t="inlineStr">
+      <c r="F10" s="92" t="inlineStr">
         <is>
           <t>feat: Redis circuit breaker for Swiggy MCP calls — 3-failure threshold, 30min open, fail-open on Redis down</t>
         </is>
       </c>
-      <c r="G13" s="56" t="inlineStr">
+      <c r="G10" s="92" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md (circuit breaker section), docs/SWIGGY_INTEGRATION.md</t>
         </is>
       </c>
-      <c r="H13" s="48" t="inlineStr">
+      <c r="H10" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I13" s="49" t="inlineStr">
+      <c r="I10" s="91" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J13" s="55" t="inlineStr">
+      <c r="J10" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K13" s="55" t="n"/>
-      <c r="L13" s="59" t="inlineStr">
+      <c r="K10" s="91" t="n"/>
+      <c r="L10" s="91" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="M13" s="58" t="n">
+      <c r="M10" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="55" t="inlineStr">
+      <c r="N10" s="92" t="inlineStr">
         <is>
           <t>P6-S04</t>
         </is>
       </c>
-      <c r="O13" s="56" t="inlineStr">
+      <c r="O10" s="92" t="inlineStr">
         <is>
           <t>Circuit opens after 3 failures; auto-resets after 30min; fail-open when Redis unavailable; call_tool() returns None immediately when circuit open</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="99" customHeight="1" s="72">
-      <c r="A14" s="44" t="inlineStr">
+    <row r="11" ht="52" customHeight="1" s="72">
+      <c r="A11" s="96" t="inlineStr">
         <is>
           <t>P6-S08</t>
         </is>
       </c>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="B11" s="97" t="n"/>
+      <c r="C11" s="97" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D11" s="97" t="inlineStr">
         <is>
           <t>Capability-to-provider registry</t>
         </is>
       </c>
-      <c r="E14" s="47" t="inlineStr">
+      <c r="E11" s="97" t="inlineStr">
         <is>
           <t>Maps planning capabilities to ordered provider lists: competitor_pricing → [swiggy, zomato], reservation_data → [swiggy, eazydiner], procurement → [swiggy], order_history → [swiggy, zomato]. Routes to highest-priority provider with active connector row for the org. Adding Zomato = 1 new connector file + 1 registry entry. No DB migration needed — reads from connectors table.</t>
         </is>
       </c>
-      <c r="F14" s="47" t="inlineStr">
+      <c r="F11" s="97" t="inlineStr">
         <is>
           <t>feat: ProviderRegistry — capability routing with multi-provider fallback, future Zomato/EazyDiner-ready</t>
         </is>
       </c>
-      <c r="G14" s="47" t="inlineStr">
+      <c r="G11" s="97" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md (provider registry section), docs/CONNECTORS.md</t>
         </is>
       </c>
-      <c r="H14" s="48" t="inlineStr">
+      <c r="H11" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I14" s="49" t="inlineStr">
+      <c r="I11" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J14" s="46" t="inlineStr">
+      <c r="J11" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K14" s="46" t="n"/>
-      <c r="L14" s="60" t="inlineStr">
+      <c r="K11" s="96" t="n"/>
+      <c r="L11" s="96" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="M14" s="51" t="n">
+      <c r="M11" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N14" s="46" t="inlineStr">
+      <c r="N11" s="97" t="inlineStr">
         <is>
           <t>P6-S05</t>
         </is>
       </c>
-      <c r="O14" s="47" t="inlineStr">
+      <c r="O11" s="97" t="inlineStr">
         <is>
           <t>competitor_pricing routes to swiggy when active; routes to zomato when swiggy connector missing; list_active used to determine available providers</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="7.95" customHeight="1" s="72">
-      <c r="A15" s="52" t="n"/>
-      <c r="B15" s="52" t="n"/>
-      <c r="C15" s="52" t="n"/>
-      <c r="D15" s="52" t="n"/>
-      <c r="E15" s="52" t="n"/>
-      <c r="F15" s="52" t="n"/>
-      <c r="G15" s="52" t="n"/>
-      <c r="H15" s="52" t="n"/>
-      <c r="I15" s="52" t="n"/>
-      <c r="J15" s="52" t="n"/>
-      <c r="K15" s="52" t="n"/>
-      <c r="L15" s="52" t="n"/>
-      <c r="M15" s="52" t="n"/>
-      <c r="N15" s="52" t="n"/>
-      <c r="O15" s="52" t="n"/>
-    </row>
-    <row r="16" ht="190.05" customHeight="1" s="72">
-      <c r="A16" s="44" t="inlineStr">
+    <row r="12" ht="52" customHeight="1" s="72">
+      <c r="A12" s="91" t="inlineStr">
         <is>
           <t>P6-S09</t>
         </is>
       </c>
-      <c r="B16" s="66" t="inlineStr">
+      <c r="B12" s="92" t="inlineStr">
         <is>
           <t>feature/agent-intelligence</t>
         </is>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C12" s="92" t="inlineStr">
         <is>
           <t>Agents + Infra</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D12" s="92" t="inlineStr">
         <is>
           <t>Agent Intelligence Bundle — smarter pipeline + agentic chatbot</t>
         </is>
       </c>
-      <c r="E16" s="47" t="inlineStr">
+      <c r="E12" s="92" t="inlineStr">
         <is>
           <t>Aggregator contradiction detection (pure Python, 0 LLM calls): detects demand_forecast vs inventory conflicts, appends DETECTED CONTRADICTIONS to critic summary. Critic replanning loop: rejected/revision → replan_orchestrator injects critic notes → aggregator re-runs → critic re-evaluates, max 2 retries (+1 LLM call/retry). Qdrant early enrichment: 1 shared retrieval step before parallel nodes, all agents get pre-loaded context. Semantic cache: Qdrant embedding-based lookup (threshold 0.92) for planning runs + chatbot queries. Chatbot tool use: Groq function calling — query_runs, get_run_detail, trigger_planning_run, get_inventory_status. Cross-session memory: Qdrant session summaries per user. Proactive pattern surfacing: chatbot detects recurring critic failures on session start.</t>
         </is>
       </c>
-      <c r="F16" s="47" t="inlineStr">
+      <c r="F12" s="92" t="inlineStr">
         <is>
           <t>feat: agent intelligence — contradiction detection, replanning loop, semantic cache, agentic chatbot</t>
         </is>
       </c>
-      <c r="G16" s="47" t="inlineStr">
+      <c r="G12" s="92" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md (replanning loop, Qdrant enrichment), docs/AGENTS.md (aggregator update)</t>
         </is>
       </c>
-      <c r="H16" s="48" t="inlineStr">
+      <c r="H12" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I16" s="53" t="inlineStr">
+      <c r="I12" s="91" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J16" s="46" t="inlineStr">
+      <c r="J12" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K16" s="50" t="n">
+      <c r="K12" s="94" t="n">
         <v>46200</v>
       </c>
-      <c r="L16" s="50" t="n">
+      <c r="L12" s="94" t="n">
         <v>46201</v>
       </c>
-      <c r="M16" s="51" t="n">
+      <c r="M12" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N16" s="46" t="inlineStr">
+      <c r="N12" s="92" t="inlineStr">
         <is>
           <t>P6-S06</t>
         </is>
       </c>
-      <c r="O16" s="47" t="inlineStr">
+      <c r="O12" s="92" t="inlineStr">
         <is>
           <t>Contradiction detection: demand_forecast vs inventory conflict fires correctly. Replanning: rejected plan routes back, critic re-evaluates with notes. Semantic cache: cache hit returns plan without LLM call. Chatbot tools: query_runs returns structured data; trigger_planning_run starts a run. Cross-session memory: session summary persists in Qdrant, retrieved on next session.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="7.95" customHeight="1" s="72">
-      <c r="A17" s="52" t="n"/>
-      <c r="B17" s="52" t="n"/>
-      <c r="C17" s="52" t="n"/>
-      <c r="D17" s="52" t="n"/>
-      <c r="E17" s="52" t="n"/>
-      <c r="F17" s="52" t="n"/>
-      <c r="G17" s="52" t="n"/>
-      <c r="H17" s="52" t="n"/>
-      <c r="I17" s="52" t="n"/>
-      <c r="J17" s="52" t="n"/>
-      <c r="K17" s="52" t="n"/>
-      <c r="L17" s="52" t="n"/>
-      <c r="M17" s="52" t="n"/>
-      <c r="N17" s="52" t="n"/>
-      <c r="O17" s="52" t="n"/>
-    </row>
-    <row r="18" ht="60" customHeight="1" s="72">
-      <c r="A18" s="44" t="inlineStr">
+    <row r="13" ht="52" customHeight="1" s="72">
+      <c r="A13" s="96" t="inlineStr">
         <is>
           <t>P6-S10</t>
         </is>
       </c>
-      <c r="B18" s="66" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>feature/swiggy-sync-feedback-reservations</t>
         </is>
       </c>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C13" s="97" t="inlineStr">
         <is>
           <t>Integrations</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D13" s="97" t="inlineStr">
         <is>
           <t>Reservation sync skeleton → reservations table</t>
         </is>
       </c>
-      <c r="E18" s="47" t="inlineStr">
+      <c r="E13" s="97" t="inlineStr">
         <is>
           <t>Completed — NOTE: syncs PERSONAL Dineout reservations (tables you booked at other restaurants), NOT your restaurant table bookings. Infrastructure built; data not useful for reservation planning node.</t>
         </is>
       </c>
-      <c r="F18" s="47" t="inlineStr">
+      <c r="F13" s="97" t="inlineStr">
         <is>
           <t>feat: reservation sync skeleton — get_booking_status → reservations table, register_booking_order_id for DineoutExecutor (P6-S44)</t>
         </is>
       </c>
-      <c r="G18" s="47" t="inlineStr">
+      <c r="G13" s="97" t="inlineStr">
         <is>
           <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md (schemas), docs/APIS.md (connectors endpoints)</t>
         </is>
       </c>
-      <c r="H18" s="48" t="inlineStr">
+      <c r="H13" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I18" s="49" t="inlineStr">
+      <c r="I13" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J18" s="46" t="inlineStr">
+      <c r="J13" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K18" s="50" t="n">
+      <c r="K13" s="98" t="n">
         <v>46202</v>
       </c>
-      <c r="L18" s="50" t="n">
+      <c r="L13" s="98" t="n">
         <v>46202</v>
       </c>
-      <c r="M18" s="51" t="n">
+      <c r="M13" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="46" t="inlineStr">
+      <c r="N13" s="97" t="inlineStr">
         <is>
           <t>P6-S09</t>
         </is>
       </c>
-      <c r="O18" s="47" t="inlineStr">
+      <c r="O13" s="97" t="inlineStr">
         <is>
           <t>test_swiggy_reservation_sync.py (5 tests)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1" s="72">
-      <c r="A19" s="44" t="inlineStr">
+    <row r="14" ht="52" customHeight="1" s="72">
+      <c r="A14" s="91" t="inlineStr">
         <is>
           <t>P6-S11</t>
         </is>
       </c>
-      <c r="B19" s="68" t="n"/>
-      <c r="C19" s="55" t="inlineStr">
+      <c r="B14" s="92" t="n"/>
+      <c r="C14" s="92" t="inlineStr">
         <is>
           <t>Integrations</t>
         </is>
       </c>
-      <c r="D19" s="56" t="inlineStr">
+      <c r="D14" s="92" t="inlineStr">
         <is>
           <t>Sync delivery performance → feedback table</t>
         </is>
       </c>
-      <c r="E19" s="56" t="inlineStr">
+      <c r="E14" s="92" t="inlineStr">
         <is>
           <t>Completed — NOTE: syncs YOUR personal delivery tracking data as a consumer, NOT restaurant delivery performance. Infrastructure built; complaint_intelligence uses internal feedback data instead.</t>
         </is>
       </c>
-      <c r="F19" s="56" t="inlineStr">
+      <c r="F14" s="92" t="inlineStr">
         <is>
           <t>feat(P6-S10/S06): fix Swiggy client response format + live sync endpoint + feedback sync + reservation sync skeleton</t>
         </is>
       </c>
-      <c r="G19" s="56" t="inlineStr">
+      <c r="G14" s="92" t="inlineStr">
         <is>
           <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md (section 3 auth + all section 16 schemas fixed to real format), docs/APIS.md</t>
         </is>
       </c>
-      <c r="H19" s="48" t="inlineStr">
+      <c r="H14" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I19" s="49" t="inlineStr">
+      <c r="I14" s="91" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J19" s="55" t="inlineStr">
+      <c r="J14" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K19" s="57" t="n">
+      <c r="K14" s="94" t="n">
         <v>46202</v>
       </c>
-      <c r="L19" s="57" t="n">
+      <c r="L14" s="94" t="n">
         <v>46202</v>
       </c>
-      <c r="M19" s="58" t="n">
+      <c r="M14" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="55" t="inlineStr">
+      <c r="N14" s="92" t="inlineStr">
         <is>
           <t>P6-S06</t>
         </is>
       </c>
-      <c r="O19" s="56" t="inlineStr">
+      <c r="O14" s="92" t="inlineStr">
         <is>
           <t>test_swiggy_feedback_sync.py (7 tests), test_swiggy_client.py updated (406 + Accept header + new format)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="7.95" customHeight="1" s="72">
-      <c r="A20" s="52" t="n"/>
-      <c r="B20" s="52" t="n"/>
-      <c r="C20" s="52" t="n"/>
-      <c r="D20" s="52" t="n"/>
-      <c r="E20" s="52" t="n"/>
-      <c r="F20" s="52" t="n"/>
-      <c r="G20" s="52" t="n"/>
-      <c r="H20" s="52" t="n"/>
-      <c r="I20" s="52" t="n"/>
-      <c r="J20" s="52" t="n"/>
-      <c r="K20" s="52" t="n"/>
-      <c r="L20" s="52" t="n"/>
-      <c r="M20" s="52" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="O20" s="52" t="n"/>
-    </row>
-    <row r="21" ht="99" customHeight="1" s="72">
-      <c r="A21" s="44" t="inlineStr">
+    <row r="15" ht="52" customHeight="1" s="72">
+      <c r="A15" s="96" t="inlineStr">
         <is>
           <t>P6-S12</t>
         </is>
       </c>
-      <c r="B21" s="69" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>feature/swiggy-market-intel-enrichers</t>
         </is>
       </c>
-      <c r="C21" s="55" t="inlineStr">
+      <c r="C15" s="97" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D21" s="56" t="inlineStr">
+      <c r="D15" s="97" t="inlineStr">
         <is>
           <t>CompetitorEnricher — Food MCP</t>
         </is>
       </c>
-      <c r="E21" s="56" t="inlineStr">
+      <c r="E15" s="97" t="inlineStr">
         <is>
           <t>Create enrichers/competitor.py. get_addresses → addressId. search_restaurants (cuisine, addressId) → filter OPEN → search_menu + get_restaurant_menu per restaurant (max 3). Build competitor_pricing dict: area avg price per dish category, pricing_alerts vs your menu. Redis cache 30min TTL. Inject into menu_intel node prompt as ## Market Context section.</t>
         </is>
       </c>
-      <c r="F21" s="56" t="inlineStr">
+      <c r="F15" s="97" t="inlineStr">
         <is>
           <t>feat: CompetitorEnricher — live competitor pricing via Food MCP</t>
         </is>
       </c>
-      <c r="G21" s="56" t="inlineStr">
+      <c r="G15" s="97" t="inlineStr">
         <is>
           <t>get_addresses, search_restaurants, search_menu, get_restaurant_menu</t>
         </is>
       </c>
-      <c r="H21" s="48" t="inlineStr">
+      <c r="H15" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I21" s="49" t="inlineStr">
+      <c r="I15" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J21" s="55" t="inlineStr">
+      <c r="J15" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K21" s="57" t="n">
+      <c r="K15" s="98" t="n">
         <v>46203</v>
       </c>
-      <c r="L21" s="57" t="n">
+      <c r="L15" s="98" t="n">
         <v>46203</v>
       </c>
-      <c r="M21" s="58" t="n">
+      <c r="M15" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="55" t="inlineStr">
+      <c r="N15" s="97" t="inlineStr">
         <is>
           <t>P6-S10</t>
         </is>
       </c>
-      <c r="O21" s="56" t="inlineStr">
+      <c r="O15" s="97" t="inlineStr">
         <is>
           <t>NEEDS: OAuth token. All read-only — works on production endpoint.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="85.95" customHeight="1" s="72">
-      <c r="A22" s="44" t="inlineStr">
+    <row r="16" ht="52" customHeight="1" s="72">
+      <c r="A16" s="91" t="inlineStr">
         <is>
           <t>P6-S13</t>
         </is>
       </c>
-      <c r="B22" s="67" t="n"/>
-      <c r="C22" s="46" t="inlineStr">
+      <c r="B16" s="92" t="n"/>
+      <c r="C16" s="92" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D16" s="92" t="inlineStr">
         <is>
           <t>OccupancyEnricher — Dineout MCP</t>
         </is>
       </c>
-      <c r="E22" s="47" t="inlineStr">
+      <c r="E16" s="92" t="inlineStr">
         <is>
           <t>Create enrichers/occupancy.py. get_saved_locations → store lat/lng. search_restaurants_dineout (cuisine, addressId) → get_restaurant_details (top 3) → get_available_slots (today). Compute occupancy_signal: HIGH if &gt;50% slots have availabilityCount &lt; 2. Redis cache 30min TTL. Inject into reservation node prompt.</t>
         </is>
       </c>
-      <c r="F22" s="47" t="inlineStr">
+      <c r="F16" s="92" t="inlineStr">
         <is>
           <t>feat: OccupancyEnricher — live competitor occupancy via Dineout MCP</t>
         </is>
       </c>
-      <c r="G22" s="47" t="inlineStr">
+      <c r="G16" s="92" t="inlineStr">
         <is>
           <t>get_saved_locations, search_restaurants_dineout, get_restaurant_details, get_available_slots</t>
         </is>
       </c>
-      <c r="H22" s="48" t="inlineStr">
+      <c r="H16" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I22" s="49" t="inlineStr">
+      <c r="I16" s="91" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J22" s="46" t="inlineStr">
+      <c r="J16" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K22" s="46" t="n"/>
-      <c r="L22" s="50" t="n">
+      <c r="K16" s="91" t="n"/>
+      <c r="L16" s="94" t="n">
         <v>46203</v>
       </c>
-      <c r="M22" s="51" t="n">
+      <c r="M16" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="46" t="inlineStr">
+      <c r="N16" s="92" t="inlineStr">
         <is>
           <t>P6-S12</t>
         </is>
       </c>
-      <c r="O22" s="47" t="inlineStr">
+      <c r="O16" s="92" t="inlineStr">
         <is>
           <t>NEEDS: OAuth token. All read-only.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="99" customHeight="1" s="72">
-      <c r="A23" s="44" t="inlineStr">
+    <row r="17" ht="52" customHeight="1" s="72">
+      <c r="A17" s="96" t="inlineStr">
         <is>
           <t>P6-S14</t>
         </is>
       </c>
-      <c r="B23" s="68" t="n"/>
-      <c r="C23" s="55" t="inlineStr">
+      <c r="B17" s="97" t="n"/>
+      <c r="C17" s="97" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D23" s="56" t="inlineStr">
+      <c r="D17" s="97" t="inlineStr">
         <is>
           <t>ProcurementEnricher — Instamart MCP</t>
         </is>
       </c>
-      <c r="E23" s="56" t="inlineStr">
+      <c r="E17" s="97" t="inlineStr">
         <is>
           <t>Create enrichers/procurement.py. search_products (per shortage item, max 5 calls/run) + your_go_to_items (frequent reorders). Output: [{ingredient, spinId, price, unit, inStock}]. spinId MUST persist in OrchestratorState — required for Instamart checkout in P6-S43. Redis cache 30 min. Returns None on any failure; inventory node falls back to its own analysis.</t>
         </is>
       </c>
-      <c r="F23" s="56" t="inlineStr">
+      <c r="F17" s="97" t="inlineStr">
         <is>
           <t>feat: ProcurementEnricher — live Instamart prices + spinIds injected into inventory node</t>
         </is>
       </c>
-      <c r="G23" s="56" t="inlineStr">
+      <c r="G17" s="97" t="inlineStr">
         <is>
           <t>docs/SWIGGY_INTEGRATION.md (P6-S14 section)</t>
         </is>
       </c>
-      <c r="H23" s="48" t="inlineStr">
+      <c r="H17" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I23" s="49" t="inlineStr">
+      <c r="I17" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J23" s="55" t="inlineStr">
+      <c r="J17" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K23" s="55" t="n"/>
-      <c r="L23" s="57" t="n">
+      <c r="K17" s="96" t="n"/>
+      <c r="L17" s="98" t="n">
         <v>46203</v>
       </c>
-      <c r="M23" s="58" t="n">
+      <c r="M17" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="55" t="inlineStr">
+      <c r="N17" s="97" t="inlineStr">
         <is>
           <t>P6-S13</t>
         </is>
       </c>
-      <c r="O23" s="56" t="inlineStr">
+      <c r="O17" s="97" t="inlineStr">
         <is>
           <t>NEEDS: OAuth token (read-only). Returns None on client failure; correct procurement_options on success; spinId present in each item; Redis caches result; max 5 search_products calls per run enforced.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="7.95" customHeight="1" s="72">
-      <c r="A24" s="52" t="n"/>
-      <c r="B24" s="52" t="n"/>
-      <c r="C24" s="52" t="n"/>
-      <c r="D24" s="52" t="n"/>
-      <c r="E24" s="52" t="n"/>
-      <c r="F24" s="52" t="n"/>
-      <c r="G24" s="52" t="n"/>
-      <c r="H24" s="52" t="n"/>
-      <c r="I24" s="52" t="n"/>
-      <c r="J24" s="52" t="n"/>
-      <c r="K24" s="52" t="n"/>
-      <c r="L24" s="52" t="n"/>
-      <c r="M24" s="52" t="n"/>
-      <c r="N24" s="52" t="n"/>
-      <c r="O24" s="52" t="n"/>
-    </row>
-    <row r="25" ht="73.05" customHeight="1" s="72">
-      <c r="A25" s="44" t="inlineStr">
+    <row r="18" ht="52" customHeight="1" s="72">
+      <c r="A18" s="91" t="inlineStr">
         <is>
           <t>P6-S15</t>
         </is>
       </c>
-      <c r="B25" s="69" t="inlineStr">
+      <c r="B18" s="92" t="inlineStr">
         <is>
           <t>feature/swiggy-market-intel-node</t>
         </is>
       </c>
-      <c r="C25" s="55" t="inlineStr">
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D25" s="56" t="inlineStr">
+      <c r="D18" s="92" t="inlineStr">
         <is>
           <t>MarketIntelService + 6 new OrchestratorState fields</t>
         </is>
       </c>
-      <c r="E25" s="56" t="inlineStr">
+      <c r="E18" s="92" t="inlineStr">
         <is>
           <t>MarketIntelService orchestrates all 3 enrichers. Adds 6 Annotated[Optional[Dict], keep_last] fields to OrchestratorState: swiggy_competitor_context, swiggy_occupancy_context, swiggy_procurement_options, swiggy_delivery_signal, market_intel_output, dineout_manager_output.</t>
         </is>
       </c>
-      <c r="F25" s="56" t="inlineStr">
+      <c r="F18" s="92" t="inlineStr">
         <is>
           <t>feat: MarketIntelService + 6 new OrchestratorState enrichment fields</t>
         </is>
       </c>
-      <c r="G25" s="56" t="inlineStr">
+      <c r="G18" s="92" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md (MarketIntelService), docs/DATA_MODEL.md (state fields)</t>
         </is>
       </c>
-      <c r="H25" s="48" t="inlineStr">
+      <c r="H18" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I25" s="49" t="inlineStr">
+      <c r="I18" s="91" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J25" s="55" t="inlineStr">
+      <c r="J18" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K25" s="57" t="n">
+      <c r="K18" s="94" t="n">
         <v>46204</v>
       </c>
-      <c r="L25" s="57" t="n">
+      <c r="L18" s="94" t="n">
         <v>46204</v>
       </c>
-      <c r="M25" s="58" t="n">
+      <c r="M18" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N25" s="55" t="inlineStr">
+      <c r="N18" s="92" t="inlineStr">
         <is>
           <t>P6-S12, P6-S13, P6-S14</t>
         </is>
       </c>
-      <c r="O25" s="56" t="inlineStr">
+      <c r="O18" s="92" t="inlineStr">
         <is>
           <t>State field type tests; MarketIntelService runs all 3 enrichers; final_assembler passes through</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="73.05" customHeight="1" s="72">
-      <c r="A26" s="44" t="inlineStr">
+    <row r="19" ht="52" customHeight="1" s="72">
+      <c r="A19" s="96" t="inlineStr">
         <is>
           <t>P6-S16</t>
         </is>
       </c>
-      <c r="B26" s="67" t="n"/>
-      <c r="C26" s="46" t="inlineStr">
+      <c r="B19" s="97" t="n"/>
+      <c r="C19" s="97" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D26" s="47" t="inlineStr">
+      <c r="D19" s="97" t="inlineStr">
         <is>
           <t>market_intel_node — 10th LangGraph node</t>
         </is>
       </c>
-      <c r="E26" s="47" t="inlineStr">
+      <c r="E19" s="97" t="inlineStr">
         <is>
           <t>New parallel domain node. Runs CompetitorEnricher + OccupancyEnricher. Outputs market_intel_output: competitor_pricing, area_occupancy, pricing_alerts. Writes market_assumptions dict. Participates in assumption diffing. Critic receives market context. Supersedes original P6-06.</t>
         </is>
       </c>
-      <c r="F26" s="47" t="inlineStr">
+      <c r="F19" s="97" t="inlineStr">
         <is>
           <t>feat: market_intel_node — 10th parallel LangGraph node, Swiggy-powered market awareness</t>
         </is>
       </c>
-      <c r="G26" s="47" t="inlineStr">
+      <c r="G19" s="97" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (market_intel_node section), docs/ARCHITECTURE.md (11-node pipeline), docs/DECISIONS.md (D-020)</t>
         </is>
       </c>
-      <c r="H26" s="48" t="inlineStr">
+      <c r="H19" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I26" s="49" t="inlineStr">
+      <c r="I19" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J26" s="46" t="inlineStr">
+      <c r="J19" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K26" s="50" t="n">
+      <c r="K19" s="98" t="n">
         <v>46204</v>
       </c>
-      <c r="L26" s="50" t="n">
+      <c r="L19" s="98" t="n">
         <v>46204</v>
       </c>
-      <c r="M26" s="51" t="n">
+      <c r="M19" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="46" t="inlineStr">
+      <c r="N19" s="97" t="inlineStr">
         <is>
           <t>P6-S15</t>
         </is>
       </c>
-      <c r="O26" s="47" t="inlineStr">
+      <c r="O19" s="97" t="inlineStr">
         <is>
           <t>Node writes market_intel_output + market_assumptions; parallel verified; assumption diffing fires; LangSmith trace shows node</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="99" customHeight="1" s="72">
-      <c r="A27" s="44" t="inlineStr">
+    <row r="20" ht="52" customHeight="1" s="72">
+      <c r="A20" s="91" t="inlineStr">
         <is>
           <t>P6-S17</t>
         </is>
       </c>
-      <c r="B27" s="67" t="n"/>
-      <c r="C27" s="55" t="inlineStr">
+      <c r="B20" s="92" t="n"/>
+      <c r="C20" s="92" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D27" s="56" t="inlineStr">
+      <c r="D20" s="92" t="inlineStr">
         <is>
           <t>dineout_manager_node — 11th LangGraph node</t>
         </is>
       </c>
-      <c r="E27" s="56" t="inlineStr">
+      <c r="E20" s="92" t="inlineStr">
         <is>
           <t>Built. Node wired into LangGraph fan-out and exits gracefully when SWIGGY_DINEOUT_RESTAURANT_ID not set. NOTE: Consumer MCP cannot manage your own restaurant Dineout slots — book_table is a consumer action (books at other restaurants). Dineout slot management needs Swiggy Partner API. Current value: competitive occupancy signal only (get_available_slots on competitors).</t>
         </is>
       </c>
-      <c r="F27" s="56" t="inlineStr">
+      <c r="F20" s="92" t="inlineStr">
         <is>
           <t>feat: dineout_manager_node — own Dineout slot monitoring wired into planning pipeline</t>
         </is>
       </c>
-      <c r="G27" s="56" t="inlineStr">
+      <c r="G20" s="92" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (dineout_manager_node spec)</t>
         </is>
       </c>
-      <c r="H27" s="48" t="inlineStr">
+      <c r="H20" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I27" s="61" t="inlineStr">
+      <c r="I20" s="91" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J27" s="55" t="inlineStr">
+      <c r="J20" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K27" s="57" t="n">
+      <c r="K20" s="94" t="n">
         <v>46204</v>
       </c>
-      <c r="L27" s="57" t="n">
+      <c r="L20" s="94" t="n">
         <v>46204</v>
       </c>
-      <c r="M27" s="58" t="n">
+      <c r="M20" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="55" t="inlineStr">
+      <c r="N20" s="92" t="inlineStr">
         <is>
           <t>P6-S15</t>
         </is>
       </c>
-      <c r="O27" s="56" t="inlineStr">
+      <c r="O20" s="92" t="inlineStr">
         <is>
           <t>Node runs in parallel fan-out; dineout_assumptions written to state; action queued when slots low + walk-in predicted high; graceful None on Swiggy failure.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1" s="72">
-      <c r="A28" s="44" t="inlineStr">
+    <row r="21" ht="52" customHeight="1" s="72">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>P6-S18</t>
         </is>
       </c>
-      <c r="B28" s="68" t="n"/>
-      <c r="C28" s="46" t="inlineStr">
+      <c r="B21" s="97" t="n"/>
+      <c r="C21" s="97" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D28" s="47" t="inlineStr">
+      <c r="D21" s="97" t="inlineStr">
         <is>
           <t>Assumption diffs 5 + 6 for new nodes</t>
         </is>
       </c>
-      <c r="E28" s="47" t="inlineStr">
+      <c r="E21" s="97" t="inlineStr">
         <is>
           <t>Diff 5: market_intel assumed_competitor_avg_price vs menu_intel items_assumed_available pricing. Diff 6: dineout_manager assumed_dineout_slots_low vs reservation assumed_peak_occupancy. Extends P6-S02. Total now 5 active diffs.</t>
         </is>
       </c>
-      <c r="F28" s="47" t="inlineStr">
+      <c r="F21" s="97" t="inlineStr">
         <is>
           <t>feat: assumption diffs 5+6 — market vs menu pricing, dineout slots vs reservation occupancy</t>
         </is>
       </c>
-      <c r="G28" s="47" t="inlineStr">
+      <c r="G21" s="97" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md (sanity checker updated), docs/AGENTS.md</t>
         </is>
       </c>
-      <c r="H28" s="48" t="inlineStr">
+      <c r="H21" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I28" s="61" t="inlineStr">
+      <c r="I21" s="96" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J28" s="46" t="inlineStr">
+      <c r="J21" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K28" s="50" t="n">
+      <c r="K21" s="98" t="n">
         <v>46204</v>
       </c>
-      <c r="L28" s="50" t="n">
+      <c r="L21" s="98" t="n">
         <v>46204</v>
       </c>
-      <c r="M28" s="51" t="n">
+      <c r="M21" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="46" t="inlineStr">
+      <c r="N21" s="97" t="inlineStr">
         <is>
           <t>P6-S16, P6-S17</t>
         </is>
       </c>
-      <c r="O28" s="47" t="inlineStr">
+      <c r="O21" s="97" t="inlineStr">
         <is>
           <t>Diff 5 + 6 fire correctly; existing 3 diffs unaffected; stale_assumptions includes new conflicts</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="7.95" customHeight="1" s="72">
-      <c r="A29" s="52" t="n"/>
-      <c r="B29" s="52" t="n"/>
-      <c r="C29" s="52" t="n"/>
-      <c r="D29" s="52" t="n"/>
-      <c r="E29" s="52" t="n"/>
-      <c r="F29" s="52" t="n"/>
-      <c r="G29" s="52" t="n"/>
-      <c r="H29" s="52" t="n"/>
-      <c r="I29" s="52" t="n"/>
-      <c r="J29" s="52" t="n"/>
-      <c r="K29" s="52" t="n"/>
-      <c r="L29" s="52" t="n"/>
-      <c r="M29" s="52" t="n"/>
-      <c r="N29" s="52" t="n"/>
-      <c r="O29" s="52" t="n"/>
-    </row>
-    <row r="30" ht="112.05" customHeight="1" s="72">
-      <c r="A30" s="44" t="inlineStr">
+    <row r="22" ht="52" customHeight="1" s="72">
+      <c r="A22" s="91" t="inlineStr">
         <is>
           <t>P6-S19</t>
         </is>
       </c>
-      <c r="B30" s="66" t="inlineStr">
+      <c r="B22" s="92" t="inlineStr">
         <is>
           <t>feature/swiggy-chatbot-tools</t>
         </is>
       </c>
-      <c r="C30" s="46" t="inlineStr">
+      <c r="C22" s="92" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D30" s="47" t="inlineStr">
+      <c r="D22" s="92" t="inlineStr">
         <is>
           <t>Swiggy-aware chatbot tools — HIGH PRIORITY FOR DEMO</t>
         </is>
       </c>
-      <c r="E30" s="47" t="inlineStr">
+      <c r="E22" s="92" t="inlineStr">
         <is>
           <t>Add 3 Groq function-calling tools to the existing agentic chatbot (P6-S09). search_menu(query, addressId): answers questions like 'what is the avg biryani price near me?' get_food_orders(addressId): answers 'what were my top Swiggy items last week?' search_products(query, addressId): answers 'what does cream cost on Instamart right now?' Makes the chatbot genuinely Swiggy-aware — very demo-friendly for the Swiggy team.</t>
         </is>
       </c>
-      <c r="F30" s="47" t="inlineStr">
+      <c r="F22" s="92" t="inlineStr">
         <is>
           <t>feat: Swiggy chatbot tools — search_menu, get_food_orders, search_products via Groq function calling</t>
         </is>
       </c>
-      <c r="G30" s="47" t="inlineStr">
+      <c r="G22" s="92" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (chatbot Swiggy tools section)</t>
         </is>
       </c>
-      <c r="H30" s="48" t="inlineStr">
+      <c r="H22" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I30" s="49" t="inlineStr">
+      <c r="I22" s="91" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J30" s="46" t="inlineStr">
+      <c r="J22" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K30" s="50" t="n">
+      <c r="K22" s="94" t="n">
         <v>46204</v>
       </c>
-      <c r="L30" s="50" t="n">
+      <c r="L22" s="94" t="n">
         <v>46204</v>
       </c>
-      <c r="M30" s="51" t="n">
+      <c r="M22" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="46" t="inlineStr">
+      <c r="N22" s="92" t="inlineStr">
         <is>
           <t>P6-S09, P6-S04</t>
         </is>
       </c>
-      <c r="O30" s="47" t="inlineStr">
+      <c r="O22" s="92" t="inlineStr">
         <is>
           <t>NEEDS: OAuth token (read-only). All 3 tools callable from /chat; correct Swiggy data returned; graceful None on Swiggy failure; tool names appear in Groq tool_calls response.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="7.95" customHeight="1" s="72">
-      <c r="A31" s="52" t="n"/>
-      <c r="B31" s="52" t="n"/>
-      <c r="C31" s="52" t="n"/>
-      <c r="D31" s="52" t="n"/>
-      <c r="E31" s="52" t="n"/>
-      <c r="F31" s="52" t="n"/>
-      <c r="G31" s="52" t="n"/>
-      <c r="H31" s="52" t="n"/>
-      <c r="I31" s="52" t="n"/>
-      <c r="J31" s="52" t="n"/>
-      <c r="K31" s="52" t="n"/>
-      <c r="L31" s="52" t="n"/>
-      <c r="M31" s="52" t="n"/>
-      <c r="N31" s="52" t="n"/>
-      <c r="O31" s="52" t="n"/>
-    </row>
-    <row r="32" ht="73.05" customHeight="1" s="72">
-      <c r="A32" s="44" t="inlineStr">
+    <row r="23" ht="52" customHeight="1" s="72">
+      <c r="A23" s="96" t="inlineStr">
         <is>
           <t>P6-F01</t>
         </is>
       </c>
-      <c r="B32" s="66" t="inlineStr">
+      <c r="B23" s="97" t="inlineStr">
         <is>
           <t>feature/swiggy-connectors-ui</t>
         </is>
       </c>
-      <c r="C32" s="46" t="inlineStr">
+      <c r="C23" s="97" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D32" s="47" t="inlineStr">
+      <c r="D23" s="97" t="inlineStr">
         <is>
           <t>/connectors page — data source management</t>
         </is>
       </c>
-      <c r="E32" s="47" t="inlineStr">
+      <c r="E23" s="97" t="inlineStr">
         <is>
           <t>New route /connectors. Lists connectors with status badges (Connected/Disconnected/Error). Shows last sync time, records synced, data freshness. Connect button triggers OAuth flow. Disconnect revokes token. Error state shows last error + reconnect. Works for Swiggy + future POS connector.</t>
         </is>
       </c>
-      <c r="F32" s="47" t="inlineStr">
+      <c r="F23" s="97" t="inlineStr">
         <is>
           <t>feat: /connectors page — platform data source management with OAuth connect flow</t>
         </is>
       </c>
-      <c r="G32" s="47" t="inlineStr">
+      <c r="G23" s="97" t="inlineStr">
         <is>
           <t>None (frontend only)</t>
         </is>
       </c>
-      <c r="H32" s="48" t="inlineStr">
+      <c r="H23" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I32" s="53" t="inlineStr">
+      <c r="I23" s="96" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J32" s="46" t="inlineStr">
+      <c r="J23" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K32" s="46" t="n"/>
-      <c r="L32" s="60" t="inlineStr">
+      <c r="K23" s="96" t="n"/>
+      <c r="L23" s="96" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="M32" s="51" t="n">
+      <c r="M23" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="46" t="inlineStr">
+      <c r="N23" s="97" t="inlineStr">
         <is>
           <t>P6-S04</t>
         </is>
       </c>
-      <c r="O32" s="47" t="inlineStr">
+      <c r="O23" s="97" t="inlineStr">
         <is>
           <t>Can build now — reads from connectors table (already exists via P6-S05)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1" s="72">
-      <c r="A33" s="44" t="inlineStr">
+    <row r="24" ht="52" customHeight="1" s="72">
+      <c r="A24" s="91" t="inlineStr">
         <is>
           <t>P6-F02</t>
         </is>
       </c>
-      <c r="B33" s="67" t="n"/>
-      <c r="C33" s="55" t="inlineStr">
+      <c r="B24" s="92" t="n"/>
+      <c r="C24" s="92" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D33" s="56" t="inlineStr">
+      <c r="D24" s="92" t="inlineStr">
         <is>
           <t>Dashboard enhancements</t>
         </is>
       </c>
-      <c r="E33" s="56" t="inlineStr">
+      <c r="E24" s="92" t="inlineStr">
         <is>
           <t>Add to existing dashboard: connector status widget (data source health bar), brief mode trigger button, today's Swiggy KPIs (orders today, delivery rating, top Swiggy seller), data_sources column on /runs list.</t>
         </is>
       </c>
-      <c r="F33" s="56" t="inlineStr">
+      <c r="F24" s="92" t="inlineStr">
         <is>
           <t>feat: dashboard — connector status widget, brief trigger, live Swiggy KPIs, data_sources on runs list</t>
         </is>
       </c>
-      <c r="G33" s="56" t="inlineStr">
+      <c r="G24" s="92" t="inlineStr">
         <is>
           <t>None (frontend only)</t>
         </is>
       </c>
-      <c r="H33" s="48" t="inlineStr">
+      <c r="H24" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I33" s="53" t="inlineStr">
+      <c r="I24" s="91" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J33" s="55" t="inlineStr">
+      <c r="J24" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K33" s="55" t="n"/>
-      <c r="L33" s="59" t="inlineStr">
+      <c r="K24" s="91" t="n"/>
+      <c r="L24" s="91" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="M33" s="58" t="n">
+      <c r="M24" s="95" t="n">
         <v>0</v>
       </c>
-      <c r="N33" s="55" t="inlineStr">
+      <c r="N24" s="92" t="inlineStr">
         <is>
           <t>P6-S04</t>
         </is>
       </c>
-      <c r="O33" s="56" t="inlineStr">
+      <c r="O24" s="92" t="inlineStr">
         <is>
           <t>Can build now — connector status widget reads connectors table</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="138" customHeight="1" s="72">
-      <c r="A34" s="44" t="inlineStr">
+    <row r="25" ht="52" customHeight="1" s="72">
+      <c r="A25" s="96" t="inlineStr">
         <is>
           <t>P6-F03</t>
         </is>
       </c>
-      <c r="B34" s="67" t="n"/>
-      <c r="C34" s="46" t="inlineStr">
+      <c r="B25" s="97" t="n"/>
+      <c r="C25" s="97" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D34" s="47" t="inlineStr">
+      <c r="D25" s="97" t="inlineStr">
         <is>
           <t>Backend bug fixes for Swiggy UI features</t>
         </is>
       </c>
-      <c r="E34" s="47" t="inlineStr">
+      <c r="E25" s="97" t="inlineStr">
         <is>
           <t>Three backend fixes: (1) final_assembler.py was not including Swiggy state fields in API response (market_intel_output, swiggy_competitor/occupancy_context, swiggy_procurement_options, dineout_manager_output) — frontend Market Intel panel was always empty. (2) connector_repository.update_sync_status silently dropped updates when no DB row existed — fixed to auto-create connector row so last_sync_at always persists. (3) main.py ConsoleSpanExporter flooding backend logs with JSON on every request — removed BatchSpanProcessor(ConsoleSpanExporter()) line.</t>
         </is>
       </c>
-      <c r="F34" s="47" t="inlineStr">
+      <c r="F25" s="97" t="inlineStr">
         <is>
           <t>fix: final_assembler Swiggy fields, connector auto-create, silence OTel console exporter</t>
         </is>
       </c>
-      <c r="G34" s="47" t="inlineStr">
+      <c r="G25" s="97" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H34" s="48" t="inlineStr">
+      <c r="H25" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I34" s="49" t="inlineStr">
+      <c r="I25" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J34" s="46" t="n"/>
-      <c r="K34" s="46" t="n"/>
-      <c r="L34" s="46" t="n"/>
-      <c r="M34" s="46" t="n"/>
-      <c r="N34" s="46" t="n"/>
-      <c r="O34" s="47" t="n"/>
-    </row>
-    <row r="35" ht="151.05" customHeight="1" s="72">
-      <c r="A35" s="44" t="inlineStr">
+      <c r="J25" s="96" t="n"/>
+      <c r="K25" s="96" t="n"/>
+      <c r="L25" s="96" t="n"/>
+      <c r="M25" s="99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="97" t="n"/>
+      <c r="O25" s="97" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1" s="72">
+      <c r="A26" s="91" t="inlineStr">
         <is>
           <t>P6-F04</t>
         </is>
       </c>
-      <c r="B35" s="67" t="n"/>
-      <c r="C35" s="55" t="inlineStr">
+      <c r="B26" s="92" t="n"/>
+      <c r="C26" s="92" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D35" s="56" t="inlineStr">
+      <c r="D26" s="92" t="inlineStr">
         <is>
           <t>Consumer API clarification — code comments + CLAUDE.md</t>
         </is>
       </c>
-      <c r="E35" s="56" t="inlineStr">
+      <c r="E26" s="92" t="inlineStr">
         <is>
           <t>Swiggy MCP confirmed 100% consumer-facing from Builders Club docs. Added FUTURE USE / CONSUMER DATA ONLY comments to: swiggy_connector.py, sync/order_sync.py, feedback_sync.py, reservation_sync.py, orchestration/nodes/dineout_manager.py (corrected docstring re book_table), orchestration/state.py (swiggy_delivery_signal), graph.py (stream message). CLAUDE.md: product vision corrected, pipeline notes, sync layer notes, Workflow 1 + 2 corrected, build steps updated. Tracker: P6-S06/S05/S06 notes updated, P6-S17/S31 re-evaluated, 4 MI tasks added for honest Swiggy feature scope.</t>
         </is>
       </c>
-      <c r="F35" s="56" t="inlineStr">
+      <c r="F26" s="92" t="inlineStr">
         <is>
           <t>docs: consumer API scope clarified across sync layer, dineout node, state, CLAUDE.md</t>
         </is>
       </c>
-      <c r="G35" s="56" t="inlineStr">
+      <c r="G26" s="92" t="inlineStr">
         <is>
           <t>CLAUDE.md, 6 source files</t>
         </is>
       </c>
-      <c r="H35" s="48" t="inlineStr">
+      <c r="H26" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I35" s="61" t="inlineStr">
+      <c r="I26" s="91" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J35" s="55" t="n"/>
-      <c r="K35" s="55" t="n"/>
-      <c r="L35" s="55" t="n"/>
-      <c r="M35" s="55" t="n"/>
-      <c r="N35" s="55" t="n"/>
-      <c r="O35" s="56" t="n"/>
-    </row>
-    <row r="36" ht="73.05" customHeight="1" s="72">
-      <c r="A36" s="44" t="inlineStr">
+      <c r="J26" s="91" t="n"/>
+      <c r="K26" s="91" t="n"/>
+      <c r="L26" s="91" t="n"/>
+      <c r="M26" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="92" t="n"/>
+      <c r="O26" s="92" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1" s="72">
+      <c r="A27" s="96" t="inlineStr">
         <is>
           <t>P6-F05</t>
         </is>
       </c>
-      <c r="B36" s="68" t="n"/>
-      <c r="C36" s="46" t="inlineStr">
+      <c r="B27" s="97" t="n"/>
+      <c r="C27" s="97" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D36" s="47" t="inlineStr">
+      <c r="D27" s="97" t="inlineStr">
         <is>
           <t>Market intelligence panel (planning results page)</t>
         </is>
       </c>
-      <c r="E36" s="47" t="inlineStr">
+      <c r="E27" s="97" t="inlineStr">
         <is>
           <t>New panel on /runs/{id}. Competitor pricing table: your price vs area avg vs cheapest competitor per dish category. Area occupancy badge (HIGH/MEDIUM/LOW). Instamart prices for shortage items. Pricing alerts (red if &gt;20% above area avg). Hidden when market_intel_output absent.</t>
         </is>
       </c>
-      <c r="F36" s="47" t="inlineStr">
+      <c r="F27" s="97" t="inlineStr">
         <is>
           <t>feat: market intelligence panel — competitor pricing + area occupancy on planning results</t>
         </is>
       </c>
-      <c r="G36" s="47" t="inlineStr">
+      <c r="G27" s="97" t="inlineStr">
         <is>
           <t>None (frontend only)</t>
         </is>
       </c>
-      <c r="H36" s="48" t="inlineStr">
+      <c r="H27" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I36" s="53" t="inlineStr">
+      <c r="I27" s="96" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J36" s="46" t="inlineStr">
+      <c r="J27" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K36" s="46" t="n"/>
-      <c r="L36" s="60" t="inlineStr">
+      <c r="K27" s="96" t="n"/>
+      <c r="L27" s="96" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="M36" s="51" t="n">
+      <c r="M27" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="46" t="inlineStr">
+      <c r="N27" s="97" t="inlineStr">
         <is>
           <t>P6-S15</t>
         </is>
       </c>
-      <c r="O36" s="47" t="inlineStr">
+      <c r="O27" s="97" t="inlineStr">
         <is>
           <t>Depends on P6-S16 (market_intel_output in plan API response)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="7.95" customHeight="1" s="72">
-      <c r="A37" s="52" t="n"/>
-      <c r="B37" s="52" t="n"/>
-      <c r="C37" s="52" t="n"/>
-      <c r="D37" s="52" t="n"/>
-      <c r="E37" s="52" t="n"/>
-      <c r="F37" s="52" t="n"/>
-      <c r="G37" s="52" t="n"/>
-      <c r="H37" s="52" t="n"/>
-      <c r="I37" s="52" t="n"/>
-      <c r="J37" s="52" t="n"/>
-      <c r="K37" s="52" t="n"/>
-      <c r="L37" s="52" t="n"/>
-      <c r="M37" s="52" t="n"/>
-      <c r="N37" s="52" t="n"/>
-      <c r="O37" s="52" t="n"/>
-    </row>
-    <row r="38" ht="138" customHeight="1" s="72">
-      <c r="A38" s="44" t="inlineStr">
+    <row r="28" ht="52" customHeight="1" s="72">
+      <c r="A28" s="91" t="inlineStr">
         <is>
           <t>P6-S20</t>
         </is>
       </c>
-      <c r="B38" s="66" t="inlineStr">
+      <c r="B28" s="92" t="inlineStr">
         <is>
           <t>feature/swiggy-prompt-injection (deleted post-merge)</t>
         </is>
       </c>
-      <c r="C38" s="46" t="inlineStr">
+      <c r="C28" s="92" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D38" s="47" t="inlineStr">
+      <c r="D28" s="92" t="inlineStr">
         <is>
           <t>Wire Swiggy enricher context into recommendation node prompts</t>
         </is>
       </c>
-      <c r="E38" s="47" t="inlineStr">
+      <c r="E28" s="92" t="inlineStr">
         <is>
           <t>Swiggy enricher prompt_text injected into 3 LLM prompts: (1) menu_intelligence gets ## Market Context (competitor prices, alerts); (2) inventory gets ## Live Procurement Options (Instamart prices per shortage item); (3) reservation gets ## Occupancy Signal (area HIGH/MEDIUM/LOW). LLM now references Swiggy data in reasoning — e.g. "Order tomatoes via Instamart at Rs.24/kg". Frontend: AgentCard swiggySignal prop shows orange Swiggy badge in card header with one-line market signal (area tonight: HIGH, 5 Instamart prices live, 2 pricing alerts). Never independently PR-ed to dev -- fix/swiggy-sse-market-intel branched off its tip and shipped it as part of that PR instead; feature/swiggy-prompt-injection deleted 2026-07-03 (remote + local), fully superseded.</t>
         </is>
       </c>
-      <c r="F38" s="47" t="inlineStr">
+      <c r="F28" s="92" t="inlineStr">
         <is>
           <t>feat: wire Swiggy enricher context into node prompts — recommendations become market-aware</t>
         </is>
       </c>
-      <c r="G38" s="47" t="inlineStr">
+      <c r="G28" s="92" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (node prompt sections updated)</t>
         </is>
       </c>
-      <c r="H38" s="48" t="inlineStr">
+      <c r="H28" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I38" s="53" t="inlineStr">
+      <c r="I28" s="91" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J38" s="46" t="n"/>
-      <c r="K38" s="46" t="n"/>
-      <c r="L38" s="46" t="n"/>
-      <c r="M38" s="46" t="n"/>
-      <c r="N38" s="46" t="n"/>
-      <c r="O38" s="47" t="n"/>
-    </row>
-    <row r="39" ht="7.95" customHeight="1" s="72">
-      <c r="A39" s="52" t="n"/>
-      <c r="B39" s="52" t="n"/>
-      <c r="C39" s="52" t="n"/>
-      <c r="D39" s="52" t="n"/>
-      <c r="E39" s="52" t="n"/>
-      <c r="F39" s="52" t="n"/>
-      <c r="G39" s="52" t="n"/>
-      <c r="H39" s="52" t="n"/>
-      <c r="I39" s="52" t="n"/>
-      <c r="J39" s="52" t="n"/>
-      <c r="K39" s="52" t="n"/>
-      <c r="L39" s="52" t="n"/>
-      <c r="M39" s="52" t="n"/>
-      <c r="N39" s="52" t="n"/>
-      <c r="O39" s="52" t="n"/>
-    </row>
-    <row r="40" ht="216" customHeight="1" s="72">
-      <c r="A40" s="44" t="inlineStr">
+      <c r="J28" s="91" t="n"/>
+      <c r="K28" s="91" t="n"/>
+      <c r="L28" s="91" t="n"/>
+      <c r="M28" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="92" t="n"/>
+      <c r="O28" s="92" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1" s="72">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>P6-S21</t>
         </is>
       </c>
-      <c r="B40" s="66" t="inlineStr">
+      <c r="B29" s="97" t="inlineStr">
         <is>
           <t>fix/swiggy-sse-market-intel</t>
         </is>
       </c>
-      <c r="C40" s="46" t="inlineStr">
+      <c r="C29" s="97" t="inlineStr">
         <is>
           <t>Reliability</t>
         </is>
       </c>
-      <c r="D40" s="47" t="inlineStr">
+      <c r="D29" s="97" t="inlineStr">
         <is>
           <t>Swiggy dashboard data-integrity fixes</t>
         </is>
       </c>
-      <c r="E40" s="47" t="inlineStr">
+      <c r="E29" s="97" t="inlineStr">
         <is>
           <t>Fixed Instamart procurement card rendering nothing despite live shortage data: frontend read item.name/item.in_stock but backend ProcurementEnricher sends item.ingredient/item.inStock (confirmed against the enricher's own test contract). Found and fixed a cost/token-attribution race: reservation and inventory nodes share the 'fast' LLM tier and run in true parallel; _inject() draining the shared provider usage buffer at node start/end let one node's drain steal the other's usage records. Fixed via per-node contextvar tagging (bind_llm_usage_node/drain_usage(node=...)) in llm/base.py + graph.py. Converted ~11 files across the Swiggy integration layer + cache/vector-memory infra from stdlib logging to structlog -- the app never calls logging.basicConfig(), so every .info()/.debug() call on those modules was being silently dropped, and .warning() lines printed unstructured with no run correlation. Merged to dev via PR #87, 2026-07-03.</t>
         </is>
       </c>
-      <c r="F40" s="47" t="inlineStr">
+      <c r="F29" s="97" t="inlineStr">
         <is>
           <t>fix: Instamart card field mapping, LLM usage attribution race, structlog conversion across Swiggy layer</t>
         </is>
       </c>
-      <c r="G40" s="47" t="inlineStr">
+      <c r="G29" s="97" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H40" s="48" t="inlineStr">
+      <c r="H29" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I40" s="49" t="inlineStr">
+      <c r="I29" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J40" s="46" t="inlineStr">
+      <c r="J29" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K40" s="50" t="n">
+      <c r="K29" s="98" t="n">
         <v>46205</v>
       </c>
-      <c r="L40" s="50" t="n">
+      <c r="L29" s="98" t="n">
         <v>46205</v>
       </c>
-      <c r="M40" s="51" t="n">
+      <c r="M29" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="46" t="inlineStr">
+      <c r="N29" s="97" t="inlineStr">
         <is>
           <t>P6-S20</t>
         </is>
       </c>
-      <c r="O40" s="47" t="inlineStr">
+      <c r="O29" s="97" t="inlineStr">
         <is>
           <t>Verified via isolated LangGraph fan-out concurrency test; 298+ backend tests passing at time of fix</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="138" customHeight="1" s="72">
-      <c r="A41" s="44" t="inlineStr">
+    <row r="30" ht="52" customHeight="1" s="72">
+      <c r="A30" s="91" t="inlineStr">
         <is>
           <t>P6-S22</t>
         </is>
       </c>
-      <c r="B41" s="67" t="n"/>
-      <c r="C41" s="55" t="inlineStr">
+      <c r="B30" s="92" t="n"/>
+      <c r="C30" s="92" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D41" s="56" t="inlineStr">
+      <c r="D30" s="92" t="inlineStr">
         <is>
           <t>Explicit Swiggy attribution on recommendation text and cards</t>
         </is>
       </c>
-      <c r="E41" s="56" t="inlineStr">
+      <c r="E30" s="92" t="inlineStr">
         <is>
           <t>Recommendation prompts (inventory/reservation/menu) now require the LLM to explicitly name 'Swiggy' when citing live competitor/occupancy/Instamart data. Added HighlightSwiggy component wired into ManagerActionPanel, InventoryAlerts, MenuInsights, ReservationSummary. Extracted a shared SwiggySignalBadge component (previously duplicated inline in AgentCard.tsx, about to be triplicated in the /runs page) and wired the same per-card Swiggy-signal computation into app/runs/page.tsx's AgentOutputCard, matching what the live dashboard already showed.</t>
         </is>
       </c>
-      <c r="F41" s="56" t="inlineStr">
+      <c r="F30" s="92" t="inlineStr">
         <is>
           <t>feat: explicit Swiggy attribution in recommendation text + shared signal badge on dashboard and /runs cards</t>
         </is>
       </c>
-      <c r="G41" s="56" t="inlineStr">
+      <c r="G30" s="92" t="inlineStr">
         <is>
           <t>None (frontend + prompt text only)</t>
         </is>
       </c>
-      <c r="H41" s="48" t="inlineStr">
+      <c r="H30" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I41" s="61" t="inlineStr">
+      <c r="I30" s="91" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J41" s="55" t="inlineStr">
+      <c r="J30" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K41" s="57" t="n">
+      <c r="K30" s="94" t="n">
         <v>46205</v>
       </c>
-      <c r="L41" s="57" t="n">
+      <c r="L30" s="94" t="n">
         <v>46205</v>
       </c>
-      <c r="M41" s="58" t="n">
+      <c r="M30" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="55" t="inlineStr">
+      <c r="N30" s="92" t="inlineStr">
         <is>
           <t>P6-S21</t>
         </is>
       </c>
-      <c r="O41" s="56" t="inlineStr">
+      <c r="O30" s="92" t="inlineStr">
         <is>
           <t>Frontend typecheck + eslint clean on all touched components</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="202.95" customHeight="1" s="72">
-      <c r="A42" s="44" t="inlineStr">
+    <row r="31" ht="52" customHeight="1" s="72">
+      <c r="A31" s="96" t="inlineStr">
         <is>
           <t>P6-S23</t>
         </is>
       </c>
-      <c r="B42" s="67" t="n"/>
-      <c r="C42" s="46" t="inlineStr">
+      <c r="B31" s="97" t="n"/>
+      <c r="C31" s="97" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D42" s="47" t="inlineStr">
+      <c r="D31" s="97" t="inlineStr">
         <is>
           <t>Eval/observability CI gate + golden-dataset bug fix</t>
         </is>
       </c>
-      <c r="E42" s="47" t="inlineStr">
+      <c r="E31" s="97" t="inlineStr">
         <is>
           <t>New .github/workflows/backend-tests.yml: unit-tests job runs pytest tests/unit on every push/PR (includes the existing offline golden-set regression gate for free); llm-quality-evals job runs DeepEval + RAGAS (skips cleanly without GROQ_API_KEY, asserts once configured). Built scripts/build_ragas_dataset.py + build_deepeval_dataset.py mirroring build_golden_dataset.py's pattern, producing human-reviewed .candidates.json files -- never auto-merged, ground_truth requires human verification by design. Found and fixed a real bug in build_golden_dataset.py: it read final_response['agents'][...] but final_assembler_node actually writes final_response['recommendations'][...] -- confirmed via the checked-in fixture (all 50 golden runs had has_shortage_alerts=false), meaning the restock_when_shortage evaluator had been silently a no-op since it was written.</t>
         </is>
       </c>
-      <c r="F42" s="47" t="inlineStr">
+      <c r="F31" s="97" t="inlineStr">
         <is>
           <t>feat: CI eval gate, RAGAS/DeepEval dataset-refresh scripts; fix: golden-dataset key-path bug (restock evaluator was a no-op)</t>
         </is>
       </c>
-      <c r="G42" s="47" t="inlineStr">
+      <c r="G31" s="97" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H42" s="48" t="inlineStr">
+      <c r="H31" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I42" s="49" t="inlineStr">
+      <c r="I31" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J42" s="46" t="inlineStr">
+      <c r="J31" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K42" s="50" t="n">
+      <c r="K31" s="98" t="n">
         <v>46205</v>
       </c>
-      <c r="L42" s="50" t="n">
+      <c r="L31" s="98" t="n">
         <v>46205</v>
       </c>
-      <c r="M42" s="51" t="n">
+      <c r="M31" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N42" s="46" t="inlineStr">
+      <c r="N31" s="97" t="inlineStr">
         <is>
           <t>P6-S21</t>
         </is>
       </c>
-      <c r="O42" s="47" t="inlineStr">
+      <c r="O31" s="97" t="inlineStr">
         <is>
           <t>6 new tests for build_golden_dataset.py extractors, 10 new tests for the two dataset-refresh scripts, 11 corrected fixtures in test_swiggy_procurement_enricher.py. ACTION NEEDED: add GROQ_API_KEY + LANGSMITH_API_KEY as GitHub repo secrets for llm-quality-evals to assert anything.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="151.05" customHeight="1" s="72">
-      <c r="A43" s="44" t="inlineStr">
+    <row r="32" ht="52" customHeight="1" s="72">
+      <c r="A32" s="91" t="inlineStr">
         <is>
           <t>P6-S24</t>
         </is>
       </c>
-      <c r="B43" s="67" t="n"/>
-      <c r="C43" s="55" t="inlineStr">
+      <c r="B32" s="92" t="n"/>
+      <c r="C32" s="92" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D43" s="56" t="inlineStr">
+      <c r="D32" s="92" t="inlineStr">
         <is>
           <t>Circuit-breaker degraded-state UX on market intel panel</t>
         </is>
       </c>
-      <c r="E43" s="56" t="inlineStr">
+      <c r="E32" s="92" t="inlineStr">
         <is>
           <t>MarketIntelService now attaches competitor_status: {state, resets_in_seconds} to market_intel_output when CompetitorEnricher returns None, distinguishing 'circuit breaker open, retrying automatically' from genuine no-data -- previously both rendered the identical blank 'No competitor pricing data' message. SwiggyMarketIntelPanel.tsx shows an amber 'temporarily unavailable, retrying in ~N min' message for the former. Root-caused via a live run where competitor pricing vanished but Instamart pricing worked in the same run, traced to the Food MCP circuit breaker being open while Instamart's was closed.</t>
         </is>
       </c>
-      <c r="F43" s="56" t="inlineStr">
+      <c r="F32" s="92" t="inlineStr">
         <is>
           <t>feat: distinguish circuit-breaker degradation from genuine no-data on market intel panel</t>
         </is>
       </c>
-      <c r="G43" s="56" t="inlineStr">
+      <c r="G32" s="92" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H43" s="48" t="inlineStr">
+      <c r="H32" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I43" s="61" t="inlineStr">
+      <c r="I32" s="91" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J43" s="55" t="inlineStr">
+      <c r="J32" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K43" s="57" t="n">
+      <c r="K32" s="94" t="n">
         <v>46205</v>
       </c>
-      <c r="L43" s="57" t="n">
+      <c r="L32" s="94" t="n">
         <v>46205</v>
       </c>
-      <c r="M43" s="58" t="n">
+      <c r="M32" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="55" t="inlineStr">
+      <c r="N32" s="92" t="inlineStr">
         <is>
           <t>P6-S21</t>
         </is>
       </c>
-      <c r="O43" s="56" t="inlineStr">
+      <c r="O32" s="92" t="inlineStr">
         <is>
           <t>4 new tests in test_market_intel_service.py; live-verified (fresh circuit trip captured correctly mid-run)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="151.05" customHeight="1" s="72">
-      <c r="A44" s="44" t="inlineStr">
+    <row r="33" ht="52" customHeight="1" s="72">
+      <c r="A33" s="96" t="inlineStr">
         <is>
           <t>P6-S25</t>
         </is>
       </c>
-      <c r="B44" s="67" t="n"/>
-      <c r="C44" s="46" t="inlineStr">
+      <c r="B33" s="97" t="n"/>
+      <c r="C33" s="97" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D44" s="47" t="inlineStr">
+      <c r="D33" s="97" t="inlineStr">
         <is>
           <t>Replan loop convergence fix</t>
         </is>
       </c>
-      <c r="E44" s="47" t="inlineStr">
+      <c r="E33" s="97" t="inlineStr">
         <is>
           <t>replan_orchestrator only ever re-ran the aggregator, never menu_intelligence -- so retries resubmitted the exact same unchanged menu_output to the critic, which correctly rejected it again every time (confirmed via a live run stuck at 3 identical critic rejections, hitting the 2-retry cap on every attempt). Rewired REPLAN_ORCHESTRATOR -&gt; MENU_INTELLIGENCE (was -&gt; AGGREGATOR), threaded replan_context through as prior_feedback into MenuService.analyse_and_recommend() and the prompt. Verified safe under LangGraph's join semantics using the same proven pattern AGGREGATOR's existing dual incoming edges already use.</t>
         </is>
       </c>
-      <c r="F44" s="47" t="inlineStr">
+      <c r="F33" s="97" t="inlineStr">
         <is>
           <t>fix: replan loop now regenerates the plan instead of resubmitting the same one -- critic retries actually converge</t>
         </is>
       </c>
-      <c r="G44" s="47" t="inlineStr">
+      <c r="G33" s="97" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H44" s="48" t="inlineStr">
+      <c r="H33" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I44" s="53" t="inlineStr">
+      <c r="I33" s="96" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J44" s="46" t="inlineStr">
+      <c r="J33" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K44" s="50" t="n">
+      <c r="K33" s="98" t="n">
         <v>46205</v>
       </c>
-      <c r="L44" s="50" t="n">
+      <c r="L33" s="98" t="n">
         <v>46205</v>
       </c>
-      <c r="M44" s="51" t="n">
+      <c r="M33" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N44" s="46" t="inlineStr">
+      <c r="N33" s="97" t="inlineStr">
         <is>
           <t>P6-S09</t>
         </is>
       </c>
-      <c r="O44" s="47" t="inlineStr">
+      <c r="O33" s="97" t="inlineStr">
         <is>
           <t>1 new graph-level integration test (test_replan_loop_integration.py) mocking a revision-then-approval cycle and asserting MenuService is called twice with feedback threaded through; live-verified end to end</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="216" customHeight="1" s="72">
-      <c r="A45" s="44" t="inlineStr">
+    <row r="34" ht="52" customHeight="1" s="72">
+      <c r="A34" s="91" t="inlineStr">
         <is>
           <t>P6-S26</t>
         </is>
       </c>
-      <c r="B45" s="67" t="n"/>
-      <c r="C45" s="55" t="inlineStr">
+      <c r="B34" s="92" t="n"/>
+      <c r="C34" s="92" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D45" s="56" t="inlineStr">
+      <c r="D34" s="92" t="inlineStr">
         <is>
           <t>Menu-synthesis context-sharing fix (capacity awareness)</t>
         </is>
       </c>
-      <c r="E45" s="56" t="inlineStr">
+      <c r="E34" s="92" t="inlineStr">
         <is>
           <t>menu_intelligence is the graph's 5-way fan-in synthesis point (RESERVATION/COMPLAINT_INTELLIGENCE/INVENTORY/MARKET_INTEL/DINEOUT_MANAGER all converge on it) but the node only ever read 3 of those 5 outputs -- it hardcoded menu_assumptions['assumed_covers_within_capacity']=True on every run because it never received reservation/occupancy data at all. This fake assumption tripped a cross-agent conflict (Diff 2 in evaluation_sanity.py) on nearly every high-occupancy Friday Rush plan. Audited every node's state reads against the graph's edges to confirm this was the only structurally broken diff of the 5 (Diffs 3/4/5/6 all compare genuinely-computed values). Threaded reservation/market-intel/dineout context into MenuService.analyse_and_recommend(), computed capacity_constrained for real from reservation's own occupancy figure, added an explicit throughput-protection rule to the menu prompt when occupancy is high.</t>
         </is>
       </c>
-      <c r="F45" s="56" t="inlineStr">
+      <c r="F34" s="92" t="inlineStr">
         <is>
           <t>fix: menu_intelligence now genuinely synthesizes all 5 fan-in inputs instead of 3 -- closes a fake cross-agent conflict that capped every high-occupancy run</t>
         </is>
       </c>
-      <c r="G45" s="56" t="inlineStr">
+      <c r="G34" s="92" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H45" s="48" t="inlineStr">
+      <c r="H34" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I45" s="53" t="inlineStr">
+      <c r="I34" s="91" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J45" s="55" t="inlineStr">
+      <c r="J34" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K45" s="57" t="n">
+      <c r="K34" s="94" t="n">
         <v>46205</v>
       </c>
-      <c r="L45" s="57" t="n">
+      <c r="L34" s="94" t="n">
         <v>46206</v>
       </c>
-      <c r="M45" s="58" t="n">
+      <c r="M34" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N45" s="55" t="inlineStr">
+      <c r="N34" s="92" t="inlineStr">
         <is>
           <t>P6-S25</t>
         </is>
       </c>
-      <c r="O45" s="56" t="inlineStr">
+      <c r="O34" s="92" t="inlineStr">
         <is>
           <t>2 new tests in test_menu_service.py, 2 in test_agent_nodes.py, 3 new Diff-2 tests in test_evaluation_sanity.py; live-verified (stale_assumptions no longer contains the fake conflict)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="190.05" customHeight="1" s="72">
-      <c r="A46" s="44" t="inlineStr">
+    <row r="35" ht="52" customHeight="1" s="72">
+      <c r="A35" s="96" t="inlineStr">
         <is>
           <t>P6-S27</t>
         </is>
       </c>
-      <c r="B46" s="67" t="n"/>
-      <c r="C46" s="46" t="inlineStr">
+      <c r="B35" s="97" t="n"/>
+      <c r="C35" s="97" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D46" s="47" t="inlineStr">
+      <c r="D35" s="97" t="inlineStr">
         <is>
           <t>Critic assumption-diff override fix</t>
         </is>
       </c>
-      <c r="E46" s="47" t="inlineStr">
+      <c r="E35" s="97" t="inlineStr">
         <is>
           <t>critic_service.py unconditionally force-downgraded approved-&gt;revision (capped score at 0.72) whenever any stale cross-agent assumption existed, regardless of the LLM critic's own judgment. A live run showed the critic explicitly reasoning through a conflict and writing 'Approving with these items noted for the manager's attention' in its own notes, then getting silently overridden to revision anyway by this code (added in an earlier hardening pass adjacent to P6-S02). Removed the automatic verdict override specifically for assumption diffs, kept it for real deterministic policy/sanity-rule violations which should stay non-negotiable. Kept full visibility (feedback, notes, DecisionLog audit trail) -- the critic's own considered judgment is now trusted.</t>
         </is>
       </c>
-      <c r="F46" s="47" t="inlineStr">
+      <c r="F35" s="97" t="inlineStr">
         <is>
           <t>fix: critic no longer overrides its own considered approval when a stale assumption exists -- visibility kept, veto removed</t>
         </is>
       </c>
-      <c r="G46" s="47" t="inlineStr">
+      <c r="G35" s="97" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H46" s="48" t="inlineStr">
+      <c r="H35" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I46" s="53" t="inlineStr">
+      <c r="I35" s="96" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J46" s="46" t="inlineStr">
+      <c r="J35" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K46" s="50" t="n">
+      <c r="K35" s="98" t="n">
         <v>46206</v>
       </c>
-      <c r="L46" s="50" t="n">
+      <c r="L35" s="98" t="n">
         <v>46206</v>
       </c>
-      <c r="M46" s="51" t="n">
+      <c r="M35" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="46" t="inlineStr">
+      <c r="N35" s="97" t="inlineStr">
         <is>
           <t>P6-S26</t>
         </is>
       </c>
-      <c r="O46" s="47" t="inlineStr">
+      <c r="O35" s="97" t="inlineStr">
         <is>
           <t>1 test rewritten in test_critic_service.py; live-verified -- same scenario now reaches approved on first pass (score 0.74-0.82 across repeated runs) instead of capping at 0.72 every time</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="294" customHeight="1" s="72">
-      <c r="A47" s="44" t="inlineStr">
+    <row r="36" ht="52" customHeight="1" s="72">
+      <c r="A36" s="91" t="inlineStr">
         <is>
           <t>P6-S28</t>
         </is>
       </c>
-      <c r="B47" s="67" t="n"/>
-      <c r="C47" s="55" t="inlineStr">
+      <c r="B36" s="92" t="n"/>
+      <c r="C36" s="92" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D47" s="56" t="inlineStr">
+      <c r="D36" s="92" t="inlineStr">
         <is>
           <t>Inventory ordering bug + guardrail price-citation loss</t>
         </is>
       </c>
-      <c r="E47" s="56" t="inlineStr">
+      <c r="E36" s="92" t="inlineStr">
         <is>
           <t>Two real bugs found and fixed, different from the originally-planned scope (occupancy-aware restock urgency was not what was actually wrong). (1) ProcurementEnricher.enrich() ran AFTER the LLM recommendation call inside the old combined analyse_and_recommend(), so procurement_context was always None when the inventory prompt was built -- the prompt's 'name Swiggy explicitly' instruction was unreachable dead code. Split InventoryService into compute_shortage_data() (pure DB/projection, no LLM) + generate_recommendation() (LLM call); inventory_node.py now computes the real shortage list first, fetches live Instamart prices for exactly those ingredients, then generates the recommendation with prices already in hand. (2) Even after reordering, build_capped_restock_actions() -- the deterministic guardrail that always overrides the LLM's proposed quantities -- rebuilt restock_actions from shortage_alerts alone with zero access to procurement_context, silently discarding any Swiggy price citation regardless of prompt quality. Threaded procurement_context through merge_guardrailed_recommendation() -&gt; build_capped_restock_actions(), which now appends 'Swiggy Instamart lists it at Rs.X/unit (in stock)' to the capped line for each priced ingredient.</t>
         </is>
       </c>
-      <c r="F47" s="56" t="inlineStr">
+      <c r="F36" s="92" t="inlineStr">
         <is>
           <t>fix: inventory Instamart price ordering + guardrail now carries Swiggy price citation through to restock_actions</t>
         </is>
       </c>
-      <c r="G47" s="56" t="inlineStr">
+      <c r="G36" s="92" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H47" s="48" t="inlineStr">
+      <c r="H36" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I47" s="49" t="inlineStr">
+      <c r="I36" s="91" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J47" s="55" t="inlineStr">
+      <c r="J36" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K47" s="57" t="n">
+      <c r="K36" s="94" t="n">
         <v>46206</v>
       </c>
-      <c r="L47" s="57" t="n">
+      <c r="L36" s="94" t="n">
         <v>46206</v>
       </c>
-      <c r="M47" s="58" t="n">
+      <c r="M36" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="55" t="inlineStr">
+      <c r="N36" s="92" t="inlineStr">
         <is>
           <t>P6-S26</t>
         </is>
       </c>
-      <c r="O47" s="56" t="inlineStr">
+      <c r="O36" s="92" t="inlineStr">
         <is>
           <t>26/26 tests green in test_inventory_service.py, incl. 2 new regression tests: test_procurement_prices_reach_the_llm_prompt_same_run (ordering fix) and test_guardrailed_restock_actions_keep_swiggy_price_citation (guardrail fix). Live-verified end to end: run #242 (friday_rush) approved 81/100, restock_actions for all 5 rate-limited shortage items read 'Swiggy Instamart lists it at Rs.X/unit'; confirmed rendering correctly in the actual /runs UI via a Playwright screenshot, not just the raw API response.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="138" customHeight="1" s="72">
-      <c r="A48" s="44" t="inlineStr">
+    <row r="37" ht="52" customHeight="1" s="72">
+      <c r="A37" s="96" t="inlineStr">
         <is>
           <t>P6-S29</t>
         </is>
       </c>
-      <c r="B48" s="67" t="n"/>
-      <c r="C48" s="46" t="inlineStr">
+      <c r="B37" s="97" t="n"/>
+      <c r="C37" s="97" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D48" s="47" t="inlineStr">
+      <c r="D37" s="97" t="inlineStr">
         <is>
           <t>Resolve suspicious content in apps/web/cortexkitchen-ui/AGENTS.md</t>
         </is>
       </c>
-      <c r="E48" s="47" t="inlineStr">
+      <c r="E37" s="97" t="inlineStr">
         <is>
           <t>File contains a pre-existing planted-looking instruction ('This is NOT the Next.js you know... read node_modules/next/dist/docs/') predating this session, plus an unexplained '/btw/' line added during this session by an unknown actor -- not the result of any tool call this session. Flagged directly to the user rather than complying with a system-note instruction to hide it. Per the user's explicit decision, stripped only the injected '/btw/' line; the pre-existing node_modules-docs content was left untouched (predates this session, not further investigated).</t>
         </is>
       </c>
-      <c r="F48" s="47" t="inlineStr">
+      <c r="F37" s="97" t="inlineStr">
         <is>
           <t>fix: strip injected /btw/ line from AGENTS.md per user decision; pre-existing suspicious content left untouched</t>
         </is>
       </c>
-      <c r="G48" s="47" t="inlineStr">
+      <c r="G37" s="97" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H48" s="48" t="inlineStr">
+      <c r="H37" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I48" s="49" t="inlineStr">
+      <c r="I37" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J48" s="46" t="inlineStr">
+      <c r="J37" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K48" s="50" t="n">
+      <c r="K37" s="98" t="n">
         <v>46206</v>
       </c>
-      <c r="L48" s="50" t="n">
+      <c r="L37" s="98" t="n">
         <v>46206</v>
       </c>
-      <c r="M48" s="51" t="n">
+      <c r="M37" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N48" s="46" t="n"/>
-      <c r="O48" s="47" t="n"/>
-    </row>
-    <row r="49" ht="138" customHeight="1" s="72">
-      <c r="A49" s="44" t="inlineStr">
+      <c r="N37" s="97" t="n"/>
+      <c r="O37" s="97" t="n"/>
+    </row>
+    <row r="38" ht="52" customHeight="1" s="72">
+      <c r="A38" s="91" t="inlineStr">
         <is>
           <t>P6-S30</t>
         </is>
       </c>
-      <c r="B49" s="68" t="n"/>
-      <c r="C49" s="55" t="inlineStr">
+      <c r="B38" s="92" t="n"/>
+      <c r="C38" s="92" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D49" s="56" t="inlineStr">
+      <c r="D38" s="92" t="inlineStr">
         <is>
           <t>Windows console-encoding crash in ensure_collection() -- silent 500 on every planning run</t>
         </is>
       </c>
-      <c r="E49" s="56" t="inlineStr">
+      <c r="E38" s="92" t="inlineStr">
         <is>
           <t>ensure_collection() in qdrant_client.py printed a checkmark (a non-ASCII Unicode symbol) on every Qdrant collection check. Windows console codepage (cp1252, not UTF-8) can't encode that character, so print() raised UnicodeEncodeError inside a FastAPI dependency (get_memory) resolved on every request that touches memory/RAG context -- i.e. every planning run. The client received a malformed non-JSON response with no clear error. Root-caused by reading the raw response body instead of assuming a timeout. Replaced both Unicode symbols with ASCII-safe '[OK]'/'[INFO]' text.</t>
         </is>
       </c>
-      <c r="F49" s="56" t="inlineStr">
+      <c r="F38" s="92" t="inlineStr">
         <is>
           <t>fix: replace non-ASCII print() characters in ensure_collection() -- was silently 500ing every planning run on Windows</t>
         </is>
       </c>
-      <c r="G49" s="56" t="inlineStr">
+      <c r="G38" s="92" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H49" s="48" t="inlineStr">
+      <c r="H38" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I49" s="53" t="inlineStr">
+      <c r="I38" s="91" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J49" s="55" t="inlineStr">
+      <c r="J38" s="91" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K49" s="57" t="n">
+      <c r="K38" s="94" t="n">
         <v>46206</v>
       </c>
-      <c r="L49" s="57" t="n">
+      <c r="L38" s="94" t="n">
         <v>46206</v>
       </c>
-      <c r="M49" s="58" t="n">
+      <c r="M38" s="95" t="n">
         <v>1</v>
       </c>
-      <c r="N49" s="55" t="inlineStr">
+      <c r="N38" s="92" t="inlineStr">
         <is>
           <t>P6-S21</t>
         </is>
       </c>
-      <c r="O49" s="56" t="inlineStr">
+      <c r="O38" s="92" t="inlineStr">
         <is>
           <t>Manual live verification: reproduced the crash via a live curl planning run returning invalid JSON, root-caused via the raw backend traceback, fixed, then re-ran the same friday_rush scenario twice (run #241, #242) end to end with no crash.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="108" customHeight="1" s="72">
-      <c r="A50" s="44" t="inlineStr">
+    <row r="39" ht="52" customHeight="1" s="72">
+      <c r="A39" s="96" t="inlineStr">
         <is>
           <t>P6-S31</t>
         </is>
       </c>
-      <c r="B50" s="68" t="inlineStr">
+      <c r="B39" s="97" t="inlineStr">
         <is>
           <t>fix/ci-fastapi-starlette-conflict</t>
         </is>
       </c>
-      <c r="C50" s="55" t="inlineStr">
+      <c r="C39" s="97" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D50" s="56" t="inlineStr">
+      <c r="D39" s="97" t="inlineStr">
         <is>
           <t>Fix CI dependency-resolution conflicts blocking backend-tests workflow</t>
         </is>
       </c>
-      <c r="E50" s="56" t="inlineStr">
+      <c r="E39" s="97" t="inlineStr">
         <is>
           <t>Two real, independent pip dependency conflicts in requirements.txt, both invisible locally because local envs already had incompatible-but-coexisting packages installed from before the pins were added, so pip never had to resolve from scratch. (1) fastapi==0.115.0 requires starlette&lt;0.39.0, but starlette==0.41.3 is pinned directly below it -- a hard, unresolvable conflict that failed every fresh install immediately. Fixed by bumping fastapi to 0.115.14, whose declared range covers the existing (deliberate) starlette pin. (2) After that fix, pip could install but pytest crashed importing deepeval: pydantic==2.9.2 and pydantic-settings==2.5.2 were too old for any current deepeval release, so the resolver silently backtracked to an ancient deepeval (~2.x) with a real packaging bug (imports posthog without reliably declaring it as a dependency) instead of erroring. Fixed by bumping pydantic to 2.13.4, pydantic-settings to 2.14.2, python-dotenv to 1.2.2 (also required by current deepeval), and pinning deepeval==4.0.7 explicitly so it can't silently drift to a broken version again. Also dropped the redis[asyncio] extra (redis-py ships asyncio support built in now; the extra no longer exists and pip warned about it on every install).</t>
         </is>
       </c>
-      <c r="F50" s="56" t="inlineStr">
+      <c r="F39" s="97" t="inlineStr">
         <is>
           <t>fix: resolve fastapi/starlette version conflict + pydantic/deepeval conflict breaking CI dependency install</t>
         </is>
       </c>
-      <c r="G50" s="56" t="inlineStr">
+      <c r="G39" s="97" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H50" s="48" t="inlineStr">
+      <c r="H39" s="93" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I50" s="53" t="inlineStr">
+      <c r="I39" s="96" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J50" s="55" t="inlineStr">
+      <c r="J39" s="96" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K50" s="57" t="n">
+      <c r="K39" s="98" t="n">
         <v>46206</v>
       </c>
-      <c r="L50" s="57" t="n">
+      <c r="L39" s="98" t="n">
         <v>46206</v>
       </c>
-      <c r="M50" s="58" t="n">
+      <c r="M39" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="55" t="inlineStr">
+      <c r="N39" s="97" t="inlineStr">
         <is>
           <t>P6-S23</t>
         </is>
       </c>
-      <c r="O50" s="56" t="inlineStr">
+      <c r="O39" s="97" t="inlineStr">
         <is>
           <t>Verified with a genuinely fresh from-scratch install (uv, not relying on previously-installed local packages): full unit test suite (343 passed) and both eval files (evals/test_deepeval_quality.py, evals/test_ragas_complaint.py -- 8 passed) run clean. Live-verified on GitHub Actions: PR #88 backend-tests workflow both jobs completed/success after the fix (both had failed -- one on install, one on test-run import crash -- before it).</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="7.95" customHeight="1" s="72">
-      <c r="A51" s="52" t="n"/>
-      <c r="B51" s="52" t="n"/>
-      <c r="C51" s="52" t="n"/>
-      <c r="D51" s="52" t="n"/>
-      <c r="E51" s="52" t="n"/>
-      <c r="F51" s="52" t="n"/>
-      <c r="G51" s="52" t="n"/>
-      <c r="H51" s="52" t="n"/>
-      <c r="I51" s="52" t="n"/>
-      <c r="J51" s="52" t="n"/>
-      <c r="K51" s="52" t="n"/>
-      <c r="L51" s="52" t="n"/>
-      <c r="M51" s="52" t="n"/>
-      <c r="N51" s="52" t="n"/>
-      <c r="O51" s="52" t="n"/>
-    </row>
-    <row r="52" ht="99" customHeight="1" s="72">
-      <c r="A52" s="62" t="inlineStr">
+    <row r="40" ht="52" customHeight="1" s="72">
+      <c r="A40" s="91" t="inlineStr">
+        <is>
+          <t>P6-F09</t>
+        </is>
+      </c>
+      <c r="B40" s="92" t="inlineStr">
+        <is>
+          <t>feature/design-system-theming</t>
+        </is>
+      </c>
+      <c r="C40" s="92" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D40" s="92" t="inlineStr">
+        <is>
+          <t>Design system: light/dark theme + token system</t>
+        </is>
+      </c>
+      <c r="E40" s="92" t="inlineStr">
+        <is>
+          <t>Add a parallel light-mode palette alongside the existing ink/ember dark tokens in globals.css (Tailwind v4 @theme), wire a theme toggle (persisted via localStorage, defaults to system prefers-color-scheme) accessible from every page's header/nav, and audit + replace ad-hoc opacity-based dark-only utility classes (text-white/65, bg-white/[0.02], etc.) across all ~35 dashboard/runs/chat components with theme-aware tokens so both modes render correctly. Target users skew middle-aged restaurant owners/managers who may find a dark-only dev-tool aesthetic hard to read or off-putting -- a toggle makes the product usable for both preferences, not just engineers. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. DONE 2026-07-04: light-mode token layer + toggle built and applied across all ~30 pages/components (not just the 5 touched in the direction prototype), via a boundary-safe scripted class rename so the same old class always maps to the same new token. 3 real bugs found only by driving the app in a browser (not catchable by a class-rename script alone): ember accent text washed out on light badges (fixed via --color-accent token), DatePicker select/date-input had inline style={{background:...}} overriding the className entirely, and no explicit color-scheme meant native &lt;select&gt;/&lt;option&gt; rendered with OS dark chrome regardless of page theme. Verified end-to-end with a real registered test account across dashboard/runs/connectors/chat in both themes -- zero console errors, zero hydration warnings, tsc + eslint clean.</t>
+        </is>
+      </c>
+      <c r="F40" s="92" t="inlineStr">
+        <is>
+          <t>feat: light/dark theme system with persisted toggle</t>
+        </is>
+      </c>
+      <c r="G40" s="92" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="H40" s="93" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I40" s="91" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J40" s="91" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K40" s="94" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L40" s="94" t="n">
+        <v>46207</v>
+      </c>
+      <c r="M40" s="95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="92" t="n"/>
+      <c r="O40" s="92" t="inlineStr">
+        <is>
+          <t>Toggle switches and persists across reload; spot-check contrast/readability of all dashboard/runs/chat components in both modes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="52" customHeight="1" s="72">
+      <c r="A41" s="96" t="inlineStr">
+        <is>
+          <t>P6-F10</t>
+        </is>
+      </c>
+      <c r="B41" s="97" t="n"/>
+      <c r="C41" s="97" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D41" s="97" t="inlineStr">
+        <is>
+          <t>De-console-ify typography and visual hierarchy</t>
+        </is>
+      </c>
+      <c r="E41" s="97" t="inlineStr">
+        <is>
+          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. NOTE: the ember-accent-text contrast fix (text-ember-300/400 -&gt; --color-accent token) was already done as part of P6-F09 verification, since it was blocking basic light-mode readability, not a nice-to-have. Remaining F10 scope: pull font-mono back from being the default label voice everywhere to a true accent. DONE 2026-07-4: two-pass conversion -- (1) mechanical pass on the specific font-mono+uppercase+tracking- combination (171 label class-strings, always a decorative label in this codebase, never data), (2) per-instance judgment pass on the remaining ~89 bare font-mono usages, since this codebase used monospace for three genuinely different things (real data, category/status labels, and even prose/error messages) that no single mechanical rule could tell apart. Demoted buttons/links/status words/category badges/prose; kept genuine data (prices, IDs, timestamps, scores, deltas, code blocks). Also caught 2 more instances of hardcoded legacy bg-navy-*/text-gold-* colors (a different legacy palette than bg-ink-*, missed by the original P6-F09 conversion script) while auditing context file-by-file. Verified in browser (dashboard, runs) both themes -- zero console errors, tsc clean. FOLLOW-UP 2026-07-4: initial Completed mark only covered the mono-demotion half; the serif-extension half (matching the landing page voice) was still missing. Fixed: dashboard hero emphasis line switched from a color gradient to the landing page's proven display-it italic accent pattern; 5 bare page titles (Plan History, Connectors, Data Health, Workspace Settings, Restaurant Profiles) converted from plain bold sans to the .display serif class; key numeric stat tiles (connectors sync counts, runs KPI Metric component) converted to .num-display serif figures. Now genuinely done both halves.</t>
+        </is>
+      </c>
+      <c r="F41" s="97" t="inlineStr">
+        <is>
+          <t>feat: rebalance typography -- monospace as accent, not primary label voice</t>
+        </is>
+      </c>
+      <c r="G41" s="97" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="H41" s="93" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I41" s="96" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J41" s="96" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K41" s="98" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L41" s="98" t="n">
+        <v>46207</v>
+      </c>
+      <c r="M41" s="99" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="97" t="inlineStr">
+        <is>
+          <t>P6-F09</t>
+        </is>
+      </c>
+      <c r="O41" s="97" t="inlineStr">
+        <is>
+          <t>Visual diff of dashboard/runs headers and stat labels before/after; landing-page-level polish confirmed by eye on both themes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="52" customHeight="1" s="72">
+      <c r="A42" s="91" t="inlineStr">
+        <is>
+          <t>P6-F11</t>
+        </is>
+      </c>
+      <c r="B42" s="92" t="n"/>
+      <c r="C42" s="92" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D42" s="92" t="inlineStr">
+        <is>
+          <t>Information architecture restructure: split the mega-dashboard into focused pages</t>
+        </is>
+      </c>
+      <c r="E42" s="92" t="inlineStr">
+        <is>
+          <t>The single /dashboard page currently tries to show demand forecast + reservations + complaints + inventory + market intel + menu + critic + connector status all at once -- reads as a diagnostics dump a manager could get lost in. Restructure into: a lightweight /dashboard 'Today' view (KPIs, alerts, pending actions only -- what a manager checks first each morning), a dedicated /operations page for the 5 planning-agent outputs in plain-language framing (not raw JSON-shaped cards), and Swiggy Market Intelligence promoted to its own dedicated /market page (competitor pricing, occupancy, Instamart procurement) so it has a clear, demo-able home separate from internal ops data -- matching the product's own internal-vs-Swiggy-data distinction already documented in CLAUDE.md. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. DONE 2026-07-04: split shipped -- /dashboard is now the lightweight 'Today' view (TodayIdleState: business KPIs, market intel teaser, actionable ops snapshot), /operations holds the 5 agent-card detail + CriticBanner + ForecastChart + ManagerActionPanel (via useSelectedRun, reads ?run={id} or falls back to most recent), /market is the dedicated Swiggy market intelligence page. Verified end-to-end via Playwright: fresh register -&gt; idle state renders clean in both themes -&gt; trigger a plan via the new PlanShiftModal -&gt; auto-redirects to /operations?run={id} with the CriticBanner visible on landing, zero console errors.</t>
+        </is>
+      </c>
+      <c r="F42" s="92" t="inlineStr">
+        <is>
+          <t>feat(P6-F11/F12): redesign Today dashboard -- modal planning flow, market-aware layout, warm theme</t>
+        </is>
+      </c>
+      <c r="G42" s="92" t="inlineStr">
+        <is>
+          <t>CLAUDE.md (nav/page map section), docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H42" s="93" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I42" s="91" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J42" s="91" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K42" s="94" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L42" s="94" t="n">
+        <v>46207</v>
+      </c>
+      <c r="M42" s="95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="92" t="inlineStr">
+        <is>
+          <t>P6-F10</t>
+        </is>
+      </c>
+      <c r="O42" s="92" t="inlineStr">
+        <is>
+          <t>Each new page renders its intended slice only; nav updated; no orphaned links to the old single-page layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="52" customHeight="1" s="72">
+      <c r="A43" s="96" t="inlineStr">
+        <is>
+          <t>P6-F18</t>
+        </is>
+      </c>
+      <c r="B43" s="97" t="inlineStr">
+        <is>
+          <t>feature/design-system-theming</t>
+        </is>
+      </c>
+      <c r="C43" s="97" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D43" s="97" t="inlineStr">
+        <is>
+          <t>Live market intelligence + business analytics endpoints, independent of planning runs</t>
+        </is>
+      </c>
+      <c r="E43" s="97" t="inlineStr">
+        <is>
+          <t>GET /api/v1/market/pulse calls CompetitorEnricher/OccupancyEnricher/ProcurementEnricher directly (no planning run required) and structures diff_pct/direction comparisons server-side, since the raw enrichers return loosely-typed dicts, not a UI-ready shape. GET /api/v1/business/performance computes real revenue/profit via a new MenuItem.cost_price column, daily trend, yesterday/today snapshots, top/bottom dishes, dine-in vs delivery channel split, complaints grouped by keyword-matched category, and peak-hours demand (orders only, so future-dated reservation seed rows don't skew 'when are we actually busy'). DONE 2026-07-04: verified against seeded data -- revenue, margin, and complaint-category counts all match expected values. NOTE: this commit's message (eaef859) and an earlier CLAUDE.md pass informally used the tag 'P6-F16', which collides with an already-used tag from the P6-F14/F15/F17 PR (2026-07-01) that was never given tracker rows -- P6-F18 is the correct sequential tracker ID; the git history is left as-is rather than rewritten.</t>
+        </is>
+      </c>
+      <c r="F43" s="97" t="inlineStr">
+        <is>
+          <t>feat(P6-F16 in commit msg / P6-F18 in tracker): live market intelligence + business analytics, independent of planning runs</t>
+        </is>
+      </c>
+      <c r="G43" s="97" t="inlineStr">
+        <is>
+          <t>CLAUDE.md (API routes section, Swiggy token/circuit-breaker gotcha)</t>
+        </is>
+      </c>
+      <c r="H43" s="93" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I43" s="96" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J43" s="96" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K43" s="98" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L43" s="98" t="n">
+        <v>46207</v>
+      </c>
+      <c r="M43" s="99" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="97" t="inlineStr">
+        <is>
+          <t>P6-S15</t>
+        </is>
+      </c>
+      <c r="O43" s="97" t="inlineStr">
+        <is>
+          <t>Hit /market/pulse and /business/performance directly against seeded data; confirm revenue/margin/complaint-category numbers match the seed script, and market pulse returns swiggy_connected + live comparisons when the token is valid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="52" customHeight="1" s="72">
+      <c r="A44" s="91" t="inlineStr">
+        <is>
+          <t>P6-F19</t>
+        </is>
+      </c>
+      <c r="B44" s="92" t="inlineStr">
+        <is>
+          <t>feature/design-system-theming</t>
+        </is>
+      </c>
+      <c r="C44" s="92" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D44" s="92" t="inlineStr">
+        <is>
+          <t>Today dashboard redesign: modal planning flow, warm theme, NavBar cleanup, date-relative seed data</t>
+        </is>
+      </c>
+      <c r="E44" s="92" t="inlineStr">
+        <is>
+          <t>TodayIdleState fully rewritten around a manager's actual priorities: overall performance chart, actionable 'tonight at a glance' reservations/inventory snapshot, yesterday's business KPIs with channel split, menu performance (top/bottom sellers), peak hours paired with a merged guest-sentiment + complaint-theme card, and a consolidated market intelligence card teasing into /market. 'Plan your next shift' now opens PlanShiftModal instead of running inline. NavBar: removed the scenario dropdown (the modal owns scenario selection now) and the stale 'Friday Rush -- not planned yet' status chip; warmer brand mark and active-tab styling. globals.css light-mode tokens rebuilt around a warm stone/parchment palette instead of cool blue-gray. Also fixed a glitch where the critic-approved banner flashed on /dashboard for one frame and vanished on redirect to /operations -- /operations now shows CriticBanner directly instead of burying the verdict in the Manager Brief modal. seed_demo_data.py no longer hardcodes 2026 calendar dates -- SEED_AS_OF anchors to run-time so 'Today' always reflects live state, and inventory was rebalanced from a permanent 11/18 shortage state to 3/18 genuinely low items. DONE 2026-07-04: verified end-to-end via Playwright (fresh register, both themes, full plan-run -&gt; redirect -&gt; critic banner flow), zero console errors.</t>
+        </is>
+      </c>
+      <c r="F44" s="92" t="inlineStr">
+        <is>
+          <t>feat(P6-F11/F12): redesign Today dashboard -- modal planning flow, market-aware layout, warm theme</t>
+        </is>
+      </c>
+      <c r="G44" s="92" t="inlineStr">
+        <is>
+          <t>CLAUDE.md (page map, theming section)</t>
+        </is>
+      </c>
+      <c r="H44" s="93" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I44" s="91" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J44" s="91" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K44" s="94" t="n">
+        <v>46207</v>
+      </c>
+      <c r="L44" s="94" t="n">
+        <v>46207</v>
+      </c>
+      <c r="M44" s="95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="92" t="inlineStr">
+        <is>
+          <t>P6-F11; P6-F18</t>
+        </is>
+      </c>
+      <c r="O44" s="92" t="inlineStr">
+        <is>
+          <t>Playwright: register -&gt; idle state renders clean (light+dark, no console errors) -&gt; open PlanShiftModal -&gt; Generate Plan -&gt; auto-redirect to /operations?run={id} with CriticBanner visible, no flash/glitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="8" customHeight="1" s="72"/>
+    <row r="46" ht="18" customHeight="1" s="72">
+      <c r="A46" s="100" t="inlineStr">
+        <is>
+          <t>PLANNED — build in this order (all below work without staging creds unless noted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1" s="72"/>
+    <row r="48" ht="18" customHeight="1" s="72">
+      <c r="A48" s="90" t="inlineStr">
+        <is>
+          <t>PRIORITY 1 — Market Intelligence Expansion (new Swiggy tools — build first)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="52" customHeight="1" s="72">
+      <c r="A49" s="101" t="inlineStr">
         <is>
           <t>P6-MI01</t>
         </is>
       </c>
-      <c r="B52" s="69" t="inlineStr">
+      <c r="B49" s="102" t="inlineStr">
         <is>
           <t>feature/swiggy-market-intel-expansion</t>
         </is>
       </c>
-      <c r="C52" s="55" t="inlineStr">
+      <c r="C49" s="102" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D52" s="56" t="inlineStr">
+      <c r="D49" s="102" t="inlineStr">
         <is>
           <t>Competitor deal &amp; offer intelligence</t>
         </is>
       </c>
-      <c r="E52" s="56" t="inlineStr">
+      <c r="E49" s="102" t="inlineStr">
         <is>
           <t>Surface deal and amenity data from get_restaurant_details (already called in OccupancyEnricher but data discarded). Extract: deals[], isFree, title, amenities[], highlights[], avgRating per competitor. Add to market_intel_output as competitor_deals list. Show in Market Intelligence panel: Competitor X running 20% off deal. Has live music + valet. No new API calls — uses data already fetched.</t>
         </is>
       </c>
-      <c r="F52" s="56" t="inlineStr">
+      <c r="F49" s="102" t="inlineStr">
         <is>
           <t>feat: surface competitor deal and amenity intelligence from Dineout MCP</t>
         </is>
       </c>
-      <c r="G52" s="56" t="inlineStr">
+      <c r="G49" s="102" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (OccupancyEnricher output extended)</t>
         </is>
       </c>
-      <c r="H52" s="63" t="inlineStr">
+      <c r="H49" s="103" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I52" s="49" t="inlineStr">
+      <c r="I49" s="101" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J52" s="55" t="n"/>
-      <c r="K52" s="55" t="n"/>
-      <c r="L52" s="55" t="n"/>
-      <c r="M52" s="55" t="n"/>
-      <c r="N52" s="55" t="n"/>
-      <c r="O52" s="56" t="n"/>
-    </row>
-    <row r="53" ht="112.05" customHeight="1" s="72">
-      <c r="A53" s="62" t="inlineStr">
+      <c r="J49" s="101" t="n"/>
+      <c r="K49" s="101" t="n"/>
+      <c r="L49" s="101" t="n"/>
+      <c r="M49" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="102" t="n"/>
+      <c r="O49" s="102" t="n"/>
+    </row>
+    <row r="50" ht="52" customHeight="1" s="72">
+      <c r="A50" s="105" t="inlineStr">
         <is>
           <t>P6-MI02</t>
         </is>
       </c>
-      <c r="B53" s="67" t="n"/>
-      <c r="C53" s="46" t="inlineStr">
+      <c r="B50" s="106" t="n"/>
+      <c r="C50" s="106" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D53" s="47" t="inlineStr">
+      <c r="D50" s="106" t="inlineStr">
         <is>
           <t>Competitor price trend tracking</t>
         </is>
       </c>
-      <c r="E53" s="47" t="inlineStr">
+      <c r="E50" s="106" t="inlineStr">
         <is>
           <t>New table: market_snapshots (org_id, snapshot_type, data jsonb, captured_at). After each planning run, persist competitor_pricing dict from CompetitorEnricher. MarketIntelService computes week-over-week delta per dish. market_intel_output gains price_trends field: [{dish, current_avg, prev_avg, delta_pct, direction}]. Panel shows: Biryani area avg up 18pct vs last week. Zero new Swiggy API calls - just persisting what we already fetch.</t>
         </is>
       </c>
-      <c r="F53" s="47" t="inlineStr">
+      <c r="F50" s="106" t="inlineStr">
         <is>
           <t>feat: competitor price trend tracking — persist snapshots, week-over-week delta</t>
         </is>
       </c>
-      <c r="G53" s="47" t="inlineStr">
+      <c r="G50" s="106" t="inlineStr">
         <is>
           <t>docs/DATA_MODEL.md (market_snapshots table), docs/AGENTS.md</t>
         </is>
       </c>
-      <c r="H53" s="63" t="inlineStr">
+      <c r="H50" s="103" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I53" s="49" t="inlineStr">
+      <c r="I50" s="105" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J53" s="46" t="n"/>
-      <c r="K53" s="46" t="n"/>
-      <c r="L53" s="46" t="n"/>
-      <c r="M53" s="46" t="n"/>
-      <c r="N53" s="46" t="n"/>
-      <c r="O53" s="47" t="n"/>
-    </row>
-    <row r="54" ht="124.95" customHeight="1" s="72">
-      <c r="A54" s="62" t="inlineStr">
+      <c r="J50" s="105" t="n"/>
+      <c r="K50" s="105" t="n"/>
+      <c r="L50" s="105" t="n"/>
+      <c r="M50" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="106" t="n"/>
+      <c r="O50" s="106" t="n"/>
+    </row>
+    <row r="51" ht="52" customHeight="1" s="72">
+      <c r="A51" s="101" t="inlineStr">
         <is>
           <t>P6-MI03</t>
         </is>
       </c>
-      <c r="B54" s="68" t="n"/>
-      <c r="C54" s="55" t="inlineStr">
+      <c r="B51" s="102" t="n"/>
+      <c r="C51" s="102" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D54" s="56" t="inlineStr">
+      <c r="D51" s="102" t="inlineStr">
         <is>
           <t>Category-level pricing analysis</t>
         </is>
       </c>
-      <c r="E54" s="56" t="inlineStr">
+      <c r="E51" s="102" t="inlineStr">
         <is>
           <t>CompetitorEnricher currently returns flat dish-&gt;price dict. Extend to group by inferred category (biryani/starters/mains/drinks). Compute area avg per category. Compare against restaurant menu categories. Output: [{category, your_avg, area_avg, diff_pct, verdict}]. menu_intelligence prompt gains: Your North Indian mains avg Rs.320 vs area Rs.275 (+16pct). Your starters Rs.180 vs area Rs.210 (-14pct underpriced). No new API calls - aggregation on existing CompetitorEnricher output.</t>
         </is>
       </c>
-      <c r="F54" s="56" t="inlineStr">
+      <c r="F51" s="102" t="inlineStr">
         <is>
           <t>feat: category-level pricing — group competitor prices by category vs your menu</t>
         </is>
       </c>
-      <c r="G54" s="56" t="inlineStr">
+      <c r="G51" s="102" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (CompetitorEnricher output extended)</t>
         </is>
       </c>
-      <c r="H54" s="63" t="inlineStr">
+      <c r="H51" s="103" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I54" s="49" t="inlineStr">
+      <c r="I51" s="101" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J54" s="55" t="n"/>
-      <c r="K54" s="55" t="n"/>
-      <c r="L54" s="55" t="n"/>
-      <c r="M54" s="55" t="n"/>
-      <c r="N54" s="55" t="n"/>
-      <c r="O54" s="56" t="n"/>
-    </row>
-    <row r="55" ht="7.95" customHeight="1" s="72">
-      <c r="A55" s="52" t="n"/>
-      <c r="B55" s="52" t="n"/>
-      <c r="C55" s="52" t="n"/>
-      <c r="D55" s="52" t="n"/>
-      <c r="E55" s="52" t="n"/>
-      <c r="F55" s="52" t="n"/>
-      <c r="G55" s="52" t="n"/>
-      <c r="H55" s="52" t="n"/>
-      <c r="I55" s="52" t="n"/>
-      <c r="J55" s="52" t="n"/>
-      <c r="K55" s="52" t="n"/>
-      <c r="L55" s="52" t="n"/>
-      <c r="M55" s="52" t="n"/>
-      <c r="N55" s="52" t="n"/>
-      <c r="O55" s="52" t="n"/>
-    </row>
-    <row r="56" ht="124.95" customHeight="1" s="72">
-      <c r="A56" s="62" t="inlineStr">
+      <c r="J51" s="101" t="n"/>
+      <c r="K51" s="101" t="n"/>
+      <c r="L51" s="101" t="n"/>
+      <c r="M51" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="102" t="n"/>
+      <c r="O51" s="102" t="n"/>
+    </row>
+    <row r="52" ht="52" customHeight="1" s="72">
+      <c r="A52" s="105" t="inlineStr">
         <is>
           <t>P6-MI04</t>
         </is>
       </c>
-      <c r="B56" s="69" t="inlineStr">
+      <c r="B52" s="106" t="inlineStr">
         <is>
           <t>feature/swiggy-chatbot-expansion</t>
         </is>
       </c>
-      <c r="C56" s="55" t="inlineStr">
+      <c r="C52" s="106" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D56" s="56" t="inlineStr">
+      <c r="D52" s="106" t="inlineStr">
         <is>
           <t>Chatbot — Dineout competitive queries</t>
         </is>
       </c>
-      <c r="E56" s="56" t="inlineStr">
+      <c r="E52" s="106" t="inlineStr">
         <is>
           <t>Add 3 new Groq function-calling tools to chatbot: get_competitor_deals(cuisine, addressId) answers what deals are competitors running tonight; get_area_occupancy(cuisine, addressId) answers how full are restaurants near me; get_trending_dishes(addressId) answers what are competitors pushing on menus. All use existing Dineout MCP tools: search_restaurants_dineout, get_restaurant_details, get_available_slots. Makes chatbot the single interface for all live Swiggy market queries.</t>
         </is>
       </c>
-      <c r="F56" s="56" t="inlineStr">
+      <c r="F52" s="106" t="inlineStr">
         <is>
           <t>feat: chatbot Dineout queries — competitor deals, area occupancy, trending dishes</t>
         </is>
       </c>
-      <c r="G56" s="56" t="inlineStr">
+      <c r="G52" s="106" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (chatbot tools section)</t>
         </is>
       </c>
-      <c r="H56" s="63" t="inlineStr">
+      <c r="H52" s="103" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I56" s="49" t="inlineStr">
+      <c r="I52" s="105" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J56" s="55" t="n"/>
-      <c r="K56" s="55" t="n"/>
-      <c r="L56" s="55" t="n"/>
-      <c r="M56" s="55" t="n"/>
-      <c r="N56" s="55" t="n"/>
-      <c r="O56" s="56" t="n"/>
-    </row>
-    <row r="57" ht="7.95" customHeight="1" s="72">
-      <c r="A57" s="52" t="n"/>
-      <c r="B57" s="52" t="n"/>
-      <c r="C57" s="52" t="n"/>
-      <c r="D57" s="52" t="n"/>
-      <c r="E57" s="52" t="n"/>
-      <c r="F57" s="52" t="n"/>
-      <c r="G57" s="52" t="n"/>
-      <c r="H57" s="52" t="n"/>
-      <c r="I57" s="52" t="n"/>
-      <c r="J57" s="52" t="n"/>
-      <c r="K57" s="52" t="n"/>
-      <c r="L57" s="52" t="n"/>
-      <c r="M57" s="52" t="n"/>
-      <c r="N57" s="52" t="n"/>
-      <c r="O57" s="52" t="n"/>
-    </row>
-    <row r="58" ht="73.05" customHeight="1" s="72">
-      <c r="A58" s="62" t="inlineStr">
+      <c r="J52" s="105" t="n"/>
+      <c r="K52" s="105" t="n"/>
+      <c r="L52" s="105" t="n"/>
+      <c r="M52" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="106" t="n"/>
+      <c r="O52" s="106" t="n"/>
+    </row>
+    <row r="53" ht="52" customHeight="1" s="72">
+      <c r="A53" s="101" t="inlineStr">
+        <is>
+          <t>P6-MI05</t>
+        </is>
+      </c>
+      <c r="B53" s="102" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-extended</t>
+        </is>
+      </c>
+      <c r="C53" s="102" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D53" s="102" t="inlineStr">
+        <is>
+          <t>search_menu dish-level pricing in CompetitorEnricher</t>
+        </is>
+      </c>
+      <c r="E53" s="102" t="inlineStr">
+        <is>
+          <t>Call search_menu(query=dish_name) for top 5 menu items. Gets ALL competitor prices for that dish in one call — more precise than parsing full menus. vegFilter support. Add dish_prices dict to result. Update prompt with per-dish competitor table: "Butter Chicken: yours Rs.320 | competitors Rs.220-280 | area avg Rs.255".</t>
+        </is>
+      </c>
+      <c r="F53" s="102" t="inlineStr">
+        <is>
+          <t>feat: search_menu dish-level competitor pricing in CompetitorEnricher</t>
+        </is>
+      </c>
+      <c r="G53" s="102" t="inlineStr">
+        <is>
+          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md</t>
+        </is>
+      </c>
+      <c r="H53" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I53" s="101" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J53" s="101" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K53" s="101" t="inlineStr"/>
+      <c r="L53" s="101" t="inlineStr"/>
+      <c r="M53" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="102" t="inlineStr">
+        <is>
+          <t>P6-MI01</t>
+        </is>
+      </c>
+      <c r="O53" s="102" t="inlineStr">
+        <is>
+          <t>dish_prices in result dict; prompt includes per-dish table; max 5 dish searches per run</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="52" customHeight="1" s="72">
+      <c r="A54" s="105" t="inlineStr">
+        <is>
+          <t>P6-MI06</t>
+        </is>
+      </c>
+      <c r="B54" s="106" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-extended</t>
+        </is>
+      </c>
+      <c r="C54" s="106" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D54" s="106" t="inlineStr">
+        <is>
+          <t>fetch_food_coupons — competitor Swiggy promotional deals</t>
+        </is>
+      </c>
+      <c r="E54" s="106" t="inlineStr">
+        <is>
+          <t>For each competitor from search_restaurants, call fetch_food_coupons(restaurantId, addressId). Filter COD-compatible (requiresOnlinePayment=False). Build competitor_deals list. Inject into menu_intel prompt and market_intel_output. "3 competitors running deals tonight" changes pricing strategy. Public data — works with any auth session.</t>
+        </is>
+      </c>
+      <c r="F54" s="106" t="inlineStr">
+        <is>
+          <t>feat: fetch_food_coupons — live competitor Swiggy promotional intelligence</t>
+        </is>
+      </c>
+      <c r="G54" s="106" t="inlineStr">
+        <is>
+          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md</t>
+        </is>
+      </c>
+      <c r="H54" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I54" s="105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J54" s="105" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K54" s="105" t="inlineStr"/>
+      <c r="L54" s="105" t="inlineStr"/>
+      <c r="M54" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="106" t="inlineStr">
+        <is>
+          <t>P6-MI05</t>
+        </is>
+      </c>
+      <c r="O54" s="106" t="inlineStr">
+        <is>
+          <t>competitor_deals in result; filters online-payment coupons; max 3 calls per run</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="52" customHeight="1" s="72">
+      <c r="A55" s="101" t="inlineStr">
+        <is>
+          <t>P6-MI07</t>
+        </is>
+      </c>
+      <c r="B55" s="102" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-extended</t>
+        </is>
+      </c>
+      <c r="C55" s="102" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D55" s="102" t="inlineStr">
+        <is>
+          <t>get_restaurant_details + slot deals[] — Dineout competitor deal intelligence</t>
+        </is>
+      </c>
+      <c r="E55" s="102" t="inlineStr">
+        <is>
+          <t>After search_restaurants_dineout, call get_restaurant_details(restaurantId, lat, lng) for top 3. Returns deals[], amenities. Parse discountPercentage, isFree, title. Also parse deals[] from already-fetched get_available_slots — zero extra calls. Inject competitor_dineout_deals into reservation node prompt. "Fatty Bao has 25% off pre-booking tonight" changes walk-in estimate.</t>
+        </is>
+      </c>
+      <c r="F55" s="102" t="inlineStr">
+        <is>
+          <t>feat: get_restaurant_details + slot deals[] — Dineout competitor deal intelligence</t>
+        </is>
+      </c>
+      <c r="G55" s="102" t="inlineStr">
+        <is>
+          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md, docs/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="H55" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I55" s="101" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J55" s="101" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K55" s="101" t="inlineStr"/>
+      <c r="L55" s="101" t="inlineStr"/>
+      <c r="M55" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="102" t="inlineStr">
+        <is>
+          <t>P6-MI06</t>
+        </is>
+      </c>
+      <c r="O55" s="102" t="inlineStr">
+        <is>
+          <t>competitor_dineout_deals in result; slot_deals_found parsed; max 3 detail calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="52" customHeight="1" s="72">
+      <c r="A56" s="105" t="inlineStr">
+        <is>
+          <t>P6-MI08</t>
+        </is>
+      </c>
+      <c r="B56" s="106" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-extended</t>
+        </is>
+      </c>
+      <c r="C56" s="106" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D56" s="106" t="inlineStr">
+        <is>
+          <t>Assumption Diff 7 — competitor deals vs occupancy signal</t>
+        </is>
+      </c>
+      <c r="E56" s="106" t="inlineStr">
+        <is>
+          <t>Add Diff 7 to EvaluationSanityChecker: if tonight_busy=HIGH AND 2+ competitors running Dineout deals, stale assumption fires. Walk-in surge predicted but competitor promotions absorb demand. Critic told to revise walk-in down 15-20%. Total active diffs: 7.</t>
+        </is>
+      </c>
+      <c r="F56" s="106" t="inlineStr">
+        <is>
+          <t>feat: assumption Diff 7 — competitor deals absorbing predicted walk-in demand</t>
+        </is>
+      </c>
+      <c r="G56" s="106" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md, docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H56" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I56" s="105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J56" s="105" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K56" s="105" t="inlineStr"/>
+      <c r="L56" s="105" t="inlineStr"/>
+      <c r="M56" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="106" t="inlineStr">
+        <is>
+          <t>P6-MI07</t>
+        </is>
+      </c>
+      <c r="O56" s="106" t="inlineStr">
+        <is>
+          <t>Diff 7 fires when tonight_busy + 2+ deals; existing 6 diffs unaffected</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="52" customHeight="1" s="72">
+      <c r="A57" s="101" t="inlineStr">
+        <is>
+          <t>P6-MI09</t>
+        </is>
+      </c>
+      <c r="B57" s="102" t="inlineStr">
+        <is>
+          <t>feature/pricing-impact-model</t>
+        </is>
+      </c>
+      <c r="C57" s="102" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D57" s="102" t="inlineStr">
+        <is>
+          <t>Pricing impact model — quantify revenue effect of pricing alerts</t>
+        </is>
+      </c>
+      <c r="E57" s="102" t="inlineStr">
+        <is>
+          <t>When price gap flagged, compute revenue impact. Elasticity model: gap_pct * -0.8 = volume_change_pct. Weekly impact = avg_order_value * weekly_orders * volume_change. Output: [{item, our_price, area_avg, gap_pct, weekly_revenue_impact_inr}] top 5 by impact. "Matching area avg could increase weekly revenue by Rs.3,800." No new Swiggy calls.</t>
+        </is>
+      </c>
+      <c r="F57" s="102" t="inlineStr">
+        <is>
+          <t>feat: pricing impact model — quantify revenue effect of competitor price gaps</t>
+        </is>
+      </c>
+      <c r="G57" s="102" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="H57" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I57" s="101" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J57" s="101" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K57" s="101" t="inlineStr"/>
+      <c r="L57" s="101" t="inlineStr"/>
+      <c r="M57" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="102" t="inlineStr">
+        <is>
+          <t>P6-MI08</t>
+        </is>
+      </c>
+      <c r="O57" s="102" t="inlineStr">
+        <is>
+          <t>pricing_impact in result; top 5 by impact; weekly_revenue_impact_inr correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="52" customHeight="1" s="72">
+      <c r="A58" s="105" t="inlineStr">
+        <is>
+          <t>P6-MI10</t>
+        </is>
+      </c>
+      <c r="B58" s="106" t="inlineStr">
+        <is>
+          <t>feature/scenario-recommendation</t>
+        </is>
+      </c>
+      <c r="C58" s="106" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D58" s="106" t="inlineStr">
+        <is>
+          <t>Proactive scenario recommendation engine</t>
+        </is>
+      </c>
+      <c r="E58" s="106" t="inlineStr">
+        <is>
+          <t>Before owner picks scenario, system suggests which to run. Factors: date (weekend/Indian holiday check), market_intel occupancy signal, recent run scores, shortage count. One LLM call. Returns recommended_scenario + reason + confidence. New endpoint: GET /planning/recommend?target_date=YYYY-MM-DD. Dashboard: "We suggest Holiday Spike — tomorrow is Diwali + HIGH occupancy."</t>
+        </is>
+      </c>
+      <c r="F58" s="106" t="inlineStr">
+        <is>
+          <t>feat: proactive scenario recommendation — market + history aware</t>
+        </is>
+      </c>
+      <c r="G58" s="106" t="inlineStr">
+        <is>
+          <t>docs/APIS.md, CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H58" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I58" s="105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J58" s="105" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K58" s="105" t="inlineStr"/>
+      <c r="L58" s="105" t="inlineStr"/>
+      <c r="M58" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="106" t="inlineStr">
+        <is>
+          <t>P6-MI09</t>
+        </is>
+      </c>
+      <c r="O58" s="106" t="inlineStr">
+        <is>
+          <t>recommendation endpoint returns correctly; 20 major Indian holidays in constants</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="52" customHeight="1" s="72">
+      <c r="A59" s="101" t="inlineStr">
+        <is>
+          <t>P6-MI11</t>
+        </is>
+      </c>
+      <c r="B59" s="102" t="inlineStr">
+        <is>
+          <t>feature/trend-analytics</t>
+        </is>
+      </c>
+      <c r="C59" s="102" t="inlineStr">
+        <is>
+          <t>Backend + Frontend</t>
+        </is>
+      </c>
+      <c r="D59" s="102" t="inlineStr">
+        <is>
+          <t>Competitor price trend view on /market page</t>
+        </is>
+      </c>
+      <c r="E59" s="102" t="inlineStr">
+        <is>
+          <t>Read market_intel_output from past N planning runs (market_snapshots table). New endpoint: GET /market/trends?days=7. Returns area_avg per dish + occupancy signal trend. Frontend: recharts line chart on /market — price trend per dish (dropdown selectable). "Butter chicken area avg up Rs.20 over last 7 days." No new Swiggy calls — uses stored data.</t>
+        </is>
+      </c>
+      <c r="F59" s="102" t="inlineStr">
+        <is>
+          <t>feat: competitor price trend chart on /market — 7-day history</t>
+        </is>
+      </c>
+      <c r="G59" s="102" t="inlineStr">
+        <is>
+          <t>docs/APIS.md</t>
+        </is>
+      </c>
+      <c r="H59" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I59" s="101" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J59" s="101" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K59" s="101" t="inlineStr"/>
+      <c r="L59" s="101" t="inlineStr"/>
+      <c r="M59" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="102" t="inlineStr">
+        <is>
+          <t>P6-MI10</t>
+        </is>
+      </c>
+      <c r="O59" s="102" t="inlineStr">
+        <is>
+          <t>GET /market/trends returns data; chart renders; empty state when &lt;3 data points</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="8" customHeight="1" s="72"/>
+    <row r="61" ht="18" customHeight="1" s="72">
+      <c r="A61" s="108" t="inlineStr">
+        <is>
+          <t>PRIORITY 2 — Action Queue (approve/reject in plan — no staging needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="52" customHeight="1" s="72">
+      <c r="A62" s="109" t="inlineStr">
         <is>
           <t>P6-S32</t>
         </is>
       </c>
-      <c r="B58" s="69" t="inlineStr">
+      <c r="B62" s="110" t="inlineStr">
         <is>
           <t>feature/action-queue</t>
         </is>
       </c>
-      <c r="C58" s="55" t="inlineStr">
+      <c r="C62" s="110" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D58" s="56" t="inlineStr">
+      <c r="D62" s="110" t="inlineStr">
         <is>
           <t>ActionQueueService + action_queue table</t>
         </is>
       </c>
-      <c r="E58" s="56" t="inlineStr">
+      <c r="E62" s="110" t="inlineStr">
         <is>
           <t>New table: id, org_id, action_type (AUTO/APPROVE_REQUIRED/RECOMMENDATION), payload jsonb, status (PENDING/APPROVED/EXECUTED/REJECTED/EXPIRED), approved_by, executed_at, error. ActionQueueService CRUD. Plan output includes action_queue section in API response.</t>
         </is>
       </c>
-      <c r="F58" s="56" t="inlineStr">
+      <c r="F62" s="110" t="inlineStr">
         <is>
           <t>feat: ActionQueueService + action_queue table — 3-tier action model with approval lifecycle</t>
         </is>
       </c>
-      <c r="G58" s="56" t="inlineStr">
+      <c r="G62" s="110" t="inlineStr">
         <is>
           <t>docs/ACTION_QUEUE.md (new), docs/APIS.md (action queue endpoints), docs/DECISIONS.md (D-021)</t>
         </is>
       </c>
-      <c r="H58" s="63" t="inlineStr">
+      <c r="H62" s="103" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I58" s="49" t="inlineStr">
+      <c r="I62" s="109" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J58" s="55" t="inlineStr">
+      <c r="J62" s="109" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K58" s="55" t="n"/>
-      <c r="L58" s="59" t="inlineStr">
+      <c r="K62" s="109" t="n"/>
+      <c r="L62" s="109" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="M58" s="58" t="n">
+      <c r="M62" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="N58" s="55" t="inlineStr">
+      <c r="N62" s="110" t="inlineStr">
         <is>
           <t>P6-S15</t>
         </is>
       </c>
-      <c r="O58" s="56" t="inlineStr">
+      <c r="O62" s="110" t="inlineStr">
         <is>
           <t>No staging creds needed — action queue is pure backend, no Swiggy write calls yet.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="7.95" customHeight="1" s="72">
-      <c r="A59" s="52" t="n"/>
-      <c r="B59" s="52" t="n"/>
-      <c r="C59" s="52" t="n"/>
-      <c r="D59" s="52" t="n"/>
-      <c r="E59" s="52" t="n"/>
-      <c r="F59" s="52" t="n"/>
-      <c r="G59" s="52" t="n"/>
-      <c r="H59" s="52" t="n"/>
-      <c r="I59" s="52" t="n"/>
-      <c r="J59" s="52" t="n"/>
-      <c r="K59" s="52" t="n"/>
-      <c r="L59" s="52" t="n"/>
-      <c r="M59" s="52" t="n"/>
-      <c r="N59" s="52" t="n"/>
-      <c r="O59" s="52" t="n"/>
-    </row>
-    <row r="60" ht="73.05" customHeight="1" s="72">
-      <c r="A60" s="62" t="inlineStr">
+    <row r="63" ht="52" customHeight="1" s="72">
+      <c r="A63" s="105" t="inlineStr">
+        <is>
+          <t>P6-F06</t>
+        </is>
+      </c>
+      <c r="B63" s="106" t="inlineStr">
+        <is>
+          <t>feature/action-queue-ui</t>
+        </is>
+      </c>
+      <c r="C63" s="106" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D63" s="106" t="inlineStr">
+        <is>
+          <t>Action queue UI + procurement tracker</t>
+        </is>
+      </c>
+      <c r="E63" s="106" t="inlineStr">
+        <is>
+          <t>New section below plan output. Lists pending actions with type badge. Approve/Reject buttons for APPROVE_REQUIRED. Instamart cart preview modal (items, total, ETA) before approving checkout. Procurement tracker in inventory panel: placed orders, status, ETA.</t>
+        </is>
+      </c>
+      <c r="F63" s="106" t="inlineStr">
+        <is>
+          <t>feat: action queue UI — approve/reject with cart preview, procurement tracker</t>
+        </is>
+      </c>
+      <c r="G63" s="106" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="H63" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I63" s="105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J63" s="105" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K63" s="105" t="n"/>
+      <c r="L63" s="105" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="M63" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="106" t="inlineStr">
+        <is>
+          <t>P6-S18, P6-F11</t>
+        </is>
+      </c>
+      <c r="O63" s="106" t="inlineStr">
+        <is>
+          <t>Depends on P6-S32 (action_queue in plan API response)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="8" customHeight="1" s="72"/>
+    <row r="65" ht="18" customHeight="1" s="72">
+      <c r="A65" s="112" t="inlineStr">
+        <is>
+          <t>PRIORITY 3 — Pipeline Improvements (cost + quality)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="52" customHeight="1" s="72">
+      <c r="A66" s="113" t="inlineStr">
         <is>
           <t>P6-S33</t>
         </is>
       </c>
-      <c r="B60" s="69" t="n"/>
-      <c r="C60" s="55" t="inlineStr">
+      <c r="B66" s="114" t="n"/>
+      <c r="C66" s="114" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D60" s="56" t="inlineStr">
+      <c r="D66" s="114" t="inlineStr">
         <is>
           <t>Structured outputs — tool_choice=required, zero JSON hallucination</t>
         </is>
       </c>
-      <c r="E60" s="56" t="inlineStr">
+      <c r="E66" s="114" t="inlineStr">
         <is>
           <t>Upgrade chatbot Groq calls to tool_choice=required + strict JSON schema. Apply to all 3 Swiggy chatbot tools (search_menu, get_food_orders, search_products). Chatbot function calls never hallucinate JSON. Zero model coupling — works on any provider.</t>
         </is>
       </c>
-      <c r="F60" s="56" t="inlineStr">
+      <c r="F66" s="114" t="inlineStr">
         <is>
           <t>feat: structured outputs — tool_choice=required across all chatbot tools</t>
         </is>
       </c>
-      <c r="G60" s="56" t="inlineStr">
+      <c r="G66" s="114" t="inlineStr">
         <is>
           <t>docs/AGENTS.md</t>
         </is>
       </c>
-      <c r="H60" s="63" t="inlineStr">
+      <c r="H66" s="103" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I60" s="49" t="inlineStr">
+      <c r="I66" s="113" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J60" s="55" t="inlineStr">
+      <c r="J66" s="113" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K60" s="55" t="n"/>
-      <c r="L60" s="59" t="inlineStr">
+      <c r="K66" s="113" t="n"/>
+      <c r="L66" s="113" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="M60" s="58" t="n">
+      <c r="M66" s="115" t="n">
         <v>0</v>
       </c>
-      <c r="N60" s="55" t="inlineStr">
+      <c r="N66" s="114" t="inlineStr">
         <is>
           <t>P6-F05</t>
         </is>
       </c>
-      <c r="O60" s="56" t="inlineStr">
+      <c r="O66" s="114" t="inlineStr">
         <is>
           <t>Schema validation test; chatbot returns valid JSON on 10 consecutive calls</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="7.95" customHeight="1" s="72">
-      <c r="A61" s="52" t="n"/>
-      <c r="B61" s="52" t="n"/>
-      <c r="C61" s="52" t="n"/>
-      <c r="D61" s="52" t="n"/>
-      <c r="E61" s="52" t="n"/>
-      <c r="F61" s="52" t="n"/>
-      <c r="G61" s="52" t="n"/>
-      <c r="H61" s="52" t="n"/>
-      <c r="I61" s="52" t="n"/>
-      <c r="J61" s="52" t="n"/>
-      <c r="K61" s="52" t="n"/>
-      <c r="L61" s="52" t="n"/>
-      <c r="M61" s="52" t="n"/>
-      <c r="N61" s="52" t="n"/>
-      <c r="O61" s="52" t="n"/>
-    </row>
-    <row r="62" ht="73.05" customHeight="1" s="72">
-      <c r="A62" s="62" t="inlineStr">
+    <row r="67" ht="52" customHeight="1" s="72">
+      <c r="A67" s="105" t="inlineStr">
         <is>
           <t>P6-S34</t>
         </is>
       </c>
-      <c r="B62" s="69" t="n"/>
-      <c r="C62" s="55" t="inlineStr">
+      <c r="B67" s="106" t="n"/>
+      <c r="C67" s="106" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D62" s="56" t="inlineStr">
+      <c r="D67" s="106" t="inlineStr">
         <is>
           <t>Prompt caching — 60-90% cost reduction on critic + aggregator</t>
         </is>
       </c>
-      <c r="E62" s="56" t="inlineStr">
+      <c r="E67" s="106" t="inlineStr">
         <is>
           <t>Add Anthropic prompt caching headers to critic and aggregator LLM calls. Both have long system prompts repeated every run. Expected saving: 60-90% of prompt token cost per planning run. Graceful fallback on cache miss. Compatible with Google Gemini too.</t>
         </is>
       </c>
-      <c r="F62" s="56" t="inlineStr">
+      <c r="F67" s="106" t="inlineStr">
         <is>
           <t>feat: prompt caching — cut LLM costs 80% on critic and aggregator nodes</t>
         </is>
       </c>
-      <c r="G62" s="56" t="inlineStr">
+      <c r="G67" s="106" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md</t>
         </is>
       </c>
-      <c r="H62" s="63" t="inlineStr">
+      <c r="H67" s="103" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I62" s="49" t="inlineStr">
+      <c r="I67" s="105" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J62" s="55" t="inlineStr">
+      <c r="J67" s="105" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K62" s="55" t="n"/>
-      <c r="L62" s="59" t="inlineStr">
+      <c r="K67" s="105" t="n"/>
+      <c r="L67" s="105" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="M62" s="58" t="n">
+      <c r="M67" s="107" t="n">
         <v>0</v>
       </c>
-      <c r="N62" s="55" t="inlineStr">
+      <c r="N67" s="106" t="inlineStr">
         <is>
           <t>P6-S33</t>
         </is>
       </c>
-      <c r="O62" s="56" t="inlineStr">
+      <c r="O67" s="106" t="inlineStr">
         <is>
           <t>Cost log shows cache_hit=true on second run of same scenario</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="7.95" customHeight="1" s="72">
-      <c r="A63" s="52" t="n"/>
-      <c r="B63" s="52" t="n"/>
-      <c r="C63" s="52" t="n"/>
-      <c r="D63" s="52" t="n"/>
-      <c r="E63" s="52" t="n"/>
-      <c r="F63" s="52" t="n"/>
-      <c r="G63" s="52" t="n"/>
-      <c r="H63" s="52" t="n"/>
-      <c r="I63" s="52" t="n"/>
-      <c r="J63" s="52" t="n"/>
-      <c r="K63" s="52" t="n"/>
-      <c r="L63" s="52" t="n"/>
-      <c r="M63" s="52" t="n"/>
-      <c r="N63" s="52" t="n"/>
-      <c r="O63" s="52" t="n"/>
-    </row>
-    <row r="64" ht="85.95" customHeight="1" s="72">
-      <c r="A64" s="62" t="inlineStr">
+    <row r="68" ht="52" customHeight="1" s="72">
+      <c r="A68" s="113" t="inlineStr">
+        <is>
+          <t>P6-S38</t>
+        </is>
+      </c>
+      <c r="B68" s="114" t="inlineStr">
+        <is>
+          <t>feature/debate-critic</t>
+        </is>
+      </c>
+      <c r="C68" s="114" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D68" s="114" t="inlineStr">
+        <is>
+          <t>Multi-agent debate critic — two critic instances, consensus scoring</t>
+        </is>
+      </c>
+      <c r="E68" s="114" t="inlineStr">
+        <is>
+          <t>Run two LLM critic instances with opposing system prompts (optimistic vs conservative). Structured debate: each scores the plan, flags disagreements, moderator LLM resolves. Final verdict is consensus or flagged-disagreement. Provably better plan quality than single critic. Zero model coupling.</t>
+        </is>
+      </c>
+      <c r="F68" s="114" t="inlineStr">
+        <is>
+          <t>feat: multi-agent debate critic — consensus scoring, catches more edge cases</t>
+        </is>
+      </c>
+      <c r="G68" s="114" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="H68" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I68" s="113" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J68" s="113" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K68" s="113" t="n"/>
+      <c r="L68" s="113" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="M68" s="115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="114" t="inlineStr">
         <is>
           <t>P6-S35</t>
         </is>
       </c>
-      <c r="B64" s="69" t="inlineStr">
+      <c r="O68" s="114" t="inlineStr">
+        <is>
+          <t>Debate resolves on 5 test plans; disagreement cases escalate correctly</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="52" customHeight="1" s="72">
+      <c r="A69" s="105" t="inlineStr">
+        <is>
+          <t>P6-S35</t>
+        </is>
+      </c>
+      <c r="B69" s="106" t="inlineStr">
         <is>
           <t>feature/workflow-system</t>
         </is>
       </c>
-      <c r="C64" s="55" t="inlineStr">
+      <c r="C69" s="106" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D64" s="56" t="inlineStr">
+      <c r="D69" s="106" t="inlineStr">
         <is>
           <t>Restaurant workflow system — owner-defined trigger-condition-action automations</t>
         </is>
       </c>
-      <c r="E64" s="56" t="inlineStr">
+      <c r="E69" s="106" t="inlineStr">
         <is>
           <t>New table: workflows (org_id, trigger, condition_json, action_type, action_payload, active). Triggers: AFTER_PLANNING_RUN, DAILY_BRIEF, ON_THRESHOLD. Actions: SEND_WHATSAPP, QUEUE_ACTION, CALL_WEBHOOK. WorkflowEngine evaluates conditions post-run and fires actions. /workflows UI page. Turns CortexKitchen from a tool into an OS.</t>
         </is>
       </c>
-      <c r="F64" s="56" t="inlineStr">
+      <c r="F69" s="106" t="inlineStr">
         <is>
           <t>feat: workflow system — restaurant owners define custom automations</t>
         </is>
       </c>
-      <c r="G64" s="56" t="inlineStr">
+      <c r="G69" s="106" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md, docs/APIS.md</t>
         </is>
       </c>
-      <c r="H64" s="63" t="inlineStr">
+      <c r="H69" s="103" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I64" s="49" t="inlineStr">
+      <c r="I69" s="105" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J64" s="55" t="inlineStr">
+      <c r="J69" s="105" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K64" s="55" t="n"/>
-      <c r="L64" s="59" t="inlineStr">
+      <c r="K69" s="105" t="n"/>
+      <c r="L69" s="105" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="M64" s="58" t="n">
+      <c r="M69" s="107" t="n">
         <v>0</v>
       </c>
-      <c r="N64" s="55" t="inlineStr">
+      <c r="N69" s="106" t="inlineStr">
         <is>
           <t>P6-S20-UNRESOLVED</t>
         </is>
       </c>
-      <c r="O64" s="56" t="inlineStr">
+      <c r="O69" s="106" t="inlineStr">
         <is>
           <t>End-to-end: planning run fires whatsapp trigger; webhook called on threshold breach</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="7.95" customHeight="1" s="72">
-      <c r="A65" s="52" t="n"/>
-      <c r="B65" s="52" t="n"/>
-      <c r="C65" s="52" t="n"/>
-      <c r="D65" s="52" t="n"/>
-      <c r="E65" s="52" t="n"/>
-      <c r="F65" s="52" t="n"/>
-      <c r="G65" s="52" t="n"/>
-      <c r="H65" s="52" t="n"/>
-      <c r="I65" s="52" t="n"/>
-      <c r="J65" s="52" t="n"/>
-      <c r="K65" s="52" t="n"/>
-      <c r="L65" s="52" t="n"/>
-      <c r="M65" s="52" t="n"/>
-      <c r="N65" s="52" t="n"/>
-      <c r="O65" s="52" t="n"/>
-    </row>
-    <row r="66" ht="99" customHeight="1" s="72">
-      <c r="A66" s="62" t="inlineStr">
+    <row r="70" ht="8" customHeight="1" s="72"/>
+    <row r="71" ht="18" customHeight="1" s="72">
+      <c r="A71" s="116" t="inlineStr">
+        <is>
+          <t>PRIORITY 4 — Product Modes (brief mode + live monitor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="52" customHeight="1" s="72">
+      <c r="A72" s="117" t="inlineStr">
         <is>
           <t>P6-S36</t>
         </is>
       </c>
-      <c r="B66" s="69" t="n"/>
-      <c r="C66" s="55" t="inlineStr">
+      <c r="B72" s="118" t="n"/>
+      <c r="C72" s="118" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D66" s="56" t="inlineStr">
+      <c r="D72" s="118" t="inlineStr">
         <is>
           <t>LiveMonitorService — SSE feed during service hours</t>
         </is>
       </c>
-      <c r="E66" s="56" t="inlineStr">
+      <c r="E72" s="118" t="inlineStr">
         <is>
           <t>APScheduler-managed SSE stream active 12:00-14:00 and 19:00-22:00 IST. Polls every 30s: get_food_orders (activeOnly=true) for active delivery orders, track_food_order for in-flight ETAs, track_order for Instamart procurement status. Pushes events to /live page frontend. Alerts on: delivery &gt; SLA threshold, order spike, ingredient delivery confirmed.</t>
         </is>
       </c>
-      <c r="F66" s="56" t="inlineStr">
+      <c r="F72" s="118" t="inlineStr">
         <is>
           <t>feat: LiveMonitorService — real-time Swiggy SSE during service hours (orders + procurement)</t>
         </is>
       </c>
-      <c r="G66" s="56" t="inlineStr">
+      <c r="G72" s="118" t="inlineStr">
         <is>
           <t>docs/PRODUCT_MODES.md (live monitor section)</t>
         </is>
       </c>
-      <c r="H66" s="63" t="inlineStr">
+      <c r="H72" s="103" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I66" s="61" t="inlineStr">
+      <c r="I72" s="117" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J66" s="55" t="inlineStr">
+      <c r="J72" s="117" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K66" s="55" t="n"/>
-      <c r="L66" s="59" t="inlineStr">
+      <c r="K72" s="117" t="n"/>
+      <c r="L72" s="117" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="M66" s="58" t="n">
+      <c r="M72" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="N66" s="55" t="inlineStr">
+      <c r="N72" s="118" t="inlineStr">
         <is>
           <t>P6-S22-UNRESOLVED, P6-S43</t>
         </is>
       </c>
-      <c r="O66" s="56" t="inlineStr">
+      <c r="O72" s="118" t="inlineStr">
         <is>
           <t>SSE stream active only during service hours IST; events emitted on each 30s poll; delivery threshold alert fires; stream stops outside service window.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="7.95" customHeight="1" s="72">
-      <c r="A67" s="52" t="n"/>
-      <c r="B67" s="52" t="n"/>
-      <c r="C67" s="52" t="n"/>
-      <c r="D67" s="52" t="n"/>
-      <c r="E67" s="52" t="n"/>
-      <c r="F67" s="52" t="n"/>
-      <c r="G67" s="52" t="n"/>
-      <c r="H67" s="52" t="n"/>
-      <c r="I67" s="52" t="n"/>
-      <c r="J67" s="52" t="n"/>
-      <c r="K67" s="52" t="n"/>
-      <c r="L67" s="52" t="n"/>
-      <c r="M67" s="52" t="n"/>
-      <c r="N67" s="52" t="n"/>
-      <c r="O67" s="52" t="n"/>
-    </row>
-    <row r="68" ht="73.05" customHeight="1" s="72">
-      <c r="A68" s="62" t="inlineStr">
+    <row r="73" ht="52" customHeight="1" s="72">
+      <c r="A73" s="105" t="inlineStr">
+        <is>
+          <t>P6-F07</t>
+        </is>
+      </c>
+      <c r="B73" s="106" t="n"/>
+      <c r="C73" s="106" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D73" s="106" t="inlineStr">
+        <is>
+          <t>/brief page — daily morning briefing</t>
+        </is>
+      </c>
+      <c r="E73" s="106" t="inlineStr">
+        <is>
+          <t>New route /brief. Overnight Swiggy performance (orders, avg delivery time, late %), today's demand forecast vs yesterday, top 3 action priorities, market snapshot. Auto-refreshes if brief is stale. Empty state when no brief yet.</t>
+        </is>
+      </c>
+      <c r="F73" s="106" t="inlineStr">
+        <is>
+          <t>feat: /brief page — daily morning operational briefing</t>
+        </is>
+      </c>
+      <c r="G73" s="106" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="H73" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I73" s="105" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J73" s="105" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K73" s="105" t="n"/>
+      <c r="L73" s="105" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="M73" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="106" t="inlineStr">
+        <is>
+          <t>P6-S44, P6-F11</t>
+        </is>
+      </c>
+      <c r="O73" s="106" t="inlineStr">
+        <is>
+          <t>Depends on P6-S22-UNRESOLVED (BriefingService)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="52" customHeight="1" s="72">
+      <c r="A74" s="117" t="inlineStr">
+        <is>
+          <t>P6-F08</t>
+        </is>
+      </c>
+      <c r="B74" s="118" t="n"/>
+      <c r="C74" s="118" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D74" s="118" t="inlineStr">
+        <is>
+          <t>/live page — real-time service monitor</t>
+        </is>
+      </c>
+      <c r="E74" s="118" t="inlineStr">
+        <is>
+          <t>New route /live. Kitchen display-grade SSE feed from LiveMonitorService (P6-S36). Shows active Swiggy delivery orders with ETA countdown, Instamart procurement status with delivery ETA, alert banner on delivery spike or ingredient arrival. Swiggy logo + 'Live via Swiggy MCP' badge. Page shows inactive state outside service hours (12-14h, 19-22h IST).</t>
+        </is>
+      </c>
+      <c r="F74" s="118" t="inlineStr">
+        <is>
+          <t>feat: /live page — SSE kitchen display for active orders and procurement tracking</t>
+        </is>
+      </c>
+      <c r="G74" s="118" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="H74" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I74" s="117" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J74" s="117" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K74" s="117" t="n"/>
+      <c r="L74" s="117" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="M74" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="118" t="inlineStr">
+        <is>
+          <t>P6-S36, P6-F11</t>
+        </is>
+      </c>
+      <c r="O74" s="118" t="inlineStr">
+        <is>
+          <t>SSE events render in real time; ETA countdown ticks; alert banner fires on delivery spike; Swiggy branding visible; inactive state shown outside service hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="8" customHeight="1" s="72"/>
+    <row r="76" ht="18" customHeight="1" s="72">
+      <c r="A76" s="112" t="inlineStr">
+        <is>
+          <t>PRIORITY 5 — Voice Interface + MCP Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="52" customHeight="1" s="72">
+      <c r="A77" s="113" t="inlineStr">
+        <is>
+          <t>P6-R01</t>
+        </is>
+      </c>
+      <c r="B77" s="114" t="inlineStr">
+        <is>
+          <t>feature/voice-interface</t>
+        </is>
+      </c>
+      <c r="C77" s="114" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D77" s="114" t="inlineStr">
+        <is>
+          <t>Voice interface — Whisper + RAG chatbot</t>
+        </is>
+      </c>
+      <c r="E77" s="114" t="inlineStr">
+        <is>
+          <t>Whisper transcription on browser-recorded question (MediaRecorder API). RAG chatbot (P5-12) answers. TTS reads back. Manager asks questions while walking the floor. Works with both synthetic and real Swiggy data now in DB. Blocked on P5-12 (already done).</t>
+        </is>
+      </c>
+      <c r="F77" s="114" t="inlineStr">
+        <is>
+          <t>feat: voice interface — Whisper transcription + RAG answer + TTS readback</t>
+        </is>
+      </c>
+      <c r="G77" s="114" t="inlineStr">
+        <is>
+          <t>docs/PRODUCT_MODES.md (voice section)</t>
+        </is>
+      </c>
+      <c r="H77" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I77" s="113" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J77" s="113" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K77" s="113" t="n"/>
+      <c r="L77" s="113" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="M77" s="115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="114" t="inlineStr">
+        <is>
+          <t>P6-S44</t>
+        </is>
+      </c>
+      <c r="O77" s="114" t="inlineStr">
+        <is>
+          <t>Transcription accuracy smoke test; end-to-end voice → RAG answer → TTS; works with real Swiggy data in DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="52" customHeight="1" s="72">
+      <c r="A78" s="105" t="inlineStr">
         <is>
           <t>P6-S37</t>
         </is>
       </c>
-      <c r="B68" s="69" t="n"/>
-      <c r="C68" s="55" t="inlineStr">
+      <c r="B78" s="106" t="n"/>
+      <c r="C78" s="106" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D68" s="56" t="inlineStr">
+      <c r="D78" s="106" t="inlineStr">
         <is>
           <t>3 new CortexKitchen MCP server tools</t>
         </is>
       </c>
-      <c r="E68" s="56" t="inlineStr">
+      <c r="E78" s="106" t="inlineStr">
         <is>
           <t>Add to mcp_server.py: get_market_brief (calls MarketIntelService live, returns competitor snapshot for Claude Desktop), get_action_queue (pending actions awaiting approval), approve_action (owner approves from Claude Desktop, triggers execution). JWT auth on all 3.</t>
         </is>
       </c>
-      <c r="F68" s="56" t="inlineStr">
+      <c r="F78" s="106" t="inlineStr">
         <is>
           <t>feat: 3 new MCP tools — get_market_brief, get_action_queue, approve_action</t>
         </is>
       </c>
-      <c r="G68" s="56" t="inlineStr">
+      <c r="G78" s="106" t="inlineStr">
         <is>
           <t>docs/APIS.md (MCP tools section), docs/ARCHITECTURE.md (MCP server updated)</t>
         </is>
       </c>
-      <c r="H68" s="63" t="inlineStr">
+      <c r="H78" s="103" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I68" s="61" t="inlineStr">
+      <c r="I78" s="105" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J68" s="55" t="inlineStr">
+      <c r="J78" s="105" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K68" s="55" t="n"/>
-      <c r="L68" s="59" t="inlineStr">
+      <c r="K78" s="105" t="n"/>
+      <c r="L78" s="105" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="M68" s="58" t="n">
+      <c r="M78" s="107" t="n">
         <v>0</v>
       </c>
-      <c r="N68" s="55" t="inlineStr">
+      <c r="N78" s="106" t="inlineStr">
         <is>
           <t>P6-S32</t>
         </is>
       </c>
-      <c r="O68" s="56" t="inlineStr">
+      <c r="O78" s="106" t="inlineStr">
         <is>
           <t>All 3 tools smoke-tested in Claude Desktop; approve_action triggers execution end-to-end; JWT enforced</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="7.95" customHeight="1" s="72">
-      <c r="A69" s="52" t="n"/>
-      <c r="B69" s="52" t="n"/>
-      <c r="C69" s="52" t="n"/>
-      <c r="D69" s="52" t="n"/>
-      <c r="E69" s="52" t="n"/>
-      <c r="F69" s="52" t="n"/>
-      <c r="G69" s="52" t="n"/>
-      <c r="H69" s="52" t="n"/>
-      <c r="I69" s="52" t="n"/>
-      <c r="J69" s="52" t="n"/>
-      <c r="K69" s="52" t="n"/>
-      <c r="L69" s="52" t="n"/>
-      <c r="M69" s="52" t="n"/>
-      <c r="N69" s="52" t="n"/>
-      <c r="O69" s="52" t="n"/>
-    </row>
-    <row r="70" ht="85.95" customHeight="1" s="72">
-      <c r="A70" s="62" t="inlineStr">
-        <is>
-          <t>P6-S38</t>
-        </is>
-      </c>
-      <c r="B70" s="69" t="inlineStr">
-        <is>
-          <t>feature/debate-critic</t>
-        </is>
-      </c>
-      <c r="C70" s="55" t="inlineStr">
+    <row r="79" ht="8" customHeight="1" s="72"/>
+    <row r="80" ht="18" customHeight="1" s="72">
+      <c r="A80" s="112" t="inlineStr">
+        <is>
+          <t>PRIORITY 6 — Infra + Eval (CI fixes, RAGAS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="52" customHeight="1" s="72">
+      <c r="A81" s="113" t="inlineStr">
+        <is>
+          <t>P6-S39</t>
+        </is>
+      </c>
+      <c r="B81" s="114" t="n"/>
+      <c r="C81" s="114" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D81" s="114" t="inlineStr">
+        <is>
+          <t>Fix SQLite/JSONB test-infra gap blocking full CI coverage</t>
+        </is>
+      </c>
+      <c r="E81" s="114" t="inlineStr">
+        <is>
+          <t>test_swiggy_reservation_sync.py and test_connector_repository.py are excluded from the CI unit-tests job (P6-Q03) because they spin up a real SQLite engine and connectors.connector_metadata uses Postgres' JSONB column type, which SQLite's compiler can't render. Either give the column a SQLite-compatible fallback type for tests, or run these two files against a real Postgres service container in CI (docker-compose.yml already defines postgres:16 for local dev -- same image could back a CI service).</t>
+        </is>
+      </c>
+      <c r="F81" s="114" t="inlineStr">
+        <is>
+          <t>fix: SQLite-compatible JSONB handling (or Postgres CI service) for excluded test files</t>
+        </is>
+      </c>
+      <c r="G81" s="114" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H81" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I81" s="113" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J81" s="113" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K81" s="113" t="n"/>
+      <c r="L81" s="113" t="n"/>
+      <c r="M81" s="115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="114" t="inlineStr">
+        <is>
+          <t>P6-S23</t>
+        </is>
+      </c>
+      <c r="O81" s="114" t="n"/>
+    </row>
+    <row r="82" ht="52" customHeight="1" s="72">
+      <c r="A82" s="105" t="inlineStr">
+        <is>
+          <t>P6-S40</t>
+        </is>
+      </c>
+      <c r="B82" s="106" t="n"/>
+      <c r="C82" s="106" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D82" s="106" t="inlineStr">
+        <is>
+          <t>Promote reviewed RAGAS/DeepEval candidates into curated eval files</t>
+        </is>
+      </c>
+      <c r="E82" s="106" t="inlineStr">
+        <is>
+          <t>build_ragas_dataset.py / build_deepeval_dataset.py (P6-Q03) produce .candidates.json files from live approved runs but never auto-merge them -- ground_truth needs human verification by design. Needs a recurring habit of actually running these periodically and hand-promoting reviewed candidates into complaint_rag_samples.json / test_deepeval_quality.py, or the static datasets stay frozen at today's size forever.</t>
+        </is>
+      </c>
+      <c r="F82" s="106" t="inlineStr">
+        <is>
+          <t>chore: promote reviewed eval candidates into curated datasets</t>
+        </is>
+      </c>
+      <c r="G82" s="106" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H82" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I82" s="105" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J82" s="105" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K82" s="105" t="n"/>
+      <c r="L82" s="105" t="n"/>
+      <c r="M82" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="106" t="inlineStr">
+        <is>
+          <t>P6-S23</t>
+        </is>
+      </c>
+      <c r="O82" s="106" t="n"/>
+    </row>
+    <row r="83" ht="52" customHeight="1" s="72">
+      <c r="A83" s="113" t="inlineStr">
+        <is>
+          <t>P6-S41</t>
+        </is>
+      </c>
+      <c r="B83" s="114" t="n"/>
+      <c r="C83" s="114" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D83" s="114" t="inlineStr">
+        <is>
+          <t>Regenerate golden_runs.json against real production data</t>
+        </is>
+      </c>
+      <c r="E83" s="114" t="inlineStr">
+        <is>
+          <t>build_golden_dataset.py's key-path bug is fixed (P6-Q03) but the checked-in fixture still reflects the old, always-empty extraction, since regenerating it requires a live Postgres populated with real run history, which wasn't available during the fix. Run scripts/build_golden_dataset.py locally once docker-compose services are up to refresh it with corrected shortage/restock data.</t>
+        </is>
+      </c>
+      <c r="F83" s="114" t="inlineStr">
+        <is>
+          <t>chore: regenerate golden_runs.json with corrected extraction logic</t>
+        </is>
+      </c>
+      <c r="G83" s="114" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H83" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I83" s="113" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J83" s="113" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K83" s="113" t="n"/>
+      <c r="L83" s="113" t="n"/>
+      <c r="M83" s="115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="114" t="inlineStr">
+        <is>
+          <t>P6-S23</t>
+        </is>
+      </c>
+      <c r="O83" s="114" t="n"/>
+    </row>
+    <row r="84" ht="8" customHeight="1" s="72"/>
+    <row r="85" ht="18" customHeight="1" s="72">
+      <c r="A85" s="112" t="inlineStr">
+        <is>
+          <t>PRIORITY 7 — UI/UX Redesign (use Claude Design for each page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="52" customHeight="1" s="72">
+      <c r="A86" s="113" t="inlineStr">
+        <is>
+          <t>P6-F12</t>
+        </is>
+      </c>
+      <c r="B86" s="114" t="n"/>
+      <c r="C86" s="114" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D86" s="114" t="inlineStr">
+        <is>
+          <t>/runs history page redesign</t>
+        </is>
+      </c>
+      <c r="E86" s="114" t="inlineStr">
+        <is>
+          <t>Apply the new design system to /runs. Restyle from a dense monospace debug trace (raw dimension-score grids, 10+ revision-reason text blocks) into something a manager can skim in under a minute. Fix the currently-unstyled raw Next.js 404 on /runs/{id} deep links -- give each run its own real page. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts.</t>
+        </is>
+      </c>
+      <c r="F86" s="114" t="inlineStr">
+        <is>
+          <t>feat: redesign /runs history page + fix /runs/{id} deep-link 404</t>
+        </is>
+      </c>
+      <c r="G86" s="114" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="H86" s="103" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I86" s="113" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J86" s="113" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K86" s="113" t="n"/>
+      <c r="L86" s="113" t="n"/>
+      <c r="M86" s="115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="114" t="inlineStr">
+        <is>
+          <t>P6-F11</t>
+        </is>
+      </c>
+      <c r="O86" s="114" t="inlineStr">
+        <is>
+          <t>Direct navigation to /runs/{id} renders the run, not a 404; skim-readability spot check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="8" customHeight="1" s="72"/>
+    <row r="88" ht="18" customHeight="1" s="72">
+      <c r="A88" s="120" t="inlineStr">
+        <is>
+          <t>BLOCKED — waiting for Swiggy staging creds (mcp-staging.swiggy.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="52" customHeight="1" s="72">
+      <c r="A89" s="121" t="inlineStr">
+        <is>
+          <t>P6-S43</t>
+        </is>
+      </c>
+      <c r="B89" s="122" t="inlineStr">
+        <is>
+          <t>feature/procurement-executor</t>
+        </is>
+      </c>
+      <c r="C89" s="122" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D70" s="56" t="inlineStr">
-        <is>
-          <t>Multi-agent debate critic — two critic instances, consensus scoring</t>
-        </is>
-      </c>
-      <c r="E70" s="56" t="inlineStr">
-        <is>
-          <t>Run two LLM critic instances with opposing system prompts (optimistic vs conservative). Structured debate: each scores the plan, flags disagreements, moderator LLM resolves. Final verdict is consensus or flagged-disagreement. Provably better plan quality than single critic. Zero model coupling.</t>
-        </is>
-      </c>
-      <c r="F70" s="56" t="inlineStr">
-        <is>
-          <t>feat: multi-agent debate critic — consensus scoring, catches more edge cases</t>
-        </is>
-      </c>
-      <c r="G70" s="56" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md</t>
-        </is>
-      </c>
-      <c r="H70" s="63" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I70" s="61" t="inlineStr">
+      <c r="D89" s="122" t="inlineStr">
+        <is>
+          <t>ProcurementExecutor — Instamart checkout with approval gate</t>
+        </is>
+      </c>
+      <c r="E89" s="122" t="inlineStr">
+        <is>
+          <t>update_cart → get_cart → LangGraph interrupt() → owner approval → checkout. check-then-retry on 5xx (call get_orders before retrying checkout — non-idempotent). Stores in procurement_orders table. COD only. BLOCKED: checkout places real Instamart orders.</t>
+        </is>
+      </c>
+      <c r="F89" s="122" t="inlineStr">
+        <is>
+          <t>feat: ProcurementExecutor — Instamart autonomous procurement with approval gate</t>
+        </is>
+      </c>
+      <c r="G89" s="122" t="inlineStr">
+        <is>
+          <t>docs/ACTION_QUEUE.md, CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H89" s="123" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="I89" s="121" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J89" s="121" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K89" s="121" t="inlineStr"/>
+      <c r="L89" s="121" t="inlineStr"/>
+      <c r="M89" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="122" t="inlineStr">
+        <is>
+          <t>P6-S32</t>
+        </is>
+      </c>
+      <c r="O89" s="122" t="inlineStr">
+        <is>
+          <t>check-then-retry on 5xx; interrupt() pauses graph; approval resumes checkout; procurement_orders row created</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="52" customHeight="1" s="72">
+      <c r="A90" s="105" t="inlineStr">
+        <is>
+          <t>P6-S44</t>
+        </is>
+      </c>
+      <c r="B90" s="106" t="inlineStr">
+        <is>
+          <t>feature/dineout-executor</t>
+        </is>
+      </c>
+      <c r="C90" s="106" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D90" s="106" t="inlineStr">
+        <is>
+          <t>Dineout table booking execution</t>
+        </is>
+      </c>
+      <c r="E90" s="106" t="inlineStr">
+        <is>
+          <t>create_cart → book_table(slotId, itemId, reservationTime, guestCount, lat, lng). check-then-retry on 5xx (get_booking_status before retrying). BLOCKED: book_table places real Dineout bookings. NOTE: Managing OWN restaurant Dineout slots requires Partner API not consumer MCP.</t>
+        </is>
+      </c>
+      <c r="F90" s="106" t="inlineStr">
+        <is>
+          <t>feat: Dineout booking execution with approval gate</t>
+        </is>
+      </c>
+      <c r="G90" s="106" t="inlineStr">
+        <is>
+          <t>docs/ACTION_QUEUE.md</t>
+        </is>
+      </c>
+      <c r="H90" s="123" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="I90" s="105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J90" s="105" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K90" s="105" t="inlineStr"/>
+      <c r="L90" s="105" t="inlineStr"/>
+      <c r="M90" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="106" t="inlineStr">
+        <is>
+          <t>P6-S43</t>
+        </is>
+      </c>
+      <c r="O90" s="106" t="inlineStr">
+        <is>
+          <t>non-idempotent retry test; confirmation in reservations table; free slots only (isFree=true)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="52" customHeight="1" s="72">
+      <c r="A91" s="121" t="inlineStr">
+        <is>
+          <t>P6-S45</t>
+        </is>
+      </c>
+      <c r="B91" s="122" t="inlineStr">
+        <is>
+          <t>feature/computer-use-partner</t>
+        </is>
+      </c>
+      <c r="C91" s="122" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D91" s="122" t="inlineStr">
+        <is>
+          <t>Computer use agent — Swiggy Partner Dashboard automation</t>
+        </is>
+      </c>
+      <c r="E91" s="122" t="inlineStr">
+        <is>
+          <t>Use Claude Computer Use to automate Swiggy Partner Dashboard actions not in MCP: menu price updates, slot management, promotional setup. Bypasses consumer MCP limitation for restaurant-side operations.</t>
+        </is>
+      </c>
+      <c r="F91" s="122" t="inlineStr">
+        <is>
+          <t>feat: computer use agent for Swiggy Partner Dashboard</t>
+        </is>
+      </c>
+      <c r="G91" s="122" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H91" s="123" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="I91" s="121" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J70" s="55" t="inlineStr">
+      <c r="J91" s="121" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K70" s="55" t="n"/>
-      <c r="L70" s="59" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="M70" s="58" t="n">
+      <c r="K91" s="121" t="inlineStr"/>
+      <c r="L91" s="121" t="inlineStr"/>
+      <c r="M91" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="N70" s="55" t="inlineStr">
-        <is>
-          <t>P6-S35</t>
-        </is>
-      </c>
-      <c r="O70" s="56" t="inlineStr">
-        <is>
-          <t>Debate resolves on 5 test plans; disagreement cases escalate correctly</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="7.95" customHeight="1" s="72">
-      <c r="A71" s="52" t="n"/>
-      <c r="B71" s="52" t="n"/>
-      <c r="C71" s="52" t="n"/>
-      <c r="D71" s="52" t="n"/>
-      <c r="E71" s="52" t="n"/>
-      <c r="F71" s="52" t="n"/>
-      <c r="G71" s="52" t="n"/>
-      <c r="H71" s="52" t="n"/>
-      <c r="I71" s="52" t="n"/>
-      <c r="J71" s="52" t="n"/>
-      <c r="K71" s="52" t="n"/>
-      <c r="L71" s="52" t="n"/>
-      <c r="M71" s="52" t="n"/>
-      <c r="N71" s="52" t="n"/>
-      <c r="O71" s="52" t="n"/>
-    </row>
-    <row r="72" ht="73.05" customHeight="1" s="72">
-      <c r="A72" s="62" t="inlineStr">
-        <is>
-          <t>P6-R01</t>
-        </is>
-      </c>
-      <c r="B72" s="69" t="inlineStr">
-        <is>
-          <t>feature/voice-interface</t>
-        </is>
-      </c>
-      <c r="C72" s="55" t="inlineStr">
+      <c r="N91" s="122" t="inlineStr">
+        <is>
+          <t>P6-S44</t>
+        </is>
+      </c>
+      <c r="O91" s="122" t="inlineStr">
+        <is>
+          <t>Computer use navigates Partner Dashboard; menu price update verified end-to-end</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1" s="72"/>
+    <row r="93" ht="18" customHeight="1" s="72">
+      <c r="A93" s="112" t="inlineStr">
+        <is>
+          <t>SUPERSEDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="52" customHeight="1" s="72">
+      <c r="A94" s="125" t="inlineStr">
+        <is>
+          <t>P6-S42</t>
+        </is>
+      </c>
+      <c r="B94" s="126" t="n"/>
+      <c r="C94" s="126" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D72" s="56" t="inlineStr">
-        <is>
-          <t>Voice interface — Whisper + RAG chatbot</t>
-        </is>
-      </c>
-      <c r="E72" s="56" t="inlineStr">
-        <is>
-          <t>Whisper transcription on browser-recorded question (MediaRecorder API). RAG chatbot (P5-12) answers. TTS reads back. Manager asks questions while walking the floor. Works with both synthetic and real Swiggy data now in DB. Blocked on P5-12 (already done).</t>
-        </is>
-      </c>
-      <c r="F72" s="56" t="inlineStr">
-        <is>
-          <t>feat: voice interface — Whisper transcription + RAG answer + TTS readback</t>
-        </is>
-      </c>
-      <c r="G72" s="56" t="inlineStr">
-        <is>
-          <t>docs/PRODUCT_MODES.md (voice section)</t>
-        </is>
-      </c>
-      <c r="H72" s="63" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I72" s="64" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J72" s="55" t="inlineStr">
+      <c r="D94" s="126" t="inlineStr">
+        <is>
+          <t>Product redesign -- move dashboard/runs pages past 'dev console' feel</t>
+        </is>
+      </c>
+      <c r="E94" s="126" t="inlineStr">
+        <is>
+          <t>Explicitly deferred this session pending a proper scoping pass. Concrete evidence gathered: /runs/{id} throws a raw unstyled Next.js 404 (no per-run deep link, only in-page sidebar selection on /runs), and the run-detail view is a dense wall of monospace-labelled text blocks (dimension scores, 10+ revision-reason cards) with little visual hierarchy -- reads like a debug trace rather than something an owner skims at 7am. The landing/hero page already looks like a real product; this needs its own scoping conversation (which pages, target feel, how much rework), not a quick fix bundled into other work. SUPERSEDED 2026-07-03 -- decomposed into concrete, sequenced tasks P6-F09 (theme system), P6-F10 (typography rebalance), P6-F11 (IA restructure), P6-F12 (/runs redesign) after a direct scoping conversation with the user, who flagged the product reads as a dev console and asked for light/dark mode + separated pages (Agents/Operations vs Swiggy Market Intel) as an explicit product-quality bar before shipping more features on top of the old layout.</t>
+        </is>
+      </c>
+      <c r="F94" s="126" t="inlineStr">
+        <is>
+          <t>TBD -- needs scoping conversation first</t>
+        </is>
+      </c>
+      <c r="G94" s="126" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H94" s="127" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="I94" s="125" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J94" s="125" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K72" s="55" t="n"/>
-      <c r="L72" s="59" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="M72" s="58" t="n">
+      <c r="K94" s="125" t="n"/>
+      <c r="L94" s="125" t="n"/>
+      <c r="M94" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="N72" s="55" t="inlineStr">
-        <is>
-          <t>P6-S44</t>
-        </is>
-      </c>
-      <c r="O72" s="56" t="inlineStr">
-        <is>
-          <t>Transcription accuracy smoke test; end-to-end voice → RAG answer → TTS; works with real Swiggy data in DB</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="7.95" customHeight="1" s="72">
-      <c r="A73" s="52" t="n"/>
-      <c r="B73" s="52" t="n"/>
-      <c r="C73" s="52" t="n"/>
-      <c r="D73" s="52" t="n"/>
-      <c r="E73" s="52" t="n"/>
-      <c r="F73" s="52" t="n"/>
-      <c r="G73" s="52" t="n"/>
-      <c r="H73" s="52" t="n"/>
-      <c r="I73" s="52" t="n"/>
-      <c r="J73" s="52" t="n"/>
-      <c r="K73" s="52" t="n"/>
-      <c r="L73" s="52" t="n"/>
-      <c r="M73" s="52" t="n"/>
-      <c r="N73" s="52" t="n"/>
-      <c r="O73" s="52" t="n"/>
-    </row>
-    <row r="74" ht="73.05" customHeight="1" s="72">
-      <c r="A74" s="62" t="inlineStr">
-        <is>
-          <t>P6-F06</t>
-        </is>
-      </c>
-      <c r="B74" s="69" t="inlineStr">
-        <is>
-          <t>feature/action-queue-ui</t>
-        </is>
-      </c>
-      <c r="C74" s="55" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D74" s="56" t="inlineStr">
-        <is>
-          <t>Action queue UI + procurement tracker</t>
-        </is>
-      </c>
-      <c r="E74" s="56" t="inlineStr">
-        <is>
-          <t>New section below plan output. Lists pending actions with type badge. Approve/Reject buttons for APPROVE_REQUIRED. Instamart cart preview modal (items, total, ETA) before approving checkout. Procurement tracker in inventory panel: placed orders, status, ETA.</t>
-        </is>
-      </c>
-      <c r="F74" s="56" t="inlineStr">
-        <is>
-          <t>feat: action queue UI — approve/reject with cart preview, procurement tracker</t>
-        </is>
-      </c>
-      <c r="G74" s="56" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="H74" s="63" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I74" s="49" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J74" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K74" s="55" t="n"/>
-      <c r="L74" s="59" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="M74" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="55" t="inlineStr">
-        <is>
-          <t>P6-S18, P6-F11</t>
-        </is>
-      </c>
-      <c r="O74" s="56" t="inlineStr">
-        <is>
-          <t>Depends on P6-S32 (action_queue in plan API response)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="7.95" customHeight="1" s="72">
-      <c r="A75" s="52" t="n"/>
-      <c r="B75" s="52" t="n"/>
-      <c r="C75" s="52" t="n"/>
-      <c r="D75" s="52" t="n"/>
-      <c r="E75" s="52" t="n"/>
-      <c r="F75" s="52" t="n"/>
-      <c r="G75" s="52" t="n"/>
-      <c r="H75" s="52" t="n"/>
-      <c r="I75" s="52" t="n"/>
-      <c r="J75" s="52" t="n"/>
-      <c r="K75" s="52" t="n"/>
-      <c r="L75" s="52" t="n"/>
-      <c r="M75" s="52" t="n"/>
-      <c r="N75" s="52" t="n"/>
-      <c r="O75" s="52" t="n"/>
-    </row>
-    <row r="76" ht="60" customHeight="1" s="72">
-      <c r="A76" s="62" t="inlineStr">
-        <is>
-          <t>P6-F07</t>
-        </is>
-      </c>
-      <c r="B76" s="69" t="n"/>
-      <c r="C76" s="55" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D76" s="56" t="inlineStr">
-        <is>
-          <t>/brief page — daily morning briefing</t>
-        </is>
-      </c>
-      <c r="E76" s="56" t="inlineStr">
-        <is>
-          <t>New route /brief. Overnight Swiggy performance (orders, avg delivery time, late %), today's demand forecast vs yesterday, top 3 action priorities, market snapshot. Auto-refreshes if brief is stale. Empty state when no brief yet.</t>
-        </is>
-      </c>
-      <c r="F76" s="56" t="inlineStr">
-        <is>
-          <t>feat: /brief page — daily morning operational briefing</t>
-        </is>
-      </c>
-      <c r="G76" s="56" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="H76" s="63" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I76" s="61" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J76" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K76" s="55" t="n"/>
-      <c r="L76" s="59" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="M76" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="55" t="inlineStr">
-        <is>
-          <t>P6-S44, P6-F11</t>
-        </is>
-      </c>
-      <c r="O76" s="56" t="inlineStr">
-        <is>
-          <t>Depends on P6-S22-UNRESOLVED (BriefingService)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="7.95" customHeight="1" s="72">
-      <c r="A77" s="52" t="n"/>
-      <c r="B77" s="52" t="n"/>
-      <c r="C77" s="52" t="n"/>
-      <c r="D77" s="52" t="n"/>
-      <c r="E77" s="52" t="n"/>
-      <c r="F77" s="52" t="n"/>
-      <c r="G77" s="52" t="n"/>
-      <c r="H77" s="52" t="n"/>
-      <c r="I77" s="52" t="n"/>
-      <c r="J77" s="52" t="n"/>
-      <c r="K77" s="52" t="n"/>
-      <c r="L77" s="52" t="n"/>
-      <c r="M77" s="52" t="n"/>
-      <c r="N77" s="52" t="n"/>
-      <c r="O77" s="52" t="n"/>
-    </row>
-    <row r="78" ht="99" customHeight="1" s="72">
-      <c r="A78" s="62" t="inlineStr">
-        <is>
-          <t>P6-F08</t>
-        </is>
-      </c>
-      <c r="B78" s="69" t="n"/>
-      <c r="C78" s="55" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D78" s="56" t="inlineStr">
-        <is>
-          <t>/live page — real-time service monitor</t>
-        </is>
-      </c>
-      <c r="E78" s="56" t="inlineStr">
-        <is>
-          <t>New route /live. Kitchen display-grade SSE feed from LiveMonitorService (P6-S36). Shows active Swiggy delivery orders with ETA countdown, Instamart procurement status with delivery ETA, alert banner on delivery spike or ingredient arrival. Swiggy logo + 'Live via Swiggy MCP' badge. Page shows inactive state outside service hours (12-14h, 19-22h IST).</t>
-        </is>
-      </c>
-      <c r="F78" s="56" t="inlineStr">
-        <is>
-          <t>feat: /live page — SSE kitchen display for active orders and procurement tracking</t>
-        </is>
-      </c>
-      <c r="G78" s="56" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="H78" s="63" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I78" s="61" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J78" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K78" s="55" t="n"/>
-      <c r="L78" s="59" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="M78" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="55" t="inlineStr">
-        <is>
-          <t>P6-S36, P6-F11</t>
-        </is>
-      </c>
-      <c r="O78" s="56" t="inlineStr">
-        <is>
-          <t>SSE events render in real time; ETA countdown ticks; alert banner fires on delivery spike; Swiggy branding visible; inactive state shown outside service hours.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="7.95" customHeight="1" s="72">
-      <c r="A79" s="52" t="n"/>
-      <c r="B79" s="52" t="n"/>
-      <c r="C79" s="52" t="n"/>
-      <c r="D79" s="52" t="n"/>
-      <c r="E79" s="52" t="n"/>
-      <c r="F79" s="52" t="n"/>
-      <c r="G79" s="52" t="n"/>
-      <c r="H79" s="52" t="n"/>
-      <c r="I79" s="52" t="n"/>
-      <c r="J79" s="52" t="n"/>
-      <c r="K79" s="52" t="n"/>
-      <c r="L79" s="52" t="n"/>
-      <c r="M79" s="52" t="n"/>
-      <c r="N79" s="52" t="n"/>
-      <c r="O79" s="52" t="n"/>
-    </row>
-    <row r="80" ht="124.95" customHeight="1" s="72">
-      <c r="A80" s="62" t="inlineStr">
-        <is>
-          <t>P6-F09</t>
-        </is>
-      </c>
-      <c r="B80" s="69" t="inlineStr">
-        <is>
-          <t>feature/design-system-theming</t>
-        </is>
-      </c>
-      <c r="C80" s="55" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D80" s="56" t="inlineStr">
-        <is>
-          <t>Design system: light/dark theme + token system</t>
-        </is>
-      </c>
-      <c r="E80" s="56" t="inlineStr">
-        <is>
-          <t>Add a parallel light-mode palette alongside the existing ink/ember dark tokens in globals.css (Tailwind v4 @theme), wire a theme toggle (persisted via localStorage, defaults to system prefers-color-scheme) accessible from every page's header/nav, and audit + replace ad-hoc opacity-based dark-only utility classes (text-white/65, bg-white/[0.02], etc.) across all ~35 dashboard/runs/chat components with theme-aware tokens so both modes render correctly. Target users skew middle-aged restaurant owners/managers who may find a dark-only dev-tool aesthetic hard to read or off-putting -- a toggle makes the product usable for both preferences, not just engineers. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. DONE 2026-07-04: light-mode token layer + toggle built and applied across all ~30 pages/components (not just the 5 touched in the direction prototype), via a boundary-safe scripted class rename so the same old class always maps to the same new token. 3 real bugs found only by driving the app in a browser (not catchable by a class-rename script alone): ember accent text washed out on light badges (fixed via --color-accent token), DatePicker select/date-input had inline style={{background:...}} overriding the className entirely, and no explicit color-scheme meant native &lt;select&gt;/&lt;option&gt; rendered with OS dark chrome regardless of page theme. Verified end-to-end with a real registered test account across dashboard/runs/connectors/chat in both themes -- zero console errors, zero hydration warnings, tsc + eslint clean.</t>
-        </is>
-      </c>
-      <c r="F80" s="56" t="inlineStr">
-        <is>
-          <t>feat: light/dark theme system with persisted toggle</t>
-        </is>
-      </c>
-      <c r="G80" s="56" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="H80" s="63" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I80" s="49" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J80" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K80" s="84" t="n">
-        <v>46207</v>
-      </c>
-      <c r="L80" s="85" t="n">
-        <v>46207</v>
-      </c>
-      <c r="M80" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" s="55" t="n"/>
-      <c r="O80" s="56" t="inlineStr">
-        <is>
-          <t>Toggle switches and persists across reload; spot-check contrast/readability of all dashboard/runs/chat components in both modes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="7.95" customHeight="1" s="72"/>
-    <row r="82" ht="112.05" customHeight="1" s="72">
-      <c r="A82" s="62" t="inlineStr">
-        <is>
-          <t>P6-F10</t>
-        </is>
-      </c>
-      <c r="B82" s="69" t="n"/>
-      <c r="C82" s="55" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D82" s="56" t="inlineStr">
-        <is>
-          <t>De-console-ify typography and visual hierarchy</t>
-        </is>
-      </c>
-      <c r="E82" s="56" t="inlineStr">
-        <is>
-          <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. NOTE: the ember-accent-text contrast fix (text-ember-300/400 -&gt; --color-accent token) was already done as part of P6-F09 verification, since it was blocking basic light-mode readability, not a nice-to-have. Remaining F10 scope: pull font-mono back from being the default label voice everywhere to a true accent. DONE 2026-07-4: two-pass conversion -- (1) mechanical pass on the specific font-mono+uppercase+tracking- combination (171 label class-strings, always a decorative label in this codebase, never data), (2) per-instance judgment pass on the remaining ~89 bare font-mono usages, since this codebase used monospace for three genuinely different things (real data, category/status labels, and even prose/error messages) that no single mechanical rule could tell apart. Demoted buttons/links/status words/category badges/prose; kept genuine data (prices, IDs, timestamps, scores, deltas, code blocks). Also caught 2 more instances of hardcoded legacy bg-navy-*/text-gold-* colors (a different legacy palette than bg-ink-*, missed by the original P6-F09 conversion script) while auditing context file-by-file. Verified in browser (dashboard, runs) both themes -- zero console errors, tsc clean. FOLLOW-UP 2026-07-4: initial Completed mark only covered the mono-demotion half; the serif-extension half (matching the landing page voice) was still missing. Fixed: dashboard hero emphasis line switched from a color gradient to the landing page's proven display-it italic accent pattern; 5 bare page titles (Plan History, Connectors, Data Health, Workspace Settings, Restaurant Profiles) converted from plain bold sans to the .display serif class; key numeric stat tiles (connectors sync counts, runs KPI Metric component) converted to .num-display serif figures. Now genuinely done both halves.</t>
-        </is>
-      </c>
-      <c r="F82" s="56" t="inlineStr">
-        <is>
-          <t>feat: rebalance typography -- monospace as accent, not primary label voice</t>
-        </is>
-      </c>
-      <c r="G82" s="56" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="H82" s="63" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I82" s="49" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J82" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K82" s="84" t="n">
-        <v>46207</v>
-      </c>
-      <c r="L82" s="85" t="n">
-        <v>46207</v>
-      </c>
-      <c r="M82" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N82" s="55" t="inlineStr">
-        <is>
-          <t>P6-F09</t>
-        </is>
-      </c>
-      <c r="O82" s="56" t="inlineStr">
-        <is>
-          <t>Visual diff of dashboard/runs headers and stat labels before/after; landing-page-level polish confirmed by eye on both themes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="7.95" customHeight="1" s="72"/>
-    <row r="84" ht="99" customHeight="1" s="72">
-      <c r="A84" s="62" t="inlineStr">
-        <is>
-          <t>P6-F11</t>
-        </is>
-      </c>
-      <c r="B84" s="69" t="n"/>
-      <c r="C84" s="55" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D84" s="56" t="inlineStr">
-        <is>
-          <t>Information architecture restructure: split the mega-dashboard into focused pages</t>
-        </is>
-      </c>
-      <c r="E84" s="56" t="inlineStr">
-        <is>
-          <t>The single /dashboard page currently tries to show demand forecast + reservations + complaints + inventory + market intel + menu + critic + connector status all at once -- reads as a diagnostics dump a manager could get lost in. Restructure into: a lightweight /dashboard 'Today' view (KPIs, alerts, pending actions only -- what a manager checks first each morning), a dedicated /operations page for the 5 planning-agent outputs in plain-language framing (not raw JSON-shaped cards), and Swiggy Market Intelligence promoted to its own dedicated /market page (competitor pricing, occupancy, Instamart procurement) so it has a clear, demo-able home separate from internal ops data -- matching the product's own internal-vs-Swiggy-data distinction already documented in CLAUDE.md. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. DONE 2026-07-04: split shipped -- /dashboard is now the lightweight 'Today' view (TodayIdleState: business KPIs, market intel teaser, actionable ops snapshot), /operations holds the 5 agent-card detail + CriticBanner + ForecastChart + ManagerActionPanel (via useSelectedRun, reads ?run={id} or falls back to most recent), /market is the dedicated Swiggy market intelligence page. Verified end-to-end via Playwright: fresh register -&gt; idle state renders clean in both themes -&gt; trigger a plan via the new PlanShiftModal -&gt; auto-redirects to /operations?run={id} with the CriticBanner visible on landing, zero console errors.</t>
-        </is>
-      </c>
-      <c r="F84" s="56" t="inlineStr">
-        <is>
-          <t>feat(P6-F11/F12): redesign Today dashboard -- modal planning flow, market-aware layout, warm theme</t>
-        </is>
-      </c>
-      <c r="G84" s="56" t="inlineStr">
-        <is>
-          <t>CLAUDE.md (nav/page map section), docs/ARCHITECTURE.md</t>
-        </is>
-      </c>
-      <c r="H84" s="63" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I84" s="49" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J84" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K84" s="84" t="n">
-        <v>46207</v>
-      </c>
-      <c r="L84" s="85" t="n">
-        <v>46207</v>
-      </c>
-      <c r="M84" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" s="55" t="inlineStr">
-        <is>
-          <t>P6-F10</t>
-        </is>
-      </c>
-      <c r="O84" s="56" t="inlineStr">
-        <is>
-          <t>Each new page renders its intended slice only; nav updated; no orphaned links to the old single-page layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="7.95" customHeight="1" s="72"/>
-    <row r="86" ht="151.05" customHeight="1" s="72">
-      <c r="A86" s="62" t="inlineStr">
-        <is>
-          <t>P6-F12</t>
-        </is>
-      </c>
-      <c r="B86" s="69" t="n"/>
-      <c r="C86" s="55" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D86" s="56" t="inlineStr">
-        <is>
-          <t>/runs history page redesign</t>
-        </is>
-      </c>
-      <c r="E86" s="56" t="inlineStr">
-        <is>
-          <t>Apply the new design system to /runs. Restyle from a dense monospace debug trace (raw dimension-score grids, 10+ revision-reason text blocks) into something a manager can skim in under a minute. Fix the currently-unstyled raw Next.js 404 on /runs/{id} deep links -- give each run its own real page. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts.</t>
-        </is>
-      </c>
-      <c r="F86" s="56" t="inlineStr">
-        <is>
-          <t>feat: redesign /runs history page + fix /runs/{id} deep-link 404</t>
-        </is>
-      </c>
-      <c r="G86" s="56" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="H86" s="63" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I86" s="49" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J86" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K86" s="55" t="n"/>
-      <c r="L86" s="59" t="n"/>
-      <c r="M86" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" s="55" t="inlineStr">
-        <is>
-          <t>P6-F11</t>
-        </is>
-      </c>
-      <c r="O86" s="56" t="inlineStr">
-        <is>
-          <t>Direct navigation to /runs/{id} renders the run, not a 404; skim-readability spot check.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="7.95" customHeight="1" s="72"/>
-    <row r="88" ht="28.05" customHeight="1" s="72">
-      <c r="A88" s="62" t="inlineStr">
-        <is>
-          <t>P6-S39</t>
-        </is>
-      </c>
-      <c r="B88" s="69" t="n"/>
-      <c r="C88" s="55" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D88" s="56" t="inlineStr">
-        <is>
-          <t>Fix SQLite/JSONB test-infra gap blocking full CI coverage</t>
-        </is>
-      </c>
-      <c r="E88" s="56" t="inlineStr">
-        <is>
-          <t>test_swiggy_reservation_sync.py and test_connector_repository.py are excluded from the CI unit-tests job (P6-Q03) because they spin up a real SQLite engine and connectors.connector_metadata uses Postgres' JSONB column type, which SQLite's compiler can't render. Either give the column a SQLite-compatible fallback type for tests, or run these two files against a real Postgres service container in CI (docker-compose.yml already defines postgres:16 for local dev -- same image could back a CI service).</t>
-        </is>
-      </c>
-      <c r="F88" s="56" t="inlineStr">
-        <is>
-          <t>fix: SQLite-compatible JSONB handling (or Postgres CI service) for excluded test files</t>
-        </is>
-      </c>
-      <c r="G88" s="56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H88" s="63" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I88" s="64" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J88" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K88" s="55" t="n"/>
-      <c r="L88" s="55" t="n"/>
-      <c r="M88" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="55" t="inlineStr">
-        <is>
-          <t>P6-S23</t>
-        </is>
-      </c>
-      <c r="O88" s="56" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="52" t="n"/>
-      <c r="B89" s="52" t="n"/>
-      <c r="C89" s="52" t="n"/>
-      <c r="D89" s="52" t="n"/>
-      <c r="E89" s="52" t="n"/>
-      <c r="F89" s="52" t="n"/>
-      <c r="G89" s="52" t="n"/>
-      <c r="H89" s="52" t="n"/>
-      <c r="I89" s="52" t="n"/>
-      <c r="J89" s="52" t="n"/>
-      <c r="K89" s="52" t="n"/>
-      <c r="L89" s="52" t="n"/>
-      <c r="M89" s="52" t="n"/>
-      <c r="N89" s="52" t="n"/>
-      <c r="O89" s="52" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="62" t="inlineStr">
-        <is>
-          <t>P6-S40</t>
-        </is>
-      </c>
-      <c r="B90" s="69" t="n"/>
-      <c r="C90" s="55" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D90" s="56" t="inlineStr">
-        <is>
-          <t>Promote reviewed RAGAS/DeepEval candidates into curated eval files</t>
-        </is>
-      </c>
-      <c r="E90" s="56" t="inlineStr">
-        <is>
-          <t>build_ragas_dataset.py / build_deepeval_dataset.py (P6-Q03) produce .candidates.json files from live approved runs but never auto-merge them -- ground_truth needs human verification by design. Needs a recurring habit of actually running these periodically and hand-promoting reviewed candidates into complaint_rag_samples.json / test_deepeval_quality.py, or the static datasets stay frozen at today's size forever.</t>
-        </is>
-      </c>
-      <c r="F90" s="56" t="inlineStr">
-        <is>
-          <t>chore: promote reviewed eval candidates into curated datasets</t>
-        </is>
-      </c>
-      <c r="G90" s="56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H90" s="63" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I90" s="64" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J90" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K90" s="55" t="n"/>
-      <c r="L90" s="55" t="n"/>
-      <c r="M90" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="55" t="inlineStr">
-        <is>
-          <t>P6-S23</t>
-        </is>
-      </c>
-      <c r="O90" s="56" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="52" t="n"/>
-      <c r="B91" s="52" t="n"/>
-      <c r="C91" s="52" t="n"/>
-      <c r="D91" s="52" t="n"/>
-      <c r="E91" s="52" t="n"/>
-      <c r="F91" s="52" t="n"/>
-      <c r="G91" s="52" t="n"/>
-      <c r="H91" s="52" t="n"/>
-      <c r="I91" s="52" t="n"/>
-      <c r="J91" s="52" t="n"/>
-      <c r="K91" s="52" t="n"/>
-      <c r="L91" s="52" t="n"/>
-      <c r="M91" s="52" t="n"/>
-      <c r="N91" s="52" t="n"/>
-      <c r="O91" s="52" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="62" t="inlineStr">
-        <is>
-          <t>P6-S41</t>
-        </is>
-      </c>
-      <c r="B92" s="69" t="n"/>
-      <c r="C92" s="55" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D92" s="56" t="inlineStr">
-        <is>
-          <t>Regenerate golden_runs.json against real production data</t>
-        </is>
-      </c>
-      <c r="E92" s="56" t="inlineStr">
-        <is>
-          <t>build_golden_dataset.py's key-path bug is fixed (P6-Q03) but the checked-in fixture still reflects the old, always-empty extraction, since regenerating it requires a live Postgres populated with real run history, which wasn't available during the fix. Run scripts/build_golden_dataset.py locally once docker-compose services are up to refresh it with corrected shortage/restock data.</t>
-        </is>
-      </c>
-      <c r="F92" s="56" t="inlineStr">
-        <is>
-          <t>chore: regenerate golden_runs.json with corrected extraction logic</t>
-        </is>
-      </c>
-      <c r="G92" s="56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H92" s="63" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I92" s="61" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J92" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K92" s="55" t="n"/>
-      <c r="L92" s="55" t="n"/>
-      <c r="M92" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="55" t="inlineStr">
-        <is>
-          <t>P6-S23</t>
-        </is>
-      </c>
-      <c r="O92" s="56" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="52" t="n"/>
-      <c r="B93" s="52" t="n"/>
-      <c r="C93" s="52" t="n"/>
-      <c r="D93" s="52" t="n"/>
-      <c r="E93" s="52" t="n"/>
-      <c r="F93" s="52" t="n"/>
-      <c r="G93" s="52" t="n"/>
-      <c r="H93" s="52" t="n"/>
-      <c r="I93" s="52" t="n"/>
-      <c r="J93" s="52" t="n"/>
-      <c r="K93" s="52" t="n"/>
-      <c r="L93" s="52" t="n"/>
-      <c r="M93" s="52" t="n"/>
-      <c r="N93" s="52" t="n"/>
-      <c r="O93" s="52" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="62" t="inlineStr">
-        <is>
-          <t>P6-S42</t>
-        </is>
-      </c>
-      <c r="B94" s="69" t="n"/>
-      <c r="C94" s="55" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D94" s="56" t="inlineStr">
-        <is>
-          <t>Product redesign -- move dashboard/runs pages past 'dev console' feel</t>
-        </is>
-      </c>
-      <c r="E94" s="56" t="inlineStr">
-        <is>
-          <t>Explicitly deferred this session pending a proper scoping pass. Concrete evidence gathered: /runs/{id} throws a raw unstyled Next.js 404 (no per-run deep link, only in-page sidebar selection on /runs), and the run-detail view is a dense wall of monospace-labelled text blocks (dimension scores, 10+ revision-reason cards) with little visual hierarchy -- reads like a debug trace rather than something an owner skims at 7am. The landing/hero page already looks like a real product; this needs its own scoping conversation (which pages, target feel, how much rework), not a quick fix bundled into other work. SUPERSEDED 2026-07-03 -- decomposed into concrete, sequenced tasks P6-F09 (theme system), P6-F10 (typography rebalance), P6-F11 (IA restructure), P6-F12 (/runs redesign) after a direct scoping conversation with the user, who flagged the product reads as a dev console and asked for light/dark mode + separated pages (Agents/Operations vs Swiggy Market Intel) as an explicit product-quality bar before shipping more features on top of the old layout.</t>
-        </is>
-      </c>
-      <c r="F94" s="56" t="inlineStr">
-        <is>
-          <t>TBD -- needs scoping conversation first</t>
-        </is>
-      </c>
-      <c r="G94" s="56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H94" s="63" t="inlineStr">
-        <is>
-          <t>Superseded</t>
-        </is>
-      </c>
-      <c r="I94" s="61" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J94" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K94" s="55" t="n"/>
-      <c r="L94" s="55" t="n"/>
-      <c r="M94" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="55" t="n"/>
-      <c r="O94" s="56" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="52" t="n"/>
-      <c r="B95" s="52" t="n"/>
-      <c r="C95" s="52" t="n"/>
-      <c r="D95" s="52" t="n"/>
-      <c r="E95" s="52" t="n"/>
-      <c r="F95" s="52" t="n"/>
-      <c r="G95" s="52" t="n"/>
-      <c r="H95" s="52" t="n"/>
-      <c r="I95" s="52" t="n"/>
-      <c r="J95" s="52" t="n"/>
-      <c r="K95" s="52" t="n"/>
-      <c r="L95" s="52" t="n"/>
-      <c r="M95" s="52" t="n"/>
-      <c r="N95" s="52" t="n"/>
-      <c r="O95" s="52" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="62" t="inlineStr">
-        <is>
-          <t>P6-F18</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>feature/design-system-theming</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Live market intelligence + business analytics endpoints, independent of planning runs</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>GET /api/v1/market/pulse calls CompetitorEnricher/OccupancyEnricher/ProcurementEnricher directly (no planning run required) and structures diff_pct/direction comparisons server-side, since the raw enrichers return loosely-typed dicts, not a UI-ready shape. GET /api/v1/business/performance computes real revenue/profit via a new MenuItem.cost_price column, daily trend, yesterday/today snapshots, top/bottom dishes, dine-in vs delivery channel split, complaints grouped by keyword-matched category, and peak-hours demand (orders only, so future-dated reservation seed rows don't skew 'when are we actually busy'). DONE 2026-07-04: verified against seeded data -- revenue, margin, and complaint-category counts all match expected values. NOTE: this commit's message (eaef859) and an earlier CLAUDE.md pass informally used the tag 'P6-F16', which collides with an already-used tag from the P6-F14/F15/F17 PR (2026-07-01) that was never given tracker rows -- P6-F18 is the correct sequential tracker ID; the git history is left as-is rather than rewritten.</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>feat(P6-F16 in commit msg / P6-F18 in tracker): live market intelligence + business analytics, independent of planning runs</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>CLAUDE.md (API routes section, Swiggy token/circuit-breaker gotcha)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K96" s="87" t="n">
-        <v>46207</v>
-      </c>
-      <c r="L96" s="87" t="n">
-        <v>46207</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1</v>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>P6-S15</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>Hit /market/pulse and /business/performance directly against seeded data; confirm revenue/margin/complaint-category numbers match the seed script, and market pulse returns swiggy_connected + live comparisons when the token is valid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="86" t="n"/>
-      <c r="B97" s="86" t="n"/>
-      <c r="C97" s="86" t="n"/>
-      <c r="D97" s="86" t="n"/>
-      <c r="E97" s="86" t="n"/>
-      <c r="F97" s="86" t="n"/>
-      <c r="G97" s="86" t="n"/>
-      <c r="H97" s="86" t="n"/>
-      <c r="I97" s="86" t="n"/>
-      <c r="J97" s="86" t="n"/>
-      <c r="K97" s="86" t="n"/>
-      <c r="L97" s="86" t="n"/>
-      <c r="M97" s="86" t="n"/>
-      <c r="N97" s="86" t="n"/>
-      <c r="O97" s="86" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="62" t="inlineStr">
-        <is>
-          <t>P6-F19</t>
-        </is>
-      </c>
-      <c r="B98" s="69" t="inlineStr">
-        <is>
-          <t>feature/design-system-theming</t>
-        </is>
-      </c>
-      <c r="C98" s="55" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D98" s="56" t="inlineStr">
-        <is>
-          <t>Today dashboard redesign: modal planning flow, warm theme, NavBar cleanup, date-relative seed data</t>
-        </is>
-      </c>
-      <c r="E98" s="56" t="inlineStr">
-        <is>
-          <t>TodayIdleState fully rewritten around a manager's actual priorities: overall performance chart, actionable 'tonight at a glance' reservations/inventory snapshot, yesterday's business KPIs with channel split, menu performance (top/bottom sellers), peak hours paired with a merged guest-sentiment + complaint-theme card, and a consolidated market intelligence card teasing into /market. 'Plan your next shift' now opens PlanShiftModal instead of running inline. NavBar: removed the scenario dropdown (the modal owns scenario selection now) and the stale 'Friday Rush -- not planned yet' status chip; warmer brand mark and active-tab styling. globals.css light-mode tokens rebuilt around a warm stone/parchment palette instead of cool blue-gray. Also fixed a glitch where the critic-approved banner flashed on /dashboard for one frame and vanished on redirect to /operations -- /operations now shows CriticBanner directly instead of burying the verdict in the Manager Brief modal. seed_demo_data.py no longer hardcodes 2026 calendar dates -- SEED_AS_OF anchors to run-time so 'Today' always reflects live state, and inventory was rebalanced from a permanent 11/18 shortage state to 3/18 genuinely low items. DONE 2026-07-04: verified end-to-end via Playwright (fresh register, both themes, full plan-run -&gt; redirect -&gt; critic banner flow), zero console errors.</t>
-        </is>
-      </c>
-      <c r="F98" s="56" t="inlineStr">
-        <is>
-          <t>feat(P6-F11/F12): redesign Today dashboard -- modal planning flow, market-aware layout, warm theme</t>
-        </is>
-      </c>
-      <c r="G98" s="56" t="inlineStr">
-        <is>
-          <t>CLAUDE.md (page map, theming section)</t>
-        </is>
-      </c>
-      <c r="H98" s="63" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I98" s="49" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J98" s="55" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K98" s="84" t="n">
-        <v>46207</v>
-      </c>
-      <c r="L98" s="85" t="n">
-        <v>46207</v>
-      </c>
-      <c r="M98" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N98" s="55" t="inlineStr">
-        <is>
-          <t>P6-F11; P6-F18</t>
-        </is>
-      </c>
-      <c r="O98" s="56" t="inlineStr">
-        <is>
-          <t>Playwright: register -&gt; idle state renders clean (light+dark, no console errors) -&gt; open PlanShiftModal -&gt; Generate Plan -&gt; auto-redirect to /operations?run={id} with CriticBanner visible, no flash/glitch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="86" t="n"/>
-      <c r="B99" s="86" t="n"/>
-      <c r="C99" s="86" t="n"/>
-      <c r="D99" s="86" t="n"/>
-      <c r="E99" s="86" t="n"/>
-      <c r="F99" s="86" t="n"/>
-      <c r="G99" s="86" t="n"/>
-      <c r="H99" s="86" t="n"/>
-      <c r="I99" s="86" t="n"/>
-      <c r="J99" s="86" t="n"/>
-      <c r="K99" s="86" t="n"/>
-      <c r="L99" s="86" t="n"/>
-      <c r="M99" s="86" t="n"/>
-      <c r="N99" s="86" t="n"/>
-      <c r="O99" s="86" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="70" t="inlineStr">
-        <is>
-          <t>→ DEMO 1  |  all above on main, docs updated, screenshots done — record full Swiggy read + AI + voice + live monitor demo ←</t>
-        </is>
-      </c>
+      <c r="N94" s="126" t="n"/>
+      <c r="O94" s="126" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B40:B49"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A100:O100"/>
+  <mergeCells count="12">
+    <mergeCell ref="A65:O65"/>
+    <mergeCell ref="A76:O76"/>
+    <mergeCell ref="A71:O71"/>
+    <mergeCell ref="A85:O85"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A46:O46"/>
+    <mergeCell ref="A80:O80"/>
+    <mergeCell ref="A93:O93"/>
+    <mergeCell ref="A61:O61"/>
+    <mergeCell ref="A88:O88"/>
+    <mergeCell ref="A48:O48"/>
+    <mergeCell ref="A3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -16386,7 +16386,7 @@
       </c>
       <c r="E53" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-05: search_menu(query=dish_name) confirmed to return ZERO results for every query tested against this Swiggy sandbox -- real API calls, real zero value, not a bug. Removed _search_dish_prices entirely rather than ship a permanently-empty feature. The per-dish competitor table this task specified was superseded by a structurally different fix instead (see P6-MI12): exact dish-name matching between our menu and competitor menus turned out to never reliably align ("Butter Chicken" vs "Butter Chicken Masala" vs "Murgh Makhani"), so dish_prices was replaced by keyword-in-name category classification. dish_prices/DishPriceEntry models removed from market.py and lib/api.ts.</t>
+          <t>DONE 2026-07-06: search_menu(query=dish_name) confirmed to return ZERO results for every query tested against this Swiggy sandbox -- real API calls, real zero value, not a bug. Removed _search_dish_prices entirely rather than ship a permanently-empty feature. The per-dish competitor table this task specified was superseded by a structurally different fix instead (see P6-MI12): exact dish-name matching between our menu and competitor menus turned out to never reliably align ("Butter Chicken" vs "Butter Chicken Masala" vs "Murgh Makhani"), so dish_prices was replaced by keyword-in-name category classification. dish_prices/DishPriceEntry models removed from market.py and lib/api.ts.</t>
         </is>
       </c>
       <c r="F53" s="44" t="inlineStr">
@@ -16415,10 +16415,10 @@
         </is>
       </c>
       <c r="K53" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="L53" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="M53" s="47" t="n">
         <v>1</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="E54" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-05: fetch_food_coupons(restaurantId, addressId) called per open competitor (max 3), filtered to COD-compatible (requiresOnlinePayment=False), building competitor_deals: [{restaurant, title, discount, code}]. Injected into menu_intel prompt and shown as its own "Competitor Swiggy Deals" card on /market with full discount/code detail per restaurant (not capped to the first result).</t>
+          <t>DONE 2026-07-06: fetch_food_coupons(restaurantId, addressId) called per open competitor (max 3), filtered to COD-compatible (requiresOnlinePayment=False), building competitor_deals: [{restaurant, title, discount, code}]. Injected into menu_intel prompt and shown as its own "Competitor Swiggy Deals" card on /market with full discount/code detail per restaurant (not capped to the first result).</t>
         </is>
       </c>
       <c r="F54" s="44" t="inlineStr">
@@ -16486,10 +16486,10 @@
         </is>
       </c>
       <c r="K54" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="L54" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="M54" s="47" t="n">
         <v>1</v>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="E55" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-05: get_restaurant_details(restaurantId, lat, lng) called for top 3 open Dineout competitors, parsing deals[]/amenities/highlights/avgRating -&gt; competitor_dineout_deals (ALL deals per restaurant shown, not just the first). get_available_slots deals[] parsed with zero extra calls -&gt; slot_deals_found, aggregated by time-of-day (_aggregate_slot_availability_by_time) and rendered as OccupancyBySlotChart (status-colored HIGH/MEDIUM/LOW). Injected into reservation node prompt via OccupancyEnricher.</t>
+          <t>DONE 2026-07-06: get_restaurant_details(restaurantId, lat, lng) called for top 3 open Dineout competitors, parsing deals[]/amenities/highlights/avgRating -&gt; competitor_dineout_deals (ALL deals per restaurant shown, not just the first). get_available_slots deals[] parsed with zero extra calls -&gt; slot_deals_found, aggregated by time-of-day (_aggregate_slot_availability_by_time) and rendered as OccupancyBySlotChart (status-colored HIGH/MEDIUM/LOW). Injected into reservation node prompt via OccupancyEnricher.</t>
         </is>
       </c>
       <c r="F55" s="44" t="inlineStr">
@@ -16557,10 +16557,10 @@
         </is>
       </c>
       <c r="K55" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="L55" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="M55" s="47" t="n">
         <v>1</v>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="E56" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-05: Diff 7 added to EvaluationSanityChecker -- fires when market_intel_a.tonight_busy is True AND dineout_deals_count &gt;= 2, flagging that predicted walk-in demand may be absorbed by competitor promotions. Total active assumption diffs: 7.</t>
+          <t>DONE 2026-07-06: Diff 7 added to EvaluationSanityChecker -- fires when market_intel_a.tonight_busy is True AND dineout_deals_count &gt;= 2, flagging that predicted walk-in demand may be absorbed by competitor promotions. Total active assumption diffs: 7.</t>
         </is>
       </c>
       <c r="F56" s="44" t="inlineStr">
@@ -16628,10 +16628,10 @@
         </is>
       </c>
       <c r="K56" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="L56" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="M56" s="47" t="n">
         <v>1</v>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="E57" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-05: Pricing impact model added (elasticity model: gap_pct * -0.8 = volume_change_pct; weekly_revenue_impact_inr computed per flagged item, top 5 by absolute impact returned). Rendered as a diverging PricingImpactChart (rose = at-risk, emerald = upside) on /market, honestly scoped to exact dish-name matches only -- a smaller "Exact Menu Matches" card, since exact matching across restaurants is unreliable (see P6-MI12).</t>
+          <t>DONE 2026-07-06: Pricing impact model added (elasticity model: gap_pct * -0.8 = volume_change_pct; weekly_revenue_impact_inr computed per flagged item, top 5 by absolute impact returned). Rendered as a diverging PricingImpactChart (rose = at-risk, emerald = upside) on /market, honestly scoped to exact dish-name matches only -- a smaller "Exact Menu Matches" card, since exact matching across restaurants is unreliable (see P6-MI12).</t>
         </is>
       </c>
       <c r="F57" s="44" t="inlineStr">
@@ -16699,10 +16699,10 @@
         </is>
       </c>
       <c r="K57" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="L57" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="M57" s="47" t="n">
         <v>1</v>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="E58" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-05: ScenarioRecommender (domain/services/scenario_recommender.py) built -- LLM-based recommendation with a deterministic rule-based fallback, factoring in recent run history, live market_intel signals, calendar context (INDIAN_HOLIDAYS_2026 added to core/constants.py, 20 holidays), and inventory shortage count. GET /planning/recommend?target_date=YYYY-MM-DD added to api/routes/planning.py.</t>
+          <t>DONE 2026-07-06: ScenarioRecommender (domain/services/scenario_recommender.py) built -- LLM-based recommendation with a deterministic rule-based fallback, factoring in recent run history, live market_intel signals, calendar context (INDIAN_HOLIDAYS_2026 added to core/constants.py, 20 holidays), and inventory shortage count. GET /planning/recommend?target_date=YYYY-MM-DD added to api/routes/planning.py.</t>
         </is>
       </c>
       <c r="F58" s="44" t="inlineStr">
@@ -16770,10 +16770,10 @@
         </is>
       </c>
       <c r="K58" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="L58" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="M58" s="47" t="n">
         <v>1</v>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="E59" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-05: GET /market/trends?days=N added -- reads market_intel from stored PlanningRun.final_response across past runs (zero new Swiggy calls), returns per-dish area_avg price history + occupancy signal history. MarketTrendChart.tsx renders both as recharts line charts on /market, dish-selectable, empty state when fewer than 3 data points.</t>
+          <t>DONE 2026-07-06: GET /market/trends?days=N added -- reads market_intel from stored PlanningRun.final_response across past runs (zero new Swiggy calls), returns per-dish area_avg price history + occupancy signal history. MarketTrendChart.tsx renders both as recharts line charts on /market, dish-selectable, empty state when fewer than 3 data points.</t>
         </is>
       </c>
       <c r="F59" s="44" t="inlineStr">
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="K59" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="L59" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="M59" s="47" t="n">
         <v>1</v>
@@ -16912,10 +16912,10 @@
         </is>
       </c>
       <c r="K60" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="L60" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="M60" s="47" t="n">
         <v>1</v>
@@ -16983,10 +16983,10 @@
         </is>
       </c>
       <c r="K61" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="L61" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="M61" s="47" t="n">
         <v>1</v>
@@ -17050,10 +17050,10 @@
         </is>
       </c>
       <c r="K62" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="L62" s="46" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="M62" s="47" t="n">
         <v>1</v>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -16152,161 +16152,169 @@
       <c r="O48" s="87" t="n"/>
     </row>
     <row r="49" ht="52.05" customHeight="1" s="77">
-      <c r="A49" s="52" t="inlineStr">
+      <c r="A49" s="72" t="inlineStr">
         <is>
           <t>P6-MI01</t>
         </is>
       </c>
-      <c r="B49" s="53" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-expansion</t>
-        </is>
-      </c>
-      <c r="C49" s="53" t="inlineStr">
+      <c r="B49" s="73" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-extended</t>
+        </is>
+      </c>
+      <c r="C49" s="73" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D49" s="53" t="inlineStr">
+      <c r="D49" s="73" t="inlineStr">
         <is>
           <t>Competitor deal &amp; offer intelligence</t>
         </is>
       </c>
-      <c r="E49" s="53" t="inlineStr">
-        <is>
-          <t>Surface deal and amenity data from get_restaurant_details (already called in OccupancyEnricher but data discarded). Extract: deals[], isFree, title, amenities[], highlights[], avgRating per competitor. Add to market_intel_output as competitor_deals list. Show in Market Intelligence panel: Competitor X running 20% off deal. Has live music + valet. No new API calls — uses data already fetched.</t>
-        </is>
-      </c>
-      <c r="F49" s="53" t="inlineStr">
+      <c r="E49" s="73" t="inlineStr">
+        <is>
+          <t>Surface deal and amenity data from get_restaurant_details (already called in OccupancyEnricher but data discarded). Extract: deals[], isFree, title, amenities[], highlights[], avgRating per competitor. Add to market_intel_output as competitor_deals list. Show in Market Intelligence panel: Competitor X running 20% off deal. Has live music + valet. No new API calls — uses data already fetched. SUPERSEDED 2026-07-06 -- delivered as part of P6-MI07 (get_restaurant_details + slot deals[]) on feature/swiggy-market-intel-extended; never built as its own separate task.</t>
+        </is>
+      </c>
+      <c r="F49" s="73" t="inlineStr">
         <is>
           <t>feat: surface competitor deal and amenity intelligence from Dineout MCP</t>
         </is>
       </c>
-      <c r="G49" s="53" t="inlineStr">
+      <c r="G49" s="73" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (OccupancyEnricher output extended)</t>
         </is>
       </c>
-      <c r="H49" s="54" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I49" s="52" t="inlineStr">
+      <c r="H49" s="74" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="I49" s="72" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J49" s="52" t="n"/>
-      <c r="K49" s="52" t="n"/>
-      <c r="L49" s="52" t="n"/>
-      <c r="M49" s="55" t="n">
+      <c r="J49" s="72" t="n"/>
+      <c r="K49" s="72" t="n"/>
+      <c r="L49" s="72" t="n"/>
+      <c r="M49" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="N49" s="53" t="n"/>
-      <c r="O49" s="53" t="n"/>
+      <c r="N49" s="73" t="n"/>
+      <c r="O49" s="73" t="n"/>
     </row>
     <row r="50" ht="52.05" customHeight="1" s="77">
-      <c r="A50" s="56" t="inlineStr">
+      <c r="A50" s="72" t="inlineStr">
         <is>
           <t>P6-MI02</t>
         </is>
       </c>
-      <c r="B50" s="57" t="n"/>
-      <c r="C50" s="57" t="inlineStr">
+      <c r="B50" s="73" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-extended</t>
+        </is>
+      </c>
+      <c r="C50" s="73" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D50" s="57" t="inlineStr">
+      <c r="D50" s="73" t="inlineStr">
         <is>
           <t>Competitor price trend tracking</t>
         </is>
       </c>
-      <c r="E50" s="57" t="inlineStr">
-        <is>
-          <t>New table: market_snapshots (org_id, snapshot_type, data jsonb, captured_at). After each planning run, persist competitor_pricing dict from CompetitorEnricher. MarketIntelService computes week-over-week delta per dish. market_intel_output gains price_trends field: [{dish, current_avg, prev_avg, delta_pct, direction}]. Panel shows: Biryani area avg up 18pct vs last week. Zero new Swiggy API calls - just persisting what we already fetch.</t>
-        </is>
-      </c>
-      <c r="F50" s="57" t="inlineStr">
+      <c r="E50" s="73" t="inlineStr">
+        <is>
+          <t>New table: market_snapshots (org_id, snapshot_type, data jsonb, captured_at). After each planning run, persist competitor_pricing dict from CompetitorEnricher. MarketIntelService computes week-over-week delta per dish. market_intel_output gains price_trends field: [{dish, current_avg, prev_avg, delta_pct, direction}]. Panel shows: Biryani area avg up 18pct vs last week. Zero new Swiggy API calls - just persisting what we already fetch. SUPERSEDED 2026-07-06 -- P6-MI11 achieved the same trend-view outcome by reading directly from stored PlanningRun.final_response on feature/swiggy-market-intel-extended; the dedicated market_snapshots table this task specified was never built.</t>
+        </is>
+      </c>
+      <c r="F50" s="73" t="inlineStr">
         <is>
           <t>feat: competitor price trend tracking — persist snapshots, week-over-week delta</t>
         </is>
       </c>
-      <c r="G50" s="57" t="inlineStr">
+      <c r="G50" s="73" t="inlineStr">
         <is>
           <t>docs/DATA_MODEL.md (market_snapshots table), docs/AGENTS.md</t>
         </is>
       </c>
-      <c r="H50" s="54" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I50" s="56" t="inlineStr">
+      <c r="H50" s="74" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="I50" s="72" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J50" s="56" t="n"/>
-      <c r="K50" s="56" t="n"/>
-      <c r="L50" s="56" t="n"/>
-      <c r="M50" s="58" t="n">
+      <c r="J50" s="72" t="n"/>
+      <c r="K50" s="72" t="n"/>
+      <c r="L50" s="72" t="n"/>
+      <c r="M50" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="N50" s="57" t="n"/>
-      <c r="O50" s="57" t="n"/>
+      <c r="N50" s="73" t="n"/>
+      <c r="O50" s="73" t="n"/>
     </row>
     <row r="51" ht="52.05" customHeight="1" s="77">
-      <c r="A51" s="52" t="inlineStr">
+      <c r="A51" s="72" t="inlineStr">
         <is>
           <t>P6-MI03</t>
         </is>
       </c>
-      <c r="B51" s="53" t="n"/>
-      <c r="C51" s="53" t="inlineStr">
+      <c r="B51" s="73" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-extended</t>
+        </is>
+      </c>
+      <c r="C51" s="73" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D51" s="53" t="inlineStr">
+      <c r="D51" s="73" t="inlineStr">
         <is>
           <t>Category-level pricing analysis</t>
         </is>
       </c>
-      <c r="E51" s="53" t="inlineStr">
-        <is>
-          <t>CompetitorEnricher currently returns flat dish-&gt;price dict. Extend to group by inferred category (biryani/starters/mains/drinks). Compute area avg per category. Compare against restaurant menu categories. Output: [{category, your_avg, area_avg, diff_pct, verdict}]. menu_intelligence prompt gains: Your North Indian mains avg Rs.320 vs area Rs.275 (+16pct). Your starters Rs.180 vs area Rs.210 (-14pct underpriced). No new API calls - aggregation on existing CompetitorEnricher output.</t>
-        </is>
-      </c>
-      <c r="F51" s="53" t="inlineStr">
+      <c r="E51" s="73" t="inlineStr">
+        <is>
+          <t>CompetitorEnricher currently returns flat dish-&gt;price dict. Extend to group by inferred category (biryani/starters/mains/drinks). Compute area avg per category. Compare against restaurant menu categories. Output: [{category, your_avg, area_avg, diff_pct, verdict}]. menu_intelligence prompt gains: Your North Indian mains avg Rs.320 vs area Rs.275 (+16pct). Your starters Rs.180 vs area Rs.210 (-14pct underpriced). No new API calls - aggregation on existing CompetitorEnricher output. SUPERSEDED 2026-07-06 -- delivered (and extended with named cheapest/priciest dishes) as part of P6-MI12 on feature/swiggy-market-intel-extended; never built as its own separate task.</t>
+        </is>
+      </c>
+      <c r="F51" s="73" t="inlineStr">
         <is>
           <t>feat: category-level pricing — group competitor prices by category vs your menu</t>
         </is>
       </c>
-      <c r="G51" s="53" t="inlineStr">
+      <c r="G51" s="73" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (CompetitorEnricher output extended)</t>
         </is>
       </c>
-      <c r="H51" s="54" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I51" s="52" t="inlineStr">
+      <c r="H51" s="74" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="I51" s="72" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J51" s="52" t="n"/>
-      <c r="K51" s="52" t="n"/>
-      <c r="L51" s="52" t="n"/>
-      <c r="M51" s="55" t="n">
+      <c r="J51" s="72" t="n"/>
+      <c r="K51" s="72" t="n"/>
+      <c r="L51" s="72" t="n"/>
+      <c r="M51" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="N51" s="53" t="n"/>
-      <c r="O51" s="53" t="n"/>
+      <c r="N51" s="73" t="n"/>
+      <c r="O51" s="73" t="n"/>
     </row>
     <row r="52" ht="52.05" customHeight="1" s="77">
       <c r="A52" s="56" t="inlineStr">
@@ -16655,7 +16663,7 @@
       </c>
       <c r="B57" s="44" t="inlineStr">
         <is>
-          <t>feature/pricing-impact-model</t>
+          <t>feature/swiggy-market-intel-extended</t>
         </is>
       </c>
       <c r="C57" s="44" t="inlineStr">
@@ -16726,7 +16734,7 @@
       </c>
       <c r="B58" s="44" t="inlineStr">
         <is>
-          <t>feature/scenario-recommendation</t>
+          <t>feature/swiggy-market-intel-extended</t>
         </is>
       </c>
       <c r="C58" s="44" t="inlineStr">
@@ -16797,7 +16805,7 @@
       </c>
       <c r="B59" s="44" t="inlineStr">
         <is>
-          <t>feature/trend-analytics</t>
+          <t>feature/swiggy-market-intel-extended</t>
         </is>
       </c>
       <c r="C59" s="44" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -145,6 +145,7 @@
       <color rgb="FF1A1A18"/>
       <sz val="10"/>
     </font>
+    <font/>
   </fonts>
   <fills count="31">
     <fill>
@@ -301,7 +302,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -397,11 +398,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D1C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D1C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D1C7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D1C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D1C7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD3D1C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -693,6 +728,9 @@
     <xf numFmtId="0" fontId="15" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13228,7 +13266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="77" min="1" max="1"/>
@@ -13250,7 +13288,7 @@
     <row r="1" ht="36" customHeight="1" s="77">
       <c r="A1" s="102" t="inlineStr">
         <is>
-          <t>CortexKitchen — Phase 6 (41 complete · planned in priority order · staging blocked at bottom)</t>
+          <t>CortexKitchen — Phase 6 (55 complete, grouped by feature branch — planned below, staging blocked at bottom)</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13372,7 @@
     <row r="3" ht="18" customHeight="1" s="77">
       <c r="A3" s="83" t="inlineStr">
         <is>
-          <t>COMPLETED — 41 tasks done</t>
+          <t>COMPLETED (incl. superseded, folded into the branch that delivered them) — 55 tasks</t>
         </is>
       </c>
       <c r="B3" s="86" t="n"/>
@@ -13424,37 +13462,37 @@
       </c>
     </row>
     <row r="5" ht="52.05" customHeight="1" s="77">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>P6-S02</t>
         </is>
       </c>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>feature/assumption-diffing</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>Cross-agent assumption diffing</t>
         </is>
       </c>
-      <c r="E5" s="49" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>4 domain nodes write assumptions dicts. EvaluationSanityChecker._diff_assumptions() runs 3 cross-diffs post fan-out. stale_assumptions injected into critic prompt + returned in API. final_assembler bug fix. 9 docs updated.</t>
         </is>
       </c>
-      <c r="F5" s="49" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>feat: cross-agent assumption diffing — O(N²) → O(N)</t>
         </is>
       </c>
-      <c r="G5" s="49" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>9 docs updated</t>
         </is>
@@ -13464,31 +13502,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I5" s="48" t="inlineStr">
+      <c r="I5" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J5" s="48" t="inlineStr">
+      <c r="J5" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K5" s="50" t="n">
+      <c r="K5" s="46" t="n">
         <v>46199</v>
       </c>
-      <c r="L5" s="50" t="n">
+      <c r="L5" s="46" t="n">
         <v>46199</v>
       </c>
-      <c r="M5" s="51" t="n">
+      <c r="M5" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N5" s="49" t="inlineStr">
+      <c r="N5" s="44" t="inlineStr">
         <is>
           <t>P6-S01</t>
         </is>
       </c>
-      <c r="O5" s="49" t="inlineStr">
+      <c r="O5" s="44" t="inlineStr">
         <is>
           <t>Existing sanity checker tests pass; stale_assumptions in API response</t>
         </is>
@@ -13566,37 +13604,37 @@
       </c>
     </row>
     <row r="7" ht="52.05" customHeight="1" s="77">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>P6-S04</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>feature/swiggy-base-connector</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
         <is>
           <t>Integrations</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="44" t="inlineStr">
         <is>
           <t>BaseConnector + SwiggyMCPClient</t>
         </is>
       </c>
-      <c r="E7" s="49" t="inlineStr">
+      <c r="E7" s="44" t="inlineStr">
         <is>
           <t>Abstract BaseConnector ABC with sync() and enrich() methods. SwiggyMCPClient: per-org OAuth token (5-day TTL, re-auth on 401, encrypted storage), JSON-RPC 2.0 calls to /food + /im + /dineout, exponential backoff retry, is_available() check, structured logging. Absorbs original P6-01.</t>
         </is>
       </c>
-      <c r="F7" s="49" t="inlineStr">
+      <c r="F7" s="44" t="inlineStr">
         <is>
           <t>feat: connector layer — BaseConnector ABC + SwiggyMCPClient with per-org OAuth</t>
         </is>
       </c>
-      <c r="G7" s="49" t="inlineStr">
+      <c r="G7" s="44" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md (connector layer section), docs/DECISIONS.md (D-019), docs/DATA_MODEL.md, CLAUDE.md (new), docs/SWIGGY_INTEGRATION.md</t>
         </is>
@@ -13606,31 +13644,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I7" s="48" t="inlineStr">
+      <c r="I7" s="43" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J7" s="48" t="inlineStr">
+      <c r="J7" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K7" s="50" t="n">
+      <c r="K7" s="46" t="n">
         <v>46200</v>
       </c>
-      <c r="L7" s="50" t="n">
+      <c r="L7" s="46" t="n">
         <v>46200</v>
       </c>
-      <c r="M7" s="51" t="n">
+      <c r="M7" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="49" t="inlineStr">
+      <c r="N7" s="44" t="inlineStr">
         <is>
           <t>P6-S03</t>
         </is>
       </c>
-      <c r="O7" s="49" t="inlineStr">
+      <c r="O7" s="44" t="inlineStr">
         <is>
           <t>13/13 pass — test_swiggy_client.py (7): is_available, 401 no-retry, 500 retry x2, success data, never raises, success=false; test_connector_repository.py (6): upsert create, upsert idempotent, get none, error_count increment, error clear on success, list_active filter</t>
         </is>
@@ -13639,10 +13677,10 @@
     <row r="8" ht="52.05" customHeight="1" s="77">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>P6-S05</t>
-        </is>
-      </c>
-      <c r="B8" s="44" t="n"/>
+          <t>P6-S07</t>
+        </is>
+      </c>
+      <c r="B8" s="103" t="n"/>
       <c r="C8" s="44" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -13650,22 +13688,22 @@
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>connectors table + async job queue</t>
+          <t>Redis-backed circuit breaker for SwiggyMCPClient</t>
         </is>
       </c>
       <c r="E8" s="44" t="inlineStr">
         <is>
-          <t>Alembic migration: connectors table (org_id, connector_type, access_token_encrypted, token_expires_at, last_sync_at, sync_status, error_count). Redis job queue for async planning runs (absorbs original P6-02): job_id, status endpoint, dedup by scenario+date, non-blocking HTTP.</t>
+          <t>3 failures in 5 min → circuit opens for 30 min, auto-resets via TTL. On Redis down → fail open (let call through). Per-endpoint circuit keys. Added beyond spec — production resilience for Swiggy MCP calls. Integrated into call_tool() in SwiggyMCPClient.</t>
         </is>
       </c>
       <c r="F8" s="44" t="inlineStr">
         <is>
-          <t>feat: connectors table + async Redis job queue for planning runs</t>
+          <t>feat: Redis circuit breaker for Swiggy MCP calls — 3-failure threshold, 30min open, fail-open on Redis down</t>
         </is>
       </c>
       <c r="G8" s="44" t="inlineStr">
         <is>
-          <t>docs/DATA_MODEL.md (connectors table, orders/reservations/feedback new cols), docs/ARCHITECTURE.md, docs/DECISIONS.md (D-019)</t>
+          <t>docs/ARCHITECTURE.md (circuit breaker section), docs/SWIGGY_INTEGRATION.md</t>
         </is>
       </c>
       <c r="H8" s="45" t="inlineStr">
@@ -13675,7 +13713,7 @@
       </c>
       <c r="I8" s="43" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J8" s="43" t="inlineStr">
@@ -13683,11 +13721,11 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K8" s="46" t="n">
-        <v>46200</v>
-      </c>
-      <c r="L8" s="46" t="n">
-        <v>46200</v>
+      <c r="K8" s="46" t="n"/>
+      <c r="L8" s="46" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
       </c>
       <c r="M8" s="47" t="n">
         <v>1</v>
@@ -13699,115 +13737,111 @@
       </c>
       <c r="O8" s="44" t="inlineStr">
         <is>
+          <t>Circuit opens after 3 failures; auto-resets after 30min; fail-open when Redis unavailable; call_tool() returns None immediately when circuit open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52.05" customHeight="1" s="77">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>P6-S05</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>connectors table + async job queue</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>Alembic migration: connectors table (org_id, connector_type, access_token_encrypted, token_expires_at, last_sync_at, sync_status, error_count). Redis job queue for async planning runs (absorbs original P6-02): job_id, status endpoint, dedup by scenario+date, non-blocking HTTP.</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>feat: connectors table + async Redis job queue for planning runs</t>
+        </is>
+      </c>
+      <c r="G9" s="44" t="inlineStr">
+        <is>
+          <t>docs/DATA_MODEL.md (connectors table, orders/reservations/feedback new cols), docs/ARCHITECTURE.md, docs/DECISIONS.md (D-019)</t>
+        </is>
+      </c>
+      <c r="H9" s="45" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I9" s="43" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J9" s="43" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K9" s="46" t="n">
+        <v>46200</v>
+      </c>
+      <c r="L9" s="46" t="n">
+        <v>46200</v>
+      </c>
+      <c r="M9" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="44" t="inlineStr">
+        <is>
+          <t>P6-S04</t>
+        </is>
+      </c>
+      <c r="O9" s="44" t="inlineStr">
+        <is>
           <t>Migration smoke test (alembic upgrade head verified live on DB); connectors table + all new cols confirmed via psycopg2; swiggy_delivery enum value present</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="52.05" customHeight="1" s="77">
-      <c r="A9" s="48" t="inlineStr">
-        <is>
-          <t>P6-S06</t>
-        </is>
-      </c>
-      <c r="B9" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-sync-orders</t>
-        </is>
-      </c>
-      <c r="C9" s="49" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="D9" s="49" t="inlineStr">
-        <is>
-          <t>Sync Swiggy orders → orders table</t>
-        </is>
-      </c>
-      <c r="E9" s="49" t="inlineStr">
-        <is>
-          <t>Completed — NOTE: syncs PERSONAL consumer orders (your Swiggy food deliveries), NOT a restaurant incoming orders. Swiggy MCP is consumer-facing. Restaurant order data needs Swiggy Partner API. Sync infrastructure built but data is not meaningful for restaurant planning nodes.</t>
-        </is>
-      </c>
-      <c r="F9" s="49" t="inlineStr">
-        <is>
-          <t>feat: swiggy order sync — get_food_orders nightly → orders table (source=swiggy, channel=delivery)</t>
-        </is>
-      </c>
-      <c r="G9" s="49" t="inlineStr">
-        <is>
-          <t>docs/SWIGGY_INTEGRATION.md (P6-S06 ✅, status header updated)</t>
-        </is>
-      </c>
-      <c r="H9" s="45" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I9" s="48" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J9" s="48" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K9" s="50" t="n">
-        <v>46200</v>
-      </c>
-      <c r="L9" s="50" t="n">
-        <v>46200</v>
-      </c>
-      <c r="M9" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="49" t="inlineStr">
-        <is>
-          <t>P6-S05</t>
-        </is>
-      </c>
-      <c r="O9" s="49" t="inlineStr">
-        <is>
-          <t>8/8 pass — correct count, correct Order fields (source/channel/is_delivery), placeholder MenuItem creation (is_available=False, category=swiggy_import), reuse existing MenuItem by name, idempotency on duplicate sync, None call_tool graceful, empty order list, external_order_id format SW-001_0/SW-001_1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52.05" customHeight="1" s="77">
       <c r="A10" s="43" t="inlineStr">
         <is>
-          <t>P6-S07</t>
+          <t>P6-S06</t>
         </is>
       </c>
       <c r="B10" s="44" t="inlineStr">
         <is>
-          <t>feature/swiggy-base-connector</t>
+          <t>feature/swiggy-sync-orders</t>
         </is>
       </c>
       <c r="C10" s="44" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Integrations</t>
         </is>
       </c>
       <c r="D10" s="44" t="inlineStr">
         <is>
-          <t>Redis-backed circuit breaker for SwiggyMCPClient</t>
+          <t>Sync Swiggy orders → orders table</t>
         </is>
       </c>
       <c r="E10" s="44" t="inlineStr">
         <is>
-          <t>3 failures in 5 min → circuit opens for 30 min, auto-resets via TTL. On Redis down → fail open (let call through). Per-endpoint circuit keys. Added beyond spec — production resilience for Swiggy MCP calls. Integrated into call_tool() in SwiggyMCPClient.</t>
+          <t>Completed — NOTE: syncs PERSONAL consumer orders (your Swiggy food deliveries), NOT a restaurant incoming orders. Swiggy MCP is consumer-facing. Restaurant order data needs Swiggy Partner API. Sync infrastructure built but data is not meaningful for restaurant planning nodes.</t>
         </is>
       </c>
       <c r="F10" s="44" t="inlineStr">
         <is>
-          <t>feat: Redis circuit breaker for Swiggy MCP calls — 3-failure threshold, 30min open, fail-open on Redis down</t>
+          <t>feat: swiggy order sync — get_food_orders nightly → orders table (source=swiggy, channel=delivery)</t>
         </is>
       </c>
       <c r="G10" s="44" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE.md (circuit breaker section), docs/SWIGGY_INTEGRATION.md</t>
+          <t>docs/SWIGGY_INTEGRATION.md (P6-S06 ✅, status header updated)</t>
         </is>
       </c>
       <c r="H10" s="45" t="inlineStr">
@@ -13825,54 +13859,54 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K10" s="43" t="n"/>
-      <c r="L10" s="43" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
+      <c r="K10" s="46" t="n">
+        <v>46200</v>
+      </c>
+      <c r="L10" s="46" t="n">
+        <v>46200</v>
       </c>
       <c r="M10" s="47" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="44" t="inlineStr">
         <is>
-          <t>P6-S04</t>
+          <t>P6-S05</t>
         </is>
       </c>
       <c r="O10" s="44" t="inlineStr">
         <is>
-          <t>Circuit opens after 3 failures; auto-resets after 30min; fail-open when Redis unavailable; call_tool() returns None immediately when circuit open</t>
+          <t>8/8 pass — correct count, correct Order fields (source/channel/is_delivery), placeholder MenuItem creation (is_available=False, category=swiggy_import), reuse existing MenuItem by name, idempotency on duplicate sync, None call_tool graceful, empty order list, external_order_id format SW-001_0/SW-001_1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52.05" customHeight="1" s="77">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>P6-S08</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n"/>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="44" t="inlineStr">
         <is>
           <t>Capability-to-provider registry</t>
         </is>
       </c>
-      <c r="E11" s="49" t="inlineStr">
+      <c r="E11" s="44" t="inlineStr">
         <is>
           <t>Maps planning capabilities to ordered provider lists: competitor_pricing → [swiggy, zomato], reservation_data → [swiggy, eazydiner], procurement → [swiggy], order_history → [swiggy, zomato]. Routes to highest-priority provider with active connector row for the org. Adding Zomato = 1 new connector file + 1 registry entry. No DB migration needed — reads from connectors table.</t>
         </is>
       </c>
-      <c r="F11" s="49" t="inlineStr">
+      <c r="F11" s="44" t="inlineStr">
         <is>
           <t>feat: ProviderRegistry — capability routing with multi-provider fallback, future Zomato/EazyDiner-ready</t>
         </is>
       </c>
-      <c r="G11" s="49" t="inlineStr">
+      <c r="G11" s="44" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md (provider registry section), docs/CONNECTORS.md</t>
         </is>
@@ -13882,31 +13916,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I11" s="48" t="inlineStr">
+      <c r="I11" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J11" s="48" t="inlineStr">
+      <c r="J11" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K11" s="48" t="n"/>
-      <c r="L11" s="48" t="inlineStr">
+      <c r="K11" s="46" t="n"/>
+      <c r="L11" s="46" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="M11" s="51" t="n">
+      <c r="M11" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N11" s="49" t="inlineStr">
+      <c r="N11" s="44" t="inlineStr">
         <is>
           <t>P6-S05</t>
         </is>
       </c>
-      <c r="O11" s="49" t="inlineStr">
+      <c r="O11" s="44" t="inlineStr">
         <is>
           <t>competitor_pricing routes to swiggy when active; routes to zomato when swiggy connector missing; list_active used to determine available providers</t>
         </is>
@@ -13984,37 +14018,37 @@
       </c>
     </row>
     <row r="13" ht="52.05" customHeight="1" s="77">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>P6-S10</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>feature/swiggy-sync-feedback-reservations</t>
         </is>
       </c>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="44" t="inlineStr">
         <is>
           <t>Integrations</t>
         </is>
       </c>
-      <c r="D13" s="49" t="inlineStr">
+      <c r="D13" s="44" t="inlineStr">
         <is>
           <t>Reservation sync skeleton → reservations table</t>
         </is>
       </c>
-      <c r="E13" s="49" t="inlineStr">
+      <c r="E13" s="44" t="inlineStr">
         <is>
           <t>Completed — NOTE: syncs PERSONAL Dineout reservations (tables you booked at other restaurants), NOT your restaurant table bookings. Infrastructure built; data not useful for reservation planning node.</t>
         </is>
       </c>
-      <c r="F13" s="49" t="inlineStr">
+      <c r="F13" s="44" t="inlineStr">
         <is>
           <t>feat: reservation sync skeleton — get_booking_status → reservations table, register_booking_order_id for DineoutExecutor (P6-S44)</t>
         </is>
       </c>
-      <c r="G13" s="49" t="inlineStr">
+      <c r="G13" s="44" t="inlineStr">
         <is>
           <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md (schemas), docs/APIS.md (connectors endpoints)</t>
         </is>
@@ -14024,31 +14058,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I13" s="48" t="inlineStr">
+      <c r="I13" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J13" s="48" t="inlineStr">
+      <c r="J13" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="K13" s="46" t="n">
         <v>46202</v>
       </c>
-      <c r="L13" s="50" t="n">
+      <c r="L13" s="46" t="n">
         <v>46202</v>
       </c>
-      <c r="M13" s="51" t="n">
+      <c r="M13" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="49" t="inlineStr">
+      <c r="N13" s="44" t="inlineStr">
         <is>
           <t>P6-S09</t>
         </is>
       </c>
-      <c r="O13" s="49" t="inlineStr">
+      <c r="O13" s="44" t="inlineStr">
         <is>
           <t>test_swiggy_reservation_sync.py (5 tests)</t>
         </is>
@@ -14122,37 +14156,37 @@
       </c>
     </row>
     <row r="15" ht="52.05" customHeight="1" s="77">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>P6-S12</t>
         </is>
       </c>
-      <c r="B15" s="49" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>feature/swiggy-market-intel-enrichers</t>
         </is>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D15" s="49" t="inlineStr">
+      <c r="D15" s="44" t="inlineStr">
         <is>
           <t>CompetitorEnricher — Food MCP</t>
         </is>
       </c>
-      <c r="E15" s="49" t="inlineStr">
+      <c r="E15" s="44" t="inlineStr">
         <is>
           <t>Create enrichers/competitor.py. get_addresses → addressId. search_restaurants (cuisine, addressId) → filter OPEN → search_menu + get_restaurant_menu per restaurant (max 3). Build competitor_pricing dict: area avg price per dish category, pricing_alerts vs your menu. Redis cache 30min TTL. Inject into menu_intel node prompt as ## Market Context section.</t>
         </is>
       </c>
-      <c r="F15" s="49" t="inlineStr">
+      <c r="F15" s="44" t="inlineStr">
         <is>
           <t>feat: CompetitorEnricher — live competitor pricing via Food MCP</t>
         </is>
       </c>
-      <c r="G15" s="49" t="inlineStr">
+      <c r="G15" s="44" t="inlineStr">
         <is>
           <t>get_addresses, search_restaurants, search_menu, get_restaurant_menu</t>
         </is>
@@ -14162,31 +14196,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I15" s="48" t="inlineStr">
+      <c r="I15" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J15" s="48" t="inlineStr">
+      <c r="J15" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K15" s="50" t="n">
+      <c r="K15" s="46" t="n">
         <v>46203</v>
       </c>
-      <c r="L15" s="50" t="n">
+      <c r="L15" s="46" t="n">
         <v>46203</v>
       </c>
-      <c r="M15" s="51" t="n">
+      <c r="M15" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="49" t="inlineStr">
+      <c r="N15" s="44" t="inlineStr">
         <is>
           <t>P6-S10</t>
         </is>
       </c>
-      <c r="O15" s="49" t="inlineStr">
+      <c r="O15" s="44" t="inlineStr">
         <is>
           <t>NEEDS: OAuth token. All read-only — works on production endpoint.</t>
         </is>
@@ -14239,7 +14273,7 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K16" s="43" t="n"/>
+      <c r="K16" s="46" t="n"/>
       <c r="L16" s="46" t="n">
         <v>46203</v>
       </c>
@@ -14258,33 +14292,33 @@
       </c>
     </row>
     <row r="17" ht="52.05" customHeight="1" s="77">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>P6-S14</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n"/>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D17" s="49" t="inlineStr">
+      <c r="D17" s="44" t="inlineStr">
         <is>
           <t>ProcurementEnricher — Instamart MCP</t>
         </is>
       </c>
-      <c r="E17" s="49" t="inlineStr">
+      <c r="E17" s="44" t="inlineStr">
         <is>
           <t>Create enrichers/procurement.py. search_products (per shortage item, max 5 calls/run) + your_go_to_items (frequent reorders). Output: [{ingredient, spinId, price, unit, inStock}]. spinId MUST persist in OrchestratorState — required for Instamart checkout in P6-S43. Redis cache 30 min. Returns None on any failure; inventory node falls back to its own analysis.</t>
         </is>
       </c>
-      <c r="F17" s="49" t="inlineStr">
+      <c r="F17" s="44" t="inlineStr">
         <is>
           <t>feat: ProcurementEnricher — live Instamart prices + spinIds injected into inventory node</t>
         </is>
       </c>
-      <c r="G17" s="49" t="inlineStr">
+      <c r="G17" s="44" t="inlineStr">
         <is>
           <t>docs/SWIGGY_INTEGRATION.md (P6-S14 section)</t>
         </is>
@@ -14294,29 +14328,29 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I17" s="48" t="inlineStr">
+      <c r="I17" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J17" s="48" t="inlineStr">
+      <c r="J17" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K17" s="48" t="n"/>
-      <c r="L17" s="50" t="n">
+      <c r="K17" s="46" t="n"/>
+      <c r="L17" s="46" t="n">
         <v>46203</v>
       </c>
-      <c r="M17" s="51" t="n">
+      <c r="M17" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="49" t="inlineStr">
+      <c r="N17" s="44" t="inlineStr">
         <is>
           <t>P6-S13</t>
         </is>
       </c>
-      <c r="O17" s="49" t="inlineStr">
+      <c r="O17" s="44" t="inlineStr">
         <is>
           <t>NEEDS: OAuth token (read-only). Returns None on client failure; correct procurement_options on success; spinId present in each item; Redis caches result; max 5 search_products calls per run enforced.</t>
         </is>
@@ -14394,33 +14428,33 @@
       </c>
     </row>
     <row r="19" ht="52.05" customHeight="1" s="77">
-      <c r="A19" s="48" t="inlineStr">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>P6-S16</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="inlineStr">
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D19" s="49" t="inlineStr">
+      <c r="D19" s="44" t="inlineStr">
         <is>
           <t>market_intel_node — 10th LangGraph node</t>
         </is>
       </c>
-      <c r="E19" s="49" t="inlineStr">
+      <c r="E19" s="44" t="inlineStr">
         <is>
           <t>New parallel domain node. Runs CompetitorEnricher + OccupancyEnricher. Outputs market_intel_output: competitor_pricing, area_occupancy, pricing_alerts. Writes market_assumptions dict. Participates in assumption diffing. Critic receives market context. Supersedes original P6-06.</t>
         </is>
       </c>
-      <c r="F19" s="49" t="inlineStr">
+      <c r="F19" s="44" t="inlineStr">
         <is>
           <t>feat: market_intel_node — 10th parallel LangGraph node, Swiggy-powered market awareness</t>
         </is>
       </c>
-      <c r="G19" s="49" t="inlineStr">
+      <c r="G19" s="44" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (market_intel_node section), docs/ARCHITECTURE.md (11-node pipeline), docs/DECISIONS.md (D-020)</t>
         </is>
@@ -14430,31 +14464,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I19" s="48" t="inlineStr">
+      <c r="I19" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J19" s="48" t="inlineStr">
+      <c r="J19" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K19" s="50" t="n">
+      <c r="K19" s="46" t="n">
         <v>46204</v>
       </c>
-      <c r="L19" s="50" t="n">
+      <c r="L19" s="46" t="n">
         <v>46204</v>
       </c>
-      <c r="M19" s="51" t="n">
+      <c r="M19" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="49" t="inlineStr">
+      <c r="N19" s="44" t="inlineStr">
         <is>
           <t>P6-S15</t>
         </is>
       </c>
-      <c r="O19" s="49" t="inlineStr">
+      <c r="O19" s="44" t="inlineStr">
         <is>
           <t>Node writes market_intel_output + market_assumptions; parallel verified; assumption diffing fires; LangSmith trace shows node</t>
         </is>
@@ -14528,33 +14562,33 @@
       </c>
     </row>
     <row r="21" ht="52.05" customHeight="1" s="77">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>P6-S18</t>
         </is>
       </c>
-      <c r="B21" s="49" t="n"/>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="B21" s="44" t="n"/>
+      <c r="C21" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D21" s="49" t="inlineStr">
+      <c r="D21" s="44" t="inlineStr">
         <is>
           <t>Assumption diffs 5 + 6 for new nodes</t>
         </is>
       </c>
-      <c r="E21" s="49" t="inlineStr">
+      <c r="E21" s="44" t="inlineStr">
         <is>
           <t>Diff 5: market_intel assumed_competitor_avg_price vs menu_intel items_assumed_available pricing. Diff 6: dineout_manager assumed_dineout_slots_low vs reservation assumed_peak_occupancy. Extends P6-S02. Total now 5 active diffs.</t>
         </is>
       </c>
-      <c r="F21" s="49" t="inlineStr">
+      <c r="F21" s="44" t="inlineStr">
         <is>
           <t>feat: assumption diffs 5+6 — market vs menu pricing, dineout slots vs reservation occupancy</t>
         </is>
       </c>
-      <c r="G21" s="49" t="inlineStr">
+      <c r="G21" s="44" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md (sanity checker updated), docs/AGENTS.md</t>
         </is>
@@ -14564,31 +14598,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I21" s="48" t="inlineStr">
+      <c r="I21" s="43" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J21" s="48" t="inlineStr">
+      <c r="J21" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K21" s="50" t="n">
+      <c r="K21" s="46" t="n">
         <v>46204</v>
       </c>
-      <c r="L21" s="50" t="n">
+      <c r="L21" s="46" t="n">
         <v>46204</v>
       </c>
-      <c r="M21" s="51" t="n">
+      <c r="M21" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="49" t="inlineStr">
+      <c r="N21" s="44" t="inlineStr">
         <is>
           <t>P6-S16, P6-S17</t>
         </is>
       </c>
-      <c r="O21" s="49" t="inlineStr">
+      <c r="O21" s="44" t="inlineStr">
         <is>
           <t>Diff 5 + 6 fire correctly; existing 3 diffs unaffected; stale_assumptions includes new conflicts</t>
         </is>
@@ -14666,37 +14700,37 @@
       </c>
     </row>
     <row r="23" ht="52.05" customHeight="1" s="77">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="43" t="inlineStr">
         <is>
           <t>P6-F01</t>
         </is>
       </c>
-      <c r="B23" s="49" t="inlineStr">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>feature/swiggy-connectors-ui</t>
         </is>
       </c>
-      <c r="C23" s="49" t="inlineStr">
+      <c r="C23" s="44" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D23" s="49" t="inlineStr">
+      <c r="D23" s="44" t="inlineStr">
         <is>
           <t>/connectors page — data source management</t>
         </is>
       </c>
-      <c r="E23" s="49" t="inlineStr">
+      <c r="E23" s="44" t="inlineStr">
         <is>
           <t>New route /connectors. Lists connectors with status badges (Connected/Disconnected/Error). Shows last sync time, records synced, data freshness. Connect button triggers OAuth flow. Disconnect revokes token. Error state shows last error + reconnect. Works for Swiggy + future POS connector.</t>
         </is>
       </c>
-      <c r="F23" s="49" t="inlineStr">
+      <c r="F23" s="44" t="inlineStr">
         <is>
           <t>feat: /connectors page — platform data source management with OAuth connect flow</t>
         </is>
       </c>
-      <c r="G23" s="49" t="inlineStr">
+      <c r="G23" s="44" t="inlineStr">
         <is>
           <t>None (frontend only)</t>
         </is>
@@ -14706,31 +14740,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I23" s="48" t="inlineStr">
+      <c r="I23" s="43" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J23" s="48" t="inlineStr">
+      <c r="J23" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K23" s="48" t="n"/>
-      <c r="L23" s="48" t="inlineStr">
+      <c r="K23" s="46" t="n"/>
+      <c r="L23" s="46" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="M23" s="51" t="n">
+      <c r="M23" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="49" t="inlineStr">
+      <c r="N23" s="44" t="inlineStr">
         <is>
           <t>P6-S04</t>
         </is>
       </c>
-      <c r="O23" s="49" t="inlineStr">
+      <c r="O23" s="44" t="inlineStr">
         <is>
           <t>Can build now — reads from connectors table (already exists via P6-S05)</t>
         </is>
@@ -14783,8 +14817,8 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K24" s="43" t="n"/>
-      <c r="L24" s="43" t="inlineStr">
+      <c r="K24" s="46" t="n"/>
+      <c r="L24" s="46" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
@@ -14804,33 +14838,33 @@
       </c>
     </row>
     <row r="25" ht="52.05" customHeight="1" s="77">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="A25" s="43" t="inlineStr">
         <is>
           <t>P6-F03</t>
         </is>
       </c>
-      <c r="B25" s="49" t="n"/>
-      <c r="C25" s="49" t="inlineStr">
+      <c r="B25" s="44" t="n"/>
+      <c r="C25" s="44" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D25" s="49" t="inlineStr">
+      <c r="D25" s="44" t="inlineStr">
         <is>
           <t>Backend bug fixes for Swiggy UI features</t>
         </is>
       </c>
-      <c r="E25" s="49" t="inlineStr">
+      <c r="E25" s="44" t="inlineStr">
         <is>
           <t>Three backend fixes: (1) final_assembler.py was not including Swiggy state fields in API response (market_intel_output, swiggy_competitor/occupancy_context, swiggy_procurement_options, dineout_manager_output) — frontend Market Intel panel was always empty. (2) connector_repository.update_sync_status silently dropped updates when no DB row existed — fixed to auto-create connector row so last_sync_at always persists. (3) main.py ConsoleSpanExporter flooding backend logs with JSON on every request — removed BatchSpanProcessor(ConsoleSpanExporter()) line.</t>
         </is>
       </c>
-      <c r="F25" s="49" t="inlineStr">
+      <c r="F25" s="44" t="inlineStr">
         <is>
           <t>fix: final_assembler Swiggy fields, connector auto-create, silence OTel console exporter</t>
         </is>
       </c>
-      <c r="G25" s="49" t="inlineStr">
+      <c r="G25" s="44" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -14840,19 +14874,19 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I25" s="48" t="inlineStr">
+      <c r="I25" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J25" s="48" t="n"/>
-      <c r="K25" s="48" t="n"/>
-      <c r="L25" s="48" t="n"/>
-      <c r="M25" s="51" t="n">
+      <c r="J25" s="43" t="n"/>
+      <c r="K25" s="46" t="n"/>
+      <c r="L25" s="46" t="n"/>
+      <c r="M25" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="49" t="n"/>
-      <c r="O25" s="49" t="n"/>
+      <c r="N25" s="44" t="n"/>
+      <c r="O25" s="44" t="n"/>
     </row>
     <row r="26" ht="52.05" customHeight="1" s="77">
       <c r="A26" s="43" t="inlineStr">
@@ -14897,8 +14931,8 @@
         </is>
       </c>
       <c r="J26" s="43" t="n"/>
-      <c r="K26" s="43" t="n"/>
-      <c r="L26" s="43" t="n"/>
+      <c r="K26" s="46" t="n"/>
+      <c r="L26" s="46" t="n"/>
       <c r="M26" s="47" t="n">
         <v>0</v>
       </c>
@@ -14906,33 +14940,33 @@
       <c r="O26" s="44" t="n"/>
     </row>
     <row r="27" ht="52.05" customHeight="1" s="77">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>P6-F05</t>
         </is>
       </c>
-      <c r="B27" s="49" t="n"/>
-      <c r="C27" s="49" t="inlineStr">
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="44" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D27" s="49" t="inlineStr">
+      <c r="D27" s="44" t="inlineStr">
         <is>
           <t>Market intelligence panel (planning results page)</t>
         </is>
       </c>
-      <c r="E27" s="49" t="inlineStr">
+      <c r="E27" s="44" t="inlineStr">
         <is>
           <t>New panel on /runs/{id}. Competitor pricing table: your price vs area avg vs cheapest competitor per dish category. Area occupancy badge (HIGH/MEDIUM/LOW). Instamart prices for shortage items. Pricing alerts (red if &gt;20% above area avg). Hidden when market_intel_output absent.</t>
         </is>
       </c>
-      <c r="F27" s="49" t="inlineStr">
+      <c r="F27" s="44" t="inlineStr">
         <is>
           <t>feat: market intelligence panel — competitor pricing + area occupancy on planning results</t>
         </is>
       </c>
-      <c r="G27" s="49" t="inlineStr">
+      <c r="G27" s="44" t="inlineStr">
         <is>
           <t>None (frontend only)</t>
         </is>
@@ -14942,31 +14976,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I27" s="48" t="inlineStr">
+      <c r="I27" s="43" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J27" s="48" t="inlineStr">
+      <c r="J27" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K27" s="48" t="n"/>
-      <c r="L27" s="48" t="inlineStr">
+      <c r="K27" s="46" t="n"/>
+      <c r="L27" s="46" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="M27" s="51" t="n">
+      <c r="M27" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="N27" s="49" t="inlineStr">
+      <c r="N27" s="44" t="inlineStr">
         <is>
           <t>P6-S15</t>
         </is>
       </c>
-      <c r="O27" s="49" t="inlineStr">
+      <c r="O27" s="44" t="inlineStr">
         <is>
           <t>Depends on P6-S16 (market_intel_output in plan API response)</t>
         </is>
@@ -15019,8 +15053,8 @@
         </is>
       </c>
       <c r="J28" s="43" t="n"/>
-      <c r="K28" s="43" t="n"/>
-      <c r="L28" s="43" t="n"/>
+      <c r="K28" s="46" t="n"/>
+      <c r="L28" s="46" t="n"/>
       <c r="M28" s="47" t="n">
         <v>0</v>
       </c>
@@ -15028,37 +15062,37 @@
       <c r="O28" s="44" t="n"/>
     </row>
     <row r="29" ht="52.05" customHeight="1" s="77">
-      <c r="A29" s="48" t="inlineStr">
+      <c r="A29" s="43" t="inlineStr">
         <is>
           <t>P6-S21</t>
         </is>
       </c>
-      <c r="B29" s="49" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>fix/swiggy-sse-market-intel</t>
         </is>
       </c>
-      <c r="C29" s="49" t="inlineStr">
+      <c r="C29" s="44" t="inlineStr">
         <is>
           <t>Reliability</t>
         </is>
       </c>
-      <c r="D29" s="49" t="inlineStr">
+      <c r="D29" s="44" t="inlineStr">
         <is>
           <t>Swiggy dashboard data-integrity fixes</t>
         </is>
       </c>
-      <c r="E29" s="49" t="inlineStr">
+      <c r="E29" s="44" t="inlineStr">
         <is>
           <t>Fixed Instamart procurement card rendering nothing despite live shortage data: frontend read item.name/item.in_stock but backend ProcurementEnricher sends item.ingredient/item.inStock (confirmed against the enricher's own test contract). Found and fixed a cost/token-attribution race: reservation and inventory nodes share the 'fast' LLM tier and run in true parallel; _inject() draining the shared provider usage buffer at node start/end let one node's drain steal the other's usage records. Fixed via per-node contextvar tagging (bind_llm_usage_node/drain_usage(node=...)) in llm/base.py + graph.py. Converted ~11 files across the Swiggy integration layer + cache/vector-memory infra from stdlib logging to structlog -- the app never calls logging.basicConfig(), so every .info()/.debug() call on those modules was being silently dropped, and .warning() lines printed unstructured with no run correlation. Merged to dev via PR #87, 2026-07-03.</t>
         </is>
       </c>
-      <c r="F29" s="49" t="inlineStr">
+      <c r="F29" s="44" t="inlineStr">
         <is>
           <t>fix: Instamart card field mapping, LLM usage attribution race, structlog conversion across Swiggy layer</t>
         </is>
       </c>
-      <c r="G29" s="49" t="inlineStr">
+      <c r="G29" s="44" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -15068,31 +15102,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I29" s="48" t="inlineStr">
+      <c r="I29" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J29" s="48" t="inlineStr">
+      <c r="J29" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K29" s="50" t="n">
+      <c r="K29" s="46" t="n">
         <v>46205</v>
       </c>
-      <c r="L29" s="50" t="n">
+      <c r="L29" s="46" t="n">
         <v>46205</v>
       </c>
-      <c r="M29" s="51" t="n">
+      <c r="M29" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="49" t="inlineStr">
+      <c r="N29" s="44" t="inlineStr">
         <is>
           <t>P6-S20</t>
         </is>
       </c>
-      <c r="O29" s="49" t="inlineStr">
+      <c r="O29" s="44" t="inlineStr">
         <is>
           <t>Verified via isolated LangGraph fan-out concurrency test; 298+ backend tests passing at time of fix</t>
         </is>
@@ -15166,33 +15200,33 @@
       </c>
     </row>
     <row r="31" ht="52.05" customHeight="1" s="77">
-      <c r="A31" s="48" t="inlineStr">
+      <c r="A31" s="43" t="inlineStr">
         <is>
           <t>P6-S23</t>
         </is>
       </c>
-      <c r="B31" s="49" t="n"/>
-      <c r="C31" s="49" t="inlineStr">
+      <c r="B31" s="44" t="n"/>
+      <c r="C31" s="44" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D31" s="49" t="inlineStr">
+      <c r="D31" s="44" t="inlineStr">
         <is>
           <t>Eval/observability CI gate + golden-dataset bug fix</t>
         </is>
       </c>
-      <c r="E31" s="49" t="inlineStr">
+      <c r="E31" s="44" t="inlineStr">
         <is>
           <t>New .github/workflows/backend-tests.yml: unit-tests job runs pytest tests/unit on every push/PR (includes the existing offline golden-set regression gate for free); llm-quality-evals job runs DeepEval + RAGAS (skips cleanly without GROQ_API_KEY, asserts once configured). Built scripts/build_ragas_dataset.py + build_deepeval_dataset.py mirroring build_golden_dataset.py's pattern, producing human-reviewed .candidates.json files -- never auto-merged, ground_truth requires human verification by design. Found and fixed a real bug in build_golden_dataset.py: it read final_response['agents'][...] but final_assembler_node actually writes final_response['recommendations'][...] -- confirmed via the checked-in fixture (all 50 golden runs had has_shortage_alerts=false), meaning the restock_when_shortage evaluator had been silently a no-op since it was written.</t>
         </is>
       </c>
-      <c r="F31" s="49" t="inlineStr">
+      <c r="F31" s="44" t="inlineStr">
         <is>
           <t>feat: CI eval gate, RAGAS/DeepEval dataset-refresh scripts; fix: golden-dataset key-path bug (restock evaluator was a no-op)</t>
         </is>
       </c>
-      <c r="G31" s="49" t="inlineStr">
+      <c r="G31" s="44" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -15202,31 +15236,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I31" s="48" t="inlineStr">
+      <c r="I31" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J31" s="48" t="inlineStr">
+      <c r="J31" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K31" s="50" t="n">
+      <c r="K31" s="46" t="n">
         <v>46205</v>
       </c>
-      <c r="L31" s="50" t="n">
+      <c r="L31" s="46" t="n">
         <v>46205</v>
       </c>
-      <c r="M31" s="51" t="n">
+      <c r="M31" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="49" t="inlineStr">
+      <c r="N31" s="44" t="inlineStr">
         <is>
           <t>P6-S21</t>
         </is>
       </c>
-      <c r="O31" s="49" t="inlineStr">
+      <c r="O31" s="44" t="inlineStr">
         <is>
           <t>6 new tests for build_golden_dataset.py extractors, 10 new tests for the two dataset-refresh scripts, 11 corrected fixtures in test_swiggy_procurement_enricher.py. ACTION NEEDED: add GROQ_API_KEY + LANGSMITH_API_KEY as GitHub repo secrets for llm-quality-evals to assert anything.</t>
         </is>
@@ -15300,33 +15334,33 @@
       </c>
     </row>
     <row r="33" ht="52.05" customHeight="1" s="77">
-      <c r="A33" s="48" t="inlineStr">
+      <c r="A33" s="43" t="inlineStr">
         <is>
           <t>P6-S25</t>
         </is>
       </c>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="49" t="inlineStr">
+      <c r="B33" s="44" t="n"/>
+      <c r="C33" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D33" s="49" t="inlineStr">
+      <c r="D33" s="44" t="inlineStr">
         <is>
           <t>Replan loop convergence fix</t>
         </is>
       </c>
-      <c r="E33" s="49" t="inlineStr">
+      <c r="E33" s="44" t="inlineStr">
         <is>
           <t>replan_orchestrator only ever re-ran the aggregator, never menu_intelligence -- so retries resubmitted the exact same unchanged menu_output to the critic, which correctly rejected it again every time (confirmed via a live run stuck at 3 identical critic rejections, hitting the 2-retry cap on every attempt). Rewired REPLAN_ORCHESTRATOR -&gt; MENU_INTELLIGENCE (was -&gt; AGGREGATOR), threaded replan_context through as prior_feedback into MenuService.analyse_and_recommend() and the prompt. Verified safe under LangGraph's join semantics using the same proven pattern AGGREGATOR's existing dual incoming edges already use.</t>
         </is>
       </c>
-      <c r="F33" s="49" t="inlineStr">
+      <c r="F33" s="44" t="inlineStr">
         <is>
           <t>fix: replan loop now regenerates the plan instead of resubmitting the same one -- critic retries actually converge</t>
         </is>
       </c>
-      <c r="G33" s="49" t="inlineStr">
+      <c r="G33" s="44" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -15336,31 +15370,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I33" s="48" t="inlineStr">
+      <c r="I33" s="43" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J33" s="48" t="inlineStr">
+      <c r="J33" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K33" s="50" t="n">
+      <c r="K33" s="46" t="n">
         <v>46205</v>
       </c>
-      <c r="L33" s="50" t="n">
+      <c r="L33" s="46" t="n">
         <v>46205</v>
       </c>
-      <c r="M33" s="51" t="n">
+      <c r="M33" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="49" t="inlineStr">
+      <c r="N33" s="44" t="inlineStr">
         <is>
           <t>P6-S09</t>
         </is>
       </c>
-      <c r="O33" s="49" t="inlineStr">
+      <c r="O33" s="44" t="inlineStr">
         <is>
           <t>1 new graph-level integration test (test_replan_loop_integration.py) mocking a revision-then-approval cycle and asserting MenuService is called twice with feedback threaded through; live-verified end to end</t>
         </is>
@@ -15434,33 +15468,33 @@
       </c>
     </row>
     <row r="35" ht="52.05" customHeight="1" s="77">
-      <c r="A35" s="48" t="inlineStr">
+      <c r="A35" s="43" t="inlineStr">
         <is>
           <t>P6-S27</t>
         </is>
       </c>
-      <c r="B35" s="49" t="n"/>
-      <c r="C35" s="49" t="inlineStr">
+      <c r="B35" s="44" t="n"/>
+      <c r="C35" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D35" s="49" t="inlineStr">
+      <c r="D35" s="44" t="inlineStr">
         <is>
           <t>Critic assumption-diff override fix</t>
         </is>
       </c>
-      <c r="E35" s="49" t="inlineStr">
+      <c r="E35" s="44" t="inlineStr">
         <is>
           <t>critic_service.py unconditionally force-downgraded approved-&gt;revision (capped score at 0.72) whenever any stale cross-agent assumption existed, regardless of the LLM critic's own judgment. A live run showed the critic explicitly reasoning through a conflict and writing 'Approving with these items noted for the manager's attention' in its own notes, then getting silently overridden to revision anyway by this code (added in an earlier hardening pass adjacent to P6-S02). Removed the automatic verdict override specifically for assumption diffs, kept it for real deterministic policy/sanity-rule violations which should stay non-negotiable. Kept full visibility (feedback, notes, DecisionLog audit trail) -- the critic's own considered judgment is now trusted.</t>
         </is>
       </c>
-      <c r="F35" s="49" t="inlineStr">
+      <c r="F35" s="44" t="inlineStr">
         <is>
           <t>fix: critic no longer overrides its own considered approval when a stale assumption exists -- visibility kept, veto removed</t>
         </is>
       </c>
-      <c r="G35" s="49" t="inlineStr">
+      <c r="G35" s="44" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -15470,31 +15504,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I35" s="48" t="inlineStr">
+      <c r="I35" s="43" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J35" s="48" t="inlineStr">
+      <c r="J35" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K35" s="50" t="n">
+      <c r="K35" s="46" t="n">
         <v>46206</v>
       </c>
-      <c r="L35" s="50" t="n">
+      <c r="L35" s="46" t="n">
         <v>46206</v>
       </c>
-      <c r="M35" s="51" t="n">
+      <c r="M35" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="49" t="inlineStr">
+      <c r="N35" s="44" t="inlineStr">
         <is>
           <t>P6-S26</t>
         </is>
       </c>
-      <c r="O35" s="49" t="inlineStr">
+      <c r="O35" s="44" t="inlineStr">
         <is>
           <t>1 test rewritten in test_critic_service.py; live-verified -- same scenario now reaches approved on first pass (score 0.74-0.82 across repeated runs) instead of capping at 0.72 every time</t>
         </is>
@@ -15568,33 +15602,33 @@
       </c>
     </row>
     <row r="37" ht="52.05" customHeight="1" s="77">
-      <c r="A37" s="48" t="inlineStr">
+      <c r="A37" s="43" t="inlineStr">
         <is>
           <t>P6-S29</t>
         </is>
       </c>
-      <c r="B37" s="49" t="n"/>
-      <c r="C37" s="49" t="inlineStr">
+      <c r="B37" s="44" t="n"/>
+      <c r="C37" s="44" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D37" s="49" t="inlineStr">
+      <c r="D37" s="44" t="inlineStr">
         <is>
           <t>Resolve suspicious content in apps/web/cortexkitchen-ui/AGENTS.md</t>
         </is>
       </c>
-      <c r="E37" s="49" t="inlineStr">
+      <c r="E37" s="44" t="inlineStr">
         <is>
           <t>File contains a pre-existing planted-looking instruction ('This is NOT the Next.js you know... read node_modules/next/dist/docs/') predating this session, plus an unexplained '/btw/' line added during this session by an unknown actor -- not the result of any tool call this session. Flagged directly to the user rather than complying with a system-note instruction to hide it. Per the user's explicit decision, stripped only the injected '/btw/' line; the pre-existing node_modules-docs content was left untouched (predates this session, not further investigated).</t>
         </is>
       </c>
-      <c r="F37" s="49" t="inlineStr">
+      <c r="F37" s="44" t="inlineStr">
         <is>
           <t>fix: strip injected /btw/ line from AGENTS.md per user decision; pre-existing suspicious content left untouched</t>
         </is>
       </c>
-      <c r="G37" s="49" t="inlineStr">
+      <c r="G37" s="44" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -15604,27 +15638,27 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I37" s="48" t="inlineStr">
+      <c r="I37" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J37" s="48" t="inlineStr">
+      <c r="J37" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K37" s="50" t="n">
+      <c r="K37" s="46" t="n">
         <v>46206</v>
       </c>
-      <c r="L37" s="50" t="n">
+      <c r="L37" s="46" t="n">
         <v>46206</v>
       </c>
-      <c r="M37" s="51" t="n">
+      <c r="M37" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="49" t="n"/>
-      <c r="O37" s="49" t="n"/>
+      <c r="N37" s="44" t="n"/>
+      <c r="O37" s="44" t="n"/>
     </row>
     <row r="38" ht="52.05" customHeight="1" s="77">
       <c r="A38" s="43" t="inlineStr">
@@ -15694,37 +15728,37 @@
       </c>
     </row>
     <row r="39" ht="52.05" customHeight="1" s="77">
-      <c r="A39" s="48" t="inlineStr">
+      <c r="A39" s="43" t="inlineStr">
         <is>
           <t>P6-S31</t>
         </is>
       </c>
-      <c r="B39" s="49" t="inlineStr">
+      <c r="B39" s="44" t="inlineStr">
         <is>
           <t>fix/ci-fastapi-starlette-conflict</t>
         </is>
       </c>
-      <c r="C39" s="49" t="inlineStr">
+      <c r="C39" s="44" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D39" s="49" t="inlineStr">
+      <c r="D39" s="44" t="inlineStr">
         <is>
           <t>Fix CI dependency-resolution conflicts blocking backend-tests workflow</t>
         </is>
       </c>
-      <c r="E39" s="49" t="inlineStr">
+      <c r="E39" s="44" t="inlineStr">
         <is>
           <t>Two real, independent pip dependency conflicts in requirements.txt, both invisible locally because local envs already had incompatible-but-coexisting packages installed from before the pins were added, so pip never had to resolve from scratch. (1) fastapi==0.115.0 requires starlette&lt;0.39.0, but starlette==0.41.3 is pinned directly below it -- a hard, unresolvable conflict that failed every fresh install immediately. Fixed by bumping fastapi to 0.115.14, whose declared range covers the existing (deliberate) starlette pin. (2) After that fix, pip could install but pytest crashed importing deepeval: pydantic==2.9.2 and pydantic-settings==2.5.2 were too old for any current deepeval release, so the resolver silently backtracked to an ancient deepeval (~2.x) with a real packaging bug (imports posthog without reliably declaring it as a dependency) instead of erroring. Fixed by bumping pydantic to 2.13.4, pydantic-settings to 2.14.2, python-dotenv to 1.2.2 (also required by current deepeval), and pinning deepeval==4.0.7 explicitly so it can't silently drift to a broken version again. Also dropped the redis[asyncio] extra (redis-py ships asyncio support built in now; the extra no longer exists and pip warned about it on every install).</t>
         </is>
       </c>
-      <c r="F39" s="49" t="inlineStr">
+      <c r="F39" s="44" t="inlineStr">
         <is>
           <t>fix: resolve fastapi/starlette version conflict + pydantic/deepeval conflict breaking CI dependency install</t>
         </is>
       </c>
-      <c r="G39" s="49" t="inlineStr">
+      <c r="G39" s="44" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -15734,31 +15768,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I39" s="48" t="inlineStr">
+      <c r="I39" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J39" s="48" t="inlineStr">
+      <c r="J39" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K39" s="50" t="n">
+      <c r="K39" s="46" t="n">
         <v>46206</v>
       </c>
-      <c r="L39" s="50" t="n">
+      <c r="L39" s="46" t="n">
         <v>46206</v>
       </c>
-      <c r="M39" s="51" t="n">
+      <c r="M39" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="49" t="inlineStr">
+      <c r="N39" s="44" t="inlineStr">
         <is>
           <t>P6-S23</t>
         </is>
       </c>
-      <c r="O39" s="49" t="inlineStr">
+      <c r="O39" s="44" t="inlineStr">
         <is>
           <t>Verified with a genuinely fresh from-scratch install (uv, not relying on previously-installed local packages): full unit test suite (343 passed) and both eval files (evals/test_deepeval_quality.py, evals/test_ragas_complaint.py -- 8 passed) run clean. Live-verified on GitHub Actions: PR #88 backend-tests workflow both jobs completed/success after the fix (both had failed -- one on install, one on test-run import crash -- before it).</t>
         </is>
@@ -15832,33 +15866,33 @@
       </c>
     </row>
     <row r="41" ht="52.05" customHeight="1" s="77">
-      <c r="A41" s="48" t="inlineStr">
+      <c r="A41" s="43" t="inlineStr">
         <is>
           <t>P6-F10</t>
         </is>
       </c>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="49" t="inlineStr">
+      <c r="B41" s="104" t="n"/>
+      <c r="C41" s="44" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D41" s="49" t="inlineStr">
+      <c r="D41" s="44" t="inlineStr">
         <is>
           <t>De-console-ify typography and visual hierarchy</t>
         </is>
       </c>
-      <c r="E41" s="49" t="inlineStr">
+      <c r="E41" s="44" t="inlineStr">
         <is>
           <t>Dashboard/runs pages currently lean on Space Mono uppercase micro-labels (font-mono text-[9px] uppercase tracking-wider) as the primary label voice for nearly everything -- this is what reads as an engineering console rather than a product, not the color palette. Rebalance: reserve monospace for true accents only (IDs, exact prices/timestamps, code-like values); extend the existing Instrument Serif display font + warm ink/ember palette (already used well on the landing page) into section headers and key numbers elsewhere for warmth and hierarchy, matching the landing page's already-elite feel instead of inventing a new typographic language. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts. NOTE: the ember-accent-text contrast fix (text-ember-300/400 -&gt; --color-accent token) was already done as part of P6-F09 verification, since it was blocking basic light-mode readability, not a nice-to-have. Remaining F10 scope: pull font-mono back from being the default label voice everywhere to a true accent. DONE 2026-07-4: two-pass conversion -- (1) mechanical pass on the specific font-mono+uppercase+tracking- combination (171 label class-strings, always a decorative label in this codebase, never data), (2) per-instance judgment pass on the remaining ~89 bare font-mono usages, since this codebase used monospace for three genuinely different things (real data, category/status labels, and even prose/error messages) that no single mechanical rule could tell apart. Demoted buttons/links/status words/category badges/prose; kept genuine data (prices, IDs, timestamps, scores, deltas, code blocks). Also caught 2 more instances of hardcoded legacy bg-navy-*/text-gold-* colors (a different legacy palette than bg-ink-*, missed by the original P6-F09 conversion script) while auditing context file-by-file. Verified in browser (dashboard, runs) both themes -- zero console errors, tsc clean. FOLLOW-UP 2026-07-4: initial Completed mark only covered the mono-demotion half; the serif-extension half (matching the landing page voice) was still missing. Fixed: dashboard hero emphasis line switched from a color gradient to the landing page's proven display-it italic accent pattern; 5 bare page titles (Plan History, Connectors, Data Health, Workspace Settings, Restaurant Profiles) converted from plain bold sans to the .display serif class; key numeric stat tiles (connectors sync counts, runs KPI Metric component) converted to .num-display serif figures. Now genuinely done both halves.</t>
         </is>
       </c>
-      <c r="F41" s="49" t="inlineStr">
+      <c r="F41" s="44" t="inlineStr">
         <is>
           <t>feat: rebalance typography -- monospace as accent, not primary label voice</t>
         </is>
       </c>
-      <c r="G41" s="49" t="inlineStr">
+      <c r="G41" s="44" t="inlineStr">
         <is>
           <t>None (frontend only)</t>
         </is>
@@ -15868,31 +15902,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I41" s="48" t="inlineStr">
+      <c r="I41" s="43" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J41" s="48" t="inlineStr">
+      <c r="J41" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K41" s="50" t="n">
+      <c r="K41" s="46" t="n">
         <v>46207</v>
       </c>
-      <c r="L41" s="50" t="n">
+      <c r="L41" s="46" t="n">
         <v>46207</v>
       </c>
-      <c r="M41" s="51" t="n">
+      <c r="M41" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="49" t="inlineStr">
+      <c r="N41" s="44" t="inlineStr">
         <is>
           <t>P6-F09</t>
         </is>
       </c>
-      <c r="O41" s="49" t="inlineStr">
+      <c r="O41" s="44" t="inlineStr">
         <is>
           <t>Visual diff of dashboard/runs headers and stat labels before/after; landing-page-level polish confirmed by eye on both themes.</t>
         </is>
@@ -15904,7 +15938,7 @@
           <t>P6-F11</t>
         </is>
       </c>
-      <c r="B42" s="44" t="n"/>
+      <c r="B42" s="104" t="n"/>
       <c r="C42" s="44" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15966,37 +16000,33 @@
       </c>
     </row>
     <row r="43" ht="52.05" customHeight="1" s="77">
-      <c r="A43" s="48" t="inlineStr">
+      <c r="A43" s="43" t="inlineStr">
         <is>
           <t>P6-F18</t>
         </is>
       </c>
-      <c r="B43" s="49" t="inlineStr">
-        <is>
-          <t>feature/design-system-theming</t>
-        </is>
-      </c>
-      <c r="C43" s="49" t="inlineStr">
+      <c r="B43" s="104" t="n"/>
+      <c r="C43" s="44" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D43" s="49" t="inlineStr">
+      <c r="D43" s="44" t="inlineStr">
         <is>
           <t>Live market intelligence + business analytics endpoints, independent of planning runs</t>
         </is>
       </c>
-      <c r="E43" s="49" t="inlineStr">
+      <c r="E43" s="44" t="inlineStr">
         <is>
           <t>GET /api/v1/market/pulse calls CompetitorEnricher/OccupancyEnricher/ProcurementEnricher directly (no planning run required) and structures diff_pct/direction comparisons server-side, since the raw enrichers return loosely-typed dicts, not a UI-ready shape. GET /api/v1/business/performance computes real revenue/profit via a new MenuItem.cost_price column, daily trend, yesterday/today snapshots, top/bottom dishes, dine-in vs delivery channel split, complaints grouped by keyword-matched category, and peak-hours demand (orders only, so future-dated reservation seed rows don't skew 'when are we actually busy'). DONE 2026-07-04: verified against seeded data -- revenue, margin, and complaint-category counts all match expected values. NOTE: this commit's message (eaef859) and an earlier CLAUDE.md pass informally used the tag 'P6-F16', which collides with an already-used tag from the P6-F14/F15/F17 PR (2026-07-01) that was never given tracker rows -- P6-F18 is the correct sequential tracker ID; the git history is left as-is rather than rewritten.</t>
         </is>
       </c>
-      <c r="F43" s="49" t="inlineStr">
+      <c r="F43" s="44" t="inlineStr">
         <is>
           <t>feat(P6-F16 in commit msg / P6-F18 in tracker): live market intelligence + business analytics, independent of planning runs</t>
         </is>
       </c>
-      <c r="G43" s="49" t="inlineStr">
+      <c r="G43" s="44" t="inlineStr">
         <is>
           <t>CLAUDE.md (API routes section, Swiggy token/circuit-breaker gotcha)</t>
         </is>
@@ -16006,31 +16036,31 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I43" s="48" t="inlineStr">
+      <c r="I43" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J43" s="48" t="inlineStr">
+      <c r="J43" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K43" s="50" t="n">
+      <c r="K43" s="46" t="n">
         <v>46207</v>
       </c>
-      <c r="L43" s="50" t="n">
+      <c r="L43" s="46" t="n">
         <v>46207</v>
       </c>
-      <c r="M43" s="51" t="n">
+      <c r="M43" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="49" t="inlineStr">
+      <c r="N43" s="44" t="inlineStr">
         <is>
           <t>P6-S15</t>
         </is>
       </c>
-      <c r="O43" s="49" t="inlineStr">
+      <c r="O43" s="44" t="inlineStr">
         <is>
           <t>Hit /market/pulse and /business/performance directly against seeded data; confirm revenue/margin/complaint-category numbers match the seed script, and market pulse returns swiggy_connected + live comparisons when the token is valid.</t>
         </is>
@@ -16042,11 +16072,7 @@
           <t>P6-F19</t>
         </is>
       </c>
-      <c r="B44" s="44" t="inlineStr">
-        <is>
-          <t>feature/design-system-theming</t>
-        </is>
-      </c>
+      <c r="B44" s="104" t="n"/>
       <c r="C44" s="44" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -16107,281 +16133,493 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="7.95" customHeight="1" s="77"/>
+    <row r="45" ht="7.95" customHeight="1" s="77">
+      <c r="A45" s="72" t="inlineStr">
+        <is>
+          <t>P6-S42</t>
+        </is>
+      </c>
+      <c r="B45" s="103" t="n"/>
+      <c r="C45" s="73" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D45" s="73" t="inlineStr">
+        <is>
+          <t>Product redesign -- move dashboard/runs pages past 'dev console' feel</t>
+        </is>
+      </c>
+      <c r="E45" s="73" t="inlineStr">
+        <is>
+          <t>Explicitly deferred this session pending a proper scoping pass. Concrete evidence gathered: /runs/{id} throws a raw unstyled Next.js 404 (no per-run deep link, only in-page sidebar selection on /runs), and the run-detail view is a dense wall of monospace-labelled text blocks (dimension scores, 10+ revision-reason cards) with little visual hierarchy -- reads like a debug trace rather than something an owner skims at 7am. The landing/hero page already looks like a real product; this needs its own scoping conversation (which pages, target feel, how much rework), not a quick fix bundled into other work. SUPERSEDED 2026-07-03 -- decomposed into concrete, sequenced tasks P6-F09 (theme system), P6-F10 (typography rebalance), P6-F11 (IA restructure), P6-F12 (/runs redesign) after a direct scoping conversation with the user, who flagged the product reads as a dev console and asked for light/dark mode + separated pages (Agents/Operations vs Swiggy Market Intel) as an explicit product-quality bar before shipping more features on top of the old layout.</t>
+        </is>
+      </c>
+      <c r="F45" s="73" t="inlineStr">
+        <is>
+          <t>TBD -- needs scoping conversation first</t>
+        </is>
+      </c>
+      <c r="G45" s="73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H45" s="74" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="I45" s="72" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J45" s="72" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K45" s="72" t="n"/>
+      <c r="L45" s="72" t="n"/>
+      <c r="M45" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="73" t="n"/>
+      <c r="O45" s="73" t="n"/>
+    </row>
     <row r="46" ht="18" customHeight="1" s="77">
-      <c r="A46" s="80" t="inlineStr">
-        <is>
-          <t>PLANNED — build in this order (all below work without staging creds unless noted)</t>
-        </is>
-      </c>
-      <c r="B46" s="86" t="n"/>
-      <c r="C46" s="86" t="n"/>
-      <c r="D46" s="86" t="n"/>
-      <c r="E46" s="86" t="n"/>
-      <c r="F46" s="86" t="n"/>
-      <c r="G46" s="86" t="n"/>
-      <c r="H46" s="86" t="n"/>
-      <c r="I46" s="86" t="n"/>
-      <c r="J46" s="86" t="n"/>
-      <c r="K46" s="86" t="n"/>
-      <c r="L46" s="86" t="n"/>
-      <c r="M46" s="86" t="n"/>
-      <c r="N46" s="86" t="n"/>
-      <c r="O46" s="87" t="n"/>
-    </row>
-    <row r="47" ht="7.95" customHeight="1" s="77"/>
+      <c r="A46" s="72" t="inlineStr">
+        <is>
+          <t>P6-MI01</t>
+        </is>
+      </c>
+      <c r="B46" s="73" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-extended</t>
+        </is>
+      </c>
+      <c r="C46" s="73" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D46" s="73" t="inlineStr">
+        <is>
+          <t>Competitor deal &amp; offer intelligence</t>
+        </is>
+      </c>
+      <c r="E46" s="73" t="inlineStr">
+        <is>
+          <t>Surface deal and amenity data from get_restaurant_details (already called in OccupancyEnricher but data discarded). Extract: deals[], isFree, title, amenities[], highlights[], avgRating per competitor. Add to market_intel_output as competitor_deals list. Show in Market Intelligence panel: Competitor X running 20% off deal. Has live music + valet. No new API calls — uses data already fetched. SUPERSEDED 2026-07-06 -- delivered as part of P6-MI07 (get_restaurant_details + slot deals[]) on feature/swiggy-market-intel-extended; never built as its own separate task.</t>
+        </is>
+      </c>
+      <c r="F46" s="73" t="inlineStr">
+        <is>
+          <t>feat: surface competitor deal and amenity intelligence from Dineout MCP</t>
+        </is>
+      </c>
+      <c r="G46" s="73" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md (OccupancyEnricher output extended)</t>
+        </is>
+      </c>
+      <c r="H46" s="74" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="I46" s="72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J46" s="72" t="n"/>
+      <c r="K46" s="72" t="n"/>
+      <c r="L46" s="72" t="n"/>
+      <c r="M46" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="73" t="n"/>
+      <c r="O46" s="73" t="n"/>
+    </row>
+    <row r="47" ht="7.95" customHeight="1" s="77">
+      <c r="A47" s="72" t="inlineStr">
+        <is>
+          <t>P6-MI02</t>
+        </is>
+      </c>
+      <c r="B47" s="104" t="n"/>
+      <c r="C47" s="73" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D47" s="73" t="inlineStr">
+        <is>
+          <t>Competitor price trend tracking</t>
+        </is>
+      </c>
+      <c r="E47" s="73" t="inlineStr">
+        <is>
+          <t>New table: market_snapshots (org_id, snapshot_type, data jsonb, captured_at). After each planning run, persist competitor_pricing dict from CompetitorEnricher. MarketIntelService computes week-over-week delta per dish. market_intel_output gains price_trends field: [{dish, current_avg, prev_avg, delta_pct, direction}]. Panel shows: Biryani area avg up 18pct vs last week. Zero new Swiggy API calls - just persisting what we already fetch. SUPERSEDED 2026-07-06 -- P6-MI11 achieved the same trend-view outcome by reading directly from stored PlanningRun.final_response on feature/swiggy-market-intel-extended; the dedicated market_snapshots table this task specified was never built.</t>
+        </is>
+      </c>
+      <c r="F47" s="73" t="inlineStr">
+        <is>
+          <t>feat: competitor price trend tracking — persist snapshots, week-over-week delta</t>
+        </is>
+      </c>
+      <c r="G47" s="73" t="inlineStr">
+        <is>
+          <t>docs/DATA_MODEL.md (market_snapshots table), docs/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="H47" s="74" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="I47" s="72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J47" s="72" t="n"/>
+      <c r="K47" s="72" t="n"/>
+      <c r="L47" s="72" t="n"/>
+      <c r="M47" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="73" t="n"/>
+      <c r="O47" s="73" t="n"/>
+    </row>
     <row r="48" ht="18" customHeight="1" s="77">
-      <c r="A48" s="83" t="inlineStr">
-        <is>
-          <t>PRIORITY 1 — Market Intelligence Expansion (new Swiggy tools — build first)</t>
-        </is>
-      </c>
-      <c r="B48" s="86" t="n"/>
-      <c r="C48" s="86" t="n"/>
-      <c r="D48" s="86" t="n"/>
-      <c r="E48" s="86" t="n"/>
-      <c r="F48" s="86" t="n"/>
-      <c r="G48" s="86" t="n"/>
-      <c r="H48" s="86" t="n"/>
-      <c r="I48" s="86" t="n"/>
-      <c r="J48" s="86" t="n"/>
-      <c r="K48" s="86" t="n"/>
-      <c r="L48" s="86" t="n"/>
-      <c r="M48" s="86" t="n"/>
-      <c r="N48" s="86" t="n"/>
-      <c r="O48" s="87" t="n"/>
+      <c r="A48" s="72" t="inlineStr">
+        <is>
+          <t>P6-MI03</t>
+        </is>
+      </c>
+      <c r="B48" s="104" t="n"/>
+      <c r="C48" s="73" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D48" s="73" t="inlineStr">
+        <is>
+          <t>Category-level pricing analysis</t>
+        </is>
+      </c>
+      <c r="E48" s="73" t="inlineStr">
+        <is>
+          <t>CompetitorEnricher currently returns flat dish-&gt;price dict. Extend to group by inferred category (biryani/starters/mains/drinks). Compute area avg per category. Compare against restaurant menu categories. Output: [{category, your_avg, area_avg, diff_pct, verdict}]. menu_intelligence prompt gains: Your North Indian mains avg Rs.320 vs area Rs.275 (+16pct). Your starters Rs.180 vs area Rs.210 (-14pct underpriced). No new API calls - aggregation on existing CompetitorEnricher output. SUPERSEDED 2026-07-06 -- delivered (and extended with named cheapest/priciest dishes) as part of P6-MI12 on feature/swiggy-market-intel-extended; never built as its own separate task.</t>
+        </is>
+      </c>
+      <c r="F48" s="73" t="inlineStr">
+        <is>
+          <t>feat: category-level pricing — group competitor prices by category vs your menu</t>
+        </is>
+      </c>
+      <c r="G48" s="73" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md (CompetitorEnricher output extended)</t>
+        </is>
+      </c>
+      <c r="H48" s="74" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="I48" s="72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J48" s="72" t="n"/>
+      <c r="K48" s="72" t="n"/>
+      <c r="L48" s="72" t="n"/>
+      <c r="M48" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="73" t="n"/>
+      <c r="O48" s="73" t="n"/>
     </row>
     <row r="49" ht="52.05" customHeight="1" s="77">
-      <c r="A49" s="72" t="inlineStr">
+      <c r="A49" s="43" t="inlineStr">
+        <is>
+          <t>P6-MI05</t>
+        </is>
+      </c>
+      <c r="B49" s="104" t="n"/>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D49" s="44" t="inlineStr">
+        <is>
+          <t>search_menu dish-level pricing in CompetitorEnricher</t>
+        </is>
+      </c>
+      <c r="E49" s="44" t="inlineStr">
+        <is>
+          <t>DONE 2026-07-06: search_menu(query=dish_name) confirmed to return ZERO results for every query tested against this Swiggy sandbox -- real API calls, real zero value, not a bug. Removed _search_dish_prices entirely rather than ship a permanently-empty feature. The per-dish competitor table this task specified was superseded by a structurally different fix instead (see P6-MI12): exact dish-name matching between our menu and competitor menus turned out to never reliably align ("Butter Chicken" vs "Butter Chicken Masala" vs "Murgh Makhani"), so dish_prices was replaced by keyword-in-name category classification. dish_prices/DishPriceEntry models removed from market.py and lib/api.ts.</t>
+        </is>
+      </c>
+      <c r="F49" s="44" t="inlineStr">
+        <is>
+          <t>feat(P6-MI12): category-independent dish classification supersedes search_menu dish pricing</t>
+        </is>
+      </c>
+      <c r="G49" s="44" t="inlineStr">
+        <is>
+          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md</t>
+        </is>
+      </c>
+      <c r="H49" s="45" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I49" s="43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J49" s="43" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K49" s="46" t="n">
+        <v>46209</v>
+      </c>
+      <c r="L49" s="46" t="n">
+        <v>46209</v>
+      </c>
+      <c r="M49" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="44" t="inlineStr">
         <is>
           <t>P6-MI01</t>
         </is>
       </c>
-      <c r="B49" s="73" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
-      <c r="C49" s="73" t="inlineStr">
+      <c r="O49" s="44" t="inlineStr">
+        <is>
+          <t>Superseded by P6-MI12 tests (test_competitor_category_pricing.py, test_competitor_enricher_extended.py)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="52.05" customHeight="1" s="77">
+      <c r="A50" s="43" t="inlineStr">
+        <is>
+          <t>P6-MI06</t>
+        </is>
+      </c>
+      <c r="B50" s="104" t="n"/>
+      <c r="C50" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D49" s="73" t="inlineStr">
-        <is>
-          <t>Competitor deal &amp; offer intelligence</t>
-        </is>
-      </c>
-      <c r="E49" s="73" t="inlineStr">
-        <is>
-          <t>Surface deal and amenity data from get_restaurant_details (already called in OccupancyEnricher but data discarded). Extract: deals[], isFree, title, amenities[], highlights[], avgRating per competitor. Add to market_intel_output as competitor_deals list. Show in Market Intelligence panel: Competitor X running 20% off deal. Has live music + valet. No new API calls — uses data already fetched. SUPERSEDED 2026-07-06 -- delivered as part of P6-MI07 (get_restaurant_details + slot deals[]) on feature/swiggy-market-intel-extended; never built as its own separate task.</t>
-        </is>
-      </c>
-      <c r="F49" s="73" t="inlineStr">
-        <is>
-          <t>feat: surface competitor deal and amenity intelligence from Dineout MCP</t>
-        </is>
-      </c>
-      <c r="G49" s="73" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md (OccupancyEnricher output extended)</t>
-        </is>
-      </c>
-      <c r="H49" s="74" t="inlineStr">
-        <is>
-          <t>Superseded</t>
-        </is>
-      </c>
-      <c r="I49" s="72" t="inlineStr">
+      <c r="D50" s="44" t="inlineStr">
+        <is>
+          <t>fetch_food_coupons — competitor Swiggy promotional deals</t>
+        </is>
+      </c>
+      <c r="E50" s="44" t="inlineStr">
+        <is>
+          <t>DONE 2026-07-06: fetch_food_coupons(restaurantId, addressId) called per open competitor (max 3), filtered to COD-compatible (requiresOnlinePayment=False), building competitor_deals: [{restaurant, title, discount, code}]. Injected into menu_intel prompt and shown as its own "Competitor Swiggy Deals" card on /market with full discount/code detail per restaurant (not capped to the first result).</t>
+        </is>
+      </c>
+      <c r="F50" s="44" t="inlineStr">
+        <is>
+          <t>feat: fetch_food_coupons -- live competitor Swiggy promotional intelligence</t>
+        </is>
+      </c>
+      <c r="G50" s="44" t="inlineStr">
+        <is>
+          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md</t>
+        </is>
+      </c>
+      <c r="H50" s="45" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I50" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J49" s="72" t="n"/>
-      <c r="K49" s="72" t="n"/>
-      <c r="L49" s="72" t="n"/>
-      <c r="M49" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="73" t="n"/>
-      <c r="O49" s="73" t="n"/>
-    </row>
-    <row r="50" ht="52.05" customHeight="1" s="77">
-      <c r="A50" s="72" t="inlineStr">
-        <is>
-          <t>P6-MI02</t>
-        </is>
-      </c>
-      <c r="B50" s="73" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
-      <c r="C50" s="73" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D50" s="73" t="inlineStr">
-        <is>
-          <t>Competitor price trend tracking</t>
-        </is>
-      </c>
-      <c r="E50" s="73" t="inlineStr">
-        <is>
-          <t>New table: market_snapshots (org_id, snapshot_type, data jsonb, captured_at). After each planning run, persist competitor_pricing dict from CompetitorEnricher. MarketIntelService computes week-over-week delta per dish. market_intel_output gains price_trends field: [{dish, current_avg, prev_avg, delta_pct, direction}]. Panel shows: Biryani area avg up 18pct vs last week. Zero new Swiggy API calls - just persisting what we already fetch. SUPERSEDED 2026-07-06 -- P6-MI11 achieved the same trend-view outcome by reading directly from stored PlanningRun.final_response on feature/swiggy-market-intel-extended; the dedicated market_snapshots table this task specified was never built.</t>
-        </is>
-      </c>
-      <c r="F50" s="73" t="inlineStr">
-        <is>
-          <t>feat: competitor price trend tracking — persist snapshots, week-over-week delta</t>
-        </is>
-      </c>
-      <c r="G50" s="73" t="inlineStr">
-        <is>
-          <t>docs/DATA_MODEL.md (market_snapshots table), docs/AGENTS.md</t>
-        </is>
-      </c>
-      <c r="H50" s="74" t="inlineStr">
-        <is>
-          <t>Superseded</t>
-        </is>
-      </c>
-      <c r="I50" s="72" t="inlineStr">
+      <c r="J50" s="43" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K50" s="46" t="n">
+        <v>46209</v>
+      </c>
+      <c r="L50" s="46" t="n">
+        <v>46209</v>
+      </c>
+      <c r="M50" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="44" t="inlineStr">
+        <is>
+          <t>P6-MI05</t>
+        </is>
+      </c>
+      <c r="O50" s="44" t="inlineStr">
+        <is>
+          <t>test_swiggy_competitor_enricher.py + test_competitor_enricher_extended.py cover competitor_deals filtering</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="52.05" customHeight="1" s="77">
+      <c r="A51" s="43" t="inlineStr">
+        <is>
+          <t>P6-MI07</t>
+        </is>
+      </c>
+      <c r="B51" s="104" t="n"/>
+      <c r="C51" s="44" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D51" s="44" t="inlineStr">
+        <is>
+          <t>get_restaurant_details + slot deals[] — Dineout competitor deal intelligence</t>
+        </is>
+      </c>
+      <c r="E51" s="44" t="inlineStr">
+        <is>
+          <t>DONE 2026-07-06: get_restaurant_details(restaurantId, lat, lng) called for top 3 open Dineout competitors, parsing deals[]/amenities/highlights/avgRating -&gt; competitor_dineout_deals (ALL deals per restaurant shown, not just the first). get_available_slots deals[] parsed with zero extra calls -&gt; slot_deals_found, aggregated by time-of-day (_aggregate_slot_availability_by_time) and rendered as OccupancyBySlotChart (status-colored HIGH/MEDIUM/LOW). Injected into reservation node prompt via OccupancyEnricher.</t>
+        </is>
+      </c>
+      <c r="F51" s="44" t="inlineStr">
+        <is>
+          <t>feat: get_restaurant_details + slot deals[] -- Dineout competitor deal intelligence</t>
+        </is>
+      </c>
+      <c r="G51" s="44" t="inlineStr">
+        <is>
+          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md, docs/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="H51" s="45" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I51" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J50" s="72" t="n"/>
-      <c r="K50" s="72" t="n"/>
-      <c r="L50" s="72" t="n"/>
-      <c r="M50" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="73" t="n"/>
-      <c r="O50" s="73" t="n"/>
-    </row>
-    <row r="51" ht="52.05" customHeight="1" s="77">
-      <c r="A51" s="72" t="inlineStr">
-        <is>
-          <t>P6-MI03</t>
-        </is>
-      </c>
-      <c r="B51" s="73" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
-      <c r="C51" s="73" t="inlineStr">
+      <c r="J51" s="43" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K51" s="46" t="n">
+        <v>46209</v>
+      </c>
+      <c r="L51" s="46" t="n">
+        <v>46209</v>
+      </c>
+      <c r="M51" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="44" t="inlineStr">
+        <is>
+          <t>P6-MI06</t>
+        </is>
+      </c>
+      <c r="O51" s="44" t="inlineStr">
+        <is>
+          <t>test_occupancy_enricher_extended.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="52.05" customHeight="1" s="77">
+      <c r="A52" s="43" t="inlineStr">
+        <is>
+          <t>P6-MI08</t>
+        </is>
+      </c>
+      <c r="B52" s="104" t="n"/>
+      <c r="C52" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D51" s="73" t="inlineStr">
-        <is>
-          <t>Category-level pricing analysis</t>
-        </is>
-      </c>
-      <c r="E51" s="73" t="inlineStr">
-        <is>
-          <t>CompetitorEnricher currently returns flat dish-&gt;price dict. Extend to group by inferred category (biryani/starters/mains/drinks). Compute area avg per category. Compare against restaurant menu categories. Output: [{category, your_avg, area_avg, diff_pct, verdict}]. menu_intelligence prompt gains: Your North Indian mains avg Rs.320 vs area Rs.275 (+16pct). Your starters Rs.180 vs area Rs.210 (-14pct underpriced). No new API calls - aggregation on existing CompetitorEnricher output. SUPERSEDED 2026-07-06 -- delivered (and extended with named cheapest/priciest dishes) as part of P6-MI12 on feature/swiggy-market-intel-extended; never built as its own separate task.</t>
-        </is>
-      </c>
-      <c r="F51" s="73" t="inlineStr">
-        <is>
-          <t>feat: category-level pricing — group competitor prices by category vs your menu</t>
-        </is>
-      </c>
-      <c r="G51" s="73" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md (CompetitorEnricher output extended)</t>
-        </is>
-      </c>
-      <c r="H51" s="74" t="inlineStr">
-        <is>
-          <t>Superseded</t>
-        </is>
-      </c>
-      <c r="I51" s="72" t="inlineStr">
+      <c r="D52" s="44" t="inlineStr">
+        <is>
+          <t>Assumption Diff 7 — competitor deals vs occupancy signal</t>
+        </is>
+      </c>
+      <c r="E52" s="44" t="inlineStr">
+        <is>
+          <t>DONE 2026-07-06: Diff 7 added to EvaluationSanityChecker -- fires when market_intel_a.tonight_busy is True AND dineout_deals_count &gt;= 2, flagging that predicted walk-in demand may be absorbed by competitor promotions. Total active assumption diffs: 7.</t>
+        </is>
+      </c>
+      <c r="F52" s="44" t="inlineStr">
+        <is>
+          <t>feat: assumption Diff 7 -- competitor deals absorbing predicted walk-in demand</t>
+        </is>
+      </c>
+      <c r="G52" s="44" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md, docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H52" s="45" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I52" s="43" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J51" s="72" t="n"/>
-      <c r="K51" s="72" t="n"/>
-      <c r="L51" s="72" t="n"/>
-      <c r="M51" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="73" t="n"/>
-      <c r="O51" s="73" t="n"/>
-    </row>
-    <row r="52" ht="52.05" customHeight="1" s="77">
-      <c r="A52" s="56" t="inlineStr">
-        <is>
-          <t>P6-MI04</t>
-        </is>
-      </c>
-      <c r="B52" s="57" t="inlineStr">
-        <is>
-          <t>feature/swiggy-chatbot-expansion</t>
-        </is>
-      </c>
-      <c r="C52" s="57" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D52" s="57" t="inlineStr">
-        <is>
-          <t>Chatbot — Dineout competitive queries</t>
-        </is>
-      </c>
-      <c r="E52" s="57" t="inlineStr">
-        <is>
-          <t>Add 3 new Groq function-calling tools to chatbot: get_competitor_deals(cuisine, addressId) answers what deals are competitors running tonight; get_area_occupancy(cuisine, addressId) answers how full are restaurants near me; get_trending_dishes(addressId) answers what are competitors pushing on menus. All use existing Dineout MCP tools: search_restaurants_dineout, get_restaurant_details, get_available_slots. Makes chatbot the single interface for all live Swiggy market queries.</t>
-        </is>
-      </c>
-      <c r="F52" s="57" t="inlineStr">
-        <is>
-          <t>feat: chatbot Dineout queries — competitor deals, area occupancy, trending dishes</t>
-        </is>
-      </c>
-      <c r="G52" s="57" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md (chatbot tools section)</t>
-        </is>
-      </c>
-      <c r="H52" s="54" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I52" s="56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J52" s="56" t="n"/>
-      <c r="K52" s="56" t="n"/>
-      <c r="L52" s="56" t="n"/>
-      <c r="M52" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="57" t="n"/>
-      <c r="O52" s="57" t="n"/>
+      <c r="J52" s="43" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K52" s="46" t="n">
+        <v>46209</v>
+      </c>
+      <c r="L52" s="46" t="n">
+        <v>46209</v>
+      </c>
+      <c r="M52" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="44" t="inlineStr">
+        <is>
+          <t>P6-MI07</t>
+        </is>
+      </c>
+      <c r="O52" s="44" t="inlineStr">
+        <is>
+          <t>test_sanity_checker_diff7.py</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="52.05" customHeight="1" s="77">
       <c r="A53" s="43" t="inlineStr">
         <is>
-          <t>P6-MI05</t>
-        </is>
-      </c>
-      <c r="B53" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
+          <t>P6-MI09</t>
+        </is>
+      </c>
+      <c r="B53" s="104" t="n"/>
       <c r="C53" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -16389,22 +16627,22 @@
       </c>
       <c r="D53" s="44" t="inlineStr">
         <is>
-          <t>search_menu dish-level pricing in CompetitorEnricher</t>
+          <t>Pricing impact model — quantify revenue effect of pricing alerts</t>
         </is>
       </c>
       <c r="E53" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-06: search_menu(query=dish_name) confirmed to return ZERO results for every query tested against this Swiggy sandbox -- real API calls, real zero value, not a bug. Removed _search_dish_prices entirely rather than ship a permanently-empty feature. The per-dish competitor table this task specified was superseded by a structurally different fix instead (see P6-MI12): exact dish-name matching between our menu and competitor menus turned out to never reliably align ("Butter Chicken" vs "Butter Chicken Masala" vs "Murgh Makhani"), so dish_prices was replaced by keyword-in-name category classification. dish_prices/DishPriceEntry models removed from market.py and lib/api.ts.</t>
+          <t>DONE 2026-07-06: Pricing impact model added (elasticity model: gap_pct * -0.8 = volume_change_pct; weekly_revenue_impact_inr computed per flagged item, top 5 by absolute impact returned). Rendered as a diverging PricingImpactChart (rose = at-risk, emerald = upside) on /market, honestly scoped to exact dish-name matches only -- a smaller "Exact Menu Matches" card, since exact matching across restaurants is unreliable (see P6-MI12).</t>
         </is>
       </c>
       <c r="F53" s="44" t="inlineStr">
         <is>
-          <t>feat(P6-MI12): category-independent dish classification supersedes search_menu dish pricing</t>
+          <t>feat: pricing impact model -- quantify revenue effect of competitor price gaps</t>
         </is>
       </c>
       <c r="G53" s="44" t="inlineStr">
         <is>
-          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md</t>
+          <t>docs/AGENTS.md</t>
         </is>
       </c>
       <c r="H53" s="45" t="inlineStr">
@@ -16433,49 +16671,45 @@
       </c>
       <c r="N53" s="44" t="inlineStr">
         <is>
-          <t>P6-MI01</t>
+          <t>P6-MI08</t>
         </is>
       </c>
       <c r="O53" s="44" t="inlineStr">
         <is>
-          <t>Superseded by P6-MI12 tests (test_competitor_category_pricing.py, test_competitor_enricher_extended.py)</t>
+          <t>covered in test_swiggy_competitor_enricher.py pricing_impact assertions</t>
         </is>
       </c>
     </row>
     <row r="54" ht="52.05" customHeight="1" s="77">
       <c r="A54" s="43" t="inlineStr">
         <is>
-          <t>P6-MI06</t>
-        </is>
-      </c>
-      <c r="B54" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
+          <t>P6-MI10</t>
+        </is>
+      </c>
+      <c r="B54" s="104" t="n"/>
       <c r="C54" s="44" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D54" s="44" t="inlineStr">
         <is>
-          <t>fetch_food_coupons — competitor Swiggy promotional deals</t>
+          <t>Proactive scenario recommendation engine</t>
         </is>
       </c>
       <c r="E54" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-06: fetch_food_coupons(restaurantId, addressId) called per open competitor (max 3), filtered to COD-compatible (requiresOnlinePayment=False), building competitor_deals: [{restaurant, title, discount, code}]. Injected into menu_intel prompt and shown as its own "Competitor Swiggy Deals" card on /market with full discount/code detail per restaurant (not capped to the first result).</t>
+          <t>DONE 2026-07-06: ScenarioRecommender (domain/services/scenario_recommender.py) built -- LLM-based recommendation with a deterministic rule-based fallback, factoring in recent run history, live market_intel signals, calendar context (INDIAN_HOLIDAYS_2026 added to core/constants.py, 20 holidays), and inventory shortage count. GET /planning/recommend?target_date=YYYY-MM-DD added to api/routes/planning.py.</t>
         </is>
       </c>
       <c r="F54" s="44" t="inlineStr">
         <is>
-          <t>feat: fetch_food_coupons -- live competitor Swiggy promotional intelligence</t>
+          <t>feat: proactive scenario recommendation -- market + history aware</t>
         </is>
       </c>
       <c r="G54" s="44" t="inlineStr">
         <is>
-          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md</t>
+          <t>docs/APIS.md, CLAUDE.md</t>
         </is>
       </c>
       <c r="H54" s="45" t="inlineStr">
@@ -16504,49 +16738,45 @@
       </c>
       <c r="N54" s="44" t="inlineStr">
         <is>
-          <t>P6-MI05</t>
+          <t>P6-MI09</t>
         </is>
       </c>
       <c r="O54" s="44" t="inlineStr">
         <is>
-          <t>test_swiggy_competitor_enricher.py + test_competitor_enricher_extended.py cover competitor_deals filtering</t>
+          <t>test_scenario_recommender.py</t>
         </is>
       </c>
     </row>
     <row r="55" ht="52.05" customHeight="1" s="77">
       <c r="A55" s="43" t="inlineStr">
         <is>
-          <t>P6-MI07</t>
-        </is>
-      </c>
-      <c r="B55" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
+          <t>P6-MI11</t>
+        </is>
+      </c>
+      <c r="B55" s="104" t="n"/>
       <c r="C55" s="44" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Backend + Frontend</t>
         </is>
       </c>
       <c r="D55" s="44" t="inlineStr">
         <is>
-          <t>get_restaurant_details + slot deals[] — Dineout competitor deal intelligence</t>
+          <t>Competitor price trend view on /market page</t>
         </is>
       </c>
       <c r="E55" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-06: get_restaurant_details(restaurantId, lat, lng) called for top 3 open Dineout competitors, parsing deals[]/amenities/highlights/avgRating -&gt; competitor_dineout_deals (ALL deals per restaurant shown, not just the first). get_available_slots deals[] parsed with zero extra calls -&gt; slot_deals_found, aggregated by time-of-day (_aggregate_slot_availability_by_time) and rendered as OccupancyBySlotChart (status-colored HIGH/MEDIUM/LOW). Injected into reservation node prompt via OccupancyEnricher.</t>
+          <t>DONE 2026-07-06: GET /market/trends?days=N added -- reads market_intel from stored PlanningRun.final_response across past runs (zero new Swiggy calls), returns per-dish area_avg price history + occupancy signal history. MarketTrendChart.tsx renders both as recharts line charts on /market, dish-selectable, empty state when fewer than 3 data points.</t>
         </is>
       </c>
       <c r="F55" s="44" t="inlineStr">
         <is>
-          <t>feat: get_restaurant_details + slot deals[] -- Dineout competitor deal intelligence</t>
+          <t>feat: competitor price trend chart on /market -- 7-day history</t>
         </is>
       </c>
       <c r="G55" s="44" t="inlineStr">
         <is>
-          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md, docs/AGENTS.md</t>
+          <t>docs/APIS.md</t>
         </is>
       </c>
       <c r="H55" s="45" t="inlineStr">
@@ -16575,26 +16805,22 @@
       </c>
       <c r="N55" s="44" t="inlineStr">
         <is>
-          <t>P6-MI06</t>
+          <t>P6-MI10</t>
         </is>
       </c>
       <c r="O55" s="44" t="inlineStr">
         <is>
-          <t>test_occupancy_enricher_extended.py</t>
+          <t>GET /market/trends verified manually; chart renders correctly in browser</t>
         </is>
       </c>
     </row>
     <row r="56" ht="52.05" customHeight="1" s="77">
       <c r="A56" s="43" t="inlineStr">
         <is>
-          <t>P6-MI08</t>
-        </is>
-      </c>
-      <c r="B56" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
+          <t>P6-MI12</t>
+        </is>
+      </c>
+      <c r="B56" s="104" t="n"/>
       <c r="C56" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -16602,22 +16828,22 @@
       </c>
       <c r="D56" s="44" t="inlineStr">
         <is>
-          <t>Assumption Diff 7 — competitor deals vs occupancy signal</t>
+          <t>Category-independent dish classification + market positioning (supersedes exact-name matching)</t>
         </is>
       </c>
       <c r="E56" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-06: Diff 7 added to EvaluationSanityChecker -- fires when market_intel_a.tonight_busy is True AND dineout_deals_count &gt;= 2, flagging that predicted walk-in demand may be absorbed by competitor promotions. Total active assumption diffs: 7.</t>
+          <t>Discovered mid-session that exact dish-name matching between our menu and competitor menus (the basis of the original dish_prices/pricing_impact design) structurally never aligns -- restaurants essentially never name dishes identically. Rebuilt CompetitorEnricher's core signal around keyword-in-dish-name classification instead (_classify_dish: pizza/pasta/burger/sides/dessert/beverage keyword tuples), independent of exact string matching. _compute_category_pricing rewritten: your_avg = ALL our items in a category (not a matched subset), area_avg = ALL competitor dishes classified into that category, plus named cheapest_dish/priciest_dish per category. Added 3 new zero-extra-API-cost signals from data already fetched in search_restaurants: _compute_positioning (ranks us among competitors by estimated cost-for-two), _compute_menu_breadth (our item count vs competitor avg), _compute_cuisine_crowding (competitors sharing our cuisine), _compute_veg_mix (veg/non-veg composition of the area). Fixed a silent full-enrichment crash: _extract_landscape did float(costForTwo) but live data returns strings like "₹500 for two" -- added _parse_cost_for_two regex extraction. Filtered sponsored/ad listings (search_restaurants returned 8/10 results tagged "(Ad)" in the name in live testing) via _is_sponsored + pagination fallback + dedup. Circuit breaker thresholds tuned (FAILURE_THRESHOLD 3-&gt;5, OPEN_SECONDS 1800-&gt;600) since the redesigned enricher makes more Food MCP calls per run.</t>
         </is>
       </c>
       <c r="F56" s="44" t="inlineStr">
         <is>
-          <t>feat: assumption Diff 7 -- competitor deals absorbing predicted walk-in demand</t>
+          <t>feat: category-independent dish classification + positioning/menu-breadth/cuisine-crowding/veg-mix</t>
         </is>
       </c>
       <c r="G56" s="44" t="inlineStr">
         <is>
-          <t>docs/AGENTS.md, docs/ARCHITECTURE.md</t>
+          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md, docs/AGENTS.md</t>
         </is>
       </c>
       <c r="H56" s="45" t="inlineStr">
@@ -16627,7 +16853,7 @@
       </c>
       <c r="I56" s="43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J56" s="43" t="inlineStr">
@@ -16646,26 +16872,22 @@
       </c>
       <c r="N56" s="44" t="inlineStr">
         <is>
-          <t>P6-MI07</t>
+          <t>P6-MI05</t>
         </is>
       </c>
       <c r="O56" s="44" t="inlineStr">
         <is>
-          <t>test_sanity_checker_diff7.py</t>
+          <t>43 tests: test_competitor_category_pricing.py (7), test_competitor_market_context.py (10), test_competitor_landscape_extraction.py (5), test_competitor_enricher_extended.py, test_swiggy_competitor_enricher.py -- all passing; live-verified against real /market/pulse (200 OK, 13.5s cold cache / ~1s warm cache)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="52.05" customHeight="1" s="77">
       <c r="A57" s="43" t="inlineStr">
         <is>
-          <t>P6-MI09</t>
-        </is>
-      </c>
-      <c r="B57" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
+          <t>P6-MI13</t>
+        </is>
+      </c>
+      <c r="B57" s="104" t="n"/>
       <c r="C57" s="44" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -16673,22 +16895,22 @@
       </c>
       <c r="D57" s="44" t="inlineStr">
         <is>
-          <t>Pricing impact model — quantify revenue effect of pricing alerts</t>
+          <t>Personal-data leak fix: your_go_to_items removed from the planning pipeline, not just the display layer</t>
         </is>
       </c>
       <c r="E57" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-06: Pricing impact model added (elasticity model: gap_pct * -0.8 = volume_change_pct; weekly_revenue_impact_inr computed per flagged item, top 5 by absolute impact returned). Rendered as a diverging PricingImpactChart (rose = at-risk, emerald = upside) on /market, honestly scoped to exact dish-name matches only -- a smaller "Exact Menu Matches" card, since exact matching across restaurants is unreliable (see P6-MI12).</t>
+          <t>A tool audit against SWIGGY_INTEGRATION.md found your_go_to_items (Instamart's personal "frequent reorder" data -- confirmed live to return pet food and personal groceries, the dev's own consumer account) was not only being surfaced on /market but was ALSO reaching the real planning pipeline's inventory LLM prompt via ProcurementEnricher._build_prompt(). Removed _fetch_go_to_items() and all call sites entirely -- ProcurementEnricher no longer calls this tool anywhere, not just in its display. Exactly the class of bug CLAUDE.md's Swiggy MCP consumer-data warning exists to prevent.</t>
         </is>
       </c>
       <c r="F57" s="44" t="inlineStr">
         <is>
-          <t>feat: pricing impact model -- quantify revenue effect of competitor price gaps</t>
+          <t>fix: remove your_go_to_items entirely -- was leaking personal consumer data into the planning pipeline</t>
         </is>
       </c>
       <c r="G57" s="44" t="inlineStr">
         <is>
-          <t>docs/AGENTS.md</t>
+          <t>CLAUDE.md (tool table), docs/SWIGGY_INTEGRATION.md</t>
         </is>
       </c>
       <c r="H57" s="45" t="inlineStr">
@@ -16698,7 +16920,7 @@
       </c>
       <c r="I57" s="43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J57" s="43" t="inlineStr">
@@ -16715,51 +16937,43 @@
       <c r="M57" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="N57" s="44" t="inlineStr">
-        <is>
-          <t>P6-MI08</t>
-        </is>
-      </c>
+      <c r="N57" s="44" t="n"/>
       <c r="O57" s="44" t="inlineStr">
         <is>
-          <t>covered in test_swiggy_competitor_enricher.py pricing_impact assertions</t>
+          <t>test_swiggy_procurement_enricher.py rewritten to assert your_go_to_items is never called</t>
         </is>
       </c>
     </row>
     <row r="58" ht="52.05" customHeight="1" s="77">
       <c r="A58" s="43" t="inlineStr">
         <is>
-          <t>P6-MI10</t>
-        </is>
-      </c>
-      <c r="B58" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
+          <t>P6-MI14</t>
+        </is>
+      </c>
+      <c r="B58" s="103" t="n"/>
       <c r="C58" s="44" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D58" s="44" t="inlineStr">
         <is>
-          <t>Proactive scenario recommendation engine</t>
+          <t>/market page redesign -- per-tool detailed cards, Market Context card, 4 new charts</t>
         </is>
       </c>
       <c r="E58" s="44" t="inlineStr">
         <is>
-          <t>DONE 2026-07-06: ScenarioRecommender (domain/services/scenario_recommender.py) built -- LLM-based recommendation with a deterministic rule-based fallback, factoring in recent run history, live market_intel signals, calendar context (INDIAN_HOLIDAYS_2026 added to core/constants.py, 20 holidays), and inventory shortage count. GET /planning/recommend?target_date=YYYY-MM-DD added to api/routes/planning.py.</t>
+          <t>Full redesign of SwiggyLiveMarketPanel.tsx: un-collapsed, tool-labelled, full-detail cards (not summarized), one card per Swiggy tool rather than one card cramming multiple charts. 10 cards: Category Pricing Intelligence (+ named cheapest/priciest per category), Market Context (menu breadth + cuisine crowding + veg mix -- replaces a redundant "All Dishes Found Nearby" card that was just re-displaying data already aggregated elsewhere), Exact Menu Matches (pricing impact, honestly scoped to exact-name matches only), Competitor Swiggy Deals, Competitor Landscape (positioning sentence + full competitor list with rating/distance/delivery-time/cost-for-two/cuisines/offer/veg), Area Occupancy, Dineout Competitor Deals (uncapped), Dineout Slot Deals Tonight (uncapped), Instamart Shortage Prices (uncapped), Ingredient Price Lookup (on-demand search, new GET /market/ingredient-search endpoint). 4 new chart components (CategoryPricingChart, PricingImpactChart, OccupancyBySlotChart, IngredientPriceLookup). Deleted SwiggyMarketIntelPanel.tsx and CompetitorLandscapeChart.tsx (an illegible unlabeled bubble chart, replaced by a labelled list) as dead/superseded. Simplified /market/page.tsx to live market intelligence only, per explicit product direction that /market should not also show the last plan run's Swiggy data.</t>
         </is>
       </c>
       <c r="F58" s="44" t="inlineStr">
         <is>
-          <t>feat: proactive scenario recommendation -- market + history aware</t>
+          <t>feat: /market page redesign -- detailed per-tool cards, 4 new charts, remove redundant/dead components</t>
         </is>
       </c>
       <c r="G58" s="44" t="inlineStr">
         <is>
-          <t>docs/APIS.md, CLAUDE.md</t>
+          <t>None (frontend only)</t>
         </is>
       </c>
       <c r="H58" s="45" t="inlineStr">
@@ -16788,649 +17002,461 @@
       </c>
       <c r="N58" s="44" t="inlineStr">
         <is>
-          <t>P6-MI09</t>
+          <t>P6-MI12</t>
         </is>
       </c>
       <c r="O58" s="44" t="inlineStr">
         <is>
-          <t>test_scenario_recommender.py</t>
+          <t>Manually verified each card renders with live data against a real /market/pulse response</t>
         </is>
       </c>
     </row>
     <row r="59" ht="52.05" customHeight="1" s="77">
-      <c r="A59" s="43" t="inlineStr">
-        <is>
-          <t>P6-MI11</t>
-        </is>
-      </c>
-      <c r="B59" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
-      <c r="C59" s="44" t="inlineStr">
-        <is>
-          <t>Backend + Frontend</t>
-        </is>
-      </c>
-      <c r="D59" s="44" t="inlineStr">
-        <is>
-          <t>Competitor price trend view on /market page</t>
-        </is>
-      </c>
-      <c r="E59" s="44" t="inlineStr">
-        <is>
-          <t>DONE 2026-07-06: GET /market/trends?days=N added -- reads market_intel from stored PlanningRun.final_response across past runs (zero new Swiggy calls), returns per-dish area_avg price history + occupancy signal history. MarketTrendChart.tsx renders both as recharts line charts on /market, dish-selectable, empty state when fewer than 3 data points.</t>
-        </is>
-      </c>
-      <c r="F59" s="44" t="inlineStr">
-        <is>
-          <t>feat: competitor price trend chart on /market -- 7-day history</t>
-        </is>
-      </c>
-      <c r="G59" s="44" t="inlineStr">
-        <is>
-          <t>docs/APIS.md</t>
-        </is>
-      </c>
-      <c r="H59" s="45" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I59" s="43" t="inlineStr">
+      <c r="A59" s="105" t="n"/>
+      <c r="B59" s="105" t="n"/>
+      <c r="C59" s="105" t="n"/>
+      <c r="D59" s="105" t="n"/>
+      <c r="E59" s="105" t="n"/>
+      <c r="F59" s="105" t="n"/>
+      <c r="G59" s="105" t="n"/>
+      <c r="H59" s="105" t="n"/>
+      <c r="I59" s="105" t="n"/>
+      <c r="J59" s="105" t="n"/>
+      <c r="K59" s="105" t="n"/>
+      <c r="L59" s="105" t="n"/>
+      <c r="M59" s="105" t="n"/>
+      <c r="N59" s="105" t="n"/>
+      <c r="O59" s="105" t="n"/>
+    </row>
+    <row r="60" ht="7.95" customHeight="1" s="77">
+      <c r="A60" s="80" t="inlineStr">
+        <is>
+          <t>PLANNED — build in this order (all below work without staging creds unless noted)</t>
+        </is>
+      </c>
+      <c r="B60" s="86" t="n"/>
+      <c r="C60" s="86" t="n"/>
+      <c r="D60" s="86" t="n"/>
+      <c r="E60" s="86" t="n"/>
+      <c r="F60" s="86" t="n"/>
+      <c r="G60" s="86" t="n"/>
+      <c r="H60" s="86" t="n"/>
+      <c r="I60" s="86" t="n"/>
+      <c r="J60" s="86" t="n"/>
+      <c r="K60" s="86" t="n"/>
+      <c r="L60" s="86" t="n"/>
+      <c r="M60" s="86" t="n"/>
+      <c r="N60" s="86" t="n"/>
+      <c r="O60" s="87" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1" s="77">
+      <c r="A61" s="105" t="n"/>
+      <c r="B61" s="105" t="n"/>
+      <c r="C61" s="105" t="n"/>
+      <c r="D61" s="105" t="n"/>
+      <c r="E61" s="105" t="n"/>
+      <c r="F61" s="105" t="n"/>
+      <c r="G61" s="105" t="n"/>
+      <c r="H61" s="105" t="n"/>
+      <c r="I61" s="105" t="n"/>
+      <c r="J61" s="105" t="n"/>
+      <c r="K61" s="105" t="n"/>
+      <c r="L61" s="105" t="n"/>
+      <c r="M61" s="105" t="n"/>
+      <c r="N61" s="105" t="n"/>
+      <c r="O61" s="105" t="n"/>
+    </row>
+    <row r="62" ht="52.05" customHeight="1" s="77">
+      <c r="A62" s="83" t="inlineStr">
+        <is>
+          <t>PRIORITY 1 — Market Intelligence Expansion (remaining)</t>
+        </is>
+      </c>
+      <c r="B62" s="86" t="n"/>
+      <c r="C62" s="86" t="n"/>
+      <c r="D62" s="86" t="n"/>
+      <c r="E62" s="86" t="n"/>
+      <c r="F62" s="86" t="n"/>
+      <c r="G62" s="86" t="n"/>
+      <c r="H62" s="86" t="n"/>
+      <c r="I62" s="86" t="n"/>
+      <c r="J62" s="86" t="n"/>
+      <c r="K62" s="86" t="n"/>
+      <c r="L62" s="86" t="n"/>
+      <c r="M62" s="86" t="n"/>
+      <c r="N62" s="86" t="n"/>
+      <c r="O62" s="87" t="n"/>
+    </row>
+    <row r="63" ht="52.05" customHeight="1" s="77">
+      <c r="A63" s="62" t="inlineStr">
+        <is>
+          <t>P6-MI04</t>
+        </is>
+      </c>
+      <c r="B63" s="63" t="inlineStr">
+        <is>
+          <t>feature/swiggy-chatbot-expansion</t>
+        </is>
+      </c>
+      <c r="C63" s="63" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D63" s="63" t="inlineStr">
+        <is>
+          <t>Chatbot — Dineout competitive queries</t>
+        </is>
+      </c>
+      <c r="E63" s="63" t="inlineStr">
+        <is>
+          <t>Add 3 new Groq function-calling tools to chatbot: get_competitor_deals(cuisine, addressId) answers what deals are competitors running tonight; get_area_occupancy(cuisine, addressId) answers how full are restaurants near me; get_trending_dishes(addressId) answers what are competitors pushing on menus. All use existing Dineout MCP tools: search_restaurants_dineout, get_restaurant_details, get_available_slots. Makes chatbot the single interface for all live Swiggy market queries.</t>
+        </is>
+      </c>
+      <c r="F63" s="63" t="inlineStr">
+        <is>
+          <t>feat: chatbot Dineout queries — competitor deals, area occupancy, trending dishes</t>
+        </is>
+      </c>
+      <c r="G63" s="63" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md (chatbot tools section)</t>
+        </is>
+      </c>
+      <c r="H63" s="54" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I63" s="62" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J59" s="43" t="inlineStr">
+      <c r="J63" s="62" t="n"/>
+      <c r="K63" s="62" t="n"/>
+      <c r="L63" s="62" t="n"/>
+      <c r="M63" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="63" t="n"/>
+      <c r="O63" s="63" t="n"/>
+    </row>
+    <row r="64" ht="7.95" customHeight="1" s="77">
+      <c r="A64" s="105" t="n"/>
+      <c r="B64" s="105" t="n"/>
+      <c r="C64" s="105" t="n"/>
+      <c r="D64" s="105" t="n"/>
+      <c r="E64" s="105" t="n"/>
+      <c r="F64" s="105" t="n"/>
+      <c r="G64" s="105" t="n"/>
+      <c r="H64" s="105" t="n"/>
+      <c r="I64" s="105" t="n"/>
+      <c r="J64" s="105" t="n"/>
+      <c r="K64" s="105" t="n"/>
+      <c r="L64" s="105" t="n"/>
+      <c r="M64" s="105" t="n"/>
+      <c r="N64" s="105" t="n"/>
+      <c r="O64" s="105" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1" s="77">
+      <c r="A65" s="81" t="inlineStr">
+        <is>
+          <t>PRIORITY 2 — Action Queue (approve/reject in plan — no staging needed)</t>
+        </is>
+      </c>
+      <c r="B65" s="86" t="n"/>
+      <c r="C65" s="86" t="n"/>
+      <c r="D65" s="86" t="n"/>
+      <c r="E65" s="86" t="n"/>
+      <c r="F65" s="86" t="n"/>
+      <c r="G65" s="86" t="n"/>
+      <c r="H65" s="86" t="n"/>
+      <c r="I65" s="86" t="n"/>
+      <c r="J65" s="86" t="n"/>
+      <c r="K65" s="86" t="n"/>
+      <c r="L65" s="86" t="n"/>
+      <c r="M65" s="86" t="n"/>
+      <c r="N65" s="86" t="n"/>
+      <c r="O65" s="87" t="n"/>
+    </row>
+    <row r="66" ht="52.05" customHeight="1" s="77">
+      <c r="A66" s="62" t="inlineStr">
+        <is>
+          <t>P6-S32</t>
+        </is>
+      </c>
+      <c r="B66" s="63" t="inlineStr">
+        <is>
+          <t>feature/action-queue</t>
+        </is>
+      </c>
+      <c r="C66" s="63" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D66" s="63" t="inlineStr">
+        <is>
+          <t>ActionQueueService + action_queue table</t>
+        </is>
+      </c>
+      <c r="E66" s="63" t="inlineStr">
+        <is>
+          <t>New table: id, org_id, action_type (AUTO/APPROVE_REQUIRED/RECOMMENDATION), payload jsonb, status (PENDING/APPROVED/EXECUTED/REJECTED/EXPIRED), approved_by, executed_at, error. ActionQueueService CRUD. Plan output includes action_queue section in API response.</t>
+        </is>
+      </c>
+      <c r="F66" s="63" t="inlineStr">
+        <is>
+          <t>feat: ActionQueueService + action_queue table — 3-tier action model with approval lifecycle</t>
+        </is>
+      </c>
+      <c r="G66" s="63" t="inlineStr">
+        <is>
+          <t>docs/ACTION_QUEUE.md (new), docs/APIS.md (action queue endpoints), docs/DECISIONS.md (D-021)</t>
+        </is>
+      </c>
+      <c r="H66" s="54" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I66" s="62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J66" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K59" s="46" t="n">
-        <v>46209</v>
-      </c>
-      <c r="L59" s="46" t="n">
-        <v>46209</v>
-      </c>
-      <c r="M59" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N59" s="44" t="inlineStr">
-        <is>
-          <t>P6-MI10</t>
-        </is>
-      </c>
-      <c r="O59" s="44" t="inlineStr">
-        <is>
-          <t>GET /market/trends verified manually; chart renders correctly in browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="7.95" customHeight="1" s="77">
-      <c r="A60" s="43" t="inlineStr">
-        <is>
-          <t>P6-MI12</t>
-        </is>
-      </c>
-      <c r="B60" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
-      <c r="C60" s="44" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="D60" s="44" t="inlineStr">
-        <is>
-          <t>Category-independent dish classification + market positioning (supersedes exact-name matching)</t>
-        </is>
-      </c>
-      <c r="E60" s="44" t="inlineStr">
-        <is>
-          <t>Discovered mid-session that exact dish-name matching between our menu and competitor menus (the basis of the original dish_prices/pricing_impact design) structurally never aligns -- restaurants essentially never name dishes identically. Rebuilt CompetitorEnricher's core signal around keyword-in-dish-name classification instead (_classify_dish: pizza/pasta/burger/sides/dessert/beverage keyword tuples), independent of exact string matching. _compute_category_pricing rewritten: your_avg = ALL our items in a category (not a matched subset), area_avg = ALL competitor dishes classified into that category, plus named cheapest_dish/priciest_dish per category. Added 3 new zero-extra-API-cost signals from data already fetched in search_restaurants: _compute_positioning (ranks us among competitors by estimated cost-for-two), _compute_menu_breadth (our item count vs competitor avg), _compute_cuisine_crowding (competitors sharing our cuisine), _compute_veg_mix (veg/non-veg composition of the area). Fixed a silent full-enrichment crash: _extract_landscape did float(costForTwo) but live data returns strings like "₹500 for two" -- added _parse_cost_for_two regex extraction. Filtered sponsored/ad listings (search_restaurants returned 8/10 results tagged "(Ad)" in the name in live testing) via _is_sponsored + pagination fallback + dedup. Circuit breaker thresholds tuned (FAILURE_THRESHOLD 3-&gt;5, OPEN_SECONDS 1800-&gt;600) since the redesigned enricher makes more Food MCP calls per run.</t>
-        </is>
-      </c>
-      <c r="F60" s="44" t="inlineStr">
-        <is>
-          <t>feat: category-independent dish classification + positioning/menu-breadth/cuisine-crowding/veg-mix</t>
-        </is>
-      </c>
-      <c r="G60" s="44" t="inlineStr">
-        <is>
-          <t>CLAUDE.md, docs/SWIGGY_INTEGRATION.md, docs/AGENTS.md</t>
-        </is>
-      </c>
-      <c r="H60" s="45" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I60" s="43" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J60" s="43" t="inlineStr">
+      <c r="K66" s="62" t="n"/>
+      <c r="L66" s="62" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="M66" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="63" t="inlineStr">
+        <is>
+          <t>P6-S15</t>
+        </is>
+      </c>
+      <c r="O66" s="63" t="inlineStr">
+        <is>
+          <t>No staging creds needed — action queue is pure backend, no Swiggy write calls yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="52.05" customHeight="1" s="77">
+      <c r="A67" s="62" t="inlineStr">
+        <is>
+          <t>P6-F06</t>
+        </is>
+      </c>
+      <c r="B67" s="63" t="inlineStr">
+        <is>
+          <t>feature/action-queue-ui</t>
+        </is>
+      </c>
+      <c r="C67" s="63" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D67" s="63" t="inlineStr">
+        <is>
+          <t>Action queue UI + procurement tracker</t>
+        </is>
+      </c>
+      <c r="E67" s="63" t="inlineStr">
+        <is>
+          <t>New section below plan output. Lists pending actions with type badge. Approve/Reject buttons for APPROVE_REQUIRED. Instamart cart preview modal (items, total, ETA) before approving checkout. Procurement tracker in inventory panel: placed orders, status, ETA.</t>
+        </is>
+      </c>
+      <c r="F67" s="63" t="inlineStr">
+        <is>
+          <t>feat: action queue UI — approve/reject with cart preview, procurement tracker</t>
+        </is>
+      </c>
+      <c r="G67" s="63" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="H67" s="54" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I67" s="62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J67" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K60" s="46" t="n">
-        <v>46209</v>
-      </c>
-      <c r="L60" s="46" t="n">
-        <v>46209</v>
-      </c>
-      <c r="M60" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="44" t="inlineStr">
-        <is>
-          <t>P6-MI05</t>
-        </is>
-      </c>
-      <c r="O60" s="44" t="inlineStr">
-        <is>
-          <t>43 tests: test_competitor_category_pricing.py (7), test_competitor_market_context.py (10), test_competitor_landscape_extraction.py (5), test_competitor_enricher_extended.py, test_swiggy_competitor_enricher.py -- all passing; live-verified against real /market/pulse (200 OK, 13.5s cold cache / ~1s warm cache)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1" s="77">
-      <c r="A61" s="43" t="inlineStr">
-        <is>
-          <t>P6-MI13</t>
-        </is>
-      </c>
-      <c r="B61" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
-      <c r="C61" s="44" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="D61" s="44" t="inlineStr">
-        <is>
-          <t>Personal-data leak fix: your_go_to_items removed from the planning pipeline, not just the display layer</t>
-        </is>
-      </c>
-      <c r="E61" s="44" t="inlineStr">
-        <is>
-          <t>A tool audit against SWIGGY_INTEGRATION.md found your_go_to_items (Instamart's personal "frequent reorder" data -- confirmed live to return pet food and personal groceries, the dev's own consumer account) was not only being surfaced on /market but was ALSO reaching the real planning pipeline's inventory LLM prompt via ProcurementEnricher._build_prompt(). Removed _fetch_go_to_items() and all call sites entirely -- ProcurementEnricher no longer calls this tool anywhere, not just in its display. Exactly the class of bug CLAUDE.md's Swiggy MCP consumer-data warning exists to prevent.</t>
-        </is>
-      </c>
-      <c r="F61" s="44" t="inlineStr">
-        <is>
-          <t>fix: remove your_go_to_items entirely -- was leaking personal consumer data into the planning pipeline</t>
-        </is>
-      </c>
-      <c r="G61" s="44" t="inlineStr">
-        <is>
-          <t>CLAUDE.md (tool table), docs/SWIGGY_INTEGRATION.md</t>
-        </is>
-      </c>
-      <c r="H61" s="45" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I61" s="43" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J61" s="43" t="inlineStr">
+      <c r="K67" s="62" t="n"/>
+      <c r="L67" s="62" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="M67" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="63" t="inlineStr">
+        <is>
+          <t>P6-S18, P6-F11</t>
+        </is>
+      </c>
+      <c r="O67" s="63" t="inlineStr">
+        <is>
+          <t>Depends on P6-S32 (action_queue in plan API response)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="52.05" customHeight="1" s="77">
+      <c r="A68" s="105" t="n"/>
+      <c r="B68" s="105" t="n"/>
+      <c r="C68" s="105" t="n"/>
+      <c r="D68" s="105" t="n"/>
+      <c r="E68" s="105" t="n"/>
+      <c r="F68" s="105" t="n"/>
+      <c r="G68" s="105" t="n"/>
+      <c r="H68" s="105" t="n"/>
+      <c r="I68" s="105" t="n"/>
+      <c r="J68" s="105" t="n"/>
+      <c r="K68" s="105" t="n"/>
+      <c r="L68" s="105" t="n"/>
+      <c r="M68" s="105" t="n"/>
+      <c r="N68" s="105" t="n"/>
+      <c r="O68" s="105" t="n"/>
+    </row>
+    <row r="69" ht="52.05" customHeight="1" s="77">
+      <c r="A69" s="76" t="inlineStr">
+        <is>
+          <t>PRIORITY 3 — Pipeline Improvements (cost + quality)</t>
+        </is>
+      </c>
+      <c r="B69" s="86" t="n"/>
+      <c r="C69" s="86" t="n"/>
+      <c r="D69" s="86" t="n"/>
+      <c r="E69" s="86" t="n"/>
+      <c r="F69" s="86" t="n"/>
+      <c r="G69" s="86" t="n"/>
+      <c r="H69" s="86" t="n"/>
+      <c r="I69" s="86" t="n"/>
+      <c r="J69" s="86" t="n"/>
+      <c r="K69" s="86" t="n"/>
+      <c r="L69" s="86" t="n"/>
+      <c r="M69" s="86" t="n"/>
+      <c r="N69" s="86" t="n"/>
+      <c r="O69" s="87" t="n"/>
+    </row>
+    <row r="70" ht="7.95" customHeight="1" s="77">
+      <c r="A70" s="62" t="inlineStr">
+        <is>
+          <t>P6-S33</t>
+        </is>
+      </c>
+      <c r="B70" s="63" t="n"/>
+      <c r="C70" s="63" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D70" s="63" t="inlineStr">
+        <is>
+          <t>Structured outputs — tool_choice=required, zero JSON hallucination</t>
+        </is>
+      </c>
+      <c r="E70" s="63" t="inlineStr">
+        <is>
+          <t>Upgrade chatbot Groq calls to tool_choice=required + strict JSON schema. Apply to all 3 Swiggy chatbot tools (search_menu, get_food_orders, search_products). Chatbot function calls never hallucinate JSON. Zero model coupling — works on any provider.</t>
+        </is>
+      </c>
+      <c r="F70" s="63" t="inlineStr">
+        <is>
+          <t>feat: structured outputs — tool_choice=required across all chatbot tools</t>
+        </is>
+      </c>
+      <c r="G70" s="63" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="H70" s="54" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I70" s="62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J70" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K61" s="46" t="n">
-        <v>46209</v>
-      </c>
-      <c r="L61" s="46" t="n">
-        <v>46209</v>
-      </c>
-      <c r="M61" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" s="44" t="n"/>
-      <c r="O61" s="44" t="inlineStr">
-        <is>
-          <t>test_swiggy_procurement_enricher.py rewritten to assert your_go_to_items is never called</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="52.05" customHeight="1" s="77">
-      <c r="A62" s="43" t="inlineStr">
-        <is>
-          <t>P6-MI14</t>
-        </is>
-      </c>
-      <c r="B62" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-extended</t>
-        </is>
-      </c>
-      <c r="C62" s="44" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D62" s="44" t="inlineStr">
-        <is>
-          <t>/market page redesign -- per-tool detailed cards, Market Context card, 4 new charts</t>
-        </is>
-      </c>
-      <c r="E62" s="44" t="inlineStr">
-        <is>
-          <t>Full redesign of SwiggyLiveMarketPanel.tsx: un-collapsed, tool-labelled, full-detail cards (not summarized), one card per Swiggy tool rather than one card cramming multiple charts. 10 cards: Category Pricing Intelligence (+ named cheapest/priciest per category), Market Context (menu breadth + cuisine crowding + veg mix -- replaces a redundant "All Dishes Found Nearby" card that was just re-displaying data already aggregated elsewhere), Exact Menu Matches (pricing impact, honestly scoped to exact-name matches only), Competitor Swiggy Deals, Competitor Landscape (positioning sentence + full competitor list with rating/distance/delivery-time/cost-for-two/cuisines/offer/veg), Area Occupancy, Dineout Competitor Deals (uncapped), Dineout Slot Deals Tonight (uncapped), Instamart Shortage Prices (uncapped), Ingredient Price Lookup (on-demand search, new GET /market/ingredient-search endpoint). 4 new chart components (CategoryPricingChart, PricingImpactChart, OccupancyBySlotChart, IngredientPriceLookup). Deleted SwiggyMarketIntelPanel.tsx and CompetitorLandscapeChart.tsx (an illegible unlabeled bubble chart, replaced by a labelled list) as dead/superseded. Simplified /market/page.tsx to live market intelligence only, per explicit product direction that /market should not also show the last plan run's Swiggy data.</t>
-        </is>
-      </c>
-      <c r="F62" s="44" t="inlineStr">
-        <is>
-          <t>feat: /market page redesign -- detailed per-tool cards, 4 new charts, remove redundant/dead components</t>
-        </is>
-      </c>
-      <c r="G62" s="44" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="H62" s="45" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I62" s="43" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J62" s="43" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K62" s="46" t="n">
-        <v>46209</v>
-      </c>
-      <c r="L62" s="46" t="n">
-        <v>46209</v>
-      </c>
-      <c r="M62" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" s="44" t="inlineStr">
-        <is>
-          <t>P6-MI12</t>
-        </is>
-      </c>
-      <c r="O62" s="44" t="inlineStr">
-        <is>
-          <t>Manually verified each card renders with live data against a real /market/pulse response</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="52.05" customHeight="1" s="77"/>
-    <row r="64" ht="7.95" customHeight="1" s="77">
-      <c r="A64" s="81" t="inlineStr">
-        <is>
-          <t>PRIORITY 2 — Action Queue (approve/reject in plan — no staging needed)</t>
-        </is>
-      </c>
-      <c r="B64" s="86" t="n"/>
-      <c r="C64" s="86" t="n"/>
-      <c r="D64" s="86" t="n"/>
-      <c r="E64" s="86" t="n"/>
-      <c r="F64" s="86" t="n"/>
-      <c r="G64" s="86" t="n"/>
-      <c r="H64" s="86" t="n"/>
-      <c r="I64" s="86" t="n"/>
-      <c r="J64" s="86" t="n"/>
-      <c r="K64" s="86" t="n"/>
-      <c r="L64" s="86" t="n"/>
-      <c r="M64" s="86" t="n"/>
-      <c r="N64" s="86" t="n"/>
-      <c r="O64" s="87" t="n"/>
-    </row>
-    <row r="65" ht="18" customHeight="1" s="77">
-      <c r="A65" s="59" t="inlineStr">
-        <is>
-          <t>P6-S32</t>
-        </is>
-      </c>
-      <c r="B65" s="60" t="inlineStr">
-        <is>
-          <t>feature/action-queue</t>
-        </is>
-      </c>
-      <c r="C65" s="60" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D65" s="60" t="inlineStr">
-        <is>
-          <t>ActionQueueService + action_queue table</t>
-        </is>
-      </c>
-      <c r="E65" s="60" t="inlineStr">
-        <is>
-          <t>New table: id, org_id, action_type (AUTO/APPROVE_REQUIRED/RECOMMENDATION), payload jsonb, status (PENDING/APPROVED/EXECUTED/REJECTED/EXPIRED), approved_by, executed_at, error. ActionQueueService CRUD. Plan output includes action_queue section in API response.</t>
-        </is>
-      </c>
-      <c r="F65" s="60" t="inlineStr">
-        <is>
-          <t>feat: ActionQueueService + action_queue table — 3-tier action model with approval lifecycle</t>
-        </is>
-      </c>
-      <c r="G65" s="60" t="inlineStr">
-        <is>
-          <t>docs/ACTION_QUEUE.md (new), docs/APIS.md (action queue endpoints), docs/DECISIONS.md (D-021)</t>
-        </is>
-      </c>
-      <c r="H65" s="54" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I65" s="59" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J65" s="59" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K65" s="59" t="n"/>
-      <c r="L65" s="59" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="M65" s="61" t="n">
+      <c r="K70" s="62" t="n"/>
+      <c r="L70" s="62" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="M70" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="N65" s="60" t="inlineStr">
-        <is>
-          <t>P6-S15</t>
-        </is>
-      </c>
-      <c r="O65" s="60" t="inlineStr">
-        <is>
-          <t>No staging creds needed — action queue is pure backend, no Swiggy write calls yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="52.05" customHeight="1" s="77">
-      <c r="A66" s="56" t="inlineStr">
-        <is>
-          <t>P6-F06</t>
-        </is>
-      </c>
-      <c r="B66" s="57" t="inlineStr">
-        <is>
-          <t>feature/action-queue-ui</t>
-        </is>
-      </c>
-      <c r="C66" s="57" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D66" s="57" t="inlineStr">
-        <is>
-          <t>Action queue UI + procurement tracker</t>
-        </is>
-      </c>
-      <c r="E66" s="57" t="inlineStr">
-        <is>
-          <t>New section below plan output. Lists pending actions with type badge. Approve/Reject buttons for APPROVE_REQUIRED. Instamart cart preview modal (items, total, ETA) before approving checkout. Procurement tracker in inventory panel: placed orders, status, ETA.</t>
-        </is>
-      </c>
-      <c r="F66" s="57" t="inlineStr">
-        <is>
-          <t>feat: action queue UI — approve/reject with cart preview, procurement tracker</t>
-        </is>
-      </c>
-      <c r="G66" s="57" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="H66" s="54" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I66" s="56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J66" s="56" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K66" s="56" t="n"/>
-      <c r="L66" s="56" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="M66" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="57" t="inlineStr">
-        <is>
-          <t>P6-S18, P6-F11</t>
-        </is>
-      </c>
-      <c r="O66" s="57" t="inlineStr">
-        <is>
-          <t>Depends on P6-S32 (action_queue in plan API response)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="52.05" customHeight="1" s="77"/>
-    <row r="68" ht="52.05" customHeight="1" s="77">
-      <c r="A68" s="76" t="inlineStr">
-        <is>
-          <t>PRIORITY 3 — Pipeline Improvements (cost + quality)</t>
-        </is>
-      </c>
-      <c r="B68" s="86" t="n"/>
-      <c r="C68" s="86" t="n"/>
-      <c r="D68" s="86" t="n"/>
-      <c r="E68" s="86" t="n"/>
-      <c r="F68" s="86" t="n"/>
-      <c r="G68" s="86" t="n"/>
-      <c r="H68" s="86" t="n"/>
-      <c r="I68" s="86" t="n"/>
-      <c r="J68" s="86" t="n"/>
-      <c r="K68" s="86" t="n"/>
-      <c r="L68" s="86" t="n"/>
-      <c r="M68" s="86" t="n"/>
-      <c r="N68" s="86" t="n"/>
-      <c r="O68" s="87" t="n"/>
-    </row>
-    <row r="69" ht="52.05" customHeight="1" s="77">
-      <c r="A69" s="62" t="inlineStr">
-        <is>
-          <t>P6-S33</t>
-        </is>
-      </c>
-      <c r="B69" s="63" t="n"/>
-      <c r="C69" s="63" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D69" s="63" t="inlineStr">
-        <is>
-          <t>Structured outputs — tool_choice=required, zero JSON hallucination</t>
-        </is>
-      </c>
-      <c r="E69" s="63" t="inlineStr">
-        <is>
-          <t>Upgrade chatbot Groq calls to tool_choice=required + strict JSON schema. Apply to all 3 Swiggy chatbot tools (search_menu, get_food_orders, search_products). Chatbot function calls never hallucinate JSON. Zero model coupling — works on any provider.</t>
-        </is>
-      </c>
-      <c r="F69" s="63" t="inlineStr">
-        <is>
-          <t>feat: structured outputs — tool_choice=required across all chatbot tools</t>
-        </is>
-      </c>
-      <c r="G69" s="63" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md</t>
-        </is>
-      </c>
-      <c r="H69" s="54" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I69" s="62" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J69" s="62" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K69" s="62" t="n"/>
-      <c r="L69" s="62" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="M69" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="63" t="inlineStr">
+      <c r="N70" s="63" t="inlineStr">
         <is>
           <t>P6-F05</t>
         </is>
       </c>
-      <c r="O69" s="63" t="inlineStr">
+      <c r="O70" s="63" t="inlineStr">
         <is>
           <t>Schema validation test; chatbot returns valid JSON on 10 consecutive calls</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="7.95" customHeight="1" s="77">
-      <c r="A70" s="56" t="inlineStr">
-        <is>
-          <t>P6-S34</t>
-        </is>
-      </c>
-      <c r="B70" s="57" t="n"/>
-      <c r="C70" s="57" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D70" s="57" t="inlineStr">
-        <is>
-          <t>Prompt caching — 60-90% cost reduction on critic + aggregator</t>
-        </is>
-      </c>
-      <c r="E70" s="57" t="inlineStr">
-        <is>
-          <t>Add Anthropic prompt caching headers to critic and aggregator LLM calls. Both have long system prompts repeated every run. Expected saving: 60-90% of prompt token cost per planning run. Graceful fallback on cache miss. Compatible with Google Gemini too.</t>
-        </is>
-      </c>
-      <c r="F70" s="57" t="inlineStr">
-        <is>
-          <t>feat: prompt caching — cut LLM costs 80% on critic and aggregator nodes</t>
-        </is>
-      </c>
-      <c r="G70" s="57" t="inlineStr">
-        <is>
-          <t>docs/ARCHITECTURE.md</t>
-        </is>
-      </c>
-      <c r="H70" s="54" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I70" s="56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J70" s="56" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K70" s="56" t="n"/>
-      <c r="L70" s="56" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="M70" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="57" t="inlineStr">
-        <is>
-          <t>P6-S33</t>
-        </is>
-      </c>
-      <c r="O70" s="57" t="inlineStr">
-        <is>
-          <t>Cost log shows cache_hit=true on second run of same scenario</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="77">
       <c r="A71" s="62" t="inlineStr">
         <is>
-          <t>P6-S38</t>
-        </is>
-      </c>
-      <c r="B71" s="63" t="inlineStr">
-        <is>
-          <t>feature/debate-critic</t>
-        </is>
-      </c>
+          <t>P6-S34</t>
+        </is>
+      </c>
+      <c r="B71" s="63" t="n"/>
       <c r="C71" s="63" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="D71" s="63" t="inlineStr">
         <is>
-          <t>Multi-agent debate critic — two critic instances, consensus scoring</t>
+          <t>Prompt caching — 60-90% cost reduction on critic + aggregator</t>
         </is>
       </c>
       <c r="E71" s="63" t="inlineStr">
         <is>
-          <t>Run two LLM critic instances with opposing system prompts (optimistic vs conservative). Structured debate: each scores the plan, flags disagreements, moderator LLM resolves. Final verdict is consensus or flagged-disagreement. Provably better plan quality than single critic. Zero model coupling.</t>
+          <t>Add Anthropic prompt caching headers to critic and aggregator LLM calls. Both have long system prompts repeated every run. Expected saving: 60-90% of prompt token cost per planning run. Graceful fallback on cache miss. Compatible with Google Gemini too.</t>
         </is>
       </c>
       <c r="F71" s="63" t="inlineStr">
         <is>
-          <t>feat: multi-agent debate critic — consensus scoring, catches more edge cases</t>
+          <t>feat: prompt caching — cut LLM costs 80% on critic and aggregator nodes</t>
         </is>
       </c>
       <c r="G71" s="63" t="inlineStr">
         <is>
-          <t>docs/AGENTS.md</t>
+          <t>docs/ARCHITECTURE.md</t>
         </is>
       </c>
       <c r="H71" s="54" t="inlineStr">
@@ -17440,7 +17466,7 @@
       </c>
       <c r="I71" s="62" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J71" s="62" t="inlineStr">
@@ -17451,7 +17477,7 @@
       <c r="K71" s="62" t="n"/>
       <c r="L71" s="62" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="M71" s="64" t="n">
@@ -17459,634 +17485,694 @@
       </c>
       <c r="N71" s="63" t="inlineStr">
         <is>
+          <t>P6-S33</t>
+        </is>
+      </c>
+      <c r="O71" s="63" t="inlineStr">
+        <is>
+          <t>Cost log shows cache_hit=true on second run of same scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="52.05" customHeight="1" s="77">
+      <c r="A72" s="62" t="inlineStr">
+        <is>
+          <t>P6-S38</t>
+        </is>
+      </c>
+      <c r="B72" s="63" t="inlineStr">
+        <is>
+          <t>feature/debate-critic</t>
+        </is>
+      </c>
+      <c r="C72" s="63" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D72" s="63" t="inlineStr">
+        <is>
+          <t>Multi-agent debate critic — two critic instances, consensus scoring</t>
+        </is>
+      </c>
+      <c r="E72" s="63" t="inlineStr">
+        <is>
+          <t>Run two LLM critic instances with opposing system prompts (optimistic vs conservative). Structured debate: each scores the plan, flags disagreements, moderator LLM resolves. Final verdict is consensus or flagged-disagreement. Provably better plan quality than single critic. Zero model coupling.</t>
+        </is>
+      </c>
+      <c r="F72" s="63" t="inlineStr">
+        <is>
+          <t>feat: multi-agent debate critic — consensus scoring, catches more edge cases</t>
+        </is>
+      </c>
+      <c r="G72" s="63" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="H72" s="54" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I72" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J72" s="62" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K72" s="62" t="n"/>
+      <c r="L72" s="62" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="M72" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="63" t="inlineStr">
+        <is>
           <t>P6-S35</t>
         </is>
       </c>
-      <c r="O71" s="63" t="inlineStr">
+      <c r="O72" s="63" t="inlineStr">
         <is>
           <t>Debate resolves on 5 test plans; disagreement cases escalate correctly</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="52.05" customHeight="1" s="77">
-      <c r="A72" s="56" t="inlineStr">
+    <row r="73" ht="52.05" customHeight="1" s="77">
+      <c r="A73" s="62" t="inlineStr">
         <is>
           <t>P6-S35</t>
         </is>
       </c>
-      <c r="B72" s="57" t="inlineStr">
+      <c r="B73" s="63" t="inlineStr">
         <is>
           <t>feature/workflow-system</t>
         </is>
       </c>
-      <c r="C72" s="57" t="inlineStr">
+      <c r="C73" s="63" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D72" s="57" t="inlineStr">
+      <c r="D73" s="63" t="inlineStr">
         <is>
           <t>Restaurant workflow system — owner-defined trigger-condition-action automations</t>
         </is>
       </c>
-      <c r="E72" s="57" t="inlineStr">
+      <c r="E73" s="63" t="inlineStr">
         <is>
           <t>New table: workflows (org_id, trigger, condition_json, action_type, action_payload, active). Triggers: AFTER_PLANNING_RUN, DAILY_BRIEF, ON_THRESHOLD. Actions: SEND_WHATSAPP, QUEUE_ACTION, CALL_WEBHOOK. WorkflowEngine evaluates conditions post-run and fires actions. /workflows UI page. Turns CortexKitchen from a tool into an OS.</t>
         </is>
       </c>
-      <c r="F72" s="57" t="inlineStr">
+      <c r="F73" s="63" t="inlineStr">
         <is>
           <t>feat: workflow system — restaurant owners define custom automations</t>
         </is>
       </c>
-      <c r="G72" s="57" t="inlineStr">
+      <c r="G73" s="63" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md, docs/APIS.md</t>
         </is>
       </c>
-      <c r="H72" s="54" t="inlineStr">
+      <c r="H73" s="54" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I72" s="56" t="inlineStr">
+      <c r="I73" s="62" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J72" s="56" t="inlineStr">
+      <c r="J73" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K72" s="56" t="n"/>
-      <c r="L72" s="56" t="inlineStr">
+      <c r="K73" s="62" t="n"/>
+      <c r="L73" s="62" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="M72" s="58" t="n">
+      <c r="M73" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="N72" s="57" t="inlineStr">
+      <c r="N73" s="63" t="inlineStr">
         <is>
           <t>P6-S20-UNRESOLVED</t>
         </is>
       </c>
-      <c r="O72" s="57" t="inlineStr">
+      <c r="O73" s="63" t="inlineStr">
         <is>
           <t>End-to-end: planning run fires whatsapp trigger; webhook called on threshold breach</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="52.05" customHeight="1" s="77"/>
     <row r="74" ht="52.05" customHeight="1" s="77">
-      <c r="A74" s="78" t="inlineStr">
+      <c r="A74" s="105" t="n"/>
+      <c r="B74" s="105" t="n"/>
+      <c r="C74" s="105" t="n"/>
+      <c r="D74" s="105" t="n"/>
+      <c r="E74" s="105" t="n"/>
+      <c r="F74" s="105" t="n"/>
+      <c r="G74" s="105" t="n"/>
+      <c r="H74" s="105" t="n"/>
+      <c r="I74" s="105" t="n"/>
+      <c r="J74" s="105" t="n"/>
+      <c r="K74" s="105" t="n"/>
+      <c r="L74" s="105" t="n"/>
+      <c r="M74" s="105" t="n"/>
+      <c r="N74" s="105" t="n"/>
+      <c r="O74" s="105" t="n"/>
+    </row>
+    <row r="75" ht="7.95" customHeight="1" s="77">
+      <c r="A75" s="78" t="inlineStr">
         <is>
           <t>PRIORITY 4 — Product Modes (brief mode + live monitor)</t>
         </is>
       </c>
-      <c r="B74" s="86" t="n"/>
-      <c r="C74" s="86" t="n"/>
-      <c r="D74" s="86" t="n"/>
-      <c r="E74" s="86" t="n"/>
-      <c r="F74" s="86" t="n"/>
-      <c r="G74" s="86" t="n"/>
-      <c r="H74" s="86" t="n"/>
-      <c r="I74" s="86" t="n"/>
-      <c r="J74" s="86" t="n"/>
-      <c r="K74" s="86" t="n"/>
-      <c r="L74" s="86" t="n"/>
-      <c r="M74" s="86" t="n"/>
-      <c r="N74" s="86" t="n"/>
-      <c r="O74" s="87" t="n"/>
-    </row>
-    <row r="75" ht="7.95" customHeight="1" s="77">
-      <c r="A75" s="65" t="inlineStr">
+      <c r="B75" s="86" t="n"/>
+      <c r="C75" s="86" t="n"/>
+      <c r="D75" s="86" t="n"/>
+      <c r="E75" s="86" t="n"/>
+      <c r="F75" s="86" t="n"/>
+      <c r="G75" s="86" t="n"/>
+      <c r="H75" s="86" t="n"/>
+      <c r="I75" s="86" t="n"/>
+      <c r="J75" s="86" t="n"/>
+      <c r="K75" s="86" t="n"/>
+      <c r="L75" s="86" t="n"/>
+      <c r="M75" s="86" t="n"/>
+      <c r="N75" s="86" t="n"/>
+      <c r="O75" s="87" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1" s="77">
+      <c r="A76" s="62" t="inlineStr">
         <is>
           <t>P6-S36</t>
         </is>
       </c>
-      <c r="B75" s="66" t="n"/>
-      <c r="C75" s="66" t="inlineStr">
+      <c r="B76" s="63" t="n"/>
+      <c r="C76" s="63" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D75" s="66" t="inlineStr">
+      <c r="D76" s="63" t="inlineStr">
         <is>
           <t>LiveMonitorService — SSE feed during service hours</t>
         </is>
       </c>
-      <c r="E75" s="66" t="inlineStr">
+      <c r="E76" s="63" t="inlineStr">
         <is>
           <t>APScheduler-managed SSE stream active 12:00-14:00 and 19:00-22:00 IST. Polls every 30s: get_food_orders (activeOnly=true) for active delivery orders, track_food_order for in-flight ETAs, track_order for Instamart procurement status. Pushes events to /live page frontend. Alerts on: delivery &gt; SLA threshold, order spike, ingredient delivery confirmed.</t>
         </is>
       </c>
-      <c r="F75" s="66" t="inlineStr">
+      <c r="F76" s="63" t="inlineStr">
         <is>
           <t>feat: LiveMonitorService — real-time Swiggy SSE during service hours (orders + procurement)</t>
         </is>
       </c>
-      <c r="G75" s="66" t="inlineStr">
+      <c r="G76" s="63" t="inlineStr">
         <is>
           <t>docs/PRODUCT_MODES.md (live monitor section)</t>
         </is>
       </c>
-      <c r="H75" s="54" t="inlineStr">
+      <c r="H76" s="54" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I75" s="65" t="inlineStr">
+      <c r="I76" s="62" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J75" s="65" t="inlineStr">
+      <c r="J76" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K75" s="65" t="n"/>
-      <c r="L75" s="65" t="inlineStr">
+      <c r="K76" s="62" t="n"/>
+      <c r="L76" s="62" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="M75" s="67" t="n">
+      <c r="M76" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="N75" s="66" t="inlineStr">
+      <c r="N76" s="63" t="inlineStr">
         <is>
           <t>P6-S22-UNRESOLVED, P6-S43</t>
         </is>
       </c>
-      <c r="O75" s="66" t="inlineStr">
+      <c r="O76" s="63" t="inlineStr">
         <is>
           <t>SSE stream active only during service hours IST; events emitted on each 30s poll; delivery threshold alert fires; stream stops outside service window.</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1" s="77">
-      <c r="A76" s="56" t="inlineStr">
+    <row r="77" ht="52.05" customHeight="1" s="77">
+      <c r="A77" s="62" t="inlineStr">
         <is>
           <t>P6-F07</t>
         </is>
       </c>
-      <c r="B76" s="57" t="n"/>
-      <c r="C76" s="57" t="inlineStr">
+      <c r="B77" s="63" t="n"/>
+      <c r="C77" s="63" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D76" s="57" t="inlineStr">
+      <c r="D77" s="63" t="inlineStr">
         <is>
           <t>/brief page — daily morning briefing</t>
         </is>
       </c>
-      <c r="E76" s="57" t="inlineStr">
+      <c r="E77" s="63" t="inlineStr">
         <is>
           <t>New route /brief. Overnight Swiggy performance (orders, avg delivery time, late %), today's demand forecast vs yesterday, top 3 action priorities, market snapshot. Auto-refreshes if brief is stale. Empty state when no brief yet.</t>
         </is>
       </c>
-      <c r="F76" s="57" t="inlineStr">
+      <c r="F77" s="63" t="inlineStr">
         <is>
           <t>feat: /brief page — daily morning operational briefing</t>
         </is>
       </c>
-      <c r="G76" s="57" t="inlineStr">
+      <c r="G77" s="63" t="inlineStr">
         <is>
           <t>None (frontend only)</t>
         </is>
       </c>
-      <c r="H76" s="54" t="inlineStr">
+      <c r="H77" s="54" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I76" s="56" t="inlineStr">
+      <c r="I77" s="62" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J76" s="56" t="inlineStr">
+      <c r="J77" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K76" s="56" t="n"/>
-      <c r="L76" s="56" t="inlineStr">
+      <c r="K77" s="62" t="n"/>
+      <c r="L77" s="62" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="M76" s="58" t="n">
+      <c r="M77" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="N76" s="57" t="inlineStr">
+      <c r="N77" s="63" t="inlineStr">
         <is>
           <t>P6-S44, P6-F11</t>
         </is>
       </c>
-      <c r="O76" s="57" t="inlineStr">
+      <c r="O77" s="63" t="inlineStr">
         <is>
           <t>Depends on P6-S22-UNRESOLVED (BriefingService)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="52.05" customHeight="1" s="77">
-      <c r="A77" s="65" t="inlineStr">
+    <row r="78" ht="52.05" customHeight="1" s="77">
+      <c r="A78" s="62" t="inlineStr">
         <is>
           <t>P6-F08</t>
         </is>
       </c>
-      <c r="B77" s="66" t="n"/>
-      <c r="C77" s="66" t="inlineStr">
+      <c r="B78" s="63" t="n"/>
+      <c r="C78" s="63" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D77" s="66" t="inlineStr">
+      <c r="D78" s="63" t="inlineStr">
         <is>
           <t>/live page — real-time service monitor</t>
         </is>
       </c>
-      <c r="E77" s="66" t="inlineStr">
+      <c r="E78" s="63" t="inlineStr">
         <is>
           <t>New route /live. Kitchen display-grade SSE feed from LiveMonitorService (P6-S36). Shows active Swiggy delivery orders with ETA countdown, Instamart procurement status with delivery ETA, alert banner on delivery spike or ingredient arrival. Swiggy logo + 'Live via Swiggy MCP' badge. Page shows inactive state outside service hours (12-14h, 19-22h IST).</t>
         </is>
       </c>
-      <c r="F77" s="66" t="inlineStr">
+      <c r="F78" s="63" t="inlineStr">
         <is>
           <t>feat: /live page — SSE kitchen display for active orders and procurement tracking</t>
         </is>
       </c>
-      <c r="G77" s="66" t="inlineStr">
+      <c r="G78" s="63" t="inlineStr">
         <is>
           <t>None (frontend only)</t>
         </is>
       </c>
-      <c r="H77" s="54" t="inlineStr">
+      <c r="H78" s="54" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I77" s="65" t="inlineStr">
+      <c r="I78" s="62" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J77" s="65" t="inlineStr">
+      <c r="J78" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K77" s="65" t="n"/>
-      <c r="L77" s="65" t="inlineStr">
+      <c r="K78" s="62" t="n"/>
+      <c r="L78" s="62" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="M77" s="67" t="n">
+      <c r="M78" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="N77" s="66" t="inlineStr">
+      <c r="N78" s="63" t="inlineStr">
         <is>
           <t>P6-S36, P6-F11</t>
         </is>
       </c>
-      <c r="O77" s="66" t="inlineStr">
+      <c r="O78" s="63" t="inlineStr">
         <is>
           <t>SSE events render in real time; ETA countdown ticks; alert banner fires on delivery spike; Swiggy branding visible; inactive state shown outside service hours.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="52.05" customHeight="1" s="77"/>
     <row r="79" ht="7.95" customHeight="1" s="77">
-      <c r="A79" s="76" t="inlineStr">
+      <c r="A79" s="105" t="n"/>
+      <c r="B79" s="105" t="n"/>
+      <c r="C79" s="105" t="n"/>
+      <c r="D79" s="105" t="n"/>
+      <c r="E79" s="105" t="n"/>
+      <c r="F79" s="105" t="n"/>
+      <c r="G79" s="105" t="n"/>
+      <c r="H79" s="105" t="n"/>
+      <c r="I79" s="105" t="n"/>
+      <c r="J79" s="105" t="n"/>
+      <c r="K79" s="105" t="n"/>
+      <c r="L79" s="105" t="n"/>
+      <c r="M79" s="105" t="n"/>
+      <c r="N79" s="105" t="n"/>
+      <c r="O79" s="105" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1" s="77">
+      <c r="A80" s="76" t="inlineStr">
         <is>
           <t>PRIORITY 5 — Voice Interface + MCP Tools</t>
         </is>
       </c>
-      <c r="B79" s="86" t="n"/>
-      <c r="C79" s="86" t="n"/>
-      <c r="D79" s="86" t="n"/>
-      <c r="E79" s="86" t="n"/>
-      <c r="F79" s="86" t="n"/>
-      <c r="G79" s="86" t="n"/>
-      <c r="H79" s="86" t="n"/>
-      <c r="I79" s="86" t="n"/>
-      <c r="J79" s="86" t="n"/>
-      <c r="K79" s="86" t="n"/>
-      <c r="L79" s="86" t="n"/>
-      <c r="M79" s="86" t="n"/>
-      <c r="N79" s="86" t="n"/>
-      <c r="O79" s="87" t="n"/>
-    </row>
-    <row r="80" ht="18" customHeight="1" s="77">
-      <c r="A80" s="62" t="inlineStr">
+      <c r="B80" s="86" t="n"/>
+      <c r="C80" s="86" t="n"/>
+      <c r="D80" s="86" t="n"/>
+      <c r="E80" s="86" t="n"/>
+      <c r="F80" s="86" t="n"/>
+      <c r="G80" s="86" t="n"/>
+      <c r="H80" s="86" t="n"/>
+      <c r="I80" s="86" t="n"/>
+      <c r="J80" s="86" t="n"/>
+      <c r="K80" s="86" t="n"/>
+      <c r="L80" s="86" t="n"/>
+      <c r="M80" s="86" t="n"/>
+      <c r="N80" s="86" t="n"/>
+      <c r="O80" s="87" t="n"/>
+    </row>
+    <row r="81" ht="52.05" customHeight="1" s="77">
+      <c r="A81" s="62" t="inlineStr">
         <is>
           <t>P6-R01</t>
         </is>
       </c>
-      <c r="B80" s="63" t="inlineStr">
+      <c r="B81" s="63" t="inlineStr">
         <is>
           <t>feature/voice-interface</t>
         </is>
       </c>
-      <c r="C80" s="63" t="inlineStr">
+      <c r="C81" s="63" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D80" s="63" t="inlineStr">
+      <c r="D81" s="63" t="inlineStr">
         <is>
           <t>Voice interface — Whisper + RAG chatbot</t>
         </is>
       </c>
-      <c r="E80" s="63" t="inlineStr">
+      <c r="E81" s="63" t="inlineStr">
         <is>
           <t>Whisper transcription on browser-recorded question (MediaRecorder API). RAG chatbot (P5-12) answers. TTS reads back. Manager asks questions while walking the floor. Works with both synthetic and real Swiggy data now in DB. Blocked on P5-12 (already done).</t>
         </is>
       </c>
-      <c r="F80" s="63" t="inlineStr">
+      <c r="F81" s="63" t="inlineStr">
         <is>
           <t>feat: voice interface — Whisper transcription + RAG answer + TTS readback</t>
         </is>
       </c>
-      <c r="G80" s="63" t="inlineStr">
+      <c r="G81" s="63" t="inlineStr">
         <is>
           <t>docs/PRODUCT_MODES.md (voice section)</t>
         </is>
       </c>
-      <c r="H80" s="54" t="inlineStr">
+      <c r="H81" s="54" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I80" s="62" t="inlineStr">
+      <c r="I81" s="62" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J80" s="62" t="inlineStr">
+      <c r="J81" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K80" s="62" t="n"/>
-      <c r="L80" s="62" t="inlineStr">
+      <c r="K81" s="62" t="n"/>
+      <c r="L81" s="62" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="M80" s="64" t="n">
+      <c r="M81" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="N80" s="63" t="inlineStr">
+      <c r="N81" s="63" t="inlineStr">
         <is>
           <t>P6-S44</t>
         </is>
       </c>
-      <c r="O80" s="63" t="inlineStr">
+      <c r="O81" s="63" t="inlineStr">
         <is>
           <t>Transcription accuracy smoke test; end-to-end voice → RAG answer → TTS; works with real Swiggy data in DB</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="52.05" customHeight="1" s="77">
-      <c r="A81" s="56" t="inlineStr">
+    <row r="82" ht="52.05" customHeight="1" s="77">
+      <c r="A82" s="62" t="inlineStr">
         <is>
           <t>P6-S37</t>
         </is>
       </c>
-      <c r="B81" s="57" t="n"/>
-      <c r="C81" s="57" t="inlineStr">
+      <c r="B82" s="63" t="n"/>
+      <c r="C82" s="63" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D81" s="57" t="inlineStr">
+      <c r="D82" s="63" t="inlineStr">
         <is>
           <t>3 new CortexKitchen MCP server tools</t>
         </is>
       </c>
-      <c r="E81" s="57" t="inlineStr">
+      <c r="E82" s="63" t="inlineStr">
         <is>
           <t>Add to mcp_server.py: get_market_brief (calls MarketIntelService live, returns competitor snapshot for Claude Desktop), get_action_queue (pending actions awaiting approval), approve_action (owner approves from Claude Desktop, triggers execution). JWT auth on all 3.</t>
         </is>
       </c>
-      <c r="F81" s="57" t="inlineStr">
+      <c r="F82" s="63" t="inlineStr">
         <is>
           <t>feat: 3 new MCP tools — get_market_brief, get_action_queue, approve_action</t>
         </is>
       </c>
-      <c r="G81" s="57" t="inlineStr">
+      <c r="G82" s="63" t="inlineStr">
         <is>
           <t>docs/APIS.md (MCP tools section), docs/ARCHITECTURE.md (MCP server updated)</t>
         </is>
       </c>
-      <c r="H81" s="54" t="inlineStr">
+      <c r="H82" s="54" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I81" s="56" t="inlineStr">
+      <c r="I82" s="62" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J81" s="56" t="inlineStr">
+      <c r="J82" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K81" s="56" t="n"/>
-      <c r="L81" s="56" t="inlineStr">
+      <c r="K82" s="62" t="n"/>
+      <c r="L82" s="62" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="M81" s="58" t="n">
+      <c r="M82" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="N81" s="57" t="inlineStr">
+      <c r="N82" s="63" t="inlineStr">
         <is>
           <t>P6-S32</t>
         </is>
       </c>
-      <c r="O81" s="57" t="inlineStr">
+      <c r="O82" s="63" t="inlineStr">
         <is>
           <t>All 3 tools smoke-tested in Claude Desktop; approve_action triggers execution end-to-end; JWT enforced</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="52.05" customHeight="1" s="77"/>
     <row r="83" ht="52.05" customHeight="1" s="77">
-      <c r="A83" s="76" t="inlineStr">
+      <c r="A83" s="105" t="n"/>
+      <c r="B83" s="105" t="n"/>
+      <c r="C83" s="105" t="n"/>
+      <c r="D83" s="105" t="n"/>
+      <c r="E83" s="105" t="n"/>
+      <c r="F83" s="105" t="n"/>
+      <c r="G83" s="105" t="n"/>
+      <c r="H83" s="105" t="n"/>
+      <c r="I83" s="105" t="n"/>
+      <c r="J83" s="105" t="n"/>
+      <c r="K83" s="105" t="n"/>
+      <c r="L83" s="105" t="n"/>
+      <c r="M83" s="105" t="n"/>
+      <c r="N83" s="105" t="n"/>
+      <c r="O83" s="105" t="n"/>
+    </row>
+    <row r="84" ht="7.95" customHeight="1" s="77">
+      <c r="A84" s="76" t="inlineStr">
         <is>
           <t>PRIORITY 6 — Infra + Eval (CI fixes, RAGAS)</t>
         </is>
       </c>
-      <c r="B83" s="86" t="n"/>
-      <c r="C83" s="86" t="n"/>
-      <c r="D83" s="86" t="n"/>
-      <c r="E83" s="86" t="n"/>
-      <c r="F83" s="86" t="n"/>
-      <c r="G83" s="86" t="n"/>
-      <c r="H83" s="86" t="n"/>
-      <c r="I83" s="86" t="n"/>
-      <c r="J83" s="86" t="n"/>
-      <c r="K83" s="86" t="n"/>
-      <c r="L83" s="86" t="n"/>
-      <c r="M83" s="86" t="n"/>
-      <c r="N83" s="86" t="n"/>
-      <c r="O83" s="87" t="n"/>
-    </row>
-    <row r="84" ht="7.95" customHeight="1" s="77">
-      <c r="A84" s="62" t="inlineStr">
+      <c r="B84" s="86" t="n"/>
+      <c r="C84" s="86" t="n"/>
+      <c r="D84" s="86" t="n"/>
+      <c r="E84" s="86" t="n"/>
+      <c r="F84" s="86" t="n"/>
+      <c r="G84" s="86" t="n"/>
+      <c r="H84" s="86" t="n"/>
+      <c r="I84" s="86" t="n"/>
+      <c r="J84" s="86" t="n"/>
+      <c r="K84" s="86" t="n"/>
+      <c r="L84" s="86" t="n"/>
+      <c r="M84" s="86" t="n"/>
+      <c r="N84" s="86" t="n"/>
+      <c r="O84" s="87" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1" s="77">
+      <c r="A85" s="62" t="inlineStr">
         <is>
           <t>P6-S39</t>
         </is>
       </c>
-      <c r="B84" s="63" t="n"/>
-      <c r="C84" s="63" t="inlineStr">
+      <c r="B85" s="63" t="n"/>
+      <c r="C85" s="63" t="inlineStr">
         <is>
           <t>Infra</t>
         </is>
       </c>
-      <c r="D84" s="63" t="inlineStr">
+      <c r="D85" s="63" t="inlineStr">
         <is>
           <t>Fix SQLite/JSONB test-infra gap blocking full CI coverage</t>
         </is>
       </c>
-      <c r="E84" s="63" t="inlineStr">
+      <c r="E85" s="63" t="inlineStr">
         <is>
           <t>test_swiggy_reservation_sync.py and test_connector_repository.py are excluded from the CI unit-tests job (P6-Q03) because they spin up a real SQLite engine and connectors.connector_metadata uses Postgres' JSONB column type, which SQLite's compiler can't render. Either give the column a SQLite-compatible fallback type for tests, or run these two files against a real Postgres service container in CI (docker-compose.yml already defines postgres:16 for local dev -- same image could back a CI service).</t>
         </is>
       </c>
-      <c r="F84" s="63" t="inlineStr">
+      <c r="F85" s="63" t="inlineStr">
         <is>
           <t>fix: SQLite-compatible JSONB handling (or Postgres CI service) for excluded test files</t>
         </is>
       </c>
-      <c r="G84" s="63" t="inlineStr">
+      <c r="G85" s="63" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H84" s="54" t="inlineStr">
+      <c r="H85" s="54" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I84" s="62" t="inlineStr">
+      <c r="I85" s="62" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J84" s="62" t="inlineStr">
+      <c r="J85" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K84" s="62" t="n"/>
-      <c r="L84" s="62" t="n"/>
-      <c r="M84" s="64" t="n">
+      <c r="K85" s="62" t="n"/>
+      <c r="L85" s="62" t="n"/>
+      <c r="M85" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="N84" s="63" t="inlineStr">
+      <c r="N85" s="63" t="inlineStr">
         <is>
           <t>P6-S23</t>
         </is>
       </c>
-      <c r="O84" s="63" t="n"/>
-    </row>
-    <row r="85" ht="18" customHeight="1" s="77">
-      <c r="A85" s="56" t="inlineStr">
-        <is>
-          <t>P6-S40</t>
-        </is>
-      </c>
-      <c r="B85" s="57" t="n"/>
-      <c r="C85" s="57" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D85" s="57" t="inlineStr">
-        <is>
-          <t>Promote reviewed RAGAS/DeepEval candidates into curated eval files</t>
-        </is>
-      </c>
-      <c r="E85" s="57" t="inlineStr">
-        <is>
-          <t>build_ragas_dataset.py / build_deepeval_dataset.py (P6-Q03) produce .candidates.json files from live approved runs but never auto-merge them -- ground_truth needs human verification by design. Needs a recurring habit of actually running these periodically and hand-promoting reviewed candidates into complaint_rag_samples.json / test_deepeval_quality.py, or the static datasets stay frozen at today's size forever.</t>
-        </is>
-      </c>
-      <c r="F85" s="57" t="inlineStr">
-        <is>
-          <t>chore: promote reviewed eval candidates into curated datasets</t>
-        </is>
-      </c>
-      <c r="G85" s="57" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H85" s="54" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I85" s="56" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J85" s="56" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K85" s="56" t="n"/>
-      <c r="L85" s="56" t="n"/>
-      <c r="M85" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="57" t="inlineStr">
-        <is>
-          <t>P6-S23</t>
-        </is>
-      </c>
-      <c r="O85" s="57" t="n"/>
+      <c r="O85" s="63" t="n"/>
     </row>
     <row r="86" ht="52.05" customHeight="1" s="77">
       <c r="A86" s="62" t="inlineStr">
         <is>
-          <t>P6-S41</t>
+          <t>P6-S40</t>
         </is>
       </c>
       <c r="B86" s="63" t="n"/>
       <c r="C86" s="63" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D86" s="63" t="inlineStr">
         <is>
-          <t>Regenerate golden_runs.json against real production data</t>
+          <t>Promote reviewed RAGAS/DeepEval candidates into curated eval files</t>
         </is>
       </c>
       <c r="E86" s="63" t="inlineStr">
         <is>
-          <t>build_golden_dataset.py's key-path bug is fixed (P6-Q03) but the checked-in fixture still reflects the old, always-empty extraction, since regenerating it requires a live Postgres populated with real run history, which wasn't available during the fix. Run scripts/build_golden_dataset.py locally once docker-compose services are up to refresh it with corrected shortage/restock data.</t>
+          <t>build_ragas_dataset.py / build_deepeval_dataset.py (P6-Q03) produce .candidates.json files from live approved runs but never auto-merge them -- ground_truth needs human verification by design. Needs a recurring habit of actually running these periodically and hand-promoting reviewed candidates into complaint_rag_samples.json / test_deepeval_quality.py, or the static datasets stay frozen at today's size forever.</t>
         </is>
       </c>
       <c r="F86" s="63" t="inlineStr">
         <is>
-          <t>chore: regenerate golden_runs.json with corrected extraction logic</t>
+          <t>chore: promote reviewed eval candidates into curated datasets</t>
         </is>
       </c>
       <c r="G86" s="63" t="inlineStr">
@@ -18101,7 +18187,7 @@
       </c>
       <c r="I86" s="62" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J86" s="62" t="inlineStr">
@@ -18121,281 +18207,305 @@
       </c>
       <c r="O86" s="63" t="n"/>
     </row>
-    <row r="87" ht="7.95" customHeight="1" s="77"/>
+    <row r="87" ht="7.95" customHeight="1" s="77">
+      <c r="A87" s="62" t="inlineStr">
+        <is>
+          <t>P6-S41</t>
+        </is>
+      </c>
+      <c r="B87" s="63" t="n"/>
+      <c r="C87" s="63" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D87" s="63" t="inlineStr">
+        <is>
+          <t>Regenerate golden_runs.json against real production data</t>
+        </is>
+      </c>
+      <c r="E87" s="63" t="inlineStr">
+        <is>
+          <t>build_golden_dataset.py's key-path bug is fixed (P6-Q03) but the checked-in fixture still reflects the old, always-empty extraction, since regenerating it requires a live Postgres populated with real run history, which wasn't available during the fix. Run scripts/build_golden_dataset.py locally once docker-compose services are up to refresh it with corrected shortage/restock data.</t>
+        </is>
+      </c>
+      <c r="F87" s="63" t="inlineStr">
+        <is>
+          <t>chore: regenerate golden_runs.json with corrected extraction logic</t>
+        </is>
+      </c>
+      <c r="G87" s="63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H87" s="54" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I87" s="62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J87" s="62" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K87" s="62" t="n"/>
+      <c r="L87" s="62" t="n"/>
+      <c r="M87" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="63" t="inlineStr">
+        <is>
+          <t>P6-S23</t>
+        </is>
+      </c>
+      <c r="O87" s="63" t="n"/>
+    </row>
     <row r="88" ht="18" customHeight="1" s="77">
-      <c r="A88" s="76" t="inlineStr">
+      <c r="A88" s="105" t="n"/>
+      <c r="B88" s="105" t="n"/>
+      <c r="C88" s="105" t="n"/>
+      <c r="D88" s="105" t="n"/>
+      <c r="E88" s="105" t="n"/>
+      <c r="F88" s="105" t="n"/>
+      <c r="G88" s="105" t="n"/>
+      <c r="H88" s="105" t="n"/>
+      <c r="I88" s="105" t="n"/>
+      <c r="J88" s="105" t="n"/>
+      <c r="K88" s="105" t="n"/>
+      <c r="L88" s="105" t="n"/>
+      <c r="M88" s="105" t="n"/>
+      <c r="N88" s="105" t="n"/>
+      <c r="O88" s="105" t="n"/>
+    </row>
+    <row r="89" ht="52.05" customHeight="1" s="77">
+      <c r="A89" s="76" t="inlineStr">
         <is>
           <t>PRIORITY 7 — UI/UX Redesign (use Claude Design for each page)</t>
         </is>
       </c>
-      <c r="B88" s="86" t="n"/>
-      <c r="C88" s="86" t="n"/>
-      <c r="D88" s="86" t="n"/>
-      <c r="E88" s="86" t="n"/>
-      <c r="F88" s="86" t="n"/>
-      <c r="G88" s="86" t="n"/>
-      <c r="H88" s="86" t="n"/>
-      <c r="I88" s="86" t="n"/>
-      <c r="J88" s="86" t="n"/>
-      <c r="K88" s="86" t="n"/>
-      <c r="L88" s="86" t="n"/>
-      <c r="M88" s="86" t="n"/>
-      <c r="N88" s="86" t="n"/>
-      <c r="O88" s="87" t="n"/>
-    </row>
-    <row r="89" ht="52.05" customHeight="1" s="77">
-      <c r="A89" s="62" t="inlineStr">
+      <c r="B89" s="86" t="n"/>
+      <c r="C89" s="86" t="n"/>
+      <c r="D89" s="86" t="n"/>
+      <c r="E89" s="86" t="n"/>
+      <c r="F89" s="86" t="n"/>
+      <c r="G89" s="86" t="n"/>
+      <c r="H89" s="86" t="n"/>
+      <c r="I89" s="86" t="n"/>
+      <c r="J89" s="86" t="n"/>
+      <c r="K89" s="86" t="n"/>
+      <c r="L89" s="86" t="n"/>
+      <c r="M89" s="86" t="n"/>
+      <c r="N89" s="86" t="n"/>
+      <c r="O89" s="87" t="n"/>
+    </row>
+    <row r="90" ht="52.05" customHeight="1" s="77">
+      <c r="A90" s="62" t="inlineStr">
         <is>
           <t>P6-F12</t>
         </is>
       </c>
-      <c r="B89" s="63" t="n"/>
-      <c r="C89" s="63" t="inlineStr">
+      <c r="B90" s="63" t="n"/>
+      <c r="C90" s="63" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D89" s="95" t="inlineStr">
+      <c r="D90" s="63" t="inlineStr">
         <is>
           <t>page redesign</t>
         </is>
       </c>
-      <c r="E89" s="63" t="inlineStr">
+      <c r="E90" s="63" t="inlineStr">
         <is>
           <t>Apply the new design system to /runs. Restyle from a dense monospace debug trace (raw dimension-score grids, 10+ revision-reason text blocks) into something a manager can skim in under a minute. Fix the currently-unstyled raw Next.js 404 on /runs/{id} deep links -- give each run its own real page. HARD CONSTRAINT (user, 2026-07-04): this redesign must never strip existing detail views, cards, or pages for a cleaner look -- agent detail drill-downs, full critic dimension breakdown + reasoning + revision history, /runs comparisons, all of it stays. Apply the new visual direction (light/dark theme, Instrument Serif + Plus Jakarta Sans, monospace as accent not primary label voice, semantic severity color kept separate from agent-category color) TO that existing depth -- never as a reason to cut it. A direction prototype (single summary screen only, not the full app) was reviewed and approved for tone/color/type before this task starts.</t>
         </is>
       </c>
-      <c r="F89" s="63" t="inlineStr">
+      <c r="F90" s="63" t="inlineStr">
         <is>
           <t>feat: redesign /runs history page + fix /runs/{id} deep-link 404</t>
         </is>
       </c>
-      <c r="G89" s="63" t="inlineStr">
+      <c r="G90" s="63" t="inlineStr">
         <is>
           <t>None (frontend only)</t>
         </is>
       </c>
-      <c r="H89" s="54" t="inlineStr">
+      <c r="H90" s="54" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I89" s="62" t="inlineStr">
+      <c r="I90" s="62" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J89" s="62" t="inlineStr">
+      <c r="J90" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K89" s="62" t="n"/>
-      <c r="L89" s="62" t="n"/>
-      <c r="M89" s="64" t="n">
+      <c r="K90" s="62" t="n"/>
+      <c r="L90" s="62" t="n"/>
+      <c r="M90" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="N89" s="63" t="inlineStr">
+      <c r="N90" s="63" t="inlineStr">
         <is>
           <t>P6-F11</t>
         </is>
       </c>
-      <c r="O89" s="63" t="inlineStr">
+      <c r="O90" s="63" t="inlineStr">
         <is>
           <t>Direct navigation to /runs/{id} renders the run, not a 404; skim-readability spot check.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="52.05" customHeight="1" s="77"/>
     <row r="91" ht="52.05" customHeight="1" s="77">
-      <c r="A91" s="82" t="inlineStr">
+      <c r="A91" s="105" t="n"/>
+      <c r="B91" s="105" t="n"/>
+      <c r="C91" s="105" t="n"/>
+      <c r="D91" s="105" t="n"/>
+      <c r="E91" s="105" t="n"/>
+      <c r="F91" s="105" t="n"/>
+      <c r="G91" s="105" t="n"/>
+      <c r="H91" s="105" t="n"/>
+      <c r="I91" s="105" t="n"/>
+      <c r="J91" s="105" t="n"/>
+      <c r="K91" s="105" t="n"/>
+      <c r="L91" s="105" t="n"/>
+      <c r="M91" s="105" t="n"/>
+      <c r="N91" s="105" t="n"/>
+      <c r="O91" s="105" t="n"/>
+    </row>
+    <row r="92" ht="7.95" customHeight="1" s="77">
+      <c r="A92" s="82" t="inlineStr">
         <is>
           <t>BLOCKED — waiting for Swiggy staging creds (mcp-staging.swiggy.com)</t>
         </is>
       </c>
-      <c r="B91" s="86" t="n"/>
-      <c r="C91" s="86" t="n"/>
-      <c r="D91" s="86" t="n"/>
-      <c r="E91" s="86" t="n"/>
-      <c r="F91" s="86" t="n"/>
-      <c r="G91" s="86" t="n"/>
-      <c r="H91" s="86" t="n"/>
-      <c r="I91" s="86" t="n"/>
-      <c r="J91" s="86" t="n"/>
-      <c r="K91" s="86" t="n"/>
-      <c r="L91" s="86" t="n"/>
-      <c r="M91" s="86" t="n"/>
-      <c r="N91" s="86" t="n"/>
-      <c r="O91" s="87" t="n"/>
-    </row>
-    <row r="92" ht="7.95" customHeight="1" s="77">
-      <c r="A92" s="68" t="inlineStr">
+      <c r="B92" s="86" t="n"/>
+      <c r="C92" s="86" t="n"/>
+      <c r="D92" s="86" t="n"/>
+      <c r="E92" s="86" t="n"/>
+      <c r="F92" s="86" t="n"/>
+      <c r="G92" s="86" t="n"/>
+      <c r="H92" s="86" t="n"/>
+      <c r="I92" s="86" t="n"/>
+      <c r="J92" s="86" t="n"/>
+      <c r="K92" s="86" t="n"/>
+      <c r="L92" s="86" t="n"/>
+      <c r="M92" s="86" t="n"/>
+      <c r="N92" s="86" t="n"/>
+      <c r="O92" s="87" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1" s="77">
+      <c r="A93" s="68" t="inlineStr">
         <is>
           <t>P6-S43</t>
         </is>
       </c>
-      <c r="B92" s="69" t="inlineStr">
+      <c r="B93" s="69" t="inlineStr">
         <is>
           <t>feature/procurement-executor</t>
         </is>
       </c>
-      <c r="C92" s="69" t="inlineStr">
+      <c r="C93" s="69" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D92" s="69" t="inlineStr">
+      <c r="D93" s="69" t="inlineStr">
         <is>
           <t>ProcurementExecutor — Instamart checkout with approval gate</t>
         </is>
       </c>
-      <c r="E92" s="69" t="inlineStr">
+      <c r="E93" s="69" t="inlineStr">
         <is>
           <t>update_cart → get_cart → LangGraph interrupt() → owner approval → checkout. check-then-retry on 5xx (call get_orders before retrying checkout — non-idempotent). Stores in procurement_orders table. COD only. BLOCKED: checkout places real Instamart orders.</t>
         </is>
       </c>
-      <c r="F92" s="69" t="inlineStr">
+      <c r="F93" s="69" t="inlineStr">
         <is>
           <t>feat: ProcurementExecutor — Instamart autonomous procurement with approval gate</t>
         </is>
       </c>
-      <c r="G92" s="69" t="inlineStr">
+      <c r="G93" s="69" t="inlineStr">
         <is>
           <t>docs/ACTION_QUEUE.md, CLAUDE.md</t>
         </is>
       </c>
-      <c r="H92" s="70" t="inlineStr">
+      <c r="H93" s="70" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="I92" s="68" t="inlineStr">
+      <c r="I93" s="68" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="J92" s="68" t="inlineStr">
+      <c r="J93" s="68" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K92" s="68" t="n"/>
-      <c r="L92" s="68" t="n"/>
-      <c r="M92" s="71" t="n">
+      <c r="K93" s="68" t="n"/>
+      <c r="L93" s="68" t="n"/>
+      <c r="M93" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="N92" s="69" t="inlineStr">
+      <c r="N93" s="69" t="inlineStr">
         <is>
           <t>P6-S32</t>
         </is>
       </c>
-      <c r="O92" s="69" t="inlineStr">
+      <c r="O93" s="69" t="inlineStr">
         <is>
           <t>check-then-retry on 5xx; interrupt() pauses graph; approval resumes checkout; procurement_orders row created</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1" s="77">
-      <c r="A93" s="56" t="inlineStr">
-        <is>
-          <t>P6-S44</t>
-        </is>
-      </c>
-      <c r="B93" s="57" t="inlineStr">
-        <is>
-          <t>feature/dineout-executor</t>
-        </is>
-      </c>
-      <c r="C93" s="57" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="D93" s="57" t="inlineStr">
-        <is>
-          <t>Dineout table booking execution</t>
-        </is>
-      </c>
-      <c r="E93" s="57" t="inlineStr">
-        <is>
-          <t>create_cart → book_table(slotId, itemId, reservationTime, guestCount, lat, lng). check-then-retry on 5xx (get_booking_status before retrying). BLOCKED: book_table places real Dineout bookings. NOTE: Managing OWN restaurant Dineout slots requires Partner API not consumer MCP.</t>
-        </is>
-      </c>
-      <c r="F93" s="57" t="inlineStr">
-        <is>
-          <t>feat: Dineout booking execution with approval gate</t>
-        </is>
-      </c>
-      <c r="G93" s="57" t="inlineStr">
-        <is>
-          <t>docs/ACTION_QUEUE.md</t>
-        </is>
-      </c>
-      <c r="H93" s="70" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
-      <c r="I93" s="56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J93" s="56" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K93" s="56" t="n"/>
-      <c r="L93" s="56" t="n"/>
-      <c r="M93" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="57" t="inlineStr">
-        <is>
-          <t>P6-S43</t>
-        </is>
-      </c>
-      <c r="O93" s="57" t="inlineStr">
-        <is>
-          <t>non-idempotent retry test; confirmation in reservations table; free slots only (isFree=true)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="52.05" customHeight="1" s="77">
       <c r="A94" s="68" t="inlineStr">
         <is>
-          <t>P6-S45</t>
+          <t>P6-S44</t>
         </is>
       </c>
       <c r="B94" s="69" t="inlineStr">
         <is>
-          <t>feature/computer-use-partner</t>
+          <t>feature/dineout-executor</t>
         </is>
       </c>
       <c r="C94" s="69" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Agents</t>
         </is>
       </c>
       <c r="D94" s="69" t="inlineStr">
         <is>
-          <t>Computer use agent — Swiggy Partner Dashboard automation</t>
+          <t>Dineout table booking execution</t>
         </is>
       </c>
       <c r="E94" s="69" t="inlineStr">
         <is>
-          <t>Use Claude Computer Use to automate Swiggy Partner Dashboard actions not in MCP: menu price updates, slot management, promotional setup. Bypasses consumer MCP limitation for restaurant-side operations.</t>
+          <t>create_cart → book_table(slotId, itemId, reservationTime, guestCount, lat, lng). check-then-retry on 5xx (get_booking_status before retrying). BLOCKED: book_table places real Dineout bookings. NOTE: Managing OWN restaurant Dineout slots requires Partner API not consumer MCP.</t>
         </is>
       </c>
       <c r="F94" s="69" t="inlineStr">
         <is>
-          <t>feat: computer use agent for Swiggy Partner Dashboard</t>
+          <t>feat: Dineout booking execution with approval gate</t>
         </is>
       </c>
       <c r="G94" s="69" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE.md</t>
+          <t>docs/ACTION_QUEUE.md</t>
         </is>
       </c>
       <c r="H94" s="70" t="inlineStr">
@@ -18405,7 +18515,7 @@
       </c>
       <c r="I94" s="68" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J94" s="68" t="inlineStr">
@@ -18420,105 +18530,98 @@
       </c>
       <c r="N94" s="69" t="inlineStr">
         <is>
+          <t>P6-S43</t>
+        </is>
+      </c>
+      <c r="O94" s="69" t="inlineStr">
+        <is>
+          <t>non-idempotent retry test; confirmation in reservations table; free slots only (isFree=true)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="68" t="inlineStr">
+        <is>
+          <t>P6-S45</t>
+        </is>
+      </c>
+      <c r="B95" s="69" t="inlineStr">
+        <is>
+          <t>feature/computer-use-partner</t>
+        </is>
+      </c>
+      <c r="C95" s="69" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D95" s="69" t="inlineStr">
+        <is>
+          <t>Computer use agent — Swiggy Partner Dashboard automation</t>
+        </is>
+      </c>
+      <c r="E95" s="69" t="inlineStr">
+        <is>
+          <t>Use Claude Computer Use to automate Swiggy Partner Dashboard actions not in MCP: menu price updates, slot management, promotional setup. Bypasses consumer MCP limitation for restaurant-side operations.</t>
+        </is>
+      </c>
+      <c r="F95" s="69" t="inlineStr">
+        <is>
+          <t>feat: computer use agent for Swiggy Partner Dashboard</t>
+        </is>
+      </c>
+      <c r="G95" s="69" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H95" s="70" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="I95" s="68" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J95" s="68" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K95" s="68" t="n"/>
+      <c r="L95" s="68" t="n"/>
+      <c r="M95" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="69" t="inlineStr">
+        <is>
           <t>P6-S44</t>
         </is>
       </c>
-      <c r="O94" s="69" t="inlineStr">
+      <c r="O95" s="69" t="inlineStr">
         <is>
           <t>Computer use navigates Partner Dashboard; menu price update verified end-to-end</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="76" t="inlineStr">
-        <is>
-          <t>SUPERSEDED</t>
-        </is>
-      </c>
-      <c r="B96" s="86" t="n"/>
-      <c r="C96" s="86" t="n"/>
-      <c r="D96" s="86" t="n"/>
-      <c r="E96" s="86" t="n"/>
-      <c r="F96" s="86" t="n"/>
-      <c r="G96" s="86" t="n"/>
-      <c r="H96" s="86" t="n"/>
-      <c r="I96" s="86" t="n"/>
-      <c r="J96" s="86" t="n"/>
-      <c r="K96" s="86" t="n"/>
-      <c r="L96" s="86" t="n"/>
-      <c r="M96" s="86" t="n"/>
-      <c r="N96" s="86" t="n"/>
-      <c r="O96" s="87" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="72" t="inlineStr">
-        <is>
-          <t>P6-S42</t>
-        </is>
-      </c>
-      <c r="B97" s="73" t="n"/>
-      <c r="C97" s="73" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D97" s="73" t="inlineStr">
-        <is>
-          <t>Product redesign -- move dashboard/runs pages past 'dev console' feel</t>
-        </is>
-      </c>
-      <c r="E97" s="73" t="inlineStr">
-        <is>
-          <t>Explicitly deferred this session pending a proper scoping pass. Concrete evidence gathered: /runs/{id} throws a raw unstyled Next.js 404 (no per-run deep link, only in-page sidebar selection on /runs), and the run-detail view is a dense wall of monospace-labelled text blocks (dimension scores, 10+ revision-reason cards) with little visual hierarchy -- reads like a debug trace rather than something an owner skims at 7am. The landing/hero page already looks like a real product; this needs its own scoping conversation (which pages, target feel, how much rework), not a quick fix bundled into other work. SUPERSEDED 2026-07-03 -- decomposed into concrete, sequenced tasks P6-F09 (theme system), P6-F10 (typography rebalance), P6-F11 (IA restructure), P6-F12 (/runs redesign) after a direct scoping conversation with the user, who flagged the product reads as a dev console and asked for light/dark mode + separated pages (Agents/Operations vs Swiggy Market Intel) as an explicit product-quality bar before shipping more features on top of the old layout.</t>
-        </is>
-      </c>
-      <c r="F97" s="73" t="inlineStr">
-        <is>
-          <t>TBD -- needs scoping conversation first</t>
-        </is>
-      </c>
-      <c r="G97" s="73" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H97" s="74" t="inlineStr">
-        <is>
-          <t>Superseded</t>
-        </is>
-      </c>
-      <c r="I97" s="72" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J97" s="72" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K97" s="72" t="n"/>
-      <c r="L97" s="72" t="n"/>
-      <c r="M97" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="73" t="n"/>
-      <c r="O97" s="73" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A83:O83"/>
-    <mergeCell ref="A88:O88"/>
-    <mergeCell ref="A96:O96"/>
-    <mergeCell ref="A64:O64"/>
-    <mergeCell ref="A68:O68"/>
+  <mergeCells count="14">
+    <mergeCell ref="A69:O69"/>
+    <mergeCell ref="A65:O65"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="A92:O92"/>
+    <mergeCell ref="A60:O60"/>
+    <mergeCell ref="A80:O80"/>
+    <mergeCell ref="A75:O75"/>
+    <mergeCell ref="A84:O84"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A89:O89"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A46:O46"/>
-    <mergeCell ref="A79:O79"/>
-    <mergeCell ref="A74:O74"/>
-    <mergeCell ref="A48:O48"/>
+    <mergeCell ref="B46:B58"/>
+    <mergeCell ref="A62:O62"/>
     <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A91:O91"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -17338,7 +17338,7 @@
     <row r="69" ht="52.05" customHeight="1" s="82">
       <c r="A69" s="42" t="inlineStr">
         <is>
-          <t>P6-A8</t>
+          <t>P6-A5</t>
         </is>
       </c>
       <c r="B69" s="92" t="inlineStr">
@@ -17401,7 +17401,7 @@
     <row r="70" ht="7.95" customHeight="1" s="82">
       <c r="A70" s="42" t="inlineStr">
         <is>
-          <t>P6-A14</t>
+          <t>P6-A6</t>
         </is>
       </c>
       <c r="B70" s="92" t="inlineStr">
@@ -17464,7 +17464,7 @@
     <row r="71" ht="18" customHeight="1" s="82">
       <c r="A71" s="42" t="inlineStr">
         <is>
-          <t>P6-A15</t>
+          <t>P6-A7</t>
         </is>
       </c>
       <c r="B71" s="72" t="n"/>
@@ -17515,7 +17515,7 @@
       </c>
       <c r="N71" s="70" t="inlineStr">
         <is>
-          <t>P6-A14</t>
+          <t>P6-A6</t>
         </is>
       </c>
       <c r="O71" s="70" t="inlineStr">
@@ -17527,7 +17527,7 @@
     <row r="72" ht="52.05" customHeight="1" s="82">
       <c r="A72" s="42" t="inlineStr">
         <is>
-          <t>P6-A18</t>
+          <t>P6-A8</t>
         </is>
       </c>
       <c r="B72" s="92" t="inlineStr">
@@ -17590,7 +17590,7 @@
     <row r="73" ht="52.05" customHeight="1" s="82">
       <c r="A73" s="42" t="inlineStr">
         <is>
-          <t>P6-A19</t>
+          <t>P6-A9</t>
         </is>
       </c>
       <c r="B73" s="72" t="n"/>
@@ -17649,7 +17649,7 @@
     <row r="74" ht="18" customHeight="1" s="82">
       <c r="A74" s="42" t="inlineStr">
         <is>
-          <t>P6-A20</t>
+          <t>P6-A10</t>
         </is>
       </c>
       <c r="B74" s="92" t="inlineStr">
@@ -17669,7 +17669,7 @@
       </c>
       <c r="E74" s="70" t="inlineStr">
         <is>
-          <t>Thread an explicit location/address context through MarketIntelService and all 3 enrichers instead of a single hardcoded SWIGGY_ADDRESS_ID -- cheap to do now, expensive to retrofit once multi-location (P6-A16) exists or once real customers have multiple outlets.</t>
+          <t>Thread an explicit location/address context through MarketIntelService and all 3 enrichers instead of a single hardcoded SWIGGY_ADDRESS_ID -- cheap to do now, expensive to retrofit once multi-location (P6-A31) exists or once real customers have multiple outlets.</t>
         </is>
       </c>
       <c r="F74" s="70" t="inlineStr">
@@ -17712,7 +17712,7 @@
     <row r="75" ht="52.05" customHeight="1" s="82">
       <c r="A75" s="42" t="inlineStr">
         <is>
-          <t>P6-A21</t>
+          <t>P6-A11</t>
         </is>
       </c>
       <c r="B75" s="72" t="n"/>
@@ -17763,7 +17763,7 @@
       </c>
       <c r="N75" s="70" t="inlineStr">
         <is>
-          <t>P6-A20</t>
+          <t>P6-A10</t>
         </is>
       </c>
       <c r="O75" s="70" t="inlineStr">
@@ -17775,7 +17775,7 @@
     <row r="76" ht="52.05" customHeight="1" s="82">
       <c r="A76" s="42" t="inlineStr">
         <is>
-          <t>P6-A24</t>
+          <t>P6-A12</t>
         </is>
       </c>
       <c r="B76" s="92" t="inlineStr">
@@ -17838,7 +17838,7 @@
     <row r="77" ht="52.05" customHeight="1" s="82">
       <c r="A77" s="42" t="inlineStr">
         <is>
-          <t>P6-A25</t>
+          <t>P6-A13</t>
         </is>
       </c>
       <c r="B77" s="72" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="N77" s="70" t="inlineStr">
         <is>
-          <t>P6-A24</t>
+          <t>P6-A12</t>
         </is>
       </c>
       <c r="O77" s="70" t="inlineStr">
@@ -17901,7 +17901,7 @@
     <row r="78" ht="52.05" customHeight="1" s="82">
       <c r="A78" s="42" t="inlineStr">
         <is>
-          <t>P6-A26</t>
+          <t>P6-A14</t>
         </is>
       </c>
       <c r="B78" s="92" t="inlineStr">
@@ -17964,7 +17964,7 @@
     <row r="79" ht="18" customHeight="1" s="82">
       <c r="A79" s="42" t="inlineStr">
         <is>
-          <t>P6-A27</t>
+          <t>P6-A15</t>
         </is>
       </c>
       <c r="B79" s="72" t="n"/>
@@ -18023,7 +18023,7 @@
     <row r="80" ht="52.05" customHeight="1" s="82">
       <c r="A80" s="42" t="inlineStr">
         <is>
-          <t>P6-A28</t>
+          <t>P6-A16</t>
         </is>
       </c>
       <c r="B80" s="92" t="inlineStr">
@@ -18086,7 +18086,7 @@
     <row r="81" ht="7.95" customHeight="1" s="82">
       <c r="A81" s="42" t="inlineStr">
         <is>
-          <t>P6-A29</t>
+          <t>P6-A17</t>
         </is>
       </c>
       <c r="B81" s="71" t="n"/>
@@ -18145,7 +18145,7 @@
     <row r="82" ht="52.05" customHeight="1" s="82">
       <c r="A82" s="42" t="inlineStr">
         <is>
-          <t>P6-A30</t>
+          <t>P6-A18</t>
         </is>
       </c>
       <c r="B82" s="72" t="n"/>
@@ -18204,7 +18204,7 @@
     <row r="83" ht="52.05" customHeight="1" s="82">
       <c r="A83" s="42" t="inlineStr">
         <is>
-          <t>P6-A31</t>
+          <t>P6-A19</t>
         </is>
       </c>
       <c r="B83" s="92" t="inlineStr">
@@ -18267,7 +18267,7 @@
     <row r="84" ht="7.95" customHeight="1" s="82">
       <c r="A84" s="42" t="inlineStr">
         <is>
-          <t>P6-A33</t>
+          <t>P6-A20</t>
         </is>
       </c>
       <c r="B84" s="92" t="inlineStr">
@@ -18330,7 +18330,7 @@
     <row r="85" ht="18" customHeight="1" s="82">
       <c r="A85" s="42" t="inlineStr">
         <is>
-          <t>P6-A34</t>
+          <t>P6-A21</t>
         </is>
       </c>
       <c r="B85" s="92" t="inlineStr">
@@ -18393,7 +18393,7 @@
     <row r="86" ht="52.05" customHeight="1" s="82">
       <c r="A86" s="42" t="inlineStr">
         <is>
-          <t>P6-A35</t>
+          <t>P6-A22</t>
         </is>
       </c>
       <c r="B86" s="92" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="N86" s="70" t="inlineStr">
         <is>
-          <t>P6-A8</t>
+          <t>P6-A5</t>
         </is>
       </c>
       <c r="O86" s="70" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="89" ht="39.6" customHeight="1" s="82">
       <c r="A89" s="42" t="inlineStr">
         <is>
-          <t>P6-A5</t>
+          <t>P6-A23</t>
         </is>
       </c>
       <c r="B89" s="92" t="inlineStr">
@@ -18547,7 +18547,7 @@
     <row r="90" ht="39.6" customHeight="1" s="82">
       <c r="A90" s="42" t="inlineStr">
         <is>
-          <t>P6-A6</t>
+          <t>P6-A24</t>
         </is>
       </c>
       <c r="B90" s="72" t="n"/>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="N90" s="70" t="inlineStr">
         <is>
-          <t>P6-A5</t>
+          <t>P6-A23</t>
         </is>
       </c>
       <c r="O90" s="70" t="inlineStr">
@@ -18610,7 +18610,7 @@
     <row r="91" ht="39.6" customHeight="1" s="82">
       <c r="A91" s="42" t="inlineStr">
         <is>
-          <t>P6-A7</t>
+          <t>P6-A25</t>
         </is>
       </c>
       <c r="B91" s="92" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="N91" s="70" t="inlineStr">
         <is>
-          <t>P6-A5</t>
+          <t>P6-A23</t>
         </is>
       </c>
       <c r="O91" s="70" t="inlineStr">
@@ -18677,7 +18677,7 @@
     <row r="92" ht="39.6" customHeight="1" s="82">
       <c r="A92" s="42" t="inlineStr">
         <is>
-          <t>P6-A9</t>
+          <t>P6-A26</t>
         </is>
       </c>
       <c r="B92" s="72" t="n"/>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="N92" s="70" t="inlineStr">
         <is>
-          <t>P6-A5</t>
+          <t>P6-A23</t>
         </is>
       </c>
       <c r="O92" s="70" t="inlineStr">
@@ -18740,7 +18740,7 @@
     <row r="93" ht="39.6" customHeight="1" s="82">
       <c r="A93" s="42" t="inlineStr">
         <is>
-          <t>P6-A10</t>
+          <t>P6-A27</t>
         </is>
       </c>
       <c r="B93" s="92" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="N93" s="70" t="inlineStr">
         <is>
-          <t>P6-A5</t>
+          <t>P6-A23</t>
         </is>
       </c>
       <c r="O93" s="70" t="inlineStr">
@@ -18807,7 +18807,7 @@
     <row r="94" ht="39.6" customHeight="1" s="82">
       <c r="A94" s="42" t="inlineStr">
         <is>
-          <t>P6-A11</t>
+          <t>P6-A28</t>
         </is>
       </c>
       <c r="B94" s="72" t="n"/>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="N94" s="70" t="inlineStr">
         <is>
-          <t>P6-A5, P6-A10</t>
+          <t>P6-A23, P6-A27</t>
         </is>
       </c>
       <c r="O94" s="70" t="inlineStr">
@@ -18870,7 +18870,7 @@
     <row r="95" ht="52.8" customHeight="1" s="82">
       <c r="A95" s="42" t="inlineStr">
         <is>
-          <t>P6-A12</t>
+          <t>P6-A29</t>
         </is>
       </c>
       <c r="B95" s="92" t="inlineStr">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="E95" s="70" t="inlineStr">
         <is>
-          <t>Full update_cart -&gt; get_cart -&gt; LangGraph interrupt() -&gt; owner approval (via Action Queue) -&gt; checkout flow, built completely end-to-end. The actual final checkout() call is stubbed/mocked, clearly labeled 'awaiting Swiggy staging creds' -- everything else (cart building, pricing, approval gate, procurement_orders row creation) is real. Swapping the mock for a real call is Phase B's entire scope for this task. DEFERRED to end of Phase A pending direct restaurant-owner research into real procurement workflow (bulk orders, WhatsApp/phone to local vendors) -- see P6-A17.</t>
+          <t>Full update_cart -&gt; get_cart -&gt; LangGraph interrupt() -&gt; owner approval (via Action Queue) -&gt; checkout flow, built completely end-to-end. The actual final checkout() call is stubbed/mocked, clearly labeled 'awaiting Swiggy staging creds' -- everything else (cart building, pricing, approval gate, procurement_orders row creation) is real. Swapping the mock for a real call is Phase B's entire scope for this task. DEFERRED to end of Phase A pending direct restaurant-owner research into real procurement workflow (bulk orders, WhatsApp/phone to local vendors) -- see P6-A32.</t>
         </is>
       </c>
       <c r="F95" s="70" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="N95" s="70" t="inlineStr">
         <is>
-          <t>P6-A5</t>
+          <t>P6-A23</t>
         </is>
       </c>
       <c r="O95" s="70" t="inlineStr">
@@ -18937,7 +18937,7 @@
     <row r="96" ht="171.6" customHeight="1" s="82">
       <c r="A96" s="42" t="inlineStr">
         <is>
-          <t>P6-A13</t>
+          <t>P6-A30</t>
         </is>
       </c>
       <c r="B96" s="72" t="n"/>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="E96" s="70" t="inlineStr">
         <is>
-          <t>Same pattern as P6-A7 for Dineout: create_cart -&gt; book_table, approval-gated via Action Queue, real logic throughout except the final book_table() call is mocked pending staging creds.</t>
+          <t>Same pattern as P6-A25 for Dineout: create_cart -&gt; book_table, approval-gated via Action Queue, real logic throughout except the final book_table() call is mocked pending staging creds.</t>
         </is>
       </c>
       <c r="F96" s="70" t="inlineStr">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="N96" s="70" t="inlineStr">
         <is>
-          <t>P6-A5, P6-A12</t>
+          <t>P6-A23, P6-A29</t>
         </is>
       </c>
       <c r="O96" s="70" t="inlineStr">
@@ -19000,7 +19000,7 @@
     <row r="97" ht="39.6" customHeight="1" s="82">
       <c r="A97" s="42" t="inlineStr">
         <is>
-          <t>P6-A16</t>
+          <t>P6-A31</t>
         </is>
       </c>
       <c r="B97" s="92" t="inlineStr">
@@ -19063,7 +19063,7 @@
     <row r="98" ht="39.6" customHeight="1" s="82">
       <c r="A98" s="42" t="inlineStr">
         <is>
-          <t>P6-A17</t>
+          <t>P6-A32</t>
         </is>
       </c>
       <c r="B98" s="72" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="N98" s="70" t="inlineStr">
         <is>
-          <t>P6-A16</t>
+          <t>P6-A31</t>
         </is>
       </c>
       <c r="O98" s="70" t="inlineStr">
@@ -19126,7 +19126,7 @@
     <row r="99" ht="52.8" customHeight="1" s="82">
       <c r="A99" s="42" t="inlineStr">
         <is>
-          <t>P6-A22</t>
+          <t>P6-A33</t>
         </is>
       </c>
       <c r="B99" s="92" t="inlineStr">
@@ -19181,7 +19181,7 @@
       </c>
       <c r="N99" s="70" t="inlineStr">
         <is>
-          <t>P6-A5</t>
+          <t>P6-A23</t>
         </is>
       </c>
       <c r="O99" s="70" t="inlineStr">
@@ -19193,7 +19193,7 @@
     <row r="100" ht="171.6" customHeight="1" s="82">
       <c r="A100" s="42" t="inlineStr">
         <is>
-          <t>P6-A23</t>
+          <t>P6-A34</t>
         </is>
       </c>
       <c r="B100" s="72" t="n"/>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="E100" s="70" t="inlineStr">
         <is>
-          <t>Wrap additional existing services as MCP tools beyond the 3 in P6-A17 -- menu insights, demand forecast, and the Phase-5 what-if simulator. Cheap since the service layer already exists; positions CortexKitchen as a general AI-accessible restaurant data layer, not just 3 utility tools.</t>
+          <t>Wrap additional existing services as MCP tools beyond the 3 in P6-A32 -- menu insights, demand forecast, and the Phase-5 what-if simulator. Cheap since the service layer already exists; positions CortexKitchen as a general AI-accessible restaurant data layer, not just 3 utility tools.</t>
         </is>
       </c>
       <c r="F100" s="70" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="N100" s="70" t="inlineStr">
         <is>
-          <t>P6-A22</t>
+          <t>P6-A33</t>
         </is>
       </c>
       <c r="O100" s="70" t="inlineStr">
@@ -19256,7 +19256,7 @@
     <row r="101">
       <c r="A101" s="42" t="inlineStr">
         <is>
-          <t>P6-A32</t>
+          <t>P6-A35</t>
         </is>
       </c>
       <c r="B101" s="92" t="inlineStr">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="N101" s="70" t="inlineStr">
         <is>
-          <t>P6-A6</t>
+          <t>P6-A24</t>
         </is>
       </c>
       <c r="O101" s="70" t="inlineStr">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="E4" s="68" t="inlineStr">
         <is>
-          <t>Phase A (P6-A12) already builds the full get_cart -&gt; update_cart -&gt; LangGraph interrupt() -&gt; owner approval -&gt; checkout flow end-to-end, with the final checkout() call mocked and labeled 'awaiting staging creds'. This task is just the swap: replace the mock with the real call. NON-IDEMPOTENT: on any 5xx from checkout, call get_orders before retrying -- never blind-retry. procurement_orders rows switch from a 'simulated' flag to real confirmed orders.</t>
+          <t>Phase A (P6-A29) already builds the full get_cart -&gt; update_cart -&gt; LangGraph interrupt() -&gt; owner approval -&gt; checkout flow end-to-end, with the final checkout() call mocked and labeled 'awaiting staging creds'. This task is just the swap: replace the mock with the real call. NON-IDEMPOTENT: on any 5xx from checkout, call get_orders before retrying -- never blind-retry. procurement_orders rows switch from a 'simulated' flag to real confirmed orders.</t>
         </is>
       </c>
       <c r="F4" s="68" t="inlineStr">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="N4" s="68" t="inlineStr">
         <is>
-          <t>P6-A12, P6-S14</t>
+          <t>P6-A29, P6-S14</t>
         </is>
       </c>
       <c r="O4" s="68" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="E6" s="68" t="inlineStr">
         <is>
-          <t>book_table in consumer MCP books a table AT another restaurant (a consumer action), not managing your own restaurant's Dineout presence -- that needs Swiggy Partner/Business API, a separate track from these creds. Phase A (P6-A13) already builds the full create_cart -&gt; book_table flow end-to-end with the final call mocked. This task swaps the mock for the real call, scoped to the consumer-booking use case only (e.g. mystery-dining a competitor for research).</t>
+          <t>book_table in consumer MCP books a table AT another restaurant (a consumer action), not managing your own restaurant's Dineout presence -- that needs Swiggy Partner/Business API, a separate track from these creds. Phase A (P6-A30) already builds the full create_cart -&gt; book_table flow end-to-end with the final call mocked. This task swaps the mock for the real call, scoped to the consumer-booking use case only (e.g. mystery-dining a competitor for research).</t>
         </is>
       </c>
       <c r="F6" s="68" t="inlineStr">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="N6" s="68" t="inlineStr">
         <is>
-          <t>P6-A13</t>
+          <t>P6-A30</t>
         </is>
       </c>
       <c r="O6" s="68" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="E8" s="68" t="inlineStr">
         <is>
-          <t>Once P7-1/P7-2 prove reliable in production, extend the trust-ladder mechanic (P6-A9) to real money-touching actions -- e.g. auto-reorder a habitually-restocked ingredient without approval once trust is established.</t>
+          <t>Once P7-1/P7-2 prove reliable in production, extend the trust-ladder mechanic (P6-A26) to real money-touching actions -- e.g. auto-reorder a habitually-restocked ingredient without approval once trust is established.</t>
         </is>
       </c>
       <c r="F8" s="68" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="N8" s="68" t="inlineStr">
         <is>
-          <t>P6-A9, P7-1, P7-2</t>
+          <t>P6-A26, P7-1, P7-2</t>
         </is>
       </c>
       <c r="O8" s="68" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="N14" s="68" t="inlineStr">
         <is>
-          <t>P6-A34</t>
+          <t>P6-A21</t>
         </is>
       </c>
       <c r="O14" s="68" t="inlineStr">
@@ -20684,6 +20684,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="68" t="inlineStr">
         <is>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -189,6 +189,7 @@
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font/>
   </fonts>
   <fills count="22">
     <fill>
@@ -302,7 +303,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -465,11 +466,12 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -755,6 +757,7 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17145,7 +17148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:O41"/>
+  <dimension ref="A2:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.109375" customWidth="1" style="72" min="1" max="1"/>
@@ -17261,7 +17264,7 @@
       </c>
       <c r="E3" s="90" t="inlineStr">
         <is>
-          <t>CompetitorEnricher already computes menu_breadth, cuisine_crowding, veg_mix, and competitor_landscape, and OccupancyEnricher computes slot_availability_by_time -- all of it reaches /market/pulse and the /market page, but NONE of it is passed into _build_prompt(), so menu_intelligence, the critic, and the actual generated plan never see it. Wire these into CompetitorEnricher._build_prompt() (and OccupancyEnricher's equivalent) so the LLM reasoning actually reflects everything already being computed, not just category pricing/positioning/deals/pricing impact. Also absorbed in this same branch (originally planned as a separate task, P6-A5, before it turned out to ship in the same PR): floating chat widget (bottom-right bubble, expandable to the full /chat page) backed by real conversation persistence -- new ChatSession/ChatMessage tables (chat history previously lived only in frontend React state per page load, nothing was queryable server-side), GET /chat/sessions (list past threads) + GET /chat/sessions/{id} (full thread), and a shared ChatSessionContext so the floating widget and the full /chat page never lose context switching between them. LIVE-VERIFIED 2026-07-06 against the real running backend (not just unit tests): cleared the stale Redis cache from before this change, confirmed CompetitorEnricher._build_prompt() now genuinely includes Menu breadth/Cuisine crowding/veg-non-veg mix/Competitor landscape sections against the real Swiggy account.</t>
+          <t>CompetitorEnricher already computes menu_breadth, cuisine_crowding, veg_mix, and competitor_landscape, and OccupancyEnricher computes slot_availability_by_time -- all of it reaches /market/pulse and the /market page, but NONE of it is passed into _build_prompt(), so menu_intelligence, the critic, and the actual generated plan never see it. Wire these into CompetitorEnricher._build_prompt() (and OccupancyEnricher's equivalent) so the LLM reasoning actually reflects everything already being computed, not just category pricing/positioning/deals/pricing impact. Also absorbed in this same branch (originally planned as a separate task, before it turned out to ship in the same PR): floating chat widget (bottom-right bubble, expandable to the full /chat page) backed by real conversation persistence -- new ChatSession/ChatMessage tables (chat history previously lived only in frontend React state per page load, nothing was queryable server-side), GET /chat/sessions (list past threads) + GET /chat/sessions/{id} (full thread), and a shared ChatSessionContext so the floating widget and the full /chat page never lose context switching between them. LIVE-VERIFIED 2026-07-06 against the real running backend (not just unit tests): cleared the stale Redis cache from before this change, confirmed CompetitorEnricher._build_prompt() now genuinely includes Menu breadth/Cuisine crowding/veg-non-veg mix/Competitor landscape sections against the real Swiggy account.</t>
         </is>
       </c>
       <c r="F3" s="90" t="inlineStr">
@@ -17515,2086 +17518,2004 @@
       </c>
     </row>
     <row r="7" ht="52.05" customFormat="1" customHeight="1" s="97">
-      <c r="A7" s="92" t="n"/>
-      <c r="B7" s="93" t="n"/>
-      <c r="C7" s="94" t="n"/>
-      <c r="D7" s="94" t="n"/>
-      <c r="E7" s="94" t="n"/>
-      <c r="F7" s="94" t="n"/>
-      <c r="G7" s="94" t="n"/>
-      <c r="H7" s="95" t="n"/>
-      <c r="I7" s="92" t="n"/>
-      <c r="J7" s="92" t="n"/>
-      <c r="K7" s="92" t="n"/>
-      <c r="L7" s="92" t="n"/>
-      <c r="M7" s="96" t="n"/>
-      <c r="N7" s="94" t="n"/>
-      <c r="O7" s="94" t="n"/>
+      <c r="A7" s="65" t="inlineStr">
+        <is>
+          <t>P6-A5</t>
+        </is>
+      </c>
+      <c r="B7" s="98" t="inlineStr">
+        <is>
+          <t>feature/multi-platform-connectors</t>
+        </is>
+      </c>
+      <c r="C7" s="90" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D7" s="90" t="inlineStr">
+        <is>
+          <t>Zomato stub connector</t>
+        </is>
+      </c>
+      <c r="E7" s="90" t="inlineStr">
+        <is>
+          <t>ZomatoConnector class following the exact BaseConnector shape (sync()/enrich()) as SwiggyConnector, registered in provider_registry.py's CAPABILITY_PROVIDERS as an actually-real (if non-functional) connector rather than a placeholder string. Proves the multi-provider architecture is real, not Swiggy-only. No live Zomato API call required -- returns a clear 'not yet connected' state.</t>
+        </is>
+      </c>
+      <c r="F7" s="90" t="inlineStr">
+        <is>
+          <t>feat: ZomatoConnector stub -- proves multi-provider architecture, no live API required</t>
+        </is>
+      </c>
+      <c r="G7" s="90" t="inlineStr">
+        <is>
+          <t>CLAUDE.md, docs/CONNECTORS.md</t>
+        </is>
+      </c>
+      <c r="H7" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I7" s="89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J7" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K7" s="89" t="n"/>
+      <c r="L7" s="89" t="n"/>
+      <c r="M7" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="90" t="n"/>
+      <c r="O7" s="90" t="inlineStr">
+        <is>
+          <t>connector registers correctly in provider_registry; enrich() returns a clean not-connected state, never raises</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52.05" customHeight="1" s="72">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>P6-A6</t>
+        </is>
+      </c>
+      <c r="B8" s="69" t="n"/>
+      <c r="C8" s="90" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D8" s="90" t="inlineStr">
+        <is>
+          <t>Public review aggregation connectors (Google/Zomato reviews)</t>
+        </is>
+      </c>
+      <c r="E8" s="90" t="inlineStr">
+        <is>
+          <t>GoogleReviewsConnector / ZomatoReviewsConnector following the same BaseConnector pattern, pulling public review data (not internal complaints) into complaint_intelligence as an additional source type. Extends the Feedback model's source concept rather than inventing a parallel system.</t>
+        </is>
+      </c>
+      <c r="F8" s="90" t="inlineStr">
+        <is>
+          <t>feat: public review aggregation -- Google/Zomato reviews via BaseConnector pattern</t>
+        </is>
+      </c>
+      <c r="G8" s="90" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md, docs/CONNECTORS.md</t>
+        </is>
+      </c>
+      <c r="H8" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I8" s="89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J8" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K8" s="89" t="n"/>
+      <c r="L8" s="89" t="n"/>
+      <c r="M8" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="90" t="inlineStr">
         <is>
           <t>P6-A5</t>
         </is>
       </c>
-      <c r="B8" s="68" t="inlineStr">
-        <is>
-          <t>feature/anomaly-agent</t>
-        </is>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="O8" s="90" t="inlineStr">
+        <is>
+          <t>reviews ingested with correct source tag; complaint_intelligence node correctly surfaces public-review-sourced themes alongside internal ones</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="7.95" customHeight="1" s="72">
+      <c r="A9" s="65" t="inlineStr">
+        <is>
+          <t>P6-A7</t>
+        </is>
+      </c>
+      <c r="B9" s="98" t="inlineStr">
+        <is>
+          <t>feature/financial-compliance</t>
+        </is>
+      </c>
+      <c r="C9" s="90" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D9" s="90" t="inlineStr">
+        <is>
+          <t>Financial scorecard -- Expense ledger + real P&amp;L</t>
+        </is>
+      </c>
+      <c r="E9" s="90" t="inlineStr">
+        <is>
+          <t>New Expense model (category: rent/utilities/marketing/labor-later/other, amount, recurrence). Extends business.py's existing revenue/margin computation into a real daily/weekly P&amp;L and one composite health score. Designed so labor slots in later as just another Expense category, not a rewrite.</t>
+        </is>
+      </c>
+      <c r="F9" s="90" t="inlineStr">
+        <is>
+          <t>feat: financial scorecard -- Expense ledger, real P&amp;L, composite health score</t>
+        </is>
+      </c>
+      <c r="G9" s="90" t="inlineStr">
+        <is>
+          <t>docs/APIS.md</t>
+        </is>
+      </c>
+      <c r="H9" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I9" s="89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J9" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K9" s="89" t="n"/>
+      <c r="L9" s="89" t="n"/>
+      <c r="M9" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="90" t="n"/>
+      <c r="O9" s="90" t="inlineStr">
+        <is>
+          <t>P&amp;L numbers match seeded expense + revenue data; health score computes deterministically from known inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="72">
+      <c r="A10" s="65" t="inlineStr">
+        <is>
+          <t>P6-A8</t>
+        </is>
+      </c>
+      <c r="B10" s="69" t="n"/>
+      <c r="C10" s="90" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D10" s="90" t="inlineStr">
+        <is>
+          <t>Compliance / Obligations calendar</t>
+        </is>
+      </c>
+      <c r="E10" s="90" t="inlineStr">
+        <is>
+          <t>Generalized Obligation model (type: license-renewal/GST-filing/inspection/other, due_date, status) with reminders delivered through the existing Phase-5 email digest mechanism rather than a new one-off sender. Not a GST computation/invoicing layer -- just a dated-obligation tracker with reminders.</t>
+        </is>
+      </c>
+      <c r="F10" s="90" t="inlineStr">
+        <is>
+          <t>feat: compliance/obligations calendar -- reminder engine reusing the existing email digest</t>
+        </is>
+      </c>
+      <c r="G10" s="90" t="inlineStr">
+        <is>
+          <t>docs/APIS.md</t>
+        </is>
+      </c>
+      <c r="H10" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I10" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J10" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K10" s="89" t="n"/>
+      <c r="L10" s="89" t="n"/>
+      <c r="M10" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="90" t="n"/>
+      <c r="O10" s="90" t="inlineStr">
+        <is>
+          <t>reminder fires at the correct lead-time before due_date; reuses existing digest delivery path</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52.05" customHeight="1" s="72">
+      <c r="A11" s="65" t="inlineStr">
+        <is>
+          <t>P6-A9</t>
+        </is>
+      </c>
+      <c r="B11" s="98" t="inlineStr">
+        <is>
+          <t>feature/location-architecture</t>
+        </is>
+      </c>
+      <c r="C11" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D11" s="90" t="inlineStr">
+        <is>
+          <t>Location-aware enrichers (hedge for multi-location)</t>
+        </is>
+      </c>
+      <c r="E11" s="90" t="inlineStr">
+        <is>
+          <t>Thread an explicit location/address context through MarketIntelService and all 3 enrichers instead of a single hardcoded SWIGGY_ADDRESS_ID -- cheap to do now, expensive to retrofit once multi-location (P6-A30) exists or once real customers have multiple outlets.</t>
+        </is>
+      </c>
+      <c r="F11" s="90" t="inlineStr">
+        <is>
+          <t>feat: location-aware enrichers -- pass address/location context through instead of one hardcoded address</t>
+        </is>
+      </c>
+      <c r="G11" s="90" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H11" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I11" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J11" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K11" s="89" t="n"/>
+      <c r="L11" s="89" t="n"/>
+      <c r="M11" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="90" t="n"/>
+      <c r="O11" s="90" t="inlineStr">
+        <is>
+          <t>enrichers accept and correctly use a passed-in address_id, defaulting to the existing single-address behavior when none given</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52.05" customHeight="1" s="72">
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>P6-A10</t>
+        </is>
+      </c>
+      <c r="B12" s="69" t="n"/>
+      <c r="C12" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D12" s="90" t="inlineStr">
+        <is>
+          <t>Multi-location / Restaurant entity -- STRATEGIC, needs explicit go/no-go</t>
+        </is>
+      </c>
+      <c r="E12" s="90" t="inlineStr">
+        <is>
+          <t>Introduce Restaurant as a first-class entity between Organization and everything else (menu, inventory, planning runs, Swiggy connector -- each physical location has its own Swiggy restaurant ID). Add restaurant_id to MenuItem/InventoryItem/PlanningRun/connectors. Cheaper to do now while the schema is small than to retrofit later. NOT started until the user confirms real near-term demand justifies it over other Phase A work.</t>
+        </is>
+      </c>
+      <c r="F12" s="90" t="inlineStr">
+        <is>
+          <t>feat: Restaurant entity -- first-class multi-location support</t>
+        </is>
+      </c>
+      <c r="G12" s="90" t="inlineStr">
+        <is>
+          <t>docs/DATA_MODEL.md, docs/DECISIONS.md</t>
+        </is>
+      </c>
+      <c r="H12" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I12" s="89" t="inlineStr">
+        <is>
+          <t>Low (pending go/no-go)</t>
+        </is>
+      </c>
+      <c r="J12" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K12" s="89" t="n"/>
+      <c r="L12" s="89" t="n"/>
+      <c r="M12" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="90" t="inlineStr">
+        <is>
+          <t>P6-A9</t>
+        </is>
+      </c>
+      <c r="O12" s="90" t="inlineStr">
+        <is>
+          <t>existing single-location orgs continue to work unchanged (default restaurant backfilled); cross-location query test once 2+ restaurants exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="72">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>P6-A11</t>
+        </is>
+      </c>
+      <c r="B13" s="98" t="inlineStr">
+        <is>
+          <t>feature/chatbot-dineout-tools</t>
+        </is>
+      </c>
+      <c r="C13" s="90" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D13" s="90" t="inlineStr">
+        <is>
+          <t>Chatbot -- Dineout competitive query tools</t>
+        </is>
+      </c>
+      <c r="E13" s="90" t="inlineStr">
+        <is>
+          <t>3 Groq function-calling tools for the existing chatbot: get_competitor_deals, get_area_occupancy, get_trending_dishes -- all using Swiggy's existing read-only Dineout MCP (search_restaurants_dineout, get_restaurant_details, get_available_slots), already-proven tools. (Formerly P6-MI04; renumbered as part of the Phase 6 replan.)</t>
+        </is>
+      </c>
+      <c r="F13" s="90" t="inlineStr">
+        <is>
+          <t>feat: chatbot Dineout tools -- competitor deals, area occupancy, trending dishes</t>
+        </is>
+      </c>
+      <c r="G13" s="90" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="H13" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I13" s="89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J13" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K13" s="89" t="n"/>
+      <c r="L13" s="89" t="n"/>
+      <c r="M13" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="90" t="n"/>
+      <c r="O13" s="90" t="inlineStr">
+        <is>
+          <t>all 3 tools callable from /chat; correct Swiggy data returned; graceful None on failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52.05" customHeight="1" s="72">
+      <c r="A14" s="65" t="inlineStr">
+        <is>
+          <t>P6-A12</t>
+        </is>
+      </c>
+      <c r="B14" s="69" t="n"/>
+      <c r="C14" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D14" s="90" t="inlineStr">
+        <is>
+          <t>Structured outputs -- tool_choice=required across chatbot tools</t>
+        </is>
+      </c>
+      <c r="E14" s="90" t="inlineStr">
+        <is>
+          <t>Upgrade chatbot Groq calls to tool_choice=required + strict JSON schema across all chatbot tools (Swiggy and internal). Chatbot function calls never hallucinate JSON.</t>
+        </is>
+      </c>
+      <c r="F14" s="90" t="inlineStr">
+        <is>
+          <t>feat: structured outputs -- tool_choice=required across all chatbot tools</t>
+        </is>
+      </c>
+      <c r="G14" s="90" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="H14" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I14" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J14" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K14" s="89" t="n"/>
+      <c r="L14" s="89" t="n"/>
+      <c r="M14" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="90" t="inlineStr">
+        <is>
+          <t>P6-A11</t>
+        </is>
+      </c>
+      <c r="O14" s="90" t="inlineStr">
+        <is>
+          <t>schema validation test; chatbot returns valid JSON on repeated calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52.05" customHeight="1" s="72">
+      <c r="A15" s="65" t="inlineStr">
+        <is>
+          <t>P6-A13</t>
+        </is>
+      </c>
+      <c r="B15" s="98" t="inlineStr">
+        <is>
+          <t>feature/llm-cost-quality</t>
+        </is>
+      </c>
+      <c r="C15" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D15" s="90" t="inlineStr">
+        <is>
+          <t>Prompt caching -- critic + aggregator</t>
+        </is>
+      </c>
+      <c r="E15" s="90" t="inlineStr">
+        <is>
+          <t>Add prompt-caching headers to critic and aggregator LLM calls (both have long, repeated system prompts). Cuts LLM cost per planning run; invisible to a demo but real cost hygiene.</t>
+        </is>
+      </c>
+      <c r="F15" s="90" t="inlineStr">
+        <is>
+          <t>feat: prompt caching -- cut LLM costs on critic and aggregator nodes</t>
+        </is>
+      </c>
+      <c r="G15" s="90" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H15" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I15" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J15" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K15" s="89" t="n"/>
+      <c r="L15" s="89" t="n"/>
+      <c r="M15" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="90" t="n"/>
+      <c r="O15" s="90" t="inlineStr">
+        <is>
+          <t>cost log shows cache_hit=true on second run of the same scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52.05" customHeight="1" s="72">
+      <c r="A16" s="65" t="inlineStr">
+        <is>
+          <t>P6-A14</t>
+        </is>
+      </c>
+      <c r="B16" s="69" t="n"/>
+      <c r="C16" s="90" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
-        <is>
-          <t>Anomaly-triggered investigation agent</t>
-        </is>
-      </c>
-      <c r="E8" s="43" t="inlineStr">
-        <is>
-          <t>A reactive service that, given a detected anomaly (e.g. a dish's sales dropped sharply vs the same weekday last period), chains the existing enrichers/services (CompetitorEnricher, complaint_intelligence, inventory) to synthesize one diagnosis instead of a human cross-referencing multiple dashboard cards. Ships with anomaly detection for the single clearest case first (dish-level sales drop) rather than a general anomaly framework. This is the clearest expression of 'separate synthesis layer' -- no single platform (Swiggy, a POS) could produce this alone.</t>
-        </is>
-      </c>
-      <c r="F8" s="43" t="inlineStr">
-        <is>
-          <t>feat: anomaly-triggered investigation agent -- reactive cross-signal diagnosis</t>
-        </is>
-      </c>
-      <c r="G8" s="43" t="inlineStr">
+      <c r="D16" s="90" t="inlineStr">
+        <is>
+          <t>Multi-agent debate critic</t>
+        </is>
+      </c>
+      <c r="E16" s="90" t="inlineStr">
+        <is>
+          <t>Two LLM critic instances (optimistic vs conservative), structured debate, moderator resolves disagreement. Marginal demo-visible upside over the existing single critic given the added cost/latency -- kept low priority.</t>
+        </is>
+      </c>
+      <c r="F16" s="90" t="inlineStr">
+        <is>
+          <t>feat: multi-agent debate critic -- consensus scoring</t>
+        </is>
+      </c>
+      <c r="G16" s="90" t="inlineStr">
         <is>
           <t>docs/AGENTS.md</t>
         </is>
       </c>
-      <c r="H8" s="41" t="inlineStr">
+      <c r="H16" s="108" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I8" s="42" t="inlineStr">
+      <c r="I16" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J16" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K16" s="89" t="n"/>
+      <c r="L16" s="89" t="n"/>
+      <c r="M16" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="90" t="n"/>
+      <c r="O16" s="90" t="inlineStr">
+        <is>
+          <t>debate resolves on test plans; disagreement cases escalate correctly</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52.05" customHeight="1" s="72">
+      <c r="A17" s="65" t="inlineStr">
+        <is>
+          <t>P6-A15</t>
+        </is>
+      </c>
+      <c r="B17" s="98" t="inlineStr">
+        <is>
+          <t>feature/ci-eval-hygiene</t>
+        </is>
+      </c>
+      <c r="C17" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D17" s="90" t="inlineStr">
+        <is>
+          <t>Fix SQLite/JSONB CI test-infra gap</t>
+        </is>
+      </c>
+      <c r="E17" s="90" t="inlineStr">
+        <is>
+          <t>test_swiggy_reservation_sync.py and test_connector_repository.py are excluded from CI because SQLite can't render Postgres JSONB columns. Either a SQLite-compatible fallback type or a Postgres CI service container.</t>
+        </is>
+      </c>
+      <c r="F17" s="90" t="inlineStr">
+        <is>
+          <t>fix: SQLite-compatible JSONB handling (or Postgres CI service) for excluded test files</t>
+        </is>
+      </c>
+      <c r="G17" s="90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H17" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I17" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J17" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K17" s="89" t="n"/>
+      <c r="L17" s="89" t="n"/>
+      <c r="M17" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="90" t="n"/>
+      <c r="O17" s="90" t="inlineStr">
+        <is>
+          <t>previously-excluded test files run in CI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="72">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
+          <t>P6-A16</t>
+        </is>
+      </c>
+      <c r="B18" s="70" t="n"/>
+      <c r="C18" s="90" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D18" s="90" t="inlineStr">
+        <is>
+          <t>Promote reviewed RAGAS/DeepEval candidates</t>
+        </is>
+      </c>
+      <c r="E18" s="90" t="inlineStr">
+        <is>
+          <t>Recurring habit of running the existing candidate-generation scripts and hand-promoting reviewed candidates into the curated eval datasets.</t>
+        </is>
+      </c>
+      <c r="F18" s="90" t="inlineStr">
+        <is>
+          <t>chore: promote reviewed eval candidates into curated datasets</t>
+        </is>
+      </c>
+      <c r="G18" s="90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H18" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I18" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J18" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K18" s="89" t="n"/>
+      <c r="L18" s="89" t="n"/>
+      <c r="M18" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="90" t="n"/>
+      <c r="O18" s="90" t="inlineStr">
+        <is>
+          <t>N/A -- ongoing process, not a one-time build</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52.05" customHeight="1" s="72">
+      <c r="A19" s="65" t="inlineStr">
+        <is>
+          <t>P6-A17</t>
+        </is>
+      </c>
+      <c r="B19" s="69" t="n"/>
+      <c r="C19" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D19" s="90" t="inlineStr">
+        <is>
+          <t>Regenerate golden_runs.json against real data</t>
+        </is>
+      </c>
+      <c r="E19" s="90" t="inlineStr">
+        <is>
+          <t>The key-path bug in build_golden_dataset.py is already fixed; the checked-in fixture still reflects the old broken extraction. Regenerate once real run history exists.</t>
+        </is>
+      </c>
+      <c r="F19" s="90" t="inlineStr">
+        <is>
+          <t>chore: regenerate golden_runs.json with corrected extraction logic</t>
+        </is>
+      </c>
+      <c r="G19" s="90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H19" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I19" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J19" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K19" s="89" t="n"/>
+      <c r="L19" s="89" t="n"/>
+      <c r="M19" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="90" t="n"/>
+      <c r="O19" s="90" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="7.95" customHeight="1" s="72">
+      <c r="A20" s="65" t="inlineStr">
+        <is>
+          <t>P6-A18</t>
+        </is>
+      </c>
+      <c r="B20" s="98" t="inlineStr">
+        <is>
+          <t>feature/menu-engineering-matrix</t>
+        </is>
+      </c>
+      <c r="C20" s="90" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D20" s="90" t="inlineStr">
+        <is>
+          <t>Menu engineering matrix UI</t>
+        </is>
+      </c>
+      <c r="E20" s="90" t="inlineStr">
+        <is>
+          <t>Stars/plow-horses/dogs/puzzles quadrant chart using margin_pct x quantity, both already computed in business.py -- just needs quadrant classification + a chart.</t>
+        </is>
+      </c>
+      <c r="F20" s="90" t="inlineStr">
+        <is>
+          <t>feat: menu engineering matrix -- margin x popularity quadrant chart</t>
+        </is>
+      </c>
+      <c r="G20" s="90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H20" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I20" s="89" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J8" s="42" t="inlineStr">
+      <c r="J20" s="89" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K8" s="42" t="n"/>
-      <c r="L8" s="42" t="n"/>
-      <c r="M8" s="44" t="n">
+      <c r="K20" s="89" t="n"/>
+      <c r="L20" s="89" t="n"/>
+      <c r="M20" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="43" t="n"/>
-      <c r="O8" s="43" t="inlineStr">
-        <is>
-          <t>given a synthetic sales-drop + competitor-deal fixture, agent correctly attributes cause</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="7.95" customHeight="1" s="72">
-      <c r="A9" s="42" t="inlineStr">
-        <is>
-          <t>P6-A6</t>
-        </is>
-      </c>
-      <c r="B9" s="68" t="inlineStr">
-        <is>
-          <t>feature/multi-platform-connectors</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="D9" s="43" t="inlineStr">
-        <is>
-          <t>Zomato stub connector</t>
-        </is>
-      </c>
-      <c r="E9" s="43" t="inlineStr">
-        <is>
-          <t>ZomatoConnector class following the exact BaseConnector shape (sync()/enrich()) as SwiggyConnector, registered in provider_registry.py's CAPABILITY_PROVIDERS as an actually-real (if non-functional) connector rather than a placeholder string. Proves the multi-provider architecture is real, not Swiggy-only. No live Zomato API call required -- returns a clear 'not yet connected' state.</t>
-        </is>
-      </c>
-      <c r="F9" s="43" t="inlineStr">
-        <is>
-          <t>feat: ZomatoConnector stub -- proves multi-provider architecture, no live API required</t>
-        </is>
-      </c>
-      <c r="G9" s="43" t="inlineStr">
-        <is>
-          <t>CLAUDE.md, docs/CONNECTORS.md</t>
-        </is>
-      </c>
-      <c r="H9" s="41" t="inlineStr">
+      <c r="N20" s="90" t="n"/>
+      <c r="O20" s="90" t="inlineStr">
+        <is>
+          <t>quadrant classification unit test; chart renders correctly</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52.05" customHeight="1" s="72">
+      <c r="A21" s="65" t="inlineStr">
+        <is>
+          <t>P6-A19</t>
+        </is>
+      </c>
+      <c r="B21" s="98" t="inlineStr">
+        <is>
+          <t>feature/pages-redesign</t>
+        </is>
+      </c>
+      <c r="C21" s="90" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D21" s="90" t="inlineStr">
+        <is>
+          <t>all page redesign via claude design</t>
+        </is>
+      </c>
+      <c r="E21" s="90" t="inlineStr">
+        <is>
+          <t>Apply the existing design system to /runs -- currently the weakest-looking screen (dense monospace debug trace). Fix the unstyled raw 404 on /runs/{id} deep links.</t>
+        </is>
+      </c>
+      <c r="F21" s="90" t="inlineStr">
+        <is>
+          <t>feat: redesign /runs history page + fix /runs/{id} deep-link 404</t>
+        </is>
+      </c>
+      <c r="G21" s="90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H21" s="108" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I9" s="42" t="inlineStr">
+      <c r="I21" s="89" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J9" s="42" t="inlineStr">
+      <c r="J21" s="89" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K9" s="42" t="n"/>
-      <c r="L9" s="42" t="n"/>
-      <c r="M9" s="44" t="n">
+      <c r="K21" s="89" t="n"/>
+      <c r="L21" s="89" t="n"/>
+      <c r="M21" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="43" t="n"/>
-      <c r="O9" s="43" t="inlineStr">
-        <is>
-          <t>connector registers correctly in provider_registry; enrich() returns a clean not-connected state, never raises</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" s="72">
-      <c r="A10" s="42" t="inlineStr">
-        <is>
-          <t>P6-A7</t>
-        </is>
-      </c>
-      <c r="B10" s="69" t="n"/>
-      <c r="C10" s="43" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="D10" s="43" t="inlineStr">
-        <is>
-          <t>Public review aggregation connectors (Google/Zomato reviews)</t>
-        </is>
-      </c>
-      <c r="E10" s="43" t="inlineStr">
-        <is>
-          <t>GoogleReviewsConnector / ZomatoReviewsConnector following the same BaseConnector pattern, pulling public review data (not internal complaints) into complaint_intelligence as an additional source type. Extends the Feedback model's source concept rather than inventing a parallel system.</t>
-        </is>
-      </c>
-      <c r="F10" s="43" t="inlineStr">
-        <is>
-          <t>feat: public review aggregation -- Google/Zomato reviews via BaseConnector pattern</t>
-        </is>
-      </c>
-      <c r="G10" s="43" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md, docs/CONNECTORS.md</t>
-        </is>
-      </c>
-      <c r="H10" s="41" t="inlineStr">
+      <c r="N21" s="90" t="n"/>
+      <c r="O21" s="90" t="inlineStr">
+        <is>
+          <t>direct navigation to /runs/{id} renders the run, not a 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52.05" customHeight="1" s="72">
+      <c r="A22" s="65" t="inlineStr">
+        <is>
+          <t>P6-A20</t>
+        </is>
+      </c>
+      <c r="B22" s="98" t="inlineStr">
+        <is>
+          <t>feature/voice-interface</t>
+        </is>
+      </c>
+      <c r="C22" s="90" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D22" s="90" t="inlineStr">
+        <is>
+          <t>Voice interface</t>
+        </is>
+      </c>
+      <c r="E22" s="90" t="inlineStr">
+        <is>
+          <t>Whisper transcription on browser-recorded question, existing RAG chatbot answers, TTS reads back.</t>
+        </is>
+      </c>
+      <c r="F22" s="90" t="inlineStr">
+        <is>
+          <t>feat: voice interface -- Whisper transcription + RAG answer + TTS readback</t>
+        </is>
+      </c>
+      <c r="G22" s="90" t="inlineStr">
+        <is>
+          <t>docs/PRODUCT_MODES.md</t>
+        </is>
+      </c>
+      <c r="H22" s="108" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I10" s="42" t="inlineStr">
+      <c r="I22" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J22" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K22" s="89" t="n"/>
+      <c r="L22" s="89" t="n"/>
+      <c r="M22" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="90" t="n"/>
+      <c r="O22" s="90" t="inlineStr">
+        <is>
+          <t>transcription accuracy smoke test; end-to-end voice -&gt; RAG answer -&gt; TTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="7.95" customHeight="1" s="72">
+      <c r="A23" s="65" t="inlineStr">
+        <is>
+          <t>P6-A21</t>
+        </is>
+      </c>
+      <c r="B23" s="98" t="inlineStr">
+        <is>
+          <t>feature/live-page-redesign</t>
+        </is>
+      </c>
+      <c r="C23" s="90" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D23" s="90" t="inlineStr">
+        <is>
+          <t>/live page -- reframed as alerts/synthesis overlay</t>
+        </is>
+      </c>
+      <c r="E23" s="90" t="inlineStr">
+        <is>
+          <t>NOT a live order board (that's POS/aggregator territory and touches personal Swiggy consumer data). Instead: an alerts-and-synthesis overlay surfacing cross-referenced signals (e.g. 'order running late -- here's why, per our own data') during service hours.</t>
+        </is>
+      </c>
+      <c r="F23" s="90" t="inlineStr">
+        <is>
+          <t>feat: /live page -- alerts and synthesis overlay, not a live order feed</t>
+        </is>
+      </c>
+      <c r="G23" s="90" t="inlineStr">
+        <is>
+          <t>docs/PRODUCT_MODES.md</t>
+        </is>
+      </c>
+      <c r="H23" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I23" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J23" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K23" s="89" t="n"/>
+      <c r="L23" s="89" t="n"/>
+      <c r="M23" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="90" t="n"/>
+      <c r="O23" s="90" t="inlineStr">
+        <is>
+          <t>manual verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="72">
+      <c r="A24" s="111" t="n"/>
+      <c r="B24" s="111" t="n"/>
+      <c r="C24" s="111" t="n"/>
+      <c r="D24" s="111" t="n"/>
+      <c r="E24" s="111" t="n"/>
+      <c r="F24" s="111" t="n"/>
+      <c r="G24" s="111" t="n"/>
+      <c r="H24" s="111" t="n"/>
+      <c r="I24" s="111" t="n"/>
+      <c r="J24" s="111" t="n"/>
+      <c r="K24" s="111" t="n"/>
+      <c r="L24" s="111" t="n"/>
+      <c r="M24" s="111" t="n"/>
+      <c r="N24" s="111" t="n"/>
+      <c r="O24" s="111" t="n"/>
+    </row>
+    <row r="25" ht="52.05" customHeight="1" s="72">
+      <c r="A25" s="109" t="inlineStr">
+        <is>
+          <t>DEFERRED TO END OF PHASE A -- pending direct restaurant-owner research into real procurement/approval workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52.8" customHeight="1" s="72">
+      <c r="A26" s="65" t="inlineStr">
+        <is>
+          <t>P6-A22</t>
+        </is>
+      </c>
+      <c r="B26" s="98" t="inlineStr">
+        <is>
+          <t>feature/action-queue</t>
+        </is>
+      </c>
+      <c r="C26" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D26" s="90" t="inlineStr">
+        <is>
+          <t>ActionQueueService + action_queue table</t>
+        </is>
+      </c>
+      <c r="E26" s="90" t="inlineStr">
+        <is>
+          <t>New table (org_id, action_type [AUTO/APPROVE_REQUIRED/RECOMMENDATION], payload jsonb, status [PENDING/APPROVED/EXECUTED/REJECTED/EXPIRED], approved_by, executed_at, error). ActionQueueService CRUD + status transitions. Plan output gains an action_queue section in the API response. Foundational -- every other agentic task below (workflow triggers, dynamic pricing, executors, trust-ladder) writes into this same table rather than inventing its own approval mechanism. DEFERRED to end of Phase A -- its main real-world value (approving reorder suggestions) is exactly the workflow that needs real restaurant-owner input first; building the approval UX before that research risks designing around the wrong assumptions.</t>
+        </is>
+      </c>
+      <c r="F26" s="90" t="inlineStr">
+        <is>
+          <t>feat: ActionQueueService + action_queue table -- 3-tier action model with approval lifecycle</t>
+        </is>
+      </c>
+      <c r="G26" s="90" t="inlineStr">
+        <is>
+          <t>docs/ACTION_QUEUE.md (new), docs/APIS.md, docs/DECISIONS.md</t>
+        </is>
+      </c>
+      <c r="H26" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I26" s="89" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J26" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K26" s="89" t="n"/>
+      <c r="L26" s="89" t="n"/>
+      <c r="M26" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="90" t="n"/>
+      <c r="O26" s="90" t="inlineStr">
+        <is>
+          <t>CRUD + status-transition unit tests; plan output includes action_queue section</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="39.6" customHeight="1" s="72">
+      <c r="A27" s="65" t="inlineStr">
+        <is>
+          <t>P6-A23</t>
+        </is>
+      </c>
+      <c r="B27" s="69" t="n"/>
+      <c r="C27" s="90" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D27" s="90" t="inlineStr">
+        <is>
+          <t>Action Queue UI</t>
+        </is>
+      </c>
+      <c r="E27" s="90" t="inlineStr">
+        <is>
+          <t>Approve/reject list with type badges, Instamart cart-preview modal before approving checkout, procurement tracker (placed orders, status, ETA) in the inventory panel.</t>
+        </is>
+      </c>
+      <c r="F27" s="90" t="inlineStr">
+        <is>
+          <t>feat: Action Queue UI -- approve/reject with cart preview, procurement tracker</t>
+        </is>
+      </c>
+      <c r="G27" s="90" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="H27" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I27" s="89" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J27" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K27" s="89" t="n"/>
+      <c r="L27" s="89" t="n"/>
+      <c r="M27" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="90" t="inlineStr">
+        <is>
+          <t>P6-A22</t>
+        </is>
+      </c>
+      <c r="O27" s="90" t="inlineStr">
+        <is>
+          <t>typecheck clean; manual verification against live action_queue data</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="39.6" customHeight="1" s="72">
+      <c r="A28" s="65" t="inlineStr">
+        <is>
+          <t>P6-A24</t>
+        </is>
+      </c>
+      <c r="B28" s="98" t="inlineStr">
+        <is>
+          <t>feature/agentic-automation</t>
+        </is>
+      </c>
+      <c r="C28" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D28" s="90" t="inlineStr">
+        <is>
+          <t>Workflow trigger engine (scoped: 2-3 built-in triggers, not a user-defined builder)</t>
+        </is>
+      </c>
+      <c r="E28" s="90" t="inlineStr">
+        <is>
+          <t>A small WorkflowEngine evaluating built-in conditions after each planning run and auto-creating action_queue rows. Ships with 2-3 real triggers to start: (1) 2+ critical shortages found -&gt; queue an urgent restock action, (2) tonight_busy + 2+ competitor Dineout deals live -&gt; queue a pricing/promo review action. Deliberately NOT the full owner-defined trigger/condition/action builder from the original workflow-system idea -- that's a much bigger UI/DB investment for marginal demo value beyond just having the triggers exist.</t>
+        </is>
+      </c>
+      <c r="F28" s="90" t="inlineStr">
+        <is>
+          <t>feat: workflow trigger engine -- built-in triggers auto-queue actions post-planning-run</t>
+        </is>
+      </c>
+      <c r="G28" s="90" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H28" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I28" s="89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J28" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K28" s="89" t="n"/>
+      <c r="L28" s="89" t="n"/>
+      <c r="M28" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="90" t="inlineStr">
+        <is>
+          <t>P6-A22</t>
+        </is>
+      </c>
+      <c r="O28" s="90" t="inlineStr">
+        <is>
+          <t>each trigger condition fires correctly and produces the right queued action</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="39.6" customHeight="1" s="72">
+      <c r="A29" s="65" t="inlineStr">
+        <is>
+          <t>P6-A25</t>
+        </is>
+      </c>
+      <c r="B29" s="69" t="n"/>
+      <c r="C29" s="90" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D29" s="90" t="inlineStr">
+        <is>
+          <t>Trust-ladder mechanic on the Action Queue</t>
+        </is>
+      </c>
+      <c r="E29" s="90" t="inlineStr">
+        <is>
+          <t>Track consecutive unedited approvals per action_type. After N consecutive approvals (default 3) of the same type, offer 'always do this automatically' -- promotes future instances of that action_type straight to AUTO tier for that org. Makes 'autonomous' a visible, explainable mechanic rather than a claim.</t>
+        </is>
+      </c>
+      <c r="F29" s="90" t="inlineStr">
+        <is>
+          <t>feat: trust-ladder -- auto-promote repeatedly-approved action types to AUTO tier</t>
+        </is>
+      </c>
+      <c r="G29" s="90" t="inlineStr">
+        <is>
+          <t>docs/ACTION_QUEUE.md</t>
+        </is>
+      </c>
+      <c r="H29" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I29" s="89" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J10" s="42" t="inlineStr">
+      <c r="J29" s="89" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K10" s="42" t="n"/>
-      <c r="L10" s="42" t="n"/>
-      <c r="M10" s="44" t="n">
+      <c r="K29" s="89" t="n"/>
+      <c r="L29" s="89" t="n"/>
+      <c r="M29" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="43" t="inlineStr">
-        <is>
-          <t>P6-A6</t>
-        </is>
-      </c>
-      <c r="O10" s="43" t="inlineStr">
-        <is>
-          <t>reviews ingested with correct source tag; complaint_intelligence node correctly surfaces public-review-sourced themes alongside internal ones</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52.05" customHeight="1" s="72">
-      <c r="A11" s="42" t="inlineStr">
-        <is>
-          <t>P6-A8</t>
-        </is>
-      </c>
-      <c r="B11" s="68" t="inlineStr">
-        <is>
-          <t>feature/financial-compliance</t>
-        </is>
-      </c>
-      <c r="C11" s="43" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D11" s="43" t="inlineStr">
-        <is>
-          <t>Financial scorecard -- Expense ledger + real P&amp;L</t>
-        </is>
-      </c>
-      <c r="E11" s="43" t="inlineStr">
-        <is>
-          <t>New Expense model (category: rent/utilities/marketing/labor-later/other, amount, recurrence). Extends business.py's existing revenue/margin computation into a real daily/weekly P&amp;L and one composite health score. Designed so labor slots in later as just another Expense category, not a rewrite.</t>
-        </is>
-      </c>
-      <c r="F11" s="43" t="inlineStr">
-        <is>
-          <t>feat: financial scorecard -- Expense ledger, real P&amp;L, composite health score</t>
-        </is>
-      </c>
-      <c r="G11" s="43" t="inlineStr">
+      <c r="N29" s="90" t="inlineStr">
+        <is>
+          <t>P6-A22</t>
+        </is>
+      </c>
+      <c r="O29" s="90" t="inlineStr">
+        <is>
+          <t>N consecutive approvals triggers promotion prompt; promoted type skips approval next time</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="39.6" customHeight="1" s="72">
+      <c r="A30" s="65" t="inlineStr">
+        <is>
+          <t>P6-A26</t>
+        </is>
+      </c>
+      <c r="B30" s="98" t="inlineStr">
+        <is>
+          <t>feature/dynamic-pricing</t>
+        </is>
+      </c>
+      <c r="C30" s="90" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D30" s="90" t="inlineStr">
+        <is>
+          <t>Dynamic pricing engine -- PriceChangeProposal (internal menu only)</t>
+        </is>
+      </c>
+      <c r="E30" s="90" t="inlineStr">
+        <is>
+          <t>New PriceChangeProposal model (item, current_price, suggested_price, reason, source, created_at). Computed from existing category_pricing/positioning data already in CompetitorEnricher. Surfaces as a new action_type in the Action Queue -- approving it updates your own MenuItem.price. Explicitly scoped to internal-only; does NOT attempt to sync price changes out to live Swiggy/Zomato listings (that needs Partner API access we don't have).</t>
+        </is>
+      </c>
+      <c r="F30" s="90" t="inlineStr">
+        <is>
+          <t>feat: dynamic pricing engine -- competitor-data-driven price suggestions via the Action Queue</t>
+        </is>
+      </c>
+      <c r="G30" s="90" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md, CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H30" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I30" s="89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J30" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K30" s="89" t="n"/>
+      <c r="L30" s="89" t="n"/>
+      <c r="M30" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="90" t="inlineStr">
+        <is>
+          <t>P6-A22</t>
+        </is>
+      </c>
+      <c r="O30" s="90" t="inlineStr">
+        <is>
+          <t>suggestion computed correctly from category_pricing gap; approving updates MenuItem.price; PriceChangeProposal row persists as an audit trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="39.6" customHeight="1" s="72">
+      <c r="A31" s="65" t="inlineStr">
+        <is>
+          <t>P6-A27</t>
+        </is>
+      </c>
+      <c r="B31" s="69" t="n"/>
+      <c r="C31" s="90" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D31" s="90" t="inlineStr">
+        <is>
+          <t>Outcome / recommendation-learning memory</t>
+        </is>
+      </c>
+      <c r="E31" s="90" t="inlineStr">
+        <is>
+          <t>Extend the existing Qdrant-backed cross-session memory pattern (P6-S09) to track whether past actions/recommendations actually worked (e.g. did an approved price change move margin next week? did an approved restock prevent a stockout?). Feed this back into future confidence scoring on similar suggestions.</t>
+        </is>
+      </c>
+      <c r="F31" s="90" t="inlineStr">
+        <is>
+          <t>feat: outcome-learning memory -- track whether past AI actions worked, feed back into future confidence</t>
+        </is>
+      </c>
+      <c r="G31" s="90" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H31" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I31" s="89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J31" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K31" s="89" t="n"/>
+      <c r="L31" s="89" t="n"/>
+      <c r="M31" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="90" t="inlineStr">
+        <is>
+          <t>P6-A22, P6-A26</t>
+        </is>
+      </c>
+      <c r="O31" s="90" t="inlineStr">
+        <is>
+          <t>outcome recorded correctly against the originating action; confidence score shifts on repeat suggestion of the same type after a bad outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="39.6" customHeight="1" s="72">
+      <c r="A32" s="65" t="inlineStr">
+        <is>
+          <t>P6-A28</t>
+        </is>
+      </c>
+      <c r="B32" s="98" t="inlineStr">
+        <is>
+          <t>feature/procurement-dineout-executors</t>
+        </is>
+      </c>
+      <c r="C32" s="90" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D32" s="90" t="inlineStr">
+        <is>
+          <t>ProcurementExecutor -- full flow, mocked final checkout call</t>
+        </is>
+      </c>
+      <c r="E32" s="90" t="inlineStr">
+        <is>
+          <t>Full update_cart -&gt; get_cart -&gt; LangGraph interrupt() -&gt; owner approval (via Action Queue) -&gt; checkout flow, built completely end-to-end. The actual final checkout() call is stubbed/mocked, clearly labeled 'awaiting Swiggy staging creds' -- everything else (cart building, pricing, approval gate, procurement_orders row creation) is real. Swapping the mock for a real call is Phase B's entire scope for this task. DEFERRED to end of Phase A pending direct restaurant-owner research into real procurement workflow (bulk orders, WhatsApp/phone to local vendors) -- see P6-A31.</t>
+        </is>
+      </c>
+      <c r="F32" s="90" t="inlineStr">
+        <is>
+          <t>feat: ProcurementExecutor -- full approval-gated Instamart flow, checkout call mocked pending staging creds</t>
+        </is>
+      </c>
+      <c r="G32" s="90" t="inlineStr">
+        <is>
+          <t>docs/ACTION_QUEUE.md, CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H32" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I32" s="89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J32" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K32" s="89" t="n"/>
+      <c r="L32" s="89" t="n"/>
+      <c r="M32" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="90" t="inlineStr">
+        <is>
+          <t>P6-A22</t>
+        </is>
+      </c>
+      <c r="O32" s="90" t="inlineStr">
+        <is>
+          <t>full flow test with mocked checkout; interrupt() pauses correctly; procurement_orders row created with a clear 'simulated' flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="39.6" customHeight="1" s="72">
+      <c r="A33" s="65" t="inlineStr">
+        <is>
+          <t>P6-A29</t>
+        </is>
+      </c>
+      <c r="B33" s="69" t="n"/>
+      <c r="C33" s="90" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D33" s="90" t="inlineStr">
+        <is>
+          <t>DineoutExecutor -- full flow, mocked final book_table call</t>
+        </is>
+      </c>
+      <c r="E33" s="90" t="inlineStr">
+        <is>
+          <t>Same pattern as P6-A24 for Dineout: create_cart -&gt; book_table, approval-gated via Action Queue, real logic throughout except the final book_table() call is mocked pending staging creds.</t>
+        </is>
+      </c>
+      <c r="F33" s="90" t="inlineStr">
+        <is>
+          <t>feat: DineoutExecutor -- full approval-gated Dineout booking flow, book_table call mocked pending staging creds</t>
+        </is>
+      </c>
+      <c r="G33" s="90" t="inlineStr">
+        <is>
+          <t>docs/ACTION_QUEUE.md</t>
+        </is>
+      </c>
+      <c r="H33" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I33" s="89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J33" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K33" s="89" t="n"/>
+      <c r="L33" s="89" t="n"/>
+      <c r="M33" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="90" t="inlineStr">
+        <is>
+          <t>P6-A22, P6-A28</t>
+        </is>
+      </c>
+      <c r="O33" s="90" t="inlineStr">
+        <is>
+          <t>full flow test with mocked book_table; reservations row created with a clear 'simulated' flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="52.8" customHeight="1" s="72">
+      <c r="A34" s="65" t="inlineStr">
+        <is>
+          <t>P6-A30</t>
+        </is>
+      </c>
+      <c r="B34" s="98" t="inlineStr">
+        <is>
+          <t>feature/recipe-vendor-foundations</t>
+        </is>
+      </c>
+      <c r="C34" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D34" s="90" t="inlineStr">
+        <is>
+          <t>Recipe + RecipeIngredient model</t>
+        </is>
+      </c>
+      <c r="E34" s="90" t="inlineStr">
+        <is>
+          <t>New Recipe (menu_item_id) + RecipeIngredient (recipe_id, ingredient, quantity, unit) tables. Bridges MenuItem and inventory -- unlocks live-computed cost_price (from real ingredient prices) instead of manual entry, and real per-dish inventory depletion instead of aggregate-only shortage tracking. DEFERRED to end of Phase A alongside the rest of the procurement/Action Queue cluster, pending direct restaurant-owner research into how real procurement actually works.</t>
+        </is>
+      </c>
+      <c r="F34" s="90" t="inlineStr">
+        <is>
+          <t>feat: Recipe + RecipeIngredient models -- dish-to-ingredient yield mapping</t>
+        </is>
+      </c>
+      <c r="G34" s="90" t="inlineStr">
+        <is>
+          <t>docs/DATA_MODEL.md</t>
+        </is>
+      </c>
+      <c r="H34" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I34" s="89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J34" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K34" s="89" t="n"/>
+      <c r="L34" s="89" t="n"/>
+      <c r="M34" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="90" t="n"/>
+      <c r="O34" s="90" t="inlineStr">
+        <is>
+          <t>recipe costing test (sum of ingredient costs matches computed cost_price); depletion test (a sale reduces linked ingredient stock by the right amount)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="171.6" customHeight="1" s="72">
+      <c r="A35" s="65" t="inlineStr">
+        <is>
+          <t>P6-A31</t>
+        </is>
+      </c>
+      <c r="B35" s="69" t="n"/>
+      <c r="C35" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D35" s="90" t="inlineStr">
+        <is>
+          <t>Vendor/Supplier model</t>
+        </is>
+      </c>
+      <c r="E35" s="90" t="inlineStr">
+        <is>
+          <t>New Vendor model (name, category, is_online, contact) + VendorPriceQuote (vendor_id, ingredient, price, quoted_at). Instamart becomes one Vendor among several (an 'online' vendor with live API pricing); local mandi/wholesale vendors become trackable entities with manually-entered or periodically-surveyed prices. Scoped as tracking/comparison only, not a marketplace. DEFERRED to end of Phase A -- exact procurement medium (Instamart API vs a WhatsApp-dispatch message to a local vendor vs other) intentionally left open pending direct conversation with a real restaurant owner/manager about their actual ordering process, before committing to a design.</t>
+        </is>
+      </c>
+      <c r="F35" s="90" t="inlineStr">
+        <is>
+          <t>feat: Vendor/Supplier model -- Instamart becomes one vendor among many, not the only source</t>
+        </is>
+      </c>
+      <c r="G35" s="90" t="inlineStr">
+        <is>
+          <t>docs/DATA_MODEL.md</t>
+        </is>
+      </c>
+      <c r="H35" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I35" s="89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J35" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K35" s="89" t="n"/>
+      <c r="L35" s="89" t="n"/>
+      <c r="M35" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="90" t="inlineStr">
+        <is>
+          <t>P6-A30</t>
+        </is>
+      </c>
+      <c r="O35" s="90" t="inlineStr">
+        <is>
+          <t>vendor price comparison query returns correct cheapest-vendor-per-ingredient</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="39.6" customHeight="1" s="72">
+      <c r="A36" s="65" t="inlineStr">
+        <is>
+          <t>P6-A32</t>
+        </is>
+      </c>
+      <c r="B36" s="98" t="inlineStr">
+        <is>
+          <t>feature/mcp-expansion</t>
+        </is>
+      </c>
+      <c r="C36" s="90" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D36" s="90" t="inlineStr">
+        <is>
+          <t>Internal MCP server -- get_market_brief / get_action_queue / approve_action</t>
+        </is>
+      </c>
+      <c r="E36" s="90" t="inlineStr">
+        <is>
+          <t>3 new tools on CortexKitchen's own MCP server (mcp_server.py), JWT-authenticated, calling MarketIntelService and ActionQueueService live. Lets an owner ask Claude Desktop directly about their restaurant and approve actions from there.</t>
+        </is>
+      </c>
+      <c r="F36" s="90" t="inlineStr">
+        <is>
+          <t>feat: 3 new MCP tools -- get_market_brief, get_action_queue, approve_action</t>
+        </is>
+      </c>
+      <c r="G36" s="90" t="inlineStr">
+        <is>
+          <t>docs/APIS.md, docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H36" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I36" s="89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J36" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K36" s="89" t="n"/>
+      <c r="L36" s="89" t="n"/>
+      <c r="M36" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="90" t="inlineStr">
+        <is>
+          <t>P6-A22</t>
+        </is>
+      </c>
+      <c r="O36" s="90" t="inlineStr">
+        <is>
+          <t>all 3 tools smoke-tested in Claude Desktop; approve_action triggers the same approval path as the web UI; JWT enforced</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="39.6" customHeight="1" s="72">
+      <c r="A37" s="65" t="inlineStr">
+        <is>
+          <t>P6-A33</t>
+        </is>
+      </c>
+      <c r="B37" s="69" t="n"/>
+      <c r="C37" s="90" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D37" s="90" t="inlineStr">
+        <is>
+          <t>Internal MCP server -- expand further (menu insights, forecast, what-if)</t>
+        </is>
+      </c>
+      <c r="E37" s="90" t="inlineStr">
+        <is>
+          <t>Wrap additional existing services as MCP tools beyond the 3 in P6-A31 -- menu insights, demand forecast, and the Phase-5 what-if simulator. Cheap since the service layer already exists; positions CortexKitchen as a general AI-accessible restaurant data layer, not just 3 utility tools.</t>
+        </is>
+      </c>
+      <c r="F37" s="90" t="inlineStr">
+        <is>
+          <t>feat: expand internal MCP server -- menu insights, forecast, what-if simulator as tools</t>
+        </is>
+      </c>
+      <c r="G37" s="90" t="inlineStr">
         <is>
           <t>docs/APIS.md</t>
         </is>
       </c>
-      <c r="H11" s="41" t="inlineStr">
+      <c r="H37" s="108" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I11" s="42" t="inlineStr">
+      <c r="I37" s="89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J37" s="89" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K37" s="89" t="n"/>
+      <c r="L37" s="89" t="n"/>
+      <c r="M37" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="90" t="inlineStr">
+        <is>
+          <t>P6-A32</t>
+        </is>
+      </c>
+      <c r="O37" s="90" t="inlineStr">
+        <is>
+          <t>each new tool smoke-tested in Claude Desktop; correct data returned matching the equivalent API endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="52.8" customHeight="1" s="72">
+      <c r="A38" s="65" t="inlineStr">
+        <is>
+          <t>P6-A34</t>
+        </is>
+      </c>
+      <c r="B38" s="98" t="inlineStr">
+        <is>
+          <t>feature/brief-page</t>
+        </is>
+      </c>
+      <c r="C38" s="90" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D38" s="90" t="inlineStr">
+        <is>
+          <t>/brief page</t>
+        </is>
+      </c>
+      <c r="E38" s="90" t="inlineStr">
+        <is>
+          <t>Daily morning briefing -- overnight performance, today's forecast vs yesterday, top 3 action priorities, market snapshot. Single-screen showcase of the whole system's intelligence.</t>
+        </is>
+      </c>
+      <c r="F38" s="90" t="inlineStr">
+        <is>
+          <t>feat: /brief page -- daily morning operational briefing</t>
+        </is>
+      </c>
+      <c r="G38" s="90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H38" s="108" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I38" s="89" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J11" s="42" t="inlineStr">
+      <c r="J38" s="89" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K11" s="42" t="n"/>
-      <c r="L11" s="42" t="n"/>
-      <c r="M11" s="44" t="n">
+      <c r="K38" s="89" t="n"/>
+      <c r="L38" s="89" t="n"/>
+      <c r="M38" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="43" t="n"/>
-      <c r="O11" s="43" t="inlineStr">
-        <is>
-          <t>P&amp;L numbers match seeded expense + revenue data; health score computes deterministically from known inputs</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52.05" customHeight="1" s="72">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>P6-A9</t>
-        </is>
-      </c>
-      <c r="B12" s="69" t="n"/>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>Compliance / Obligations calendar</t>
-        </is>
-      </c>
-      <c r="E12" s="43" t="inlineStr">
-        <is>
-          <t>Generalized Obligation model (type: license-renewal/GST-filing/inspection/other, due_date, status) with reminders delivered through the existing Phase-5 email digest mechanism rather than a new one-off sender. Not a GST computation/invoicing layer -- just a dated-obligation tracker with reminders.</t>
-        </is>
-      </c>
-      <c r="F12" s="43" t="inlineStr">
-        <is>
-          <t>feat: compliance/obligations calendar -- reminder engine reusing the existing email digest</t>
-        </is>
-      </c>
-      <c r="G12" s="43" t="inlineStr">
-        <is>
-          <t>docs/APIS.md</t>
-        </is>
-      </c>
-      <c r="H12" s="41" t="inlineStr">
+      <c r="N38" s="90" t="inlineStr">
+        <is>
+          <t>P6-A23</t>
+        </is>
+      </c>
+      <c r="O38" s="90" t="inlineStr">
+        <is>
+          <t>manual verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="171.6" customHeight="1" s="72">
+      <c r="A39" s="65" t="inlineStr">
+        <is>
+          <t>P6-A35</t>
+        </is>
+      </c>
+      <c r="B39" s="98" t="n"/>
+      <c r="C39" s="90" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D39" s="90" t="inlineStr">
+        <is>
+          <t>Post-Phase-A documentation, test, CI, observability, and eval refresh</t>
+        </is>
+      </c>
+      <c r="E39" s="90" t="inlineStr">
+        <is>
+          <t>Once Phase A ships, a lot of new surface area will have landed at once -- Action Queue, workflow triggers, the anomaly agent, both executors, new connectors (Zomato stub, reviews), new data models (Recipe, Vendor, Expense, Obligation), MCP expansion. Do a full pass rather than letting docs drift: update every docs/*.md file, CLAUDE.md, README, and any screenshots referenced in docs to reflect what actually shipped. Audit test coverage for every new service/model added in Phase A -- confirm nothing shipped without tests. Re-check the CI pipeline includes all new test files. Re-run/expand RAGAS + DeepEval evals to cover the new agentic behaviors (anomaly diagnoses, dynamic pricing suggestions), since the existing eval sets predate all of this and won't catch regressions in it.</t>
+        </is>
+      </c>
+      <c r="F39" s="90" t="inlineStr">
+        <is>
+          <t>docs: full documentation, test-coverage, CI, and eval refresh after the Phase A agentic core ships</t>
+        </is>
+      </c>
+      <c r="G39" s="90" t="inlineStr">
+        <is>
+          <t>All docs/*.md, CLAUDE.md, README.md</t>
+        </is>
+      </c>
+      <c r="H39" s="108" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I12" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J12" s="42" t="inlineStr">
+      <c r="I39" s="89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J39" s="89" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="44" t="n">
+      <c r="K39" s="89" t="n"/>
+      <c r="L39" s="89" t="n"/>
+      <c r="M39" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="43" t="n"/>
-      <c r="O12" s="43" t="inlineStr">
-        <is>
-          <t>reminder fires at the correct lead-time before due_date; reuses existing digest delivery path</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" s="72">
-      <c r="A13" s="42" t="inlineStr">
-        <is>
-          <t>P6-A10</t>
-        </is>
-      </c>
-      <c r="B13" s="68" t="inlineStr">
-        <is>
-          <t>feature/location-architecture</t>
-        </is>
-      </c>
-      <c r="C13" s="43" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D13" s="43" t="inlineStr">
-        <is>
-          <t>Location-aware enrichers (hedge for multi-location)</t>
-        </is>
-      </c>
-      <c r="E13" s="43" t="inlineStr">
-        <is>
-          <t>Thread an explicit location/address context through MarketIntelService and all 3 enrichers instead of a single hardcoded SWIGGY_ADDRESS_ID -- cheap to do now, expensive to retrofit once multi-location (P6-A31) exists or once real customers have multiple outlets.</t>
-        </is>
-      </c>
-      <c r="F13" s="43" t="inlineStr">
-        <is>
-          <t>feat: location-aware enrichers -- pass address/location context through instead of one hardcoded address</t>
-        </is>
-      </c>
-      <c r="G13" s="43" t="inlineStr">
-        <is>
-          <t>CLAUDE.md</t>
-        </is>
-      </c>
-      <c r="H13" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I13" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J13" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="43" t="n"/>
-      <c r="O13" s="43" t="inlineStr">
-        <is>
-          <t>enrichers accept and correctly use a passed-in address_id, defaulting to the existing single-address behavior when none given</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52.05" customHeight="1" s="72">
-      <c r="A14" s="42" t="inlineStr">
-        <is>
-          <t>P6-A11</t>
-        </is>
-      </c>
-      <c r="B14" s="69" t="n"/>
-      <c r="C14" s="43" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D14" s="43" t="inlineStr">
-        <is>
-          <t>Multi-location / Restaurant entity -- STRATEGIC, needs explicit go/no-go</t>
-        </is>
-      </c>
-      <c r="E14" s="43" t="inlineStr">
-        <is>
-          <t>Introduce Restaurant as a first-class entity between Organization and everything else (menu, inventory, planning runs, Swiggy connector -- each physical location has its own Swiggy restaurant ID). Add restaurant_id to MenuItem/InventoryItem/PlanningRun/connectors. Cheaper to do now while the schema is small than to retrofit later. NOT started until the user confirms real near-term demand justifies it over other Phase A work.</t>
-        </is>
-      </c>
-      <c r="F14" s="43" t="inlineStr">
-        <is>
-          <t>feat: Restaurant entity -- first-class multi-location support</t>
-        </is>
-      </c>
-      <c r="G14" s="43" t="inlineStr">
-        <is>
-          <t>docs/DATA_MODEL.md, docs/DECISIONS.md</t>
-        </is>
-      </c>
-      <c r="H14" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I14" s="42" t="inlineStr">
-        <is>
-          <t>Low (pending go/no-go)</t>
-        </is>
-      </c>
-      <c r="J14" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K14" s="42" t="n"/>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="43" t="inlineStr">
-        <is>
-          <t>P6-A10</t>
-        </is>
-      </c>
-      <c r="O14" s="43" t="inlineStr">
-        <is>
-          <t>existing single-location orgs continue to work unchanged (default restaurant backfilled); cross-location query test once 2+ restaurants exist</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52.05" customHeight="1" s="72">
-      <c r="A15" s="42" t="inlineStr">
-        <is>
-          <t>P6-A12</t>
-        </is>
-      </c>
-      <c r="B15" s="68" t="inlineStr">
-        <is>
-          <t>feature/chatbot-dineout-tools</t>
-        </is>
-      </c>
-      <c r="C15" s="43" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D15" s="43" t="inlineStr">
-        <is>
-          <t>Chatbot -- Dineout competitive query tools</t>
-        </is>
-      </c>
-      <c r="E15" s="43" t="inlineStr">
-        <is>
-          <t>3 Groq function-calling tools for the existing chatbot: get_competitor_deals, get_area_occupancy, get_trending_dishes -- all using Swiggy's existing read-only Dineout MCP (search_restaurants_dineout, get_restaurant_details, get_available_slots), already-proven tools. (Formerly P6-MI04; renumbered as part of the Phase 6 replan.)</t>
-        </is>
-      </c>
-      <c r="F15" s="43" t="inlineStr">
-        <is>
-          <t>feat: chatbot Dineout tools -- competitor deals, area occupancy, trending dishes</t>
-        </is>
-      </c>
-      <c r="G15" s="43" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md</t>
-        </is>
-      </c>
-      <c r="H15" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I15" s="42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J15" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K15" s="42" t="n"/>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="43" t="n"/>
-      <c r="O15" s="43" t="inlineStr">
-        <is>
-          <t>all 3 tools callable from /chat; correct Swiggy data returned; graceful None on failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52.05" customHeight="1" s="72">
-      <c r="A16" s="42" t="inlineStr">
-        <is>
-          <t>P6-A13</t>
-        </is>
-      </c>
-      <c r="B16" s="69" t="n"/>
-      <c r="C16" s="43" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D16" s="43" t="inlineStr">
-        <is>
-          <t>Structured outputs -- tool_choice=required across chatbot tools</t>
-        </is>
-      </c>
-      <c r="E16" s="43" t="inlineStr">
-        <is>
-          <t>Upgrade chatbot Groq calls to tool_choice=required + strict JSON schema across all chatbot tools (Swiggy and internal). Chatbot function calls never hallucinate JSON.</t>
-        </is>
-      </c>
-      <c r="F16" s="43" t="inlineStr">
-        <is>
-          <t>feat: structured outputs -- tool_choice=required across all chatbot tools</t>
-        </is>
-      </c>
-      <c r="G16" s="43" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md</t>
-        </is>
-      </c>
-      <c r="H16" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I16" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J16" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K16" s="42" t="n"/>
-      <c r="L16" s="42" t="n"/>
-      <c r="M16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="43" t="inlineStr">
-        <is>
-          <t>P6-A12</t>
-        </is>
-      </c>
-      <c r="O16" s="43" t="inlineStr">
-        <is>
-          <t>schema validation test; chatbot returns valid JSON on repeated calls</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52.05" customHeight="1" s="72">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>P6-A14</t>
-        </is>
-      </c>
-      <c r="B17" s="68" t="inlineStr">
-        <is>
-          <t>feature/llm-cost-quality</t>
-        </is>
-      </c>
-      <c r="C17" s="43" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D17" s="43" t="inlineStr">
-        <is>
-          <t>Prompt caching -- critic + aggregator</t>
-        </is>
-      </c>
-      <c r="E17" s="43" t="inlineStr">
-        <is>
-          <t>Add prompt-caching headers to critic and aggregator LLM calls (both have long, repeated system prompts). Cuts LLM cost per planning run; invisible to a demo but real cost hygiene.</t>
-        </is>
-      </c>
-      <c r="F17" s="43" t="inlineStr">
-        <is>
-          <t>feat: prompt caching -- cut LLM costs on critic and aggregator nodes</t>
-        </is>
-      </c>
-      <c r="G17" s="43" t="inlineStr">
-        <is>
-          <t>docs/ARCHITECTURE.md</t>
-        </is>
-      </c>
-      <c r="H17" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I17" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J17" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K17" s="42" t="n"/>
-      <c r="L17" s="42" t="n"/>
-      <c r="M17" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="43" t="n"/>
-      <c r="O17" s="43" t="inlineStr">
-        <is>
-          <t>cost log shows cache_hit=true on second run of the same scenario</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" s="72">
-      <c r="A18" s="42" t="inlineStr">
-        <is>
-          <t>P6-A15</t>
-        </is>
-      </c>
-      <c r="B18" s="69" t="n"/>
-      <c r="C18" s="43" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="D18" s="43" t="inlineStr">
-        <is>
-          <t>Multi-agent debate critic</t>
-        </is>
-      </c>
-      <c r="E18" s="43" t="inlineStr">
-        <is>
-          <t>Two LLM critic instances (optimistic vs conservative), structured debate, moderator resolves disagreement. Marginal demo-visible upside over the existing single critic given the added cost/latency -- kept low priority.</t>
-        </is>
-      </c>
-      <c r="F18" s="43" t="inlineStr">
-        <is>
-          <t>feat: multi-agent debate critic -- consensus scoring</t>
-        </is>
-      </c>
-      <c r="G18" s="43" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md</t>
-        </is>
-      </c>
-      <c r="H18" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I18" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J18" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K18" s="42" t="n"/>
-      <c r="L18" s="42" t="n"/>
-      <c r="M18" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="43" t="n"/>
-      <c r="O18" s="43" t="inlineStr">
-        <is>
-          <t>debate resolves on test plans; disagreement cases escalate correctly</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52.05" customHeight="1" s="72">
-      <c r="A19" s="42" t="inlineStr">
-        <is>
-          <t>P6-A16</t>
-        </is>
-      </c>
-      <c r="B19" s="68" t="inlineStr">
-        <is>
-          <t>feature/ci-eval-hygiene</t>
-        </is>
-      </c>
-      <c r="C19" s="43" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D19" s="43" t="inlineStr">
-        <is>
-          <t>Fix SQLite/JSONB CI test-infra gap</t>
-        </is>
-      </c>
-      <c r="E19" s="43" t="inlineStr">
-        <is>
-          <t>test_swiggy_reservation_sync.py and test_connector_repository.py are excluded from CI because SQLite can't render Postgres JSONB columns. Either a SQLite-compatible fallback type or a Postgres CI service container.</t>
-        </is>
-      </c>
-      <c r="F19" s="43" t="inlineStr">
-        <is>
-          <t>fix: SQLite-compatible JSONB handling (or Postgres CI service) for excluded test files</t>
-        </is>
-      </c>
-      <c r="G19" s="43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H19" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I19" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J19" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K19" s="42" t="n"/>
-      <c r="L19" s="42" t="n"/>
-      <c r="M19" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="43" t="n"/>
-      <c r="O19" s="43" t="inlineStr">
-        <is>
-          <t>previously-excluded test files run in CI</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="7.95" customHeight="1" s="72">
-      <c r="A20" s="42" t="inlineStr">
-        <is>
-          <t>P6-A17</t>
-        </is>
-      </c>
-      <c r="B20" s="70" t="n"/>
-      <c r="C20" s="43" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D20" s="43" t="inlineStr">
-        <is>
-          <t>Promote reviewed RAGAS/DeepEval candidates</t>
-        </is>
-      </c>
-      <c r="E20" s="43" t="inlineStr">
-        <is>
-          <t>Recurring habit of running the existing candidate-generation scripts and hand-promoting reviewed candidates into the curated eval datasets.</t>
-        </is>
-      </c>
-      <c r="F20" s="43" t="inlineStr">
-        <is>
-          <t>chore: promote reviewed eval candidates into curated datasets</t>
-        </is>
-      </c>
-      <c r="G20" s="43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H20" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I20" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J20" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K20" s="42" t="n"/>
-      <c r="L20" s="42" t="n"/>
-      <c r="M20" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="43" t="n"/>
-      <c r="O20" s="43" t="inlineStr">
-        <is>
-          <t>N/A -- ongoing process, not a one-time build</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="52.05" customHeight="1" s="72">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>P6-A18</t>
-        </is>
-      </c>
-      <c r="B21" s="69" t="n"/>
-      <c r="C21" s="43" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D21" s="43" t="inlineStr">
-        <is>
-          <t>Regenerate golden_runs.json against real data</t>
-        </is>
-      </c>
-      <c r="E21" s="43" t="inlineStr">
-        <is>
-          <t>The key-path bug in build_golden_dataset.py is already fixed; the checked-in fixture still reflects the old broken extraction. Regenerate once real run history exists.</t>
-        </is>
-      </c>
-      <c r="F21" s="43" t="inlineStr">
-        <is>
-          <t>chore: regenerate golden_runs.json with corrected extraction logic</t>
-        </is>
-      </c>
-      <c r="G21" s="43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H21" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I21" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J21" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K21" s="42" t="n"/>
-      <c r="L21" s="42" t="n"/>
-      <c r="M21" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="43" t="n"/>
-      <c r="O21" s="43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="52.05" customHeight="1" s="72">
-      <c r="A22" s="42" t="inlineStr">
-        <is>
-          <t>P6-A19</t>
-        </is>
-      </c>
-      <c r="B22" s="68" t="inlineStr">
-        <is>
-          <t>feature/menu-engineering-matrix</t>
-        </is>
-      </c>
-      <c r="C22" s="43" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D22" s="43" t="inlineStr">
-        <is>
-          <t>Menu engineering matrix UI</t>
-        </is>
-      </c>
-      <c r="E22" s="43" t="inlineStr">
-        <is>
-          <t>Stars/plow-horses/dogs/puzzles quadrant chart using margin_pct x quantity, both already computed in business.py -- just needs quadrant classification + a chart.</t>
-        </is>
-      </c>
-      <c r="F22" s="43" t="inlineStr">
-        <is>
-          <t>feat: menu engineering matrix -- margin x popularity quadrant chart</t>
-        </is>
-      </c>
-      <c r="G22" s="43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H22" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I22" s="42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J22" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K22" s="42" t="n"/>
-      <c r="L22" s="42" t="n"/>
-      <c r="M22" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="43" t="n"/>
-      <c r="O22" s="43" t="inlineStr">
-        <is>
-          <t>quadrant classification unit test; chart renders correctly</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="7.95" customHeight="1" s="72">
-      <c r="A23" s="42" t="inlineStr">
-        <is>
-          <t>P6-A20</t>
-        </is>
-      </c>
-      <c r="B23" s="68" t="inlineStr">
-        <is>
-          <t>feature/pages-redesign</t>
-        </is>
-      </c>
-      <c r="C23" s="43" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D23" s="43" t="inlineStr">
-        <is>
-          <t>all page redesign via claude design</t>
-        </is>
-      </c>
-      <c r="E23" s="43" t="inlineStr">
-        <is>
-          <t>Apply the existing design system to /runs -- currently the weakest-looking screen (dense monospace debug trace). Fix the unstyled raw 404 on /runs/{id} deep links.</t>
-        </is>
-      </c>
-      <c r="F23" s="43" t="inlineStr">
-        <is>
-          <t>feat: redesign /runs history page + fix /runs/{id} deep-link 404</t>
-        </is>
-      </c>
-      <c r="G23" s="43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H23" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I23" s="42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J23" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K23" s="42" t="n"/>
-      <c r="L23" s="42" t="n"/>
-      <c r="M23" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="43" t="n"/>
-      <c r="O23" s="43" t="inlineStr">
-        <is>
-          <t>direct navigation to /runs/{id} renders the run, not a 404</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" s="72">
-      <c r="A24" s="42" t="inlineStr">
-        <is>
-          <t>P6-A21</t>
-        </is>
-      </c>
-      <c r="B24" s="68" t="inlineStr">
-        <is>
-          <t>feature/voice-interface</t>
-        </is>
-      </c>
-      <c r="C24" s="43" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D24" s="43" t="inlineStr">
-        <is>
-          <t>Voice interface</t>
-        </is>
-      </c>
-      <c r="E24" s="43" t="inlineStr">
-        <is>
-          <t>Whisper transcription on browser-recorded question, existing RAG chatbot answers, TTS reads back.</t>
-        </is>
-      </c>
-      <c r="F24" s="43" t="inlineStr">
-        <is>
-          <t>feat: voice interface -- Whisper transcription + RAG answer + TTS readback</t>
-        </is>
-      </c>
-      <c r="G24" s="43" t="inlineStr">
-        <is>
-          <t>docs/PRODUCT_MODES.md</t>
-        </is>
-      </c>
-      <c r="H24" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I24" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J24" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K24" s="42" t="n"/>
-      <c r="L24" s="42" t="n"/>
-      <c r="M24" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="43" t="n"/>
-      <c r="O24" s="43" t="inlineStr">
-        <is>
-          <t>transcription accuracy smoke test; end-to-end voice -&gt; RAG answer -&gt; TTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="52.05" customHeight="1" s="72">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>P6-A22</t>
-        </is>
-      </c>
-      <c r="B25" s="68" t="inlineStr">
-        <is>
-          <t>feature/live-page-redesign</t>
-        </is>
-      </c>
-      <c r="C25" s="43" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D25" s="43" t="inlineStr">
-        <is>
-          <t>/live page -- reframed as alerts/synthesis overlay</t>
-        </is>
-      </c>
-      <c r="E25" s="43" t="inlineStr">
-        <is>
-          <t>NOT a live order board (that's POS/aggregator territory and touches personal Swiggy consumer data). Instead: an alerts-and-synthesis overlay surfacing cross-referenced signals (e.g. 'order running late -- here's why, per our own data') during service hours.</t>
-        </is>
-      </c>
-      <c r="F25" s="43" t="inlineStr">
-        <is>
-          <t>feat: /live page -- alerts and synthesis overlay, not a live order feed</t>
-        </is>
-      </c>
-      <c r="G25" s="43" t="inlineStr">
-        <is>
-          <t>docs/PRODUCT_MODES.md</t>
-        </is>
-      </c>
-      <c r="H25" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I25" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J25" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K25" s="42" t="n"/>
-      <c r="L25" s="42" t="n"/>
-      <c r="M25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="43" t="inlineStr">
-        <is>
-          <t>P6-A5</t>
-        </is>
-      </c>
-      <c r="O25" s="43" t="inlineStr">
-        <is>
-          <t>manual verification</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="52.8" customHeight="1" s="72">
-      <c r="A26" s="67" t="n"/>
-      <c r="B26" s="67" t="n"/>
-      <c r="C26" s="67" t="n"/>
-      <c r="D26" s="67" t="n"/>
-      <c r="E26" s="67" t="n"/>
-      <c r="F26" s="67" t="n"/>
-      <c r="G26" s="67" t="n"/>
-      <c r="H26" s="67" t="n"/>
-      <c r="I26" s="67" t="n"/>
-      <c r="J26" s="67" t="n"/>
-      <c r="K26" s="67" t="n"/>
-      <c r="L26" s="67" t="n"/>
-      <c r="M26" s="67" t="n"/>
-      <c r="N26" s="67" t="n"/>
-      <c r="O26" s="67" t="n"/>
-    </row>
-    <row r="27" ht="39.6" customHeight="1" s="72">
-      <c r="A27" s="109" t="inlineStr">
-        <is>
-          <t>DEFERRED TO END OF PHASE A -- pending direct restaurant-owner research into real procurement/approval workflow</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="39.6" customHeight="1" s="72">
-      <c r="A28" s="42" t="inlineStr">
-        <is>
-          <t>P6-A23</t>
-        </is>
-      </c>
-      <c r="B28" s="68" t="inlineStr">
-        <is>
-          <t>feature/action-queue</t>
-        </is>
-      </c>
-      <c r="C28" s="43" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>ActionQueueService + action_queue table</t>
-        </is>
-      </c>
-      <c r="E28" s="43" t="inlineStr">
-        <is>
-          <t>New table (org_id, action_type [AUTO/APPROVE_REQUIRED/RECOMMENDATION], payload jsonb, status [PENDING/APPROVED/EXECUTED/REJECTED/EXPIRED], approved_by, executed_at, error). ActionQueueService CRUD + status transitions. Plan output gains an action_queue section in the API response. Foundational -- every other agentic task below (workflow triggers, dynamic pricing, executors, trust-ladder) writes into this same table rather than inventing its own approval mechanism. DEFERRED to end of Phase A -- its main real-world value (approving reorder suggestions) is exactly the workflow that needs real restaurant-owner input first; building the approval UX before that research risks designing around the wrong assumptions.</t>
-        </is>
-      </c>
-      <c r="F28" s="43" t="inlineStr">
-        <is>
-          <t>feat: ActionQueueService + action_queue table -- 3-tier action model with approval lifecycle</t>
-        </is>
-      </c>
-      <c r="G28" s="43" t="inlineStr">
-        <is>
-          <t>docs/ACTION_QUEUE.md (new), docs/APIS.md, docs/DECISIONS.md</t>
-        </is>
-      </c>
-      <c r="H28" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I28" s="42" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J28" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K28" s="42" t="n"/>
-      <c r="L28" s="42" t="n"/>
-      <c r="M28" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="43" t="n"/>
-      <c r="O28" s="43" t="inlineStr">
-        <is>
-          <t>CRUD + status-transition unit tests; plan output includes action_queue section</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="39.6" customHeight="1" s="72">
-      <c r="A29" s="42" t="inlineStr">
-        <is>
-          <t>P6-A24</t>
-        </is>
-      </c>
-      <c r="B29" s="69" t="n"/>
-      <c r="C29" s="43" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D29" s="43" t="inlineStr">
-        <is>
-          <t>Action Queue UI</t>
-        </is>
-      </c>
-      <c r="E29" s="43" t="inlineStr">
-        <is>
-          <t>Approve/reject list with type badges, Instamart cart-preview modal before approving checkout, procurement tracker (placed orders, status, ETA) in the inventory panel.</t>
-        </is>
-      </c>
-      <c r="F29" s="43" t="inlineStr">
-        <is>
-          <t>feat: Action Queue UI -- approve/reject with cart preview, procurement tracker</t>
-        </is>
-      </c>
-      <c r="G29" s="43" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="H29" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I29" s="42" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J29" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K29" s="42" t="n"/>
-      <c r="L29" s="42" t="n"/>
-      <c r="M29" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="43" t="inlineStr">
-        <is>
-          <t>P6-A23</t>
-        </is>
-      </c>
-      <c r="O29" s="43" t="inlineStr">
-        <is>
-          <t>typecheck clean; manual verification against live action_queue data</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="39.6" customHeight="1" s="72">
-      <c r="A30" s="42" t="inlineStr">
-        <is>
-          <t>P6-A25</t>
-        </is>
-      </c>
-      <c r="B30" s="68" t="inlineStr">
-        <is>
-          <t>feature/agentic-automation</t>
-        </is>
-      </c>
-      <c r="C30" s="43" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D30" s="43" t="inlineStr">
-        <is>
-          <t>Workflow trigger engine (scoped: 2-3 built-in triggers, not a user-defined builder)</t>
-        </is>
-      </c>
-      <c r="E30" s="43" t="inlineStr">
-        <is>
-          <t>A small WorkflowEngine evaluating built-in conditions after each planning run and auto-creating action_queue rows. Ships with 2-3 real triggers to start: (1) 2+ critical shortages found -&gt; queue an urgent restock action, (2) tonight_busy + 2+ competitor Dineout deals live -&gt; queue a pricing/promo review action. Deliberately NOT the full owner-defined trigger/condition/action builder from the original workflow-system idea -- that's a much bigger UI/DB investment for marginal demo value beyond just having the triggers exist.</t>
-        </is>
-      </c>
-      <c r="F30" s="43" t="inlineStr">
-        <is>
-          <t>feat: workflow trigger engine -- built-in triggers auto-queue actions post-planning-run</t>
-        </is>
-      </c>
-      <c r="G30" s="43" t="inlineStr">
-        <is>
-          <t>docs/ARCHITECTURE.md</t>
-        </is>
-      </c>
-      <c r="H30" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I30" s="42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J30" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K30" s="42" t="n"/>
-      <c r="L30" s="42" t="n"/>
-      <c r="M30" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="43" t="inlineStr">
-        <is>
-          <t>P6-A23</t>
-        </is>
-      </c>
-      <c r="O30" s="43" t="inlineStr">
-        <is>
-          <t>each trigger condition fires correctly and produces the right queued action</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="39.6" customHeight="1" s="72">
-      <c r="A31" s="42" t="inlineStr">
-        <is>
-          <t>P6-A26</t>
-        </is>
-      </c>
-      <c r="B31" s="69" t="n"/>
-      <c r="C31" s="43" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D31" s="43" t="inlineStr">
-        <is>
-          <t>Trust-ladder mechanic on the Action Queue</t>
-        </is>
-      </c>
-      <c r="E31" s="43" t="inlineStr">
-        <is>
-          <t>Track consecutive unedited approvals per action_type. After N consecutive approvals (default 3) of the same type, offer 'always do this automatically' -- promotes future instances of that action_type straight to AUTO tier for that org. Makes 'autonomous' a visible, explainable mechanic rather than a claim.</t>
-        </is>
-      </c>
-      <c r="F31" s="43" t="inlineStr">
-        <is>
-          <t>feat: trust-ladder -- auto-promote repeatedly-approved action types to AUTO tier</t>
-        </is>
-      </c>
-      <c r="G31" s="43" t="inlineStr">
-        <is>
-          <t>docs/ACTION_QUEUE.md</t>
-        </is>
-      </c>
-      <c r="H31" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I31" s="42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J31" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K31" s="42" t="n"/>
-      <c r="L31" s="42" t="n"/>
-      <c r="M31" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="43" t="inlineStr">
-        <is>
-          <t>P6-A23</t>
-        </is>
-      </c>
-      <c r="O31" s="43" t="inlineStr">
-        <is>
-          <t>N consecutive approvals triggers promotion prompt; promoted type skips approval next time</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="39.6" customHeight="1" s="72">
-      <c r="A32" s="42" t="inlineStr">
-        <is>
-          <t>P6-A27</t>
-        </is>
-      </c>
-      <c r="B32" s="68" t="inlineStr">
-        <is>
-          <t>feature/dynamic-pricing</t>
-        </is>
-      </c>
-      <c r="C32" s="43" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="D32" s="43" t="inlineStr">
-        <is>
-          <t>Dynamic pricing engine -- PriceChangeProposal (internal menu only)</t>
-        </is>
-      </c>
-      <c r="E32" s="43" t="inlineStr">
-        <is>
-          <t>New PriceChangeProposal model (item, current_price, suggested_price, reason, source, created_at). Computed from existing category_pricing/positioning data already in CompetitorEnricher. Surfaces as a new action_type in the Action Queue -- approving it updates your own MenuItem.price. Explicitly scoped to internal-only; does NOT attempt to sync price changes out to live Swiggy/Zomato listings (that needs Partner API access we don't have).</t>
-        </is>
-      </c>
-      <c r="F32" s="43" t="inlineStr">
-        <is>
-          <t>feat: dynamic pricing engine -- competitor-data-driven price suggestions via the Action Queue</t>
-        </is>
-      </c>
-      <c r="G32" s="43" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md, CLAUDE.md</t>
-        </is>
-      </c>
-      <c r="H32" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I32" s="42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J32" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K32" s="42" t="n"/>
-      <c r="L32" s="42" t="n"/>
-      <c r="M32" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="43" t="inlineStr">
-        <is>
-          <t>P6-A23</t>
-        </is>
-      </c>
-      <c r="O32" s="43" t="inlineStr">
-        <is>
-          <t>suggestion computed correctly from category_pricing gap; approving updates MenuItem.price; PriceChangeProposal row persists as an audit trail</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="39.6" customHeight="1" s="72">
-      <c r="A33" s="42" t="inlineStr">
-        <is>
-          <t>P6-A28</t>
-        </is>
-      </c>
-      <c r="B33" s="69" t="n"/>
-      <c r="C33" s="43" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t>Outcome / recommendation-learning memory</t>
-        </is>
-      </c>
-      <c r="E33" s="43" t="inlineStr">
-        <is>
-          <t>Extend the existing Qdrant-backed cross-session memory pattern (P6-S09) to track whether past actions/recommendations actually worked (e.g. did an approved price change move margin next week? did an approved restock prevent a stockout?). Feed this back into future confidence scoring on similar suggestions.</t>
-        </is>
-      </c>
-      <c r="F33" s="43" t="inlineStr">
-        <is>
-          <t>feat: outcome-learning memory -- track whether past AI actions worked, feed back into future confidence</t>
-        </is>
-      </c>
-      <c r="G33" s="43" t="inlineStr">
-        <is>
-          <t>docs/ARCHITECTURE.md</t>
-        </is>
-      </c>
-      <c r="H33" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I33" s="42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J33" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K33" s="42" t="n"/>
-      <c r="L33" s="42" t="n"/>
-      <c r="M33" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="43" t="inlineStr">
-        <is>
-          <t>P6-A23, P6-A27</t>
-        </is>
-      </c>
-      <c r="O33" s="43" t="inlineStr">
-        <is>
-          <t>outcome recorded correctly against the originating action; confidence score shifts on repeat suggestion of the same type after a bad outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="52.8" customHeight="1" s="72">
-      <c r="A34" s="42" t="inlineStr">
-        <is>
-          <t>P6-A29</t>
-        </is>
-      </c>
-      <c r="B34" s="68" t="inlineStr">
-        <is>
-          <t>feature/procurement-dineout-executors</t>
-        </is>
-      </c>
-      <c r="C34" s="43" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="D34" s="43" t="inlineStr">
-        <is>
-          <t>ProcurementExecutor -- full flow, mocked final checkout call</t>
-        </is>
-      </c>
-      <c r="E34" s="43" t="inlineStr">
-        <is>
-          <t>Full update_cart -&gt; get_cart -&gt; LangGraph interrupt() -&gt; owner approval (via Action Queue) -&gt; checkout flow, built completely end-to-end. The actual final checkout() call is stubbed/mocked, clearly labeled 'awaiting Swiggy staging creds' -- everything else (cart building, pricing, approval gate, procurement_orders row creation) is real. Swapping the mock for a real call is Phase B's entire scope for this task. DEFERRED to end of Phase A pending direct restaurant-owner research into real procurement workflow (bulk orders, WhatsApp/phone to local vendors) -- see P6-A32.</t>
-        </is>
-      </c>
-      <c r="F34" s="43" t="inlineStr">
-        <is>
-          <t>feat: ProcurementExecutor -- full approval-gated Instamart flow, checkout call mocked pending staging creds</t>
-        </is>
-      </c>
-      <c r="G34" s="43" t="inlineStr">
-        <is>
-          <t>docs/ACTION_QUEUE.md, CLAUDE.md</t>
-        </is>
-      </c>
-      <c r="H34" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I34" s="42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J34" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K34" s="42" t="n"/>
-      <c r="L34" s="42" t="n"/>
-      <c r="M34" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="43" t="inlineStr">
-        <is>
-          <t>P6-A23</t>
-        </is>
-      </c>
-      <c r="O34" s="43" t="inlineStr">
-        <is>
-          <t>full flow test with mocked checkout; interrupt() pauses correctly; procurement_orders row created with a clear 'simulated' flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="171.6" customHeight="1" s="72">
-      <c r="A35" s="42" t="inlineStr">
-        <is>
-          <t>P6-A30</t>
-        </is>
-      </c>
-      <c r="B35" s="69" t="n"/>
-      <c r="C35" s="43" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="D35" s="43" t="inlineStr">
-        <is>
-          <t>DineoutExecutor -- full flow, mocked final book_table call</t>
-        </is>
-      </c>
-      <c r="E35" s="43" t="inlineStr">
-        <is>
-          <t>Same pattern as P6-A25 for Dineout: create_cart -&gt; book_table, approval-gated via Action Queue, real logic throughout except the final book_table() call is mocked pending staging creds.</t>
-        </is>
-      </c>
-      <c r="F35" s="43" t="inlineStr">
-        <is>
-          <t>feat: DineoutExecutor -- full approval-gated Dineout booking flow, book_table call mocked pending staging creds</t>
-        </is>
-      </c>
-      <c r="G35" s="43" t="inlineStr">
-        <is>
-          <t>docs/ACTION_QUEUE.md</t>
-        </is>
-      </c>
-      <c r="H35" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I35" s="42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J35" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K35" s="42" t="n"/>
-      <c r="L35" s="42" t="n"/>
-      <c r="M35" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="43" t="inlineStr">
-        <is>
-          <t>P6-A23, P6-A29</t>
-        </is>
-      </c>
-      <c r="O35" s="43" t="inlineStr">
-        <is>
-          <t>full flow test with mocked book_table; reservations row created with a clear 'simulated' flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="39.6" customHeight="1" s="72">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>P6-A31</t>
-        </is>
-      </c>
-      <c r="B36" s="68" t="inlineStr">
-        <is>
-          <t>feature/recipe-vendor-foundations</t>
-        </is>
-      </c>
-      <c r="C36" s="43" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D36" s="43" t="inlineStr">
-        <is>
-          <t>Recipe + RecipeIngredient model</t>
-        </is>
-      </c>
-      <c r="E36" s="43" t="inlineStr">
-        <is>
-          <t>New Recipe (menu_item_id) + RecipeIngredient (recipe_id, ingredient, quantity, unit) tables. Bridges MenuItem and inventory -- unlocks live-computed cost_price (from real ingredient prices) instead of manual entry, and real per-dish inventory depletion instead of aggregate-only shortage tracking. DEFERRED to end of Phase A alongside the rest of the procurement/Action Queue cluster, pending direct restaurant-owner research into how real procurement actually works.</t>
-        </is>
-      </c>
-      <c r="F36" s="43" t="inlineStr">
-        <is>
-          <t>feat: Recipe + RecipeIngredient models -- dish-to-ingredient yield mapping</t>
-        </is>
-      </c>
-      <c r="G36" s="43" t="inlineStr">
-        <is>
-          <t>docs/DATA_MODEL.md</t>
-        </is>
-      </c>
-      <c r="H36" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I36" s="42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J36" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K36" s="42" t="n"/>
-      <c r="L36" s="42" t="n"/>
-      <c r="M36" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="43" t="n"/>
-      <c r="O36" s="43" t="inlineStr">
-        <is>
-          <t>recipe costing test (sum of ingredient costs matches computed cost_price); depletion test (a sale reduces linked ingredient stock by the right amount)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="39.6" customHeight="1" s="72">
-      <c r="A37" s="42" t="inlineStr">
-        <is>
-          <t>P6-A32</t>
-        </is>
-      </c>
-      <c r="B37" s="69" t="n"/>
-      <c r="C37" s="43" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="D37" s="43" t="inlineStr">
-        <is>
-          <t>Vendor/Supplier model</t>
-        </is>
-      </c>
-      <c r="E37" s="43" t="inlineStr">
-        <is>
-          <t>New Vendor model (name, category, is_online, contact) + VendorPriceQuote (vendor_id, ingredient, price, quoted_at). Instamart becomes one Vendor among several (an 'online' vendor with live API pricing); local mandi/wholesale vendors become trackable entities with manually-entered or periodically-surveyed prices. Scoped as tracking/comparison only, not a marketplace. DEFERRED to end of Phase A -- exact procurement medium (Instamart API vs a WhatsApp-dispatch message to a local vendor vs other) intentionally left open pending direct conversation with a real restaurant owner/manager about their actual ordering process, before committing to a design.</t>
-        </is>
-      </c>
-      <c r="F37" s="43" t="inlineStr">
-        <is>
-          <t>feat: Vendor/Supplier model -- Instamart becomes one vendor among many, not the only source</t>
-        </is>
-      </c>
-      <c r="G37" s="43" t="inlineStr">
-        <is>
-          <t>docs/DATA_MODEL.md</t>
-        </is>
-      </c>
-      <c r="H37" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I37" s="42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J37" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K37" s="42" t="n"/>
-      <c r="L37" s="42" t="n"/>
-      <c r="M37" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="43" t="inlineStr">
-        <is>
-          <t>P6-A31</t>
-        </is>
-      </c>
-      <c r="O37" s="43" t="inlineStr">
-        <is>
-          <t>vendor price comparison query returns correct cheapest-vendor-per-ingredient</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="52.8" customHeight="1" s="72">
-      <c r="A38" s="42" t="inlineStr">
-        <is>
-          <t>P6-A33</t>
-        </is>
-      </c>
-      <c r="B38" s="68" t="inlineStr">
-        <is>
-          <t>feature/mcp-expansion</t>
-        </is>
-      </c>
-      <c r="C38" s="43" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D38" s="43" t="inlineStr">
-        <is>
-          <t>Internal MCP server -- get_market_brief / get_action_queue / approve_action</t>
-        </is>
-      </c>
-      <c r="E38" s="43" t="inlineStr">
-        <is>
-          <t>3 new tools on CortexKitchen's own MCP server (mcp_server.py), JWT-authenticated, calling MarketIntelService and ActionQueueService live. Lets an owner ask Claude Desktop directly about their restaurant and approve actions from there.</t>
-        </is>
-      </c>
-      <c r="F38" s="43" t="inlineStr">
-        <is>
-          <t>feat: 3 new MCP tools -- get_market_brief, get_action_queue, approve_action</t>
-        </is>
-      </c>
-      <c r="G38" s="43" t="inlineStr">
-        <is>
-          <t>docs/APIS.md, docs/ARCHITECTURE.md</t>
-        </is>
-      </c>
-      <c r="H38" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I38" s="42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J38" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K38" s="42" t="n"/>
-      <c r="L38" s="42" t="n"/>
-      <c r="M38" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="43" t="inlineStr">
-        <is>
-          <t>P6-A23</t>
-        </is>
-      </c>
-      <c r="O38" s="43" t="inlineStr">
-        <is>
-          <t>all 3 tools smoke-tested in Claude Desktop; approve_action triggers the same approval path as the web UI; JWT enforced</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="171.6" customHeight="1" s="72">
-      <c r="A39" s="42" t="inlineStr">
-        <is>
-          <t>P6-A34</t>
-        </is>
-      </c>
-      <c r="B39" s="69" t="n"/>
-      <c r="C39" s="43" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D39" s="43" t="inlineStr">
-        <is>
-          <t>Internal MCP server -- expand further (menu insights, forecast, what-if)</t>
-        </is>
-      </c>
-      <c r="E39" s="43" t="inlineStr">
-        <is>
-          <t>Wrap additional existing services as MCP tools beyond the 3 in P6-A32 -- menu insights, demand forecast, and the Phase-5 what-if simulator. Cheap since the service layer already exists; positions CortexKitchen as a general AI-accessible restaurant data layer, not just 3 utility tools.</t>
-        </is>
-      </c>
-      <c r="F39" s="43" t="inlineStr">
-        <is>
-          <t>feat: expand internal MCP server -- menu insights, forecast, what-if simulator as tools</t>
-        </is>
-      </c>
-      <c r="G39" s="43" t="inlineStr">
-        <is>
-          <t>docs/APIS.md</t>
-        </is>
-      </c>
-      <c r="H39" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I39" s="42" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J39" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K39" s="42" t="n"/>
-      <c r="L39" s="42" t="n"/>
-      <c r="M39" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="43" t="inlineStr">
-        <is>
-          <t>P6-A33</t>
-        </is>
-      </c>
-      <c r="O39" s="43" t="inlineStr">
-        <is>
-          <t>each new tool smoke-tested in Claude Desktop; correct data returned matching the equivalent API endpoint</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="39.6" customHeight="1" s="72">
-      <c r="A40" s="42" t="inlineStr">
-        <is>
-          <t>P6-A35</t>
-        </is>
-      </c>
-      <c r="B40" s="68" t="inlineStr">
-        <is>
-          <t>feature/brief-page</t>
-        </is>
-      </c>
-      <c r="C40" s="43" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D40" s="43" t="inlineStr">
-        <is>
-          <t>/brief page</t>
-        </is>
-      </c>
-      <c r="E40" s="43" t="inlineStr">
-        <is>
-          <t>Daily morning briefing -- overnight performance, today's forecast vs yesterday, top 3 action priorities, market snapshot. Single-screen showcase of the whole system's intelligence.</t>
-        </is>
-      </c>
-      <c r="F40" s="43" t="inlineStr">
-        <is>
-          <t>feat: /brief page -- daily morning operational briefing</t>
-        </is>
-      </c>
-      <c r="G40" s="43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H40" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I40" s="42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J40" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K40" s="42" t="n"/>
-      <c r="L40" s="42" t="n"/>
-      <c r="M40" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="43" t="inlineStr">
-        <is>
-          <t>P6-A24</t>
-        </is>
-      </c>
-      <c r="O40" s="43" t="inlineStr">
-        <is>
-          <t>manual verification</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="171.6" customHeight="1" s="72">
-      <c r="A41" s="42" t="inlineStr">
-        <is>
-          <t>P6-A36</t>
-        </is>
-      </c>
-      <c r="B41" s="68" t="n"/>
-      <c r="C41" s="43" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="D41" s="43" t="inlineStr">
-        <is>
-          <t>Post-Phase-A documentation, test, CI, observability, and eval refresh</t>
-        </is>
-      </c>
-      <c r="E41" s="43" t="inlineStr">
-        <is>
-          <t>Once Phase A ships, a lot of new surface area will have landed at once -- Action Queue, workflow triggers, the anomaly agent, both executors, new connectors (Zomato stub, reviews), new data models (Recipe, Vendor, Expense, Obligation), MCP expansion. Do a full pass rather than letting docs drift: update every docs/*.md file, CLAUDE.md, README, and any screenshots referenced in docs to reflect what actually shipped. Audit test coverage for every new service/model added in Phase A -- confirm nothing shipped without tests. Re-check the CI pipeline includes all new test files. Re-run/expand RAGAS + DeepEval evals to cover the new agentic behaviors (anomaly diagnoses, dynamic pricing suggestions), since the existing eval sets predate all of this and won't catch regressions in it.</t>
-        </is>
-      </c>
-      <c r="F41" s="43" t="inlineStr">
-        <is>
-          <t>docs: full documentation, test-coverage, CI, and eval refresh after the Phase A agentic core ships</t>
-        </is>
-      </c>
-      <c r="G41" s="43" t="inlineStr">
-        <is>
-          <t>All docs/*.md, CLAUDE.md, README.md</t>
-        </is>
-      </c>
-      <c r="H41" s="41" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I41" s="42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J41" s="42" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K41" s="42" t="n"/>
-      <c r="L41" s="42" t="n"/>
-      <c r="M41" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="43" t="inlineStr">
+      <c r="N39" s="90" t="inlineStr">
         <is>
           <t>All P6-A tasks</t>
         </is>
       </c>
-      <c r="O41" s="43" t="inlineStr">
+      <c r="O39" s="90" t="inlineStr">
         <is>
           <t>Every new service/model has test coverage; CI includes all new test files; RAGAS/DeepEval sets include at least one case per new agentic behavior; docs/screenshots match shipped behavior</t>
         </is>
       </c>
     </row>
+    <row r="40" ht="39.6" customHeight="1" s="72"/>
+    <row r="41" ht="171.6" customHeight="1" s="72"/>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="B17:B19"/>
     <mergeCell ref="B32:B33"/>
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B19:B21"/>
     <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B26:B27"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B15:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -19744,7 +19665,7 @@
       </c>
       <c r="E4" s="62" t="inlineStr">
         <is>
-          <t>Phase A (P6-A29) already builds the full get_cart -&gt; update_cart -&gt; LangGraph interrupt() -&gt; owner approval -&gt; checkout flow end-to-end, with the final checkout() call mocked and labeled 'awaiting staging creds'. This task is just the swap: replace the mock with the real call. NON-IDEMPOTENT: on any 5xx from checkout, call get_orders before retrying -- never blind-retry. procurement_orders rows switch from a 'simulated' flag to real confirmed orders.</t>
+          <t>Phase A (P6-A28) already builds the full get_cart -&gt; update_cart -&gt; LangGraph interrupt() -&gt; owner approval -&gt; checkout flow end-to-end, with the final checkout() call mocked and labeled 'awaiting staging creds'. This task is just the swap: replace the mock with the real call. NON-IDEMPOTENT: on any 5xx from checkout, call get_orders before retrying -- never blind-retry. procurement_orders rows switch from a 'simulated' flag to real confirmed orders.</t>
         </is>
       </c>
       <c r="F4" s="62" t="inlineStr">
@@ -19779,7 +19700,7 @@
       </c>
       <c r="N4" s="62" t="inlineStr">
         <is>
-          <t>P6-A29, P6-S14</t>
+          <t>P6-A28, P6-S14</t>
         </is>
       </c>
       <c r="O4" s="62" t="inlineStr">
@@ -19828,7 +19749,7 @@
       </c>
       <c r="E6" s="62" t="inlineStr">
         <is>
-          <t>book_table in consumer MCP books a table AT another restaurant (a consumer action), not managing your own restaurant's Dineout presence -- that needs Swiggy Partner/Business API, a separate track from these creds. Phase A (P6-A30) already builds the full create_cart -&gt; book_table flow end-to-end with the final call mocked. This task swaps the mock for the real call, scoped to the consumer-booking use case only (e.g. mystery-dining a competitor for research).</t>
+          <t>book_table in consumer MCP books a table AT another restaurant (a consumer action), not managing your own restaurant's Dineout presence -- that needs Swiggy Partner/Business API, a separate track from these creds. Phase A (P6-A29) already builds the full create_cart -&gt; book_table flow end-to-end with the final call mocked. This task swaps the mock for the real call, scoped to the consumer-booking use case only (e.g. mystery-dining a competitor for research).</t>
         </is>
       </c>
       <c r="F6" s="62" t="inlineStr">
@@ -19863,7 +19784,7 @@
       </c>
       <c r="N6" s="62" t="inlineStr">
         <is>
-          <t>P6-A30</t>
+          <t>P6-A29</t>
         </is>
       </c>
       <c r="O6" s="62" t="inlineStr">
@@ -19908,7 +19829,7 @@
       </c>
       <c r="E8" s="62" t="inlineStr">
         <is>
-          <t>Once P7-1/P7-2 prove reliable in production, extend the trust-ladder mechanic (P6-A26) to real money-touching actions -- e.g. auto-reorder a habitually-restocked ingredient without approval once trust is established.</t>
+          <t>Once P7-1/P7-2 prove reliable in production, extend the trust-ladder mechanic (P6-A25) to real money-touching actions -- e.g. auto-reorder a habitually-restocked ingredient without approval once trust is established.</t>
         </is>
       </c>
       <c r="F8" s="62" t="inlineStr">
@@ -19943,7 +19864,7 @@
       </c>
       <c r="N8" s="62" t="inlineStr">
         <is>
-          <t>P6-A26, P7-1, P7-2</t>
+          <t>P6-A25, P7-1, P7-2</t>
         </is>
       </c>
       <c r="O8" s="62" t="inlineStr">
@@ -20131,7 +20052,7 @@
       </c>
       <c r="N14" s="62" t="inlineStr">
         <is>
-          <t>P6-A21</t>
+          <t>P6-A20</t>
         </is>
       </c>
       <c r="O14" s="62" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -17540,7 +17540,7 @@
       </c>
       <c r="E7" s="90" t="inlineStr">
         <is>
-          <t>ZomatoConnector class following the exact BaseConnector shape (sync()/enrich()) as SwiggyConnector, registered in provider_registry.py's CAPABILITY_PROVIDERS as an actually-real (if non-functional) connector rather than a placeholder string. Proves the multi-provider architecture is real, not Swiggy-only. No live Zomato API call required -- returns a clear 'not yet connected' state.</t>
+          <t>ZomatoConnector class following the exact BaseConnector shape (sync()/enrich()) as SwiggyConnector, registered in provider_registry.py's CAPABILITY_PROVIDERS as an actually-real (if non-functional) connector rather than a placeholder string. Proves the multi-provider architecture is real, not Swiggy-only. No live Zomato API call required -- returns a clear 'not yet connected' state. Moved BaseConnector out of the swiggy package to a shared location (app/infrastructure/base_connector.py) as part of this task, since a genuinely platform-agnostic base class living inside a Swiggy-specific package undercut its own point.</t>
         </is>
       </c>
       <c r="F7" s="90" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="H7" s="108" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I7" s="89" t="inlineStr">
@@ -17568,10 +17568,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K7" s="89" t="n"/>
-      <c r="L7" s="89" t="n"/>
+      <c r="K7" s="89" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="L7" s="89" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
       <c r="M7" s="91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="90" t="n"/>
       <c r="O7" s="90" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -471,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -758,6 +758,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17594,30 +17598,34 @@
           <t>P6-A6</t>
         </is>
       </c>
-      <c r="B8" s="69" t="n"/>
+      <c r="B8" s="98" t="inlineStr">
+        <is>
+          <t>feature/financial-compliance</t>
+        </is>
+      </c>
       <c r="C8" s="90" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D8" s="90" t="inlineStr">
         <is>
-          <t>Public review aggregation connectors (Google/Zomato reviews)</t>
+          <t>Financial scorecard -- Expense ledger + real P&amp;L</t>
         </is>
       </c>
       <c r="E8" s="90" t="inlineStr">
         <is>
-          <t>GoogleReviewsConnector / ZomatoReviewsConnector following the same BaseConnector pattern, pulling public review data (not internal complaints) into complaint_intelligence as an additional source type. Extends the Feedback model's source concept rather than inventing a parallel system.</t>
+          <t>New Expense model (category: rent/utilities/marketing/labor-later/other, amount, recurrence). Extends business.py's existing revenue/margin computation into a real daily/weekly P&amp;L and one composite health score. Designed so labor slots in later as just another Expense category, not a rewrite.</t>
         </is>
       </c>
       <c r="F8" s="90" t="inlineStr">
         <is>
-          <t>feat: public review aggregation -- Google/Zomato reviews via BaseConnector pattern</t>
+          <t>feat: financial scorecard -- Expense ledger, real P&amp;L, composite health score</t>
         </is>
       </c>
       <c r="G8" s="90" t="inlineStr">
         <is>
-          <t>docs/AGENTS.md, docs/CONNECTORS.md</t>
+          <t>docs/APIS.md</t>
         </is>
       </c>
       <c r="H8" s="108" t="inlineStr">
@@ -17640,14 +17648,10 @@
       <c r="M8" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="90" t="inlineStr">
-        <is>
-          <t>P6-A5</t>
-        </is>
-      </c>
+      <c r="N8" s="90" t="n"/>
       <c r="O8" s="90" t="inlineStr">
         <is>
-          <t>reviews ingested with correct source tag; complaint_intelligence node correctly surfaces public-review-sourced themes alongside internal ones</t>
+          <t>P&amp;L numbers match seeded expense + revenue data; health score computes deterministically from known inputs</t>
         </is>
       </c>
     </row>
@@ -17657,11 +17661,7 @@
           <t>P6-A7</t>
         </is>
       </c>
-      <c r="B9" s="98" t="inlineStr">
-        <is>
-          <t>feature/financial-compliance</t>
-        </is>
-      </c>
+      <c r="B9" s="69" t="n"/>
       <c r="C9" s="90" t="inlineStr">
         <is>
           <t>Backend</t>
@@ -17669,17 +17669,17 @@
       </c>
       <c r="D9" s="90" t="inlineStr">
         <is>
-          <t>Financial scorecard -- Expense ledger + real P&amp;L</t>
+          <t>Compliance / Obligations calendar</t>
         </is>
       </c>
       <c r="E9" s="90" t="inlineStr">
         <is>
-          <t>New Expense model (category: rent/utilities/marketing/labor-later/other, amount, recurrence). Extends business.py's existing revenue/margin computation into a real daily/weekly P&amp;L and one composite health score. Designed so labor slots in later as just another Expense category, not a rewrite.</t>
+          <t>Generalized Obligation model (type: license-renewal/GST-filing/inspection/other, due_date, status) with reminders delivered through the existing Phase-5 email digest mechanism rather than a new one-off sender. Not a GST computation/invoicing layer -- just a dated-obligation tracker with reminders.</t>
         </is>
       </c>
       <c r="F9" s="90" t="inlineStr">
         <is>
-          <t>feat: financial scorecard -- Expense ledger, real P&amp;L, composite health score</t>
+          <t>feat: compliance/obligations calendar -- reminder engine reusing the existing email digest</t>
         </is>
       </c>
       <c r="G9" s="90" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="I9" s="89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J9" s="89" t="inlineStr">
@@ -17710,7 +17710,7 @@
       <c r="N9" s="90" t="n"/>
       <c r="O9" s="90" t="inlineStr">
         <is>
-          <t>P&amp;L numbers match seeded expense + revenue data; health score computes deterministically from known inputs</t>
+          <t>reminder fires at the correct lead-time before due_date; reuses existing digest delivery path</t>
         </is>
       </c>
     </row>
@@ -17720,30 +17720,34 @@
           <t>P6-A8</t>
         </is>
       </c>
-      <c r="B10" s="69" t="n"/>
+      <c r="B10" s="98" t="inlineStr">
+        <is>
+          <t>feature/location-architecture</t>
+        </is>
+      </c>
       <c r="C10" s="90" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="D10" s="90" t="inlineStr">
         <is>
-          <t>Compliance / Obligations calendar</t>
+          <t>Location-aware enrichers (hedge for multi-location)</t>
         </is>
       </c>
       <c r="E10" s="90" t="inlineStr">
         <is>
-          <t>Generalized Obligation model (type: license-renewal/GST-filing/inspection/other, due_date, status) with reminders delivered through the existing Phase-5 email digest mechanism rather than a new one-off sender. Not a GST computation/invoicing layer -- just a dated-obligation tracker with reminders.</t>
+          <t>Thread an explicit location/address context through MarketIntelService and all 3 enrichers instead of a single hardcoded SWIGGY_ADDRESS_ID -- cheap to do now, expensive to retrofit once multi-location (P6-A29) exists or once real customers have multiple outlets.</t>
         </is>
       </c>
       <c r="F10" s="90" t="inlineStr">
         <is>
-          <t>feat: compliance/obligations calendar -- reminder engine reusing the existing email digest</t>
+          <t>feat: location-aware enrichers -- pass address/location context through instead of one hardcoded address</t>
         </is>
       </c>
       <c r="G10" s="90" t="inlineStr">
         <is>
-          <t>docs/APIS.md</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="H10" s="108" t="inlineStr">
@@ -17769,7 +17773,7 @@
       <c r="N10" s="90" t="n"/>
       <c r="O10" s="90" t="inlineStr">
         <is>
-          <t>reminder fires at the correct lead-time before due_date; reuses existing digest delivery path</t>
+          <t>enrichers accept and correctly use a passed-in address_id, defaulting to the existing single-address behavior when none given</t>
         </is>
       </c>
     </row>
@@ -17779,11 +17783,7 @@
           <t>P6-A9</t>
         </is>
       </c>
-      <c r="B11" s="98" t="inlineStr">
-        <is>
-          <t>feature/location-architecture</t>
-        </is>
-      </c>
+      <c r="B11" s="69" t="n"/>
       <c r="C11" s="90" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -17791,22 +17791,22 @@
       </c>
       <c r="D11" s="90" t="inlineStr">
         <is>
-          <t>Location-aware enrichers (hedge for multi-location)</t>
+          <t>Multi-location / Restaurant entity -- STRATEGIC, needs explicit go/no-go</t>
         </is>
       </c>
       <c r="E11" s="90" t="inlineStr">
         <is>
-          <t>Thread an explicit location/address context through MarketIntelService and all 3 enrichers instead of a single hardcoded SWIGGY_ADDRESS_ID -- cheap to do now, expensive to retrofit once multi-location (P6-A30) exists or once real customers have multiple outlets.</t>
+          <t>Introduce Restaurant as a first-class entity between Organization and everything else (menu, inventory, planning runs, Swiggy connector -- each physical location has its own Swiggy restaurant ID). Add restaurant_id to MenuItem/InventoryItem/PlanningRun/connectors. Cheaper to do now while the schema is small than to retrofit later. NOT started until the user confirms real near-term demand justifies it over other Phase A work.</t>
         </is>
       </c>
       <c r="F11" s="90" t="inlineStr">
         <is>
-          <t>feat: location-aware enrichers -- pass address/location context through instead of one hardcoded address</t>
+          <t>feat: Restaurant entity -- first-class multi-location support</t>
         </is>
       </c>
       <c r="G11" s="90" t="inlineStr">
         <is>
-          <t>CLAUDE.md</t>
+          <t>docs/DATA_MODEL.md, docs/DECISIONS.md</t>
         </is>
       </c>
       <c r="H11" s="108" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="I11" s="89" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Low (pending go/no-go)</t>
         </is>
       </c>
       <c r="J11" s="89" t="inlineStr">
@@ -17829,10 +17829,14 @@
       <c r="M11" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="90" t="n"/>
+      <c r="N11" s="90" t="inlineStr">
+        <is>
+          <t>P6-A8</t>
+        </is>
+      </c>
       <c r="O11" s="90" t="inlineStr">
         <is>
-          <t>enrichers accept and correctly use a passed-in address_id, defaulting to the existing single-address behavior when none given</t>
+          <t>existing single-location orgs continue to work unchanged (default restaurant backfilled); cross-location query test once 2+ restaurants exist</t>
         </is>
       </c>
     </row>
@@ -17842,30 +17846,34 @@
           <t>P6-A10</t>
         </is>
       </c>
-      <c r="B12" s="69" t="n"/>
+      <c r="B12" s="98" t="inlineStr">
+        <is>
+          <t>feature/chatbot-dineout-tools</t>
+        </is>
+      </c>
       <c r="C12" s="90" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D12" s="90" t="inlineStr">
         <is>
-          <t>Multi-location / Restaurant entity -- STRATEGIC, needs explicit go/no-go</t>
+          <t>Chatbot -- Dineout competitive query tools</t>
         </is>
       </c>
       <c r="E12" s="90" t="inlineStr">
         <is>
-          <t>Introduce Restaurant as a first-class entity between Organization and everything else (menu, inventory, planning runs, Swiggy connector -- each physical location has its own Swiggy restaurant ID). Add restaurant_id to MenuItem/InventoryItem/PlanningRun/connectors. Cheaper to do now while the schema is small than to retrofit later. NOT started until the user confirms real near-term demand justifies it over other Phase A work.</t>
+          <t>3 Groq function-calling tools for the existing chatbot: get_competitor_deals, get_area_occupancy, get_trending_dishes -- all using Swiggy's existing read-only Dineout MCP (search_restaurants_dineout, get_restaurant_details, get_available_slots), already-proven tools. (Formerly P6-MI04; renumbered as part of the Phase 6 replan.)</t>
         </is>
       </c>
       <c r="F12" s="90" t="inlineStr">
         <is>
-          <t>feat: Restaurant entity -- first-class multi-location support</t>
+          <t>feat: chatbot Dineout tools -- competitor deals, area occupancy, trending dishes</t>
         </is>
       </c>
       <c r="G12" s="90" t="inlineStr">
         <is>
-          <t>docs/DATA_MODEL.md, docs/DECISIONS.md</t>
+          <t>docs/AGENTS.md</t>
         </is>
       </c>
       <c r="H12" s="108" t="inlineStr">
@@ -17875,7 +17883,7 @@
       </c>
       <c r="I12" s="89" t="inlineStr">
         <is>
-          <t>Low (pending go/no-go)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J12" s="89" t="inlineStr">
@@ -17888,14 +17896,10 @@
       <c r="M12" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="90" t="inlineStr">
-        <is>
-          <t>P6-A9</t>
-        </is>
-      </c>
+      <c r="N12" s="90" t="n"/>
       <c r="O12" s="90" t="inlineStr">
         <is>
-          <t>existing single-location orgs continue to work unchanged (default restaurant backfilled); cross-location query test once 2+ restaurants exist</t>
+          <t>all 3 tools callable from /chat; correct Swiggy data returned; graceful None on failure</t>
         </is>
       </c>
     </row>
@@ -17905,29 +17909,25 @@
           <t>P6-A11</t>
         </is>
       </c>
-      <c r="B13" s="98" t="inlineStr">
-        <is>
-          <t>feature/chatbot-dineout-tools</t>
-        </is>
-      </c>
+      <c r="B13" s="69" t="n"/>
       <c r="C13" s="90" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="D13" s="90" t="inlineStr">
         <is>
-          <t>Chatbot -- Dineout competitive query tools</t>
+          <t>Structured outputs -- tool_choice=required across chatbot tools</t>
         </is>
       </c>
       <c r="E13" s="90" t="inlineStr">
         <is>
-          <t>3 Groq function-calling tools for the existing chatbot: get_competitor_deals, get_area_occupancy, get_trending_dishes -- all using Swiggy's existing read-only Dineout MCP (search_restaurants_dineout, get_restaurant_details, get_available_slots), already-proven tools. (Formerly P6-MI04; renumbered as part of the Phase 6 replan.)</t>
+          <t>Upgrade chatbot Groq calls to tool_choice=required + strict JSON schema across all chatbot tools (Swiggy and internal). Chatbot function calls never hallucinate JSON.</t>
         </is>
       </c>
       <c r="F13" s="90" t="inlineStr">
         <is>
-          <t>feat: chatbot Dineout tools -- competitor deals, area occupancy, trending dishes</t>
+          <t>feat: structured outputs -- tool_choice=required across all chatbot tools</t>
         </is>
       </c>
       <c r="G13" s="90" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="I13" s="89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J13" s="89" t="inlineStr">
@@ -17955,10 +17955,14 @@
       <c r="M13" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="90" t="n"/>
+      <c r="N13" s="90" t="inlineStr">
+        <is>
+          <t>P6-A10</t>
+        </is>
+      </c>
       <c r="O13" s="90" t="inlineStr">
         <is>
-          <t>all 3 tools callable from /chat; correct Swiggy data returned; graceful None on failure</t>
+          <t>schema validation test; chatbot returns valid JSON on repeated calls</t>
         </is>
       </c>
     </row>
@@ -17968,7 +17972,11 @@
           <t>P6-A12</t>
         </is>
       </c>
-      <c r="B14" s="69" t="n"/>
+      <c r="B14" s="98" t="inlineStr">
+        <is>
+          <t>feature/llm-cost-quality</t>
+        </is>
+      </c>
       <c r="C14" s="90" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -17976,22 +17984,22 @@
       </c>
       <c r="D14" s="90" t="inlineStr">
         <is>
-          <t>Structured outputs -- tool_choice=required across chatbot tools</t>
+          <t>Prompt caching -- critic + aggregator</t>
         </is>
       </c>
       <c r="E14" s="90" t="inlineStr">
         <is>
-          <t>Upgrade chatbot Groq calls to tool_choice=required + strict JSON schema across all chatbot tools (Swiggy and internal). Chatbot function calls never hallucinate JSON.</t>
+          <t>Add prompt-caching headers to critic and aggregator LLM calls (both have long, repeated system prompts). Cuts LLM cost per planning run; invisible to a demo but real cost hygiene.</t>
         </is>
       </c>
       <c r="F14" s="90" t="inlineStr">
         <is>
-          <t>feat: structured outputs -- tool_choice=required across all chatbot tools</t>
+          <t>feat: prompt caching -- cut LLM costs on critic and aggregator nodes</t>
         </is>
       </c>
       <c r="G14" s="90" t="inlineStr">
         <is>
-          <t>docs/AGENTS.md</t>
+          <t>docs/ARCHITECTURE.md</t>
         </is>
       </c>
       <c r="H14" s="108" t="inlineStr">
@@ -18014,14 +18022,10 @@
       <c r="M14" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="90" t="inlineStr">
-        <is>
-          <t>P6-A11</t>
-        </is>
-      </c>
+      <c r="N14" s="90" t="n"/>
       <c r="O14" s="90" t="inlineStr">
         <is>
-          <t>schema validation test; chatbot returns valid JSON on repeated calls</t>
+          <t>cost log shows cache_hit=true on second run of the same scenario</t>
         </is>
       </c>
     </row>
@@ -18031,34 +18035,30 @@
           <t>P6-A13</t>
         </is>
       </c>
-      <c r="B15" s="98" t="inlineStr">
-        <is>
-          <t>feature/llm-cost-quality</t>
-        </is>
-      </c>
+      <c r="B15" s="69" t="n"/>
       <c r="C15" s="90" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Agents</t>
         </is>
       </c>
       <c r="D15" s="90" t="inlineStr">
         <is>
-          <t>Prompt caching -- critic + aggregator</t>
+          <t>Multi-agent debate critic</t>
         </is>
       </c>
       <c r="E15" s="90" t="inlineStr">
         <is>
-          <t>Add prompt-caching headers to critic and aggregator LLM calls (both have long, repeated system prompts). Cuts LLM cost per planning run; invisible to a demo but real cost hygiene.</t>
+          <t>Two LLM critic instances (optimistic vs conservative), structured debate, moderator resolves disagreement. Marginal demo-visible upside over the existing single critic given the added cost/latency -- kept low priority.</t>
         </is>
       </c>
       <c r="F15" s="90" t="inlineStr">
         <is>
-          <t>feat: prompt caching -- cut LLM costs on critic and aggregator nodes</t>
+          <t>feat: multi-agent debate critic -- consensus scoring</t>
         </is>
       </c>
       <c r="G15" s="90" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE.md</t>
+          <t>docs/AGENTS.md</t>
         </is>
       </c>
       <c r="H15" s="108" t="inlineStr">
@@ -18084,7 +18084,7 @@
       <c r="N15" s="90" t="n"/>
       <c r="O15" s="90" t="inlineStr">
         <is>
-          <t>cost log shows cache_hit=true on second run of the same scenario</t>
+          <t>debate resolves on test plans; disagreement cases escalate correctly</t>
         </is>
       </c>
     </row>
@@ -18094,30 +18094,34 @@
           <t>P6-A14</t>
         </is>
       </c>
-      <c r="B16" s="69" t="n"/>
+      <c r="B16" s="98" t="inlineStr">
+        <is>
+          <t>feature/ci-eval-hygiene</t>
+        </is>
+      </c>
       <c r="C16" s="90" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="D16" s="90" t="inlineStr">
         <is>
-          <t>Multi-agent debate critic</t>
+          <t>Fix SQLite/JSONB CI test-infra gap</t>
         </is>
       </c>
       <c r="E16" s="90" t="inlineStr">
         <is>
-          <t>Two LLM critic instances (optimistic vs conservative), structured debate, moderator resolves disagreement. Marginal demo-visible upside over the existing single critic given the added cost/latency -- kept low priority.</t>
+          <t>test_swiggy_reservation_sync.py and test_connector_repository.py are excluded from CI because SQLite can't render Postgres JSONB columns. Either a SQLite-compatible fallback type or a Postgres CI service container.</t>
         </is>
       </c>
       <c r="F16" s="90" t="inlineStr">
         <is>
-          <t>feat: multi-agent debate critic -- consensus scoring</t>
+          <t>fix: SQLite-compatible JSONB handling (or Postgres CI service) for excluded test files</t>
         </is>
       </c>
       <c r="G16" s="90" t="inlineStr">
         <is>
-          <t>docs/AGENTS.md</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H16" s="108" t="inlineStr">
@@ -18143,7 +18147,7 @@
       <c r="N16" s="90" t="n"/>
       <c r="O16" s="90" t="inlineStr">
         <is>
-          <t>debate resolves on test plans; disagreement cases escalate correctly</t>
+          <t>previously-excluded test files run in CI</t>
         </is>
       </c>
     </row>
@@ -18153,29 +18157,25 @@
           <t>P6-A15</t>
         </is>
       </c>
-      <c r="B17" s="98" t="inlineStr">
-        <is>
-          <t>feature/ci-eval-hygiene</t>
-        </is>
-      </c>
+      <c r="B17" s="70" t="n"/>
       <c r="C17" s="90" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D17" s="90" t="inlineStr">
         <is>
-          <t>Fix SQLite/JSONB CI test-infra gap</t>
+          <t>Promote reviewed RAGAS/DeepEval candidates</t>
         </is>
       </c>
       <c r="E17" s="90" t="inlineStr">
         <is>
-          <t>test_swiggy_reservation_sync.py and test_connector_repository.py are excluded from CI because SQLite can't render Postgres JSONB columns. Either a SQLite-compatible fallback type or a Postgres CI service container.</t>
+          <t>Recurring habit of running the existing candidate-generation scripts and hand-promoting reviewed candidates into the curated eval datasets.</t>
         </is>
       </c>
       <c r="F17" s="90" t="inlineStr">
         <is>
-          <t>fix: SQLite-compatible JSONB handling (or Postgres CI service) for excluded test files</t>
+          <t>chore: promote reviewed eval candidates into curated datasets</t>
         </is>
       </c>
       <c r="G17" s="90" t="inlineStr">
@@ -18206,7 +18206,7 @@
       <c r="N17" s="90" t="n"/>
       <c r="O17" s="90" t="inlineStr">
         <is>
-          <t>previously-excluded test files run in CI</t>
+          <t>N/A -- ongoing process, not a one-time build</t>
         </is>
       </c>
     </row>
@@ -18216,25 +18216,25 @@
           <t>P6-A16</t>
         </is>
       </c>
-      <c r="B18" s="70" t="n"/>
+      <c r="B18" s="69" t="n"/>
       <c r="C18" s="90" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="D18" s="90" t="inlineStr">
         <is>
-          <t>Promote reviewed RAGAS/DeepEval candidates</t>
+          <t>Regenerate golden_runs.json against real data</t>
         </is>
       </c>
       <c r="E18" s="90" t="inlineStr">
         <is>
-          <t>Recurring habit of running the existing candidate-generation scripts and hand-promoting reviewed candidates into the curated eval datasets.</t>
+          <t>The key-path bug in build_golden_dataset.py is already fixed; the checked-in fixture still reflects the old broken extraction. Regenerate once real run history exists.</t>
         </is>
       </c>
       <c r="F18" s="90" t="inlineStr">
         <is>
-          <t>chore: promote reviewed eval candidates into curated datasets</t>
+          <t>chore: regenerate golden_runs.json with corrected extraction logic</t>
         </is>
       </c>
       <c r="G18" s="90" t="inlineStr">
@@ -18265,7 +18265,7 @@
       <c r="N18" s="90" t="n"/>
       <c r="O18" s="90" t="inlineStr">
         <is>
-          <t>N/A -- ongoing process, not a one-time build</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18275,25 +18275,29 @@
           <t>P6-A17</t>
         </is>
       </c>
-      <c r="B19" s="69" t="n"/>
+      <c r="B19" s="98" t="inlineStr">
+        <is>
+          <t>feature/menu-engineering-matrix</t>
+        </is>
+      </c>
       <c r="C19" s="90" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D19" s="90" t="inlineStr">
         <is>
-          <t>Regenerate golden_runs.json against real data</t>
+          <t>Menu engineering matrix UI</t>
         </is>
       </c>
       <c r="E19" s="90" t="inlineStr">
         <is>
-          <t>The key-path bug in build_golden_dataset.py is already fixed; the checked-in fixture still reflects the old broken extraction. Regenerate once real run history exists.</t>
+          <t>Stars/plow-horses/dogs/puzzles quadrant chart using margin_pct x quantity, both already computed in business.py -- just needs quadrant classification + a chart.</t>
         </is>
       </c>
       <c r="F19" s="90" t="inlineStr">
         <is>
-          <t>chore: regenerate golden_runs.json with corrected extraction logic</t>
+          <t>feat: menu engineering matrix -- margin x popularity quadrant chart</t>
         </is>
       </c>
       <c r="G19" s="90" t="inlineStr">
@@ -18308,7 +18312,7 @@
       </c>
       <c r="I19" s="89" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J19" s="89" t="inlineStr">
@@ -18324,7 +18328,7 @@
       <c r="N19" s="90" t="n"/>
       <c r="O19" s="90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>quadrant classification unit test; chart renders correctly</t>
         </is>
       </c>
     </row>
@@ -18336,7 +18340,7 @@
       </c>
       <c r="B20" s="98" t="inlineStr">
         <is>
-          <t>feature/menu-engineering-matrix</t>
+          <t>feature/pages-redesign</t>
         </is>
       </c>
       <c r="C20" s="90" t="inlineStr">
@@ -18346,17 +18350,17 @@
       </c>
       <c r="D20" s="90" t="inlineStr">
         <is>
-          <t>Menu engineering matrix UI</t>
+          <t>all page redesign via claude design</t>
         </is>
       </c>
       <c r="E20" s="90" t="inlineStr">
         <is>
-          <t>Stars/plow-horses/dogs/puzzles quadrant chart using margin_pct x quantity, both already computed in business.py -- just needs quadrant classification + a chart.</t>
+          <t>Apply the existing design system to /runs -- currently the weakest-looking screen (dense monospace debug trace). Fix the unstyled raw 404 on /runs/{id} deep links.</t>
         </is>
       </c>
       <c r="F20" s="90" t="inlineStr">
         <is>
-          <t>feat: menu engineering matrix -- margin x popularity quadrant chart</t>
+          <t>feat: redesign /runs history page + fix /runs/{id} deep-link 404</t>
         </is>
       </c>
       <c r="G20" s="90" t="inlineStr">
@@ -18371,7 +18375,7 @@
       </c>
       <c r="I20" s="89" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J20" s="89" t="inlineStr">
@@ -18387,7 +18391,7 @@
       <c r="N20" s="90" t="n"/>
       <c r="O20" s="90" t="inlineStr">
         <is>
-          <t>quadrant classification unit test; chart renders correctly</t>
+          <t>direct navigation to /runs/{id} renders the run, not a 404</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18403,7 @@
       </c>
       <c r="B21" s="98" t="inlineStr">
         <is>
-          <t>feature/pages-redesign</t>
+          <t>feature/voice-interface</t>
         </is>
       </c>
       <c r="C21" s="90" t="inlineStr">
@@ -18409,22 +18413,22 @@
       </c>
       <c r="D21" s="90" t="inlineStr">
         <is>
-          <t>all page redesign via claude design</t>
+          <t>Voice interface</t>
         </is>
       </c>
       <c r="E21" s="90" t="inlineStr">
         <is>
-          <t>Apply the existing design system to /runs -- currently the weakest-looking screen (dense monospace debug trace). Fix the unstyled raw 404 on /runs/{id} deep links.</t>
+          <t>Whisper transcription on browser-recorded question, existing RAG chatbot answers, TTS reads back.</t>
         </is>
       </c>
       <c r="F21" s="90" t="inlineStr">
         <is>
-          <t>feat: redesign /runs history page + fix /runs/{id} deep-link 404</t>
+          <t>feat: voice interface -- Whisper transcription + RAG answer + TTS readback</t>
         </is>
       </c>
       <c r="G21" s="90" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>docs/PRODUCT_MODES.md</t>
         </is>
       </c>
       <c r="H21" s="108" t="inlineStr">
@@ -18434,7 +18438,7 @@
       </c>
       <c r="I21" s="89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J21" s="89" t="inlineStr">
@@ -18450,7 +18454,7 @@
       <c r="N21" s="90" t="n"/>
       <c r="O21" s="90" t="inlineStr">
         <is>
-          <t>direct navigation to /runs/{id} renders the run, not a 404</t>
+          <t>transcription accuracy smoke test; end-to-end voice -&gt; RAG answer -&gt; TTS</t>
         </is>
       </c>
     </row>
@@ -18462,7 +18466,7 @@
       </c>
       <c r="B22" s="98" t="inlineStr">
         <is>
-          <t>feature/voice-interface</t>
+          <t>feature/live-page-redesign</t>
         </is>
       </c>
       <c r="C22" s="90" t="inlineStr">
@@ -18472,17 +18476,17 @@
       </c>
       <c r="D22" s="90" t="inlineStr">
         <is>
-          <t>Voice interface</t>
+          <t>/live page -- reframed as alerts/synthesis overlay</t>
         </is>
       </c>
       <c r="E22" s="90" t="inlineStr">
         <is>
-          <t>Whisper transcription on browser-recorded question, existing RAG chatbot answers, TTS reads back.</t>
+          <t>NOT a live order board (that's POS/aggregator territory and touches personal Swiggy consumer data). Instead: an alerts-and-synthesis overlay surfacing cross-referenced signals (e.g. 'order running late -- here's why, per our own data') during service hours.</t>
         </is>
       </c>
       <c r="F22" s="90" t="inlineStr">
         <is>
-          <t>feat: voice interface -- Whisper transcription + RAG answer + TTS readback</t>
+          <t>feat: /live page -- alerts and synthesis overlay, not a live order feed</t>
         </is>
       </c>
       <c r="G22" s="90" t="inlineStr">
@@ -18513,94 +18517,94 @@
       <c r="N22" s="90" t="n"/>
       <c r="O22" s="90" t="inlineStr">
         <is>
-          <t>transcription accuracy smoke test; end-to-end voice -&gt; RAG answer -&gt; TTS</t>
+          <t>manual verification</t>
         </is>
       </c>
     </row>
     <row r="23" ht="7.95" customHeight="1" s="72">
-      <c r="A23" s="65" t="inlineStr">
+      <c r="A23" s="111" t="n"/>
+      <c r="B23" s="111" t="n"/>
+      <c r="C23" s="111" t="n"/>
+      <c r="D23" s="111" t="n"/>
+      <c r="E23" s="111" t="n"/>
+      <c r="F23" s="111" t="n"/>
+      <c r="G23" s="111" t="n"/>
+      <c r="H23" s="111" t="n"/>
+      <c r="I23" s="111" t="n"/>
+      <c r="J23" s="111" t="n"/>
+      <c r="K23" s="111" t="n"/>
+      <c r="L23" s="111" t="n"/>
+      <c r="M23" s="111" t="n"/>
+      <c r="N23" s="111" t="n"/>
+      <c r="O23" s="111" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="72">
+      <c r="A24" s="109" t="inlineStr">
+        <is>
+          <t>DEFERRED TO END OF PHASE A -- pending direct restaurant-owner research into real procurement/approval workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52.05" customHeight="1" s="72">
+      <c r="A25" s="65" t="inlineStr">
         <is>
           <t>P6-A21</t>
         </is>
       </c>
-      <c r="B23" s="98" t="inlineStr">
-        <is>
-          <t>feature/live-page-redesign</t>
-        </is>
-      </c>
-      <c r="C23" s="90" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D23" s="90" t="inlineStr">
-        <is>
-          <t>/live page -- reframed as alerts/synthesis overlay</t>
-        </is>
-      </c>
-      <c r="E23" s="90" t="inlineStr">
-        <is>
-          <t>NOT a live order board (that's POS/aggregator territory and touches personal Swiggy consumer data). Instead: an alerts-and-synthesis overlay surfacing cross-referenced signals (e.g. 'order running late -- here's why, per our own data') during service hours.</t>
-        </is>
-      </c>
-      <c r="F23" s="90" t="inlineStr">
-        <is>
-          <t>feat: /live page -- alerts and synthesis overlay, not a live order feed</t>
-        </is>
-      </c>
-      <c r="G23" s="90" t="inlineStr">
-        <is>
-          <t>docs/PRODUCT_MODES.md</t>
-        </is>
-      </c>
-      <c r="H23" s="108" t="inlineStr">
+      <c r="B25" s="98" t="inlineStr">
+        <is>
+          <t>feature/action-queue</t>
+        </is>
+      </c>
+      <c r="C25" s="90" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="D25" s="90" t="inlineStr">
+        <is>
+          <t>ActionQueueService + action_queue table</t>
+        </is>
+      </c>
+      <c r="E25" s="90" t="inlineStr">
+        <is>
+          <t>New table (org_id, action_type [AUTO/APPROVE_REQUIRED/RECOMMENDATION], payload jsonb, status [PENDING/APPROVED/EXECUTED/REJECTED/EXPIRED], approved_by, executed_at, error). ActionQueueService CRUD + status transitions. Plan output gains an action_queue section in the API response. Foundational -- every other agentic task below (workflow triggers, dynamic pricing, executors, trust-ladder) writes into this same table rather than inventing its own approval mechanism. DEFERRED to end of Phase A -- its main real-world value (approving reorder suggestions) is exactly the workflow that needs real restaurant-owner input first; building the approval UX before that research risks designing around the wrong assumptions.</t>
+        </is>
+      </c>
+      <c r="F25" s="90" t="inlineStr">
+        <is>
+          <t>feat: ActionQueueService + action_queue table -- 3-tier action model with approval lifecycle</t>
+        </is>
+      </c>
+      <c r="G25" s="90" t="inlineStr">
+        <is>
+          <t>docs/ACTION_QUEUE.md (new), docs/APIS.md, docs/DECISIONS.md</t>
+        </is>
+      </c>
+      <c r="H25" s="108" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I23" s="89" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J23" s="89" t="inlineStr">
+      <c r="I25" s="89" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J25" s="89" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K23" s="89" t="n"/>
-      <c r="L23" s="89" t="n"/>
-      <c r="M23" s="91" t="n">
+      <c r="K25" s="89" t="n"/>
+      <c r="L25" s="89" t="n"/>
+      <c r="M25" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="90" t="n"/>
-      <c r="O23" s="90" t="inlineStr">
-        <is>
-          <t>manual verification</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" s="72">
-      <c r="A24" s="111" t="n"/>
-      <c r="B24" s="111" t="n"/>
-      <c r="C24" s="111" t="n"/>
-      <c r="D24" s="111" t="n"/>
-      <c r="E24" s="111" t="n"/>
-      <c r="F24" s="111" t="n"/>
-      <c r="G24" s="111" t="n"/>
-      <c r="H24" s="111" t="n"/>
-      <c r="I24" s="111" t="n"/>
-      <c r="J24" s="111" t="n"/>
-      <c r="K24" s="111" t="n"/>
-      <c r="L24" s="111" t="n"/>
-      <c r="M24" s="111" t="n"/>
-      <c r="N24" s="111" t="n"/>
-      <c r="O24" s="111" t="n"/>
-    </row>
-    <row r="25" ht="52.05" customHeight="1" s="72">
-      <c r="A25" s="109" t="inlineStr">
-        <is>
-          <t>DEFERRED TO END OF PHASE A -- pending direct restaurant-owner research into real procurement/approval workflow</t>
+      <c r="N25" s="90" t="n"/>
+      <c r="O25" s="90" t="inlineStr">
+        <is>
+          <t>CRUD + status-transition unit tests; plan output includes action_queue section</t>
         </is>
       </c>
     </row>
@@ -18610,34 +18614,30 @@
           <t>P6-A22</t>
         </is>
       </c>
-      <c r="B26" s="98" t="inlineStr">
-        <is>
-          <t>feature/action-queue</t>
-        </is>
-      </c>
+      <c r="B26" s="69" t="n"/>
       <c r="C26" s="90" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D26" s="90" t="inlineStr">
         <is>
-          <t>ActionQueueService + action_queue table</t>
+          <t>Action Queue UI</t>
         </is>
       </c>
       <c r="E26" s="90" t="inlineStr">
         <is>
-          <t>New table (org_id, action_type [AUTO/APPROVE_REQUIRED/RECOMMENDATION], payload jsonb, status [PENDING/APPROVED/EXECUTED/REJECTED/EXPIRED], approved_by, executed_at, error). ActionQueueService CRUD + status transitions. Plan output gains an action_queue section in the API response. Foundational -- every other agentic task below (workflow triggers, dynamic pricing, executors, trust-ladder) writes into this same table rather than inventing its own approval mechanism. DEFERRED to end of Phase A -- its main real-world value (approving reorder suggestions) is exactly the workflow that needs real restaurant-owner input first; building the approval UX before that research risks designing around the wrong assumptions.</t>
+          <t>Approve/reject list with type badges, Instamart cart-preview modal before approving checkout, procurement tracker (placed orders, status, ETA) in the inventory panel.</t>
         </is>
       </c>
       <c r="F26" s="90" t="inlineStr">
         <is>
-          <t>feat: ActionQueueService + action_queue table -- 3-tier action model with approval lifecycle</t>
+          <t>feat: Action Queue UI -- approve/reject with cart preview, procurement tracker</t>
         </is>
       </c>
       <c r="G26" s="90" t="inlineStr">
         <is>
-          <t>docs/ACTION_QUEUE.md (new), docs/APIS.md, docs/DECISIONS.md</t>
+          <t>None (frontend only)</t>
         </is>
       </c>
       <c r="H26" s="108" t="inlineStr">
@@ -18660,10 +18660,14 @@
       <c r="M26" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="90" t="n"/>
+      <c r="N26" s="90" t="inlineStr">
+        <is>
+          <t>P6-A21</t>
+        </is>
+      </c>
       <c r="O26" s="90" t="inlineStr">
         <is>
-          <t>CRUD + status-transition unit tests; plan output includes action_queue section</t>
+          <t>typecheck clean; manual verification against live action_queue data</t>
         </is>
       </c>
     </row>
@@ -18673,30 +18677,34 @@
           <t>P6-A23</t>
         </is>
       </c>
-      <c r="B27" s="69" t="n"/>
+      <c r="B27" s="98" t="inlineStr">
+        <is>
+          <t>feature/agentic-automation</t>
+        </is>
+      </c>
       <c r="C27" s="90" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="D27" s="90" t="inlineStr">
         <is>
-          <t>Action Queue UI</t>
+          <t>Workflow trigger engine (scoped: 2-3 built-in triggers, not a user-defined builder)</t>
         </is>
       </c>
       <c r="E27" s="90" t="inlineStr">
         <is>
-          <t>Approve/reject list with type badges, Instamart cart-preview modal before approving checkout, procurement tracker (placed orders, status, ETA) in the inventory panel.</t>
+          <t>A small WorkflowEngine evaluating built-in conditions after each planning run and auto-creating action_queue rows. Ships with 2-3 real triggers to start: (1) 2+ critical shortages found -&gt; queue an urgent restock action, (2) tonight_busy + 2+ competitor Dineout deals live -&gt; queue a pricing/promo review action. Deliberately NOT the full owner-defined trigger/condition/action builder from the original workflow-system idea -- that's a much bigger UI/DB investment for marginal demo value beyond just having the triggers exist.</t>
         </is>
       </c>
       <c r="F27" s="90" t="inlineStr">
         <is>
-          <t>feat: Action Queue UI -- approve/reject with cart preview, procurement tracker</t>
+          <t>feat: workflow trigger engine -- built-in triggers auto-queue actions post-planning-run</t>
         </is>
       </c>
       <c r="G27" s="90" t="inlineStr">
         <is>
-          <t>None (frontend only)</t>
+          <t>docs/ARCHITECTURE.md</t>
         </is>
       </c>
       <c r="H27" s="108" t="inlineStr">
@@ -18706,7 +18714,7 @@
       </c>
       <c r="I27" s="89" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J27" s="89" t="inlineStr">
@@ -18721,12 +18729,12 @@
       </c>
       <c r="N27" s="90" t="inlineStr">
         <is>
-          <t>P6-A22</t>
+          <t>P6-A21</t>
         </is>
       </c>
       <c r="O27" s="90" t="inlineStr">
         <is>
-          <t>typecheck clean; manual verification against live action_queue data</t>
+          <t>each trigger condition fires correctly and produces the right queued action</t>
         </is>
       </c>
     </row>
@@ -18736,34 +18744,30 @@
           <t>P6-A24</t>
         </is>
       </c>
-      <c r="B28" s="98" t="inlineStr">
-        <is>
-          <t>feature/agentic-automation</t>
-        </is>
-      </c>
+      <c r="B28" s="69" t="n"/>
       <c r="C28" s="90" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D28" s="90" t="inlineStr">
         <is>
-          <t>Workflow trigger engine (scoped: 2-3 built-in triggers, not a user-defined builder)</t>
+          <t>Trust-ladder mechanic on the Action Queue</t>
         </is>
       </c>
       <c r="E28" s="90" t="inlineStr">
         <is>
-          <t>A small WorkflowEngine evaluating built-in conditions after each planning run and auto-creating action_queue rows. Ships with 2-3 real triggers to start: (1) 2+ critical shortages found -&gt; queue an urgent restock action, (2) tonight_busy + 2+ competitor Dineout deals live -&gt; queue a pricing/promo review action. Deliberately NOT the full owner-defined trigger/condition/action builder from the original workflow-system idea -- that's a much bigger UI/DB investment for marginal demo value beyond just having the triggers exist.</t>
+          <t>Track consecutive unedited approvals per action_type. After N consecutive approvals (default 3) of the same type, offer 'always do this automatically' -- promotes future instances of that action_type straight to AUTO tier for that org. Makes 'autonomous' a visible, explainable mechanic rather than a claim.</t>
         </is>
       </c>
       <c r="F28" s="90" t="inlineStr">
         <is>
-          <t>feat: workflow trigger engine -- built-in triggers auto-queue actions post-planning-run</t>
+          <t>feat: trust-ladder -- auto-promote repeatedly-approved action types to AUTO tier</t>
         </is>
       </c>
       <c r="G28" s="90" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE.md</t>
+          <t>docs/ACTION_QUEUE.md</t>
         </is>
       </c>
       <c r="H28" s="108" t="inlineStr">
@@ -18773,7 +18777,7 @@
       </c>
       <c r="I28" s="89" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J28" s="89" t="inlineStr">
@@ -18788,12 +18792,12 @@
       </c>
       <c r="N28" s="90" t="inlineStr">
         <is>
-          <t>P6-A22</t>
+          <t>P6-A21</t>
         </is>
       </c>
       <c r="O28" s="90" t="inlineStr">
         <is>
-          <t>each trigger condition fires correctly and produces the right queued action</t>
+          <t>N consecutive approvals triggers promotion prompt; promoted type skips approval next time</t>
         </is>
       </c>
     </row>
@@ -18803,30 +18807,34 @@
           <t>P6-A25</t>
         </is>
       </c>
-      <c r="B29" s="69" t="n"/>
+      <c r="B29" s="98" t="inlineStr">
+        <is>
+          <t>feature/dynamic-pricing</t>
+        </is>
+      </c>
       <c r="C29" s="90" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Agents</t>
         </is>
       </c>
       <c r="D29" s="90" t="inlineStr">
         <is>
-          <t>Trust-ladder mechanic on the Action Queue</t>
+          <t>Dynamic pricing engine -- PriceChangeProposal (internal menu only)</t>
         </is>
       </c>
       <c r="E29" s="90" t="inlineStr">
         <is>
-          <t>Track consecutive unedited approvals per action_type. After N consecutive approvals (default 3) of the same type, offer 'always do this automatically' -- promotes future instances of that action_type straight to AUTO tier for that org. Makes 'autonomous' a visible, explainable mechanic rather than a claim.</t>
+          <t>New PriceChangeProposal model (item, current_price, suggested_price, reason, source, created_at). Computed from existing category_pricing/positioning data already in CompetitorEnricher. Surfaces as a new action_type in the Action Queue -- approving it updates your own MenuItem.price. Explicitly scoped to internal-only; does NOT attempt to sync price changes out to live Swiggy/Zomato listings (that needs Partner API access we don't have).</t>
         </is>
       </c>
       <c r="F29" s="90" t="inlineStr">
         <is>
-          <t>feat: trust-ladder -- auto-promote repeatedly-approved action types to AUTO tier</t>
+          <t>feat: dynamic pricing engine -- competitor-data-driven price suggestions via the Action Queue</t>
         </is>
       </c>
       <c r="G29" s="90" t="inlineStr">
         <is>
-          <t>docs/ACTION_QUEUE.md</t>
+          <t>docs/AGENTS.md, CLAUDE.md</t>
         </is>
       </c>
       <c r="H29" s="108" t="inlineStr">
@@ -18836,7 +18844,7 @@
       </c>
       <c r="I29" s="89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J29" s="89" t="inlineStr">
@@ -18851,12 +18859,12 @@
       </c>
       <c r="N29" s="90" t="inlineStr">
         <is>
-          <t>P6-A22</t>
+          <t>P6-A21</t>
         </is>
       </c>
       <c r="O29" s="90" t="inlineStr">
         <is>
-          <t>N consecutive approvals triggers promotion prompt; promoted type skips approval next time</t>
+          <t>suggestion computed correctly from category_pricing gap; approving updates MenuItem.price; PriceChangeProposal row persists as an audit trail</t>
         </is>
       </c>
     </row>
@@ -18866,11 +18874,7 @@
           <t>P6-A26</t>
         </is>
       </c>
-      <c r="B30" s="98" t="inlineStr">
-        <is>
-          <t>feature/dynamic-pricing</t>
-        </is>
-      </c>
+      <c r="B30" s="69" t="n"/>
       <c r="C30" s="90" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -18878,22 +18882,22 @@
       </c>
       <c r="D30" s="90" t="inlineStr">
         <is>
-          <t>Dynamic pricing engine -- PriceChangeProposal (internal menu only)</t>
+          <t>Outcome / recommendation-learning memory</t>
         </is>
       </c>
       <c r="E30" s="90" t="inlineStr">
         <is>
-          <t>New PriceChangeProposal model (item, current_price, suggested_price, reason, source, created_at). Computed from existing category_pricing/positioning data already in CompetitorEnricher. Surfaces as a new action_type in the Action Queue -- approving it updates your own MenuItem.price. Explicitly scoped to internal-only; does NOT attempt to sync price changes out to live Swiggy/Zomato listings (that needs Partner API access we don't have).</t>
+          <t>Extend the existing Qdrant-backed cross-session memory pattern (P6-S09) to track whether past actions/recommendations actually worked (e.g. did an approved price change move margin next week? did an approved restock prevent a stockout?). Feed this back into future confidence scoring on similar suggestions.</t>
         </is>
       </c>
       <c r="F30" s="90" t="inlineStr">
         <is>
-          <t>feat: dynamic pricing engine -- competitor-data-driven price suggestions via the Action Queue</t>
+          <t>feat: outcome-learning memory -- track whether past AI actions worked, feed back into future confidence</t>
         </is>
       </c>
       <c r="G30" s="90" t="inlineStr">
         <is>
-          <t>docs/AGENTS.md, CLAUDE.md</t>
+          <t>docs/ARCHITECTURE.md</t>
         </is>
       </c>
       <c r="H30" s="108" t="inlineStr">
@@ -18903,7 +18907,7 @@
       </c>
       <c r="I30" s="89" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J30" s="89" t="inlineStr">
@@ -18918,12 +18922,12 @@
       </c>
       <c r="N30" s="90" t="inlineStr">
         <is>
-          <t>P6-A22</t>
+          <t>P6-A21, P6-A25</t>
         </is>
       </c>
       <c r="O30" s="90" t="inlineStr">
         <is>
-          <t>suggestion computed correctly from category_pricing gap; approving updates MenuItem.price; PriceChangeProposal row persists as an audit trail</t>
+          <t>outcome recorded correctly against the originating action; confidence score shifts on repeat suggestion of the same type after a bad outcome</t>
         </is>
       </c>
     </row>
@@ -18933,7 +18937,11 @@
           <t>P6-A27</t>
         </is>
       </c>
-      <c r="B31" s="69" t="n"/>
+      <c r="B31" s="98" t="inlineStr">
+        <is>
+          <t>feature/procurement-dineout-executors</t>
+        </is>
+      </c>
       <c r="C31" s="90" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -18941,22 +18949,22 @@
       </c>
       <c r="D31" s="90" t="inlineStr">
         <is>
-          <t>Outcome / recommendation-learning memory</t>
+          <t>ProcurementExecutor -- full flow, mocked final checkout call</t>
         </is>
       </c>
       <c r="E31" s="90" t="inlineStr">
         <is>
-          <t>Extend the existing Qdrant-backed cross-session memory pattern (P6-S09) to track whether past actions/recommendations actually worked (e.g. did an approved price change move margin next week? did an approved restock prevent a stockout?). Feed this back into future confidence scoring on similar suggestions.</t>
+          <t>Full update_cart -&gt; get_cart -&gt; LangGraph interrupt() -&gt; owner approval (via Action Queue) -&gt; checkout flow, built completely end-to-end. The actual final checkout() call is stubbed/mocked, clearly labeled 'awaiting Swiggy staging creds' -- everything else (cart building, pricing, approval gate, procurement_orders row creation) is real. Swapping the mock for a real call is Phase B's entire scope for this task. DEFERRED to end of Phase A pending direct restaurant-owner research into real procurement workflow (bulk orders, WhatsApp/phone to local vendors) -- see P6-A30.</t>
         </is>
       </c>
       <c r="F31" s="90" t="inlineStr">
         <is>
-          <t>feat: outcome-learning memory -- track whether past AI actions worked, feed back into future confidence</t>
+          <t>feat: ProcurementExecutor -- full approval-gated Instamart flow, checkout call mocked pending staging creds</t>
         </is>
       </c>
       <c r="G31" s="90" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE.md</t>
+          <t>docs/ACTION_QUEUE.md, CLAUDE.md</t>
         </is>
       </c>
       <c r="H31" s="108" t="inlineStr">
@@ -18966,7 +18974,7 @@
       </c>
       <c r="I31" s="89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J31" s="89" t="inlineStr">
@@ -18981,12 +18989,12 @@
       </c>
       <c r="N31" s="90" t="inlineStr">
         <is>
-          <t>P6-A22, P6-A26</t>
+          <t>P6-A21</t>
         </is>
       </c>
       <c r="O31" s="90" t="inlineStr">
         <is>
-          <t>outcome recorded correctly against the originating action; confidence score shifts on repeat suggestion of the same type after a bad outcome</t>
+          <t>full flow test with mocked checkout; interrupt() pauses correctly; procurement_orders row created with a clear 'simulated' flag</t>
         </is>
       </c>
     </row>
@@ -18996,11 +19004,7 @@
           <t>P6-A28</t>
         </is>
       </c>
-      <c r="B32" s="98" t="inlineStr">
-        <is>
-          <t>feature/procurement-dineout-executors</t>
-        </is>
-      </c>
+      <c r="B32" s="69" t="n"/>
       <c r="C32" s="90" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -19008,22 +19012,22 @@
       </c>
       <c r="D32" s="90" t="inlineStr">
         <is>
-          <t>ProcurementExecutor -- full flow, mocked final checkout call</t>
+          <t>DineoutExecutor -- full flow, mocked final book_table call</t>
         </is>
       </c>
       <c r="E32" s="90" t="inlineStr">
         <is>
-          <t>Full update_cart -&gt; get_cart -&gt; LangGraph interrupt() -&gt; owner approval (via Action Queue) -&gt; checkout flow, built completely end-to-end. The actual final checkout() call is stubbed/mocked, clearly labeled 'awaiting Swiggy staging creds' -- everything else (cart building, pricing, approval gate, procurement_orders row creation) is real. Swapping the mock for a real call is Phase B's entire scope for this task. DEFERRED to end of Phase A pending direct restaurant-owner research into real procurement workflow (bulk orders, WhatsApp/phone to local vendors) -- see P6-A31.</t>
+          <t>Same pattern as P6-A23 for Dineout: create_cart -&gt; book_table, approval-gated via Action Queue, real logic throughout except the final book_table() call is mocked pending staging creds.</t>
         </is>
       </c>
       <c r="F32" s="90" t="inlineStr">
         <is>
-          <t>feat: ProcurementExecutor -- full approval-gated Instamart flow, checkout call mocked pending staging creds</t>
+          <t>feat: DineoutExecutor -- full approval-gated Dineout booking flow, book_table call mocked pending staging creds</t>
         </is>
       </c>
       <c r="G32" s="90" t="inlineStr">
         <is>
-          <t>docs/ACTION_QUEUE.md, CLAUDE.md</t>
+          <t>docs/ACTION_QUEUE.md</t>
         </is>
       </c>
       <c r="H32" s="108" t="inlineStr">
@@ -19033,7 +19037,7 @@
       </c>
       <c r="I32" s="89" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J32" s="89" t="inlineStr">
@@ -19048,12 +19052,12 @@
       </c>
       <c r="N32" s="90" t="inlineStr">
         <is>
-          <t>P6-A22</t>
+          <t>P6-A21, P6-A27</t>
         </is>
       </c>
       <c r="O32" s="90" t="inlineStr">
         <is>
-          <t>full flow test with mocked checkout; interrupt() pauses correctly; procurement_orders row created with a clear 'simulated' flag</t>
+          <t>full flow test with mocked book_table; reservations row created with a clear 'simulated' flag</t>
         </is>
       </c>
     </row>
@@ -19063,30 +19067,34 @@
           <t>P6-A29</t>
         </is>
       </c>
-      <c r="B33" s="69" t="n"/>
+      <c r="B33" s="98" t="inlineStr">
+        <is>
+          <t>feature/recipe-vendor-foundations</t>
+        </is>
+      </c>
       <c r="C33" s="90" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="D33" s="90" t="inlineStr">
         <is>
-          <t>DineoutExecutor -- full flow, mocked final book_table call</t>
+          <t>Recipe + RecipeIngredient model</t>
         </is>
       </c>
       <c r="E33" s="90" t="inlineStr">
         <is>
-          <t>Same pattern as P6-A24 for Dineout: create_cart -&gt; book_table, approval-gated via Action Queue, real logic throughout except the final book_table() call is mocked pending staging creds.</t>
+          <t>New Recipe (menu_item_id) + RecipeIngredient (recipe_id, ingredient, quantity, unit) tables. Bridges MenuItem and inventory -- unlocks live-computed cost_price (from real ingredient prices) instead of manual entry, and real per-dish inventory depletion instead of aggregate-only shortage tracking. DEFERRED to end of Phase A alongside the rest of the procurement/Action Queue cluster, pending direct restaurant-owner research into how real procurement actually works.</t>
         </is>
       </c>
       <c r="F33" s="90" t="inlineStr">
         <is>
-          <t>feat: DineoutExecutor -- full approval-gated Dineout booking flow, book_table call mocked pending staging creds</t>
+          <t>feat: Recipe + RecipeIngredient models -- dish-to-ingredient yield mapping</t>
         </is>
       </c>
       <c r="G33" s="90" t="inlineStr">
         <is>
-          <t>docs/ACTION_QUEUE.md</t>
+          <t>docs/DATA_MODEL.md</t>
         </is>
       </c>
       <c r="H33" s="108" t="inlineStr">
@@ -19096,7 +19104,7 @@
       </c>
       <c r="I33" s="89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J33" s="89" t="inlineStr">
@@ -19109,14 +19117,10 @@
       <c r="M33" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N33" s="90" t="inlineStr">
-        <is>
-          <t>P6-A22, P6-A28</t>
-        </is>
-      </c>
+      <c r="N33" s="90" t="n"/>
       <c r="O33" s="90" t="inlineStr">
         <is>
-          <t>full flow test with mocked book_table; reservations row created with a clear 'simulated' flag</t>
+          <t>recipe costing test (sum of ingredient costs matches computed cost_price); depletion test (a sale reduces linked ingredient stock by the right amount)</t>
         </is>
       </c>
     </row>
@@ -19126,11 +19130,7 @@
           <t>P6-A30</t>
         </is>
       </c>
-      <c r="B34" s="98" t="inlineStr">
-        <is>
-          <t>feature/recipe-vendor-foundations</t>
-        </is>
-      </c>
+      <c r="B34" s="69" t="n"/>
       <c r="C34" s="90" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -19138,17 +19138,17 @@
       </c>
       <c r="D34" s="90" t="inlineStr">
         <is>
-          <t>Recipe + RecipeIngredient model</t>
+          <t>Vendor/Supplier model</t>
         </is>
       </c>
       <c r="E34" s="90" t="inlineStr">
         <is>
-          <t>New Recipe (menu_item_id) + RecipeIngredient (recipe_id, ingredient, quantity, unit) tables. Bridges MenuItem and inventory -- unlocks live-computed cost_price (from real ingredient prices) instead of manual entry, and real per-dish inventory depletion instead of aggregate-only shortage tracking. DEFERRED to end of Phase A alongside the rest of the procurement/Action Queue cluster, pending direct restaurant-owner research into how real procurement actually works.</t>
+          <t>New Vendor model (name, category, is_online, contact) + VendorPriceQuote (vendor_id, ingredient, price, quoted_at). Instamart becomes one Vendor among several (an 'online' vendor with live API pricing); local mandi/wholesale vendors become trackable entities with manually-entered or periodically-surveyed prices. Scoped as tracking/comparison only, not a marketplace. DEFERRED to end of Phase A -- exact procurement medium (Instamart API vs a WhatsApp-dispatch message to a local vendor vs other) intentionally left open pending direct conversation with a real restaurant owner/manager about their actual ordering process, before committing to a design.</t>
         </is>
       </c>
       <c r="F34" s="90" t="inlineStr">
         <is>
-          <t>feat: Recipe + RecipeIngredient models -- dish-to-ingredient yield mapping</t>
+          <t>feat: Vendor/Supplier model -- Instamart becomes one vendor among many, not the only source</t>
         </is>
       </c>
       <c r="G34" s="90" t="inlineStr">
@@ -19163,7 +19163,7 @@
       </c>
       <c r="I34" s="89" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J34" s="89" t="inlineStr">
@@ -19176,10 +19176,14 @@
       <c r="M34" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="90" t="n"/>
+      <c r="N34" s="90" t="inlineStr">
+        <is>
+          <t>P6-A29</t>
+        </is>
+      </c>
       <c r="O34" s="90" t="inlineStr">
         <is>
-          <t>recipe costing test (sum of ingredient costs matches computed cost_price); depletion test (a sale reduces linked ingredient stock by the right amount)</t>
+          <t>vendor price comparison query returns correct cheapest-vendor-per-ingredient</t>
         </is>
       </c>
     </row>
@@ -19189,30 +19193,34 @@
           <t>P6-A31</t>
         </is>
       </c>
-      <c r="B35" s="69" t="n"/>
+      <c r="B35" s="98" t="inlineStr">
+        <is>
+          <t>feature/mcp-expansion</t>
+        </is>
+      </c>
       <c r="C35" s="90" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D35" s="90" t="inlineStr">
         <is>
-          <t>Vendor/Supplier model</t>
+          <t>Internal MCP server -- get_market_brief / get_action_queue / approve_action</t>
         </is>
       </c>
       <c r="E35" s="90" t="inlineStr">
         <is>
-          <t>New Vendor model (name, category, is_online, contact) + VendorPriceQuote (vendor_id, ingredient, price, quoted_at). Instamart becomes one Vendor among several (an 'online' vendor with live API pricing); local mandi/wholesale vendors become trackable entities with manually-entered or periodically-surveyed prices. Scoped as tracking/comparison only, not a marketplace. DEFERRED to end of Phase A -- exact procurement medium (Instamart API vs a WhatsApp-dispatch message to a local vendor vs other) intentionally left open pending direct conversation with a real restaurant owner/manager about their actual ordering process, before committing to a design.</t>
+          <t>3 new tools on CortexKitchen's own MCP server (mcp_server.py), JWT-authenticated, calling MarketIntelService and ActionQueueService live. Lets an owner ask Claude Desktop directly about their restaurant and approve actions from there.</t>
         </is>
       </c>
       <c r="F35" s="90" t="inlineStr">
         <is>
-          <t>feat: Vendor/Supplier model -- Instamart becomes one vendor among many, not the only source</t>
+          <t>feat: 3 new MCP tools -- get_market_brief, get_action_queue, approve_action</t>
         </is>
       </c>
       <c r="G35" s="90" t="inlineStr">
         <is>
-          <t>docs/DATA_MODEL.md</t>
+          <t>docs/APIS.md, docs/ARCHITECTURE.md</t>
         </is>
       </c>
       <c r="H35" s="108" t="inlineStr">
@@ -19237,12 +19245,12 @@
       </c>
       <c r="N35" s="90" t="inlineStr">
         <is>
-          <t>P6-A30</t>
+          <t>P6-A21</t>
         </is>
       </c>
       <c r="O35" s="90" t="inlineStr">
         <is>
-          <t>vendor price comparison query returns correct cheapest-vendor-per-ingredient</t>
+          <t>all 3 tools smoke-tested in Claude Desktop; approve_action triggers the same approval path as the web UI; JWT enforced</t>
         </is>
       </c>
     </row>
@@ -19252,11 +19260,7 @@
           <t>P6-A32</t>
         </is>
       </c>
-      <c r="B36" s="98" t="inlineStr">
-        <is>
-          <t>feature/mcp-expansion</t>
-        </is>
-      </c>
+      <c r="B36" s="69" t="n"/>
       <c r="C36" s="90" t="inlineStr">
         <is>
           <t>Product</t>
@@ -19264,22 +19268,22 @@
       </c>
       <c r="D36" s="90" t="inlineStr">
         <is>
-          <t>Internal MCP server -- get_market_brief / get_action_queue / approve_action</t>
+          <t>Internal MCP server -- expand further (menu insights, forecast, what-if)</t>
         </is>
       </c>
       <c r="E36" s="90" t="inlineStr">
         <is>
-          <t>3 new tools on CortexKitchen's own MCP server (mcp_server.py), JWT-authenticated, calling MarketIntelService and ActionQueueService live. Lets an owner ask Claude Desktop directly about their restaurant and approve actions from there.</t>
+          <t>Wrap additional existing services as MCP tools beyond the 3 in P6-A30 -- menu insights, demand forecast, and the Phase-5 what-if simulator. Cheap since the service layer already exists; positions CortexKitchen as a general AI-accessible restaurant data layer, not just 3 utility tools.</t>
         </is>
       </c>
       <c r="F36" s="90" t="inlineStr">
         <is>
-          <t>feat: 3 new MCP tools -- get_market_brief, get_action_queue, approve_action</t>
+          <t>feat: expand internal MCP server -- menu insights, forecast, what-if simulator as tools</t>
         </is>
       </c>
       <c r="G36" s="90" t="inlineStr">
         <is>
-          <t>docs/APIS.md, docs/ARCHITECTURE.md</t>
+          <t>docs/APIS.md</t>
         </is>
       </c>
       <c r="H36" s="108" t="inlineStr">
@@ -19289,7 +19293,7 @@
       </c>
       <c r="I36" s="89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J36" s="89" t="inlineStr">
@@ -19304,12 +19308,12 @@
       </c>
       <c r="N36" s="90" t="inlineStr">
         <is>
-          <t>P6-A22</t>
+          <t>P6-A31</t>
         </is>
       </c>
       <c r="O36" s="90" t="inlineStr">
         <is>
-          <t>all 3 tools smoke-tested in Claude Desktop; approve_action triggers the same approval path as the web UI; JWT enforced</t>
+          <t>each new tool smoke-tested in Claude Desktop; correct data returned matching the equivalent API endpoint</t>
         </is>
       </c>
     </row>
@@ -19319,30 +19323,34 @@
           <t>P6-A33</t>
         </is>
       </c>
-      <c r="B37" s="69" t="n"/>
+      <c r="B37" s="98" t="inlineStr">
+        <is>
+          <t>feature/brief-page</t>
+        </is>
+      </c>
       <c r="C37" s="90" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D37" s="90" t="inlineStr">
         <is>
-          <t>Internal MCP server -- expand further (menu insights, forecast, what-if)</t>
+          <t>/brief page</t>
         </is>
       </c>
       <c r="E37" s="90" t="inlineStr">
         <is>
-          <t>Wrap additional existing services as MCP tools beyond the 3 in P6-A31 -- menu insights, demand forecast, and the Phase-5 what-if simulator. Cheap since the service layer already exists; positions CortexKitchen as a general AI-accessible restaurant data layer, not just 3 utility tools.</t>
+          <t>Daily morning briefing -- overnight performance, today's forecast vs yesterday, top 3 action priorities, market snapshot. Single-screen showcase of the whole system's intelligence.</t>
         </is>
       </c>
       <c r="F37" s="90" t="inlineStr">
         <is>
-          <t>feat: expand internal MCP server -- menu insights, forecast, what-if simulator as tools</t>
+          <t>feat: /brief page -- daily morning operational briefing</t>
         </is>
       </c>
       <c r="G37" s="90" t="inlineStr">
         <is>
-          <t>docs/APIS.md</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H37" s="108" t="inlineStr">
@@ -19352,7 +19360,7 @@
       </c>
       <c r="I37" s="89" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J37" s="89" t="inlineStr">
@@ -19367,12 +19375,12 @@
       </c>
       <c r="N37" s="90" t="inlineStr">
         <is>
-          <t>P6-A32</t>
+          <t>P6-A22</t>
         </is>
       </c>
       <c r="O37" s="90" t="inlineStr">
         <is>
-          <t>each new tool smoke-tested in Claude Desktop; correct data returned matching the equivalent API endpoint</t>
+          <t>manual verification</t>
         </is>
       </c>
     </row>
@@ -19382,34 +19390,30 @@
           <t>P6-A34</t>
         </is>
       </c>
-      <c r="B38" s="98" t="inlineStr">
-        <is>
-          <t>feature/brief-page</t>
-        </is>
-      </c>
+      <c r="B38" s="98" t="n"/>
       <c r="C38" s="90" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="D38" s="90" t="inlineStr">
         <is>
-          <t>/brief page</t>
+          <t>Post-Phase-A documentation, test, CI, observability, and eval refresh</t>
         </is>
       </c>
       <c r="E38" s="90" t="inlineStr">
         <is>
-          <t>Daily morning briefing -- overnight performance, today's forecast vs yesterday, top 3 action priorities, market snapshot. Single-screen showcase of the whole system's intelligence.</t>
+          <t>Once Phase A ships, a lot of new surface area will have landed at once -- Action Queue, workflow triggers, the anomaly agent, both executors, new connectors (Zomato stub, reviews), new data models (Recipe, Vendor, Expense, Obligation), MCP expansion. Do a full pass rather than letting docs drift: update every docs/*.md file, CLAUDE.md, README, and any screenshots referenced in docs to reflect what actually shipped. Audit test coverage for every new service/model added in Phase A -- confirm nothing shipped without tests. Re-check the CI pipeline includes all new test files. Re-run/expand RAGAS + DeepEval evals to cover the new agentic behaviors (anomaly diagnoses, dynamic pricing suggestions), since the existing eval sets predate all of this and won't catch regressions in it.</t>
         </is>
       </c>
       <c r="F38" s="90" t="inlineStr">
         <is>
-          <t>feat: /brief page -- daily morning operational briefing</t>
+          <t>docs: full documentation, test-coverage, CI, and eval refresh after the Phase A agentic core ships</t>
         </is>
       </c>
       <c r="G38" s="90" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>All docs/*.md, CLAUDE.md, README.md</t>
         </is>
       </c>
       <c r="H38" s="108" t="inlineStr">
@@ -19419,7 +19423,7 @@
       </c>
       <c r="I38" s="89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J38" s="89" t="inlineStr">
@@ -19434,96 +19438,49 @@
       </c>
       <c r="N38" s="90" t="inlineStr">
         <is>
-          <t>P6-A23</t>
+          <t>All P6-A tasks</t>
         </is>
       </c>
       <c r="O38" s="90" t="inlineStr">
         <is>
-          <t>manual verification</t>
+          <t>Every new service/model has test coverage; CI includes all new test files; RAGAS/DeepEval sets include at least one case per new agentic behavior; docs/screenshots match shipped behavior</t>
         </is>
       </c>
     </row>
     <row r="39" ht="171.6" customHeight="1" s="72">
-      <c r="A39" s="65" t="inlineStr">
-        <is>
-          <t>P6-A35</t>
-        </is>
-      </c>
-      <c r="B39" s="98" t="n"/>
-      <c r="C39" s="90" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="D39" s="90" t="inlineStr">
-        <is>
-          <t>Post-Phase-A documentation, test, CI, observability, and eval refresh</t>
-        </is>
-      </c>
-      <c r="E39" s="90" t="inlineStr">
-        <is>
-          <t>Once Phase A ships, a lot of new surface area will have landed at once -- Action Queue, workflow triggers, the anomaly agent, both executors, new connectors (Zomato stub, reviews), new data models (Recipe, Vendor, Expense, Obligation), MCP expansion. Do a full pass rather than letting docs drift: update every docs/*.md file, CLAUDE.md, README, and any screenshots referenced in docs to reflect what actually shipped. Audit test coverage for every new service/model added in Phase A -- confirm nothing shipped without tests. Re-check the CI pipeline includes all new test files. Re-run/expand RAGAS + DeepEval evals to cover the new agentic behaviors (anomaly diagnoses, dynamic pricing suggestions), since the existing eval sets predate all of this and won't catch regressions in it.</t>
-        </is>
-      </c>
-      <c r="F39" s="90" t="inlineStr">
-        <is>
-          <t>docs: full documentation, test-coverage, CI, and eval refresh after the Phase A agentic core ships</t>
-        </is>
-      </c>
-      <c r="G39" s="90" t="inlineStr">
-        <is>
-          <t>All docs/*.md, CLAUDE.md, README.md</t>
-        </is>
-      </c>
-      <c r="H39" s="108" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I39" s="89" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J39" s="89" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K39" s="89" t="n"/>
-      <c r="L39" s="89" t="n"/>
-      <c r="M39" s="91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="90" t="inlineStr">
-        <is>
-          <t>All P6-A tasks</t>
-        </is>
-      </c>
-      <c r="O39" s="90" t="inlineStr">
-        <is>
-          <t>Every new service/model has test coverage; CI includes all new test files; RAGAS/DeepEval sets include at least one case per new agentic behavior; docs/screenshots match shipped behavior</t>
-        </is>
-      </c>
+      <c r="A39" s="111" t="n"/>
+      <c r="B39" s="111" t="n"/>
+      <c r="C39" s="111" t="n"/>
+      <c r="D39" s="111" t="n"/>
+      <c r="E39" s="111" t="n"/>
+      <c r="F39" s="111" t="n"/>
+      <c r="G39" s="111" t="n"/>
+      <c r="H39" s="111" t="n"/>
+      <c r="I39" s="111" t="n"/>
+      <c r="J39" s="111" t="n"/>
+      <c r="K39" s="111" t="n"/>
+      <c r="L39" s="111" t="n"/>
+      <c r="M39" s="111" t="n"/>
+      <c r="N39" s="111" t="n"/>
+      <c r="O39" s="111" t="n"/>
     </row>
     <row r="40" ht="39.6" customHeight="1" s="72"/>
     <row r="41" ht="171.6" customHeight="1" s="72"/>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B7:B8"/>
+  <mergeCells count="13">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B33:B34"/>
     <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -19536,7 +19493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="40.77734375" customWidth="1" style="72" min="1" max="1"/>
@@ -19673,7 +19630,7 @@
       </c>
       <c r="E4" s="62" t="inlineStr">
         <is>
-          <t>Phase A (P6-A28) already builds the full get_cart -&gt; update_cart -&gt; LangGraph interrupt() -&gt; owner approval -&gt; checkout flow end-to-end, with the final checkout() call mocked and labeled 'awaiting staging creds'. This task is just the swap: replace the mock with the real call. NON-IDEMPOTENT: on any 5xx from checkout, call get_orders before retrying -- never blind-retry. procurement_orders rows switch from a 'simulated' flag to real confirmed orders.</t>
+          <t>Phase A (P6-A27) already builds the full get_cart -&gt; update_cart -&gt; LangGraph interrupt() -&gt; owner approval -&gt; checkout flow end-to-end, with the final checkout() call mocked and labeled 'awaiting staging creds'. This task is just the swap: replace the mock with the real call. NON-IDEMPOTENT: on any 5xx from checkout, call get_orders before retrying -- never blind-retry. procurement_orders rows switch from a 'simulated' flag to real confirmed orders.</t>
         </is>
       </c>
       <c r="F4" s="62" t="inlineStr">
@@ -19708,7 +19665,7 @@
       </c>
       <c r="N4" s="62" t="inlineStr">
         <is>
-          <t>P6-A28, P6-S14</t>
+          <t>P6-A27, P6-S14</t>
         </is>
       </c>
       <c r="O4" s="62" t="inlineStr">
@@ -19757,7 +19714,7 @@
       </c>
       <c r="E6" s="62" t="inlineStr">
         <is>
-          <t>book_table in consumer MCP books a table AT another restaurant (a consumer action), not managing your own restaurant's Dineout presence -- that needs Swiggy Partner/Business API, a separate track from these creds. Phase A (P6-A29) already builds the full create_cart -&gt; book_table flow end-to-end with the final call mocked. This task swaps the mock for the real call, scoped to the consumer-booking use case only (e.g. mystery-dining a competitor for research).</t>
+          <t>book_table in consumer MCP books a table AT another restaurant (a consumer action), not managing your own restaurant's Dineout presence -- that needs Swiggy Partner/Business API, a separate track from these creds. Phase A (P6-A28) already builds the full create_cart -&gt; book_table flow end-to-end with the final call mocked. This task swaps the mock for the real call, scoped to the consumer-booking use case only (e.g. mystery-dining a competitor for research).</t>
         </is>
       </c>
       <c r="F6" s="62" t="inlineStr">
@@ -19792,7 +19749,7 @@
       </c>
       <c r="N6" s="62" t="inlineStr">
         <is>
-          <t>P6-A29</t>
+          <t>P6-A28</t>
         </is>
       </c>
       <c r="O6" s="62" t="inlineStr">
@@ -19837,7 +19794,7 @@
       </c>
       <c r="E8" s="62" t="inlineStr">
         <is>
-          <t>Once P7-1/P7-2 prove reliable in production, extend the trust-ladder mechanic (P6-A25) to real money-touching actions -- e.g. auto-reorder a habitually-restocked ingredient without approval once trust is established.</t>
+          <t>Once P7-1/P7-2 prove reliable in production, extend the trust-ladder mechanic (P6-A24) to real money-touching actions -- e.g. auto-reorder a habitually-restocked ingredient without approval once trust is established.</t>
         </is>
       </c>
       <c r="F8" s="62" t="inlineStr">
@@ -19872,7 +19829,7 @@
       </c>
       <c r="N8" s="62" t="inlineStr">
         <is>
-          <t>P6-A25, P7-1, P7-2</t>
+          <t>P6-A24, P7-1, P7-2</t>
         </is>
       </c>
       <c r="O8" s="62" t="inlineStr">
@@ -20060,7 +20017,7 @@
       </c>
       <c r="N14" s="62" t="inlineStr">
         <is>
-          <t>P6-A20</t>
+          <t>P6-A19</t>
         </is>
       </c>
       <c r="O14" s="62" t="inlineStr">
@@ -20797,6 +20754,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="62" t="inlineStr">
         <is>
@@ -20864,12 +20822,83 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="110" t="inlineStr">
+        <is>
+          <t>BLOCKED -- needs a real restaurant (not seeded/synthetic data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="112" t="inlineStr">
+        <is>
+          <t>P7-15</t>
+        </is>
+      </c>
+      <c r="B42" s="112" t="inlineStr">
+        <is>
+          <t>feature/multi-platform-connectors</t>
+        </is>
+      </c>
+      <c r="C42" s="112" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="D42" s="112" t="inlineStr">
+        <is>
+          <t>Public review aggregation connectors (Google/Zomato reviews)</t>
+        </is>
+      </c>
+      <c r="E42" s="112" t="inlineStr">
+        <is>
+          <t>GoogleReviewsConnector / ZomatoReviewsConnector following the same BaseConnector pattern, pulling public review data (not internal complaints) into complaint_intelligence as an additional source type. Extends the Feedback model's source concept rather than inventing a parallel system. DEFERRED 2026-07-07 from Phase 6A -- unlike the Zomato stub connector (which only needed to prove the architecture, not pull real data), this task's entire value IS real review data. There is no real Google/Zomato business listing for this restaurant to pull reviews from yet, so even a demoable version isn't possible until a real restaurant customer exists. Revisit then.</t>
+        </is>
+      </c>
+      <c r="F42" s="112" t="inlineStr">
+        <is>
+          <t>feat: public review aggregation -- Google/Zomato reviews via BaseConnector pattern</t>
+        </is>
+      </c>
+      <c r="G42" s="112" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md, docs/CONNECTORS.md</t>
+        </is>
+      </c>
+      <c r="H42" s="112" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="I42" s="112" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J42" s="112" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K42" s="113" t="n"/>
+      <c r="L42" s="112" t="n"/>
+      <c r="M42" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="112" t="n"/>
+      <c r="O42" s="112" t="inlineStr">
+        <is>
+          <t>reviews ingested with correct source tag; complaint_intelligence node correctly surfaces public-review-sourced themes alongside internal ones</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A12:O12"/>
     <mergeCell ref="A20:O20"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A40:O40"/>
     <mergeCell ref="A18:O18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -17152,7 +17152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:O39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.109375" customWidth="1" style="72" min="1" max="1"/>
@@ -17600,7 +17600,7 @@
       </c>
       <c r="B8" s="98" t="inlineStr">
         <is>
-          <t>feature/financial-compliance</t>
+          <t>feature/financial-scorecard</t>
         </is>
       </c>
       <c r="C8" s="90" t="inlineStr">
@@ -17625,12 +17625,12 @@
       </c>
       <c r="G8" s="90" t="inlineStr">
         <is>
-          <t>docs/APIS.md</t>
+          <t>CLAUDE.md, docs/APIS.md</t>
         </is>
       </c>
       <c r="H8" s="108" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I8" s="89" t="inlineStr">
@@ -17643,10 +17643,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K8" s="89" t="n"/>
-      <c r="L8" s="89" t="n"/>
+      <c r="K8" s="89" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="L8" s="89" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
       <c r="M8" s="91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="90" t="n"/>
       <c r="O8" s="90" t="inlineStr">
@@ -19469,17 +19477,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A24:O24"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B25:B26"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="B25:B26"/>
     <mergeCell ref="B16:B18"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B29:B30"/>
     <mergeCell ref="B31:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20754,7 +20762,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="62" t="inlineStr">
         <is>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -17798,7 +17798,7 @@
       </c>
       <c r="E11" s="63" t="inlineStr">
         <is>
-          <t>Confirmed via direct restaurant-owner research (2026-07-08 call): procurement here is manual -- the manager coordinates with known vendors by phone, in-person market visits, or WhatsApp; there is no e-commerce checkout step to automate. Closes the loop between an inventory shortage signal and the real communication channel this restaurant actually uses: the agent drafts a vendor message from a shortage row (e.g. 'Mozzarella running low, 2.6kg left vs 8kg threshold -- order more from Ramesh Traders') and sends it via Twilio's WhatsApp Sandbox API to a demo vendor number. Replaces the originally-planned Instamart-checkout ProcurementExecutor, which this call confirmed doesn't match how this restaurant procures (see deleted P7-23; P7-1's premise flagged as stale for this restaurant). Routes through the Action Queue (P6-A7/P6-A8): the agent creates a PENDING action_queue row with the drafted message, the manager approves via the Action Queue UI, and only then does it send via Twilio -- not an unreviewed auto-send. Repeated approvals of the same vendor/ingredient pattern can, via the trust-ladder mechanic (P6-A12), eventually promote future instances to auto-send.</t>
+          <t>Confirmed via direct restaurant-owner research (2026-07-08 call): procurement here is manual -- the manager coordinates with known vendors by phone, in-person market visits, or WhatsApp; there is no e-commerce checkout step to automate. Closes the loop between an inventory shortage signal and the real communication channel this restaurant actually uses: the agent drafts a vendor message from a shortage row (e.g. 'Mozzarella running low, 2.6kg left vs 8kg threshold -- order more from Ramesh Traders') and sends it via Twilio's WhatsApp Sandbox API to a demo vendor number. Replaces the originally-planned Instamart-checkout ProcurementExecutor task (deleted -- this call confirmed Instamart checkout doesn't match how this restaurant procures; P7-1's premise is flagged as stale for this restaurant as a result). Routes through the Action Queue (P6-A7/P6-A8): the agent creates a PENDING action_queue row with the drafted message, the manager approves via the Action Queue UI, and only then does it send via Twilio -- not an unreviewed auto-send. Repeated approvals of the same vendor/ingredient pattern can, via the trust-ladder mechanic (P6-A12), eventually promote future instances to auto-send. LIVE-VERIFIED 2026-07-08: real Twilio WhatsApp Sandbox message sent and received on the demo phone; approve-triggers-send flow confirmed end-to-end through the Action Queue UI; Twilio-failure path (missing vendor, missing message, Twilio exception) verified to mark the action errored without crashing, via 5 unit tests mocking Twilio.</t>
         </is>
       </c>
       <c r="F11" s="63" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="H11" s="68" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I11" s="62" t="inlineStr">
@@ -17826,10 +17826,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K11" s="62" t="n"/>
-      <c r="L11" s="62" t="n"/>
+      <c r="K11" s="62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="L11" s="62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="M11" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="63" t="inlineStr">
         <is>
@@ -17861,7 +17869,7 @@
       </c>
       <c r="E12" s="63" t="inlineStr">
         <is>
-          <t>New Vendor model (name, category, is_online, contact/WhatsApp number) + VendorPriceQuote (vendor_id, ingredient, price, quoted_at). Instamart becomes one Vendor among several (an 'online' vendor with live API pricing); local vendors become trackable entities with a WhatsApp contact, matching the real procurement pattern confirmed on the 2026-07-08 restaurant-owner call. Pulled forward out of its original pairing with Recipe/RecipeIngredient (now P7-21, still deferred) now that a real, demo-relevant use exists for it (the WhatsApp task above) -- it only needs a name+contact+ingredients-supplied mapping, not full recipe costing.</t>
+          <t>New Vendor model (name, category, is_online, contact/WhatsApp number) + VendorPriceQuote (vendor_id, ingredient, price, quoted_at). Instamart becomes one Vendor among several (an 'online' vendor with live API pricing); local vendors become trackable entities with a WhatsApp contact, matching the real procurement pattern confirmed on the 2026-07-08 restaurant-owner call. Pulled forward out of its original pairing with Recipe/RecipeIngredient (now P7-21, still deferred) now that a real, demo-relevant use exists for it (the WhatsApp task above) -- it only needs a name+contact+ingredients-supplied mapping, not full recipe costing. LIVE-VERIFIED 2026-07-08: 6/6 unit tests passing, including cheapest-vendor-per-ingredient query; seed data updated with 3 real vendor rows (2 local WhatsApp vendors, 1 online) and 3 price quotes.</t>
         </is>
       </c>
       <c r="F12" s="63" t="inlineStr">
@@ -17876,7 +17884,7 @@
       </c>
       <c r="H12" s="68" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I12" s="62" t="inlineStr">
@@ -17889,10 +17897,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K12" s="62" t="n"/>
-      <c r="L12" s="62" t="n"/>
+      <c r="K12" s="62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="L12" s="62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="M12" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="63" t="n"/>
       <c r="O12" s="63" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -17940,7 +17940,7 @@
       </c>
       <c r="E13" s="63" t="inlineStr">
         <is>
-          <t>A small WorkflowEngine evaluating built-in conditions after each planning run and auto-creating action_queue rows. Ships with 2-3 real triggers to start: (1) 2+ critical shortages found -&gt; queue an urgent restock action, (2) tonight_busy + 2+ competitor Dineout deals live -&gt; queue a pricing/promo review action. Deliberately NOT the full owner-defined trigger/condition/action builder from the original workflow-system idea -- that's a much bigger UI/DB investment for marginal demo value beyond just having the triggers exist.</t>
+          <t>A small WorkflowEngine evaluating built-in conditions after each planning run and auto-creating action_queue rows. Ships with 2-3 real triggers to start: (1) 2+ critical shortages found -&gt; queue an urgent restock action, (2) tonight_busy + 2+ competitor Dineout deals live -&gt; queue a pricing/promo review action. Deliberately NOT the full owner-defined trigger/condition/action builder from the original workflow-system idea -- that's a much bigger UI/DB investment for marginal demo value beyond just having the triggers exist. LIVE-VERIFIED 2026-07-08 against a real planning run (groq/llama-3.3-70b, low_stock_weekend scenario): the critical-shortages trigger correctly created a real restock_alert action from a genuine 3-shortage plan; repeat runs (including a semantic-cache hit, which required a separate fix since cache hits were initially skipping trigger evaluation entirely) correctly avoided duplicating the still-pending action. 10/10 unit tests passing.</t>
         </is>
       </c>
       <c r="F13" s="63" t="inlineStr">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="H13" s="68" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I13" s="62" t="inlineStr">
@@ -17968,10 +17968,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K13" s="62" t="n"/>
-      <c r="L13" s="62" t="n"/>
+      <c r="K13" s="62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="L13" s="62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="M13" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="63" t="inlineStr">
         <is>
@@ -18003,12 +18011,12 @@
       </c>
       <c r="E14" s="63" t="inlineStr">
         <is>
-          <t>Track consecutive unedited approvals per action_type. After N consecutive approvals (default 3) of the same type, offer 'always do this automatically' -- promotes future instances of that action_type straight to AUTO tier for that org. Makes 'autonomous' a visible, explainable mechanic rather than a claim.</t>
+          <t>RESCOPED 2026-07-08, before build: the original spec (auto-promote a category to AUTO tier -- skip approval entirely -- after N consecutive approvals) was cut after review. The restaurant-owner call confirmed the manager wants to stay in the loop on every vendor communication and pricing decision right now; auto-bypassing approval would directly contradict that confirmed reality, not just be unproven. Built instead: TrustLadderService.count_consecutive_approvals(org_id, category) -- counts an unbroken streak of approved/executed decisions for a category, broken by the first rejection, excluding still-pending items from the count. Surfaced as a read-only "Approved Nx in a row" badge on GET /action-queue and in the Action Queue UI -- an honest signal, never an autonomy grant. LIVE-VERIFIED 2026-07-08: seed data includes 2 historical decided WhatsApp orders so the badge shows real data on a fresh seed; confirmed rendering correctly in the browser. 6/6 unit tests passing.</t>
         </is>
       </c>
       <c r="F14" s="63" t="inlineStr">
         <is>
-          <t>feat: trust-ladder -- auto-promote repeatedly-approved action types to AUTO tier</t>
+          <t>feat: trust-ladder -- read-only approval-streak badge, no auto-bypass</t>
         </is>
       </c>
       <c r="G14" s="63" t="inlineStr">
@@ -18018,7 +18026,7 @@
       </c>
       <c r="H14" s="68" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I14" s="62" t="inlineStr">
@@ -18031,10 +18039,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K14" s="62" t="n"/>
-      <c r="L14" s="62" t="n"/>
+      <c r="K14" s="62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="L14" s="62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="M14" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="63" t="inlineStr">
         <is>
@@ -18043,7 +18059,7 @@
       </c>
       <c r="O14" s="63" t="inlineStr">
         <is>
-          <t>N consecutive approvals triggers promotion prompt; promoted type skips approval next time</t>
+          <t>approval streak counts correctly across approve/reject/pending sequences, scoped per org and category</t>
         </is>
       </c>
     </row>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -18389,12 +18389,12 @@
       </c>
       <c r="E20" s="63" t="inlineStr">
         <is>
-          <t>test_swiggy_reservation_sync.py and test_connector_repository.py are excluded from CI because SQLite can't render Postgres JSONB columns. Either a SQLite-compatible fallback type or a Postgres CI service container.</t>
+          <t>test_swiggy_reservation_sync.py and test_connector_repository.py were excluded from CI because SQLite can't render Postgres JSONB columns (Connector.connector_metadata). Fixed at the root: converted every JSONB column in the schema to plain JSON (Organization.settings, DecisionLog.metadata, PlanningRun.final_response/recommendations/rag_context/critic/metadata, Connector.connector_metadata) -- none of them used any Postgres-only JSONB feature (no .astext, .contains(), or GIN index usage anywhere in the codebase, confirmed via full-repo grep before choosing this fix over a Postgres CI service container). Both previously-excluded test files now run in the standard suite with no fixture workarounds needed. LIVE-VERIFIED 2026-07-08: full suite is 462 passed / 0 errors (the first fully clean run this project has had); a real planning run via the internal MCP server confirmed PlanningRun.final_response (now plain JSON) still writes and reads correctly in production.</t>
         </is>
       </c>
       <c r="F20" s="63" t="inlineStr">
         <is>
-          <t>fix: SQLite-compatible JSONB handling (or Postgres CI service) for excluded test files</t>
+          <t>fix: convert every JSONB column to plain JSON -- eliminates the SQLite/CI test-infra gap at the root</t>
         </is>
       </c>
       <c r="G20" s="63" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="H20" s="68" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I20" s="62" t="inlineStr">
@@ -18417,10 +18417,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K20" s="62" t="n"/>
-      <c r="L20" s="62" t="n"/>
+      <c r="K20" s="62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="L20" s="62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="M20" s="64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="63" t="n"/>
       <c r="O20" s="63" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -1036,12 +1036,12 @@
     <row r="3" ht="14.4" customHeight="1" s="73">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Current: Phase 6 — 55 done (41 + P6-MI05-14). Next: P6-S32/F06 (action queue)</t>
+          <t>Current: Phase 6 -- 69 done (55 Phase 6 + 14 Phase 6A: A1-A13, A18). Next: P6-A14 (weather + holiday signals)</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>14 Swiggy tools live (search_menu confirmed non-viable, removed). Market intel: category pricing, positioning, deals, trends all shipped</t>
+          <t>Action Queue live with trust-ladder + WhatsApp vendor execution. MCP server (5 tools) + in-app chatbot both expose get_market_brief/get_action_queue/approve_action. Financial scorecard (real P&amp;L, health score) shipped.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1072,12 +1072,12 @@
     <row r="4" ht="14.4" customHeight="1" s="73">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Last done: P6-MI05-MI14 — market intel expansion + category-independent redesign + personal-data leak fix</t>
+          <t>Last done: P6-A13 -- Internal MCP server + in-app chatbot tools (get_market_brief, get_action_queue, approve_action)</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Design system, 11-node pipeline, enrichers, market/operations/connectors pages, full market intel expansion shipped</t>
+          <t>Both surfaces share ActionQueueService + action_execution_service.approve_and_execute so approval behaves identically from Claude Desktop, in-app chat, or the UI button. Live-verified against real demo org 2026-07-08.</t>
         </is>
       </c>
       <c r="C4" s="1" t="n"/>
@@ -1108,7 +1108,7 @@
     <row r="5" ht="14.4" customHeight="1" s="73">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Priority: S32/F06 (action queue) → S33/S34 → S36/F07/F08 → R01 → staging creds → P7</t>
+          <t>Priority: A14 (weather/holiday signals) -&gt; A15 (menu engineering UI) -&gt; A16 (Dineout chatbot tools) -&gt; A17 (structured outputs) -&gt; A19/A20 (eval datasets) -&gt; A21 (redesign) -&gt; A22 (voice) -&gt; A23 (docs refresh) -&gt; A24 (sync to main) -&gt; staging creds -&gt; P7</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1541,11 +1541,11 @@
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>0.6892</v>
+        <v>0.8734</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Swiggy-native restaurant OS: connector layer (Swiggy first, POS second), 11-node LangGraph pipeline, action queue with approval gates, 3 product modes (ops/brief/live), voice interface, 5 new frontend pages</t>
+          <t>Swiggy-native restaurant OS: connector layer, 11-node LangGraph pipeline, Action Queue with approval gates + trust ladder + WhatsApp execution, financial scorecard, MCP server + in-app chatbot tool parity, 5 new frontend pages</t>
         </is>
       </c>
     </row>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -18425,7 +18425,7 @@
       </c>
       <c r="E19" s="70" t="inlineStr">
         <is>
-          <t>Delete the Zomato stub connector entirely -- confirmed via codebase audit this is more than a name in one file. Remove: apps/api/app/infrastructure/zomato/ (ZomatoConnector), its CAPABILITY_PROVIDERS entries in provider_registry.py (currently lists zomato alongside swiggy under 'competitor_pricing' and 'order_history' -- bad optics under clause 17 audit rights even though the connector never makes a live call), the Zomato card on the /connectors frontend page ("Import orders and customer reviews from Zomato" -- visible in any demo), and test_zomato_connector.py. Remove ConnectorType.zomato from infrastructure/db/models.py. Do NOT touch FeedbackSource.zomato (separate enum, same file) -- that's just a provenance tag for feedback that originated from a Zomato review, no live Zomato connection involved, legitimate to keep. Clause 6.1 of the signed Swiggy Integration Agreement bars partnering with any other food delivery/dining/quick-commerce platform for a similar solution -- mark P6-A5 as Removed in this tracker.</t>
+          <t>Delete the Zomato stub connector entirely -- confirmed via codebase audit this is more than a name in one file. Remove: apps/api/app/infrastructure/zomato/ (ZomatoConnector), its CAPABILITY_PROVIDERS entries in provider_registry.py (currently lists zomato alongside swiggy under 'competitor_pricing' and 'order_history' -- bad optics under clause 17 audit rights even though the connector never makes a live call), the Zomato card on the /connectors frontend page ("Import orders and customer reviews from Zomato" -- visible in any demo), and test_zomato_connector.py. Remove ConnectorType.zomato from infrastructure/db/models.py. Do NOT touch FeedbackSource.zomato (separate enum, same file) -- that's just a provenance tag for feedback that originated from a Zomato review, no live Zomato connection involved, legitimate to keep. Clause 6.1 of the signed Swiggy Integration Agreement bars partnering with any other food delivery/dining/quick-commerce platform for a similar solution -- mark P6-A5 as Removed in this tracker. The multi-provider architecture itself is NOT the compliance problem and stays intact -- BaseConnector, provider_registry.py's CAPABILITY_PROVIDERS pattern, and ConnectorType stay exactly as they are, already proven extensible by pos_square and google_reviews (neither is a food-delivery/dining/quick-commerce competitor, so both are unaffected). Only the one concrete entry naming an actual competing platform (zomato) is removed. base_connector.py's module docstring updated to state what the pattern may extend to going forward (POS systems, loyalty/rewards platforms, accounting/inventory tools, review aggregators, payment processors) and what it must not (any other food delivery/dining-out/quick-commerce platform, e.g. Zomato, EazyDiner, while clause 6.1 is in effect).</t>
         </is>
       </c>
       <c r="F19" s="70" t="inlineStr">
@@ -18435,12 +18435,12 @@
       </c>
       <c r="G19" s="70" t="inlineStr">
         <is>
-          <t>CLAUDE.md (remove Zomato references), docs/ARCHITECTURE.md</t>
+          <t>CLAUDE.md, docs/ARCHITECTURE.md, docs/DATA_MODEL.md, docs/SWIGGY_INTEGRATION.md</t>
         </is>
       </c>
       <c r="H19" s="71" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I19" s="69" t="inlineStr">
@@ -18456,7 +18456,7 @@
       <c r="K19" s="69" t="n"/>
       <c r="L19" s="69" t="n"/>
       <c r="M19" s="72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="70" t="n"/>
       <c r="O19" s="70" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -18425,7 +18425,7 @@
       </c>
       <c r="E19" s="70" t="inlineStr">
         <is>
-          <t>Delete the Zomato stub connector entirely -- confirmed via codebase audit this is more than a name in one file. Remove: apps/api/app/infrastructure/zomato/ (ZomatoConnector), its CAPABILITY_PROVIDERS entries in provider_registry.py (currently lists zomato alongside swiggy under 'competitor_pricing' and 'order_history' -- bad optics under clause 17 audit rights even though the connector never makes a live call), the Zomato card on the /connectors frontend page ("Import orders and customer reviews from Zomato" -- visible in any demo), and test_zomato_connector.py. Remove ConnectorType.zomato from infrastructure/db/models.py. Do NOT touch FeedbackSource.zomato (separate enum, same file) -- that's just a provenance tag for feedback that originated from a Zomato review, no live Zomato connection involved, legitimate to keep. Clause 6.1 of the signed Swiggy Integration Agreement bars partnering with any other food delivery/dining/quick-commerce platform for a similar solution -- mark P6-A5 as Removed in this tracker. The multi-provider architecture itself is NOT the compliance problem and stays intact -- BaseConnector, provider_registry.py's CAPABILITY_PROVIDERS pattern, and ConnectorType stay exactly as they are, already proven extensible by pos_square and google_reviews (neither is a food-delivery/dining/quick-commerce competitor, so both are unaffected). Only the one concrete entry naming an actual competing platform (zomato) is removed. base_connector.py's module docstring updated to state what the pattern may extend to going forward (POS systems, loyalty/rewards platforms, accounting/inventory tools, review aggregators, payment processors) and what it must not (any other food delivery/dining-out/quick-commerce platform, e.g. Zomato, EazyDiner, while clause 6.1 is in effect).</t>
+          <t>DONE on feature/compliance-fixes (commits 1cebdfa, d75dfbd). Deleted the Zomato stub connector entirely -- codebase audit found it was more than a name in one file: apps/api/app/infrastructure/zomato/ (ZomatoConnector) removed; provider_registry.py's CAPABILITY_PROVIDERS had zomato under 'competitor_pricing' and 'order_history', PLUS an eazydiner entry under 'reservation_data' found during the same audit (EazyDiner is Zomato's own dining-reservation vertical, same category, also just an unimplemented placeholder with no connector class) -- both removed, all four capability lists now read ['swiggy'] only. Removed the Zomato card from the /connectors frontend page and test_zomato_connector.py. Removed ConnectorType.zomato from infrastructure/db/models.py -- confirmed connector_type is a plain String(50) column, not a DB enum, so no Alembic migration was needed. Did NOT touch FeedbackSource.zomato (separate enum, same file) -- that's just a provenance tag for feedback that originated from a Zomato review, no live connection, legitimate to keep. The multi-provider architecture itself was never the problem and stays fully intact -- BaseConnector, provider_registry.py's pattern, and ConnectorType stay exactly as they are, already proven extensible by pos_square and google_reviews (neither is a food-delivery/dining/quick-commerce competitor). base_connector.py's docstring and provider_registry.py's comments were updated to state what the pattern extends to going forward (POS systems, loyalty/rewards platforms, accounting/inventory tools, review aggregators, payment processors) -- phrased as ordinary architectural framing ("kept single-provider for now"), not as legal/clause citations; that level of detail stays only in CLAUDE.md's dedicated compliance section, not scattered across code comments or public docs. docs/ARCHITECTURE.md, docs/DATA_MODEL.md, and docs/SWIGGY_INTEGRATION.md updated to match -- all three had stale code snippets/schema tables still listing zomato/eazydiner as live options. docs/DECISIONS.md deliberately left untouched -- it's a point-in-time ADR, not a current-state doc. scripts/seed_demo_data.py has an expense note "Swiggy/Zomato ad spend" -- left as-is, it's realistic demo financial data (a restaurant advertising on both platforms), not a technical Zomato connection; flagged to the user as a judgment call, not yet asked to change it.</t>
         </is>
       </c>
       <c r="F19" s="70" t="inlineStr">
@@ -18461,7 +18461,7 @@
       <c r="N19" s="70" t="n"/>
       <c r="O19" s="70" t="inlineStr">
         <is>
-          <t>grep -ri zomato across apps/ returns zero hits except FeedbackSource.zomato (intentionally kept); no ConnectorType.zomato in models.py; provider_registry.py competitor_pricing/order_history lists contain only swiggy; /connectors page has no Zomato card; CI passes</t>
+          <t>VERIFIED: grep -ri "zomato|eazydiner" across apps/ returns only FeedbackSource.zomato (models.py, intentionally kept) and the explanatory mentions in base_connector.py's docstring; provider_registry.py's four CAPABILITY_PROVIDERS lists contain only 'swiggy'; /connectors page has no Zomato card; test_zomato_connector.py deleted, one stray "zomato" example string in test_connector_repository.py swapped to "pos_square"; 487 backend tests pass; frontend typechecks clean (npx tsc --noEmit, zero errors).</t>
         </is>
       </c>
     </row>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -18488,7 +18488,7 @@
       </c>
       <c r="E20" s="74" t="inlineStr">
         <is>
-          <t>Update CompetitorEnricher and OccupancyEnricher to remove specific restaurant names and individual pricing from all outputs. Replace with area-level aggregates only: "area avg for North Indian mains: Rs.265" not "Biryani House charges Rs.280". Occupancy: "3 restaurants in your area are HIGH occupancy tonight" not named ones. Deals: "2 restaurants near you have Dineout deals tonight" — no names. This keeps the feature useful for operator planning while removing the competitive intelligence angle that clause 4(iv) restricts. Update all prompt injections, market panel UI, and API responses accordingly.</t>
+          <t>DONE on feature/compliance-fixes (commits after 1cebdfa/d75dfbd). CompetitorEnricher and OccupancyEnricher result dicts, prompt_text, and every downstream consumer updated to area aggregates only -- no restaurant is individually named or attributed a specific price/deal/rating/occupancy figure anywhere in the system. Removed from CompetitorEnricher: 'restaurants' (name list), 'cheapest' (dish -&gt; price+restaurant), raw 'competitor_deals' list, raw 'competitor_landscape' list. Added: area_restaurant_count, deals_active_count, deals_summary, landscape_summary (count/avg_rating/cost_for_two range/offers_count). category_pricing's cheapest_dish/priciest_dish keep the dish name (not restaurant-identifying) but drop which restaurant serves it. Removed from OccupancyEnricher: raw 'competitor_dineout_deals' list -- replaced with dineout_deals_count/dineout_deals_summary. slot_deals_found and slot_availability_by_time were already time-keyed, not restaurant-named, so both were left as-is. _build_prompt() rewritten on both enrichers: 'Market Context' header renamed 'Area Market Signals', 'Competitors checked: {names}' -&gt; a count, named landscape/deals sections replaced with aggregate lines, 'Competitor Dineout Deals Tonight' -&gt; 'Dineout Deals Tonight'. Propagated through every consumer found in a full-codebase audit (26 files referenced the removed fields): market_intel_service.py's _assemble_market_intel/_empty_result, market_intel.py node's dineout_deals_count computation, workflow_trigger_service.py's trigger 2, mcp_server.py's get_market_brief (was iterating named deals -- now shows deals_summary), chat_service.py's three swiggy_get_* chatbot tools (tool descriptions also reworded off 'competitor' framing; swiggy_get_competitor_deals' handler was forwarding raw named lists verbatim to the LLM -- now forwards summaries only), market.py's Pydantic models (removed CompetitorDeal, CompetitorLandscapeEntry, CompetitorDineoutDeal, NamedDish-with-restaurant; added DishPrice, LandscapeSummary; CompetitorPricing/AreaOccupancy fields renamed to match), lib/api.ts's matching TS types, and SwiggyLiveMarketPanel.tsx's three named-data cards (Competitor Swiggy Deals, Competitor Landscape, Dineout Competitor Deals) rebuilt as aggregate cards (Area Deals Tonight, Nearby Market Landscape, Dineout Deals Tonight) plus the restaurants_checked name-pill list replaced with a count. evaluation_sanity.py's Diff 7 already read a count field (dineout_deals_count), not the raw list, so needed no change. Code comments and docs (base_connector.py, provider_registry.py, ARCHITECTURE.md, SWIGGY_INTEGRATION.md from P6-A19) already avoid citing specific legal clauses per the earlier softening decision -- same standard applied here; full compliance detail stays only in CLAUDE.md's dedicated section.</t>
         </is>
       </c>
       <c r="F20" s="74" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="H20" s="71" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I20" s="73" t="inlineStr">
@@ -18519,7 +18519,7 @@
       <c r="K20" s="73" t="n"/>
       <c r="L20" s="73" t="n"/>
       <c r="M20" s="75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="74" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
       </c>
       <c r="O20" s="74" t="inlineStr">
         <is>
-          <t>No restaurant names in enricher outputs; area aggregates correct; market panel shows anonymised data; existing pipeline tests pass</t>
+          <t>VERIFIED: 487 backend tests pass (16 pre-existing tests updated across test_swiggy_competitor_enricher.py, test_competitor_category_pricing.py, test_market_signals_prompt_wiring.py, test_occupancy_enricher_extended.py, test_chat_service_swiggy_dineout_tools.py, test_workflow_trigger_service.py -- old assertions on named-restaurant fields replaced with assertions that those names are ABSENT and the aggregate fields are correct); frontend typechecks clean (npx tsc --noEmit, zero errors) after the panel rewrite. Manually swept the full codebase post-change (grep for the removed field names) and confirmed zero remaining references outside historical/unrelated ones.</t>
         </is>
       </c>
     </row>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -569,7 +569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -944,6 +944,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1272,7 +1284,7 @@
     <row r="3" ht="14.4" customHeight="1" s="90">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Current: Phase 6A (restaurant OS). Phase 6B (guest concierge) starts after 6A syncs to main.</t>
+          <t>Current: Phase 6A (restaurant OS) -- compliance batch DONE (P6-A19, P6-A20). Live-intelligence + scenario overhaul next (P6-A21-A26). Phase 6B (guest concierge) starts after 6A syncs to main.</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -1308,7 +1320,7 @@
     <row r="4" ht="14.4" customHeight="1" s="90">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Phase 6B: guest concierge — 4 tasks before staging creds, 2 blocked, then demo-ready.</t>
+          <t>Phase 6B: guest concierge -- 9 tasks (P6-B1-B9), gated on P6-B1 (Swiggy written consent, clause 2.1v) before any code.</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1344,7 +1356,7 @@
     <row r="5" ht="14.4" customHeight="1" s="90">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Staging creds unlock: Instamart checkout (P6-A32, P6-B08) + Dineout book_table (P6-A33, P6-B07)</t>
+          <t>Staging creds unlock: Instamart checkout (within P6-A27 procurement loop; also P6-B7 Guest Concierge) + Dineout book_table (P6-B5 Guest Concierge).</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1380,7 +1392,7 @@
     <row r="6" ht="14.4" customHeight="1" s="90">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Compliance: P6-A26 (remove Zomato stub) + P6-A25 (anonymise market intel) — do these FIRST</t>
+          <t>Compliance: P6-A19 (remove Zomato stub) + P6-A20 (anonymise market intel) -- DONE, merged to dev.</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -17334,7 +17346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="90" min="1" max="1"/>
@@ -18534,636 +18546,926 @@
     </row>
     <row r="21" ht="7.95" customHeight="1" s="90"/>
     <row r="22" ht="18" customHeight="1" s="90">
-      <c r="A22" s="93" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>RESTAURANT OS — remaining planned tasks (no staging creds needed)</t>
         </is>
       </c>
-      <c r="B22" s="96" t="n"/>
-      <c r="C22" s="96" t="n"/>
-      <c r="D22" s="96" t="n"/>
-      <c r="E22" s="96" t="n"/>
-      <c r="F22" s="96" t="n"/>
-      <c r="G22" s="96" t="n"/>
-      <c r="H22" s="96" t="n"/>
-      <c r="I22" s="96" t="n"/>
-      <c r="J22" s="96" t="n"/>
-      <c r="K22" s="96" t="n"/>
-      <c r="L22" s="96" t="n"/>
-      <c r="M22" s="96" t="n"/>
-      <c r="N22" s="96" t="n"/>
-      <c r="O22" s="97" t="n"/>
     </row>
     <row r="23" ht="52.05" customHeight="1" s="90">
-      <c r="A23" s="117" t="inlineStr">
+      <c r="A23" s="136" t="inlineStr">
         <is>
           <t>P6-A21</t>
         </is>
       </c>
-      <c r="B23" s="77" t="inlineStr">
-        <is>
-          <t>feature/weather-holiday-signals</t>
-        </is>
-      </c>
-      <c r="C23" s="77" t="inlineStr">
+      <c r="B23" s="137" t="inlineStr">
+        <is>
+          <t>feature/live-intelligence-signals</t>
+        </is>
+      </c>
+      <c r="C23" s="137" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D23" s="77" t="inlineStr">
-        <is>
-          <t>Weather + holiday signals in demand forecast</t>
-        </is>
-      </c>
-      <c r="E23" s="77" t="inlineStr">
-        <is>
-          <t>Integrate Open-Meteo API (free, no key needed) for weather forecast at restaurant address. Add Indian holidays list (already in constants.py). Inject both signals into demand_forecast node context: "Rain forecast tomorrow evening: +30% delivery expected, -20% dine-in." "Tomorrow is Diwali: expect 2x normal demand, start prep by 3pm." New OrchestratorState field: weather_signal (temp, condition, rain_probability). ScenarioRecommender uses both signals to suggest correct scenario. Open-Meteo endpoint: https://api.open-meteo.com/v1/forecast (latitude, longitude, hourly=precipitation_probability,temperature_2m)</t>
-        </is>
-      </c>
-      <c r="F23" s="77" t="inlineStr">
-        <is>
-          <t>feat: weather + holiday demand signals — Open-Meteo + Indian holidays in forecast node</t>
-        </is>
-      </c>
-      <c r="G23" s="77" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md (demand_forecast node updated), CLAUDE.md</t>
-        </is>
-      </c>
-      <c r="H23" s="71" t="inlineStr">
+      <c r="D23" s="137" t="inlineStr">
+        <is>
+          <t>Live signal 1/4: Weather + holiday-awareness in demand forecast</t>
+        </is>
+      </c>
+      <c r="E23" s="137" t="inlineStr">
+        <is>
+          <t>First of four independently-failing live-intelligence services feeding the planning pipeline (P6-A24 unifies all four). New WeatherService (infrastructure/external/weather_service.py) calls Open-Meteo (free, no API key) for current + 48h forecast at the restaurant's location -- rain/heat forecasts shift the plan toward delivery-heavy staffing and prep, clear days toward walk-in/outdoor capacity. INDIAN_HOLIDAYS_2026 already exists in core/constants.py and already feeds ScenarioRecommender in the background -- this task surfaces it explicitly into demand_forecast's own prompt too ('today is Gandhi Jayanti -- public holiday, expect elevated demand'), not just the scenario suggestion. Never raises -- returns None on any failure so demand_forecast runs fine without it. New OrchestratorState field: weather_signal.</t>
+        </is>
+      </c>
+      <c r="F23" s="137" t="inlineStr">
+        <is>
+          <t>feat: weather + holiday-awareness signal -- Open-Meteo integration (live signal 1/4)</t>
+        </is>
+      </c>
+      <c r="G23" s="137" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md, docs/ARCHITECTURE.md, CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H23" s="138" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I23" s="76" t="inlineStr">
+      <c r="I23" s="136" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J23" s="76" t="inlineStr">
+      <c r="J23" s="136" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K23" s="76" t="n"/>
-      <c r="L23" s="76" t="n"/>
-      <c r="M23" s="78" t="n">
+      <c r="K23" s="136" t="n"/>
+      <c r="L23" s="136" t="n"/>
+      <c r="M23" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="77" t="n"/>
-      <c r="O23" s="77" t="inlineStr">
-        <is>
-          <t>Weather signal in OrchestratorState; ScenarioRecommender uses it; prompt includes weather context; Open-Meteo call works for Navi Mumbai coords</t>
+      <c r="N23" s="137" t="n"/>
+      <c r="O23" s="137" t="inlineStr">
+        <is>
+          <t>Weather API call returns current+forecast conditions for a known lat/lng and gracefully degrades to None on API failure; holiday lookup correctly identifies a known date against INDIAN_HOLIDAYS_2026; both signals appear in demand_forecast's prompt on a known test date</t>
         </is>
       </c>
     </row>
     <row r="24" ht="52.05" customHeight="1" s="90">
-      <c r="A24" s="117" t="inlineStr">
+      <c r="A24" s="136" t="inlineStr">
         <is>
           <t>P6-A22</t>
         </is>
       </c>
-      <c r="B24" s="74" t="inlineStr">
+      <c r="B24" s="137" t="inlineStr">
+        <is>
+          <t>feature/live-intelligence-signals</t>
+        </is>
+      </c>
+      <c r="C24" s="137" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D24" s="137" t="inlineStr">
+        <is>
+          <t>Live signal 2/4: Industry trends (RSS-only, no paid API)</t>
+        </is>
+      </c>
+      <c r="E24" s="137" t="inlineStr">
+        <is>
+          <t>Second live-intelligence service. New TrendsService -- a curated list of Indian F&amp;B/hospitality trade-press RSS feeds, fetched via feedparser (new free/open-source dependency) and summarized into a short 'what's trending' digest using the existing Groq LLM client (no new LLM integration needed). RSS-only deliberately, not Google Trends/pytrends -- pytrends scrapes Google's internal endpoint, a ToS gray area we chose to avoid given how carefully we've treated Swiggy's terms; RSS is meant for syndication, zero ToS risk. Independently fail-open: if all feeds are unreachable, returns None and does not block weather/compliance/Swiggy signals. New OrchestratorState field: trends_signal.</t>
+        </is>
+      </c>
+      <c r="F24" s="137" t="inlineStr">
+        <is>
+          <t>feat: industry trends signal -- curated RSS feeds only, no paid API (live signal 2/4)</t>
+        </is>
+      </c>
+      <c r="G24" s="137" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md, docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H24" s="138" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I24" s="136" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J24" s="136" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K24" s="136" t="n"/>
+      <c r="L24" s="136" t="n"/>
+      <c r="M24" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="137" t="n"/>
+      <c r="O24" s="137" t="inlineStr">
+        <is>
+          <t>RSS fetch+parse works against a known feed in a live test; degrades to None if all feeds are unreachable (simulated); LLM produces a coherent digest from real feed content</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52.05" customHeight="1" s="90">
+      <c r="A25" s="136" t="inlineStr">
+        <is>
+          <t>P6-A23</t>
+        </is>
+      </c>
+      <c r="B25" s="137" t="inlineStr">
+        <is>
+          <t>feature/live-intelligence-signals</t>
+        </is>
+      </c>
+      <c r="C25" s="137" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D25" s="137" t="inlineStr">
+        <is>
+          <t>Live signal 3/4: Regulatory/compliance alerts (FSSAI public notices)</t>
+        </is>
+      </c>
+      <c r="E25" s="137" t="inlineStr">
+        <is>
+          <t>Third live-intelligence service. New ComplianceAlertsService scrapes FSSAI's public notifications page (fssai.gov.in/notifications.php) via beautifulsoup4 (new dependency) -- confirmed live (2026-07-11) this page has no RSS feed, is plain server-side-rendered HTML (not JS-dependent), so a lightweight parser is sufficient without a headless browser. Public government regulatory data, no ToS tension of any kind -- cleanest source of the four on that front. Explicit fail-open contract given HTML scraping is inherently more fragile than RSS (any FSSAI site redesign breaks the parser) -- must degrade to None cleanly, never raise, never block the other three signals. New OrchestratorState field: compliance_alerts_signal.</t>
+        </is>
+      </c>
+      <c r="F25" s="137" t="inlineStr">
+        <is>
+          <t>feat: regulatory/compliance alerts signal -- FSSAI public notices scrape (live signal 3/4)</t>
+        </is>
+      </c>
+      <c r="G25" s="137" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md, docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="H25" s="138" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I25" s="136" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J25" s="136" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K25" s="136" t="n"/>
+      <c r="L25" s="136" t="n"/>
+      <c r="M25" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="137" t="n"/>
+      <c r="O25" s="137" t="inlineStr">
+        <is>
+          <t>Scrape returns real recent notices in a live test; degrades to None on parse failure (simulate an unexpected page structure); no crash on an empty result set</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52.05" customHeight="1" s="90">
+      <c r="A26" s="136" t="inlineStr">
+        <is>
+          <t>P6-A24</t>
+        </is>
+      </c>
+      <c r="B26" s="137" t="inlineStr">
+        <is>
+          <t>feature/live-intelligence-signals</t>
+        </is>
+      </c>
+      <c r="C26" s="137" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D26" s="137" t="inlineStr">
+        <is>
+          <t>Live signal 4/4: Wire all live signals into the planning pipeline (unify)</t>
+        </is>
+      </c>
+      <c r="E26" s="137" t="inlineStr">
+        <is>
+          <t>Merges weather/holiday (P6-A21) + industry trends (P6-A22) + compliance alerts (P6-A23) + the existing anonymised Swiggy area signals (P6-A20) into one combined 'Area &amp; Live Signals' section. Added INSIDE the existing market_intel_node / MarketIntelService rather than a new 12th LangGraph node -- MarketIntelService already runs multiple enrichers concurrently and fails open per-enricher, so this is additive to a proven pattern, not a new one. Critically, this preserves the existing state field names (swiggy_competitor_context, swiggy_occupancy_context, market_intel_output) that 5+ files and the frontend already read by name -- confirmed via audit that renaming them would be a wide, unnecessary blast radius. No frontend SSE changes needed since the node count doesn't change. Injected into demand_forecast, menu_intelligence, and the critic's prompt via aggregator.py's _build_critic_summary. Each of the 4 sources stays independently fail-open all the way through -- one going down never blocks the others or crashes the node.</t>
+        </is>
+      </c>
+      <c r="F26" s="137" t="inlineStr">
+        <is>
+          <t>feat: wire live signals into planning pipeline -- unified Area &amp; Live Signals section</t>
+        </is>
+      </c>
+      <c r="G26" s="137" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md, docs/ARCHITECTURE.md, CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H26" s="138" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I26" s="136" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J26" s="136" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K26" s="136" t="n"/>
+      <c r="L26" s="136" t="n"/>
+      <c r="M26" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="137" t="inlineStr">
+        <is>
+          <t>P6-A21, P6-A22, P6-A23</t>
+        </is>
+      </c>
+      <c r="O26" s="137" t="inlineStr">
+        <is>
+          <t>demand_forecast/menu_intelligence/critic prompts include all present sources; simulated failure of any one source doesn't block the others or crash the node; aggregator's critic summary includes a live-signals section; existing Swiggy state field names unchanged, all P6-A19/A20 tests still pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="52.05" customHeight="1" s="90">
+      <c r="A27" s="136" t="inlineStr">
+        <is>
+          <t>P6-A25</t>
+        </is>
+      </c>
+      <c r="B27" s="137" t="inlineStr">
+        <is>
+          <t>feature/live-intelligence-signals</t>
+        </is>
+      </c>
+      <c r="C27" s="137" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D27" s="137" t="inlineStr">
+        <is>
+          <t>Scenario selection overhaul -- natural language + dynamic profiles</t>
+        </is>
+      </c>
+      <c r="E27" s="137" t="inlineStr">
+        <is>
+          <t>Confirmed via audit: all 4 scenarios (friday_rush/weekday_lunch/holiday_spike/low_stock_weekend) are hardcoded end-to-end -- a Pydantic Literal type in PlanningRunRequest, ops_manager_node rejects anything else, and the frontend has the same 4-item array duplicated in dashboard/page.tsx AND TodayIdleState.tsx. demand_forecast doesn't actually branch its algorithm on scenario today -- Prophet runs identically regardless, scenario only affects labeling and target_date. This task: relax PlanningScenarioId off the hardcoded Literal to accept a custom profile payload. New service turns free-form natural language ('we're hosting an event today, expecting large turnover') into an ad-hoc scenario_profile dict (label/service_window/operational_focus, LLM-derived) -- the 4 existing presets remain as one-click shortcuts, NOT replaced (explicit product decision). ops_manager_node's SUPPORTED_SCENARIOS check updated to admit custom profiles alongside the presets. Frontend: dedupe the two duplicated SCENARIO_OPTIONS arrays into one shared source; add a natural-language text input alongside the existing tile picker in PlanShiftModal.tsx -- user's choice of either mode, not a replacement of the tiles.</t>
+        </is>
+      </c>
+      <c r="F27" s="137" t="inlineStr">
+        <is>
+          <t>feat: scenario selection overhaul -- natural-language intake + dynamic profiles alongside presets</t>
+        </is>
+      </c>
+      <c r="G27" s="137" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md, docs/ARCHITECTURE.md, docs/PRODUCT_MODES.md, CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H27" s="138" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I27" s="136" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J27" s="136" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K27" s="136" t="n"/>
+      <c r="L27" s="136" t="n"/>
+      <c r="M27" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="137" t="n"/>
+      <c r="O27" s="137" t="inlineStr">
+        <is>
+          <t>Natural-language input produces a valid scenario_profile dict with sensible defaults for missing fields; existing 4 presets still work completely unchanged; ops_manager_node accepts a custom profile without rejecting it; frontend offers both input modes; SCENARIO_OPTIONS no longer duplicated across two files</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52.05" customHeight="1" s="90">
+      <c r="A28" s="136" t="inlineStr">
+        <is>
+          <t>P6-A26</t>
+        </is>
+      </c>
+      <c r="B28" s="137" t="inlineStr">
+        <is>
+          <t>feature/live-intelligence-signals</t>
+        </is>
+      </c>
+      <c r="C28" s="137" t="inlineStr">
+        <is>
+          <t>Eval</t>
+        </is>
+      </c>
+      <c r="D28" s="137" t="inlineStr">
+        <is>
+          <t>Validate action-item specificity after live signals land (conditional)</t>
+        </is>
+      </c>
+      <c r="E28" s="137" t="inlineStr">
+        <is>
+          <t>Not a guaranteed code task -- a validation checkpoint. Research confirmed aggregator.py/critic_service.py already favor structured, itemized output (bulleted restock actions, explicit dish names, numeric thresholds, dimension scores) over narrative paragraphs, so the 'standard, generic response' feedback is more likely an input-richness problem than a prompt-engineering problem. After P6-A24 ships, manually review 3-5 generated plans against known-rich live-signal test dates (a rain-forecast night, a real upcoming holiday, an active trend, a live FSSAI notice) to check whether output is now sufficiently specific/actionable. If yes: close this task, no further work needed. If still generic: scope a real follow-up prompt-engineering task against aggregator/critic with concrete before/after examples.</t>
+        </is>
+      </c>
+      <c r="F28" s="137" t="inlineStr">
+        <is>
+          <t>None yet -- validation checkpoint, code only if the review finds a real gap</t>
+        </is>
+      </c>
+      <c r="G28" s="137" t="inlineStr">
+        <is>
+          <t>None yet</t>
+        </is>
+      </c>
+      <c r="H28" s="138" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I28" s="136" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J28" s="136" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K28" s="136" t="n"/>
+      <c r="L28" s="136" t="n"/>
+      <c r="M28" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="137" t="inlineStr">
+        <is>
+          <t>P6-A24</t>
+        </is>
+      </c>
+      <c r="O28" s="137" t="inlineStr">
+        <is>
+          <t>N/A -- manual review checkpoint, not an automated test</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52.05" customHeight="1" s="90">
+      <c r="A29" s="136" t="inlineStr">
+        <is>
+          <t>P6-A27</t>
+        </is>
+      </c>
+      <c r="B29" s="137" t="inlineStr">
         <is>
           <t>feature/procurement-loop-endtoend</t>
         </is>
       </c>
-      <c r="C24" s="74" t="inlineStr">
+      <c r="C29" s="137" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D24" s="74" t="inlineStr">
+      <c r="D29" s="137" t="inlineStr">
         <is>
           <t>Autonomous procurement loop — end-to-end wire</t>
         </is>
       </c>
-      <c r="E24" s="74" t="inlineStr">
+      <c r="E29" s="137" t="inlineStr">
         <is>
           <t>Connect: weather/holiday signal → demand_forecast surge → inventory shortage detection → ProcurementEnricher Instamart prices → ActionQueue APPROVE_REQUIRED action → trust ladder → checkout (staging creds) OR WhatsApp vendor fallback. This is the flagship restaurant OS demo moment. The plan output must clearly show: shortage detected → Instamart has it at Rs.24/kg → approve to order → or WhatsApp vendor if not on Instamart. Wire trust ladder: orders under Rs.500 auto-approved, over Rs.500 needs manual approval in action queue UI.</t>
         </is>
       </c>
-      <c r="F24" s="74" t="inlineStr">
+      <c r="F29" s="137" t="inlineStr">
         <is>
           <t>feat: autonomous procurement loop — weather → forecast → shortage → Instamart → action queue</t>
         </is>
       </c>
-      <c r="G24" s="74" t="inlineStr">
+      <c r="G29" s="137" t="inlineStr">
         <is>
           <t>CLAUDE.md, docs/ARCHITECTURE.md (procurement loop diagram)</t>
         </is>
       </c>
-      <c r="H24" s="71" t="inlineStr">
+      <c r="H29" s="138" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I24" s="73" t="inlineStr">
+      <c r="I29" s="136" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J24" s="73" t="inlineStr">
+      <c r="J29" s="136" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K24" s="73" t="n"/>
-      <c r="L24" s="73" t="n"/>
-      <c r="M24" s="75" t="n">
+      <c r="K29" s="136" t="n"/>
+      <c r="L29" s="136" t="n"/>
+      <c r="M29" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="74" t="inlineStr">
-        <is>
-          <t>P6-A21</t>
-        </is>
-      </c>
-      <c r="O24" s="74" t="inlineStr">
+      <c r="N29" s="137" t="inlineStr">
+        <is>
+          <t>P6-A24</t>
+        </is>
+      </c>
+      <c r="O29" s="137" t="inlineStr">
         <is>
           <t>Full loop runs end-to-end in demo; trust ladder fires correctly; action queue shows Instamart procurement with price + spinId; WhatsApp fallback triggers when product not found on Instamart</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="52.05" customHeight="1" s="90">
-      <c r="A25" s="117" t="inlineStr">
-        <is>
-          <t>P6-A23</t>
-        </is>
-      </c>
-      <c r="B25" s="77" t="inlineStr">
+    <row r="30" ht="63" customHeight="1" s="90">
+      <c r="A30" s="136" t="inlineStr">
+        <is>
+          <t>P6-A28</t>
+        </is>
+      </c>
+      <c r="B30" s="137" t="inlineStr">
         <is>
           <t>feature/instamart-event-supplies</t>
         </is>
       </c>
-      <c r="C25" s="77" t="inlineStr">
+      <c r="C30" s="137" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D25" s="77" t="inlineStr">
+      <c r="D30" s="137" t="inlineStr">
         <is>
           <t>Instamart event supplies in operator chatbot</t>
         </is>
       </c>
-      <c r="E25" s="77" t="inlineStr">
+      <c r="E30" s="137" t="inlineStr">
         <is>
           <t>Extend operator chatbot with event supplies tool: "we are hosting a birthday event tonight, need supplies." Calls search_products for non-food items: candles, paper plates, cups, napkins, soft drinks, basic decorations, cleaning supplies, batteries. Returns real Instamart prices and availability. Creates ActionQueue procurement action for approval. Key insight: Instamart is not just food ingredients — managers use it for quick supply runs that previously required leaving the restaurant. New chatbot tool: get_event_supplies(event_type, headcount)</t>
         </is>
       </c>
-      <c r="F25" s="77" t="inlineStr">
+      <c r="F30" s="137" t="inlineStr">
         <is>
           <t>feat: Instamart event supplies tool in operator chatbot</t>
         </is>
       </c>
-      <c r="G25" s="77" t="inlineStr">
+      <c r="G30" s="137" t="inlineStr">
         <is>
           <t>docs/AGENTS.md (chatbot tools updated)</t>
         </is>
       </c>
-      <c r="H25" s="71" t="inlineStr">
+      <c r="H30" s="138" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I25" s="76" t="inlineStr">
+      <c r="I30" s="136" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J25" s="76" t="inlineStr">
+      <c r="J30" s="136" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K25" s="76" t="n"/>
-      <c r="L25" s="76" t="n"/>
-      <c r="M25" s="78" t="n">
+      <c r="K30" s="136" t="n"/>
+      <c r="L30" s="136" t="n"/>
+      <c r="M30" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="77" t="n"/>
-      <c r="O25" s="77" t="inlineStr">
+      <c r="N30" s="137" t="n"/>
+      <c r="O30" s="137" t="inlineStr">
         <is>
           <t>search_products returns real results for non-food queries; ActionQueue action created; trust ladder applied; chatbot responds naturally to event supply requests</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="52.05" customHeight="1" s="90">
-      <c r="A26" s="117" t="inlineStr">
-        <is>
-          <t>P6-A24</t>
-        </is>
-      </c>
-      <c r="B26" s="74" t="inlineStr">
+    <row r="31" ht="18" customHeight="1" s="90">
+      <c r="A31" s="139" t="inlineStr">
+        <is>
+          <t>P6-A29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>feature/menu-engineering-matrix</t>
         </is>
       </c>
-      <c r="C26" s="74" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D26" s="74" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Menu engineering matrix UI</t>
         </is>
       </c>
-      <c r="E26" s="74" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Visual matrix: dish margin (y-axis) vs order popularity (x-axis). Four quadrants: Stars (high margin + high orders — promote), Plowhorses (low margin + high orders — reprice or remove), Puzzles (high margin + low orders — market better), Dogs (low margin + low orders — remove). Data from BusinessAnalyticsService (already has margin + popularity). Interactive: click a dish to see full margin breakdown. Shown on /operations page as a new panel. Connects to planning: critic uses quadrant data to validate menu recommendations.</t>
         </is>
       </c>
-      <c r="F26" s="74" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>feat: menu engineering matrix — margin vs popularity quadrant chart</t>
         </is>
       </c>
-      <c r="G26" s="74" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>None (frontend only)</t>
         </is>
       </c>
-      <c r="H26" s="71" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I26" s="73" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J26" s="73" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K26" s="73" t="n"/>
-      <c r="L26" s="73" t="n"/>
-      <c r="M26" s="75" t="n">
+      <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="74" t="n"/>
-      <c r="O26" s="74" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Matrix renders with correct quadrant assignment; click through shows dish margin detail; Stars/Plowhorses/Puzzles/Dogs correctly classified</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="52.05" customHeight="1" s="90">
-      <c r="A27" s="117" t="inlineStr">
-        <is>
-          <t>P6-A25</t>
-        </is>
-      </c>
-      <c r="B27" s="77" t="inlineStr">
+    <row r="32" ht="52.05" customHeight="1" s="90">
+      <c r="A32" s="136" t="inlineStr">
+        <is>
+          <t>P6-A30</t>
+        </is>
+      </c>
+      <c r="B32" s="137" t="inlineStr">
         <is>
           <t>feature/structured-outputs</t>
         </is>
       </c>
-      <c r="C27" s="77" t="inlineStr">
+      <c r="C32" s="137" t="inlineStr">
         <is>
           <t>Agents</t>
         </is>
       </c>
-      <c r="D27" s="77" t="inlineStr">
+      <c r="D32" s="137" t="inlineStr">
         <is>
           <t>Structured outputs — tool_choice=required across chatbot</t>
         </is>
       </c>
-      <c r="E27" s="77" t="inlineStr">
+      <c r="E32" s="137" t="inlineStr">
         <is>
           <t>Force structured JSON outputs from Groq function calling. Eliminates cases where chatbot returns freeform text instead of calling the right tool. Add response validation layer. Makes chatbot more reliable for demo — no unexpected text responses.</t>
         </is>
       </c>
-      <c r="F27" s="77" t="inlineStr">
+      <c r="F32" s="137" t="inlineStr">
         <is>
           <t>feat: structured outputs — force tool_choice=required in chatbot</t>
         </is>
       </c>
-      <c r="G27" s="77" t="inlineStr">
+      <c r="G32" s="137" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H27" s="71" t="inlineStr">
+      <c r="H32" s="138" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I27" s="76" t="inlineStr">
+      <c r="I32" s="136" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J27" s="76" t="inlineStr">
+      <c r="J32" s="136" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K27" s="76" t="n"/>
-      <c r="L27" s="76" t="n"/>
-      <c r="M27" s="78" t="n">
+      <c r="K32" s="136" t="n"/>
+      <c r="L32" s="136" t="n"/>
+      <c r="M32" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N27" s="77" t="n"/>
-      <c r="O27" s="77" t="inlineStr">
+      <c r="N32" s="137" t="n"/>
+      <c r="O32" s="137" t="inlineStr">
         <is>
           <t>Chatbot always calls a tool when one applies; no unexpected freeform responses; existing chatbot tests pass</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="52.05" customHeight="1" s="90">
-      <c r="A28" s="117" t="inlineStr">
-        <is>
-          <t>P6-A26</t>
-        </is>
-      </c>
-      <c r="B28" s="74" t="inlineStr">
+    <row r="33" ht="52.05" customHeight="1" s="90">
+      <c r="A33" s="136" t="inlineStr">
+        <is>
+          <t>P6-A31</t>
+        </is>
+      </c>
+      <c r="B33" s="137" t="inlineStr">
         <is>
           <t>feature/voice-interface</t>
         </is>
       </c>
-      <c r="C28" s="74" t="inlineStr">
+      <c r="C33" s="137" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D28" s="74" t="inlineStr">
+      <c r="D33" s="137" t="inlineStr">
         <is>
           <t>Voice interface — Whisper transcription + TTS response</t>
         </is>
       </c>
-      <c r="E28" s="74" t="inlineStr">
+      <c r="E33" s="137" t="inlineStr">
         <is>
           <t>Restaurant operator speaks to CortexKitchen instead of typing. Browser MediaRecorder API captures audio. Whisper (via Groq) transcribes to text. Existing chatbot processes the text query. TTS reads back the response. Use case: manager walking the floor asks questions hands-free. "What does the plan say about staffing tonight?" "How many covers are we expecting?" Add mic button to existing /chat page. Works for operator side only initially.</t>
         </is>
       </c>
-      <c r="F28" s="74" t="inlineStr">
+      <c r="F33" s="137" t="inlineStr">
         <is>
           <t>feat: voice interface — Whisper transcription + TTS on /chat page</t>
         </is>
       </c>
-      <c r="G28" s="74" t="inlineStr">
+      <c r="G33" s="137" t="inlineStr">
         <is>
           <t>docs/PRODUCT_MODES.md (voice mode section)</t>
         </is>
       </c>
-      <c r="H28" s="71" t="inlineStr">
+      <c r="H33" s="138" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I28" s="73" t="inlineStr">
+      <c r="I33" s="136" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J28" s="73" t="inlineStr">
+      <c r="J33" s="136" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K28" s="73" t="n"/>
-      <c r="L28" s="73" t="n"/>
-      <c r="M28" s="75" t="n">
+      <c r="K33" s="136" t="n"/>
+      <c r="L33" s="136" t="n"/>
+      <c r="M33" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N28" s="74" t="n"/>
-      <c r="O28" s="74" t="inlineStr">
+      <c r="N33" s="137" t="n"/>
+      <c r="O33" s="137" t="inlineStr">
         <is>
           <t>Audio recorded and transcribed correctly; chatbot processes transcription; TTS plays response; mic button shows recording state</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="52.05" customHeight="1" s="90">
-      <c r="A29" s="117" t="inlineStr">
+    <row r="34" ht="7.95" customHeight="1" s="90">
+      <c r="A34" s="136" t="inlineStr">
+        <is>
+          <t>P6-A32</t>
+        </is>
+      </c>
+      <c r="B34" s="137" t="inlineStr">
+        <is>
+          <t>feature/eval-pipeline</t>
+        </is>
+      </c>
+      <c r="C34" s="137" t="inlineStr">
+        <is>
+          <t>Eval</t>
+        </is>
+      </c>
+      <c r="D34" s="137" t="inlineStr">
+        <is>
+          <t>Promote RAGAS/DeepEval candidates + regenerate golden runs</t>
+        </is>
+      </c>
+      <c r="E34" s="137" t="inlineStr">
+        <is>
+          <t>Review RAGAS and DeepEval eval candidates. Promote passing ones to the CI gate. Regenerate golden_runs.json against real planning data. Ensures eval pipeline catches regressions after compliance changes and new feature additions.</t>
+        </is>
+      </c>
+      <c r="F34" s="137" t="inlineStr">
+        <is>
+          <t>feat: eval pipeline — promote RAGAS/DeepEval + regenerate golden runs</t>
+        </is>
+      </c>
+      <c r="G34" s="137" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H34" s="138" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I34" s="136" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J34" s="136" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K34" s="136" t="n"/>
+      <c r="L34" s="136" t="n"/>
+      <c r="M34" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="137" t="inlineStr">
         <is>
           <t>P6-A27</t>
         </is>
       </c>
-      <c r="B29" s="77" t="inlineStr">
-        <is>
-          <t>feature/eval-pipeline</t>
-        </is>
-      </c>
-      <c r="C29" s="77" t="inlineStr">
-        <is>
-          <t>Eval</t>
-        </is>
-      </c>
-      <c r="D29" s="77" t="inlineStr">
-        <is>
-          <t>Promote RAGAS/DeepEval candidates + regenerate golden runs</t>
-        </is>
-      </c>
-      <c r="E29" s="77" t="inlineStr">
-        <is>
-          <t>Review RAGAS and DeepEval eval candidates. Promote passing ones to the CI gate. Regenerate golden_runs.json against real planning data. Ensures eval pipeline catches regressions after compliance changes and new feature additions.</t>
-        </is>
-      </c>
-      <c r="F29" s="77" t="inlineStr">
-        <is>
-          <t>feat: eval pipeline — promote RAGAS/DeepEval + regenerate golden runs</t>
-        </is>
-      </c>
-      <c r="G29" s="77" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H29" s="71" t="inlineStr">
+      <c r="O34" s="137" t="inlineStr">
+        <is>
+          <t>CI eval gate passes; golden_runs.json reflects current system; regressions caught in 2+ test scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DOCS + SYNC — end of Phase 6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="136" t="inlineStr">
+        <is>
+          <t>P6-A33</t>
+        </is>
+      </c>
+      <c r="B37" s="137" t="inlineStr">
+        <is>
+          <t>feature/documentation</t>
+        </is>
+      </c>
+      <c r="C37" s="137" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D37" s="137" t="inlineStr">
+        <is>
+          <t>Whole-system documentation + screenshots refresh</t>
+        </is>
+      </c>
+      <c r="E37" s="137" t="inlineStr">
+        <is>
+          <t>Update all docs to reflect: new two-sided product vision, compliance changes (Zomato removed, market intel anonymised), autonomous procurement loop, weather signals, voice interface. New product vision statement in README. Screenshots of the operator portal (dashboard, operations, market, action queue, chat) for portfolio -- Guest Concierge screenshots belong to Phase 6B docs (P6-B9), not here, since Guest Concierge does not exist yet at this point.</t>
+        </is>
+      </c>
+      <c r="F37" s="137" t="inlineStr">
+        <is>
+          <t>docs: whole-system documentation refresh — new product vision</t>
+        </is>
+      </c>
+      <c r="G37" s="137" t="inlineStr">
+        <is>
+          <t>README.md, docs/ARCHITECTURE.md, docs/AGENTS.md, CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H37" s="138" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I29" s="76" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J29" s="76" t="inlineStr">
+      <c r="I37" s="136" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J37" s="136" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K29" s="76" t="n"/>
-      <c r="L29" s="76" t="n"/>
-      <c r="M29" s="78" t="n">
+      <c r="K37" s="136" t="n"/>
+      <c r="L37" s="136" t="n"/>
+      <c r="M37" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="77" t="inlineStr">
-        <is>
-          <t>P6-A22</t>
-        </is>
-      </c>
-      <c r="O29" s="77" t="inlineStr">
-        <is>
-          <t>CI eval gate passes; golden_runs.json reflects current system; regressions caught in 2+ test scenarios</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="63" customHeight="1" s="90"/>
-    <row r="31" ht="18" customHeight="1" s="90">
-      <c r="A31" s="118" t="inlineStr">
-        <is>
-          <t>DOCS + SYNC — end of Phase 6A</t>
-        </is>
-      </c>
-      <c r="B31" s="131" t="n"/>
-      <c r="C31" s="131" t="n"/>
-      <c r="D31" s="131" t="n"/>
-      <c r="E31" s="131" t="n"/>
-      <c r="F31" s="131" t="n"/>
-      <c r="G31" s="131" t="n"/>
-      <c r="H31" s="131" t="n"/>
-      <c r="I31" s="131" t="n"/>
-      <c r="J31" s="131" t="n"/>
-      <c r="K31" s="131" t="n"/>
-      <c r="L31" s="131" t="n"/>
-      <c r="M31" s="131" t="n"/>
-      <c r="N31" s="131" t="n"/>
-      <c r="O31" s="131" t="n"/>
-    </row>
-    <row r="32" ht="52.05" customHeight="1" s="90">
-      <c r="A32" s="120" t="inlineStr">
-        <is>
-          <t>P6-A28</t>
-        </is>
-      </c>
-      <c r="B32" s="81" t="inlineStr">
-        <is>
-          <t>feature/documentation</t>
-        </is>
-      </c>
-      <c r="C32" s="81" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="D32" s="81" t="inlineStr">
-        <is>
-          <t>Whole-system documentation + screenshots refresh</t>
-        </is>
-      </c>
-      <c r="E32" s="81" t="inlineStr">
-        <is>
-          <t>Update all docs to reflect: new two-sided product vision, compliance changes (Zomato removed, market intel anonymised), autonomous procurement loop, weather signals, voice interface. New product vision statement in README. Screenshots of the operator portal (dashboard, operations, market, action queue, chat) for portfolio -- Guest Concierge screenshots belong to Phase 6B docs (P6-B9), not here, since Guest Concierge does not exist yet at this point.</t>
-        </is>
-      </c>
-      <c r="F32" s="81" t="inlineStr">
-        <is>
-          <t>docs: whole-system documentation refresh — new product vision</t>
-        </is>
-      </c>
-      <c r="G32" s="81" t="inlineStr">
-        <is>
-          <t>README.md, docs/ARCHITECTURE.md, docs/AGENTS.md, CLAUDE.md</t>
-        </is>
-      </c>
-      <c r="H32" s="71" t="inlineStr">
+      <c r="N37" s="137" t="inlineStr">
+        <is>
+          <t>P6-A32</t>
+        </is>
+      </c>
+      <c r="O37" s="137" t="inlineStr">
+        <is>
+          <t>README reflects two-sided platform; all compliance changes documented; screenshots current</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="136" t="inlineStr">
+        <is>
+          <t>P6-A34</t>
+        </is>
+      </c>
+      <c r="B38" s="137" t="inlineStr">
+        <is>
+          <t>dev -&gt; main</t>
+        </is>
+      </c>
+      <c r="C38" s="137" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="D38" s="137" t="inlineStr">
+        <is>
+          <t>Sync Phase 6A to main</t>
+        </is>
+      </c>
+      <c r="E38" s="137" t="inlineStr">
+        <is>
+          <t>Merge dev → main. All compliance fixes confirmed. Autonomous procurement loop working (minus checkout — staging creds). Restaurant OS demo-ready. Phase 6B starts after this.</t>
+        </is>
+      </c>
+      <c r="F38" s="137" t="inlineStr">
+        <is>
+          <t>release: Phase 6A complete — restaurant OS + compliance fixes</t>
+        </is>
+      </c>
+      <c r="G38" s="137" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="H38" s="138" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I32" s="80" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J32" s="80" t="inlineStr">
+      <c r="I38" s="136" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J38" s="136" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K32" s="80" t="n"/>
-      <c r="L32" s="80" t="n"/>
-      <c r="M32" s="82" t="n">
+      <c r="K38" s="136" t="n"/>
+      <c r="L38" s="136" t="n"/>
+      <c r="M38" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="81" t="inlineStr">
-        <is>
-          <t>P6-A27</t>
-        </is>
-      </c>
-      <c r="O32" s="81" t="inlineStr">
-        <is>
-          <t>README reflects two-sided platform; all compliance changes documented; screenshots current</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="52.05" customHeight="1" s="90">
-      <c r="A33" s="116" t="inlineStr">
-        <is>
-          <t>P6-A29</t>
-        </is>
-      </c>
-      <c r="B33" s="74" t="inlineStr">
-        <is>
-          <t>dev -&gt; main</t>
-        </is>
-      </c>
-      <c r="C33" s="74" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="D33" s="74" t="inlineStr">
-        <is>
-          <t>Sync Phase 6A to main</t>
-        </is>
-      </c>
-      <c r="E33" s="74" t="inlineStr">
-        <is>
-          <t>Merge dev → main. All compliance fixes confirmed. Autonomous procurement loop working (minus checkout — staging creds). Restaurant OS demo-ready. Phase 6B starts after this.</t>
-        </is>
-      </c>
-      <c r="F33" s="74" t="inlineStr">
-        <is>
-          <t>release: Phase 6A complete — restaurant OS + compliance fixes</t>
-        </is>
-      </c>
-      <c r="G33" s="74" t="inlineStr">
-        <is>
-          <t>README.md</t>
-        </is>
-      </c>
-      <c r="H33" s="71" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="I33" s="73" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J33" s="73" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="K33" s="73" t="n"/>
-      <c r="L33" s="73" t="n"/>
-      <c r="M33" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="74" t="inlineStr">
-        <is>
-          <t>P6-A28</t>
-        </is>
-      </c>
-      <c r="O33" s="74" t="inlineStr">
+      <c r="N38" s="137" t="inlineStr">
+        <is>
+          <t>P6-A33</t>
+        </is>
+      </c>
+      <c r="O38" s="137" t="inlineStr">
         <is>
           <t>Full test suite green; compliance fixes verified; no Zomato references; market intel anonymised; demo flow works</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="7.95" customHeight="1" s="90"/>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A36:O36"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A31:O31"/>
     <mergeCell ref="A22:O22"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="A3:O3"/>
@@ -19688,7 +19990,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>search_products for decorations, cake, drinks, party supplies matching the event brief -- same tool pattern as the Restaurant OS operator-facing get_event_supplies (P6-A23), but consumer-facing and for the guest's own event rather than restaurant procurement. Cart/checkout once creds land.</t>
+          <t>search_products for decorations, cake, drinks, party supplies matching the event brief -- same tool pattern as the Restaurant OS operator-facing get_event_supplies (P6-A28), but consumer-facing and for the guest's own event rather than restaurant procurement. Cart/checkout once creds land.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -20398,7 +20700,7 @@
       </c>
       <c r="N14" s="59" t="inlineStr">
         <is>
-          <t>P6-A22</t>
+          <t>P6-A31</t>
         </is>
       </c>
       <c r="O14" s="59" t="inlineStr">
@@ -22056,7 +22358,7 @@
       </c>
       <c r="E63" s="59" t="inlineStr">
         <is>
-          <t>Audit test coverage for every new service/model added in Phase 6A (Action Queue, workflow triggers, trust-ladder, WhatsApp vendor flow, Vendor/Supplier model, Menu Engineering Matrix) -- confirm nothing shipped without tests. Re-check the CI pipeline includes all new test files. Re-run/expand RAGAS + DeepEval evals to cover the new agentic behaviors (workflow-triggered actions, trust-ladder promotions), since the existing eval sets predate all of this and won't catch regressions in it. (Docs + screenshots refresh is P6-A23, done before the demo video; this is the deeper test/CI/eval hygiene pass that doesn't need to block the video.)</t>
+          <t>Audit test coverage for every new service/model added in Phase 6A (Action Queue, workflow triggers, trust-ladder, WhatsApp vendor flow, Vendor/Supplier model, Menu Engineering Matrix) -- confirm nothing shipped without tests. Re-check the CI pipeline includes all new test files. Re-run/expand RAGAS + DeepEval evals to cover the new agentic behaviors (workflow-triggered actions, trust-ladder promotions), since the existing eval sets predate all of this and won't catch regressions in it. (Docs + screenshots refresh is P6-A33, done before the demo video; this is the deeper test/CI/eval hygiene pass that doesn't need to block the video.)</t>
         </is>
       </c>
       <c r="F63" s="59" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -569,7 +569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -956,6 +956,7 @@
     <xf numFmtId="0" fontId="27" fillId="25" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1356,7 +1357,7 @@
     <row r="5" ht="14.4" customHeight="1" s="90">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Staging creds unlock: Instamart checkout (within P6-A27 procurement loop; also P6-B7 Guest Concierge) + Dineout book_table (P6-B5 Guest Concierge).</t>
+          <t>Staging creds unlock: Instamart checkout (within P6-A30 procurement loop; also P6-B7 Guest Concierge) + Dineout book_table (P6-B5 Guest Concierge).</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -17346,7 +17347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="90" min="1" max="1"/>
@@ -18546,7 +18547,7 @@
     </row>
     <row r="21" ht="7.95" customHeight="1" s="90"/>
     <row r="22" ht="18" customHeight="1" s="90">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="140" t="inlineStr">
         <is>
           <t>RESTAURANT OS — remaining planned tasks (no staging creds needed)</t>
         </is>
@@ -18831,7 +18832,7 @@
       </c>
       <c r="E27" s="137" t="inlineStr">
         <is>
-          <t>Confirmed via audit: all 4 scenarios (friday_rush/weekday_lunch/holiday_spike/low_stock_weekend) are hardcoded end-to-end -- a Pydantic Literal type in PlanningRunRequest, ops_manager_node rejects anything else, and the frontend has the same 4-item array duplicated in dashboard/page.tsx AND TodayIdleState.tsx. demand_forecast doesn't actually branch its algorithm on scenario today -- Prophet runs identically regardless, scenario only affects labeling and target_date. This task: relax PlanningScenarioId off the hardcoded Literal to accept a custom profile payload. New service turns free-form natural language ('we're hosting an event today, expecting large turnover') into an ad-hoc scenario_profile dict (label/service_window/operational_focus, LLM-derived) -- the 4 existing presets remain as one-click shortcuts, NOT replaced (explicit product decision). ops_manager_node's SUPPORTED_SCENARIOS check updated to admit custom profiles alongside the presets. Frontend: dedupe the two duplicated SCENARIO_OPTIONS arrays into one shared source; add a natural-language text input alongside the existing tile picker in PlanShiftModal.tsx -- user's choice of either mode, not a replacement of the tiles.</t>
+          <t>Confirmed via audit: all 4 scenarios (friday_rush/weekday_lunch/holiday_spike/low_stock_weekend) are hardcoded end-to-end -- a Pydantic Literal type in PlanningRunRequest, ops_manager_node rejects anything else, and the frontend has the same 4-item array duplicated in dashboard/page.tsx AND TodayIdleState.tsx. demand_forecast doesn't actually branch its algorithm on scenario today -- Prophet runs identically regardless, scenario only affects labeling and target_date. This task: relax PlanningScenarioId off the hardcoded Literal to accept a custom profile payload. New service turns free-form natural language ('we're hosting an event today, expecting large turnover') into an ad-hoc scenario_profile dict (label/service_window/operational_focus, LLM-derived) -- the 4 existing presets remain as one-click shortcuts, NOT replaced (explicit product decision). ops_manager_node's SUPPORTED_SCENARIOS check updated to admit custom profiles alongside the presets. Frontend: dedupe the two duplicated SCENARIO_OPTIONS arrays into one shared source; add a natural-language text input alongside the existing tile picker in PlanShiftModal.tsx -- user's choice of either mode, not a replacement of the tiles. Scope boundary: this task owns the backend (schema relaxation, natural-language-to-profile service) and the input widget itself; where that widget sits in the page layout, the live-signals context strip, and Action Queue placement belong to the new Today Dashboard redesign task (P6-A26) that follows.</t>
         </is>
       </c>
       <c r="F27" s="137" t="inlineStr">
@@ -18884,27 +18885,27 @@
       </c>
       <c r="C28" s="137" t="inlineStr">
         <is>
-          <t>Eval</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D28" s="137" t="inlineStr">
         <is>
-          <t>Validate action-item specificity after live signals land (conditional)</t>
+          <t>Today Dashboard redesign -- merge /operations in, live-signals context strip, Action Queue front-and-center</t>
         </is>
       </c>
       <c r="E28" s="137" t="inlineStr">
         <is>
-          <t>Not a guaranteed code task -- a validation checkpoint. Research confirmed aggregator.py/critic_service.py already favor structured, itemized output (bulleted restock actions, explicit dish names, numeric thresholds, dimension scores) over narrative paragraphs, so the 'standard, generic response' feedback is more likely an input-richness problem than a prompt-engineering problem. After P6-A24 ships, manually review 3-5 generated plans against known-rich live-signal test dates (a rain-forecast night, a real upcoming holiday, an active trend, a live FSSAI notice) to check whether output is now sufficiently specific/actionable. If yes: close this task, no further work needed. If still generic: scope a real follow-up prompt-engineering task against aggregator/critic with concrete before/after examples.</t>
+          <t>Real-product IA decision: merge /operations (agent cards, forecast chart, critic banner) into /dashboard so triggering a plan and watching it build/complete happens in one continuous view, not a page navigation -- a manager clicking 'plan your shift' shouldn't have to go somewhere else to see what they just asked for. Adds a condensed 'Today's Context' strip (weather/holiday/trend/compliance badges, from the four live signals unified in P6-A24) positioned next to the plan trigger, visible while choosing a scenario or typing a natural-language description (P6-A25) -- not on a separate /market page nobody checks daily. Adds the Action Queue (pending restock alerts, WhatsApp vendor drafts, pricing/promo reviews, trust-ladder approve/reject) prominently on this page -- currently the single biggest existing feature (P6-A7/A8/A9/A12) with no clear primary-nav home at all. Surfaces day-of KPIs (net margin, health score, revenue vs yesterday from GET /business/performance, P6-A6) at the top. /operations route redirects to /dashboard once the merge is verified working.</t>
         </is>
       </c>
       <c r="F28" s="137" t="inlineStr">
         <is>
-          <t>None yet -- validation checkpoint, code only if the review finds a real gap</t>
+          <t>feat: Today Dashboard redesign -- merge /operations, live-signals context strip, Action Queue front-and-center</t>
         </is>
       </c>
       <c r="G28" s="137" t="inlineStr">
         <is>
-          <t>None yet</t>
+          <t>docs/PRODUCT_MODES.md, docs/ARCHITECTURE.md, CLAUDE.md</t>
         </is>
       </c>
       <c r="H28" s="138" t="inlineStr">
@@ -18914,7 +18915,7 @@
       </c>
       <c r="I28" s="136" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J28" s="136" t="inlineStr">
@@ -18929,12 +18930,12 @@
       </c>
       <c r="N28" s="137" t="inlineStr">
         <is>
-          <t>P6-A24</t>
+          <t>P6-A24, P6-A25</t>
         </is>
       </c>
       <c r="O28" s="137" t="inlineStr">
         <is>
-          <t>N/A -- manual review checkpoint, not an automated test</t>
+          <t>Triggering a plan from Today shows agent cards/forecast chart/critic banner inline with no navigation; context strip shows all 4 live signals when present and degrades gracefully per-signal when one is missing; Action Queue pending items are visible and directly actionable (approve/reject) from this page; KPI snapshot renders real data from GET /business/performance; /operations redirects correctly</t>
         </is>
       </c>
     </row>
@@ -18946,32 +18947,32 @@
       </c>
       <c r="B29" s="137" t="inlineStr">
         <is>
-          <t>feature/procurement-loop-endtoend</t>
+          <t>feature/live-intelligence-signals</t>
         </is>
       </c>
       <c r="C29" s="137" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D29" s="137" t="inlineStr">
         <is>
-          <t>Autonomous procurement loop — end-to-end wire</t>
+          <t>Data page redesign -- merge /runs + /data-health, add Action Queue history</t>
         </is>
       </c>
       <c r="E29" s="137" t="inlineStr">
         <is>
-          <t>Connect: weather/holiday signal → demand_forecast surge → inventory shortage detection → ProcurementEnricher Instamart prices → ActionQueue APPROVE_REQUIRED action → trust ladder → checkout (staging creds) OR WhatsApp vendor fallback. This is the flagship restaurant OS demo moment. The plan output must clearly show: shortage detected → Instamart has it at Rs.24/kg → approve to order → or WhatsApp vendor if not on Instamart. Wire trust ladder: orders under Rs.500 auto-approved, over Rs.500 needs manual approval in action queue UI.</t>
+          <t>Real-product IA decision: a manager doesn't think of 'run history' as a separate audit concept from 'system data/health' -- merges /runs (plan run history, currently the weakest-looking screen: dense monospace debug trace) and /data-health (sync status, freshness) into one 'Data' page with clearly separated sections, applying the existing design system instead of the current raw trace view. Adds a new section with no home anywhere today: Action Queue history -- the audit trail of every action approved/rejected/executed over time (restocks sent, WhatsApp messages, pricing reviews). Fixes the known unstyled /runs/{id} deep-link 404 while in here.</t>
         </is>
       </c>
       <c r="F29" s="137" t="inlineStr">
         <is>
-          <t>feat: autonomous procurement loop — weather → forecast → shortage → Instamart → action queue</t>
+          <t>feat: Data page redesign -- merge /runs + /data-health, add Action Queue history</t>
         </is>
       </c>
       <c r="G29" s="137" t="inlineStr">
         <is>
-          <t>CLAUDE.md, docs/ARCHITECTURE.md (procurement loop diagram)</t>
+          <t>docs/ARCHITECTURE.md, CLAUDE.md</t>
         </is>
       </c>
       <c r="H29" s="138" t="inlineStr">
@@ -18981,7 +18982,7 @@
       </c>
       <c r="I29" s="136" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J29" s="136" t="inlineStr">
@@ -18994,14 +18995,10 @@
       <c r="M29" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="137" t="inlineStr">
-        <is>
-          <t>P6-A24</t>
-        </is>
-      </c>
+      <c r="N29" s="137" t="n"/>
       <c r="O29" s="137" t="inlineStr">
         <is>
-          <t>Full loop runs end-to-end in demo; trust ladder fires correctly; action queue shows Instamart procurement with price + spinId; WhatsApp fallback triggers when product not found on Instamart</t>
+          <t>/runs and /data-health content both accessible from one page with consistent design-system styling; direct navigation to /runs/{id} deep-link renders the run, not a 404; Action Queue history shows past actions with correct status/timestamps</t>
         </is>
       </c>
     </row>
@@ -19013,32 +19010,32 @@
       </c>
       <c r="B30" s="137" t="inlineStr">
         <is>
-          <t>feature/instamart-event-supplies</t>
+          <t>feature/live-intelligence-signals</t>
         </is>
       </c>
       <c r="C30" s="137" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D30" s="137" t="inlineStr">
         <is>
-          <t>Instamart event supplies in operator chatbot</t>
+          <t>Menu engineering matrix UI</t>
         </is>
       </c>
       <c r="E30" s="137" t="inlineStr">
         <is>
-          <t>Extend operator chatbot with event supplies tool: "we are hosting a birthday event tonight, need supplies." Calls search_products for non-food items: candles, paper plates, cups, napkins, soft drinks, basic decorations, cleaning supplies, batteries. Returns real Instamart prices and availability. Creates ActionQueue procurement action for approval. Key insight: Instamart is not just food ingredients — managers use it for quick supply runs that previously required leaving the restaurant. New chatbot tool: get_event_supplies(event_type, headcount)</t>
+          <t>Visual matrix: dish margin (y-axis) vs order popularity (x-axis). Four quadrants: Stars (high margin + high orders — promote), Plowhorses (low margin + high orders — reprice or remove), Puzzles (high margin + low orders — market better), Dogs (low margin + low orders — remove). Data from BusinessAnalyticsService (already has margin + popularity). Interactive: click a dish to see full margin breakdown. Shown on the new Data page (P6-A27), not /operations -- /operations is merged into Today Dashboard (P6-A26) and this is analytical/historical review, not a daily trigger-time decision, so it belongs with run history, not the plan-trigger flow. Connects to planning: critic uses quadrant data to validate menu recommendations.</t>
         </is>
       </c>
       <c r="F30" s="137" t="inlineStr">
         <is>
-          <t>feat: Instamart event supplies tool in operator chatbot</t>
+          <t>feat: menu engineering matrix — margin vs popularity quadrant chart</t>
         </is>
       </c>
       <c r="G30" s="137" t="inlineStr">
         <is>
-          <t>docs/AGENTS.md (chatbot tools updated)</t>
+          <t>None (frontend only)</t>
         </is>
       </c>
       <c r="H30" s="138" t="inlineStr">
@@ -19048,7 +19045,7 @@
       </c>
       <c r="I30" s="136" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J30" s="136" t="inlineStr">
@@ -19061,70 +19058,81 @@
       <c r="M30" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="137" t="n"/>
+      <c r="N30" s="137" t="inlineStr">
+        <is>
+          <t>P6-A27</t>
+        </is>
+      </c>
       <c r="O30" s="137" t="inlineStr">
         <is>
-          <t>search_products returns real results for non-food queries; ActionQueue action created; trust ladder applied; chatbot responds naturally to event supply requests</t>
+          <t>Matrix renders with correct quadrant assignment; click through shows dish margin detail; Stars/Plowhorses/Puzzles/Dogs correctly classified</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="90">
-      <c r="A31" s="139" t="inlineStr">
+      <c r="A31" s="136" t="inlineStr">
         <is>
           <t>P6-A29</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>feature/menu-engineering-matrix</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Menu engineering matrix UI</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Visual matrix: dish margin (y-axis) vs order popularity (x-axis). Four quadrants: Stars (high margin + high orders — promote), Plowhorses (low margin + high orders — reprice or remove), Puzzles (high margin + low orders — market better), Dogs (low margin + low orders — remove). Data from BusinessAnalyticsService (already has margin + popularity). Interactive: click a dish to see full margin breakdown. Shown on /operations page as a new panel. Connects to planning: critic uses quadrant data to validate menu recommendations.</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>feat: menu engineering matrix — margin vs popularity quadrant chart</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="B31" s="137" t="inlineStr">
+        <is>
+          <t>feature/live-intelligence-signals</t>
+        </is>
+      </c>
+      <c r="C31" s="137" t="inlineStr">
+        <is>
+          <t>Eval</t>
+        </is>
+      </c>
+      <c r="D31" s="137" t="inlineStr">
+        <is>
+          <t>Validate action-item specificity after live signals land (conditional)</t>
+        </is>
+      </c>
+      <c r="E31" s="137" t="inlineStr">
+        <is>
+          <t>Not a guaranteed code task -- a validation checkpoint. Research confirmed aggregator.py/critic_service.py already favor structured, itemized output (bulleted restock actions, explicit dish names, numeric thresholds, dimension scores) over narrative paragraphs, so the 'standard, generic response' feedback is more likely an input-richness problem than a prompt-engineering problem. After P6-A24 ships, manually review 3-5 generated plans against known-rich live-signal test dates (a rain-forecast night, a real upcoming holiday, an active trend, a live FSSAI notice) to check whether output is now sufficiently specific/actionable. If yes: close this task, no further work needed. If still generic: scope a real follow-up prompt-engineering task against aggregator/critic with concrete before/after examples.</t>
+        </is>
+      </c>
+      <c r="F31" s="137" t="inlineStr">
+        <is>
+          <t>None yet -- validation checkpoint, code only if the review finds a real gap</t>
+        </is>
+      </c>
+      <c r="G31" s="137" t="inlineStr">
+        <is>
+          <t>None yet</t>
+        </is>
+      </c>
+      <c r="H31" s="138" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="I31" s="136" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J31" s="136" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="K31" s="136" t="n"/>
+      <c r="L31" s="136" t="n"/>
+      <c r="M31" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Matrix renders with correct quadrant assignment; click through shows dish margin detail; Stars/Plowhorses/Puzzles/Dogs correctly classified</t>
+      <c r="N31" s="137" t="inlineStr">
+        <is>
+          <t>P6-A24, P6-A26</t>
+        </is>
+      </c>
+      <c r="O31" s="137" t="inlineStr">
+        <is>
+          <t>N/A -- manual review checkpoint, not an automated test</t>
         </is>
       </c>
     </row>
@@ -19136,7 +19144,7 @@
       </c>
       <c r="B32" s="137" t="inlineStr">
         <is>
-          <t>feature/structured-outputs</t>
+          <t>feature/procurement-loop-endtoend</t>
         </is>
       </c>
       <c r="C32" s="137" t="inlineStr">
@@ -19146,22 +19154,22 @@
       </c>
       <c r="D32" s="137" t="inlineStr">
         <is>
-          <t>Structured outputs — tool_choice=required across chatbot</t>
+          <t>Autonomous procurement loop — end-to-end wire</t>
         </is>
       </c>
       <c r="E32" s="137" t="inlineStr">
         <is>
-          <t>Force structured JSON outputs from Groq function calling. Eliminates cases where chatbot returns freeform text instead of calling the right tool. Add response validation layer. Makes chatbot more reliable for demo — no unexpected text responses.</t>
+          <t>Connect: weather/holiday signal → demand_forecast surge → inventory shortage detection → ProcurementEnricher Instamart prices → ActionQueue APPROVE_REQUIRED action → trust ladder → checkout (staging creds) OR WhatsApp vendor fallback. This is the flagship restaurant OS demo moment. The plan output must clearly show: shortage detected → Instamart has it at Rs.24/kg → approve to order → or WhatsApp vendor if not on Instamart. Wire trust ladder: orders under Rs.500 auto-approved, over Rs.500 needs manual approval in action queue UI.</t>
         </is>
       </c>
       <c r="F32" s="137" t="inlineStr">
         <is>
-          <t>feat: structured outputs — force tool_choice=required in chatbot</t>
+          <t>feat: autonomous procurement loop — weather → forecast → shortage → Instamart → action queue</t>
         </is>
       </c>
       <c r="G32" s="137" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CLAUDE.md, docs/ARCHITECTURE.md (procurement loop diagram)</t>
         </is>
       </c>
       <c r="H32" s="138" t="inlineStr">
@@ -19171,7 +19179,7 @@
       </c>
       <c r="I32" s="136" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J32" s="136" t="inlineStr">
@@ -19184,10 +19192,14 @@
       <c r="M32" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="137" t="n"/>
+      <c r="N32" s="137" t="inlineStr">
+        <is>
+          <t>P6-A24</t>
+        </is>
+      </c>
       <c r="O32" s="137" t="inlineStr">
         <is>
-          <t>Chatbot always calls a tool when one applies; no unexpected freeform responses; existing chatbot tests pass</t>
+          <t>Full loop runs end-to-end in demo; trust ladder fires correctly; action queue shows Instamart procurement with price + spinId; WhatsApp fallback triggers when product not found on Instamart</t>
         </is>
       </c>
     </row>
@@ -19199,32 +19211,32 @@
       </c>
       <c r="B33" s="137" t="inlineStr">
         <is>
-          <t>feature/voice-interface</t>
+          <t>feature/instamart-event-supplies</t>
         </is>
       </c>
       <c r="C33" s="137" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Agents</t>
         </is>
       </c>
       <c r="D33" s="137" t="inlineStr">
         <is>
-          <t>Voice interface — Whisper transcription + TTS response</t>
+          <t>Instamart event supplies in operator chatbot</t>
         </is>
       </c>
       <c r="E33" s="137" t="inlineStr">
         <is>
-          <t>Restaurant operator speaks to CortexKitchen instead of typing. Browser MediaRecorder API captures audio. Whisper (via Groq) transcribes to text. Existing chatbot processes the text query. TTS reads back the response. Use case: manager walking the floor asks questions hands-free. "What does the plan say about staffing tonight?" "How many covers are we expecting?" Add mic button to existing /chat page. Works for operator side only initially.</t>
+          <t>Extend operator chatbot with event supplies tool: "we are hosting a birthday event tonight, need supplies." Calls search_products for non-food items: candles, paper plates, cups, napkins, soft drinks, basic decorations, cleaning supplies, batteries. Returns real Instamart prices and availability. Creates ActionQueue procurement action for approval. Key insight: Instamart is not just food ingredients — managers use it for quick supply runs that previously required leaving the restaurant. New chatbot tool: get_event_supplies(event_type, headcount)</t>
         </is>
       </c>
       <c r="F33" s="137" t="inlineStr">
         <is>
-          <t>feat: voice interface — Whisper transcription + TTS on /chat page</t>
+          <t>feat: Instamart event supplies tool in operator chatbot</t>
         </is>
       </c>
       <c r="G33" s="137" t="inlineStr">
         <is>
-          <t>docs/PRODUCT_MODES.md (voice mode section)</t>
+          <t>docs/AGENTS.md (chatbot tools updated)</t>
         </is>
       </c>
       <c r="H33" s="138" t="inlineStr">
@@ -19234,7 +19246,7 @@
       </c>
       <c r="I33" s="136" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J33" s="136" t="inlineStr">
@@ -19250,7 +19262,7 @@
       <c r="N33" s="137" t="n"/>
       <c r="O33" s="137" t="inlineStr">
         <is>
-          <t>Audio recorded and transcribed correctly; chatbot processes transcription; TTS plays response; mic button shows recording state</t>
+          <t>search_products returns real results for non-food queries; ActionQueue action created; trust ladder applied; chatbot responds naturally to event supply requests</t>
         </is>
       </c>
     </row>
@@ -19262,27 +19274,27 @@
       </c>
       <c r="B34" s="137" t="inlineStr">
         <is>
-          <t>feature/eval-pipeline</t>
+          <t>feature/structured-outputs</t>
         </is>
       </c>
       <c r="C34" s="137" t="inlineStr">
         <is>
-          <t>Eval</t>
+          <t>Agents</t>
         </is>
       </c>
       <c r="D34" s="137" t="inlineStr">
         <is>
-          <t>Promote RAGAS/DeepEval candidates + regenerate golden runs</t>
+          <t>Structured outputs — tool_choice=required across chatbot</t>
         </is>
       </c>
       <c r="E34" s="137" t="inlineStr">
         <is>
-          <t>Review RAGAS and DeepEval eval candidates. Promote passing ones to the CI gate. Regenerate golden_runs.json against real planning data. Ensures eval pipeline catches regressions after compliance changes and new feature additions.</t>
+          <t>Force structured JSON outputs from Groq function calling. Eliminates cases where chatbot returns freeform text instead of calling the right tool. Add response validation layer. Makes chatbot more reliable for demo — no unexpected text responses.</t>
         </is>
       </c>
       <c r="F34" s="137" t="inlineStr">
         <is>
-          <t>feat: eval pipeline — promote RAGAS/DeepEval + regenerate golden runs</t>
+          <t>feat: structured outputs — force tool_choice=required in chatbot</t>
         </is>
       </c>
       <c r="G34" s="137" t="inlineStr">
@@ -19297,7 +19309,7 @@
       </c>
       <c r="I34" s="136" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J34" s="136" t="inlineStr">
@@ -19310,153 +19322,279 @@
       <c r="M34" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="137" t="inlineStr">
-        <is>
-          <t>P6-A27</t>
-        </is>
-      </c>
+      <c r="N34" s="137" t="n"/>
       <c r="O34" s="137" t="inlineStr">
         <is>
+          <t>Chatbot always calls a tool when one applies; no unexpected freeform responses; existing chatbot tests pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="136" t="inlineStr">
+        <is>
+          <t>P6-A33</t>
+        </is>
+      </c>
+      <c r="B35" s="137" t="inlineStr">
+        <is>
+          <t>feature/voice-interface</t>
+        </is>
+      </c>
+      <c r="C35" s="137" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D35" s="137" t="inlineStr">
+        <is>
+          <t>Voice interface — Whisper transcription + TTS response</t>
+        </is>
+      </c>
+      <c r="E35" s="137" t="inlineStr">
+        <is>
+          <t>Restaurant operator speaks to CortexKitchen instead of typing. Browser MediaRecorder API captures audio. Whisper (via Groq) transcribes to text. Existing chatbot processes the text query. TTS reads back the response. Use case: manager walking the floor asks questions hands-free. "What does the plan say about staffing tonight?" "How many covers are we expecting?" Add mic button to existing /chat page. Works for operator side only initially.</t>
+        </is>
+      </c>
+      <c r="F35" s="137" t="inlineStr">
+        <is>
+          <t>feat: voice interface — Whisper transcription + TTS on /chat page</t>
+        </is>
+      </c>
+      <c r="G35" s="137" t="inlineStr">
+        <is>
+          <t>docs/PRODUCT_MODES.md (voice mode section)</t>
+        </is>
+      </c>
+      <c r="H35" s="138" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I35" s="136" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J35" s="136" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K35" s="136" t="n"/>
+      <c r="L35" s="136" t="n"/>
+      <c r="M35" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="137" t="n"/>
+      <c r="O35" s="137" t="inlineStr">
+        <is>
+          <t>Audio recorded and transcribed correctly; chatbot processes transcription; TTS plays response; mic button shows recording state</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="136" t="inlineStr">
+        <is>
+          <t>P6-A34</t>
+        </is>
+      </c>
+      <c r="B36" s="137" t="inlineStr">
+        <is>
+          <t>feature/eval-pipeline</t>
+        </is>
+      </c>
+      <c r="C36" s="137" t="inlineStr">
+        <is>
+          <t>Eval</t>
+        </is>
+      </c>
+      <c r="D36" s="137" t="inlineStr">
+        <is>
+          <t>Promote RAGAS/DeepEval candidates + regenerate golden runs</t>
+        </is>
+      </c>
+      <c r="E36" s="137" t="inlineStr">
+        <is>
+          <t>Review RAGAS and DeepEval eval candidates. Promote passing ones to the CI gate. Regenerate golden_runs.json against real planning data. Ensures eval pipeline catches regressions after compliance changes and new feature additions.</t>
+        </is>
+      </c>
+      <c r="F36" s="137" t="inlineStr">
+        <is>
+          <t>feat: eval pipeline — promote RAGAS/DeepEval + regenerate golden runs</t>
+        </is>
+      </c>
+      <c r="G36" s="137" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H36" s="138" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I36" s="136" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J36" s="136" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K36" s="136" t="n"/>
+      <c r="L36" s="136" t="n"/>
+      <c r="M36" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="137" t="inlineStr">
+        <is>
+          <t>P6-A30</t>
+        </is>
+      </c>
+      <c r="O36" s="137" t="inlineStr">
+        <is>
           <t>CI eval gate passes; golden_runs.json reflects current system; regressions caught in 2+ test scenarios</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="140" t="inlineStr">
         <is>
           <t>DOCS + SYNC — end of Phase 6A</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="136" t="inlineStr">
-        <is>
-          <t>P6-A33</t>
-        </is>
-      </c>
-      <c r="B37" s="137" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="136" t="inlineStr">
+        <is>
+          <t>P6-A35</t>
+        </is>
+      </c>
+      <c r="B39" s="137" t="inlineStr">
         <is>
           <t>feature/documentation</t>
         </is>
       </c>
-      <c r="C37" s="137" t="inlineStr">
+      <c r="C39" s="137" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D37" s="137" t="inlineStr">
+      <c r="D39" s="137" t="inlineStr">
         <is>
           <t>Whole-system documentation + screenshots refresh</t>
         </is>
       </c>
-      <c r="E37" s="137" t="inlineStr">
+      <c r="E39" s="137" t="inlineStr">
         <is>
           <t>Update all docs to reflect: new two-sided product vision, compliance changes (Zomato removed, market intel anonymised), autonomous procurement loop, weather signals, voice interface. New product vision statement in README. Screenshots of the operator portal (dashboard, operations, market, action queue, chat) for portfolio -- Guest Concierge screenshots belong to Phase 6B docs (P6-B9), not here, since Guest Concierge does not exist yet at this point.</t>
         </is>
       </c>
-      <c r="F37" s="137" t="inlineStr">
+      <c r="F39" s="137" t="inlineStr">
         <is>
           <t>docs: whole-system documentation refresh — new product vision</t>
         </is>
       </c>
-      <c r="G37" s="137" t="inlineStr">
+      <c r="G39" s="137" t="inlineStr">
         <is>
           <t>README.md, docs/ARCHITECTURE.md, docs/AGENTS.md, CLAUDE.md</t>
         </is>
       </c>
-      <c r="H37" s="138" t="inlineStr">
+      <c r="H39" s="138" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I37" s="136" t="inlineStr">
+      <c r="I39" s="136" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J37" s="136" t="inlineStr">
+      <c r="J39" s="136" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K37" s="136" t="n"/>
-      <c r="L37" s="136" t="n"/>
-      <c r="M37" s="136" t="n">
+      <c r="K39" s="136" t="n"/>
+      <c r="L39" s="136" t="n"/>
+      <c r="M39" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="137" t="inlineStr">
-        <is>
-          <t>P6-A32</t>
-        </is>
-      </c>
-      <c r="O37" s="137" t="inlineStr">
+      <c r="N39" s="137" t="inlineStr">
+        <is>
+          <t>P6-A34</t>
+        </is>
+      </c>
+      <c r="O39" s="137" t="inlineStr">
         <is>
           <t>README reflects two-sided platform; all compliance changes documented; screenshots current</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="136" t="inlineStr">
-        <is>
-          <t>P6-A34</t>
-        </is>
-      </c>
-      <c r="B38" s="137" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="136" t="inlineStr">
+        <is>
+          <t>P6-A36</t>
+        </is>
+      </c>
+      <c r="B40" s="137" t="inlineStr">
         <is>
           <t>dev -&gt; main</t>
         </is>
       </c>
-      <c r="C38" s="137" t="inlineStr">
+      <c r="C40" s="137" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
       </c>
-      <c r="D38" s="137" t="inlineStr">
+      <c r="D40" s="137" t="inlineStr">
         <is>
           <t>Sync Phase 6A to main</t>
         </is>
       </c>
-      <c r="E38" s="137" t="inlineStr">
+      <c r="E40" s="137" t="inlineStr">
         <is>
           <t>Merge dev → main. All compliance fixes confirmed. Autonomous procurement loop working (minus checkout — staging creds). Restaurant OS demo-ready. Phase 6B starts after this.</t>
         </is>
       </c>
-      <c r="F38" s="137" t="inlineStr">
+      <c r="F40" s="137" t="inlineStr">
         <is>
           <t>release: Phase 6A complete — restaurant OS + compliance fixes</t>
         </is>
       </c>
-      <c r="G38" s="137" t="inlineStr">
+      <c r="G40" s="137" t="inlineStr">
         <is>
           <t>README.md</t>
         </is>
       </c>
-      <c r="H38" s="138" t="inlineStr">
+      <c r="H40" s="138" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="I38" s="136" t="inlineStr">
+      <c r="I40" s="136" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J38" s="136" t="inlineStr">
+      <c r="J40" s="136" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K38" s="136" t="n"/>
-      <c r="L38" s="136" t="n"/>
-      <c r="M38" s="136" t="n">
+      <c r="K40" s="136" t="n"/>
+      <c r="L40" s="136" t="n"/>
+      <c r="M40" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="137" t="inlineStr">
-        <is>
-          <t>P6-A33</t>
-        </is>
-      </c>
-      <c r="O38" s="137" t="inlineStr">
+      <c r="N40" s="137" t="inlineStr">
+        <is>
+          <t>P6-A35</t>
+        </is>
+      </c>
+      <c r="O40" s="137" t="inlineStr">
         <is>
           <t>Full test suite green; compliance fixes verified; no Zomato references; market intel anonymised; demo flow works</t>
         </is>
@@ -19464,7 +19602,7 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="A38:O38"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A22:O22"/>
     <mergeCell ref="A18:O18"/>
@@ -19990,7 +20128,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>search_products for decorations, cake, drinks, party supplies matching the event brief -- same tool pattern as the Restaurant OS operator-facing get_event_supplies (P6-A28), but consumer-facing and for the guest's own event rather than restaurant procurement. Cart/checkout once creds land.</t>
+          <t>search_products for decorations, cake, drinks, party supplies matching the event brief -- same tool pattern as the Restaurant OS operator-facing get_event_supplies (P6-A31), but consumer-facing and for the guest's own event rather than restaurant procurement. Cart/checkout once creds land.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -20700,7 +20838,7 @@
       </c>
       <c r="N14" s="59" t="inlineStr">
         <is>
-          <t>P6-A31</t>
+          <t>P6-A33</t>
         </is>
       </c>
       <c r="O14" s="59" t="inlineStr">
@@ -22358,7 +22496,7 @@
       </c>
       <c r="E63" s="59" t="inlineStr">
         <is>
-          <t>Audit test coverage for every new service/model added in Phase 6A (Action Queue, workflow triggers, trust-ladder, WhatsApp vendor flow, Vendor/Supplier model, Menu Engineering Matrix) -- confirm nothing shipped without tests. Re-check the CI pipeline includes all new test files. Re-run/expand RAGAS + DeepEval evals to cover the new agentic behaviors (workflow-triggered actions, trust-ladder promotions), since the existing eval sets predate all of this and won't catch regressions in it. (Docs + screenshots refresh is P6-A33, done before the demo video; this is the deeper test/CI/eval hygiene pass that doesn't need to block the video.)</t>
+          <t>Audit test coverage for every new service/model added in Phase 6A (Action Queue, workflow triggers, trust-ladder, WhatsApp vendor flow, Vendor/Supplier model, Menu Engineering Matrix) -- confirm nothing shipped without tests. Re-check the CI pipeline includes all new test files. Re-run/expand RAGAS + DeepEval evals to cover the new agentic behaviors (workflow-triggered actions, trust-ladder promotions), since the existing eval sets predate all of this and won't catch regressions in it. (Docs + screenshots refresh is P6-A35, done before the demo video; this is the deeper test/CI/eval hygiene pass that doesn't need to block the video.)</t>
         </is>
       </c>
       <c r="F63" s="59" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -18576,7 +18576,7 @@
       </c>
       <c r="E23" s="137" t="inlineStr">
         <is>
-          <t>First of four independently-failing live-intelligence services feeding the planning pipeline (P6-A24 unifies all four). New WeatherService (infrastructure/external/weather_service.py) calls Open-Meteo (free, no API key) for current + 48h forecast at the restaurant's location -- rain/heat forecasts shift the plan toward delivery-heavy staffing and prep, clear days toward walk-in/outdoor capacity. INDIAN_HOLIDAYS_2026 already exists in core/constants.py and already feeds ScenarioRecommender in the background -- this task surfaces it explicitly into demand_forecast's own prompt too ('today is Gandhi Jayanti -- public holiday, expect elevated demand'), not just the scenario suggestion. Never raises -- returns None on any failure so demand_forecast runs fine without it. New OrchestratorState field: weather_signal.</t>
+          <t>DONE on feature/live-intelligence-signals. New WeatherService (infrastructure/external/weather_service.py) -- Open-Meteo, free, keyless -- averages temperature/precipitation across the target date's 18:00-22:00 dinner window, classifies heavy_rain/light_rain/very_hot/clear, returns a conservative demand_multiplier (1.03-1.10) plus descriptive delivery_impact/dinein_impact strings. New app/core/calendar_utils.py extracts the holiday/weekend lookup that used to live only inside ScenarioRecommender._date_context, so it's shared rather than duplicated as a second consumer (demand_forecast) needed it. THE ACTUAL FIX: ForecastService._apply_signal_adjustments() applies a deterministic multiplier (holiday x1.4, weather x1.03-1.10, stacked when both apply) to Prophet's raw predicted_orders/predicted_peak_orders -- previously weather/holiday would only ever have reached the LLM recommendation step as narrative text it may or may not act on; now they move the actual predicted number. Transparent by construction: predicted_orders_pre_adjustment, adjustment_multiplier, and adjustment_reasons are all preserved alongside the adjusted figure, so nothing is a silent change to what Prophet said. demand_forecast_node fetches both signals and passes them into analyse_and_recommend(); writes state['weather_signal']. ScenarioRecommender also wired to use the weather signal alongside its existing holiday context. GET /market/pulse returns weather + upcoming_holiday (a cheap 14-day dict scan against INDIAN_HOLIDAYS_2026, no API call) -- both explicitly independent of swiggy_connected, since neither is Swiggy MCP; the original handler had an early return on Swiggy-unavailable that would have hidden both, fixed during implementation. New 'Weather &amp; Holidays' card on /market (SwiggyLiveMarketPanel.tsx) -- also fixed the same early-return bug on the frontend side so the card renders even when Swiggy isn't connected. Default coordinates (core/constants.py: DEFAULT_RESTAURANT_LAT/LNG, Navi Mumbai, matching SWIGGY_ADDRESS_ID's approximate area) used since RestaurantProfile has no stored lat/lng column. As a side effect, fixed a pre-existing environment issue: reportlab was declared in requirements.txt but never actually installed, breaking test_pdf_export.py's collection (11 tests) -- installed, unrelated to this task's code but blocking a clean full-suite run.</t>
         </is>
       </c>
       <c r="F23" s="137" t="inlineStr">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="H23" s="138" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I23" s="136" t="inlineStr">
@@ -18607,12 +18607,12 @@
       <c r="K23" s="136" t="n"/>
       <c r="L23" s="136" t="n"/>
       <c r="M23" s="136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="137" t="n"/>
       <c r="O23" s="137" t="inlineStr">
         <is>
-          <t>Weather API call returns current+forecast conditions for a known lat/lng and gracefully degrades to None on API failure; holiday lookup correctly identifies a known date against INDIAN_HOLIDAYS_2026; both signals appear in demand_forecast's prompt on a known test date</t>
+          <t>VERIFIED: 519 backend tests pass (498 pre-existing + 21 new across test_calendar_utils.py, test_weather_service.py, test_forecast_signal_adjustments.py -- classification thresholds, dinner-window extraction, fail-open on HTTP error/malformed response/out-of-range date, multiplier math including holiday+weather stacking, and the predicted_orders_pre_adjustment/adjustment_multiplier/adjustment_reasons transparency fields); frontend typechecks clean (npx tsc --noEmit, zero errors); zero regressions in existing ScenarioRecommender/ForecastService/demand_forecast tests since all new params are optional with defaults.</t>
         </is>
       </c>
     </row>
@@ -19459,6 +19459,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="140" t="inlineStr">
         <is>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Tracker ( 1 - 5 )" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 6" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 6A" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 6B" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staging Creds + Phase 7" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doc Strategy" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git Practices" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Phase Tracker ( 1 - 5 )" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Phase 6" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Phase 6A" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Phase 6B" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Staging Creds + Phase 7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Doc Strategy" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Git Practices" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="E24" s="137" t="inlineStr">
         <is>
-          <t>Second live-intelligence service. New TrendsService -- a curated list of Indian F&amp;B/hospitality trade-press RSS feeds, fetched via feedparser (new free/open-source dependency) and summarized into a short 'what's trending' digest using the existing Groq LLM client (no new LLM integration needed). RSS-only deliberately, not Google Trends/pytrends -- pytrends scrapes Google's internal endpoint, a ToS gray area we chose to avoid given how carefully we've treated Swiggy's terms; RSS is meant for syndication, zero ToS risk. Independently fail-open: if all feeds are unreachable, returns None and does not block weather/compliance/Swiggy signals. New OrchestratorState field: trends_signal.</t>
+          <t>DONE on feature/live-intelligence-signals. New TrendsService (infrastructure/external/trends_service.py) -- fetches 2 curated Indian F&amp;B/agri-business RSS feeds (ET Retail Food &amp; Entertainment, Hindu BusinessLine Agri-Business; a generic retail top-stories feed was tried and dropped -- it diluted the digest with non-food retail news) via feedparser, then summarizes headlines PLUS article summaries into a short digest via the existing create_llm_provider() factory (no new LLM integration). Prompt tuned twice after live review: first pass read as restated headlines, so the prompt now requires a specific fact plus a concrete operational implication per bullet; second pass had a bullet reading as scrutiny of Swiggy's FSSAI compliance, so the prompt now stays neutral/factual about any named platform and redirects to the restaurant's OWN compliance action instead. Independently fail-open: returns None if every feed is unreachable or the LLM call fails, cached in Redis 1 hour. New OrchestratorState field: trends_signal (not yet read by any node -- that's P6-A24). Wired into GET /market/pulse (independent of swiggy_connected) and a new Industry Trends card on /market. Also fixed the shared Card component always showing a 'via Swiggy MCP' badge even on non-Swiggy cards (Weather, now Trends too).</t>
         </is>
       </c>
       <c r="F24" s="137" t="inlineStr">
@@ -18654,7 +18654,7 @@
       </c>
       <c r="H24" s="138" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I24" s="136" t="inlineStr">
@@ -18670,12 +18670,12 @@
       <c r="K24" s="136" t="n"/>
       <c r="L24" s="136" t="n"/>
       <c r="M24" s="136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="137" t="n"/>
       <c r="O24" s="137" t="inlineStr">
         <is>
-          <t>RSS fetch+parse works against a known feed in a live test; degrades to None if all feeds are unreachable (simulated); LLM produces a coherent digest from real feed content</t>
+          <t>VERIFIED: live integration test (tests/integration/test_trends_service.py) confirms real RSS fetch+parse against both feeds and a coherent, specific digest from the real LLM provider; 5 unit tests cover all-feeds-unreachable -&gt; None, LLM-failure -&gt; None, partial feed failure still produces a digest, and cache-hit skip. Frontend typechecks clean (npx tsc --noEmit, zero errors).</t>
         </is>
       </c>
     </row>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="E25" s="137" t="inlineStr">
         <is>
-          <t>Third live-intelligence service. New ComplianceAlertsService scrapes FSSAI's public notifications page (fssai.gov.in/notifications.php) via beautifulsoup4 (new dependency) -- confirmed live (2026-07-11) this page has no RSS feed, is plain server-side-rendered HTML (not JS-dependent), so a lightweight parser is sufficient without a headless browser. Public government regulatory data, no ToS tension of any kind -- cleanest source of the four on that front. Explicit fail-open contract given HTML scraping is inherently more fragile than RSS (any FSSAI site redesign breaks the parser) -- must degrade to None cleanly, never raise, never block the other three signals. New OrchestratorState field: compliance_alerts_signal.</t>
+          <t>DONE on feature/live-intelligence-signals. New ComplianceAlertsService (infrastructure/external/compliance_alerts_service.py) scrapes FSSAI's public notifications page, Gazette Notification category (finalized regulations, not drafts/comments-under-review) via beautifulsoup4 -- confirmed live this page has no RSS feed but is plain server-side-rendered HTML (a category &lt;select&gt; + form GET reload, no JS/AJAX), so a lightweight parser is sufficient. Parses each notice's title/upload-date/PDF link from the real 'Title [Uploaded on : DD-MM-YYYY]' text pattern. Public government regulatory data -- no ToS tension of any kind, cleanest source of the four live-intelligence signals on that front. Independently fail-open: returns None on HTTP failure, an empty result set ('No records found'), or an unexpected page structure (simulated in tests) -- never raises, never blocks weather/trends/Swiggy signals. New OrchestratorState field: compliance_alerts_signal (not yet read by any node -- that's P6-A24). Wired into GET /market/pulse (independent of swiggy_connected) and a new Regulatory Alerts card on /market, linking each notice's real FSSAI PDF.</t>
         </is>
       </c>
       <c r="F25" s="137" t="inlineStr">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="H25" s="138" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I25" s="136" t="inlineStr">
@@ -18733,12 +18733,12 @@
       <c r="K25" s="136" t="n"/>
       <c r="L25" s="136" t="n"/>
       <c r="M25" s="136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="137" t="n"/>
       <c r="O25" s="137" t="inlineStr">
         <is>
-          <t>Scrape returns real recent notices in a live test; degrades to None on parse failure (simulate an unexpected page structure); no crash on an empty result set</t>
+          <t>VERIFIED: live integration test (tests/integration/test_compliance_alerts_service.py) confirms real notices scraped from the live FSSAI page (5 real Gazette notifications, e.g. Vegan Foods labelling, Contaminants/Toxins/Residues amendments); 6 unit tests cover no-records-found -&gt; None, HTTP error -&gt; None, unexpected page structure (simulated redesign) -&gt; None, and a malformed single notice being skipped without crashing well-formed siblings. Frontend typechecks clean (npx tsc --noEmit, zero errors).</t>
         </is>
       </c>
     </row>
@@ -19459,7 +19459,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="140" t="inlineStr">
         <is>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -18765,7 +18765,7 @@
       </c>
       <c r="E26" s="137" t="inlineStr">
         <is>
-          <t>Merges weather/holiday (P6-A21) + industry trends (P6-A22) + compliance alerts (P6-A23) + the existing anonymised Swiggy area signals (P6-A20) into one combined 'Area &amp; Live Signals' section. Added INSIDE the existing market_intel_node / MarketIntelService rather than a new 12th LangGraph node -- MarketIntelService already runs multiple enrichers concurrently and fails open per-enricher, so this is additive to a proven pattern, not a new one. Critically, this preserves the existing state field names (swiggy_competitor_context, swiggy_occupancy_context, market_intel_output) that 5+ files and the frontend already read by name -- confirmed via audit that renaming them would be a wide, unnecessary blast radius. No frontend SSE changes needed since the node count doesn't change. Injected into demand_forecast, menu_intelligence, and the critic's prompt via aggregator.py's _build_critic_summary. Each of the 4 sources stays independently fail-open all the way through -- one going down never blocks the others or crashes the node.</t>
+          <t>DONE on feature/live-intelligence-signals. Merges weather/holiday (P6-A21) + industry trends (P6-A22) + regulatory alerts (P6-A23) + the existing anonymised Swiggy competitor/occupancy signals into one 'Area &amp; Live Signals' text (MarketIntelService._build_live_signals_text), added inside the existing market_intel_node/MarketIntelService rather than a new graph node. Existing state field names unchanged -- only a new market_intel_output['live_signals_text'] key was added. Since demand_forecast_node runs before the qdrant_enrichment fan-out (so it can't read market_intel_output), it fetches all three non-Swiggy signals itself, writes them to state (weather_signal/trends_signal/compliance_alerts_signal), and injects trends/compliance directly into its own LLM narrative (text-only -- only weather shifts the actual forecast number). market_intel_node reads the same three back from state (never re-fetches) and merges them with Swiggy competitor/occupancy prompt text. Critically, market_intel_node no longer nulls market_intel_output to None when Swiggy is unavailable -- it now returns MarketIntelService.build_signals_only_result() so weather/trends/compliance still reach menu_intelligence/critic even when Swiggy is down (found via test_skips_db_query_when_swiggy_unavailable asserting the old None behavior -- updated to match the new, correct contract). Read by menu_intelligence (MenuService's market_context, preferring live_signals_text over the old competitor-only prompt_text with a fallback) and condensed into an aggregator '[Live Signals]' line for the critic (full prose stays menu_intelligence's job, not the critic's, to avoid prompt bloat).</t>
         </is>
       </c>
       <c r="F26" s="137" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="H26" s="138" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I26" s="136" t="inlineStr">
@@ -18796,7 +18796,7 @@
       <c r="K26" s="136" t="n"/>
       <c r="L26" s="136" t="n"/>
       <c r="M26" s="136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="137" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
       </c>
       <c r="O26" s="137" t="inlineStr">
         <is>
-          <t>demand_forecast/menu_intelligence/critic prompts include all present sources; simulated failure of any one source doesn't block the others or crash the node; aggregator's critic summary includes a live-signals section; existing Swiggy state field names unchanged, all P6-A19/A20 tests still pass</t>
+          <t>VERIFIED: demand_forecast/menu_intelligence/critic prompts all include present sources (test_trends_and_compliance_appear_in_llm_prompt_not_the_multiplier, test_menu_service_prefers_unified_live_signals_text, test_live_signals_section_present_when_any_signal_available); simulated failure of any one source doesn't block the others (test_live_signals_text_omits_missing_sources_without_failing, test_live_signals_surface_even_when_swiggy_unavailable, test_live_signals_partial_availability_does_not_crash); existing Swiggy state field names unchanged, all prior market_intel/menu_service tests still pass. 133 tests across the full affected surface (market_intel node+service, demand_forecast, forecast signal adjustments, menu service, aggregator, graph flow, evaluation sanity, replan loop, critic service) pass clean. Also fixed a test-hygiene issue found along the way: demand_forecast_node's existing production-mode tests were making real unmocked RSS+LLM network calls once TrendsService/ComplianceAlertsService were added -- now mocked, test runtime dropped from ~1.8s to ~0.02s combined.</t>
         </is>
       </c>
     </row>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -18832,7 +18832,7 @@
       </c>
       <c r="E27" s="137" t="inlineStr">
         <is>
-          <t>Confirmed via audit: all 4 scenarios (friday_rush/weekday_lunch/holiday_spike/low_stock_weekend) are hardcoded end-to-end -- a Pydantic Literal type in PlanningRunRequest, ops_manager_node rejects anything else, and the frontend has the same 4-item array duplicated in dashboard/page.tsx AND TodayIdleState.tsx. demand_forecast doesn't actually branch its algorithm on scenario today -- Prophet runs identically regardless, scenario only affects labeling and target_date. This task: relax PlanningScenarioId off the hardcoded Literal to accept a custom profile payload. New service turns free-form natural language ('we're hosting an event today, expecting large turnover') into an ad-hoc scenario_profile dict (label/service_window/operational_focus, LLM-derived) -- the 4 existing presets remain as one-click shortcuts, NOT replaced (explicit product decision). ops_manager_node's SUPPORTED_SCENARIOS check updated to admit custom profiles alongside the presets. Frontend: dedupe the two duplicated SCENARIO_OPTIONS arrays into one shared source; add a natural-language text input alongside the existing tile picker in PlanShiftModal.tsx -- user's choice of either mode, not a replacement of the tiles. Scope boundary: this task owns the backend (schema relaxation, natural-language-to-profile service) and the input widget itself; where that widget sits in the page layout, the live-signals context strip, and Action Queue placement belong to the new Today Dashboard redesign task (P6-A26) that follows.</t>
+          <t>DONE on feature/live-intelligence-signals. Backend: PlanningRunRequest.scenario relaxed from a 4-value Literal to a plain str; new custom_profile field (ScenarioProfilePayload -- id/label/description/service_window/operational_focus/cuisine). New ScenarioProfileService.derive_profile() (new POST /planning/scenario-from-text route) turns free-form text into that profile via an LLM call, mirroring ScenarioRecommender's never-raise + deterministic-fallback pattern -- always fills all 3 required keys, since complaint_service/inventory_service/reservation_service read scenario_profile['label'] etc. via direct dict access (not .get()) once scenario_profile is truthy, so an incomplete profile would KeyError deep in the pipeline otherwise. ops_manager_node's SUPPORTED_SCENARIOS check now branches: known preset -&gt; unchanged behavior; unknown scenario + custom_profile present -&gt; build scenario_profile from that; unknown scenario + no custom_profile -&gt; still a hard error (safety preserved). New OrchestratorState field: custom_profile, threaded through make_initial_state/run_planning_scenario/stream_planning_scenario. Custom-profile runs bypass both the semantic cache and the Redis plan cache (two different free-text descriptions would otherwise collide on the same scenario='custom' cache key). Frontend: deduplicated the two verbatim-identical SCENARIO_OPTIONS arrays (dashboard/page.tsx, TodayIdleState.tsx) into one shared lib/scenarios.ts; widened the 4-literal-union types (FridayRushRequest.scenario, PlanningScenarioOption.id, DashboardContext's DashScenario) to string; PlanShiftModal.tsx now has a free-text input alongside the existing tile grid -- deriving a profile synthesizes a 5th 'custom' tile, selects it, and threads the full ScenarioProfile through onRun -&gt; trigger() -&gt; the request body, all without replacing the 4 preset tiles. New docs/PRODUCT_MODES.md explains both intake modes end to end.</t>
         </is>
       </c>
       <c r="F27" s="137" t="inlineStr">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="H27" s="138" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I27" s="136" t="inlineStr">
@@ -18863,12 +18863,12 @@
       <c r="K27" s="136" t="n"/>
       <c r="L27" s="136" t="n"/>
       <c r="M27" s="136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="137" t="n"/>
       <c r="O27" s="137" t="inlineStr">
         <is>
-          <t>Natural-language input produces a valid scenario_profile dict with sensible defaults for missing fields; existing 4 presets still work completely unchanged; ops_manager_node accepts a custom profile without rejecting it; frontend offers both input modes; SCENARIO_OPTIONS no longer duplicated across two files</t>
+          <t>VERIFIED: 16 new/updated backend tests (test_scenario_profile_service.py -- valid LLM response, missing label/malformed service_window/non-dict LLM response/LLM exception all falling back correctly, empty text skips the LLM call entirely, long input truncated; test_scenario_expansion.py -- ops_manager builds scenario_profile from custom_profile, rejects unknown scenario with no custom_profile, presets stay unaffected even if a custom_profile happens to be present, full run_planning_scenario pipeline run with a custom profile end to end). 545 backend unit tests pass total, zero regressions. Frontend typechecks clean (npx tsc --noEmit, zero errors) after widening all 3 literal-union choke points. NOT visually tested in a running browser (user's own npm dev server was already running -- avoided starting a second one) -- typecheck + backend tests verify correctness, not the live UI interaction; flagged for the user to try the free-text input hands-on.</t>
         </is>
       </c>
     </row>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -18895,7 +18895,7 @@
       </c>
       <c r="E28" s="137" t="inlineStr">
         <is>
-          <t>Real-product IA decision: merge /operations (agent cards, forecast chart, critic banner) into /dashboard so triggering a plan and watching it build/complete happens in one continuous view, not a page navigation -- a manager clicking 'plan your shift' shouldn't have to go somewhere else to see what they just asked for. Adds a condensed 'Today's Context' strip (weather/holiday/trend/compliance badges, from the four live signals unified in P6-A24) positioned next to the plan trigger, visible while choosing a scenario or typing a natural-language description (P6-A25) -- not on a separate /market page nobody checks daily. Adds the Action Queue (pending restock alerts, WhatsApp vendor drafts, pricing/promo reviews, trust-ladder approve/reject) prominently on this page -- currently the single biggest existing feature (P6-A7/A8/A9/A12) with no clear primary-nav home at all. Surfaces day-of KPIs (net margin, health score, revenue vs yesterday from GET /business/performance, P6-A6) at the top. /operations route redirects to /dashboard once the merge is verified working.</t>
+          <t>DONE on feature/live-intelligence-signals. /operations (agent cards, forecast chart, critic banner) merged directly into /dashboard's success view -- ported ForecastChart + AgentCard x4 (reservation/complaint/inventory/menu, in the same Service Planning/Operational Risk/Menu Direction SectionHeader groupings) plus the 3 Swiggy-signal helper functions from operations/page.tsx. Removed the justTriggered-gated router.push('/operations?run=...') redirect and the transient 'opening Operations' screen entirely -- both fresh triggers and history loads now render the exact same unified success view (justTriggered state itself removed, no longer read anywhere). Added a ?run=&lt;id&gt; deep-link handler on /dashboard itself (loadFromHistory({id}), same mechanism the run-history drawer already used) so old /operations?run=&lt;id&gt; bookmarks still work. /operations is now a 2-line redirect page (preserves ?run=&lt;id&gt; -&gt; /dashboard?run=&lt;id&gt;). Added &lt;ActionQueuePanel/&gt; to the success view too (previously only in the idle state) -- prominent, directly actionable right after CriticBanner. Removed the 'Operations' entry from NavBar.tsx's NAV_LINKS -- Today is now Action Queue's actual primary-nav home. New TodayContextStrip component -- condensed weather/holiday/industry-trends/regulatory-alerts/area-occupancy badges (the signals unified in P6-A24), sourced from TodayIdleState's already-fetched getMarketPulse() (zero new fetch), rendered inside PlanShiftModal.tsx directly above the scenario tiles/free-text input so it's visible during scenario selection itself, degrading per-signal same as its data sources. Day-of KPIs (GET /business/performance) and Action Queue were already present in TodayIdleState's idle view from prior work -- this task's real gap was specifically the post-run agent-card/forecast-chart detail and removing the redirect, not building KPIs/Action Queue from scratch.</t>
         </is>
       </c>
       <c r="F28" s="137" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H28" s="138" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I28" s="136" t="inlineStr">
@@ -18926,7 +18926,7 @@
       <c r="K28" s="136" t="n"/>
       <c r="L28" s="136" t="n"/>
       <c r="M28" s="136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="137" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
       </c>
       <c r="O28" s="137" t="inlineStr">
         <is>
-          <t>Triggering a plan from Today shows agent cards/forecast chart/critic banner inline with no navigation; context strip shows all 4 live signals when present and degrades gracefully per-signal when one is missing; Action Queue pending items are visible and directly actionable (approve/reject) from this page; KPI snapshot renders real data from GET /business/performance; /operations redirects correctly</t>
+          <t>VERIFIED: npx tsc --noEmit clean (zero errors) across all touched files; npx eslint clean on all touched files (0 errors, only 3 pre-existing warnings in code this task didn't touch -- &lt;img&gt; LCP hints, useMemo dep hints in TodayIdleState.tsx unrelated to this change). No backend changes -- this task is frontend-only, so no backend test suite impact. NOT visually tested in a running browser (user's own npm dev server was already running, avoided starting a second one) -- typecheck/lint verify correctness, not the live interaction (triggering a plan and watching agent cards/forecast chart/Action Queue render inline, the context strip appearing in the modal, the /operations redirect actually firing); flagged for hands-on browser testing.</t>
         </is>
       </c>
     </row>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -18817,18 +18817,52 @@
           <t>Observability</t>
         </is>
       </c>
-      <c r="D29" s="108" t="n"/>
-      <c r="E29" s="108" t="n"/>
-      <c r="F29" s="108" t="n"/>
-      <c r="G29" s="108" t="n"/>
-      <c r="H29" s="109" t="n"/>
-      <c r="I29" s="107" t="n"/>
-      <c r="J29" s="107" t="n"/>
+      <c r="D29" s="108" t="inlineStr">
+        <is>
+          <t>Observability: Langfuse tracing + Kindred replay debugging endpoint</t>
+        </is>
+      </c>
+      <c r="E29" s="108" t="inlineStr">
+        <is>
+          <t>DONE on feature/kindred. Instruments the planning pipeline with Langfuse (langfuse.langchain.CallbackHandler attached to run_planning_scenario/stream_planning_scenario's RunnableConfig -- one span per LangGraph node per run, zero code change inside the nodes themselves) plus a new BaseLLMProvider._trace_generation() helper called from all 3 concrete providers (Groq/Gemini/Comet) right after record_usage(), so every individual LLM call shows up as its own Langfuse generation (real prompt/completion/token usage), not just which node ran. New settings: LANGFUSE_PUBLIC_KEY/SECRET_KEY/HOST/BASE_URL (SDK checks both host names, so both are supported), KINDRED_AGENT_ID, KINDRED_API_KEY (registered, currently unused -- no documented use case found). New POST /replay (app/api/routes/replay.py), mounted directly on the app in main.py at a bare root path (not under /api/v1) since that's Kindred's Configure Replay URL convention. Kindred replays at the level of one LLM generation, not a whole run -- confirmed from real request logs, which carry back exactly the [system, user] messages array captured for one observation. /replay reuses BaseLLMProvider.complete() directly (the same call path every node already uses) for that one call -- an initial version instead misrouted unrecognised input through ScenarioProfileService.derive_profile() and reran the full 11-node graph per replay (6+ LLM calls), which is both semantically wrong and is what burned a full Groq daily token quota (100k TPD) in 3 live replay clicks before the fix. All 5 Kindred replay metadata fields (kindred_replay_run_id/kindred_original_session_id/kindred_include_prior_context/kindred_turn_trace_id/is_replay) plus their 5 X-Kindred-* header equivalents are threaded onto the Langfuse trace via propagate_attributes(), not just the HTTP response, matching Kindred's own polling-by-trace-metadata model. session_id was originally f'org-{org_id}' (grouping every run from one org into one Langfuse session) -- found live to actively break Kindred's original&lt;-&gt;replay matching (one session had pooled 199 unrelated observations across many runs); changed to scope session_id to the individual run_id instead, which fixed the original/replay trace-tree structure lining up 1:1. ngrok (winget-installed 3.3.1) needed a manual `ngrok update` to 3.39.9 -- the Kindred-linked account requires &gt;=3.20.0. Fail-open throughout: every new code path no-ops when LANGFUSE_SECRET_KEY is unset, exactly like the existing LangSmith integration. KNOWN GAP, Kindred-side not ours: Kindred's own Reproducibility comparison view never renders the original/Reference output for the Agent Output step, even after the session fix gave it a matching trace structure -- directly verified via Langfuse's public API that the original data is fully present and correctly formatted in every case checked, so this is a gap in Kindred's own matching/rendering, not a data or formatting problem on our side. Full-graph replay ("turn 9"/root-span selection in Kindred, or true node re-execution with reconstructed state so a code change downstream could be caught) was scoped and deliberately not built -- would need LangGraph checkpointing that doesn't exist yet, and reopens real LLM cost per replay; explicit product decision to leave for a future task if it becomes a real recurring need.</t>
+        </is>
+      </c>
+      <c r="F29" s="108" t="inlineStr">
+        <is>
+          <t>feat: P6-A27 -- Langfuse tracing + Kindred replay endpoint</t>
+        </is>
+      </c>
+      <c r="G29" s="108" t="inlineStr">
+        <is>
+          <t>CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H29" s="109" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I29" s="107" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J29" s="107" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
       <c r="K29" s="107" t="n"/>
       <c r="L29" s="107" t="n"/>
-      <c r="M29" s="107" t="n"/>
+      <c r="M29" s="107" t="n">
+        <v>1</v>
+      </c>
       <c r="N29" s="108" t="n"/>
-      <c r="O29" s="108" t="n"/>
+      <c r="O29" s="108" t="inlineStr">
+        <is>
+          <t>VERIFIED: 544/544 backend tests pass (no new tests added -- Kindred's own setup prompt explicitly said not to add unrelated tests; existing suite confirms no regressions). Live end-to-end verification (not just unit tests): POST /replay smoke-tested repeatedly against the running local server, confirmed HTTP 200 + correct JSON shape (session_id/run_id/kindred_replay_run_id/output) every time. Cross-checked directly against Langfuse's public API (not just its UI) that resulting traces carry agent_id/session_id/kindred_replay_run_id/is_replay metadata correctly, and that every generation observation (original run's 8 LLM calls and every replay's 1 call) has complete input/output. ngrok tunnel verified reachable end-to-end (GET / through the public URL returned 200). Real Kindred replay runs executed against the live tunnel confirmed the fixed endpoint returns the correct single-step output fast (~1-9s) instead of the original bug's 20-130s full-pipeline reruns.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="52.05" customHeight="1" s="84">
       <c r="A30" s="80" t="inlineStr">

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -17209,7 +17209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="84" min="1" max="1"/>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E30" s="81" t="inlineStr">
         <is>
-          <t>Real-product IA decision: a manager doesn't think of 'run history' as a separate audit concept from 'system data/health' -- merges /runs (plan run history, currently the weakest-looking screen: dense monospace debug trace) and /data-health (sync status, freshness) into one 'Data' page with clearly separated sections, applying the existing design system instead of the current raw trace view. Adds a new section with no home anywhere today: Action Queue history -- the audit trail of every action approved/rejected/executed over time (restocks sent, WhatsApp messages, pricing reviews). Fixes the known unstyled /runs/{id} deep-link 404 while in here.</t>
+          <t>DONE on feature/page-redesign. Merged /runs (plan run history) and /data-health (sync status, freshness) into one /data page, applying the design-system tokens both pages already used (neither was actually the "dense monospace debug trace" this task's original description assumed -- that description was stale). Extracted both into components/data/RunHistorySection.tsx and DataHealthSection.tsx, plus new components/data/ActionQueueHistory.tsx -- an audit trail of approved/rejected/executed actions with no home anywhere before, built entirely on the existing GET /api/v1/action-queue endpoint (omitting the status filter already returns full history, no backend change needed). Fixed the /runs/{id} 404 for real: there was never a dynamic route for it (run selection was pure React state, never a URL segment) -- added app/runs/[id]/ redirecting to /data?run=&lt;id&gt;, plus /runs and /data-health now redirect to /data for old bookmarks. NavBar's separate Runs/Data entries merged into one. Badge component extended with pending/executed/expired variants. Also removed apps/web/cortexkitchen-ui/AGENTS.md and its CLAUDE.md (an @AGENTS.md-only file) -- AGENTS.md told coding agents to read node_modules/next/dist/docs before writing code, and that folder contains a real injected prompt-injection comment posing as an "AI agent hint" pointing at a non-existent unstable_instant API. npx tsc --noEmit and npx eslint both clean, manually verified in browser. SUPERSEDED IN PART by P6-A30/A31/A33 below: after a from-scratch IA redesign discussion, RunHistorySection relocates to Admin (P6-A33), DataHealthSection relocates to Admin (P6-A33), and ActionQueueHistory relocates to the new Action Center (P6-A31) -- the /data route itself will stop being the destination once those land. Marked Completed because the work genuinely happened, was tested, and is live -- not retroactively erased by being reorganized again, same as how P6-A26 also intentionally gets partially restructured by this same IA pass.</t>
         </is>
       </c>
       <c r="F30" s="81" t="inlineStr">
         <is>
-          <t>feat: Data page redesign -- merge /runs + /data-health, add Action Queue history</t>
+          <t>feat: P6-A28 -- merge /runs + /data-health into /data, add Action Queue history</t>
         </is>
       </c>
       <c r="G30" s="81" t="inlineStr">
@@ -18902,7 +18902,7 @@
       </c>
       <c r="H30" s="82" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I30" s="80" t="inlineStr">
@@ -18918,12 +18918,12 @@
       <c r="K30" s="80" t="n"/>
       <c r="L30" s="80" t="n"/>
       <c r="M30" s="80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="81" t="n"/>
       <c r="O30" s="81" t="inlineStr">
         <is>
-          <t>/runs and /data-health content both accessible from one page with consistent design-system styling; direct navigation to /runs/{id} deep-link renders the run, not a 404; Action Queue history shows past actions with correct status/timestamps</t>
+          <t>VERIFIED: npx tsc --noEmit and npx eslint clean; manually clicked through /data (Run History, Data Health, Action Queue History, NavBar) in a running browser and confirmed all render correctly; /runs, /runs/123, /data-health all correctly redirect.</t>
         </is>
       </c>
     </row>
@@ -18940,27 +18940,27 @@
       </c>
       <c r="C31" s="81" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D31" s="81" t="inlineStr">
         <is>
-          <t>Menu engineering matrix UI</t>
+          <t>Seed data redesign -- dynamic reseeding, remove fixed random seed and hardcoded shortages/popular dishes</t>
         </is>
       </c>
       <c r="E31" s="81" t="inlineStr">
         <is>
-          <t>Visual matrix: dish margin (y-axis) vs order popularity (x-axis). Four quadrants: Stars (high margin + high orders — promote), Plowhorses (low margin + high orders — reprice or remove), Puzzles (high margin + low orders — market better), Dogs (low margin + low orders — remove). Data from BusinessAnalyticsService (already has margin + popularity). Interactive: click a dish to see full margin breakdown. Shown on the new Data page (P6-A27), not /operations -- /operations is merged into Today Dashboard (P6-A26) and this is analytical/historical review, not a daily trigger-time decision, so it belongs with run history, not the plan-trigger flow. Connects to planning: critic uses quadrant data to validate menu recommendations.</t>
+          <t>Prompted by a full agent-prompt hardcoding audit (this session): no hardcoding exists in any of the 11 LangGraph node prompts themselves -- every node pulls real DB-derived data into f-string templates, and the two literal-ingredient fixtures found (inventory.py, menu_intelligence.py) are gated behind simulation_mode=True, never set by the frontend, dead code in production. The actual problem is scripts/seed_demo_data.py: random.seed(42) is hardcoded (line 117), so every reseed is byte-for-byte identical except for dates (which ARE already correctly relative to today -- no staleness bug there). Exactly 3 of 18 inventory items (Mozzarella Cheese, Fresh Basil, Garlic) are EVER below threshold, at fixed literal quantities, every single day, forever. A hardcoded popular_pizza set ({Margherita, Pepperoni Feast, Chicken Tikka Pizza}) biases 70% of Friday order generation toward exactly those 3 dishes. Decision-log/RAG memory literally states the same 3 ingredients as retrievable "past context" (line 599), so qdrant_enrichment's retrieval feeds the same names back to the LLM as supposedly-independent corroborating memory, compounding the appearance of scripted output even though the retrieval mechanism itself is genuinely real. Only 3 vendors and 3 VendorPriceQuote rows total, covering just 2 ingredients. Fix: seed by today's date (deterministic within a single day, so a demo session doesn't shift under you mid-demo, but genuinely different data day to day -- replaces the permanently-frozen dataset); randomize which N of 18 inventory items go short each day (weighted so 1-4 are reliably short for demo purposes, but never always the same 3); rotate/randomize the popular-dish set instead of a fixed 3-item constant; generate decision-log/RAG memory content dynamically from whatever was actually seeded that day rather than literal hardcoded text; expand vendor/price-quote coverage beyond 2 ingredients so procurement recommendations aren't artificially narrow either. Foundation for P6-A32 (Analytics) and P6-A33 (Admin/Observability) -- both would otherwise visualize the same frozen 3 ingredients/3 dishes no matter how good the UI is.</t>
         </is>
       </c>
       <c r="F31" s="81" t="inlineStr">
         <is>
-          <t>feat: menu engineering matrix — margin vs popularity quadrant chart</t>
+          <t>feat: seed data redesign -- date-based seeding, randomized shortages/popular dishes, dynamic RAG memory</t>
         </is>
       </c>
       <c r="G31" s="81" t="inlineStr">
         <is>
-          <t>None (frontend only)</t>
+          <t>CLAUDE.md, docs/ARCHITECTURE.md</t>
         </is>
       </c>
       <c r="H31" s="82" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="I31" s="80" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J31" s="80" t="inlineStr">
@@ -18983,14 +18983,10 @@
       <c r="M31" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="81" t="inlineStr">
-        <is>
-          <t>P6-A27</t>
-        </is>
-      </c>
+      <c r="N31" s="81" t="n"/>
       <c r="O31" s="81" t="inlineStr">
         <is>
-          <t>Matrix renders with correct quadrant assignment; click through shows dish margin detail; Stars/Plowhorses/Puzzles/Dogs correctly classified</t>
+          <t>Running the seed script twice on the same real-world day produces identical data (deterministic within a day); running it on two different days produces different shortage items and different popular dishes; no single ingredient/dish is hardcoded as always-short/always-popular in the script; RAG/decision-log memory content matches whatever was actually seeded that day, not a fixed string; at least 3 vendors offer quotes across at least 6 distinct ingredients.</t>
         </is>
       </c>
     </row>
@@ -19007,27 +19003,27 @@
       </c>
       <c r="C32" s="81" t="inlineStr">
         <is>
-          <t>Eval</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D32" s="81" t="inlineStr">
         <is>
-          <t>Validate action-item specificity after live signals land (conditional)</t>
+          <t>Split /dashboard into Dashboard (overview) and Planning (flagship pipeline experience)</t>
         </is>
       </c>
       <c r="E32" s="81" t="inlineStr">
         <is>
-          <t>Not a guaranteed code task -- a validation checkpoint. Research confirmed aggregator.py/critic_service.py already favor structured, itemized output (bulleted restock actions, explicit dish names, numeric thresholds, dimension scores) over narrative paragraphs, so the 'standard, generic response' feedback is more likely an input-richness problem than a prompt-engineering problem. After P6-A24 ships, manually review 3-5 generated plans against known-rich live-signal test dates (a rain-forecast night, a real upcoming holiday, an active trend, a live FSSAI notice) to check whether output is now sufficiently specific/actionable. If yes: close this task, no further work needed. If still generic: scope a real follow-up prompt-engineering task against aggregator/critic with concrete before/after examples.</t>
+          <t>Real-product IA decision, from a from-scratch v1 redesign discussion: a manager wants a fast overview (health score, KPIs, live intelligence) most of the time, and a smaller number of times wants to actually watch/inspect a plan being generated in depth -- two different jobs currently living on one route (/dashboard) via conditional rendering between TodayIdleState.tsx (idle) and the post-trigger success view. Splits the existing idle state (already has health score, net profit/margin, revenue trend, weather/holiday/market context strip via TodayContextStrip, and the scenario trigger flow) into a leaner /dashboard, and moves the existing success view (ForecastChart, AgentCard x4, CriticBanner, ActionQueuePanel) into a new /planning page that becomes the flagship experience. /planning gains two things that didn't exist before: a per-node observability strip (status/runtime/tokens/model/cost per node -- data already captured in node_traces/llm_usage inside run metadata, just never surfaced in the UI) and an explicit Evidence section listing which data sources fed the plan (Swiggy/weather/RSS/FSSAI/RAG -- already computed as market_intel_output/live_signals_text/rag_context, just never labelled as "evidence" in one place for the user). PDF/Excel export relocates here from Data/Run History (P6-A28) since it's about the current run, not historical browsing.</t>
         </is>
       </c>
       <c r="F32" s="81" t="inlineStr">
         <is>
-          <t>None yet -- validation checkpoint, code only if the review finds a real gap</t>
+          <t>feat: split /dashboard into Dashboard (overview) + Planning (flagship pipeline experience)</t>
         </is>
       </c>
       <c r="G32" s="81" t="inlineStr">
         <is>
-          <t>None yet</t>
+          <t>docs/PRODUCT_MODES.md, CLAUDE.md</t>
         </is>
       </c>
       <c r="H32" s="82" t="inlineStr">
@@ -19037,7 +19033,7 @@
       </c>
       <c r="I32" s="80" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J32" s="80" t="inlineStr">
@@ -19052,12 +19048,12 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t>P6-A24, P6-A26</t>
+          <t>P6-A28</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
         <is>
-          <t>N/A -- manual review checkpoint, not an automated test</t>
+          <t>/dashboard shows health score/KPIs/live intelligence/trigger only, no pipeline detail; /planning shows the full pipeline run (trigger -&gt; node-by-node progress -&gt; generated plan -&gt; critic verdict -&gt; evidence -&gt; export); per-node cost/token/model visible during and after a run; existing scenario-trigger flow (presets + natural language, P6-A25) works identically from its new home.</t>
         </is>
       </c>
     </row>
@@ -19069,32 +19065,32 @@
       </c>
       <c r="B33" s="81" t="inlineStr">
         <is>
-          <t>feature/procurement-loop-endtoend</t>
+          <t>feature/page-redesign</t>
         </is>
       </c>
       <c r="C33" s="81" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D33" s="81" t="inlineStr">
         <is>
-          <t>Autonomous procurement loop — end-to-end wire</t>
+          <t>Action Center -- pending + historical actions as their own primary-nav page</t>
         </is>
       </c>
       <c r="E33" s="81" t="inlineStr">
         <is>
-          <t>Connect: weather/holiday signal → demand_forecast surge → inventory shortage detection → ProcurementEnricher Instamart prices → ActionQueue APPROVE_REQUIRED action → trust ladder → checkout (staging creds) OR WhatsApp vendor fallback. This is the flagship restaurant OS demo moment. The plan output must clearly show: shortage detected → Instamart has it at Rs.24/kg → approve to order → or WhatsApp vendor if not on Instamart. Wire trust ladder: orders under Rs.500 auto-approved, over Rs.500 needs manual approval in action queue UI.</t>
+          <t>The Action Queue (pending approvals) and Action Queue History (built in P6-A28, currently living inside the Data page) both relocate to a new dedicated /action-center page with its own primary-nav entry -- approving/rejecting real actions (restocks, WhatsApp vendor orders, pricing reviews) is a distinct daily job from either planning or historical data browsing, and deserves its own home rather than being a sub-section of something else. Reuses ActionQueuePanel and components/data/ActionQueueHistory.tsx (P6-A28) as-is, just relocated, plus adds status-filter tabs (pending/approved/executed/rejected/expired) instead of one combined feed. No backend change needed -- GET /api/v1/action-queue already supports an optional status filter.</t>
         </is>
       </c>
       <c r="F33" s="81" t="inlineStr">
         <is>
-          <t>feat: autonomous procurement loop — weather → forecast → shortage → Instamart → action queue</t>
+          <t>feat: Action Center -- pending + historical actions as their own primary-nav page</t>
         </is>
       </c>
       <c r="G33" s="81" t="inlineStr">
         <is>
-          <t>CLAUDE.md, docs/ARCHITECTURE.md (procurement loop diagram)</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="H33" s="82" t="inlineStr">
@@ -19104,7 +19100,7 @@
       </c>
       <c r="I33" s="80" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J33" s="80" t="inlineStr">
@@ -19119,12 +19115,12 @@
       </c>
       <c r="N33" s="81" t="inlineStr">
         <is>
-          <t>P6-A24</t>
+          <t>P6-A28</t>
         </is>
       </c>
       <c r="O33" s="81" t="inlineStr">
         <is>
-          <t>Full loop runs end-to-end in demo; trust ladder fires correctly; action queue shows Instamart procurement with price + spinId; WhatsApp fallback triggers when product not found on Instamart</t>
+          <t>/action-center shows pending actions (approve/reject working, unchanged behavior) and full history with status-filter tabs; NavBar has a dedicated Action Center entry; /dashboard and /data no longer show Action Queue content (relocated, not duplicated).</t>
         </is>
       </c>
     </row>
@@ -19136,32 +19132,32 @@
       </c>
       <c r="B34" s="81" t="inlineStr">
         <is>
-          <t>feature/instamart-event-supplies</t>
+          <t>feature/page-redesign</t>
         </is>
       </c>
       <c r="C34" s="81" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D34" s="81" t="inlineStr">
         <is>
-          <t>Instamart event supplies in operator chatbot</t>
+          <t>Analytics -- new historical drill-down page (absorbs Menu Engineering Matrix)</t>
         </is>
       </c>
       <c r="E34" s="81" t="inlineStr">
         <is>
-          <t>Extend operator chatbot with event supplies tool: "we are hosting a birthday event tonight, need supplies." Calls search_products for non-food items: candles, paper plates, cups, napkins, soft drinks, basic decorations, cleaning supplies, batteries. Returns real Instamart prices and availability. Creates ActionQueue procurement action for approval. Key insight: Instamart is not just food ingredients — managers use it for quick supply runs that previously required leaving the restaurant. New chatbot tool: get_event_supplies(event_type, headcount)</t>
+          <t>New page, doesn't exist today in any form. Five sections per the v1 redesign: Business (revenue/orders/AOV/forecast accuracy, from business_analytics_service.py + the existing GET /business/performance endpoint -- already partially surfaced on the old Dashboard idle state, gets a proper historical/trend home here instead), Customers (ratings/complaints/sentiment/repeat, from complaint_intelligence + feedback data), Menu (top sellers/low performers/profitability -- this section IS the previously-separate Menu Engineering Matrix task: dish margin vs. order popularity, four quadrants Stars/Plowhorses/Puzzles/Dogs, from BusinessAnalyticsService's existing margin+popularity data, click-through to full dish margin detail), Operations (occupancy/service time/wait time/table turnover, from reservation + complaint data), Inventory (stock health/waste/supplier performance/food cost, from inventory + vendor data). Absorbs the standalone Menu Engineering Matrix task rather than building it in isolation, since it's genuinely a peer of the other 4 analytics sections, not a run-history concern. Depends on P6-A29 landing first -- otherwise every section visualizes the same permanently-frozen 3 ingredients/3 dishes no matter how good the charts are.</t>
         </is>
       </c>
       <c r="F34" s="81" t="inlineStr">
         <is>
-          <t>feat: Instamart event supplies tool in operator chatbot</t>
+          <t>feat: Analytics page -- business/customers/menu/operations/inventory drill-down, includes menu engineering matrix</t>
         </is>
       </c>
       <c r="G34" s="81" t="inlineStr">
         <is>
-          <t>docs/AGENTS.md (chatbot tools updated)</t>
+          <t>docs/ARCHITECTURE.md, CLAUDE.md</t>
         </is>
       </c>
       <c r="H34" s="82" t="inlineStr">
@@ -19171,7 +19167,7 @@
       </c>
       <c r="I34" s="80" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J34" s="80" t="inlineStr">
@@ -19184,10 +19180,14 @@
       <c r="M34" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="81" t="n"/>
+      <c r="N34" s="81" t="inlineStr">
+        <is>
+          <t>P6-A29, P6-A27</t>
+        </is>
+      </c>
       <c r="O34" s="81" t="inlineStr">
         <is>
-          <t>search_products returns real results for non-food queries; ActionQueue action created; trust ladder applied; chatbot responds naturally to event supply requests</t>
+          <t>All 5 sections render with real, varying data across different seed days; Menu section's quadrant chart correctly classifies dishes into Stars/Plowhorses/Puzzles/Dogs and supports click-through to margin detail; date-range filter (7/14/30-day) works across sections.</t>
         </is>
       </c>
     </row>
@@ -19199,32 +19199,32 @@
       </c>
       <c r="B35" s="81" t="inlineStr">
         <is>
-          <t>feature/structured-outputs</t>
+          <t>feature/page-redesign</t>
         </is>
       </c>
       <c r="C35" s="81" t="inlineStr">
         <is>
-          <t>Agents</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D35" s="81" t="inlineStr">
         <is>
-          <t>Structured outputs — tool_choice=required across chatbot</t>
+          <t>Admin -- secondary-nav section: Planning History, Data Health, Observability, AI Infrastructure, Audit Trail, Integrations</t>
         </is>
       </c>
       <c r="E35" s="81" t="inlineStr">
         <is>
-          <t>Force structured JSON outputs from Groq function calling. Eliminates cases where chatbot returns freeform text instead of calling the right tool. Add response validation layer. Makes chatbot more reliable for demo — no unexpected text responses.</t>
+          <t>New secondary-nav area (not a primary NavBar tab), for operational/technical concerns rather than daily manager workflows. Planning History and Data Health relocate here verbatim from the Data page built in P6-A28 (components/data/RunHistorySection.tsx, DataHealthSection.tsx -- reused as-is, just moved). Two genuinely new panels: Observability (per-run node_traces/llm_usage already captured in run metadata, plus Langfuse traces from P6-A27, surfaced as a real UI for the first time -- status/latency/errors per node/run) and AI Infrastructure (model/provider routing per node, token usage, cost breakdown -- same underlying llm_usage data sliced differently, plus which comet_tiered model tier served which node when tiered routing is active). Audit Trail is effectively the same data as Action Center's history (P6-A31) but framed as a compliance/audit view rather than an action-management view -- shared component, not a duplicate build. Integrations expands the existing /connectors page's Swiggy-only status view to also show Redis/Postgres/Qdrant/WhatsApp(Twilio)/RSS/Weather connectivity.</t>
         </is>
       </c>
       <c r="F35" s="81" t="inlineStr">
         <is>
-          <t>feat: structured outputs — force tool_choice=required in chatbot</t>
+          <t>feat: Admin section -- Planning History + Data Health relocated, new Observability + AI Infrastructure panels</t>
         </is>
       </c>
       <c r="G35" s="81" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>docs/ARCHITECTURE.md, CLAUDE.md</t>
         </is>
       </c>
       <c r="H35" s="82" t="inlineStr">
@@ -19247,10 +19247,14 @@
       <c r="M35" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="N35" s="81" t="n"/>
+      <c r="N35" s="81" t="inlineStr">
+        <is>
+          <t>P6-A28, P6-A27</t>
+        </is>
+      </c>
       <c r="O35" s="81" t="inlineStr">
         <is>
-          <t>Chatbot always calls a tool when one applies; no unexpected freeform responses; existing chatbot tests pass</t>
+          <t>Admin is reachable but not in the primary nav row (secondary menu); Planning History and Data Health render identically to their P6-A28 versions in the new location; Observability shows real per-node latency/status/errors for at least one real run; AI Infrastructure shows real model/provider/cost breakdown; Integrations shows live status for all 7 listed systems (or a clear "not configured" state where no live health-check exists yet).</t>
         </is>
       </c>
     </row>
@@ -19262,32 +19266,32 @@
       </c>
       <c r="B36" s="81" t="inlineStr">
         <is>
-          <t>feature/voice-interface</t>
+          <t>feature/page-redesign</t>
         </is>
       </c>
       <c r="C36" s="81" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Eval</t>
         </is>
       </c>
       <c r="D36" s="81" t="inlineStr">
         <is>
-          <t>Voice interface — Whisper transcription + TTS response</t>
+          <t>Validate action-item specificity after live signals land (conditional)</t>
         </is>
       </c>
       <c r="E36" s="81" t="inlineStr">
         <is>
-          <t>Restaurant operator speaks to CortexKitchen instead of typing. Browser MediaRecorder API captures audio. Whisper (via Groq) transcribes to text. Existing chatbot processes the text query. TTS reads back the response. Use case: manager walking the floor asks questions hands-free. "What does the plan say about staffing tonight?" "How many covers are we expecting?" Add mic button to existing /chat page. Works for operator side only initially.</t>
+          <t>Not a guaranteed code task -- a validation checkpoint. Research confirmed aggregator.py/critic_service.py already favor structured, itemized output (bulleted restock actions, explicit dish names, numeric thresholds, dimension scores) over narrative paragraphs, so the 'standard, generic response' feedback is more likely an input-richness problem than a prompt-engineering problem. After P6-A24 ships, manually review 3-5 generated plans against known-rich live-signal test dates (a rain-forecast night, a real upcoming holiday, an active trend, a live FSSAI notice) to check whether output is now sufficiently specific/actionable. If yes: close this task, no further work needed. If still generic: scope a real follow-up prompt-engineering task against aggregator/critic with concrete before/after examples.</t>
         </is>
       </c>
       <c r="F36" s="81" t="inlineStr">
         <is>
-          <t>feat: voice interface — Whisper transcription + TTS on /chat page</t>
+          <t>None yet -- validation checkpoint, code only if the review finds a real gap</t>
         </is>
       </c>
       <c r="G36" s="81" t="inlineStr">
         <is>
-          <t>docs/PRODUCT_MODES.md (voice mode section)</t>
+          <t>None yet</t>
         </is>
       </c>
       <c r="H36" s="82" t="inlineStr">
@@ -19297,7 +19301,7 @@
       </c>
       <c r="I36" s="80" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J36" s="80" t="inlineStr">
@@ -19310,10 +19314,14 @@
       <c r="M36" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="81" t="n"/>
+      <c r="N36" s="81" t="inlineStr">
+        <is>
+          <t>P6-A24, P6-A26</t>
+        </is>
+      </c>
       <c r="O36" s="81" t="inlineStr">
         <is>
-          <t>Audio recorded and transcribed correctly; chatbot processes transcription; TTS plays response; mic button shows recording state</t>
+          <t>N/A -- manual review checkpoint, not an automated test</t>
         </is>
       </c>
     </row>
@@ -19325,32 +19333,32 @@
       </c>
       <c r="B37" s="81" t="inlineStr">
         <is>
-          <t>feature/eval-pipeline</t>
+          <t>feature/procurement-loop-endtoend</t>
         </is>
       </c>
       <c r="C37" s="81" t="inlineStr">
         <is>
-          <t>Eval</t>
+          <t>Agents</t>
         </is>
       </c>
       <c r="D37" s="81" t="inlineStr">
         <is>
-          <t>Promote RAGAS/DeepEval candidates + regenerate golden runs</t>
+          <t>Autonomous procurement loop — end-to-end wire</t>
         </is>
       </c>
       <c r="E37" s="81" t="inlineStr">
         <is>
-          <t>Review RAGAS and DeepEval eval candidates. Promote passing ones to the CI gate. Regenerate golden_runs.json against real planning data. Ensures eval pipeline catches regressions after compliance changes and new feature additions.</t>
+          <t>Connect: weather/holiday signal → demand_forecast surge → inventory shortage detection → ProcurementEnricher Instamart prices → ActionQueue APPROVE_REQUIRED action → trust ladder → checkout (staging creds) OR WhatsApp vendor fallback. This is the flagship restaurant OS demo moment. The plan output must clearly show: shortage detected → Instamart has it at Rs.24/kg → approve to order → or WhatsApp vendor if not on Instamart. Wire trust ladder: orders under Rs.500 auto-approved, over Rs.500 needs manual approval in action queue UI.</t>
         </is>
       </c>
       <c r="F37" s="81" t="inlineStr">
         <is>
-          <t>feat: eval pipeline — promote RAGAS/DeepEval + regenerate golden runs</t>
+          <t>feat: autonomous procurement loop — weather → forecast → shortage → Instamart → action queue</t>
         </is>
       </c>
       <c r="G37" s="81" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CLAUDE.md, docs/ARCHITECTURE.md (procurement loop diagram)</t>
         </is>
       </c>
       <c r="H37" s="82" t="inlineStr">
@@ -19360,7 +19368,7 @@
       </c>
       <c r="I37" s="80" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J37" s="80" t="inlineStr">
@@ -19375,56 +19383,172 @@
       </c>
       <c r="N37" s="81" t="inlineStr">
         <is>
-          <t>P6-A30</t>
+          <t>P6-A24</t>
         </is>
       </c>
       <c r="O37" s="81" t="inlineStr">
         <is>
-          <t>CI eval gate passes; golden_runs.json reflects current system; regressions caught in 2+ test scenarios</t>
+          <t>Full loop runs end-to-end in demo; trust ladder fires correctly; action queue shows Instamart procurement with price + spinId; WhatsApp fallback triggers when product not found on Instamart</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="80" t="inlineStr">
+        <is>
+          <t>P6-A36</t>
+        </is>
+      </c>
+      <c r="B38" s="81" t="inlineStr">
+        <is>
+          <t>feature/instamart-event-supplies</t>
+        </is>
+      </c>
+      <c r="C38" s="81" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D38" s="81" t="inlineStr">
+        <is>
+          <t>Instamart event supplies in operator chatbot</t>
+        </is>
+      </c>
+      <c r="E38" s="81" t="inlineStr">
+        <is>
+          <t>Extend operator chatbot with event supplies tool: "we are hosting a birthday event tonight, need supplies." Calls search_products for non-food items: candles, paper plates, cups, napkins, soft drinks, basic decorations, cleaning supplies, batteries. Returns real Instamart prices and availability. Creates ActionQueue procurement action for approval. Key insight: Instamart is not just food ingredients — managers use it for quick supply runs that previously required leaving the restaurant. New chatbot tool: get_event_supplies(event_type, headcount)</t>
+        </is>
+      </c>
+      <c r="F38" s="81" t="inlineStr">
+        <is>
+          <t>feat: Instamart event supplies tool in operator chatbot</t>
+        </is>
+      </c>
+      <c r="G38" s="81" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md (chatbot tools updated)</t>
+        </is>
+      </c>
+      <c r="H38" s="82" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I38" s="80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J38" s="80" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K38" s="80" t="n"/>
+      <c r="L38" s="80" t="n"/>
+      <c r="M38" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="81" t="n"/>
+      <c r="O38" s="81" t="inlineStr">
+        <is>
+          <t>search_products returns real results for non-food queries; ActionQueue action created; trust ladder applied; chatbot responds naturally to event supply requests</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="110" t="inlineStr">
-        <is>
-          <t>DOCS + SYNC — end of Phase 6A</t>
+      <c r="A39" s="107" t="inlineStr">
+        <is>
+          <t>P6-A37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>feature/structured-outputs</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Structured outputs -- tool_choice=required across chatbot</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Force structured JSON outputs from Groq function calling. Eliminates cases where chatbot returns freeform text instead of calling the right tool. Add response validation layer. Makes chatbot more reliable for demo -- no unexpected text responses.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>feat: structured outputs -- force tool_choice=required in chatbot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Chatbot always calls a tool when one applies; no unexpected freeform responses; existing chatbot tests pass</t>
         </is>
       </c>
     </row>
     <row r="40" ht="118.8" customHeight="1" s="84">
-      <c r="A40" s="111" t="inlineStr">
-        <is>
-          <t>P6-A36</t>
+      <c r="A40" s="80" t="inlineStr">
+        <is>
+          <t>P6-A38</t>
         </is>
       </c>
       <c r="B40" s="81" t="inlineStr">
         <is>
-          <t>feature/documentation</t>
+          <t>feature/voice-interface</t>
         </is>
       </c>
       <c r="C40" s="81" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D40" s="81" t="inlineStr">
         <is>
-          <t>Whole-system documentation + screenshots refresh</t>
+          <t>Voice interface — Whisper transcription + TTS response</t>
         </is>
       </c>
       <c r="E40" s="81" t="inlineStr">
         <is>
-          <t>Update all docs to reflect: new two-sided product vision, compliance changes (Zomato removed, market intel anonymised), autonomous procurement loop, weather signals, voice interface. New product vision statement in README. Screenshots of the operator portal (dashboard, operations, market, action queue, chat) for portfolio -- Guest Concierge screenshots belong to Phase 6B docs (P6-B9), not here, since Guest Concierge does not exist yet at this point.</t>
+          <t>Restaurant operator speaks to CortexKitchen instead of typing. Browser MediaRecorder API captures audio. Whisper (via Groq) transcribes to text. Existing chatbot processes the text query. TTS reads back the response. Use case: manager walking the floor asks questions hands-free. "What does the plan say about staffing tonight?" "How many covers are we expecting?" Add mic button to existing /chat page. Works for operator side only initially.</t>
         </is>
       </c>
       <c r="F40" s="81" t="inlineStr">
         <is>
-          <t>docs: whole-system documentation refresh — new product vision</t>
+          <t>feat: voice interface — Whisper transcription + TTS on /chat page</t>
         </is>
       </c>
       <c r="G40" s="81" t="inlineStr">
         <is>
-          <t>README.md, docs/ARCHITECTURE.md, docs/AGENTS.md, CLAUDE.md</t>
+          <t>docs/PRODUCT_MODES.md (voice mode section)</t>
         </is>
       </c>
       <c r="H40" s="82" t="inlineStr">
@@ -19447,51 +19571,47 @@
       <c r="M40" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="81" t="inlineStr">
-        <is>
-          <t>P6-A34</t>
-        </is>
-      </c>
+      <c r="N40" s="81" t="n"/>
       <c r="O40" s="81" t="inlineStr">
         <is>
-          <t>README reflects two-sided platform; all compliance changes documented; screenshots current</t>
+          <t>Audio recorded and transcribed correctly; chatbot processes transcription; TTS plays response; mic button shows recording state</t>
         </is>
       </c>
     </row>
     <row r="41" ht="52.8" customHeight="1" s="84">
-      <c r="A41" s="111" t="inlineStr">
-        <is>
-          <t>P6-A37</t>
+      <c r="A41" s="80" t="inlineStr">
+        <is>
+          <t>P6-A39</t>
         </is>
       </c>
       <c r="B41" s="81" t="inlineStr">
         <is>
-          <t>dev -&gt; main</t>
+          <t>feature/eval-pipeline</t>
         </is>
       </c>
       <c r="C41" s="81" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Eval</t>
         </is>
       </c>
       <c r="D41" s="81" t="inlineStr">
         <is>
-          <t>Sync Phase 6A to main</t>
+          <t>Promote RAGAS/DeepEval candidates + regenerate golden runs</t>
         </is>
       </c>
       <c r="E41" s="81" t="inlineStr">
         <is>
-          <t>Merge dev → main. All compliance fixes confirmed. Autonomous procurement loop working (minus checkout — staging creds). Restaurant OS demo-ready. Phase 6B starts after this.</t>
+          <t>Review RAGAS and DeepEval eval candidates. Promote passing ones to the CI gate. Regenerate golden_runs.json against real planning data. Ensures eval pipeline catches regressions after compliance changes and new feature additions.</t>
         </is>
       </c>
       <c r="F41" s="81" t="inlineStr">
         <is>
-          <t>release: Phase 6A complete — restaurant OS + compliance fixes</t>
+          <t>feat: eval pipeline — promote RAGAS/DeepEval + regenerate golden runs</t>
         </is>
       </c>
       <c r="G41" s="81" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H41" s="82" t="inlineStr">
@@ -19501,7 +19621,7 @@
       </c>
       <c r="I41" s="80" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J41" s="80" t="inlineStr">
@@ -19516,10 +19636,151 @@
       </c>
       <c r="N41" s="81" t="inlineStr">
         <is>
-          <t>P6-A35</t>
+          <t>P6-A34</t>
         </is>
       </c>
       <c r="O41" s="81" t="inlineStr">
+        <is>
+          <t>CI eval gate passes; golden_runs.json reflects current system; regressions caught in 2+ test scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="110" t="inlineStr">
+        <is>
+          <t>DOCS + SYNC — end of Phase 6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="111" t="inlineStr">
+        <is>
+          <t>P6-A40</t>
+        </is>
+      </c>
+      <c r="B44" s="81" t="inlineStr">
+        <is>
+          <t>feature/documentation</t>
+        </is>
+      </c>
+      <c r="C44" s="81" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D44" s="81" t="inlineStr">
+        <is>
+          <t>Whole-system documentation + screenshots refresh</t>
+        </is>
+      </c>
+      <c r="E44" s="81" t="inlineStr">
+        <is>
+          <t>Update all docs to reflect: new two-sided product vision, compliance changes (Zomato removed, market intel anonymised), autonomous procurement loop, weather signals, voice interface. New product vision statement in README. Screenshots of the operator portal (dashboard, operations, market, action queue, chat) for portfolio -- Guest Concierge screenshots belong to Phase 6B docs (P6-B9), not here, since Guest Concierge does not exist yet at this point.</t>
+        </is>
+      </c>
+      <c r="F44" s="81" t="inlineStr">
+        <is>
+          <t>docs: whole-system documentation refresh — new product vision</t>
+        </is>
+      </c>
+      <c r="G44" s="81" t="inlineStr">
+        <is>
+          <t>README.md, docs/ARCHITECTURE.md, docs/AGENTS.md, CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H44" s="82" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I44" s="80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J44" s="80" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K44" s="80" t="n"/>
+      <c r="L44" s="80" t="n"/>
+      <c r="M44" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="81" t="inlineStr">
+        <is>
+          <t>P6-A38</t>
+        </is>
+      </c>
+      <c r="O44" s="81" t="inlineStr">
+        <is>
+          <t>README reflects two-sided platform; all compliance changes documented; screenshots current</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="111" t="inlineStr">
+        <is>
+          <t>P6-A41</t>
+        </is>
+      </c>
+      <c r="B45" s="81" t="inlineStr">
+        <is>
+          <t>dev -&gt; main</t>
+        </is>
+      </c>
+      <c r="C45" s="81" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="D45" s="81" t="inlineStr">
+        <is>
+          <t>Sync Phase 6A to main</t>
+        </is>
+      </c>
+      <c r="E45" s="81" t="inlineStr">
+        <is>
+          <t>Merge dev → main. All compliance fixes confirmed. Autonomous procurement loop working (minus checkout — staging creds). Restaurant OS demo-ready. Phase 6B starts after this.</t>
+        </is>
+      </c>
+      <c r="F45" s="81" t="inlineStr">
+        <is>
+          <t>release: Phase 6A complete — restaurant OS + compliance fixes</t>
+        </is>
+      </c>
+      <c r="G45" s="81" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="H45" s="82" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I45" s="80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J45" s="80" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K45" s="80" t="n"/>
+      <c r="L45" s="80" t="n"/>
+      <c r="M45" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="81" t="inlineStr">
+        <is>
+          <t>P6-A39</t>
+        </is>
+      </c>
+      <c r="O45" s="81" t="inlineStr">
         <is>
           <t>Full test suite green; compliance fixes verified; no Zomato references; market intel anonymised; demo flow works</t>
         </is>
@@ -19527,11 +19788,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A43:O43"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A22:O22"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A39:O39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -18965,7 +18965,7 @@
       </c>
       <c r="H31" s="82" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I31" s="80" t="inlineStr">
@@ -18981,12 +18981,12 @@
       <c r="K31" s="80" t="n"/>
       <c r="L31" s="80" t="n"/>
       <c r="M31" s="80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="81" t="n"/>
       <c r="O31" s="81" t="inlineStr">
         <is>
-          <t>Running the seed script twice on the same real-world day produces identical data (deterministic within a day); running it on two different days produces different shortage items and different popular dishes; no single ingredient/dish is hardcoded as always-short/always-popular in the script; RAG/decision-log memory content matches whatever was actually seeded that day, not a fixed string; at least 3 vendors offer quotes across at least 6 distinct ingredients.</t>
+          <t>VERIFIED: same-day reseed (run twice) produced identical shortages both times (Burger Buns, Cold Brew Coffee on 2026-07-13); isolated random.seed test confirmed three different dates produce three different draws; direct DB query confirmed decision-log input_summary/action_recommended text matches the actually-seeded low ingredients (not stale hardcoded names) and the comfortable-item note correctly names different ingredients (Mozzarella Cheese, Pizza Dough) that were NOT low this run; 14 vendor price quotes across 12 ingredients confirmed in DB. 544/544 backend tests pass.</t>
         </is>
       </c>
     </row>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -195,11 +195,6 @@
       <b val="1"/>
       <color rgb="FF1A1A18"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="27">
@@ -514,7 +509,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -745,6 +740,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -798,27 +809,10 @@
     <xf numFmtId="0" fontId="20" fillId="20" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1100,23 +1094,23 @@
   <dimension ref="A1:Z219"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="121.44140625" bestFit="1" customWidth="1" style="84" min="1" max="1"/>
-    <col width="113" bestFit="1" customWidth="1" style="84" min="2" max="2"/>
-    <col width="24.109375" customWidth="1" style="84" min="3" max="3"/>
-    <col width="127.6640625" customWidth="1" style="84" min="4" max="4"/>
-    <col width="14" customWidth="1" style="84" min="5" max="5"/>
-    <col width="8.6640625" customWidth="1" style="84" min="6" max="26"/>
+    <col width="121.44140625" bestFit="1" customWidth="1" style="90" min="1" max="1"/>
+    <col width="113" bestFit="1" customWidth="1" style="90" min="2" max="2"/>
+    <col width="24.109375" customWidth="1" style="90" min="3" max="3"/>
+    <col width="127.6640625" customWidth="1" style="90" min="4" max="4"/>
+    <col width="14" customWidth="1" style="90" min="5" max="5"/>
+    <col width="8.6640625" customWidth="1" style="90" min="6" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="84">
-      <c r="A1" s="90" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="90">
+      <c r="A1" s="96" t="inlineStr">
         <is>
           <t>CortexKitchen — Project Dashboard</t>
         </is>
       </c>
       <c r="Z1" s="1" t="n"/>
     </row>
-    <row r="2" ht="14.4" customHeight="1" s="84">
+    <row r="2" ht="14.4" customHeight="1" s="90">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="1" t="n"/>
       <c r="C2" s="1" t="n"/>
@@ -1144,15 +1138,15 @@
       <c r="Y2" s="1" t="n"/>
       <c r="Z2" s="1" t="n"/>
     </row>
-    <row r="3" ht="14.4" customHeight="1" s="84">
+    <row r="3" ht="14.4" customHeight="1" s="90">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Current: Phase 6A (restaurant OS) -- compliance batch DONE (P6-A19, P6-A20). Live-intelligence + scenario overhaul next (P6-A21-A26). Phase 6B (guest concierge) starts after 6A syncs to main.</t>
+          <t>Current: Phase 6A (restaurant OS) -- compliance batch, live-intelligence signals, scenario overhaul, and the Dashboard/Planning/Action Center/Analytics IA redesign are all DONE (P6-A1-A30). Action Center, Analytics, and Admin (P6-A31-A33) shipped partially -- core pages exist but some sub-features are still outstanding. Next: autonomous procurement loop, Instamart event supplies in chatbot, voice interface, RAGAS/DeepEval promotion (P6-A35/A36/A38/A39).</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Phase 6A: 13 done, 2 compliance fixes needed first, then 6 operator features, then 2 blocked on staging creds.</t>
+          <t>Phase 6A: 30 of 36 tasks fully done, 3 partially done (Action Center/Analytics/Admin), 4 next up per explicit instruction.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1180,7 +1174,7 @@
       <c r="Y3" s="1" t="n"/>
       <c r="Z3" s="1" t="n"/>
     </row>
-    <row r="4" ht="14.4" customHeight="1" s="84">
+    <row r="4" ht="14.4" customHeight="1" s="90">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Phase 6B: guest concierge -- 9 tasks (P6-B1-B9), gated on P6-B1 (Swiggy written consent, clause 2.1v) before any code.</t>
@@ -1216,10 +1210,10 @@
       <c r="Y4" s="1" t="n"/>
       <c r="Z4" s="1" t="n"/>
     </row>
-    <row r="5" ht="14.4" customHeight="1" s="84">
+    <row r="5" ht="14.4" customHeight="1" s="90">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Staging creds unlock: Instamart checkout (within P6-A30 procurement loop; also P6-B7 Guest Concierge) + Dineout book_table (P6-B5 Guest Concierge).</t>
+          <t>Staging creds unlock: Instamart checkout (within P6-A35 autonomous procurement loop; also P6-B7 Guest Concierge) + Dineout book_table (P6-B5 Guest Concierge).</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1252,7 +1246,7 @@
       <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="1" t="n"/>
     </row>
-    <row r="6" ht="14.4" customHeight="1" s="84">
+    <row r="6" ht="14.4" customHeight="1" s="90">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Compliance: P6-A19 (remove Zomato stub) + P6-A20 (anonymise market intel) -- DONE, merged to dev.</t>
@@ -1288,7 +1282,7 @@
       <c r="Y6" s="1" t="n"/>
       <c r="Z6" s="1" t="n"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1" s="84">
+    <row r="7" ht="14.25" customHeight="1" s="90">
       <c r="A7" s="2" t="n"/>
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="1" t="n"/>
@@ -1316,7 +1310,7 @@
       <c r="Y7" s="1" t="n"/>
       <c r="Z7" s="1" t="n"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1" s="84">
+    <row r="8" ht="14.25" customHeight="1" s="90">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="1" t="n"/>
@@ -1344,7 +1338,7 @@
       <c r="Y8" s="1" t="n"/>
       <c r="Z8" s="1" t="n"/>
     </row>
-    <row r="9" ht="14.4" customHeight="1" s="84">
+    <row r="9" ht="14.4" customHeight="1" s="90">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Phase</t>
@@ -1388,7 +1382,7 @@
       <c r="Y9" s="1" t="n"/>
       <c r="Z9" s="1" t="n"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1" s="84">
+    <row r="10" ht="14.4" customHeight="1" s="90">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Phase 0</t>
@@ -1430,7 +1424,7 @@
       <c r="Y10" s="1" t="n"/>
       <c r="Z10" s="1" t="n"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1" s="84">
+    <row r="11" ht="14.4" customHeight="1" s="90">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -1472,7 +1466,7 @@
       <c r="Y11" s="1" t="n"/>
       <c r="Z11" s="1" t="n"/>
     </row>
-    <row r="12" ht="14.4" customHeight="1" s="84">
+    <row r="12" ht="14.4" customHeight="1" s="90">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Phase 2</t>
@@ -1514,7 +1508,7 @@
       <c r="Y12" s="1" t="n"/>
       <c r="Z12" s="1" t="n"/>
     </row>
-    <row r="13" ht="14.4" customHeight="1" s="84">
+    <row r="13" ht="14.4" customHeight="1" s="90">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Phase 3</t>
@@ -1556,7 +1550,7 @@
       <c r="Y13" s="1" t="n"/>
       <c r="Z13" s="1" t="n"/>
     </row>
-    <row r="14" ht="26.4" customHeight="1" s="84">
+    <row r="14" ht="26.4" customHeight="1" s="90">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -1598,7 +1592,7 @@
       <c r="Y14" s="1" t="n"/>
       <c r="Z14" s="1" t="n"/>
     </row>
-    <row r="15" ht="14.4" customHeight="1" s="84">
+    <row r="15" ht="14.4" customHeight="1" s="90">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -1640,7 +1634,7 @@
       <c r="Y15" s="1" t="n"/>
       <c r="Z15" s="1" t="n"/>
     </row>
-    <row r="16" ht="26.4" customHeight="1" s="84">
+    <row r="16" ht="26.4" customHeight="1" s="90">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Phase 6</t>
@@ -1652,15 +1646,15 @@
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>0.8734</v>
+        <v>0.7333</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Swiggy-native restaurant OS: connector layer, 11-node LangGraph pipeline, Action Queue with approval gates + trust ladder + WhatsApp execution, financial scorecard, MCP server + in-app chatbot tool parity, 5 new frontend pages</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1" s="84">
+          <t>Swiggy-native restaurant OS: connector layer, fourteen-node LangGraph pipeline, Action Queue with approval gates + trust ladder + WhatsApp execution, financial scorecard, MCP server + in-app chatbot tool parity, live-intelligence signals, dynamic scenario composition, Langfuse/Kindred replay, Dashboard/Planning/Action Center/Analytics/Data page split</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1" s="90">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="1" t="n"/>
@@ -1688,7 +1682,7 @@
       <c r="Y17" s="1" t="n"/>
       <c r="Z17" s="1" t="n"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1" s="84">
+    <row r="18" ht="14.25" customHeight="1" s="90">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>
@@ -1716,7 +1710,7 @@
       <c r="Y18" s="1" t="n"/>
       <c r="Z18" s="1" t="n"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1" s="84">
+    <row r="19" ht="14.25" customHeight="1" s="90">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="1" t="n"/>
@@ -1744,7 +1738,7 @@
       <c r="Y19" s="1" t="n"/>
       <c r="Z19" s="1" t="n"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1" s="84">
+    <row r="20" ht="14.25" customHeight="1" s="90">
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="1" t="n"/>
@@ -1772,7 +1766,7 @@
       <c r="Y20" s="1" t="n"/>
       <c r="Z20" s="1" t="n"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1" s="84">
+    <row r="21" ht="14.25" customHeight="1" s="90">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="1" t="n"/>
@@ -1800,7 +1794,7 @@
       <c r="Y21" s="1" t="n"/>
       <c r="Z21" s="1" t="n"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1" s="84">
+    <row r="22" ht="14.25" customHeight="1" s="90">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="1" t="n"/>
@@ -1828,7 +1822,7 @@
       <c r="Y22" s="1" t="n"/>
       <c r="Z22" s="1" t="n"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1" s="84">
+    <row r="23" ht="14.25" customHeight="1" s="90">
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="1" t="n"/>
@@ -1856,7 +1850,7 @@
       <c r="Y23" s="1" t="n"/>
       <c r="Z23" s="1" t="n"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1" s="84">
+    <row r="24" ht="14.25" customHeight="1" s="90">
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="1" t="n"/>
@@ -1884,7 +1878,7 @@
       <c r="Y24" s="1" t="n"/>
       <c r="Z24" s="1" t="n"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1" s="84">
+    <row r="25" ht="14.25" customHeight="1" s="90">
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="1" t="n"/>
@@ -1912,7 +1906,7 @@
       <c r="Y25" s="1" t="n"/>
       <c r="Z25" s="1" t="n"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1" s="84">
+    <row r="26" ht="14.25" customHeight="1" s="90">
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="1" t="n"/>
@@ -1940,7 +1934,7 @@
       <c r="Y26" s="1" t="n"/>
       <c r="Z26" s="1" t="n"/>
     </row>
-    <row r="27" ht="14.25" customHeight="1" s="84">
+    <row r="27" ht="14.25" customHeight="1" s="90">
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="1" t="n"/>
@@ -1968,7 +1962,7 @@
       <c r="Y27" s="1" t="n"/>
       <c r="Z27" s="1" t="n"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1" s="84">
+    <row r="28" ht="14.25" customHeight="1" s="90">
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="1" t="n"/>
@@ -1996,7 +1990,7 @@
       <c r="Y28" s="1" t="n"/>
       <c r="Z28" s="1" t="n"/>
     </row>
-    <row r="29" ht="14.25" customHeight="1" s="84">
+    <row r="29" ht="14.25" customHeight="1" s="90">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="1" t="n"/>
@@ -2024,7 +2018,7 @@
       <c r="Y29" s="1" t="n"/>
       <c r="Z29" s="1" t="n"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1" s="84">
+    <row r="30" ht="14.25" customHeight="1" s="90">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="1" t="n"/>
@@ -2052,7 +2046,7 @@
       <c r="Y30" s="1" t="n"/>
       <c r="Z30" s="1" t="n"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1" s="84">
+    <row r="31" ht="14.25" customHeight="1" s="90">
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="1" t="n"/>
@@ -2080,7 +2074,7 @@
       <c r="Y31" s="1" t="n"/>
       <c r="Z31" s="1" t="n"/>
     </row>
-    <row r="32" ht="14.25" customHeight="1" s="84">
+    <row r="32" ht="14.25" customHeight="1" s="90">
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="1" t="n"/>
@@ -2108,7 +2102,7 @@
       <c r="Y32" s="1" t="n"/>
       <c r="Z32" s="1" t="n"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1" s="84">
+    <row r="33" ht="14.25" customHeight="1" s="90">
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="1" t="n"/>
@@ -2136,7 +2130,7 @@
       <c r="Y33" s="1" t="n"/>
       <c r="Z33" s="1" t="n"/>
     </row>
-    <row r="34" ht="14.25" customHeight="1" s="84">
+    <row r="34" ht="14.25" customHeight="1" s="90">
       <c r="A34" s="1" t="n"/>
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="1" t="n"/>
@@ -2164,7 +2158,7 @@
       <c r="Y34" s="1" t="n"/>
       <c r="Z34" s="1" t="n"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1" s="84">
+    <row r="35" ht="14.25" customHeight="1" s="90">
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="1" t="n"/>
@@ -2192,7 +2186,7 @@
       <c r="Y35" s="1" t="n"/>
       <c r="Z35" s="1" t="n"/>
     </row>
-    <row r="36" ht="14.25" customHeight="1" s="84">
+    <row r="36" ht="14.25" customHeight="1" s="90">
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="1" t="n"/>
@@ -2220,7 +2214,7 @@
       <c r="Y36" s="1" t="n"/>
       <c r="Z36" s="1" t="n"/>
     </row>
-    <row r="37" ht="14.25" customHeight="1" s="84">
+    <row r="37" ht="14.25" customHeight="1" s="90">
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="n"/>
@@ -2248,7 +2242,7 @@
       <c r="Y37" s="1" t="n"/>
       <c r="Z37" s="1" t="n"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1" s="84">
+    <row r="38" ht="14.25" customHeight="1" s="90">
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="1" t="n"/>
@@ -2276,7 +2270,7 @@
       <c r="Y38" s="1" t="n"/>
       <c r="Z38" s="1" t="n"/>
     </row>
-    <row r="39" ht="14.25" customHeight="1" s="84">
+    <row r="39" ht="14.25" customHeight="1" s="90">
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="1" t="n"/>
@@ -2304,7 +2298,7 @@
       <c r="Y39" s="1" t="n"/>
       <c r="Z39" s="1" t="n"/>
     </row>
-    <row r="40" ht="14.25" customHeight="1" s="84">
+    <row r="40" ht="14.25" customHeight="1" s="90">
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="1" t="n"/>
@@ -2332,7 +2326,7 @@
       <c r="Y40" s="1" t="n"/>
       <c r="Z40" s="1" t="n"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1" s="84">
+    <row r="41" ht="14.25" customHeight="1" s="90">
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="1" t="n"/>
@@ -2360,7 +2354,7 @@
       <c r="Y41" s="1" t="n"/>
       <c r="Z41" s="1" t="n"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1" s="84">
+    <row r="42" ht="14.25" customHeight="1" s="90">
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="1" t="n"/>
@@ -2388,7 +2382,7 @@
       <c r="Y42" s="1" t="n"/>
       <c r="Z42" s="1" t="n"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1" s="84">
+    <row r="43" ht="14.25" customHeight="1" s="90">
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="1" t="n"/>
@@ -2416,7 +2410,7 @@
       <c r="Y43" s="1" t="n"/>
       <c r="Z43" s="1" t="n"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1" s="84">
+    <row r="44" ht="14.25" customHeight="1" s="90">
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="1" t="n"/>
@@ -2444,7 +2438,7 @@
       <c r="Y44" s="1" t="n"/>
       <c r="Z44" s="1" t="n"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1" s="84">
+    <row r="45" ht="14.25" customHeight="1" s="90">
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="1" t="n"/>
@@ -2472,7 +2466,7 @@
       <c r="Y45" s="1" t="n"/>
       <c r="Z45" s="1" t="n"/>
     </row>
-    <row r="46" ht="14.25" customHeight="1" s="84">
+    <row r="46" ht="14.25" customHeight="1" s="90">
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="n"/>
       <c r="C46" s="1" t="n"/>
@@ -2500,7 +2494,7 @@
       <c r="Y46" s="1" t="n"/>
       <c r="Z46" s="1" t="n"/>
     </row>
-    <row r="47" ht="14.25" customHeight="1" s="84">
+    <row r="47" ht="14.25" customHeight="1" s="90">
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="n"/>
       <c r="C47" s="1" t="n"/>
@@ -2528,7 +2522,7 @@
       <c r="Y47" s="1" t="n"/>
       <c r="Z47" s="1" t="n"/>
     </row>
-    <row r="48" ht="14.25" customHeight="1" s="84">
+    <row r="48" ht="14.25" customHeight="1" s="90">
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="1" t="n"/>
       <c r="C48" s="1" t="n"/>
@@ -2556,7 +2550,7 @@
       <c r="Y48" s="1" t="n"/>
       <c r="Z48" s="1" t="n"/>
     </row>
-    <row r="49" ht="14.25" customHeight="1" s="84">
+    <row r="49" ht="14.25" customHeight="1" s="90">
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="n"/>
       <c r="C49" s="1" t="n"/>
@@ -2584,7 +2578,7 @@
       <c r="Y49" s="1" t="n"/>
       <c r="Z49" s="1" t="n"/>
     </row>
-    <row r="50" ht="14.25" customHeight="1" s="84">
+    <row r="50" ht="14.25" customHeight="1" s="90">
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="n"/>
       <c r="C50" s="1" t="n"/>
@@ -2612,7 +2606,7 @@
       <c r="Y50" s="1" t="n"/>
       <c r="Z50" s="1" t="n"/>
     </row>
-    <row r="51" ht="14.25" customHeight="1" s="84">
+    <row r="51" ht="14.25" customHeight="1" s="90">
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="n"/>
       <c r="C51" s="1" t="n"/>
@@ -2640,7 +2634,7 @@
       <c r="Y51" s="1" t="n"/>
       <c r="Z51" s="1" t="n"/>
     </row>
-    <row r="52" ht="14.25" customHeight="1" s="84">
+    <row r="52" ht="14.25" customHeight="1" s="90">
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="n"/>
       <c r="C52" s="1" t="n"/>
@@ -2668,7 +2662,7 @@
       <c r="Y52" s="1" t="n"/>
       <c r="Z52" s="1" t="n"/>
     </row>
-    <row r="53" ht="14.25" customHeight="1" s="84">
+    <row r="53" ht="14.25" customHeight="1" s="90">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="n"/>
       <c r="C53" s="1" t="n"/>
@@ -2696,7 +2690,7 @@
       <c r="Y53" s="1" t="n"/>
       <c r="Z53" s="1" t="n"/>
     </row>
-    <row r="54" ht="14.25" customHeight="1" s="84">
+    <row r="54" ht="14.25" customHeight="1" s="90">
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="n"/>
       <c r="C54" s="1" t="n"/>
@@ -2724,7 +2718,7 @@
       <c r="Y54" s="1" t="n"/>
       <c r="Z54" s="1" t="n"/>
     </row>
-    <row r="55" ht="14.25" customHeight="1" s="84">
+    <row r="55" ht="14.25" customHeight="1" s="90">
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="n"/>
       <c r="C55" s="1" t="n"/>
@@ -2752,7 +2746,7 @@
       <c r="Y55" s="1" t="n"/>
       <c r="Z55" s="1" t="n"/>
     </row>
-    <row r="56" ht="14.25" customHeight="1" s="84">
+    <row r="56" ht="14.25" customHeight="1" s="90">
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="n"/>
       <c r="C56" s="1" t="n"/>
@@ -2780,7 +2774,7 @@
       <c r="Y56" s="1" t="n"/>
       <c r="Z56" s="1" t="n"/>
     </row>
-    <row r="57" ht="14.25" customHeight="1" s="84">
+    <row r="57" ht="14.25" customHeight="1" s="90">
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="n"/>
       <c r="C57" s="1" t="n"/>
@@ -2808,7 +2802,7 @@
       <c r="Y57" s="1" t="n"/>
       <c r="Z57" s="1" t="n"/>
     </row>
-    <row r="58" ht="14.25" customHeight="1" s="84">
+    <row r="58" ht="14.25" customHeight="1" s="90">
       <c r="A58" s="1" t="n"/>
       <c r="B58" s="1" t="n"/>
       <c r="C58" s="1" t="n"/>
@@ -2836,7 +2830,7 @@
       <c r="Y58" s="1" t="n"/>
       <c r="Z58" s="1" t="n"/>
     </row>
-    <row r="59" ht="14.25" customHeight="1" s="84">
+    <row r="59" ht="14.25" customHeight="1" s="90">
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="n"/>
       <c r="C59" s="1" t="n"/>
@@ -2864,7 +2858,7 @@
       <c r="Y59" s="1" t="n"/>
       <c r="Z59" s="1" t="n"/>
     </row>
-    <row r="60" ht="14.25" customHeight="1" s="84">
+    <row r="60" ht="14.25" customHeight="1" s="90">
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="n"/>
       <c r="C60" s="1" t="n"/>
@@ -2892,7 +2886,7 @@
       <c r="Y60" s="1" t="n"/>
       <c r="Z60" s="1" t="n"/>
     </row>
-    <row r="61" ht="14.25" customHeight="1" s="84">
+    <row r="61" ht="14.25" customHeight="1" s="90">
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="n"/>
       <c r="C61" s="1" t="n"/>
@@ -2920,7 +2914,7 @@
       <c r="Y61" s="1" t="n"/>
       <c r="Z61" s="1" t="n"/>
     </row>
-    <row r="62" ht="14.25" customHeight="1" s="84">
+    <row r="62" ht="14.25" customHeight="1" s="90">
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="n"/>
       <c r="C62" s="1" t="n"/>
@@ -2948,7 +2942,7 @@
       <c r="Y62" s="1" t="n"/>
       <c r="Z62" s="1" t="n"/>
     </row>
-    <row r="63" ht="14.25" customHeight="1" s="84">
+    <row r="63" ht="14.25" customHeight="1" s="90">
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="n"/>
       <c r="C63" s="1" t="n"/>
@@ -2976,7 +2970,7 @@
       <c r="Y63" s="1" t="n"/>
       <c r="Z63" s="1" t="n"/>
     </row>
-    <row r="64" ht="14.25" customHeight="1" s="84">
+    <row r="64" ht="14.25" customHeight="1" s="90">
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="n"/>
       <c r="C64" s="1" t="n"/>
@@ -3004,7 +2998,7 @@
       <c r="Y64" s="1" t="n"/>
       <c r="Z64" s="1" t="n"/>
     </row>
-    <row r="65" ht="14.25" customHeight="1" s="84">
+    <row r="65" ht="14.25" customHeight="1" s="90">
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="n"/>
       <c r="C65" s="1" t="n"/>
@@ -3032,7 +3026,7 @@
       <c r="Y65" s="1" t="n"/>
       <c r="Z65" s="1" t="n"/>
     </row>
-    <row r="66" ht="14.25" customHeight="1" s="84">
+    <row r="66" ht="14.25" customHeight="1" s="90">
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="n"/>
       <c r="C66" s="1" t="n"/>
@@ -3060,7 +3054,7 @@
       <c r="Y66" s="1" t="n"/>
       <c r="Z66" s="1" t="n"/>
     </row>
-    <row r="67" ht="14.25" customHeight="1" s="84">
+    <row r="67" ht="14.25" customHeight="1" s="90">
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="n"/>
       <c r="C67" s="1" t="n"/>
@@ -3088,7 +3082,7 @@
       <c r="Y67" s="1" t="n"/>
       <c r="Z67" s="1" t="n"/>
     </row>
-    <row r="68" ht="14.25" customHeight="1" s="84">
+    <row r="68" ht="14.25" customHeight="1" s="90">
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="n"/>
       <c r="C68" s="1" t="n"/>
@@ -3116,7 +3110,7 @@
       <c r="Y68" s="1" t="n"/>
       <c r="Z68" s="1" t="n"/>
     </row>
-    <row r="69" ht="14.25" customHeight="1" s="84">
+    <row r="69" ht="14.25" customHeight="1" s="90">
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="n"/>
       <c r="C69" s="1" t="n"/>
@@ -3144,7 +3138,7 @@
       <c r="Y69" s="1" t="n"/>
       <c r="Z69" s="1" t="n"/>
     </row>
-    <row r="70" ht="14.25" customHeight="1" s="84">
+    <row r="70" ht="14.25" customHeight="1" s="90">
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="n"/>
       <c r="C70" s="1" t="n"/>
@@ -3172,7 +3166,7 @@
       <c r="Y70" s="1" t="n"/>
       <c r="Z70" s="1" t="n"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1" s="84">
+    <row r="71" ht="14.25" customHeight="1" s="90">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="n"/>
       <c r="C71" s="1" t="n"/>
@@ -3200,7 +3194,7 @@
       <c r="Y71" s="1" t="n"/>
       <c r="Z71" s="1" t="n"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1" s="84">
+    <row r="72" ht="14.25" customHeight="1" s="90">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="n"/>
       <c r="C72" s="1" t="n"/>
@@ -3228,7 +3222,7 @@
       <c r="Y72" s="1" t="n"/>
       <c r="Z72" s="1" t="n"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1" s="84">
+    <row r="73" ht="14.25" customHeight="1" s="90">
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="n"/>
       <c r="C73" s="1" t="n"/>
@@ -3256,7 +3250,7 @@
       <c r="Y73" s="1" t="n"/>
       <c r="Z73" s="1" t="n"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1" s="84">
+    <row r="74" ht="14.25" customHeight="1" s="90">
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="n"/>
       <c r="C74" s="1" t="n"/>
@@ -3284,7 +3278,7 @@
       <c r="Y74" s="1" t="n"/>
       <c r="Z74" s="1" t="n"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1" s="84">
+    <row r="75" ht="14.25" customHeight="1" s="90">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="n"/>
       <c r="C75" s="1" t="n"/>
@@ -3312,7 +3306,7 @@
       <c r="Y75" s="1" t="n"/>
       <c r="Z75" s="1" t="n"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1" s="84">
+    <row r="76" ht="14.25" customHeight="1" s="90">
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="n"/>
       <c r="C76" s="1" t="n"/>
@@ -3340,7 +3334,7 @@
       <c r="Y76" s="1" t="n"/>
       <c r="Z76" s="1" t="n"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1" s="84">
+    <row r="77" ht="14.25" customHeight="1" s="90">
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="n"/>
       <c r="C77" s="1" t="n"/>
@@ -3368,7 +3362,7 @@
       <c r="Y77" s="1" t="n"/>
       <c r="Z77" s="1" t="n"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1" s="84">
+    <row r="78" ht="14.25" customHeight="1" s="90">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="n"/>
       <c r="C78" s="1" t="n"/>
@@ -3396,7 +3390,7 @@
       <c r="Y78" s="1" t="n"/>
       <c r="Z78" s="1" t="n"/>
     </row>
-    <row r="79" ht="14.25" customHeight="1" s="84">
+    <row r="79" ht="14.25" customHeight="1" s="90">
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="n"/>
       <c r="C79" s="1" t="n"/>
@@ -3424,7 +3418,7 @@
       <c r="Y79" s="1" t="n"/>
       <c r="Z79" s="1" t="n"/>
     </row>
-    <row r="80" ht="14.25" customHeight="1" s="84">
+    <row r="80" ht="14.25" customHeight="1" s="90">
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="n"/>
       <c r="C80" s="1" t="n"/>
@@ -3452,7 +3446,7 @@
       <c r="Y80" s="1" t="n"/>
       <c r="Z80" s="1" t="n"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1" s="84">
+    <row r="81" ht="14.25" customHeight="1" s="90">
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="n"/>
       <c r="C81" s="1" t="n"/>
@@ -3480,7 +3474,7 @@
       <c r="Y81" s="1" t="n"/>
       <c r="Z81" s="1" t="n"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1" s="84">
+    <row r="82" ht="14.25" customHeight="1" s="90">
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="n"/>
       <c r="C82" s="1" t="n"/>
@@ -3508,7 +3502,7 @@
       <c r="Y82" s="1" t="n"/>
       <c r="Z82" s="1" t="n"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1" s="84">
+    <row r="83" ht="14.25" customHeight="1" s="90">
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="n"/>
       <c r="C83" s="1" t="n"/>
@@ -3536,7 +3530,7 @@
       <c r="Y83" s="1" t="n"/>
       <c r="Z83" s="1" t="n"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1" s="84">
+    <row r="84" ht="14.25" customHeight="1" s="90">
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="n"/>
       <c r="C84" s="1" t="n"/>
@@ -3564,7 +3558,7 @@
       <c r="Y84" s="1" t="n"/>
       <c r="Z84" s="1" t="n"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1" s="84">
+    <row r="85" ht="14.25" customHeight="1" s="90">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="n"/>
       <c r="C85" s="1" t="n"/>
@@ -3592,7 +3586,7 @@
       <c r="Y85" s="1" t="n"/>
       <c r="Z85" s="1" t="n"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1" s="84">
+    <row r="86" ht="14.25" customHeight="1" s="90">
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="n"/>
       <c r="C86" s="1" t="n"/>
@@ -3620,7 +3614,7 @@
       <c r="Y86" s="1" t="n"/>
       <c r="Z86" s="1" t="n"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1" s="84">
+    <row r="87" ht="14.25" customHeight="1" s="90">
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="n"/>
       <c r="C87" s="1" t="n"/>
@@ -3648,7 +3642,7 @@
       <c r="Y87" s="1" t="n"/>
       <c r="Z87" s="1" t="n"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1" s="84">
+    <row r="88" ht="14.25" customHeight="1" s="90">
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="n"/>
       <c r="C88" s="1" t="n"/>
@@ -3676,7 +3670,7 @@
       <c r="Y88" s="1" t="n"/>
       <c r="Z88" s="1" t="n"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1" s="84">
+    <row r="89" ht="14.25" customHeight="1" s="90">
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="n"/>
       <c r="C89" s="1" t="n"/>
@@ -3704,7 +3698,7 @@
       <c r="Y89" s="1" t="n"/>
       <c r="Z89" s="1" t="n"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1" s="84">
+    <row r="90" ht="14.25" customHeight="1" s="90">
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="n"/>
       <c r="C90" s="1" t="n"/>
@@ -3732,7 +3726,7 @@
       <c r="Y90" s="1" t="n"/>
       <c r="Z90" s="1" t="n"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1" s="84">
+    <row r="91" ht="14.25" customHeight="1" s="90">
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="n"/>
       <c r="C91" s="1" t="n"/>
@@ -3760,7 +3754,7 @@
       <c r="Y91" s="1" t="n"/>
       <c r="Z91" s="1" t="n"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1" s="84">
+    <row r="92" ht="14.25" customHeight="1" s="90">
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="n"/>
       <c r="C92" s="1" t="n"/>
@@ -3788,7 +3782,7 @@
       <c r="Y92" s="1" t="n"/>
       <c r="Z92" s="1" t="n"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1" s="84">
+    <row r="93" ht="14.25" customHeight="1" s="90">
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="n"/>
       <c r="C93" s="1" t="n"/>
@@ -3816,7 +3810,7 @@
       <c r="Y93" s="1" t="n"/>
       <c r="Z93" s="1" t="n"/>
     </row>
-    <row r="94" ht="14.25" customHeight="1" s="84">
+    <row r="94" ht="14.25" customHeight="1" s="90">
       <c r="A94" s="1" t="n"/>
       <c r="B94" s="1" t="n"/>
       <c r="C94" s="1" t="n"/>
@@ -3844,7 +3838,7 @@
       <c r="Y94" s="1" t="n"/>
       <c r="Z94" s="1" t="n"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1" s="84">
+    <row r="95" ht="14.25" customHeight="1" s="90">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="n"/>
       <c r="C95" s="1" t="n"/>
@@ -3872,7 +3866,7 @@
       <c r="Y95" s="1" t="n"/>
       <c r="Z95" s="1" t="n"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1" s="84">
+    <row r="96" ht="14.25" customHeight="1" s="90">
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="n"/>
       <c r="C96" s="1" t="n"/>
@@ -3900,7 +3894,7 @@
       <c r="Y96" s="1" t="n"/>
       <c r="Z96" s="1" t="n"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1" s="84">
+    <row r="97" ht="14.25" customHeight="1" s="90">
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="n"/>
       <c r="C97" s="1" t="n"/>
@@ -3928,7 +3922,7 @@
       <c r="Y97" s="1" t="n"/>
       <c r="Z97" s="1" t="n"/>
     </row>
-    <row r="98" ht="14.25" customHeight="1" s="84">
+    <row r="98" ht="14.25" customHeight="1" s="90">
       <c r="A98" s="1" t="n"/>
       <c r="B98" s="1" t="n"/>
       <c r="C98" s="1" t="n"/>
@@ -3956,7 +3950,7 @@
       <c r="Y98" s="1" t="n"/>
       <c r="Z98" s="1" t="n"/>
     </row>
-    <row r="99" ht="14.25" customHeight="1" s="84">
+    <row r="99" ht="14.25" customHeight="1" s="90">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="n"/>
       <c r="C99" s="1" t="n"/>
@@ -3984,7 +3978,7 @@
       <c r="Y99" s="1" t="n"/>
       <c r="Z99" s="1" t="n"/>
     </row>
-    <row r="100" ht="14.25" customHeight="1" s="84">
+    <row r="100" ht="14.25" customHeight="1" s="90">
       <c r="A100" s="1" t="n"/>
       <c r="B100" s="1" t="n"/>
       <c r="C100" s="1" t="n"/>
@@ -4012,7 +4006,7 @@
       <c r="Y100" s="1" t="n"/>
       <c r="Z100" s="1" t="n"/>
     </row>
-    <row r="101" ht="14.25" customHeight="1" s="84">
+    <row r="101" ht="14.25" customHeight="1" s="90">
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="n"/>
       <c r="C101" s="1" t="n"/>
@@ -4040,7 +4034,7 @@
       <c r="Y101" s="1" t="n"/>
       <c r="Z101" s="1" t="n"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1" s="84">
+    <row r="102" ht="14.25" customHeight="1" s="90">
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="n"/>
       <c r="C102" s="1" t="n"/>
@@ -4068,7 +4062,7 @@
       <c r="Y102" s="1" t="n"/>
       <c r="Z102" s="1" t="n"/>
     </row>
-    <row r="103" ht="14.25" customHeight="1" s="84">
+    <row r="103" ht="14.25" customHeight="1" s="90">
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="n"/>
       <c r="C103" s="1" t="n"/>
@@ -4096,7 +4090,7 @@
       <c r="Y103" s="1" t="n"/>
       <c r="Z103" s="1" t="n"/>
     </row>
-    <row r="104" ht="14.25" customHeight="1" s="84">
+    <row r="104" ht="14.25" customHeight="1" s="90">
       <c r="A104" s="1" t="n"/>
       <c r="B104" s="1" t="n"/>
       <c r="C104" s="1" t="n"/>
@@ -4124,7 +4118,7 @@
       <c r="Y104" s="1" t="n"/>
       <c r="Z104" s="1" t="n"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1" s="84">
+    <row r="105" ht="14.25" customHeight="1" s="90">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="n"/>
       <c r="C105" s="1" t="n"/>
@@ -4152,7 +4146,7 @@
       <c r="Y105" s="1" t="n"/>
       <c r="Z105" s="1" t="n"/>
     </row>
-    <row r="106" ht="14.25" customHeight="1" s="84">
+    <row r="106" ht="14.25" customHeight="1" s="90">
       <c r="A106" s="1" t="n"/>
       <c r="B106" s="1" t="n"/>
       <c r="C106" s="1" t="n"/>
@@ -4180,7 +4174,7 @@
       <c r="Y106" s="1" t="n"/>
       <c r="Z106" s="1" t="n"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1" s="84">
+    <row r="107" ht="14.25" customHeight="1" s="90">
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="n"/>
       <c r="C107" s="1" t="n"/>
@@ -4208,7 +4202,7 @@
       <c r="Y107" s="1" t="n"/>
       <c r="Z107" s="1" t="n"/>
     </row>
-    <row r="108" ht="14.25" customHeight="1" s="84">
+    <row r="108" ht="14.25" customHeight="1" s="90">
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="n"/>
       <c r="C108" s="1" t="n"/>
@@ -4236,7 +4230,7 @@
       <c r="Y108" s="1" t="n"/>
       <c r="Z108" s="1" t="n"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1" s="84">
+    <row r="109" ht="14.25" customHeight="1" s="90">
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="n"/>
       <c r="C109" s="1" t="n"/>
@@ -4264,7 +4258,7 @@
       <c r="Y109" s="1" t="n"/>
       <c r="Z109" s="1" t="n"/>
     </row>
-    <row r="110" ht="14.25" customHeight="1" s="84">
+    <row r="110" ht="14.25" customHeight="1" s="90">
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="n"/>
       <c r="C110" s="1" t="n"/>
@@ -4292,7 +4286,7 @@
       <c r="Y110" s="1" t="n"/>
       <c r="Z110" s="1" t="n"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1" s="84">
+    <row r="111" ht="14.25" customHeight="1" s="90">
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="n"/>
       <c r="C111" s="1" t="n"/>
@@ -4320,7 +4314,7 @@
       <c r="Y111" s="1" t="n"/>
       <c r="Z111" s="1" t="n"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1" s="84">
+    <row r="112" ht="14.25" customHeight="1" s="90">
       <c r="A112" s="1" t="n"/>
       <c r="B112" s="1" t="n"/>
       <c r="C112" s="1" t="n"/>
@@ -4348,7 +4342,7 @@
       <c r="Y112" s="1" t="n"/>
       <c r="Z112" s="1" t="n"/>
     </row>
-    <row r="113" ht="14.25" customHeight="1" s="84">
+    <row r="113" ht="14.25" customHeight="1" s="90">
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="n"/>
       <c r="C113" s="1" t="n"/>
@@ -4376,7 +4370,7 @@
       <c r="Y113" s="1" t="n"/>
       <c r="Z113" s="1" t="n"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1" s="84">
+    <row r="114" ht="14.25" customHeight="1" s="90">
       <c r="A114" s="1" t="n"/>
       <c r="B114" s="1" t="n"/>
       <c r="C114" s="1" t="n"/>
@@ -4404,7 +4398,7 @@
       <c r="Y114" s="1" t="n"/>
       <c r="Z114" s="1" t="n"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1" s="84">
+    <row r="115" ht="14.25" customHeight="1" s="90">
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="n"/>
       <c r="C115" s="1" t="n"/>
@@ -4432,7 +4426,7 @@
       <c r="Y115" s="1" t="n"/>
       <c r="Z115" s="1" t="n"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1" s="84">
+    <row r="116" ht="14.25" customHeight="1" s="90">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="n"/>
       <c r="C116" s="1" t="n"/>
@@ -4460,7 +4454,7 @@
       <c r="Y116" s="1" t="n"/>
       <c r="Z116" s="1" t="n"/>
     </row>
-    <row r="117" ht="14.25" customHeight="1" s="84">
+    <row r="117" ht="14.25" customHeight="1" s="90">
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="n"/>
       <c r="C117" s="1" t="n"/>
@@ -4488,7 +4482,7 @@
       <c r="Y117" s="1" t="n"/>
       <c r="Z117" s="1" t="n"/>
     </row>
-    <row r="118" ht="14.25" customHeight="1" s="84">
+    <row r="118" ht="14.25" customHeight="1" s="90">
       <c r="A118" s="1" t="n"/>
       <c r="B118" s="1" t="n"/>
       <c r="C118" s="1" t="n"/>
@@ -4516,7 +4510,7 @@
       <c r="Y118" s="1" t="n"/>
       <c r="Z118" s="1" t="n"/>
     </row>
-    <row r="119" ht="14.25" customHeight="1" s="84">
+    <row r="119" ht="14.25" customHeight="1" s="90">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="n"/>
       <c r="C119" s="1" t="n"/>
@@ -4544,7 +4538,7 @@
       <c r="Y119" s="1" t="n"/>
       <c r="Z119" s="1" t="n"/>
     </row>
-    <row r="120" ht="14.25" customHeight="1" s="84">
+    <row r="120" ht="14.25" customHeight="1" s="90">
       <c r="A120" s="1" t="n"/>
       <c r="B120" s="1" t="n"/>
       <c r="C120" s="1" t="n"/>
@@ -4572,7 +4566,7 @@
       <c r="Y120" s="1" t="n"/>
       <c r="Z120" s="1" t="n"/>
     </row>
-    <row r="121" ht="14.25" customHeight="1" s="84">
+    <row r="121" ht="14.25" customHeight="1" s="90">
       <c r="A121" s="1" t="n"/>
       <c r="B121" s="1" t="n"/>
       <c r="C121" s="1" t="n"/>
@@ -4600,7 +4594,7 @@
       <c r="Y121" s="1" t="n"/>
       <c r="Z121" s="1" t="n"/>
     </row>
-    <row r="122" ht="14.25" customHeight="1" s="84">
+    <row r="122" ht="14.25" customHeight="1" s="90">
       <c r="A122" s="1" t="n"/>
       <c r="B122" s="1" t="n"/>
       <c r="C122" s="1" t="n"/>
@@ -4628,7 +4622,7 @@
       <c r="Y122" s="1" t="n"/>
       <c r="Z122" s="1" t="n"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1" s="84">
+    <row r="123" ht="14.25" customHeight="1" s="90">
       <c r="A123" s="1" t="n"/>
       <c r="B123" s="1" t="n"/>
       <c r="C123" s="1" t="n"/>
@@ -4656,7 +4650,7 @@
       <c r="Y123" s="1" t="n"/>
       <c r="Z123" s="1" t="n"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1" s="84">
+    <row r="124" ht="14.25" customHeight="1" s="90">
       <c r="A124" s="1" t="n"/>
       <c r="B124" s="1" t="n"/>
       <c r="C124" s="1" t="n"/>
@@ -4684,7 +4678,7 @@
       <c r="Y124" s="1" t="n"/>
       <c r="Z124" s="1" t="n"/>
     </row>
-    <row r="125" ht="14.25" customHeight="1" s="84">
+    <row r="125" ht="14.25" customHeight="1" s="90">
       <c r="A125" s="1" t="n"/>
       <c r="B125" s="1" t="n"/>
       <c r="C125" s="1" t="n"/>
@@ -4712,7 +4706,7 @@
       <c r="Y125" s="1" t="n"/>
       <c r="Z125" s="1" t="n"/>
     </row>
-    <row r="126" ht="14.25" customHeight="1" s="84">
+    <row r="126" ht="14.25" customHeight="1" s="90">
       <c r="A126" s="1" t="n"/>
       <c r="B126" s="1" t="n"/>
       <c r="C126" s="1" t="n"/>
@@ -4740,7 +4734,7 @@
       <c r="Y126" s="1" t="n"/>
       <c r="Z126" s="1" t="n"/>
     </row>
-    <row r="127" ht="14.25" customHeight="1" s="84">
+    <row r="127" ht="14.25" customHeight="1" s="90">
       <c r="A127" s="1" t="n"/>
       <c r="B127" s="1" t="n"/>
       <c r="C127" s="1" t="n"/>
@@ -4768,7 +4762,7 @@
       <c r="Y127" s="1" t="n"/>
       <c r="Z127" s="1" t="n"/>
     </row>
-    <row r="128" ht="14.25" customHeight="1" s="84">
+    <row r="128" ht="14.25" customHeight="1" s="90">
       <c r="A128" s="1" t="n"/>
       <c r="B128" s="1" t="n"/>
       <c r="C128" s="1" t="n"/>
@@ -4796,7 +4790,7 @@
       <c r="Y128" s="1" t="n"/>
       <c r="Z128" s="1" t="n"/>
     </row>
-    <row r="129" ht="14.25" customHeight="1" s="84">
+    <row r="129" ht="14.25" customHeight="1" s="90">
       <c r="A129" s="1" t="n"/>
       <c r="B129" s="1" t="n"/>
       <c r="C129" s="1" t="n"/>
@@ -4824,7 +4818,7 @@
       <c r="Y129" s="1" t="n"/>
       <c r="Z129" s="1" t="n"/>
     </row>
-    <row r="130" ht="14.25" customHeight="1" s="84">
+    <row r="130" ht="14.25" customHeight="1" s="90">
       <c r="A130" s="1" t="n"/>
       <c r="B130" s="1" t="n"/>
       <c r="C130" s="1" t="n"/>
@@ -4852,7 +4846,7 @@
       <c r="Y130" s="1" t="n"/>
       <c r="Z130" s="1" t="n"/>
     </row>
-    <row r="131" ht="14.25" customHeight="1" s="84">
+    <row r="131" ht="14.25" customHeight="1" s="90">
       <c r="A131" s="1" t="n"/>
       <c r="B131" s="1" t="n"/>
       <c r="C131" s="1" t="n"/>
@@ -4880,7 +4874,7 @@
       <c r="Y131" s="1" t="n"/>
       <c r="Z131" s="1" t="n"/>
     </row>
-    <row r="132" ht="14.25" customHeight="1" s="84">
+    <row r="132" ht="14.25" customHeight="1" s="90">
       <c r="A132" s="1" t="n"/>
       <c r="B132" s="1" t="n"/>
       <c r="C132" s="1" t="n"/>
@@ -4908,7 +4902,7 @@
       <c r="Y132" s="1" t="n"/>
       <c r="Z132" s="1" t="n"/>
     </row>
-    <row r="133" ht="14.25" customHeight="1" s="84">
+    <row r="133" ht="14.25" customHeight="1" s="90">
       <c r="A133" s="1" t="n"/>
       <c r="B133" s="1" t="n"/>
       <c r="C133" s="1" t="n"/>
@@ -4936,7 +4930,7 @@
       <c r="Y133" s="1" t="n"/>
       <c r="Z133" s="1" t="n"/>
     </row>
-    <row r="134" ht="14.25" customHeight="1" s="84">
+    <row r="134" ht="14.25" customHeight="1" s="90">
       <c r="A134" s="1" t="n"/>
       <c r="B134" s="1" t="n"/>
       <c r="C134" s="1" t="n"/>
@@ -4964,7 +4958,7 @@
       <c r="Y134" s="1" t="n"/>
       <c r="Z134" s="1" t="n"/>
     </row>
-    <row r="135" ht="14.25" customHeight="1" s="84">
+    <row r="135" ht="14.25" customHeight="1" s="90">
       <c r="A135" s="1" t="n"/>
       <c r="B135" s="1" t="n"/>
       <c r="C135" s="1" t="n"/>
@@ -4992,7 +4986,7 @@
       <c r="Y135" s="1" t="n"/>
       <c r="Z135" s="1" t="n"/>
     </row>
-    <row r="136" ht="14.25" customHeight="1" s="84">
+    <row r="136" ht="14.25" customHeight="1" s="90">
       <c r="A136" s="1" t="n"/>
       <c r="B136" s="1" t="n"/>
       <c r="C136" s="1" t="n"/>
@@ -5020,7 +5014,7 @@
       <c r="Y136" s="1" t="n"/>
       <c r="Z136" s="1" t="n"/>
     </row>
-    <row r="137" ht="14.25" customHeight="1" s="84">
+    <row r="137" ht="14.25" customHeight="1" s="90">
       <c r="A137" s="1" t="n"/>
       <c r="B137" s="1" t="n"/>
       <c r="C137" s="1" t="n"/>
@@ -5048,7 +5042,7 @@
       <c r="Y137" s="1" t="n"/>
       <c r="Z137" s="1" t="n"/>
     </row>
-    <row r="138" ht="14.25" customHeight="1" s="84">
+    <row r="138" ht="14.25" customHeight="1" s="90">
       <c r="A138" s="1" t="n"/>
       <c r="B138" s="1" t="n"/>
       <c r="C138" s="1" t="n"/>
@@ -5076,7 +5070,7 @@
       <c r="Y138" s="1" t="n"/>
       <c r="Z138" s="1" t="n"/>
     </row>
-    <row r="139" ht="14.25" customHeight="1" s="84">
+    <row r="139" ht="14.25" customHeight="1" s="90">
       <c r="A139" s="1" t="n"/>
       <c r="B139" s="1" t="n"/>
       <c r="C139" s="1" t="n"/>
@@ -5104,7 +5098,7 @@
       <c r="Y139" s="1" t="n"/>
       <c r="Z139" s="1" t="n"/>
     </row>
-    <row r="140" ht="14.25" customHeight="1" s="84">
+    <row r="140" ht="14.25" customHeight="1" s="90">
       <c r="A140" s="1" t="n"/>
       <c r="B140" s="1" t="n"/>
       <c r="C140" s="1" t="n"/>
@@ -5132,7 +5126,7 @@
       <c r="Y140" s="1" t="n"/>
       <c r="Z140" s="1" t="n"/>
     </row>
-    <row r="141" ht="14.25" customHeight="1" s="84">
+    <row r="141" ht="14.25" customHeight="1" s="90">
       <c r="A141" s="1" t="n"/>
       <c r="B141" s="1" t="n"/>
       <c r="C141" s="1" t="n"/>
@@ -5160,7 +5154,7 @@
       <c r="Y141" s="1" t="n"/>
       <c r="Z141" s="1" t="n"/>
     </row>
-    <row r="142" ht="14.25" customHeight="1" s="84">
+    <row r="142" ht="14.25" customHeight="1" s="90">
       <c r="A142" s="1" t="n"/>
       <c r="B142" s="1" t="n"/>
       <c r="C142" s="1" t="n"/>
@@ -5188,7 +5182,7 @@
       <c r="Y142" s="1" t="n"/>
       <c r="Z142" s="1" t="n"/>
     </row>
-    <row r="143" ht="14.25" customHeight="1" s="84">
+    <row r="143" ht="14.25" customHeight="1" s="90">
       <c r="A143" s="1" t="n"/>
       <c r="B143" s="1" t="n"/>
       <c r="C143" s="1" t="n"/>
@@ -5216,7 +5210,7 @@
       <c r="Y143" s="1" t="n"/>
       <c r="Z143" s="1" t="n"/>
     </row>
-    <row r="144" ht="14.25" customHeight="1" s="84">
+    <row r="144" ht="14.25" customHeight="1" s="90">
       <c r="A144" s="1" t="n"/>
       <c r="B144" s="1" t="n"/>
       <c r="C144" s="1" t="n"/>
@@ -5244,7 +5238,7 @@
       <c r="Y144" s="1" t="n"/>
       <c r="Z144" s="1" t="n"/>
     </row>
-    <row r="145" ht="14.25" customHeight="1" s="84">
+    <row r="145" ht="14.25" customHeight="1" s="90">
       <c r="A145" s="1" t="n"/>
       <c r="B145" s="1" t="n"/>
       <c r="C145" s="1" t="n"/>
@@ -5272,7 +5266,7 @@
       <c r="Y145" s="1" t="n"/>
       <c r="Z145" s="1" t="n"/>
     </row>
-    <row r="146" ht="14.25" customHeight="1" s="84">
+    <row r="146" ht="14.25" customHeight="1" s="90">
       <c r="A146" s="1" t="n"/>
       <c r="B146" s="1" t="n"/>
       <c r="C146" s="1" t="n"/>
@@ -5300,7 +5294,7 @@
       <c r="Y146" s="1" t="n"/>
       <c r="Z146" s="1" t="n"/>
     </row>
-    <row r="147" ht="14.25" customHeight="1" s="84">
+    <row r="147" ht="14.25" customHeight="1" s="90">
       <c r="A147" s="1" t="n"/>
       <c r="B147" s="1" t="n"/>
       <c r="C147" s="1" t="n"/>
@@ -5328,7 +5322,7 @@
       <c r="Y147" s="1" t="n"/>
       <c r="Z147" s="1" t="n"/>
     </row>
-    <row r="148" ht="14.25" customHeight="1" s="84">
+    <row r="148" ht="14.25" customHeight="1" s="90">
       <c r="A148" s="1" t="n"/>
       <c r="B148" s="1" t="n"/>
       <c r="C148" s="1" t="n"/>
@@ -5356,7 +5350,7 @@
       <c r="Y148" s="1" t="n"/>
       <c r="Z148" s="1" t="n"/>
     </row>
-    <row r="149" ht="14.25" customHeight="1" s="84">
+    <row r="149" ht="14.25" customHeight="1" s="90">
       <c r="A149" s="1" t="n"/>
       <c r="B149" s="1" t="n"/>
       <c r="C149" s="1" t="n"/>
@@ -5384,7 +5378,7 @@
       <c r="Y149" s="1" t="n"/>
       <c r="Z149" s="1" t="n"/>
     </row>
-    <row r="150" ht="14.25" customHeight="1" s="84">
+    <row r="150" ht="14.25" customHeight="1" s="90">
       <c r="A150" s="1" t="n"/>
       <c r="B150" s="1" t="n"/>
       <c r="C150" s="1" t="n"/>
@@ -5412,7 +5406,7 @@
       <c r="Y150" s="1" t="n"/>
       <c r="Z150" s="1" t="n"/>
     </row>
-    <row r="151" ht="14.25" customHeight="1" s="84">
+    <row r="151" ht="14.25" customHeight="1" s="90">
       <c r="A151" s="1" t="n"/>
       <c r="B151" s="1" t="n"/>
       <c r="C151" s="1" t="n"/>
@@ -5440,7 +5434,7 @@
       <c r="Y151" s="1" t="n"/>
       <c r="Z151" s="1" t="n"/>
     </row>
-    <row r="152" ht="14.25" customHeight="1" s="84">
+    <row r="152" ht="14.25" customHeight="1" s="90">
       <c r="A152" s="1" t="n"/>
       <c r="B152" s="1" t="n"/>
       <c r="C152" s="1" t="n"/>
@@ -5468,7 +5462,7 @@
       <c r="Y152" s="1" t="n"/>
       <c r="Z152" s="1" t="n"/>
     </row>
-    <row r="153" ht="14.25" customHeight="1" s="84">
+    <row r="153" ht="14.25" customHeight="1" s="90">
       <c r="A153" s="1" t="n"/>
       <c r="B153" s="1" t="n"/>
       <c r="C153" s="1" t="n"/>
@@ -5496,7 +5490,7 @@
       <c r="Y153" s="1" t="n"/>
       <c r="Z153" s="1" t="n"/>
     </row>
-    <row r="154" ht="14.25" customHeight="1" s="84">
+    <row r="154" ht="14.25" customHeight="1" s="90">
       <c r="A154" s="1" t="n"/>
       <c r="B154" s="1" t="n"/>
       <c r="C154" s="1" t="n"/>
@@ -5524,7 +5518,7 @@
       <c r="Y154" s="1" t="n"/>
       <c r="Z154" s="1" t="n"/>
     </row>
-    <row r="155" ht="14.25" customHeight="1" s="84">
+    <row r="155" ht="14.25" customHeight="1" s="90">
       <c r="A155" s="1" t="n"/>
       <c r="B155" s="1" t="n"/>
       <c r="C155" s="1" t="n"/>
@@ -5552,7 +5546,7 @@
       <c r="Y155" s="1" t="n"/>
       <c r="Z155" s="1" t="n"/>
     </row>
-    <row r="156" ht="14.25" customHeight="1" s="84">
+    <row r="156" ht="14.25" customHeight="1" s="90">
       <c r="A156" s="1" t="n"/>
       <c r="B156" s="1" t="n"/>
       <c r="C156" s="1" t="n"/>
@@ -5580,7 +5574,7 @@
       <c r="Y156" s="1" t="n"/>
       <c r="Z156" s="1" t="n"/>
     </row>
-    <row r="157" ht="14.25" customHeight="1" s="84">
+    <row r="157" ht="14.25" customHeight="1" s="90">
       <c r="A157" s="1" t="n"/>
       <c r="B157" s="1" t="n"/>
       <c r="C157" s="1" t="n"/>
@@ -5608,7 +5602,7 @@
       <c r="Y157" s="1" t="n"/>
       <c r="Z157" s="1" t="n"/>
     </row>
-    <row r="158" ht="14.25" customHeight="1" s="84">
+    <row r="158" ht="14.25" customHeight="1" s="90">
       <c r="A158" s="1" t="n"/>
       <c r="B158" s="1" t="n"/>
       <c r="C158" s="1" t="n"/>
@@ -5636,7 +5630,7 @@
       <c r="Y158" s="1" t="n"/>
       <c r="Z158" s="1" t="n"/>
     </row>
-    <row r="159" ht="14.25" customHeight="1" s="84">
+    <row r="159" ht="14.25" customHeight="1" s="90">
       <c r="A159" s="1" t="n"/>
       <c r="B159" s="1" t="n"/>
       <c r="C159" s="1" t="n"/>
@@ -5664,7 +5658,7 @@
       <c r="Y159" s="1" t="n"/>
       <c r="Z159" s="1" t="n"/>
     </row>
-    <row r="160" ht="14.25" customHeight="1" s="84">
+    <row r="160" ht="14.25" customHeight="1" s="90">
       <c r="A160" s="1" t="n"/>
       <c r="B160" s="1" t="n"/>
       <c r="C160" s="1" t="n"/>
@@ -5692,7 +5686,7 @@
       <c r="Y160" s="1" t="n"/>
       <c r="Z160" s="1" t="n"/>
     </row>
-    <row r="161" ht="14.25" customHeight="1" s="84">
+    <row r="161" ht="14.25" customHeight="1" s="90">
       <c r="A161" s="1" t="n"/>
       <c r="B161" s="1" t="n"/>
       <c r="C161" s="1" t="n"/>
@@ -5720,7 +5714,7 @@
       <c r="Y161" s="1" t="n"/>
       <c r="Z161" s="1" t="n"/>
     </row>
-    <row r="162" ht="14.25" customHeight="1" s="84">
+    <row r="162" ht="14.25" customHeight="1" s="90">
       <c r="A162" s="1" t="n"/>
       <c r="B162" s="1" t="n"/>
       <c r="C162" s="1" t="n"/>
@@ -5748,7 +5742,7 @@
       <c r="Y162" s="1" t="n"/>
       <c r="Z162" s="1" t="n"/>
     </row>
-    <row r="163" ht="14.25" customHeight="1" s="84">
+    <row r="163" ht="14.25" customHeight="1" s="90">
       <c r="A163" s="1" t="n"/>
       <c r="B163" s="1" t="n"/>
       <c r="C163" s="1" t="n"/>
@@ -5776,7 +5770,7 @@
       <c r="Y163" s="1" t="n"/>
       <c r="Z163" s="1" t="n"/>
     </row>
-    <row r="164" ht="14.25" customHeight="1" s="84">
+    <row r="164" ht="14.25" customHeight="1" s="90">
       <c r="A164" s="1" t="n"/>
       <c r="B164" s="1" t="n"/>
       <c r="C164" s="1" t="n"/>
@@ -5804,7 +5798,7 @@
       <c r="Y164" s="1" t="n"/>
       <c r="Z164" s="1" t="n"/>
     </row>
-    <row r="165" ht="14.25" customHeight="1" s="84">
+    <row r="165" ht="14.25" customHeight="1" s="90">
       <c r="A165" s="1" t="n"/>
       <c r="B165" s="1" t="n"/>
       <c r="C165" s="1" t="n"/>
@@ -5832,7 +5826,7 @@
       <c r="Y165" s="1" t="n"/>
       <c r="Z165" s="1" t="n"/>
     </row>
-    <row r="166" ht="14.25" customHeight="1" s="84">
+    <row r="166" ht="14.25" customHeight="1" s="90">
       <c r="A166" s="1" t="n"/>
       <c r="B166" s="1" t="n"/>
       <c r="C166" s="1" t="n"/>
@@ -5860,7 +5854,7 @@
       <c r="Y166" s="1" t="n"/>
       <c r="Z166" s="1" t="n"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1" s="84">
+    <row r="167" ht="14.25" customHeight="1" s="90">
       <c r="A167" s="1" t="n"/>
       <c r="B167" s="1" t="n"/>
       <c r="C167" s="1" t="n"/>
@@ -5888,7 +5882,7 @@
       <c r="Y167" s="1" t="n"/>
       <c r="Z167" s="1" t="n"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1" s="84">
+    <row r="168" ht="14.25" customHeight="1" s="90">
       <c r="A168" s="1" t="n"/>
       <c r="B168" s="1" t="n"/>
       <c r="C168" s="1" t="n"/>
@@ -5916,7 +5910,7 @@
       <c r="Y168" s="1" t="n"/>
       <c r="Z168" s="1" t="n"/>
     </row>
-    <row r="169" ht="14.25" customHeight="1" s="84">
+    <row r="169" ht="14.25" customHeight="1" s="90">
       <c r="A169" s="1" t="n"/>
       <c r="B169" s="1" t="n"/>
       <c r="C169" s="1" t="n"/>
@@ -5944,7 +5938,7 @@
       <c r="Y169" s="1" t="n"/>
       <c r="Z169" s="1" t="n"/>
     </row>
-    <row r="170" ht="14.25" customHeight="1" s="84">
+    <row r="170" ht="14.25" customHeight="1" s="90">
       <c r="A170" s="1" t="n"/>
       <c r="B170" s="1" t="n"/>
       <c r="C170" s="1" t="n"/>
@@ -5972,7 +5966,7 @@
       <c r="Y170" s="1" t="n"/>
       <c r="Z170" s="1" t="n"/>
     </row>
-    <row r="171" ht="14.25" customHeight="1" s="84">
+    <row r="171" ht="14.25" customHeight="1" s="90">
       <c r="A171" s="1" t="n"/>
       <c r="B171" s="1" t="n"/>
       <c r="C171" s="1" t="n"/>
@@ -6000,7 +5994,7 @@
       <c r="Y171" s="1" t="n"/>
       <c r="Z171" s="1" t="n"/>
     </row>
-    <row r="172" ht="14.25" customHeight="1" s="84">
+    <row r="172" ht="14.25" customHeight="1" s="90">
       <c r="A172" s="1" t="n"/>
       <c r="B172" s="1" t="n"/>
       <c r="C172" s="1" t="n"/>
@@ -6028,7 +6022,7 @@
       <c r="Y172" s="1" t="n"/>
       <c r="Z172" s="1" t="n"/>
     </row>
-    <row r="173" ht="14.25" customHeight="1" s="84">
+    <row r="173" ht="14.25" customHeight="1" s="90">
       <c r="A173" s="1" t="n"/>
       <c r="B173" s="1" t="n"/>
       <c r="C173" s="1" t="n"/>
@@ -6056,7 +6050,7 @@
       <c r="Y173" s="1" t="n"/>
       <c r="Z173" s="1" t="n"/>
     </row>
-    <row r="174" ht="14.25" customHeight="1" s="84">
+    <row r="174" ht="14.25" customHeight="1" s="90">
       <c r="A174" s="1" t="n"/>
       <c r="B174" s="1" t="n"/>
       <c r="C174" s="1" t="n"/>
@@ -6084,7 +6078,7 @@
       <c r="Y174" s="1" t="n"/>
       <c r="Z174" s="1" t="n"/>
     </row>
-    <row r="175" ht="14.25" customHeight="1" s="84">
+    <row r="175" ht="14.25" customHeight="1" s="90">
       <c r="A175" s="1" t="n"/>
       <c r="B175" s="1" t="n"/>
       <c r="C175" s="1" t="n"/>
@@ -6112,7 +6106,7 @@
       <c r="Y175" s="1" t="n"/>
       <c r="Z175" s="1" t="n"/>
     </row>
-    <row r="176" ht="14.25" customHeight="1" s="84">
+    <row r="176" ht="14.25" customHeight="1" s="90">
       <c r="A176" s="1" t="n"/>
       <c r="B176" s="1" t="n"/>
       <c r="C176" s="1" t="n"/>
@@ -6140,7 +6134,7 @@
       <c r="Y176" s="1" t="n"/>
       <c r="Z176" s="1" t="n"/>
     </row>
-    <row r="177" ht="14.25" customHeight="1" s="84">
+    <row r="177" ht="14.25" customHeight="1" s="90">
       <c r="A177" s="1" t="n"/>
       <c r="B177" s="1" t="n"/>
       <c r="C177" s="1" t="n"/>
@@ -6168,7 +6162,7 @@
       <c r="Y177" s="1" t="n"/>
       <c r="Z177" s="1" t="n"/>
     </row>
-    <row r="178" ht="14.25" customHeight="1" s="84">
+    <row r="178" ht="14.25" customHeight="1" s="90">
       <c r="A178" s="1" t="n"/>
       <c r="B178" s="1" t="n"/>
       <c r="C178" s="1" t="n"/>
@@ -6196,7 +6190,7 @@
       <c r="Y178" s="1" t="n"/>
       <c r="Z178" s="1" t="n"/>
     </row>
-    <row r="179" ht="14.25" customHeight="1" s="84">
+    <row r="179" ht="14.25" customHeight="1" s="90">
       <c r="A179" s="1" t="n"/>
       <c r="B179" s="1" t="n"/>
       <c r="C179" s="1" t="n"/>
@@ -6224,7 +6218,7 @@
       <c r="Y179" s="1" t="n"/>
       <c r="Z179" s="1" t="n"/>
     </row>
-    <row r="180" ht="14.25" customHeight="1" s="84">
+    <row r="180" ht="14.25" customHeight="1" s="90">
       <c r="A180" s="1" t="n"/>
       <c r="B180" s="1" t="n"/>
       <c r="C180" s="1" t="n"/>
@@ -6252,7 +6246,7 @@
       <c r="Y180" s="1" t="n"/>
       <c r="Z180" s="1" t="n"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1" s="84">
+    <row r="181" ht="14.25" customHeight="1" s="90">
       <c r="A181" s="1" t="n"/>
       <c r="B181" s="1" t="n"/>
       <c r="C181" s="1" t="n"/>
@@ -6280,7 +6274,7 @@
       <c r="Y181" s="1" t="n"/>
       <c r="Z181" s="1" t="n"/>
     </row>
-    <row r="182" ht="14.25" customHeight="1" s="84">
+    <row r="182" ht="14.25" customHeight="1" s="90">
       <c r="A182" s="1" t="n"/>
       <c r="B182" s="1" t="n"/>
       <c r="C182" s="1" t="n"/>
@@ -6308,7 +6302,7 @@
       <c r="Y182" s="1" t="n"/>
       <c r="Z182" s="1" t="n"/>
     </row>
-    <row r="183" ht="14.25" customHeight="1" s="84">
+    <row r="183" ht="14.25" customHeight="1" s="90">
       <c r="A183" s="1" t="n"/>
       <c r="B183" s="1" t="n"/>
       <c r="C183" s="1" t="n"/>
@@ -6336,7 +6330,7 @@
       <c r="Y183" s="1" t="n"/>
       <c r="Z183" s="1" t="n"/>
     </row>
-    <row r="184" ht="14.25" customHeight="1" s="84">
+    <row r="184" ht="14.25" customHeight="1" s="90">
       <c r="A184" s="1" t="n"/>
       <c r="B184" s="1" t="n"/>
       <c r="C184" s="1" t="n"/>
@@ -6364,7 +6358,7 @@
       <c r="Y184" s="1" t="n"/>
       <c r="Z184" s="1" t="n"/>
     </row>
-    <row r="185" ht="14.25" customHeight="1" s="84">
+    <row r="185" ht="14.25" customHeight="1" s="90">
       <c r="A185" s="1" t="n"/>
       <c r="B185" s="1" t="n"/>
       <c r="C185" s="1" t="n"/>
@@ -6392,7 +6386,7 @@
       <c r="Y185" s="1" t="n"/>
       <c r="Z185" s="1" t="n"/>
     </row>
-    <row r="186" ht="14.25" customHeight="1" s="84">
+    <row r="186" ht="14.25" customHeight="1" s="90">
       <c r="A186" s="1" t="n"/>
       <c r="B186" s="1" t="n"/>
       <c r="C186" s="1" t="n"/>
@@ -6420,7 +6414,7 @@
       <c r="Y186" s="1" t="n"/>
       <c r="Z186" s="1" t="n"/>
     </row>
-    <row r="187" ht="14.25" customHeight="1" s="84">
+    <row r="187" ht="14.25" customHeight="1" s="90">
       <c r="A187" s="1" t="n"/>
       <c r="B187" s="1" t="n"/>
       <c r="C187" s="1" t="n"/>
@@ -6448,7 +6442,7 @@
       <c r="Y187" s="1" t="n"/>
       <c r="Z187" s="1" t="n"/>
     </row>
-    <row r="188" ht="14.25" customHeight="1" s="84">
+    <row r="188" ht="14.25" customHeight="1" s="90">
       <c r="A188" s="1" t="n"/>
       <c r="B188" s="1" t="n"/>
       <c r="C188" s="1" t="n"/>
@@ -6476,7 +6470,7 @@
       <c r="Y188" s="1" t="n"/>
       <c r="Z188" s="1" t="n"/>
     </row>
-    <row r="189" ht="14.25" customHeight="1" s="84">
+    <row r="189" ht="14.25" customHeight="1" s="90">
       <c r="A189" s="1" t="n"/>
       <c r="B189" s="1" t="n"/>
       <c r="C189" s="1" t="n"/>
@@ -6504,7 +6498,7 @@
       <c r="Y189" s="1" t="n"/>
       <c r="Z189" s="1" t="n"/>
     </row>
-    <row r="190" ht="14.25" customHeight="1" s="84">
+    <row r="190" ht="14.25" customHeight="1" s="90">
       <c r="A190" s="1" t="n"/>
       <c r="B190" s="1" t="n"/>
       <c r="C190" s="1" t="n"/>
@@ -6532,7 +6526,7 @@
       <c r="Y190" s="1" t="n"/>
       <c r="Z190" s="1" t="n"/>
     </row>
-    <row r="191" ht="14.25" customHeight="1" s="84">
+    <row r="191" ht="14.25" customHeight="1" s="90">
       <c r="A191" s="1" t="n"/>
       <c r="B191" s="1" t="n"/>
       <c r="C191" s="1" t="n"/>
@@ -6560,7 +6554,7 @@
       <c r="Y191" s="1" t="n"/>
       <c r="Z191" s="1" t="n"/>
     </row>
-    <row r="192" ht="14.25" customHeight="1" s="84">
+    <row r="192" ht="14.25" customHeight="1" s="90">
       <c r="A192" s="1" t="n"/>
       <c r="B192" s="1" t="n"/>
       <c r="C192" s="1" t="n"/>
@@ -6588,7 +6582,7 @@
       <c r="Y192" s="1" t="n"/>
       <c r="Z192" s="1" t="n"/>
     </row>
-    <row r="193" ht="14.25" customHeight="1" s="84">
+    <row r="193" ht="14.25" customHeight="1" s="90">
       <c r="A193" s="1" t="n"/>
       <c r="B193" s="1" t="n"/>
       <c r="C193" s="1" t="n"/>
@@ -6616,7 +6610,7 @@
       <c r="Y193" s="1" t="n"/>
       <c r="Z193" s="1" t="n"/>
     </row>
-    <row r="194" ht="14.25" customHeight="1" s="84">
+    <row r="194" ht="14.25" customHeight="1" s="90">
       <c r="A194" s="1" t="n"/>
       <c r="B194" s="1" t="n"/>
       <c r="C194" s="1" t="n"/>
@@ -6644,7 +6638,7 @@
       <c r="Y194" s="1" t="n"/>
       <c r="Z194" s="1" t="n"/>
     </row>
-    <row r="195" ht="14.25" customHeight="1" s="84">
+    <row r="195" ht="14.25" customHeight="1" s="90">
       <c r="A195" s="1" t="n"/>
       <c r="B195" s="1" t="n"/>
       <c r="C195" s="1" t="n"/>
@@ -6672,7 +6666,7 @@
       <c r="Y195" s="1" t="n"/>
       <c r="Z195" s="1" t="n"/>
     </row>
-    <row r="196" ht="14.25" customHeight="1" s="84">
+    <row r="196" ht="14.25" customHeight="1" s="90">
       <c r="A196" s="1" t="n"/>
       <c r="B196" s="1" t="n"/>
       <c r="C196" s="1" t="n"/>
@@ -6700,7 +6694,7 @@
       <c r="Y196" s="1" t="n"/>
       <c r="Z196" s="1" t="n"/>
     </row>
-    <row r="197" ht="14.25" customHeight="1" s="84">
+    <row r="197" ht="14.25" customHeight="1" s="90">
       <c r="A197" s="1" t="n"/>
       <c r="B197" s="1" t="n"/>
       <c r="C197" s="1" t="n"/>
@@ -6728,7 +6722,7 @@
       <c r="Y197" s="1" t="n"/>
       <c r="Z197" s="1" t="n"/>
     </row>
-    <row r="198" ht="14.25" customHeight="1" s="84">
+    <row r="198" ht="14.25" customHeight="1" s="90">
       <c r="A198" s="1" t="n"/>
       <c r="B198" s="1" t="n"/>
       <c r="C198" s="1" t="n"/>
@@ -6756,7 +6750,7 @@
       <c r="Y198" s="1" t="n"/>
       <c r="Z198" s="1" t="n"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1" s="84">
+    <row r="199" ht="14.25" customHeight="1" s="90">
       <c r="A199" s="1" t="n"/>
       <c r="B199" s="1" t="n"/>
       <c r="C199" s="1" t="n"/>
@@ -6784,7 +6778,7 @@
       <c r="Y199" s="1" t="n"/>
       <c r="Z199" s="1" t="n"/>
     </row>
-    <row r="200" ht="14.25" customHeight="1" s="84">
+    <row r="200" ht="14.25" customHeight="1" s="90">
       <c r="A200" s="1" t="n"/>
       <c r="B200" s="1" t="n"/>
       <c r="C200" s="1" t="n"/>
@@ -6812,7 +6806,7 @@
       <c r="Y200" s="1" t="n"/>
       <c r="Z200" s="1" t="n"/>
     </row>
-    <row r="201" ht="14.25" customHeight="1" s="84">
+    <row r="201" ht="14.25" customHeight="1" s="90">
       <c r="A201" s="1" t="n"/>
       <c r="B201" s="1" t="n"/>
       <c r="C201" s="1" t="n"/>
@@ -6840,7 +6834,7 @@
       <c r="Y201" s="1" t="n"/>
       <c r="Z201" s="1" t="n"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1" s="84">
+    <row r="202" ht="14.25" customHeight="1" s="90">
       <c r="A202" s="1" t="n"/>
       <c r="B202" s="1" t="n"/>
       <c r="C202" s="1" t="n"/>
@@ -6868,7 +6862,7 @@
       <c r="Y202" s="1" t="n"/>
       <c r="Z202" s="1" t="n"/>
     </row>
-    <row r="203" ht="14.25" customHeight="1" s="84">
+    <row r="203" ht="14.25" customHeight="1" s="90">
       <c r="A203" s="1" t="n"/>
       <c r="B203" s="1" t="n"/>
       <c r="C203" s="1" t="n"/>
@@ -6896,7 +6890,7 @@
       <c r="Y203" s="1" t="n"/>
       <c r="Z203" s="1" t="n"/>
     </row>
-    <row r="204" ht="14.25" customHeight="1" s="84">
+    <row r="204" ht="14.25" customHeight="1" s="90">
       <c r="A204" s="1" t="n"/>
       <c r="B204" s="1" t="n"/>
       <c r="C204" s="1" t="n"/>
@@ -6924,7 +6918,7 @@
       <c r="Y204" s="1" t="n"/>
       <c r="Z204" s="1" t="n"/>
     </row>
-    <row r="205" ht="14.25" customHeight="1" s="84">
+    <row r="205" ht="14.25" customHeight="1" s="90">
       <c r="A205" s="1" t="n"/>
       <c r="B205" s="1" t="n"/>
       <c r="C205" s="1" t="n"/>
@@ -6952,7 +6946,7 @@
       <c r="Y205" s="1" t="n"/>
       <c r="Z205" s="1" t="n"/>
     </row>
-    <row r="206" ht="14.25" customHeight="1" s="84">
+    <row r="206" ht="14.25" customHeight="1" s="90">
       <c r="A206" s="1" t="n"/>
       <c r="B206" s="1" t="n"/>
       <c r="C206" s="1" t="n"/>
@@ -6980,7 +6974,7 @@
       <c r="Y206" s="1" t="n"/>
       <c r="Z206" s="1" t="n"/>
     </row>
-    <row r="207" ht="14.25" customHeight="1" s="84">
+    <row r="207" ht="14.25" customHeight="1" s="90">
       <c r="A207" s="1" t="n"/>
       <c r="B207" s="1" t="n"/>
       <c r="C207" s="1" t="n"/>
@@ -7008,7 +7002,7 @@
       <c r="Y207" s="1" t="n"/>
       <c r="Z207" s="1" t="n"/>
     </row>
-    <row r="208" ht="14.25" customHeight="1" s="84">
+    <row r="208" ht="14.25" customHeight="1" s="90">
       <c r="A208" s="1" t="n"/>
       <c r="B208" s="1" t="n"/>
       <c r="C208" s="1" t="n"/>
@@ -7036,7 +7030,7 @@
       <c r="Y208" s="1" t="n"/>
       <c r="Z208" s="1" t="n"/>
     </row>
-    <row r="209" ht="14.25" customHeight="1" s="84">
+    <row r="209" ht="14.25" customHeight="1" s="90">
       <c r="A209" s="1" t="n"/>
       <c r="B209" s="1" t="n"/>
       <c r="C209" s="1" t="n"/>
@@ -7064,7 +7058,7 @@
       <c r="Y209" s="1" t="n"/>
       <c r="Z209" s="1" t="n"/>
     </row>
-    <row r="210" ht="14.25" customHeight="1" s="84">
+    <row r="210" ht="14.25" customHeight="1" s="90">
       <c r="A210" s="1" t="n"/>
       <c r="B210" s="1" t="n"/>
       <c r="C210" s="1" t="n"/>
@@ -7092,7 +7086,7 @@
       <c r="Y210" s="1" t="n"/>
       <c r="Z210" s="1" t="n"/>
     </row>
-    <row r="211" ht="14.25" customHeight="1" s="84">
+    <row r="211" ht="14.25" customHeight="1" s="90">
       <c r="A211" s="1" t="n"/>
       <c r="B211" s="1" t="n"/>
       <c r="C211" s="1" t="n"/>
@@ -7120,7 +7114,7 @@
       <c r="Y211" s="1" t="n"/>
       <c r="Z211" s="1" t="n"/>
     </row>
-    <row r="212" ht="14.25" customHeight="1" s="84">
+    <row r="212" ht="14.25" customHeight="1" s="90">
       <c r="A212" s="1" t="n"/>
       <c r="B212" s="1" t="n"/>
       <c r="C212" s="1" t="n"/>
@@ -7148,7 +7142,7 @@
       <c r="Y212" s="1" t="n"/>
       <c r="Z212" s="1" t="n"/>
     </row>
-    <row r="213" ht="14.25" customHeight="1" s="84">
+    <row r="213" ht="14.25" customHeight="1" s="90">
       <c r="A213" s="1" t="n"/>
       <c r="B213" s="1" t="n"/>
       <c r="C213" s="1" t="n"/>
@@ -7176,7 +7170,7 @@
       <c r="Y213" s="1" t="n"/>
       <c r="Z213" s="1" t="n"/>
     </row>
-    <row r="214" ht="14.25" customHeight="1" s="84">
+    <row r="214" ht="14.25" customHeight="1" s="90">
       <c r="A214" s="1" t="n"/>
       <c r="B214" s="1" t="n"/>
       <c r="C214" s="1" t="n"/>
@@ -7204,7 +7198,7 @@
       <c r="Y214" s="1" t="n"/>
       <c r="Z214" s="1" t="n"/>
     </row>
-    <row r="215" ht="14.25" customHeight="1" s="84">
+    <row r="215" ht="14.25" customHeight="1" s="90">
       <c r="A215" s="1" t="n"/>
       <c r="B215" s="1" t="n"/>
       <c r="C215" s="1" t="n"/>
@@ -7232,7 +7226,7 @@
       <c r="Y215" s="1" t="n"/>
       <c r="Z215" s="1" t="n"/>
     </row>
-    <row r="216" ht="14.25" customHeight="1" s="84">
+    <row r="216" ht="14.25" customHeight="1" s="90">
       <c r="A216" s="1" t="n"/>
       <c r="B216" s="1" t="n"/>
       <c r="C216" s="1" t="n"/>
@@ -7260,7 +7254,7 @@
       <c r="Y216" s="1" t="n"/>
       <c r="Z216" s="1" t="n"/>
     </row>
-    <row r="217" ht="14.25" customHeight="1" s="84">
+    <row r="217" ht="14.25" customHeight="1" s="90">
       <c r="A217" s="1" t="n"/>
       <c r="B217" s="1" t="n"/>
       <c r="C217" s="1" t="n"/>
@@ -7288,7 +7282,7 @@
       <c r="Y217" s="1" t="n"/>
       <c r="Z217" s="1" t="n"/>
     </row>
-    <row r="218" ht="14.25" customHeight="1" s="84">
+    <row r="218" ht="14.25" customHeight="1" s="90">
       <c r="A218" s="1" t="n"/>
       <c r="B218" s="1" t="n"/>
       <c r="C218" s="1" t="n"/>
@@ -7316,7 +7310,7 @@
       <c r="Y218" s="1" t="n"/>
       <c r="Z218" s="1" t="n"/>
     </row>
-    <row r="219" ht="14.25" customHeight="1" s="84">
+    <row r="219" ht="14.25" customHeight="1" s="90">
       <c r="A219" t="inlineStr">
         <is>
           <t>Phase 7</t>
@@ -7336,785 +7330,785 @@
         </is>
       </c>
     </row>
-    <row r="220" ht="14.25" customHeight="1" s="84"/>
-    <row r="221" ht="14.25" customHeight="1" s="84"/>
-    <row r="222" ht="14.25" customHeight="1" s="84"/>
-    <row r="223" ht="14.25" customHeight="1" s="84"/>
-    <row r="224" ht="14.25" customHeight="1" s="84"/>
-    <row r="225" ht="14.25" customHeight="1" s="84"/>
-    <row r="226" ht="14.25" customHeight="1" s="84"/>
-    <row r="227" ht="14.25" customHeight="1" s="84"/>
-    <row r="228" ht="14.25" customHeight="1" s="84"/>
-    <row r="229" ht="14.25" customHeight="1" s="84"/>
-    <row r="230" ht="14.25" customHeight="1" s="84"/>
-    <row r="231" ht="14.25" customHeight="1" s="84"/>
-    <row r="232" ht="14.25" customHeight="1" s="84"/>
-    <row r="233" ht="14.25" customHeight="1" s="84"/>
-    <row r="234" ht="14.25" customHeight="1" s="84"/>
-    <row r="235" ht="14.25" customHeight="1" s="84"/>
-    <row r="236" ht="14.25" customHeight="1" s="84"/>
-    <row r="237" ht="14.25" customHeight="1" s="84"/>
-    <row r="238" ht="14.25" customHeight="1" s="84"/>
-    <row r="239" ht="14.25" customHeight="1" s="84"/>
-    <row r="240" ht="14.25" customHeight="1" s="84"/>
-    <row r="241" ht="14.25" customHeight="1" s="84"/>
-    <row r="242" ht="14.25" customHeight="1" s="84"/>
-    <row r="243" ht="14.25" customHeight="1" s="84"/>
-    <row r="244" ht="14.25" customHeight="1" s="84"/>
-    <row r="245" ht="14.25" customHeight="1" s="84"/>
-    <row r="246" ht="14.25" customHeight="1" s="84"/>
-    <row r="247" ht="14.25" customHeight="1" s="84"/>
-    <row r="248" ht="14.25" customHeight="1" s="84"/>
-    <row r="249" ht="14.25" customHeight="1" s="84"/>
-    <row r="250" ht="14.25" customHeight="1" s="84"/>
-    <row r="251" ht="14.25" customHeight="1" s="84"/>
-    <row r="252" ht="14.25" customHeight="1" s="84"/>
-    <row r="253" ht="14.25" customHeight="1" s="84"/>
-    <row r="254" ht="14.25" customHeight="1" s="84"/>
-    <row r="255" ht="14.25" customHeight="1" s="84"/>
-    <row r="256" ht="14.25" customHeight="1" s="84"/>
-    <row r="257" ht="14.25" customHeight="1" s="84"/>
-    <row r="258" ht="14.25" customHeight="1" s="84"/>
-    <row r="259" ht="14.25" customHeight="1" s="84"/>
-    <row r="260" ht="14.25" customHeight="1" s="84"/>
-    <row r="261" ht="14.25" customHeight="1" s="84"/>
-    <row r="262" ht="14.25" customHeight="1" s="84"/>
-    <row r="263" ht="14.25" customHeight="1" s="84"/>
-    <row r="264" ht="14.25" customHeight="1" s="84"/>
-    <row r="265" ht="14.25" customHeight="1" s="84"/>
-    <row r="266" ht="14.25" customHeight="1" s="84"/>
-    <row r="267" ht="14.25" customHeight="1" s="84"/>
-    <row r="268" ht="14.25" customHeight="1" s="84"/>
-    <row r="269" ht="14.25" customHeight="1" s="84"/>
-    <row r="270" ht="14.25" customHeight="1" s="84"/>
-    <row r="271" ht="14.25" customHeight="1" s="84"/>
-    <row r="272" ht="14.25" customHeight="1" s="84"/>
-    <row r="273" ht="14.25" customHeight="1" s="84"/>
-    <row r="274" ht="14.25" customHeight="1" s="84"/>
-    <row r="275" ht="14.25" customHeight="1" s="84"/>
-    <row r="276" ht="14.25" customHeight="1" s="84"/>
-    <row r="277" ht="14.25" customHeight="1" s="84"/>
-    <row r="278" ht="14.25" customHeight="1" s="84"/>
-    <row r="279" ht="14.25" customHeight="1" s="84"/>
-    <row r="280" ht="14.25" customHeight="1" s="84"/>
-    <row r="281" ht="14.25" customHeight="1" s="84"/>
-    <row r="282" ht="14.25" customHeight="1" s="84"/>
-    <row r="283" ht="14.25" customHeight="1" s="84"/>
-    <row r="284" ht="14.25" customHeight="1" s="84"/>
-    <row r="285" ht="14.25" customHeight="1" s="84"/>
-    <row r="286" ht="14.25" customHeight="1" s="84"/>
-    <row r="287" ht="14.25" customHeight="1" s="84"/>
-    <row r="288" ht="14.25" customHeight="1" s="84"/>
-    <row r="289" ht="14.25" customHeight="1" s="84"/>
-    <row r="290" ht="14.25" customHeight="1" s="84"/>
-    <row r="291" ht="14.25" customHeight="1" s="84"/>
-    <row r="292" ht="14.25" customHeight="1" s="84"/>
-    <row r="293" ht="14.25" customHeight="1" s="84"/>
-    <row r="294" ht="14.25" customHeight="1" s="84"/>
-    <row r="295" ht="14.25" customHeight="1" s="84"/>
-    <row r="296" ht="14.25" customHeight="1" s="84"/>
-    <row r="297" ht="14.25" customHeight="1" s="84"/>
-    <row r="298" ht="14.25" customHeight="1" s="84"/>
-    <row r="299" ht="14.25" customHeight="1" s="84"/>
-    <row r="300" ht="14.25" customHeight="1" s="84"/>
-    <row r="301" ht="14.25" customHeight="1" s="84"/>
-    <row r="302" ht="14.25" customHeight="1" s="84"/>
-    <row r="303" ht="14.25" customHeight="1" s="84"/>
-    <row r="304" ht="14.25" customHeight="1" s="84"/>
-    <row r="305" ht="14.25" customHeight="1" s="84"/>
-    <row r="306" ht="14.25" customHeight="1" s="84"/>
-    <row r="307" ht="14.25" customHeight="1" s="84"/>
-    <row r="308" ht="14.25" customHeight="1" s="84"/>
-    <row r="309" ht="14.25" customHeight="1" s="84"/>
-    <row r="310" ht="14.25" customHeight="1" s="84"/>
-    <row r="311" ht="14.25" customHeight="1" s="84"/>
-    <row r="312" ht="14.25" customHeight="1" s="84"/>
-    <row r="313" ht="14.25" customHeight="1" s="84"/>
-    <row r="314" ht="14.25" customHeight="1" s="84"/>
-    <row r="315" ht="14.25" customHeight="1" s="84"/>
-    <row r="316" ht="14.25" customHeight="1" s="84"/>
-    <row r="317" ht="14.25" customHeight="1" s="84"/>
-    <row r="318" ht="14.25" customHeight="1" s="84"/>
-    <row r="319" ht="14.25" customHeight="1" s="84"/>
-    <row r="320" ht="14.25" customHeight="1" s="84"/>
-    <row r="321" ht="14.25" customHeight="1" s="84"/>
-    <row r="322" ht="14.25" customHeight="1" s="84"/>
-    <row r="323" ht="14.25" customHeight="1" s="84"/>
-    <row r="324" ht="14.25" customHeight="1" s="84"/>
-    <row r="325" ht="14.25" customHeight="1" s="84"/>
-    <row r="326" ht="14.25" customHeight="1" s="84"/>
-    <row r="327" ht="14.25" customHeight="1" s="84"/>
-    <row r="328" ht="14.25" customHeight="1" s="84"/>
-    <row r="329" ht="14.25" customHeight="1" s="84"/>
-    <row r="330" ht="14.25" customHeight="1" s="84"/>
-    <row r="331" ht="14.25" customHeight="1" s="84"/>
-    <row r="332" ht="14.25" customHeight="1" s="84"/>
-    <row r="333" ht="14.25" customHeight="1" s="84"/>
-    <row r="334" ht="14.25" customHeight="1" s="84"/>
-    <row r="335" ht="14.25" customHeight="1" s="84"/>
-    <row r="336" ht="14.25" customHeight="1" s="84"/>
-    <row r="337" ht="14.25" customHeight="1" s="84"/>
-    <row r="338" ht="14.25" customHeight="1" s="84"/>
-    <row r="339" ht="14.25" customHeight="1" s="84"/>
-    <row r="340" ht="14.25" customHeight="1" s="84"/>
-    <row r="341" ht="14.25" customHeight="1" s="84"/>
-    <row r="342" ht="14.25" customHeight="1" s="84"/>
-    <row r="343" ht="14.25" customHeight="1" s="84"/>
-    <row r="344" ht="14.25" customHeight="1" s="84"/>
-    <row r="345" ht="14.25" customHeight="1" s="84"/>
-    <row r="346" ht="14.25" customHeight="1" s="84"/>
-    <row r="347" ht="14.25" customHeight="1" s="84"/>
-    <row r="348" ht="14.25" customHeight="1" s="84"/>
-    <row r="349" ht="14.25" customHeight="1" s="84"/>
-    <row r="350" ht="14.25" customHeight="1" s="84"/>
-    <row r="351" ht="14.25" customHeight="1" s="84"/>
-    <row r="352" ht="14.25" customHeight="1" s="84"/>
-    <row r="353" ht="14.25" customHeight="1" s="84"/>
-    <row r="354" ht="14.25" customHeight="1" s="84"/>
-    <row r="355" ht="14.25" customHeight="1" s="84"/>
-    <row r="356" ht="14.25" customHeight="1" s="84"/>
-    <row r="357" ht="14.25" customHeight="1" s="84"/>
-    <row r="358" ht="14.25" customHeight="1" s="84"/>
-    <row r="359" ht="14.25" customHeight="1" s="84"/>
-    <row r="360" ht="14.25" customHeight="1" s="84"/>
-    <row r="361" ht="14.25" customHeight="1" s="84"/>
-    <row r="362" ht="14.25" customHeight="1" s="84"/>
-    <row r="363" ht="14.25" customHeight="1" s="84"/>
-    <row r="364" ht="14.25" customHeight="1" s="84"/>
-    <row r="365" ht="14.25" customHeight="1" s="84"/>
-    <row r="366" ht="14.25" customHeight="1" s="84"/>
-    <row r="367" ht="14.25" customHeight="1" s="84"/>
-    <row r="368" ht="14.25" customHeight="1" s="84"/>
-    <row r="369" ht="14.25" customHeight="1" s="84"/>
-    <row r="370" ht="14.25" customHeight="1" s="84"/>
-    <row r="371" ht="14.25" customHeight="1" s="84"/>
-    <row r="372" ht="14.25" customHeight="1" s="84"/>
-    <row r="373" ht="14.25" customHeight="1" s="84"/>
-    <row r="374" ht="14.25" customHeight="1" s="84"/>
-    <row r="375" ht="14.25" customHeight="1" s="84"/>
-    <row r="376" ht="14.25" customHeight="1" s="84"/>
-    <row r="377" ht="14.25" customHeight="1" s="84"/>
-    <row r="378" ht="14.25" customHeight="1" s="84"/>
-    <row r="379" ht="14.25" customHeight="1" s="84"/>
-    <row r="380" ht="14.25" customHeight="1" s="84"/>
-    <row r="381" ht="14.25" customHeight="1" s="84"/>
-    <row r="382" ht="14.25" customHeight="1" s="84"/>
-    <row r="383" ht="14.25" customHeight="1" s="84"/>
-    <row r="384" ht="14.25" customHeight="1" s="84"/>
-    <row r="385" ht="14.25" customHeight="1" s="84"/>
-    <row r="386" ht="14.25" customHeight="1" s="84"/>
-    <row r="387" ht="14.25" customHeight="1" s="84"/>
-    <row r="388" ht="14.25" customHeight="1" s="84"/>
-    <row r="389" ht="14.25" customHeight="1" s="84"/>
-    <row r="390" ht="14.25" customHeight="1" s="84"/>
-    <row r="391" ht="14.25" customHeight="1" s="84"/>
-    <row r="392" ht="14.25" customHeight="1" s="84"/>
-    <row r="393" ht="14.25" customHeight="1" s="84"/>
-    <row r="394" ht="14.25" customHeight="1" s="84"/>
-    <row r="395" ht="14.25" customHeight="1" s="84"/>
-    <row r="396" ht="14.25" customHeight="1" s="84"/>
-    <row r="397" ht="14.25" customHeight="1" s="84"/>
-    <row r="398" ht="14.25" customHeight="1" s="84"/>
-    <row r="399" ht="14.25" customHeight="1" s="84"/>
-    <row r="400" ht="14.25" customHeight="1" s="84"/>
-    <row r="401" ht="14.25" customHeight="1" s="84"/>
-    <row r="402" ht="14.25" customHeight="1" s="84"/>
-    <row r="403" ht="14.25" customHeight="1" s="84"/>
-    <row r="404" ht="14.25" customHeight="1" s="84"/>
-    <row r="405" ht="14.25" customHeight="1" s="84"/>
-    <row r="406" ht="14.25" customHeight="1" s="84"/>
-    <row r="407" ht="14.25" customHeight="1" s="84"/>
-    <row r="408" ht="14.25" customHeight="1" s="84"/>
-    <row r="409" ht="14.25" customHeight="1" s="84"/>
-    <row r="410" ht="14.25" customHeight="1" s="84"/>
-    <row r="411" ht="14.25" customHeight="1" s="84"/>
-    <row r="412" ht="14.25" customHeight="1" s="84"/>
-    <row r="413" ht="14.25" customHeight="1" s="84"/>
-    <row r="414" ht="14.25" customHeight="1" s="84"/>
-    <row r="415" ht="14.25" customHeight="1" s="84"/>
-    <row r="416" ht="14.25" customHeight="1" s="84"/>
-    <row r="417" ht="14.25" customHeight="1" s="84"/>
-    <row r="418" ht="14.25" customHeight="1" s="84"/>
-    <row r="419" ht="14.25" customHeight="1" s="84"/>
-    <row r="420" ht="14.25" customHeight="1" s="84"/>
-    <row r="421" ht="14.25" customHeight="1" s="84"/>
-    <row r="422" ht="14.25" customHeight="1" s="84"/>
-    <row r="423" ht="14.25" customHeight="1" s="84"/>
-    <row r="424" ht="14.25" customHeight="1" s="84"/>
-    <row r="425" ht="14.25" customHeight="1" s="84"/>
-    <row r="426" ht="14.25" customHeight="1" s="84"/>
-    <row r="427" ht="14.25" customHeight="1" s="84"/>
-    <row r="428" ht="14.25" customHeight="1" s="84"/>
-    <row r="429" ht="14.25" customHeight="1" s="84"/>
-    <row r="430" ht="14.25" customHeight="1" s="84"/>
-    <row r="431" ht="14.25" customHeight="1" s="84"/>
-    <row r="432" ht="14.25" customHeight="1" s="84"/>
-    <row r="433" ht="14.25" customHeight="1" s="84"/>
-    <row r="434" ht="14.25" customHeight="1" s="84"/>
-    <row r="435" ht="14.25" customHeight="1" s="84"/>
-    <row r="436" ht="14.25" customHeight="1" s="84"/>
-    <row r="437" ht="14.25" customHeight="1" s="84"/>
-    <row r="438" ht="14.25" customHeight="1" s="84"/>
-    <row r="439" ht="14.25" customHeight="1" s="84"/>
-    <row r="440" ht="14.25" customHeight="1" s="84"/>
-    <row r="441" ht="14.25" customHeight="1" s="84"/>
-    <row r="442" ht="14.25" customHeight="1" s="84"/>
-    <row r="443" ht="14.25" customHeight="1" s="84"/>
-    <row r="444" ht="14.25" customHeight="1" s="84"/>
-    <row r="445" ht="14.25" customHeight="1" s="84"/>
-    <row r="446" ht="14.25" customHeight="1" s="84"/>
-    <row r="447" ht="14.25" customHeight="1" s="84"/>
-    <row r="448" ht="14.25" customHeight="1" s="84"/>
-    <row r="449" ht="14.25" customHeight="1" s="84"/>
-    <row r="450" ht="14.25" customHeight="1" s="84"/>
-    <row r="451" ht="14.25" customHeight="1" s="84"/>
-    <row r="452" ht="14.25" customHeight="1" s="84"/>
-    <row r="453" ht="14.25" customHeight="1" s="84"/>
-    <row r="454" ht="14.25" customHeight="1" s="84"/>
-    <row r="455" ht="14.25" customHeight="1" s="84"/>
-    <row r="456" ht="14.25" customHeight="1" s="84"/>
-    <row r="457" ht="14.25" customHeight="1" s="84"/>
-    <row r="458" ht="14.25" customHeight="1" s="84"/>
-    <row r="459" ht="14.25" customHeight="1" s="84"/>
-    <row r="460" ht="14.25" customHeight="1" s="84"/>
-    <row r="461" ht="14.25" customHeight="1" s="84"/>
-    <row r="462" ht="14.25" customHeight="1" s="84"/>
-    <row r="463" ht="14.25" customHeight="1" s="84"/>
-    <row r="464" ht="14.25" customHeight="1" s="84"/>
-    <row r="465" ht="14.25" customHeight="1" s="84"/>
-    <row r="466" ht="14.25" customHeight="1" s="84"/>
-    <row r="467" ht="14.25" customHeight="1" s="84"/>
-    <row r="468" ht="14.25" customHeight="1" s="84"/>
-    <row r="469" ht="14.25" customHeight="1" s="84"/>
-    <row r="470" ht="14.25" customHeight="1" s="84"/>
-    <row r="471" ht="14.25" customHeight="1" s="84"/>
-    <row r="472" ht="14.25" customHeight="1" s="84"/>
-    <row r="473" ht="14.25" customHeight="1" s="84"/>
-    <row r="474" ht="14.25" customHeight="1" s="84"/>
-    <row r="475" ht="14.25" customHeight="1" s="84"/>
-    <row r="476" ht="14.25" customHeight="1" s="84"/>
-    <row r="477" ht="14.25" customHeight="1" s="84"/>
-    <row r="478" ht="14.25" customHeight="1" s="84"/>
-    <row r="479" ht="14.25" customHeight="1" s="84"/>
-    <row r="480" ht="14.25" customHeight="1" s="84"/>
-    <row r="481" ht="14.25" customHeight="1" s="84"/>
-    <row r="482" ht="14.25" customHeight="1" s="84"/>
-    <row r="483" ht="14.25" customHeight="1" s="84"/>
-    <row r="484" ht="14.25" customHeight="1" s="84"/>
-    <row r="485" ht="14.25" customHeight="1" s="84"/>
-    <row r="486" ht="14.25" customHeight="1" s="84"/>
-    <row r="487" ht="14.25" customHeight="1" s="84"/>
-    <row r="488" ht="14.25" customHeight="1" s="84"/>
-    <row r="489" ht="14.25" customHeight="1" s="84"/>
-    <row r="490" ht="14.25" customHeight="1" s="84"/>
-    <row r="491" ht="14.25" customHeight="1" s="84"/>
-    <row r="492" ht="14.25" customHeight="1" s="84"/>
-    <row r="493" ht="14.25" customHeight="1" s="84"/>
-    <row r="494" ht="14.25" customHeight="1" s="84"/>
-    <row r="495" ht="14.25" customHeight="1" s="84"/>
-    <row r="496" ht="14.25" customHeight="1" s="84"/>
-    <row r="497" ht="14.25" customHeight="1" s="84"/>
-    <row r="498" ht="14.25" customHeight="1" s="84"/>
-    <row r="499" ht="14.25" customHeight="1" s="84"/>
-    <row r="500" ht="14.25" customHeight="1" s="84"/>
-    <row r="501" ht="14.25" customHeight="1" s="84"/>
-    <row r="502" ht="14.25" customHeight="1" s="84"/>
-    <row r="503" ht="14.25" customHeight="1" s="84"/>
-    <row r="504" ht="14.25" customHeight="1" s="84"/>
-    <row r="505" ht="14.25" customHeight="1" s="84"/>
-    <row r="506" ht="14.25" customHeight="1" s="84"/>
-    <row r="507" ht="14.25" customHeight="1" s="84"/>
-    <row r="508" ht="14.25" customHeight="1" s="84"/>
-    <row r="509" ht="14.25" customHeight="1" s="84"/>
-    <row r="510" ht="14.25" customHeight="1" s="84"/>
-    <row r="511" ht="14.25" customHeight="1" s="84"/>
-    <row r="512" ht="14.25" customHeight="1" s="84"/>
-    <row r="513" ht="14.25" customHeight="1" s="84"/>
-    <row r="514" ht="14.25" customHeight="1" s="84"/>
-    <row r="515" ht="14.25" customHeight="1" s="84"/>
-    <row r="516" ht="14.25" customHeight="1" s="84"/>
-    <row r="517" ht="14.25" customHeight="1" s="84"/>
-    <row r="518" ht="14.25" customHeight="1" s="84"/>
-    <row r="519" ht="14.25" customHeight="1" s="84"/>
-    <row r="520" ht="14.25" customHeight="1" s="84"/>
-    <row r="521" ht="14.25" customHeight="1" s="84"/>
-    <row r="522" ht="14.25" customHeight="1" s="84"/>
-    <row r="523" ht="14.25" customHeight="1" s="84"/>
-    <row r="524" ht="14.25" customHeight="1" s="84"/>
-    <row r="525" ht="14.25" customHeight="1" s="84"/>
-    <row r="526" ht="14.25" customHeight="1" s="84"/>
-    <row r="527" ht="14.25" customHeight="1" s="84"/>
-    <row r="528" ht="14.25" customHeight="1" s="84"/>
-    <row r="529" ht="14.25" customHeight="1" s="84"/>
-    <row r="530" ht="14.25" customHeight="1" s="84"/>
-    <row r="531" ht="14.25" customHeight="1" s="84"/>
-    <row r="532" ht="14.25" customHeight="1" s="84"/>
-    <row r="533" ht="14.25" customHeight="1" s="84"/>
-    <row r="534" ht="14.25" customHeight="1" s="84"/>
-    <row r="535" ht="14.25" customHeight="1" s="84"/>
-    <row r="536" ht="14.25" customHeight="1" s="84"/>
-    <row r="537" ht="14.25" customHeight="1" s="84"/>
-    <row r="538" ht="14.25" customHeight="1" s="84"/>
-    <row r="539" ht="14.25" customHeight="1" s="84"/>
-    <row r="540" ht="14.25" customHeight="1" s="84"/>
-    <row r="541" ht="14.25" customHeight="1" s="84"/>
-    <row r="542" ht="14.25" customHeight="1" s="84"/>
-    <row r="543" ht="14.25" customHeight="1" s="84"/>
-    <row r="544" ht="14.25" customHeight="1" s="84"/>
-    <row r="545" ht="14.25" customHeight="1" s="84"/>
-    <row r="546" ht="14.25" customHeight="1" s="84"/>
-    <row r="547" ht="14.25" customHeight="1" s="84"/>
-    <row r="548" ht="14.25" customHeight="1" s="84"/>
-    <row r="549" ht="14.25" customHeight="1" s="84"/>
-    <row r="550" ht="14.25" customHeight="1" s="84"/>
-    <row r="551" ht="14.25" customHeight="1" s="84"/>
-    <row r="552" ht="14.25" customHeight="1" s="84"/>
-    <row r="553" ht="14.25" customHeight="1" s="84"/>
-    <row r="554" ht="14.25" customHeight="1" s="84"/>
-    <row r="555" ht="14.25" customHeight="1" s="84"/>
-    <row r="556" ht="14.25" customHeight="1" s="84"/>
-    <row r="557" ht="14.25" customHeight="1" s="84"/>
-    <row r="558" ht="14.25" customHeight="1" s="84"/>
-    <row r="559" ht="14.25" customHeight="1" s="84"/>
-    <row r="560" ht="14.25" customHeight="1" s="84"/>
-    <row r="561" ht="14.25" customHeight="1" s="84"/>
-    <row r="562" ht="14.25" customHeight="1" s="84"/>
-    <row r="563" ht="14.25" customHeight="1" s="84"/>
-    <row r="564" ht="14.25" customHeight="1" s="84"/>
-    <row r="565" ht="14.25" customHeight="1" s="84"/>
-    <row r="566" ht="14.25" customHeight="1" s="84"/>
-    <row r="567" ht="14.25" customHeight="1" s="84"/>
-    <row r="568" ht="14.25" customHeight="1" s="84"/>
-    <row r="569" ht="14.25" customHeight="1" s="84"/>
-    <row r="570" ht="14.25" customHeight="1" s="84"/>
-    <row r="571" ht="14.25" customHeight="1" s="84"/>
-    <row r="572" ht="14.25" customHeight="1" s="84"/>
-    <row r="573" ht="14.25" customHeight="1" s="84"/>
-    <row r="574" ht="14.25" customHeight="1" s="84"/>
-    <row r="575" ht="14.25" customHeight="1" s="84"/>
-    <row r="576" ht="14.25" customHeight="1" s="84"/>
-    <row r="577" ht="14.25" customHeight="1" s="84"/>
-    <row r="578" ht="14.25" customHeight="1" s="84"/>
-    <row r="579" ht="14.25" customHeight="1" s="84"/>
-    <row r="580" ht="14.25" customHeight="1" s="84"/>
-    <row r="581" ht="14.25" customHeight="1" s="84"/>
-    <row r="582" ht="14.25" customHeight="1" s="84"/>
-    <row r="583" ht="14.25" customHeight="1" s="84"/>
-    <row r="584" ht="14.25" customHeight="1" s="84"/>
-    <row r="585" ht="14.25" customHeight="1" s="84"/>
-    <row r="586" ht="14.25" customHeight="1" s="84"/>
-    <row r="587" ht="14.25" customHeight="1" s="84"/>
-    <row r="588" ht="14.25" customHeight="1" s="84"/>
-    <row r="589" ht="14.25" customHeight="1" s="84"/>
-    <row r="590" ht="14.25" customHeight="1" s="84"/>
-    <row r="591" ht="14.25" customHeight="1" s="84"/>
-    <row r="592" ht="14.25" customHeight="1" s="84"/>
-    <row r="593" ht="14.25" customHeight="1" s="84"/>
-    <row r="594" ht="14.25" customHeight="1" s="84"/>
-    <row r="595" ht="14.25" customHeight="1" s="84"/>
-    <row r="596" ht="14.25" customHeight="1" s="84"/>
-    <row r="597" ht="14.25" customHeight="1" s="84"/>
-    <row r="598" ht="14.25" customHeight="1" s="84"/>
-    <row r="599" ht="14.25" customHeight="1" s="84"/>
-    <row r="600" ht="14.25" customHeight="1" s="84"/>
-    <row r="601" ht="14.25" customHeight="1" s="84"/>
-    <row r="602" ht="14.25" customHeight="1" s="84"/>
-    <row r="603" ht="14.25" customHeight="1" s="84"/>
-    <row r="604" ht="14.25" customHeight="1" s="84"/>
-    <row r="605" ht="14.25" customHeight="1" s="84"/>
-    <row r="606" ht="14.25" customHeight="1" s="84"/>
-    <row r="607" ht="14.25" customHeight="1" s="84"/>
-    <row r="608" ht="14.25" customHeight="1" s="84"/>
-    <row r="609" ht="14.25" customHeight="1" s="84"/>
-    <row r="610" ht="14.25" customHeight="1" s="84"/>
-    <row r="611" ht="14.25" customHeight="1" s="84"/>
-    <row r="612" ht="14.25" customHeight="1" s="84"/>
-    <row r="613" ht="14.25" customHeight="1" s="84"/>
-    <row r="614" ht="14.25" customHeight="1" s="84"/>
-    <row r="615" ht="14.25" customHeight="1" s="84"/>
-    <row r="616" ht="14.25" customHeight="1" s="84"/>
-    <row r="617" ht="14.25" customHeight="1" s="84"/>
-    <row r="618" ht="14.25" customHeight="1" s="84"/>
-    <row r="619" ht="14.25" customHeight="1" s="84"/>
-    <row r="620" ht="14.25" customHeight="1" s="84"/>
-    <row r="621" ht="14.25" customHeight="1" s="84"/>
-    <row r="622" ht="14.25" customHeight="1" s="84"/>
-    <row r="623" ht="14.25" customHeight="1" s="84"/>
-    <row r="624" ht="14.25" customHeight="1" s="84"/>
-    <row r="625" ht="14.25" customHeight="1" s="84"/>
-    <row r="626" ht="14.25" customHeight="1" s="84"/>
-    <row r="627" ht="14.25" customHeight="1" s="84"/>
-    <row r="628" ht="14.25" customHeight="1" s="84"/>
-    <row r="629" ht="14.25" customHeight="1" s="84"/>
-    <row r="630" ht="14.25" customHeight="1" s="84"/>
-    <row r="631" ht="14.25" customHeight="1" s="84"/>
-    <row r="632" ht="14.25" customHeight="1" s="84"/>
-    <row r="633" ht="14.25" customHeight="1" s="84"/>
-    <row r="634" ht="14.25" customHeight="1" s="84"/>
-    <row r="635" ht="14.25" customHeight="1" s="84"/>
-    <row r="636" ht="14.25" customHeight="1" s="84"/>
-    <row r="637" ht="14.25" customHeight="1" s="84"/>
-    <row r="638" ht="14.25" customHeight="1" s="84"/>
-    <row r="639" ht="14.25" customHeight="1" s="84"/>
-    <row r="640" ht="14.25" customHeight="1" s="84"/>
-    <row r="641" ht="14.25" customHeight="1" s="84"/>
-    <row r="642" ht="14.25" customHeight="1" s="84"/>
-    <row r="643" ht="14.25" customHeight="1" s="84"/>
-    <row r="644" ht="14.25" customHeight="1" s="84"/>
-    <row r="645" ht="14.25" customHeight="1" s="84"/>
-    <row r="646" ht="14.25" customHeight="1" s="84"/>
-    <row r="647" ht="14.25" customHeight="1" s="84"/>
-    <row r="648" ht="14.25" customHeight="1" s="84"/>
-    <row r="649" ht="14.25" customHeight="1" s="84"/>
-    <row r="650" ht="14.25" customHeight="1" s="84"/>
-    <row r="651" ht="14.25" customHeight="1" s="84"/>
-    <row r="652" ht="14.25" customHeight="1" s="84"/>
-    <row r="653" ht="14.25" customHeight="1" s="84"/>
-    <row r="654" ht="14.25" customHeight="1" s="84"/>
-    <row r="655" ht="14.25" customHeight="1" s="84"/>
-    <row r="656" ht="14.25" customHeight="1" s="84"/>
-    <row r="657" ht="14.25" customHeight="1" s="84"/>
-    <row r="658" ht="14.25" customHeight="1" s="84"/>
-    <row r="659" ht="14.25" customHeight="1" s="84"/>
-    <row r="660" ht="14.25" customHeight="1" s="84"/>
-    <row r="661" ht="14.25" customHeight="1" s="84"/>
-    <row r="662" ht="14.25" customHeight="1" s="84"/>
-    <row r="663" ht="14.25" customHeight="1" s="84"/>
-    <row r="664" ht="14.25" customHeight="1" s="84"/>
-    <row r="665" ht="14.25" customHeight="1" s="84"/>
-    <row r="666" ht="14.25" customHeight="1" s="84"/>
-    <row r="667" ht="14.25" customHeight="1" s="84"/>
-    <row r="668" ht="14.25" customHeight="1" s="84"/>
-    <row r="669" ht="14.25" customHeight="1" s="84"/>
-    <row r="670" ht="14.25" customHeight="1" s="84"/>
-    <row r="671" ht="14.25" customHeight="1" s="84"/>
-    <row r="672" ht="14.25" customHeight="1" s="84"/>
-    <row r="673" ht="14.25" customHeight="1" s="84"/>
-    <row r="674" ht="14.25" customHeight="1" s="84"/>
-    <row r="675" ht="14.25" customHeight="1" s="84"/>
-    <row r="676" ht="14.25" customHeight="1" s="84"/>
-    <row r="677" ht="14.25" customHeight="1" s="84"/>
-    <row r="678" ht="14.25" customHeight="1" s="84"/>
-    <row r="679" ht="14.25" customHeight="1" s="84"/>
-    <row r="680" ht="14.25" customHeight="1" s="84"/>
-    <row r="681" ht="14.25" customHeight="1" s="84"/>
-    <row r="682" ht="14.25" customHeight="1" s="84"/>
-    <row r="683" ht="14.25" customHeight="1" s="84"/>
-    <row r="684" ht="14.25" customHeight="1" s="84"/>
-    <row r="685" ht="14.25" customHeight="1" s="84"/>
-    <row r="686" ht="14.25" customHeight="1" s="84"/>
-    <row r="687" ht="14.25" customHeight="1" s="84"/>
-    <row r="688" ht="14.25" customHeight="1" s="84"/>
-    <row r="689" ht="14.25" customHeight="1" s="84"/>
-    <row r="690" ht="14.25" customHeight="1" s="84"/>
-    <row r="691" ht="14.25" customHeight="1" s="84"/>
-    <row r="692" ht="14.25" customHeight="1" s="84"/>
-    <row r="693" ht="14.25" customHeight="1" s="84"/>
-    <row r="694" ht="14.25" customHeight="1" s="84"/>
-    <row r="695" ht="14.25" customHeight="1" s="84"/>
-    <row r="696" ht="14.25" customHeight="1" s="84"/>
-    <row r="697" ht="14.25" customHeight="1" s="84"/>
-    <row r="698" ht="14.25" customHeight="1" s="84"/>
-    <row r="699" ht="14.25" customHeight="1" s="84"/>
-    <row r="700" ht="14.25" customHeight="1" s="84"/>
-    <row r="701" ht="14.25" customHeight="1" s="84"/>
-    <row r="702" ht="14.25" customHeight="1" s="84"/>
-    <row r="703" ht="14.25" customHeight="1" s="84"/>
-    <row r="704" ht="14.25" customHeight="1" s="84"/>
-    <row r="705" ht="14.25" customHeight="1" s="84"/>
-    <row r="706" ht="14.25" customHeight="1" s="84"/>
-    <row r="707" ht="14.25" customHeight="1" s="84"/>
-    <row r="708" ht="14.25" customHeight="1" s="84"/>
-    <row r="709" ht="14.25" customHeight="1" s="84"/>
-    <row r="710" ht="14.25" customHeight="1" s="84"/>
-    <row r="711" ht="14.25" customHeight="1" s="84"/>
-    <row r="712" ht="14.25" customHeight="1" s="84"/>
-    <row r="713" ht="14.25" customHeight="1" s="84"/>
-    <row r="714" ht="14.25" customHeight="1" s="84"/>
-    <row r="715" ht="14.25" customHeight="1" s="84"/>
-    <row r="716" ht="14.25" customHeight="1" s="84"/>
-    <row r="717" ht="14.25" customHeight="1" s="84"/>
-    <row r="718" ht="14.25" customHeight="1" s="84"/>
-    <row r="719" ht="14.25" customHeight="1" s="84"/>
-    <row r="720" ht="14.25" customHeight="1" s="84"/>
-    <row r="721" ht="14.25" customHeight="1" s="84"/>
-    <row r="722" ht="14.25" customHeight="1" s="84"/>
-    <row r="723" ht="14.25" customHeight="1" s="84"/>
-    <row r="724" ht="14.25" customHeight="1" s="84"/>
-    <row r="725" ht="14.25" customHeight="1" s="84"/>
-    <row r="726" ht="14.25" customHeight="1" s="84"/>
-    <row r="727" ht="14.25" customHeight="1" s="84"/>
-    <row r="728" ht="14.25" customHeight="1" s="84"/>
-    <row r="729" ht="14.25" customHeight="1" s="84"/>
-    <row r="730" ht="14.25" customHeight="1" s="84"/>
-    <row r="731" ht="14.25" customHeight="1" s="84"/>
-    <row r="732" ht="14.25" customHeight="1" s="84"/>
-    <row r="733" ht="14.25" customHeight="1" s="84"/>
-    <row r="734" ht="14.25" customHeight="1" s="84"/>
-    <row r="735" ht="14.25" customHeight="1" s="84"/>
-    <row r="736" ht="14.25" customHeight="1" s="84"/>
-    <row r="737" ht="14.25" customHeight="1" s="84"/>
-    <row r="738" ht="14.25" customHeight="1" s="84"/>
-    <row r="739" ht="14.25" customHeight="1" s="84"/>
-    <row r="740" ht="14.25" customHeight="1" s="84"/>
-    <row r="741" ht="14.25" customHeight="1" s="84"/>
-    <row r="742" ht="14.25" customHeight="1" s="84"/>
-    <row r="743" ht="14.25" customHeight="1" s="84"/>
-    <row r="744" ht="14.25" customHeight="1" s="84"/>
-    <row r="745" ht="14.25" customHeight="1" s="84"/>
-    <row r="746" ht="14.25" customHeight="1" s="84"/>
-    <row r="747" ht="14.25" customHeight="1" s="84"/>
-    <row r="748" ht="14.25" customHeight="1" s="84"/>
-    <row r="749" ht="14.25" customHeight="1" s="84"/>
-    <row r="750" ht="14.25" customHeight="1" s="84"/>
-    <row r="751" ht="14.25" customHeight="1" s="84"/>
-    <row r="752" ht="14.25" customHeight="1" s="84"/>
-    <row r="753" ht="14.25" customHeight="1" s="84"/>
-    <row r="754" ht="14.25" customHeight="1" s="84"/>
-    <row r="755" ht="14.25" customHeight="1" s="84"/>
-    <row r="756" ht="14.25" customHeight="1" s="84"/>
-    <row r="757" ht="14.25" customHeight="1" s="84"/>
-    <row r="758" ht="14.25" customHeight="1" s="84"/>
-    <row r="759" ht="14.25" customHeight="1" s="84"/>
-    <row r="760" ht="14.25" customHeight="1" s="84"/>
-    <row r="761" ht="14.25" customHeight="1" s="84"/>
-    <row r="762" ht="14.25" customHeight="1" s="84"/>
-    <row r="763" ht="14.25" customHeight="1" s="84"/>
-    <row r="764" ht="14.25" customHeight="1" s="84"/>
-    <row r="765" ht="14.25" customHeight="1" s="84"/>
-    <row r="766" ht="14.25" customHeight="1" s="84"/>
-    <row r="767" ht="14.25" customHeight="1" s="84"/>
-    <row r="768" ht="14.25" customHeight="1" s="84"/>
-    <row r="769" ht="14.25" customHeight="1" s="84"/>
-    <row r="770" ht="14.25" customHeight="1" s="84"/>
-    <row r="771" ht="14.25" customHeight="1" s="84"/>
-    <row r="772" ht="14.25" customHeight="1" s="84"/>
-    <row r="773" ht="14.25" customHeight="1" s="84"/>
-    <row r="774" ht="14.25" customHeight="1" s="84"/>
-    <row r="775" ht="14.25" customHeight="1" s="84"/>
-    <row r="776" ht="14.25" customHeight="1" s="84"/>
-    <row r="777" ht="14.25" customHeight="1" s="84"/>
-    <row r="778" ht="14.25" customHeight="1" s="84"/>
-    <row r="779" ht="14.25" customHeight="1" s="84"/>
-    <row r="780" ht="14.25" customHeight="1" s="84"/>
-    <row r="781" ht="14.25" customHeight="1" s="84"/>
-    <row r="782" ht="14.25" customHeight="1" s="84"/>
-    <row r="783" ht="14.25" customHeight="1" s="84"/>
-    <row r="784" ht="14.25" customHeight="1" s="84"/>
-    <row r="785" ht="14.25" customHeight="1" s="84"/>
-    <row r="786" ht="14.25" customHeight="1" s="84"/>
-    <row r="787" ht="14.25" customHeight="1" s="84"/>
-    <row r="788" ht="14.25" customHeight="1" s="84"/>
-    <row r="789" ht="14.25" customHeight="1" s="84"/>
-    <row r="790" ht="14.25" customHeight="1" s="84"/>
-    <row r="791" ht="14.25" customHeight="1" s="84"/>
-    <row r="792" ht="14.25" customHeight="1" s="84"/>
-    <row r="793" ht="14.25" customHeight="1" s="84"/>
-    <row r="794" ht="14.25" customHeight="1" s="84"/>
-    <row r="795" ht="14.25" customHeight="1" s="84"/>
-    <row r="796" ht="14.25" customHeight="1" s="84"/>
-    <row r="797" ht="14.25" customHeight="1" s="84"/>
-    <row r="798" ht="14.25" customHeight="1" s="84"/>
-    <row r="799" ht="14.25" customHeight="1" s="84"/>
-    <row r="800" ht="14.25" customHeight="1" s="84"/>
-    <row r="801" ht="14.25" customHeight="1" s="84"/>
-    <row r="802" ht="14.25" customHeight="1" s="84"/>
-    <row r="803" ht="14.25" customHeight="1" s="84"/>
-    <row r="804" ht="14.25" customHeight="1" s="84"/>
-    <row r="805" ht="14.25" customHeight="1" s="84"/>
-    <row r="806" ht="14.25" customHeight="1" s="84"/>
-    <row r="807" ht="14.25" customHeight="1" s="84"/>
-    <row r="808" ht="14.25" customHeight="1" s="84"/>
-    <row r="809" ht="14.25" customHeight="1" s="84"/>
-    <row r="810" ht="14.25" customHeight="1" s="84"/>
-    <row r="811" ht="14.25" customHeight="1" s="84"/>
-    <row r="812" ht="14.25" customHeight="1" s="84"/>
-    <row r="813" ht="14.25" customHeight="1" s="84"/>
-    <row r="814" ht="14.25" customHeight="1" s="84"/>
-    <row r="815" ht="14.25" customHeight="1" s="84"/>
-    <row r="816" ht="14.25" customHeight="1" s="84"/>
-    <row r="817" ht="14.25" customHeight="1" s="84"/>
-    <row r="818" ht="14.25" customHeight="1" s="84"/>
-    <row r="819" ht="14.25" customHeight="1" s="84"/>
-    <row r="820" ht="14.25" customHeight="1" s="84"/>
-    <row r="821" ht="14.25" customHeight="1" s="84"/>
-    <row r="822" ht="14.25" customHeight="1" s="84"/>
-    <row r="823" ht="14.25" customHeight="1" s="84"/>
-    <row r="824" ht="14.25" customHeight="1" s="84"/>
-    <row r="825" ht="14.25" customHeight="1" s="84"/>
-    <row r="826" ht="14.25" customHeight="1" s="84"/>
-    <row r="827" ht="14.25" customHeight="1" s="84"/>
-    <row r="828" ht="14.25" customHeight="1" s="84"/>
-    <row r="829" ht="14.25" customHeight="1" s="84"/>
-    <row r="830" ht="14.25" customHeight="1" s="84"/>
-    <row r="831" ht="14.25" customHeight="1" s="84"/>
-    <row r="832" ht="14.25" customHeight="1" s="84"/>
-    <row r="833" ht="14.25" customHeight="1" s="84"/>
-    <row r="834" ht="14.25" customHeight="1" s="84"/>
-    <row r="835" ht="14.25" customHeight="1" s="84"/>
-    <row r="836" ht="14.25" customHeight="1" s="84"/>
-    <row r="837" ht="14.25" customHeight="1" s="84"/>
-    <row r="838" ht="14.25" customHeight="1" s="84"/>
-    <row r="839" ht="14.25" customHeight="1" s="84"/>
-    <row r="840" ht="14.25" customHeight="1" s="84"/>
-    <row r="841" ht="14.25" customHeight="1" s="84"/>
-    <row r="842" ht="14.25" customHeight="1" s="84"/>
-    <row r="843" ht="14.25" customHeight="1" s="84"/>
-    <row r="844" ht="14.25" customHeight="1" s="84"/>
-    <row r="845" ht="14.25" customHeight="1" s="84"/>
-    <row r="846" ht="14.25" customHeight="1" s="84"/>
-    <row r="847" ht="14.25" customHeight="1" s="84"/>
-    <row r="848" ht="14.25" customHeight="1" s="84"/>
-    <row r="849" ht="14.25" customHeight="1" s="84"/>
-    <row r="850" ht="14.25" customHeight="1" s="84"/>
-    <row r="851" ht="14.25" customHeight="1" s="84"/>
-    <row r="852" ht="14.25" customHeight="1" s="84"/>
-    <row r="853" ht="14.25" customHeight="1" s="84"/>
-    <row r="854" ht="14.25" customHeight="1" s="84"/>
-    <row r="855" ht="14.25" customHeight="1" s="84"/>
-    <row r="856" ht="14.25" customHeight="1" s="84"/>
-    <row r="857" ht="14.25" customHeight="1" s="84"/>
-    <row r="858" ht="14.25" customHeight="1" s="84"/>
-    <row r="859" ht="14.25" customHeight="1" s="84"/>
-    <row r="860" ht="14.25" customHeight="1" s="84"/>
-    <row r="861" ht="14.25" customHeight="1" s="84"/>
-    <row r="862" ht="14.25" customHeight="1" s="84"/>
-    <row r="863" ht="14.25" customHeight="1" s="84"/>
-    <row r="864" ht="14.25" customHeight="1" s="84"/>
-    <row r="865" ht="14.25" customHeight="1" s="84"/>
-    <row r="866" ht="14.25" customHeight="1" s="84"/>
-    <row r="867" ht="14.25" customHeight="1" s="84"/>
-    <row r="868" ht="14.25" customHeight="1" s="84"/>
-    <row r="869" ht="14.25" customHeight="1" s="84"/>
-    <row r="870" ht="14.25" customHeight="1" s="84"/>
-    <row r="871" ht="14.25" customHeight="1" s="84"/>
-    <row r="872" ht="14.25" customHeight="1" s="84"/>
-    <row r="873" ht="14.25" customHeight="1" s="84"/>
-    <row r="874" ht="14.25" customHeight="1" s="84"/>
-    <row r="875" ht="14.25" customHeight="1" s="84"/>
-    <row r="876" ht="14.25" customHeight="1" s="84"/>
-    <row r="877" ht="14.25" customHeight="1" s="84"/>
-    <row r="878" ht="14.25" customHeight="1" s="84"/>
-    <row r="879" ht="14.25" customHeight="1" s="84"/>
-    <row r="880" ht="14.25" customHeight="1" s="84"/>
-    <row r="881" ht="14.25" customHeight="1" s="84"/>
-    <row r="882" ht="14.25" customHeight="1" s="84"/>
-    <row r="883" ht="14.25" customHeight="1" s="84"/>
-    <row r="884" ht="14.25" customHeight="1" s="84"/>
-    <row r="885" ht="14.25" customHeight="1" s="84"/>
-    <row r="886" ht="14.25" customHeight="1" s="84"/>
-    <row r="887" ht="14.25" customHeight="1" s="84"/>
-    <row r="888" ht="14.25" customHeight="1" s="84"/>
-    <row r="889" ht="14.25" customHeight="1" s="84"/>
-    <row r="890" ht="14.25" customHeight="1" s="84"/>
-    <row r="891" ht="14.25" customHeight="1" s="84"/>
-    <row r="892" ht="14.25" customHeight="1" s="84"/>
-    <row r="893" ht="14.25" customHeight="1" s="84"/>
-    <row r="894" ht="14.25" customHeight="1" s="84"/>
-    <row r="895" ht="14.25" customHeight="1" s="84"/>
-    <row r="896" ht="14.25" customHeight="1" s="84"/>
-    <row r="897" ht="14.25" customHeight="1" s="84"/>
-    <row r="898" ht="14.25" customHeight="1" s="84"/>
-    <row r="899" ht="14.25" customHeight="1" s="84"/>
-    <row r="900" ht="14.25" customHeight="1" s="84"/>
-    <row r="901" ht="14.25" customHeight="1" s="84"/>
-    <row r="902" ht="14.25" customHeight="1" s="84"/>
-    <row r="903" ht="14.25" customHeight="1" s="84"/>
-    <row r="904" ht="14.25" customHeight="1" s="84"/>
-    <row r="905" ht="14.25" customHeight="1" s="84"/>
-    <row r="906" ht="14.25" customHeight="1" s="84"/>
-    <row r="907" ht="14.25" customHeight="1" s="84"/>
-    <row r="908" ht="14.25" customHeight="1" s="84"/>
-    <row r="909" ht="14.25" customHeight="1" s="84"/>
-    <row r="910" ht="14.25" customHeight="1" s="84"/>
-    <row r="911" ht="14.25" customHeight="1" s="84"/>
-    <row r="912" ht="14.25" customHeight="1" s="84"/>
-    <row r="913" ht="14.25" customHeight="1" s="84"/>
-    <row r="914" ht="14.25" customHeight="1" s="84"/>
-    <row r="915" ht="14.25" customHeight="1" s="84"/>
-    <row r="916" ht="14.25" customHeight="1" s="84"/>
-    <row r="917" ht="14.25" customHeight="1" s="84"/>
-    <row r="918" ht="14.25" customHeight="1" s="84"/>
-    <row r="919" ht="14.25" customHeight="1" s="84"/>
-    <row r="920" ht="14.25" customHeight="1" s="84"/>
-    <row r="921" ht="14.25" customHeight="1" s="84"/>
-    <row r="922" ht="14.25" customHeight="1" s="84"/>
-    <row r="923" ht="14.25" customHeight="1" s="84"/>
-    <row r="924" ht="14.25" customHeight="1" s="84"/>
-    <row r="925" ht="14.25" customHeight="1" s="84"/>
-    <row r="926" ht="14.25" customHeight="1" s="84"/>
-    <row r="927" ht="14.25" customHeight="1" s="84"/>
-    <row r="928" ht="14.25" customHeight="1" s="84"/>
-    <row r="929" ht="14.25" customHeight="1" s="84"/>
-    <row r="930" ht="14.25" customHeight="1" s="84"/>
-    <row r="931" ht="14.25" customHeight="1" s="84"/>
-    <row r="932" ht="14.25" customHeight="1" s="84"/>
-    <row r="933" ht="14.25" customHeight="1" s="84"/>
-    <row r="934" ht="14.25" customHeight="1" s="84"/>
-    <row r="935" ht="14.25" customHeight="1" s="84"/>
-    <row r="936" ht="14.25" customHeight="1" s="84"/>
-    <row r="937" ht="14.25" customHeight="1" s="84"/>
-    <row r="938" ht="14.25" customHeight="1" s="84"/>
-    <row r="939" ht="14.25" customHeight="1" s="84"/>
-    <row r="940" ht="14.25" customHeight="1" s="84"/>
-    <row r="941" ht="14.25" customHeight="1" s="84"/>
-    <row r="942" ht="14.25" customHeight="1" s="84"/>
-    <row r="943" ht="14.25" customHeight="1" s="84"/>
-    <row r="944" ht="14.25" customHeight="1" s="84"/>
-    <row r="945" ht="14.25" customHeight="1" s="84"/>
-    <row r="946" ht="14.25" customHeight="1" s="84"/>
-    <row r="947" ht="14.25" customHeight="1" s="84"/>
-    <row r="948" ht="14.25" customHeight="1" s="84"/>
-    <row r="949" ht="14.25" customHeight="1" s="84"/>
-    <row r="950" ht="14.25" customHeight="1" s="84"/>
-    <row r="951" ht="14.25" customHeight="1" s="84"/>
-    <row r="952" ht="14.25" customHeight="1" s="84"/>
-    <row r="953" ht="14.25" customHeight="1" s="84"/>
-    <row r="954" ht="14.25" customHeight="1" s="84"/>
-    <row r="955" ht="14.25" customHeight="1" s="84"/>
-    <row r="956" ht="14.25" customHeight="1" s="84"/>
-    <row r="957" ht="14.25" customHeight="1" s="84"/>
-    <row r="958" ht="14.25" customHeight="1" s="84"/>
-    <row r="959" ht="14.25" customHeight="1" s="84"/>
-    <row r="960" ht="14.25" customHeight="1" s="84"/>
-    <row r="961" ht="14.25" customHeight="1" s="84"/>
-    <row r="962" ht="14.25" customHeight="1" s="84"/>
-    <row r="963" ht="14.25" customHeight="1" s="84"/>
-    <row r="964" ht="14.25" customHeight="1" s="84"/>
-    <row r="965" ht="14.25" customHeight="1" s="84"/>
-    <row r="966" ht="14.25" customHeight="1" s="84"/>
-    <row r="967" ht="14.25" customHeight="1" s="84"/>
-    <row r="968" ht="14.25" customHeight="1" s="84"/>
-    <row r="969" ht="14.25" customHeight="1" s="84"/>
-    <row r="970" ht="14.25" customHeight="1" s="84"/>
-    <row r="971" ht="14.25" customHeight="1" s="84"/>
-    <row r="972" ht="14.25" customHeight="1" s="84"/>
-    <row r="973" ht="14.25" customHeight="1" s="84"/>
-    <row r="974" ht="14.25" customHeight="1" s="84"/>
-    <row r="975" ht="14.25" customHeight="1" s="84"/>
-    <row r="976" ht="14.25" customHeight="1" s="84"/>
-    <row r="977" ht="14.25" customHeight="1" s="84"/>
-    <row r="978" ht="14.25" customHeight="1" s="84"/>
-    <row r="979" ht="14.25" customHeight="1" s="84"/>
-    <row r="980" ht="14.25" customHeight="1" s="84"/>
-    <row r="981" ht="14.25" customHeight="1" s="84"/>
-    <row r="982" ht="14.25" customHeight="1" s="84"/>
-    <row r="983" ht="14.25" customHeight="1" s="84"/>
-    <row r="984" ht="14.25" customHeight="1" s="84"/>
-    <row r="985" ht="14.25" customHeight="1" s="84"/>
-    <row r="986" ht="14.25" customHeight="1" s="84"/>
-    <row r="987" ht="14.25" customHeight="1" s="84"/>
-    <row r="988" ht="14.25" customHeight="1" s="84"/>
-    <row r="989" ht="14.25" customHeight="1" s="84"/>
-    <row r="990" ht="14.25" customHeight="1" s="84"/>
-    <row r="991" ht="14.25" customHeight="1" s="84"/>
-    <row r="992" ht="14.25" customHeight="1" s="84"/>
-    <row r="993" ht="14.25" customHeight="1" s="84"/>
-    <row r="994" ht="14.25" customHeight="1" s="84"/>
-    <row r="995" ht="14.25" customHeight="1" s="84"/>
-    <row r="996" ht="14.25" customHeight="1" s="84"/>
-    <row r="997" ht="14.25" customHeight="1" s="84"/>
-    <row r="998" ht="14.25" customHeight="1" s="84"/>
+    <row r="220" ht="14.25" customHeight="1" s="90"/>
+    <row r="221" ht="14.25" customHeight="1" s="90"/>
+    <row r="222" ht="14.25" customHeight="1" s="90"/>
+    <row r="223" ht="14.25" customHeight="1" s="90"/>
+    <row r="224" ht="14.25" customHeight="1" s="90"/>
+    <row r="225" ht="14.25" customHeight="1" s="90"/>
+    <row r="226" ht="14.25" customHeight="1" s="90"/>
+    <row r="227" ht="14.25" customHeight="1" s="90"/>
+    <row r="228" ht="14.25" customHeight="1" s="90"/>
+    <row r="229" ht="14.25" customHeight="1" s="90"/>
+    <row r="230" ht="14.25" customHeight="1" s="90"/>
+    <row r="231" ht="14.25" customHeight="1" s="90"/>
+    <row r="232" ht="14.25" customHeight="1" s="90"/>
+    <row r="233" ht="14.25" customHeight="1" s="90"/>
+    <row r="234" ht="14.25" customHeight="1" s="90"/>
+    <row r="235" ht="14.25" customHeight="1" s="90"/>
+    <row r="236" ht="14.25" customHeight="1" s="90"/>
+    <row r="237" ht="14.25" customHeight="1" s="90"/>
+    <row r="238" ht="14.25" customHeight="1" s="90"/>
+    <row r="239" ht="14.25" customHeight="1" s="90"/>
+    <row r="240" ht="14.25" customHeight="1" s="90"/>
+    <row r="241" ht="14.25" customHeight="1" s="90"/>
+    <row r="242" ht="14.25" customHeight="1" s="90"/>
+    <row r="243" ht="14.25" customHeight="1" s="90"/>
+    <row r="244" ht="14.25" customHeight="1" s="90"/>
+    <row r="245" ht="14.25" customHeight="1" s="90"/>
+    <row r="246" ht="14.25" customHeight="1" s="90"/>
+    <row r="247" ht="14.25" customHeight="1" s="90"/>
+    <row r="248" ht="14.25" customHeight="1" s="90"/>
+    <row r="249" ht="14.25" customHeight="1" s="90"/>
+    <row r="250" ht="14.25" customHeight="1" s="90"/>
+    <row r="251" ht="14.25" customHeight="1" s="90"/>
+    <row r="252" ht="14.25" customHeight="1" s="90"/>
+    <row r="253" ht="14.25" customHeight="1" s="90"/>
+    <row r="254" ht="14.25" customHeight="1" s="90"/>
+    <row r="255" ht="14.25" customHeight="1" s="90"/>
+    <row r="256" ht="14.25" customHeight="1" s="90"/>
+    <row r="257" ht="14.25" customHeight="1" s="90"/>
+    <row r="258" ht="14.25" customHeight="1" s="90"/>
+    <row r="259" ht="14.25" customHeight="1" s="90"/>
+    <row r="260" ht="14.25" customHeight="1" s="90"/>
+    <row r="261" ht="14.25" customHeight="1" s="90"/>
+    <row r="262" ht="14.25" customHeight="1" s="90"/>
+    <row r="263" ht="14.25" customHeight="1" s="90"/>
+    <row r="264" ht="14.25" customHeight="1" s="90"/>
+    <row r="265" ht="14.25" customHeight="1" s="90"/>
+    <row r="266" ht="14.25" customHeight="1" s="90"/>
+    <row r="267" ht="14.25" customHeight="1" s="90"/>
+    <row r="268" ht="14.25" customHeight="1" s="90"/>
+    <row r="269" ht="14.25" customHeight="1" s="90"/>
+    <row r="270" ht="14.25" customHeight="1" s="90"/>
+    <row r="271" ht="14.25" customHeight="1" s="90"/>
+    <row r="272" ht="14.25" customHeight="1" s="90"/>
+    <row r="273" ht="14.25" customHeight="1" s="90"/>
+    <row r="274" ht="14.25" customHeight="1" s="90"/>
+    <row r="275" ht="14.25" customHeight="1" s="90"/>
+    <row r="276" ht="14.25" customHeight="1" s="90"/>
+    <row r="277" ht="14.25" customHeight="1" s="90"/>
+    <row r="278" ht="14.25" customHeight="1" s="90"/>
+    <row r="279" ht="14.25" customHeight="1" s="90"/>
+    <row r="280" ht="14.25" customHeight="1" s="90"/>
+    <row r="281" ht="14.25" customHeight="1" s="90"/>
+    <row r="282" ht="14.25" customHeight="1" s="90"/>
+    <row r="283" ht="14.25" customHeight="1" s="90"/>
+    <row r="284" ht="14.25" customHeight="1" s="90"/>
+    <row r="285" ht="14.25" customHeight="1" s="90"/>
+    <row r="286" ht="14.25" customHeight="1" s="90"/>
+    <row r="287" ht="14.25" customHeight="1" s="90"/>
+    <row r="288" ht="14.25" customHeight="1" s="90"/>
+    <row r="289" ht="14.25" customHeight="1" s="90"/>
+    <row r="290" ht="14.25" customHeight="1" s="90"/>
+    <row r="291" ht="14.25" customHeight="1" s="90"/>
+    <row r="292" ht="14.25" customHeight="1" s="90"/>
+    <row r="293" ht="14.25" customHeight="1" s="90"/>
+    <row r="294" ht="14.25" customHeight="1" s="90"/>
+    <row r="295" ht="14.25" customHeight="1" s="90"/>
+    <row r="296" ht="14.25" customHeight="1" s="90"/>
+    <row r="297" ht="14.25" customHeight="1" s="90"/>
+    <row r="298" ht="14.25" customHeight="1" s="90"/>
+    <row r="299" ht="14.25" customHeight="1" s="90"/>
+    <row r="300" ht="14.25" customHeight="1" s="90"/>
+    <row r="301" ht="14.25" customHeight="1" s="90"/>
+    <row r="302" ht="14.25" customHeight="1" s="90"/>
+    <row r="303" ht="14.25" customHeight="1" s="90"/>
+    <row r="304" ht="14.25" customHeight="1" s="90"/>
+    <row r="305" ht="14.25" customHeight="1" s="90"/>
+    <row r="306" ht="14.25" customHeight="1" s="90"/>
+    <row r="307" ht="14.25" customHeight="1" s="90"/>
+    <row r="308" ht="14.25" customHeight="1" s="90"/>
+    <row r="309" ht="14.25" customHeight="1" s="90"/>
+    <row r="310" ht="14.25" customHeight="1" s="90"/>
+    <row r="311" ht="14.25" customHeight="1" s="90"/>
+    <row r="312" ht="14.25" customHeight="1" s="90"/>
+    <row r="313" ht="14.25" customHeight="1" s="90"/>
+    <row r="314" ht="14.25" customHeight="1" s="90"/>
+    <row r="315" ht="14.25" customHeight="1" s="90"/>
+    <row r="316" ht="14.25" customHeight="1" s="90"/>
+    <row r="317" ht="14.25" customHeight="1" s="90"/>
+    <row r="318" ht="14.25" customHeight="1" s="90"/>
+    <row r="319" ht="14.25" customHeight="1" s="90"/>
+    <row r="320" ht="14.25" customHeight="1" s="90"/>
+    <row r="321" ht="14.25" customHeight="1" s="90"/>
+    <row r="322" ht="14.25" customHeight="1" s="90"/>
+    <row r="323" ht="14.25" customHeight="1" s="90"/>
+    <row r="324" ht="14.25" customHeight="1" s="90"/>
+    <row r="325" ht="14.25" customHeight="1" s="90"/>
+    <row r="326" ht="14.25" customHeight="1" s="90"/>
+    <row r="327" ht="14.25" customHeight="1" s="90"/>
+    <row r="328" ht="14.25" customHeight="1" s="90"/>
+    <row r="329" ht="14.25" customHeight="1" s="90"/>
+    <row r="330" ht="14.25" customHeight="1" s="90"/>
+    <row r="331" ht="14.25" customHeight="1" s="90"/>
+    <row r="332" ht="14.25" customHeight="1" s="90"/>
+    <row r="333" ht="14.25" customHeight="1" s="90"/>
+    <row r="334" ht="14.25" customHeight="1" s="90"/>
+    <row r="335" ht="14.25" customHeight="1" s="90"/>
+    <row r="336" ht="14.25" customHeight="1" s="90"/>
+    <row r="337" ht="14.25" customHeight="1" s="90"/>
+    <row r="338" ht="14.25" customHeight="1" s="90"/>
+    <row r="339" ht="14.25" customHeight="1" s="90"/>
+    <row r="340" ht="14.25" customHeight="1" s="90"/>
+    <row r="341" ht="14.25" customHeight="1" s="90"/>
+    <row r="342" ht="14.25" customHeight="1" s="90"/>
+    <row r="343" ht="14.25" customHeight="1" s="90"/>
+    <row r="344" ht="14.25" customHeight="1" s="90"/>
+    <row r="345" ht="14.25" customHeight="1" s="90"/>
+    <row r="346" ht="14.25" customHeight="1" s="90"/>
+    <row r="347" ht="14.25" customHeight="1" s="90"/>
+    <row r="348" ht="14.25" customHeight="1" s="90"/>
+    <row r="349" ht="14.25" customHeight="1" s="90"/>
+    <row r="350" ht="14.25" customHeight="1" s="90"/>
+    <row r="351" ht="14.25" customHeight="1" s="90"/>
+    <row r="352" ht="14.25" customHeight="1" s="90"/>
+    <row r="353" ht="14.25" customHeight="1" s="90"/>
+    <row r="354" ht="14.25" customHeight="1" s="90"/>
+    <row r="355" ht="14.25" customHeight="1" s="90"/>
+    <row r="356" ht="14.25" customHeight="1" s="90"/>
+    <row r="357" ht="14.25" customHeight="1" s="90"/>
+    <row r="358" ht="14.25" customHeight="1" s="90"/>
+    <row r="359" ht="14.25" customHeight="1" s="90"/>
+    <row r="360" ht="14.25" customHeight="1" s="90"/>
+    <row r="361" ht="14.25" customHeight="1" s="90"/>
+    <row r="362" ht="14.25" customHeight="1" s="90"/>
+    <row r="363" ht="14.25" customHeight="1" s="90"/>
+    <row r="364" ht="14.25" customHeight="1" s="90"/>
+    <row r="365" ht="14.25" customHeight="1" s="90"/>
+    <row r="366" ht="14.25" customHeight="1" s="90"/>
+    <row r="367" ht="14.25" customHeight="1" s="90"/>
+    <row r="368" ht="14.25" customHeight="1" s="90"/>
+    <row r="369" ht="14.25" customHeight="1" s="90"/>
+    <row r="370" ht="14.25" customHeight="1" s="90"/>
+    <row r="371" ht="14.25" customHeight="1" s="90"/>
+    <row r="372" ht="14.25" customHeight="1" s="90"/>
+    <row r="373" ht="14.25" customHeight="1" s="90"/>
+    <row r="374" ht="14.25" customHeight="1" s="90"/>
+    <row r="375" ht="14.25" customHeight="1" s="90"/>
+    <row r="376" ht="14.25" customHeight="1" s="90"/>
+    <row r="377" ht="14.25" customHeight="1" s="90"/>
+    <row r="378" ht="14.25" customHeight="1" s="90"/>
+    <row r="379" ht="14.25" customHeight="1" s="90"/>
+    <row r="380" ht="14.25" customHeight="1" s="90"/>
+    <row r="381" ht="14.25" customHeight="1" s="90"/>
+    <row r="382" ht="14.25" customHeight="1" s="90"/>
+    <row r="383" ht="14.25" customHeight="1" s="90"/>
+    <row r="384" ht="14.25" customHeight="1" s="90"/>
+    <row r="385" ht="14.25" customHeight="1" s="90"/>
+    <row r="386" ht="14.25" customHeight="1" s="90"/>
+    <row r="387" ht="14.25" customHeight="1" s="90"/>
+    <row r="388" ht="14.25" customHeight="1" s="90"/>
+    <row r="389" ht="14.25" customHeight="1" s="90"/>
+    <row r="390" ht="14.25" customHeight="1" s="90"/>
+    <row r="391" ht="14.25" customHeight="1" s="90"/>
+    <row r="392" ht="14.25" customHeight="1" s="90"/>
+    <row r="393" ht="14.25" customHeight="1" s="90"/>
+    <row r="394" ht="14.25" customHeight="1" s="90"/>
+    <row r="395" ht="14.25" customHeight="1" s="90"/>
+    <row r="396" ht="14.25" customHeight="1" s="90"/>
+    <row r="397" ht="14.25" customHeight="1" s="90"/>
+    <row r="398" ht="14.25" customHeight="1" s="90"/>
+    <row r="399" ht="14.25" customHeight="1" s="90"/>
+    <row r="400" ht="14.25" customHeight="1" s="90"/>
+    <row r="401" ht="14.25" customHeight="1" s="90"/>
+    <row r="402" ht="14.25" customHeight="1" s="90"/>
+    <row r="403" ht="14.25" customHeight="1" s="90"/>
+    <row r="404" ht="14.25" customHeight="1" s="90"/>
+    <row r="405" ht="14.25" customHeight="1" s="90"/>
+    <row r="406" ht="14.25" customHeight="1" s="90"/>
+    <row r="407" ht="14.25" customHeight="1" s="90"/>
+    <row r="408" ht="14.25" customHeight="1" s="90"/>
+    <row r="409" ht="14.25" customHeight="1" s="90"/>
+    <row r="410" ht="14.25" customHeight="1" s="90"/>
+    <row r="411" ht="14.25" customHeight="1" s="90"/>
+    <row r="412" ht="14.25" customHeight="1" s="90"/>
+    <row r="413" ht="14.25" customHeight="1" s="90"/>
+    <row r="414" ht="14.25" customHeight="1" s="90"/>
+    <row r="415" ht="14.25" customHeight="1" s="90"/>
+    <row r="416" ht="14.25" customHeight="1" s="90"/>
+    <row r="417" ht="14.25" customHeight="1" s="90"/>
+    <row r="418" ht="14.25" customHeight="1" s="90"/>
+    <row r="419" ht="14.25" customHeight="1" s="90"/>
+    <row r="420" ht="14.25" customHeight="1" s="90"/>
+    <row r="421" ht="14.25" customHeight="1" s="90"/>
+    <row r="422" ht="14.25" customHeight="1" s="90"/>
+    <row r="423" ht="14.25" customHeight="1" s="90"/>
+    <row r="424" ht="14.25" customHeight="1" s="90"/>
+    <row r="425" ht="14.25" customHeight="1" s="90"/>
+    <row r="426" ht="14.25" customHeight="1" s="90"/>
+    <row r="427" ht="14.25" customHeight="1" s="90"/>
+    <row r="428" ht="14.25" customHeight="1" s="90"/>
+    <row r="429" ht="14.25" customHeight="1" s="90"/>
+    <row r="430" ht="14.25" customHeight="1" s="90"/>
+    <row r="431" ht="14.25" customHeight="1" s="90"/>
+    <row r="432" ht="14.25" customHeight="1" s="90"/>
+    <row r="433" ht="14.25" customHeight="1" s="90"/>
+    <row r="434" ht="14.25" customHeight="1" s="90"/>
+    <row r="435" ht="14.25" customHeight="1" s="90"/>
+    <row r="436" ht="14.25" customHeight="1" s="90"/>
+    <row r="437" ht="14.25" customHeight="1" s="90"/>
+    <row r="438" ht="14.25" customHeight="1" s="90"/>
+    <row r="439" ht="14.25" customHeight="1" s="90"/>
+    <row r="440" ht="14.25" customHeight="1" s="90"/>
+    <row r="441" ht="14.25" customHeight="1" s="90"/>
+    <row r="442" ht="14.25" customHeight="1" s="90"/>
+    <row r="443" ht="14.25" customHeight="1" s="90"/>
+    <row r="444" ht="14.25" customHeight="1" s="90"/>
+    <row r="445" ht="14.25" customHeight="1" s="90"/>
+    <row r="446" ht="14.25" customHeight="1" s="90"/>
+    <row r="447" ht="14.25" customHeight="1" s="90"/>
+    <row r="448" ht="14.25" customHeight="1" s="90"/>
+    <row r="449" ht="14.25" customHeight="1" s="90"/>
+    <row r="450" ht="14.25" customHeight="1" s="90"/>
+    <row r="451" ht="14.25" customHeight="1" s="90"/>
+    <row r="452" ht="14.25" customHeight="1" s="90"/>
+    <row r="453" ht="14.25" customHeight="1" s="90"/>
+    <row r="454" ht="14.25" customHeight="1" s="90"/>
+    <row r="455" ht="14.25" customHeight="1" s="90"/>
+    <row r="456" ht="14.25" customHeight="1" s="90"/>
+    <row r="457" ht="14.25" customHeight="1" s="90"/>
+    <row r="458" ht="14.25" customHeight="1" s="90"/>
+    <row r="459" ht="14.25" customHeight="1" s="90"/>
+    <row r="460" ht="14.25" customHeight="1" s="90"/>
+    <row r="461" ht="14.25" customHeight="1" s="90"/>
+    <row r="462" ht="14.25" customHeight="1" s="90"/>
+    <row r="463" ht="14.25" customHeight="1" s="90"/>
+    <row r="464" ht="14.25" customHeight="1" s="90"/>
+    <row r="465" ht="14.25" customHeight="1" s="90"/>
+    <row r="466" ht="14.25" customHeight="1" s="90"/>
+    <row r="467" ht="14.25" customHeight="1" s="90"/>
+    <row r="468" ht="14.25" customHeight="1" s="90"/>
+    <row r="469" ht="14.25" customHeight="1" s="90"/>
+    <row r="470" ht="14.25" customHeight="1" s="90"/>
+    <row r="471" ht="14.25" customHeight="1" s="90"/>
+    <row r="472" ht="14.25" customHeight="1" s="90"/>
+    <row r="473" ht="14.25" customHeight="1" s="90"/>
+    <row r="474" ht="14.25" customHeight="1" s="90"/>
+    <row r="475" ht="14.25" customHeight="1" s="90"/>
+    <row r="476" ht="14.25" customHeight="1" s="90"/>
+    <row r="477" ht="14.25" customHeight="1" s="90"/>
+    <row r="478" ht="14.25" customHeight="1" s="90"/>
+    <row r="479" ht="14.25" customHeight="1" s="90"/>
+    <row r="480" ht="14.25" customHeight="1" s="90"/>
+    <row r="481" ht="14.25" customHeight="1" s="90"/>
+    <row r="482" ht="14.25" customHeight="1" s="90"/>
+    <row r="483" ht="14.25" customHeight="1" s="90"/>
+    <row r="484" ht="14.25" customHeight="1" s="90"/>
+    <row r="485" ht="14.25" customHeight="1" s="90"/>
+    <row r="486" ht="14.25" customHeight="1" s="90"/>
+    <row r="487" ht="14.25" customHeight="1" s="90"/>
+    <row r="488" ht="14.25" customHeight="1" s="90"/>
+    <row r="489" ht="14.25" customHeight="1" s="90"/>
+    <row r="490" ht="14.25" customHeight="1" s="90"/>
+    <row r="491" ht="14.25" customHeight="1" s="90"/>
+    <row r="492" ht="14.25" customHeight="1" s="90"/>
+    <row r="493" ht="14.25" customHeight="1" s="90"/>
+    <row r="494" ht="14.25" customHeight="1" s="90"/>
+    <row r="495" ht="14.25" customHeight="1" s="90"/>
+    <row r="496" ht="14.25" customHeight="1" s="90"/>
+    <row r="497" ht="14.25" customHeight="1" s="90"/>
+    <row r="498" ht="14.25" customHeight="1" s="90"/>
+    <row r="499" ht="14.25" customHeight="1" s="90"/>
+    <row r="500" ht="14.25" customHeight="1" s="90"/>
+    <row r="501" ht="14.25" customHeight="1" s="90"/>
+    <row r="502" ht="14.25" customHeight="1" s="90"/>
+    <row r="503" ht="14.25" customHeight="1" s="90"/>
+    <row r="504" ht="14.25" customHeight="1" s="90"/>
+    <row r="505" ht="14.25" customHeight="1" s="90"/>
+    <row r="506" ht="14.25" customHeight="1" s="90"/>
+    <row r="507" ht="14.25" customHeight="1" s="90"/>
+    <row r="508" ht="14.25" customHeight="1" s="90"/>
+    <row r="509" ht="14.25" customHeight="1" s="90"/>
+    <row r="510" ht="14.25" customHeight="1" s="90"/>
+    <row r="511" ht="14.25" customHeight="1" s="90"/>
+    <row r="512" ht="14.25" customHeight="1" s="90"/>
+    <row r="513" ht="14.25" customHeight="1" s="90"/>
+    <row r="514" ht="14.25" customHeight="1" s="90"/>
+    <row r="515" ht="14.25" customHeight="1" s="90"/>
+    <row r="516" ht="14.25" customHeight="1" s="90"/>
+    <row r="517" ht="14.25" customHeight="1" s="90"/>
+    <row r="518" ht="14.25" customHeight="1" s="90"/>
+    <row r="519" ht="14.25" customHeight="1" s="90"/>
+    <row r="520" ht="14.25" customHeight="1" s="90"/>
+    <row r="521" ht="14.25" customHeight="1" s="90"/>
+    <row r="522" ht="14.25" customHeight="1" s="90"/>
+    <row r="523" ht="14.25" customHeight="1" s="90"/>
+    <row r="524" ht="14.25" customHeight="1" s="90"/>
+    <row r="525" ht="14.25" customHeight="1" s="90"/>
+    <row r="526" ht="14.25" customHeight="1" s="90"/>
+    <row r="527" ht="14.25" customHeight="1" s="90"/>
+    <row r="528" ht="14.25" customHeight="1" s="90"/>
+    <row r="529" ht="14.25" customHeight="1" s="90"/>
+    <row r="530" ht="14.25" customHeight="1" s="90"/>
+    <row r="531" ht="14.25" customHeight="1" s="90"/>
+    <row r="532" ht="14.25" customHeight="1" s="90"/>
+    <row r="533" ht="14.25" customHeight="1" s="90"/>
+    <row r="534" ht="14.25" customHeight="1" s="90"/>
+    <row r="535" ht="14.25" customHeight="1" s="90"/>
+    <row r="536" ht="14.25" customHeight="1" s="90"/>
+    <row r="537" ht="14.25" customHeight="1" s="90"/>
+    <row r="538" ht="14.25" customHeight="1" s="90"/>
+    <row r="539" ht="14.25" customHeight="1" s="90"/>
+    <row r="540" ht="14.25" customHeight="1" s="90"/>
+    <row r="541" ht="14.25" customHeight="1" s="90"/>
+    <row r="542" ht="14.25" customHeight="1" s="90"/>
+    <row r="543" ht="14.25" customHeight="1" s="90"/>
+    <row r="544" ht="14.25" customHeight="1" s="90"/>
+    <row r="545" ht="14.25" customHeight="1" s="90"/>
+    <row r="546" ht="14.25" customHeight="1" s="90"/>
+    <row r="547" ht="14.25" customHeight="1" s="90"/>
+    <row r="548" ht="14.25" customHeight="1" s="90"/>
+    <row r="549" ht="14.25" customHeight="1" s="90"/>
+    <row r="550" ht="14.25" customHeight="1" s="90"/>
+    <row r="551" ht="14.25" customHeight="1" s="90"/>
+    <row r="552" ht="14.25" customHeight="1" s="90"/>
+    <row r="553" ht="14.25" customHeight="1" s="90"/>
+    <row r="554" ht="14.25" customHeight="1" s="90"/>
+    <row r="555" ht="14.25" customHeight="1" s="90"/>
+    <row r="556" ht="14.25" customHeight="1" s="90"/>
+    <row r="557" ht="14.25" customHeight="1" s="90"/>
+    <row r="558" ht="14.25" customHeight="1" s="90"/>
+    <row r="559" ht="14.25" customHeight="1" s="90"/>
+    <row r="560" ht="14.25" customHeight="1" s="90"/>
+    <row r="561" ht="14.25" customHeight="1" s="90"/>
+    <row r="562" ht="14.25" customHeight="1" s="90"/>
+    <row r="563" ht="14.25" customHeight="1" s="90"/>
+    <row r="564" ht="14.25" customHeight="1" s="90"/>
+    <row r="565" ht="14.25" customHeight="1" s="90"/>
+    <row r="566" ht="14.25" customHeight="1" s="90"/>
+    <row r="567" ht="14.25" customHeight="1" s="90"/>
+    <row r="568" ht="14.25" customHeight="1" s="90"/>
+    <row r="569" ht="14.25" customHeight="1" s="90"/>
+    <row r="570" ht="14.25" customHeight="1" s="90"/>
+    <row r="571" ht="14.25" customHeight="1" s="90"/>
+    <row r="572" ht="14.25" customHeight="1" s="90"/>
+    <row r="573" ht="14.25" customHeight="1" s="90"/>
+    <row r="574" ht="14.25" customHeight="1" s="90"/>
+    <row r="575" ht="14.25" customHeight="1" s="90"/>
+    <row r="576" ht="14.25" customHeight="1" s="90"/>
+    <row r="577" ht="14.25" customHeight="1" s="90"/>
+    <row r="578" ht="14.25" customHeight="1" s="90"/>
+    <row r="579" ht="14.25" customHeight="1" s="90"/>
+    <row r="580" ht="14.25" customHeight="1" s="90"/>
+    <row r="581" ht="14.25" customHeight="1" s="90"/>
+    <row r="582" ht="14.25" customHeight="1" s="90"/>
+    <row r="583" ht="14.25" customHeight="1" s="90"/>
+    <row r="584" ht="14.25" customHeight="1" s="90"/>
+    <row r="585" ht="14.25" customHeight="1" s="90"/>
+    <row r="586" ht="14.25" customHeight="1" s="90"/>
+    <row r="587" ht="14.25" customHeight="1" s="90"/>
+    <row r="588" ht="14.25" customHeight="1" s="90"/>
+    <row r="589" ht="14.25" customHeight="1" s="90"/>
+    <row r="590" ht="14.25" customHeight="1" s="90"/>
+    <row r="591" ht="14.25" customHeight="1" s="90"/>
+    <row r="592" ht="14.25" customHeight="1" s="90"/>
+    <row r="593" ht="14.25" customHeight="1" s="90"/>
+    <row r="594" ht="14.25" customHeight="1" s="90"/>
+    <row r="595" ht="14.25" customHeight="1" s="90"/>
+    <row r="596" ht="14.25" customHeight="1" s="90"/>
+    <row r="597" ht="14.25" customHeight="1" s="90"/>
+    <row r="598" ht="14.25" customHeight="1" s="90"/>
+    <row r="599" ht="14.25" customHeight="1" s="90"/>
+    <row r="600" ht="14.25" customHeight="1" s="90"/>
+    <row r="601" ht="14.25" customHeight="1" s="90"/>
+    <row r="602" ht="14.25" customHeight="1" s="90"/>
+    <row r="603" ht="14.25" customHeight="1" s="90"/>
+    <row r="604" ht="14.25" customHeight="1" s="90"/>
+    <row r="605" ht="14.25" customHeight="1" s="90"/>
+    <row r="606" ht="14.25" customHeight="1" s="90"/>
+    <row r="607" ht="14.25" customHeight="1" s="90"/>
+    <row r="608" ht="14.25" customHeight="1" s="90"/>
+    <row r="609" ht="14.25" customHeight="1" s="90"/>
+    <row r="610" ht="14.25" customHeight="1" s="90"/>
+    <row r="611" ht="14.25" customHeight="1" s="90"/>
+    <row r="612" ht="14.25" customHeight="1" s="90"/>
+    <row r="613" ht="14.25" customHeight="1" s="90"/>
+    <row r="614" ht="14.25" customHeight="1" s="90"/>
+    <row r="615" ht="14.25" customHeight="1" s="90"/>
+    <row r="616" ht="14.25" customHeight="1" s="90"/>
+    <row r="617" ht="14.25" customHeight="1" s="90"/>
+    <row r="618" ht="14.25" customHeight="1" s="90"/>
+    <row r="619" ht="14.25" customHeight="1" s="90"/>
+    <row r="620" ht="14.25" customHeight="1" s="90"/>
+    <row r="621" ht="14.25" customHeight="1" s="90"/>
+    <row r="622" ht="14.25" customHeight="1" s="90"/>
+    <row r="623" ht="14.25" customHeight="1" s="90"/>
+    <row r="624" ht="14.25" customHeight="1" s="90"/>
+    <row r="625" ht="14.25" customHeight="1" s="90"/>
+    <row r="626" ht="14.25" customHeight="1" s="90"/>
+    <row r="627" ht="14.25" customHeight="1" s="90"/>
+    <row r="628" ht="14.25" customHeight="1" s="90"/>
+    <row r="629" ht="14.25" customHeight="1" s="90"/>
+    <row r="630" ht="14.25" customHeight="1" s="90"/>
+    <row r="631" ht="14.25" customHeight="1" s="90"/>
+    <row r="632" ht="14.25" customHeight="1" s="90"/>
+    <row r="633" ht="14.25" customHeight="1" s="90"/>
+    <row r="634" ht="14.25" customHeight="1" s="90"/>
+    <row r="635" ht="14.25" customHeight="1" s="90"/>
+    <row r="636" ht="14.25" customHeight="1" s="90"/>
+    <row r="637" ht="14.25" customHeight="1" s="90"/>
+    <row r="638" ht="14.25" customHeight="1" s="90"/>
+    <row r="639" ht="14.25" customHeight="1" s="90"/>
+    <row r="640" ht="14.25" customHeight="1" s="90"/>
+    <row r="641" ht="14.25" customHeight="1" s="90"/>
+    <row r="642" ht="14.25" customHeight="1" s="90"/>
+    <row r="643" ht="14.25" customHeight="1" s="90"/>
+    <row r="644" ht="14.25" customHeight="1" s="90"/>
+    <row r="645" ht="14.25" customHeight="1" s="90"/>
+    <row r="646" ht="14.25" customHeight="1" s="90"/>
+    <row r="647" ht="14.25" customHeight="1" s="90"/>
+    <row r="648" ht="14.25" customHeight="1" s="90"/>
+    <row r="649" ht="14.25" customHeight="1" s="90"/>
+    <row r="650" ht="14.25" customHeight="1" s="90"/>
+    <row r="651" ht="14.25" customHeight="1" s="90"/>
+    <row r="652" ht="14.25" customHeight="1" s="90"/>
+    <row r="653" ht="14.25" customHeight="1" s="90"/>
+    <row r="654" ht="14.25" customHeight="1" s="90"/>
+    <row r="655" ht="14.25" customHeight="1" s="90"/>
+    <row r="656" ht="14.25" customHeight="1" s="90"/>
+    <row r="657" ht="14.25" customHeight="1" s="90"/>
+    <row r="658" ht="14.25" customHeight="1" s="90"/>
+    <row r="659" ht="14.25" customHeight="1" s="90"/>
+    <row r="660" ht="14.25" customHeight="1" s="90"/>
+    <row r="661" ht="14.25" customHeight="1" s="90"/>
+    <row r="662" ht="14.25" customHeight="1" s="90"/>
+    <row r="663" ht="14.25" customHeight="1" s="90"/>
+    <row r="664" ht="14.25" customHeight="1" s="90"/>
+    <row r="665" ht="14.25" customHeight="1" s="90"/>
+    <row r="666" ht="14.25" customHeight="1" s="90"/>
+    <row r="667" ht="14.25" customHeight="1" s="90"/>
+    <row r="668" ht="14.25" customHeight="1" s="90"/>
+    <row r="669" ht="14.25" customHeight="1" s="90"/>
+    <row r="670" ht="14.25" customHeight="1" s="90"/>
+    <row r="671" ht="14.25" customHeight="1" s="90"/>
+    <row r="672" ht="14.25" customHeight="1" s="90"/>
+    <row r="673" ht="14.25" customHeight="1" s="90"/>
+    <row r="674" ht="14.25" customHeight="1" s="90"/>
+    <row r="675" ht="14.25" customHeight="1" s="90"/>
+    <row r="676" ht="14.25" customHeight="1" s="90"/>
+    <row r="677" ht="14.25" customHeight="1" s="90"/>
+    <row r="678" ht="14.25" customHeight="1" s="90"/>
+    <row r="679" ht="14.25" customHeight="1" s="90"/>
+    <row r="680" ht="14.25" customHeight="1" s="90"/>
+    <row r="681" ht="14.25" customHeight="1" s="90"/>
+    <row r="682" ht="14.25" customHeight="1" s="90"/>
+    <row r="683" ht="14.25" customHeight="1" s="90"/>
+    <row r="684" ht="14.25" customHeight="1" s="90"/>
+    <row r="685" ht="14.25" customHeight="1" s="90"/>
+    <row r="686" ht="14.25" customHeight="1" s="90"/>
+    <row r="687" ht="14.25" customHeight="1" s="90"/>
+    <row r="688" ht="14.25" customHeight="1" s="90"/>
+    <row r="689" ht="14.25" customHeight="1" s="90"/>
+    <row r="690" ht="14.25" customHeight="1" s="90"/>
+    <row r="691" ht="14.25" customHeight="1" s="90"/>
+    <row r="692" ht="14.25" customHeight="1" s="90"/>
+    <row r="693" ht="14.25" customHeight="1" s="90"/>
+    <row r="694" ht="14.25" customHeight="1" s="90"/>
+    <row r="695" ht="14.25" customHeight="1" s="90"/>
+    <row r="696" ht="14.25" customHeight="1" s="90"/>
+    <row r="697" ht="14.25" customHeight="1" s="90"/>
+    <row r="698" ht="14.25" customHeight="1" s="90"/>
+    <row r="699" ht="14.25" customHeight="1" s="90"/>
+    <row r="700" ht="14.25" customHeight="1" s="90"/>
+    <row r="701" ht="14.25" customHeight="1" s="90"/>
+    <row r="702" ht="14.25" customHeight="1" s="90"/>
+    <row r="703" ht="14.25" customHeight="1" s="90"/>
+    <row r="704" ht="14.25" customHeight="1" s="90"/>
+    <row r="705" ht="14.25" customHeight="1" s="90"/>
+    <row r="706" ht="14.25" customHeight="1" s="90"/>
+    <row r="707" ht="14.25" customHeight="1" s="90"/>
+    <row r="708" ht="14.25" customHeight="1" s="90"/>
+    <row r="709" ht="14.25" customHeight="1" s="90"/>
+    <row r="710" ht="14.25" customHeight="1" s="90"/>
+    <row r="711" ht="14.25" customHeight="1" s="90"/>
+    <row r="712" ht="14.25" customHeight="1" s="90"/>
+    <row r="713" ht="14.25" customHeight="1" s="90"/>
+    <row r="714" ht="14.25" customHeight="1" s="90"/>
+    <row r="715" ht="14.25" customHeight="1" s="90"/>
+    <row r="716" ht="14.25" customHeight="1" s="90"/>
+    <row r="717" ht="14.25" customHeight="1" s="90"/>
+    <row r="718" ht="14.25" customHeight="1" s="90"/>
+    <row r="719" ht="14.25" customHeight="1" s="90"/>
+    <row r="720" ht="14.25" customHeight="1" s="90"/>
+    <row r="721" ht="14.25" customHeight="1" s="90"/>
+    <row r="722" ht="14.25" customHeight="1" s="90"/>
+    <row r="723" ht="14.25" customHeight="1" s="90"/>
+    <row r="724" ht="14.25" customHeight="1" s="90"/>
+    <row r="725" ht="14.25" customHeight="1" s="90"/>
+    <row r="726" ht="14.25" customHeight="1" s="90"/>
+    <row r="727" ht="14.25" customHeight="1" s="90"/>
+    <row r="728" ht="14.25" customHeight="1" s="90"/>
+    <row r="729" ht="14.25" customHeight="1" s="90"/>
+    <row r="730" ht="14.25" customHeight="1" s="90"/>
+    <row r="731" ht="14.25" customHeight="1" s="90"/>
+    <row r="732" ht="14.25" customHeight="1" s="90"/>
+    <row r="733" ht="14.25" customHeight="1" s="90"/>
+    <row r="734" ht="14.25" customHeight="1" s="90"/>
+    <row r="735" ht="14.25" customHeight="1" s="90"/>
+    <row r="736" ht="14.25" customHeight="1" s="90"/>
+    <row r="737" ht="14.25" customHeight="1" s="90"/>
+    <row r="738" ht="14.25" customHeight="1" s="90"/>
+    <row r="739" ht="14.25" customHeight="1" s="90"/>
+    <row r="740" ht="14.25" customHeight="1" s="90"/>
+    <row r="741" ht="14.25" customHeight="1" s="90"/>
+    <row r="742" ht="14.25" customHeight="1" s="90"/>
+    <row r="743" ht="14.25" customHeight="1" s="90"/>
+    <row r="744" ht="14.25" customHeight="1" s="90"/>
+    <row r="745" ht="14.25" customHeight="1" s="90"/>
+    <row r="746" ht="14.25" customHeight="1" s="90"/>
+    <row r="747" ht="14.25" customHeight="1" s="90"/>
+    <row r="748" ht="14.25" customHeight="1" s="90"/>
+    <row r="749" ht="14.25" customHeight="1" s="90"/>
+    <row r="750" ht="14.25" customHeight="1" s="90"/>
+    <row r="751" ht="14.25" customHeight="1" s="90"/>
+    <row r="752" ht="14.25" customHeight="1" s="90"/>
+    <row r="753" ht="14.25" customHeight="1" s="90"/>
+    <row r="754" ht="14.25" customHeight="1" s="90"/>
+    <row r="755" ht="14.25" customHeight="1" s="90"/>
+    <row r="756" ht="14.25" customHeight="1" s="90"/>
+    <row r="757" ht="14.25" customHeight="1" s="90"/>
+    <row r="758" ht="14.25" customHeight="1" s="90"/>
+    <row r="759" ht="14.25" customHeight="1" s="90"/>
+    <row r="760" ht="14.25" customHeight="1" s="90"/>
+    <row r="761" ht="14.25" customHeight="1" s="90"/>
+    <row r="762" ht="14.25" customHeight="1" s="90"/>
+    <row r="763" ht="14.25" customHeight="1" s="90"/>
+    <row r="764" ht="14.25" customHeight="1" s="90"/>
+    <row r="765" ht="14.25" customHeight="1" s="90"/>
+    <row r="766" ht="14.25" customHeight="1" s="90"/>
+    <row r="767" ht="14.25" customHeight="1" s="90"/>
+    <row r="768" ht="14.25" customHeight="1" s="90"/>
+    <row r="769" ht="14.25" customHeight="1" s="90"/>
+    <row r="770" ht="14.25" customHeight="1" s="90"/>
+    <row r="771" ht="14.25" customHeight="1" s="90"/>
+    <row r="772" ht="14.25" customHeight="1" s="90"/>
+    <row r="773" ht="14.25" customHeight="1" s="90"/>
+    <row r="774" ht="14.25" customHeight="1" s="90"/>
+    <row r="775" ht="14.25" customHeight="1" s="90"/>
+    <row r="776" ht="14.25" customHeight="1" s="90"/>
+    <row r="777" ht="14.25" customHeight="1" s="90"/>
+    <row r="778" ht="14.25" customHeight="1" s="90"/>
+    <row r="779" ht="14.25" customHeight="1" s="90"/>
+    <row r="780" ht="14.25" customHeight="1" s="90"/>
+    <row r="781" ht="14.25" customHeight="1" s="90"/>
+    <row r="782" ht="14.25" customHeight="1" s="90"/>
+    <row r="783" ht="14.25" customHeight="1" s="90"/>
+    <row r="784" ht="14.25" customHeight="1" s="90"/>
+    <row r="785" ht="14.25" customHeight="1" s="90"/>
+    <row r="786" ht="14.25" customHeight="1" s="90"/>
+    <row r="787" ht="14.25" customHeight="1" s="90"/>
+    <row r="788" ht="14.25" customHeight="1" s="90"/>
+    <row r="789" ht="14.25" customHeight="1" s="90"/>
+    <row r="790" ht="14.25" customHeight="1" s="90"/>
+    <row r="791" ht="14.25" customHeight="1" s="90"/>
+    <row r="792" ht="14.25" customHeight="1" s="90"/>
+    <row r="793" ht="14.25" customHeight="1" s="90"/>
+    <row r="794" ht="14.25" customHeight="1" s="90"/>
+    <row r="795" ht="14.25" customHeight="1" s="90"/>
+    <row r="796" ht="14.25" customHeight="1" s="90"/>
+    <row r="797" ht="14.25" customHeight="1" s="90"/>
+    <row r="798" ht="14.25" customHeight="1" s="90"/>
+    <row r="799" ht="14.25" customHeight="1" s="90"/>
+    <row r="800" ht="14.25" customHeight="1" s="90"/>
+    <row r="801" ht="14.25" customHeight="1" s="90"/>
+    <row r="802" ht="14.25" customHeight="1" s="90"/>
+    <row r="803" ht="14.25" customHeight="1" s="90"/>
+    <row r="804" ht="14.25" customHeight="1" s="90"/>
+    <row r="805" ht="14.25" customHeight="1" s="90"/>
+    <row r="806" ht="14.25" customHeight="1" s="90"/>
+    <row r="807" ht="14.25" customHeight="1" s="90"/>
+    <row r="808" ht="14.25" customHeight="1" s="90"/>
+    <row r="809" ht="14.25" customHeight="1" s="90"/>
+    <row r="810" ht="14.25" customHeight="1" s="90"/>
+    <row r="811" ht="14.25" customHeight="1" s="90"/>
+    <row r="812" ht="14.25" customHeight="1" s="90"/>
+    <row r="813" ht="14.25" customHeight="1" s="90"/>
+    <row r="814" ht="14.25" customHeight="1" s="90"/>
+    <row r="815" ht="14.25" customHeight="1" s="90"/>
+    <row r="816" ht="14.25" customHeight="1" s="90"/>
+    <row r="817" ht="14.25" customHeight="1" s="90"/>
+    <row r="818" ht="14.25" customHeight="1" s="90"/>
+    <row r="819" ht="14.25" customHeight="1" s="90"/>
+    <row r="820" ht="14.25" customHeight="1" s="90"/>
+    <row r="821" ht="14.25" customHeight="1" s="90"/>
+    <row r="822" ht="14.25" customHeight="1" s="90"/>
+    <row r="823" ht="14.25" customHeight="1" s="90"/>
+    <row r="824" ht="14.25" customHeight="1" s="90"/>
+    <row r="825" ht="14.25" customHeight="1" s="90"/>
+    <row r="826" ht="14.25" customHeight="1" s="90"/>
+    <row r="827" ht="14.25" customHeight="1" s="90"/>
+    <row r="828" ht="14.25" customHeight="1" s="90"/>
+    <row r="829" ht="14.25" customHeight="1" s="90"/>
+    <row r="830" ht="14.25" customHeight="1" s="90"/>
+    <row r="831" ht="14.25" customHeight="1" s="90"/>
+    <row r="832" ht="14.25" customHeight="1" s="90"/>
+    <row r="833" ht="14.25" customHeight="1" s="90"/>
+    <row r="834" ht="14.25" customHeight="1" s="90"/>
+    <row r="835" ht="14.25" customHeight="1" s="90"/>
+    <row r="836" ht="14.25" customHeight="1" s="90"/>
+    <row r="837" ht="14.25" customHeight="1" s="90"/>
+    <row r="838" ht="14.25" customHeight="1" s="90"/>
+    <row r="839" ht="14.25" customHeight="1" s="90"/>
+    <row r="840" ht="14.25" customHeight="1" s="90"/>
+    <row r="841" ht="14.25" customHeight="1" s="90"/>
+    <row r="842" ht="14.25" customHeight="1" s="90"/>
+    <row r="843" ht="14.25" customHeight="1" s="90"/>
+    <row r="844" ht="14.25" customHeight="1" s="90"/>
+    <row r="845" ht="14.25" customHeight="1" s="90"/>
+    <row r="846" ht="14.25" customHeight="1" s="90"/>
+    <row r="847" ht="14.25" customHeight="1" s="90"/>
+    <row r="848" ht="14.25" customHeight="1" s="90"/>
+    <row r="849" ht="14.25" customHeight="1" s="90"/>
+    <row r="850" ht="14.25" customHeight="1" s="90"/>
+    <row r="851" ht="14.25" customHeight="1" s="90"/>
+    <row r="852" ht="14.25" customHeight="1" s="90"/>
+    <row r="853" ht="14.25" customHeight="1" s="90"/>
+    <row r="854" ht="14.25" customHeight="1" s="90"/>
+    <row r="855" ht="14.25" customHeight="1" s="90"/>
+    <row r="856" ht="14.25" customHeight="1" s="90"/>
+    <row r="857" ht="14.25" customHeight="1" s="90"/>
+    <row r="858" ht="14.25" customHeight="1" s="90"/>
+    <row r="859" ht="14.25" customHeight="1" s="90"/>
+    <row r="860" ht="14.25" customHeight="1" s="90"/>
+    <row r="861" ht="14.25" customHeight="1" s="90"/>
+    <row r="862" ht="14.25" customHeight="1" s="90"/>
+    <row r="863" ht="14.25" customHeight="1" s="90"/>
+    <row r="864" ht="14.25" customHeight="1" s="90"/>
+    <row r="865" ht="14.25" customHeight="1" s="90"/>
+    <row r="866" ht="14.25" customHeight="1" s="90"/>
+    <row r="867" ht="14.25" customHeight="1" s="90"/>
+    <row r="868" ht="14.25" customHeight="1" s="90"/>
+    <row r="869" ht="14.25" customHeight="1" s="90"/>
+    <row r="870" ht="14.25" customHeight="1" s="90"/>
+    <row r="871" ht="14.25" customHeight="1" s="90"/>
+    <row r="872" ht="14.25" customHeight="1" s="90"/>
+    <row r="873" ht="14.25" customHeight="1" s="90"/>
+    <row r="874" ht="14.25" customHeight="1" s="90"/>
+    <row r="875" ht="14.25" customHeight="1" s="90"/>
+    <row r="876" ht="14.25" customHeight="1" s="90"/>
+    <row r="877" ht="14.25" customHeight="1" s="90"/>
+    <row r="878" ht="14.25" customHeight="1" s="90"/>
+    <row r="879" ht="14.25" customHeight="1" s="90"/>
+    <row r="880" ht="14.25" customHeight="1" s="90"/>
+    <row r="881" ht="14.25" customHeight="1" s="90"/>
+    <row r="882" ht="14.25" customHeight="1" s="90"/>
+    <row r="883" ht="14.25" customHeight="1" s="90"/>
+    <row r="884" ht="14.25" customHeight="1" s="90"/>
+    <row r="885" ht="14.25" customHeight="1" s="90"/>
+    <row r="886" ht="14.25" customHeight="1" s="90"/>
+    <row r="887" ht="14.25" customHeight="1" s="90"/>
+    <row r="888" ht="14.25" customHeight="1" s="90"/>
+    <row r="889" ht="14.25" customHeight="1" s="90"/>
+    <row r="890" ht="14.25" customHeight="1" s="90"/>
+    <row r="891" ht="14.25" customHeight="1" s="90"/>
+    <row r="892" ht="14.25" customHeight="1" s="90"/>
+    <row r="893" ht="14.25" customHeight="1" s="90"/>
+    <row r="894" ht="14.25" customHeight="1" s="90"/>
+    <row r="895" ht="14.25" customHeight="1" s="90"/>
+    <row r="896" ht="14.25" customHeight="1" s="90"/>
+    <row r="897" ht="14.25" customHeight="1" s="90"/>
+    <row r="898" ht="14.25" customHeight="1" s="90"/>
+    <row r="899" ht="14.25" customHeight="1" s="90"/>
+    <row r="900" ht="14.25" customHeight="1" s="90"/>
+    <row r="901" ht="14.25" customHeight="1" s="90"/>
+    <row r="902" ht="14.25" customHeight="1" s="90"/>
+    <row r="903" ht="14.25" customHeight="1" s="90"/>
+    <row r="904" ht="14.25" customHeight="1" s="90"/>
+    <row r="905" ht="14.25" customHeight="1" s="90"/>
+    <row r="906" ht="14.25" customHeight="1" s="90"/>
+    <row r="907" ht="14.25" customHeight="1" s="90"/>
+    <row r="908" ht="14.25" customHeight="1" s="90"/>
+    <row r="909" ht="14.25" customHeight="1" s="90"/>
+    <row r="910" ht="14.25" customHeight="1" s="90"/>
+    <row r="911" ht="14.25" customHeight="1" s="90"/>
+    <row r="912" ht="14.25" customHeight="1" s="90"/>
+    <row r="913" ht="14.25" customHeight="1" s="90"/>
+    <row r="914" ht="14.25" customHeight="1" s="90"/>
+    <row r="915" ht="14.25" customHeight="1" s="90"/>
+    <row r="916" ht="14.25" customHeight="1" s="90"/>
+    <row r="917" ht="14.25" customHeight="1" s="90"/>
+    <row r="918" ht="14.25" customHeight="1" s="90"/>
+    <row r="919" ht="14.25" customHeight="1" s="90"/>
+    <row r="920" ht="14.25" customHeight="1" s="90"/>
+    <row r="921" ht="14.25" customHeight="1" s="90"/>
+    <row r="922" ht="14.25" customHeight="1" s="90"/>
+    <row r="923" ht="14.25" customHeight="1" s="90"/>
+    <row r="924" ht="14.25" customHeight="1" s="90"/>
+    <row r="925" ht="14.25" customHeight="1" s="90"/>
+    <row r="926" ht="14.25" customHeight="1" s="90"/>
+    <row r="927" ht="14.25" customHeight="1" s="90"/>
+    <row r="928" ht="14.25" customHeight="1" s="90"/>
+    <row r="929" ht="14.25" customHeight="1" s="90"/>
+    <row r="930" ht="14.25" customHeight="1" s="90"/>
+    <row r="931" ht="14.25" customHeight="1" s="90"/>
+    <row r="932" ht="14.25" customHeight="1" s="90"/>
+    <row r="933" ht="14.25" customHeight="1" s="90"/>
+    <row r="934" ht="14.25" customHeight="1" s="90"/>
+    <row r="935" ht="14.25" customHeight="1" s="90"/>
+    <row r="936" ht="14.25" customHeight="1" s="90"/>
+    <row r="937" ht="14.25" customHeight="1" s="90"/>
+    <row r="938" ht="14.25" customHeight="1" s="90"/>
+    <row r="939" ht="14.25" customHeight="1" s="90"/>
+    <row r="940" ht="14.25" customHeight="1" s="90"/>
+    <row r="941" ht="14.25" customHeight="1" s="90"/>
+    <row r="942" ht="14.25" customHeight="1" s="90"/>
+    <row r="943" ht="14.25" customHeight="1" s="90"/>
+    <row r="944" ht="14.25" customHeight="1" s="90"/>
+    <row r="945" ht="14.25" customHeight="1" s="90"/>
+    <row r="946" ht="14.25" customHeight="1" s="90"/>
+    <row r="947" ht="14.25" customHeight="1" s="90"/>
+    <row r="948" ht="14.25" customHeight="1" s="90"/>
+    <row r="949" ht="14.25" customHeight="1" s="90"/>
+    <row r="950" ht="14.25" customHeight="1" s="90"/>
+    <row r="951" ht="14.25" customHeight="1" s="90"/>
+    <row r="952" ht="14.25" customHeight="1" s="90"/>
+    <row r="953" ht="14.25" customHeight="1" s="90"/>
+    <row r="954" ht="14.25" customHeight="1" s="90"/>
+    <row r="955" ht="14.25" customHeight="1" s="90"/>
+    <row r="956" ht="14.25" customHeight="1" s="90"/>
+    <row r="957" ht="14.25" customHeight="1" s="90"/>
+    <row r="958" ht="14.25" customHeight="1" s="90"/>
+    <row r="959" ht="14.25" customHeight="1" s="90"/>
+    <row r="960" ht="14.25" customHeight="1" s="90"/>
+    <row r="961" ht="14.25" customHeight="1" s="90"/>
+    <row r="962" ht="14.25" customHeight="1" s="90"/>
+    <row r="963" ht="14.25" customHeight="1" s="90"/>
+    <row r="964" ht="14.25" customHeight="1" s="90"/>
+    <row r="965" ht="14.25" customHeight="1" s="90"/>
+    <row r="966" ht="14.25" customHeight="1" s="90"/>
+    <row r="967" ht="14.25" customHeight="1" s="90"/>
+    <row r="968" ht="14.25" customHeight="1" s="90"/>
+    <row r="969" ht="14.25" customHeight="1" s="90"/>
+    <row r="970" ht="14.25" customHeight="1" s="90"/>
+    <row r="971" ht="14.25" customHeight="1" s="90"/>
+    <row r="972" ht="14.25" customHeight="1" s="90"/>
+    <row r="973" ht="14.25" customHeight="1" s="90"/>
+    <row r="974" ht="14.25" customHeight="1" s="90"/>
+    <row r="975" ht="14.25" customHeight="1" s="90"/>
+    <row r="976" ht="14.25" customHeight="1" s="90"/>
+    <row r="977" ht="14.25" customHeight="1" s="90"/>
+    <row r="978" ht="14.25" customHeight="1" s="90"/>
+    <row r="979" ht="14.25" customHeight="1" s="90"/>
+    <row r="980" ht="14.25" customHeight="1" s="90"/>
+    <row r="981" ht="14.25" customHeight="1" s="90"/>
+    <row r="982" ht="14.25" customHeight="1" s="90"/>
+    <row r="983" ht="14.25" customHeight="1" s="90"/>
+    <row r="984" ht="14.25" customHeight="1" s="90"/>
+    <row r="985" ht="14.25" customHeight="1" s="90"/>
+    <row r="986" ht="14.25" customHeight="1" s="90"/>
+    <row r="987" ht="14.25" customHeight="1" s="90"/>
+    <row r="988" ht="14.25" customHeight="1" s="90"/>
+    <row r="989" ht="14.25" customHeight="1" s="90"/>
+    <row r="990" ht="14.25" customHeight="1" s="90"/>
+    <row r="991" ht="14.25" customHeight="1" s="90"/>
+    <row r="992" ht="14.25" customHeight="1" s="90"/>
+    <row r="993" ht="14.25" customHeight="1" s="90"/>
+    <row r="994" ht="14.25" customHeight="1" s="90"/>
+    <row r="995" ht="14.25" customHeight="1" s="90"/>
+    <row r="996" ht="14.25" customHeight="1" s="90"/>
+    <row r="997" ht="14.25" customHeight="1" s="90"/>
+    <row r="998" ht="14.25" customHeight="1" s="90"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:Y1"/>
@@ -8133,54 +8127,54 @@
   <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="8" customWidth="1" style="84" min="1" max="1"/>
-    <col width="6" customWidth="1" style="84" min="2" max="2"/>
-    <col width="8" customWidth="1" style="84" min="3" max="3"/>
-    <col width="14" customWidth="1" style="84" min="4" max="4"/>
-    <col width="28" customWidth="1" style="84" min="5" max="5"/>
-    <col width="46" customWidth="1" style="84" min="6" max="6"/>
-    <col width="28" customWidth="1" style="84" min="7" max="7"/>
-    <col width="11" customWidth="1" style="84" min="8" max="8"/>
-    <col width="9" customWidth="1" style="84" min="9" max="9"/>
-    <col width="10" customWidth="1" style="84" min="10" max="10"/>
-    <col width="12" customWidth="1" style="84" min="11" max="13"/>
-    <col width="9" customWidth="1" style="84" min="14" max="14"/>
-    <col width="12" customWidth="1" style="84" min="15" max="15"/>
-    <col width="28" customWidth="1" style="84" min="16" max="16"/>
-    <col width="24" customWidth="1" style="84" min="17" max="17"/>
+    <col width="8" customWidth="1" style="90" min="1" max="1"/>
+    <col width="6" customWidth="1" style="90" min="2" max="2"/>
+    <col width="8" customWidth="1" style="90" min="3" max="3"/>
+    <col width="14" customWidth="1" style="90" min="4" max="4"/>
+    <col width="28" customWidth="1" style="90" min="5" max="5"/>
+    <col width="46" customWidth="1" style="90" min="6" max="6"/>
+    <col width="28" customWidth="1" style="90" min="7" max="7"/>
+    <col width="11" customWidth="1" style="90" min="8" max="8"/>
+    <col width="9" customWidth="1" style="90" min="9" max="9"/>
+    <col width="10" customWidth="1" style="90" min="10" max="10"/>
+    <col width="12" customWidth="1" style="90" min="11" max="13"/>
+    <col width="9" customWidth="1" style="90" min="14" max="14"/>
+    <col width="12" customWidth="1" style="90" min="15" max="15"/>
+    <col width="28" customWidth="1" style="90" min="16" max="16"/>
+    <col width="24" customWidth="1" style="90" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="84">
-      <c r="A1" s="96" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="90">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>CortexKitchen — Phase Tracker (P0 through P6-S11 complete)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16.05" customHeight="1" s="84">
-      <c r="A2" s="94" t="inlineStr">
+    <row r="2" ht="16.05" customHeight="1" s="90">
+      <c r="A2" s="100" t="inlineStr">
         <is>
           <t>Phase 6 planned tasks (P6-01 onwards) live in the Phase 6 sheet  ·  This sheet = historical record only</t>
         </is>
       </c>
-      <c r="B2" s="87" t="n"/>
-      <c r="C2" s="87" t="n"/>
-      <c r="D2" s="87" t="n"/>
-      <c r="E2" s="87" t="n"/>
-      <c r="F2" s="87" t="n"/>
-      <c r="G2" s="87" t="n"/>
-      <c r="H2" s="87" t="n"/>
-      <c r="I2" s="87" t="n"/>
-      <c r="J2" s="87" t="n"/>
-      <c r="K2" s="87" t="n"/>
-      <c r="L2" s="87" t="n"/>
-      <c r="M2" s="87" t="n"/>
-      <c r="N2" s="87" t="n"/>
-      <c r="O2" s="87" t="n"/>
-      <c r="P2" s="87" t="n"/>
-      <c r="Q2" s="88" t="n"/>
-    </row>
-    <row r="3" ht="19.95" customHeight="1" s="84">
+      <c r="B2" s="93" t="n"/>
+      <c r="C2" s="93" t="n"/>
+      <c r="D2" s="93" t="n"/>
+      <c r="E2" s="93" t="n"/>
+      <c r="F2" s="93" t="n"/>
+      <c r="G2" s="93" t="n"/>
+      <c r="H2" s="93" t="n"/>
+      <c r="I2" s="93" t="n"/>
+      <c r="J2" s="93" t="n"/>
+      <c r="K2" s="93" t="n"/>
+      <c r="L2" s="93" t="n"/>
+      <c r="M2" s="93" t="n"/>
+      <c r="N2" s="93" t="n"/>
+      <c r="O2" s="93" t="n"/>
+      <c r="P2" s="93" t="n"/>
+      <c r="Q2" s="94" t="n"/>
+    </row>
+    <row r="3" ht="19.95" customHeight="1" s="90">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Phase</t>
@@ -8267,30 +8261,30 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="84">
-      <c r="A4" s="93" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="90">
+      <c r="A4" s="99" t="inlineStr">
         <is>
           <t>Phase 0</t>
         </is>
       </c>
-      <c r="B4" s="87" t="n"/>
-      <c r="C4" s="87" t="n"/>
-      <c r="D4" s="87" t="n"/>
-      <c r="E4" s="87" t="n"/>
-      <c r="F4" s="87" t="n"/>
-      <c r="G4" s="87" t="n"/>
-      <c r="H4" s="87" t="n"/>
-      <c r="I4" s="87" t="n"/>
-      <c r="J4" s="87" t="n"/>
-      <c r="K4" s="87" t="n"/>
-      <c r="L4" s="87" t="n"/>
-      <c r="M4" s="87" t="n"/>
-      <c r="N4" s="87" t="n"/>
-      <c r="O4" s="87" t="n"/>
-      <c r="P4" s="87" t="n"/>
-      <c r="Q4" s="88" t="n"/>
-    </row>
-    <row r="5" ht="48" customHeight="1" s="84">
+      <c r="B4" s="93" t="n"/>
+      <c r="C4" s="93" t="n"/>
+      <c r="D4" s="93" t="n"/>
+      <c r="E4" s="93" t="n"/>
+      <c r="F4" s="93" t="n"/>
+      <c r="G4" s="93" t="n"/>
+      <c r="H4" s="93" t="n"/>
+      <c r="I4" s="93" t="n"/>
+      <c r="J4" s="93" t="n"/>
+      <c r="K4" s="93" t="n"/>
+      <c r="L4" s="93" t="n"/>
+      <c r="M4" s="93" t="n"/>
+      <c r="N4" s="93" t="n"/>
+      <c r="O4" s="93" t="n"/>
+      <c r="P4" s="93" t="n"/>
+      <c r="Q4" s="94" t="n"/>
+    </row>
+    <row r="5" ht="48" customHeight="1" s="90">
       <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Phase 0</t>
@@ -8363,7 +8357,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1" s="84">
+    <row r="6" ht="48" customHeight="1" s="90">
       <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Phase 0</t>
@@ -8440,7 +8434,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" s="84">
+    <row r="7" ht="48" customHeight="1" s="90">
       <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Phase 0</t>
@@ -8517,7 +8511,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" s="84">
+    <row r="8" ht="48" customHeight="1" s="90">
       <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Phase 0</t>
@@ -8594,7 +8588,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1" s="84">
+    <row r="9" ht="48" customHeight="1" s="90">
       <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Phase 0</t>
@@ -8675,30 +8669,30 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" s="84">
-      <c r="A10" s="93" t="inlineStr">
+    <row r="10" ht="18" customHeight="1" s="90">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B10" s="87" t="n"/>
-      <c r="C10" s="87" t="n"/>
-      <c r="D10" s="87" t="n"/>
-      <c r="E10" s="87" t="n"/>
-      <c r="F10" s="87" t="n"/>
-      <c r="G10" s="87" t="n"/>
-      <c r="H10" s="87" t="n"/>
-      <c r="I10" s="87" t="n"/>
-      <c r="J10" s="87" t="n"/>
-      <c r="K10" s="87" t="n"/>
-      <c r="L10" s="87" t="n"/>
-      <c r="M10" s="87" t="n"/>
-      <c r="N10" s="87" t="n"/>
-      <c r="O10" s="87" t="n"/>
-      <c r="P10" s="87" t="n"/>
-      <c r="Q10" s="88" t="n"/>
-    </row>
-    <row r="11" ht="48" customHeight="1" s="84">
+      <c r="B10" s="93" t="n"/>
+      <c r="C10" s="93" t="n"/>
+      <c r="D10" s="93" t="n"/>
+      <c r="E10" s="93" t="n"/>
+      <c r="F10" s="93" t="n"/>
+      <c r="G10" s="93" t="n"/>
+      <c r="H10" s="93" t="n"/>
+      <c r="I10" s="93" t="n"/>
+      <c r="J10" s="93" t="n"/>
+      <c r="K10" s="93" t="n"/>
+      <c r="L10" s="93" t="n"/>
+      <c r="M10" s="93" t="n"/>
+      <c r="N10" s="93" t="n"/>
+      <c r="O10" s="93" t="n"/>
+      <c r="P10" s="93" t="n"/>
+      <c r="Q10" s="94" t="n"/>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="90">
       <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -8781,7 +8775,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1" s="84">
+    <row r="12" ht="48" customHeight="1" s="90">
       <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -8858,7 +8852,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1" s="84">
+    <row r="13" ht="48" customHeight="1" s="90">
       <c r="A13" s="24" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -8935,7 +8929,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1" s="84">
+    <row r="14" ht="48" customHeight="1" s="90">
       <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -9012,7 +9006,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1" s="84">
+    <row r="15" ht="48" customHeight="1" s="90">
       <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -9089,7 +9083,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1" s="84">
+    <row r="16" ht="48" customHeight="1" s="90">
       <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -9166,7 +9160,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1" s="84">
+    <row r="17" ht="48" customHeight="1" s="90">
       <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -9243,7 +9237,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1" s="84">
+    <row r="18" ht="48" customHeight="1" s="90">
       <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -9320,7 +9314,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1" s="84">
+    <row r="19" ht="48" customHeight="1" s="90">
       <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -9397,7 +9391,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1" s="84">
+    <row r="20" ht="48" customHeight="1" s="90">
       <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -9474,7 +9468,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1" s="84">
+    <row r="21" ht="48" customHeight="1" s="90">
       <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -9551,7 +9545,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="48" customHeight="1" s="84">
+    <row r="22" ht="48" customHeight="1" s="90">
       <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Phase 1</t>
@@ -9628,30 +9622,30 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1" s="84">
-      <c r="A23" s="92" t="inlineStr">
+    <row r="23" ht="18" customHeight="1" s="90">
+      <c r="A23" s="98" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="B23" s="87" t="n"/>
-      <c r="C23" s="87" t="n"/>
-      <c r="D23" s="87" t="n"/>
-      <c r="E23" s="87" t="n"/>
-      <c r="F23" s="87" t="n"/>
-      <c r="G23" s="87" t="n"/>
-      <c r="H23" s="87" t="n"/>
-      <c r="I23" s="87" t="n"/>
-      <c r="J23" s="87" t="n"/>
-      <c r="K23" s="87" t="n"/>
-      <c r="L23" s="87" t="n"/>
-      <c r="M23" s="87" t="n"/>
-      <c r="N23" s="87" t="n"/>
-      <c r="O23" s="87" t="n"/>
-      <c r="P23" s="87" t="n"/>
-      <c r="Q23" s="88" t="n"/>
-    </row>
-    <row r="24" ht="48" customHeight="1" s="84">
+      <c r="B23" s="93" t="n"/>
+      <c r="C23" s="93" t="n"/>
+      <c r="D23" s="93" t="n"/>
+      <c r="E23" s="93" t="n"/>
+      <c r="F23" s="93" t="n"/>
+      <c r="G23" s="93" t="n"/>
+      <c r="H23" s="93" t="n"/>
+      <c r="I23" s="93" t="n"/>
+      <c r="J23" s="93" t="n"/>
+      <c r="K23" s="93" t="n"/>
+      <c r="L23" s="93" t="n"/>
+      <c r="M23" s="93" t="n"/>
+      <c r="N23" s="93" t="n"/>
+      <c r="O23" s="93" t="n"/>
+      <c r="P23" s="93" t="n"/>
+      <c r="Q23" s="94" t="n"/>
+    </row>
+    <row r="24" ht="48" customHeight="1" s="90">
       <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Phase 2</t>
@@ -9728,7 +9722,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="48" customHeight="1" s="84">
+    <row r="25" ht="48" customHeight="1" s="90">
       <c r="A25" s="28" t="inlineStr">
         <is>
           <t>Phase 2</t>
@@ -9805,7 +9799,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1" s="84">
+    <row r="26" ht="48" customHeight="1" s="90">
       <c r="A26" s="24" t="inlineStr">
         <is>
           <t>Phase 2</t>
@@ -9882,7 +9876,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1" s="84">
+    <row r="27" ht="48" customHeight="1" s="90">
       <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Phase 2</t>
@@ -9959,7 +9953,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1" s="84">
+    <row r="28" ht="48" customHeight="1" s="90">
       <c r="A28" s="24" t="inlineStr">
         <is>
           <t>Phase 2</t>
@@ -10036,7 +10030,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1" s="84">
+    <row r="29" ht="48" customHeight="1" s="90">
       <c r="A29" s="28" t="inlineStr">
         <is>
           <t>Phase 2</t>
@@ -10113,30 +10107,30 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1" s="84">
-      <c r="A30" s="92" t="inlineStr">
+    <row r="30" ht="18" customHeight="1" s="90">
+      <c r="A30" s="98" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="B30" s="87" t="n"/>
-      <c r="C30" s="87" t="n"/>
-      <c r="D30" s="87" t="n"/>
-      <c r="E30" s="87" t="n"/>
-      <c r="F30" s="87" t="n"/>
-      <c r="G30" s="87" t="n"/>
-      <c r="H30" s="87" t="n"/>
-      <c r="I30" s="87" t="n"/>
-      <c r="J30" s="87" t="n"/>
-      <c r="K30" s="87" t="n"/>
-      <c r="L30" s="87" t="n"/>
-      <c r="M30" s="87" t="n"/>
-      <c r="N30" s="87" t="n"/>
-      <c r="O30" s="87" t="n"/>
-      <c r="P30" s="87" t="n"/>
-      <c r="Q30" s="88" t="n"/>
-    </row>
-    <row r="31" ht="48" customHeight="1" s="84">
+      <c r="B30" s="93" t="n"/>
+      <c r="C30" s="93" t="n"/>
+      <c r="D30" s="93" t="n"/>
+      <c r="E30" s="93" t="n"/>
+      <c r="F30" s="93" t="n"/>
+      <c r="G30" s="93" t="n"/>
+      <c r="H30" s="93" t="n"/>
+      <c r="I30" s="93" t="n"/>
+      <c r="J30" s="93" t="n"/>
+      <c r="K30" s="93" t="n"/>
+      <c r="L30" s="93" t="n"/>
+      <c r="M30" s="93" t="n"/>
+      <c r="N30" s="93" t="n"/>
+      <c r="O30" s="93" t="n"/>
+      <c r="P30" s="93" t="n"/>
+      <c r="Q30" s="94" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1" s="90">
       <c r="A31" s="24" t="inlineStr">
         <is>
           <t>Phase 3</t>
@@ -10213,7 +10207,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="48" customHeight="1" s="84">
+    <row r="32" ht="48" customHeight="1" s="90">
       <c r="A32" s="28" t="inlineStr">
         <is>
           <t>Phase 3</t>
@@ -10290,7 +10284,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="48" customHeight="1" s="84">
+    <row r="33" ht="48" customHeight="1" s="90">
       <c r="A33" s="24" t="inlineStr">
         <is>
           <t>Phase 3</t>
@@ -10367,7 +10361,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="48" customHeight="1" s="84">
+    <row r="34" ht="48" customHeight="1" s="90">
       <c r="A34" s="28" t="inlineStr">
         <is>
           <t>Phase 3</t>
@@ -10444,7 +10438,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="48" customHeight="1" s="84">
+    <row r="35" ht="48" customHeight="1" s="90">
       <c r="A35" s="24" t="inlineStr">
         <is>
           <t>Phase 3</t>
@@ -10521,30 +10515,30 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1" s="84">
-      <c r="A36" s="97" t="inlineStr">
+    <row r="36" ht="18" customHeight="1" s="90">
+      <c r="A36" s="103" t="inlineStr">
         <is>
           <t>Demo prep</t>
         </is>
       </c>
-      <c r="B36" s="87" t="n"/>
-      <c r="C36" s="87" t="n"/>
-      <c r="D36" s="87" t="n"/>
-      <c r="E36" s="87" t="n"/>
-      <c r="F36" s="87" t="n"/>
-      <c r="G36" s="87" t="n"/>
-      <c r="H36" s="87" t="n"/>
-      <c r="I36" s="87" t="n"/>
-      <c r="J36" s="87" t="n"/>
-      <c r="K36" s="87" t="n"/>
-      <c r="L36" s="87" t="n"/>
-      <c r="M36" s="87" t="n"/>
-      <c r="N36" s="87" t="n"/>
-      <c r="O36" s="87" t="n"/>
-      <c r="P36" s="87" t="n"/>
-      <c r="Q36" s="88" t="n"/>
-    </row>
-    <row r="37" ht="48" customHeight="1" s="84">
+      <c r="B36" s="93" t="n"/>
+      <c r="C36" s="93" t="n"/>
+      <c r="D36" s="93" t="n"/>
+      <c r="E36" s="93" t="n"/>
+      <c r="F36" s="93" t="n"/>
+      <c r="G36" s="93" t="n"/>
+      <c r="H36" s="93" t="n"/>
+      <c r="I36" s="93" t="n"/>
+      <c r="J36" s="93" t="n"/>
+      <c r="K36" s="93" t="n"/>
+      <c r="L36" s="93" t="n"/>
+      <c r="M36" s="93" t="n"/>
+      <c r="N36" s="93" t="n"/>
+      <c r="O36" s="93" t="n"/>
+      <c r="P36" s="93" t="n"/>
+      <c r="Q36" s="94" t="n"/>
+    </row>
+    <row r="37" ht="48" customHeight="1" s="90">
       <c r="A37" s="32" t="inlineStr">
         <is>
           <t>Demo prep</t>
@@ -10621,7 +10615,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="48" customHeight="1" s="84">
+    <row r="38" ht="48" customHeight="1" s="90">
       <c r="A38" s="24" t="inlineStr">
         <is>
           <t>Demo prep</t>
@@ -10698,7 +10692,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="48" customHeight="1" s="84">
+    <row r="39" ht="48" customHeight="1" s="90">
       <c r="A39" s="32" t="inlineStr">
         <is>
           <t>Demo prep</t>
@@ -10775,30 +10769,30 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1" s="84">
-      <c r="A40" s="91" t="inlineStr">
+    <row r="40" ht="18" customHeight="1" s="90">
+      <c r="A40" s="97" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="B40" s="87" t="n"/>
-      <c r="C40" s="87" t="n"/>
-      <c r="D40" s="87" t="n"/>
-      <c r="E40" s="87" t="n"/>
-      <c r="F40" s="87" t="n"/>
-      <c r="G40" s="87" t="n"/>
-      <c r="H40" s="87" t="n"/>
-      <c r="I40" s="87" t="n"/>
-      <c r="J40" s="87" t="n"/>
-      <c r="K40" s="87" t="n"/>
-      <c r="L40" s="87" t="n"/>
-      <c r="M40" s="87" t="n"/>
-      <c r="N40" s="87" t="n"/>
-      <c r="O40" s="87" t="n"/>
-      <c r="P40" s="87" t="n"/>
-      <c r="Q40" s="88" t="n"/>
-    </row>
-    <row r="41" ht="48" customHeight="1" s="84">
+      <c r="B40" s="93" t="n"/>
+      <c r="C40" s="93" t="n"/>
+      <c r="D40" s="93" t="n"/>
+      <c r="E40" s="93" t="n"/>
+      <c r="F40" s="93" t="n"/>
+      <c r="G40" s="93" t="n"/>
+      <c r="H40" s="93" t="n"/>
+      <c r="I40" s="93" t="n"/>
+      <c r="J40" s="93" t="n"/>
+      <c r="K40" s="93" t="n"/>
+      <c r="L40" s="93" t="n"/>
+      <c r="M40" s="93" t="n"/>
+      <c r="N40" s="93" t="n"/>
+      <c r="O40" s="93" t="n"/>
+      <c r="P40" s="93" t="n"/>
+      <c r="Q40" s="94" t="n"/>
+    </row>
+    <row r="41" ht="48" customHeight="1" s="90">
       <c r="A41" s="24" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -10875,7 +10869,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="48" customHeight="1" s="84">
+    <row r="42" ht="48" customHeight="1" s="90">
       <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -10952,7 +10946,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="48" customHeight="1" s="84">
+    <row r="43" ht="48" customHeight="1" s="90">
       <c r="A43" s="24" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11029,7 +11023,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="48" customHeight="1" s="84">
+    <row r="44" ht="48" customHeight="1" s="90">
       <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11106,7 +11100,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="48" customHeight="1" s="84">
+    <row r="45" ht="48" customHeight="1" s="90">
       <c r="A45" s="24" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11183,7 +11177,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="48" customHeight="1" s="84">
+    <row r="46" ht="48" customHeight="1" s="90">
       <c r="A46" s="19" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11260,7 +11254,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="48" customHeight="1" s="84">
+    <row r="47" ht="48" customHeight="1" s="90">
       <c r="A47" s="24" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11337,7 +11331,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="48" customHeight="1" s="84">
+    <row r="48" ht="48" customHeight="1" s="90">
       <c r="A48" s="19" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11414,7 +11408,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="48" customHeight="1" s="84">
+    <row r="49" ht="48" customHeight="1" s="90">
       <c r="A49" s="24" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11491,7 +11485,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="48" customHeight="1" s="84">
+    <row r="50" ht="48" customHeight="1" s="90">
       <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11568,7 +11562,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="48" customHeight="1" s="84">
+    <row r="51" ht="48" customHeight="1" s="90">
       <c r="A51" s="24" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11645,7 +11639,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="48" customHeight="1" s="84">
+    <row r="52" ht="48" customHeight="1" s="90">
       <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11722,7 +11716,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="48" customHeight="1" s="84">
+    <row r="53" ht="48" customHeight="1" s="90">
       <c r="A53" s="24" t="inlineStr">
         <is>
           <t>Phase 4</t>
@@ -11799,30 +11793,30 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1" s="84">
-      <c r="A54" s="91" t="inlineStr">
+    <row r="54" ht="18" customHeight="1" s="90">
+      <c r="A54" s="97" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B54" s="87" t="n"/>
-      <c r="C54" s="87" t="n"/>
-      <c r="D54" s="87" t="n"/>
-      <c r="E54" s="87" t="n"/>
-      <c r="F54" s="87" t="n"/>
-      <c r="G54" s="87" t="n"/>
-      <c r="H54" s="87" t="n"/>
-      <c r="I54" s="87" t="n"/>
-      <c r="J54" s="87" t="n"/>
-      <c r="K54" s="87" t="n"/>
-      <c r="L54" s="87" t="n"/>
-      <c r="M54" s="87" t="n"/>
-      <c r="N54" s="87" t="n"/>
-      <c r="O54" s="87" t="n"/>
-      <c r="P54" s="87" t="n"/>
-      <c r="Q54" s="88" t="n"/>
-    </row>
-    <row r="55" ht="48" customHeight="1" s="84">
+      <c r="B54" s="93" t="n"/>
+      <c r="C54" s="93" t="n"/>
+      <c r="D54" s="93" t="n"/>
+      <c r="E54" s="93" t="n"/>
+      <c r="F54" s="93" t="n"/>
+      <c r="G54" s="93" t="n"/>
+      <c r="H54" s="93" t="n"/>
+      <c r="I54" s="93" t="n"/>
+      <c r="J54" s="93" t="n"/>
+      <c r="K54" s="93" t="n"/>
+      <c r="L54" s="93" t="n"/>
+      <c r="M54" s="93" t="n"/>
+      <c r="N54" s="93" t="n"/>
+      <c r="O54" s="93" t="n"/>
+      <c r="P54" s="93" t="n"/>
+      <c r="Q54" s="94" t="n"/>
+    </row>
+    <row r="55" ht="48" customHeight="1" s="90">
       <c r="A55" s="19" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -11893,7 +11887,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="48" customHeight="1" s="84">
+    <row r="56" ht="48" customHeight="1" s="90">
       <c r="A56" s="24" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -11964,7 +11958,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="48" customHeight="1" s="84">
+    <row r="57" ht="48" customHeight="1" s="90">
       <c r="A57" s="19" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12035,7 +12029,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="48" customHeight="1" s="84">
+    <row r="58" ht="48" customHeight="1" s="90">
       <c r="A58" s="24" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12106,7 +12100,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="48" customHeight="1" s="84">
+    <row r="59" ht="48" customHeight="1" s="90">
       <c r="A59" s="19" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12177,7 +12171,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="48" customHeight="1" s="84">
+    <row r="60" ht="48" customHeight="1" s="90">
       <c r="A60" s="24" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12248,7 +12242,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="48" customHeight="1" s="84">
+    <row r="61" ht="48" customHeight="1" s="90">
       <c r="A61" s="19" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12319,7 +12313,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="48" customHeight="1" s="84">
+    <row r="62" ht="48" customHeight="1" s="90">
       <c r="A62" s="24" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12390,7 +12384,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="48" customHeight="1" s="84">
+    <row r="63" ht="48" customHeight="1" s="90">
       <c r="A63" s="19" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12461,7 +12455,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="48" customHeight="1" s="84">
+    <row r="64" ht="48" customHeight="1" s="90">
       <c r="A64" s="24" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12532,7 +12526,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="48" customHeight="1" s="84">
+    <row r="65" ht="48" customHeight="1" s="90">
       <c r="A65" s="19" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12603,7 +12597,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="48" customHeight="1" s="84">
+    <row r="66" ht="48" customHeight="1" s="90">
       <c r="A66" s="24" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12674,7 +12668,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="48" customHeight="1" s="84">
+    <row r="67" ht="48" customHeight="1" s="90">
       <c r="A67" s="19" t="inlineStr">
         <is>
           <t>Phase 5</t>
@@ -12745,30 +12739,30 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1" s="84">
-      <c r="A68" s="95" t="inlineStr">
+    <row r="68" ht="18" customHeight="1" s="90">
+      <c r="A68" s="101" t="inlineStr">
         <is>
           <t>Phase 6</t>
         </is>
       </c>
-      <c r="B68" s="87" t="n"/>
-      <c r="C68" s="87" t="n"/>
-      <c r="D68" s="87" t="n"/>
-      <c r="E68" s="87" t="n"/>
-      <c r="F68" s="87" t="n"/>
-      <c r="G68" s="87" t="n"/>
-      <c r="H68" s="87" t="n"/>
-      <c r="I68" s="87" t="n"/>
-      <c r="J68" s="87" t="n"/>
-      <c r="K68" s="87" t="n"/>
-      <c r="L68" s="87" t="n"/>
-      <c r="M68" s="87" t="n"/>
-      <c r="N68" s="87" t="n"/>
-      <c r="O68" s="87" t="n"/>
-      <c r="P68" s="87" t="n"/>
-      <c r="Q68" s="88" t="n"/>
-    </row>
-    <row r="69" ht="48" customHeight="1" s="84">
+      <c r="B68" s="93" t="n"/>
+      <c r="C68" s="93" t="n"/>
+      <c r="D68" s="93" t="n"/>
+      <c r="E68" s="93" t="n"/>
+      <c r="F68" s="93" t="n"/>
+      <c r="G68" s="93" t="n"/>
+      <c r="H68" s="93" t="n"/>
+      <c r="I68" s="93" t="n"/>
+      <c r="J68" s="93" t="n"/>
+      <c r="K68" s="93" t="n"/>
+      <c r="L68" s="93" t="n"/>
+      <c r="M68" s="93" t="n"/>
+      <c r="N68" s="93" t="n"/>
+      <c r="O68" s="93" t="n"/>
+      <c r="P68" s="93" t="n"/>
+      <c r="Q68" s="94" t="n"/>
+    </row>
+    <row r="69" ht="48" customHeight="1" s="90">
       <c r="A69" s="24" t="inlineStr">
         <is>
           <t>Phase 6</t>
@@ -12841,7 +12835,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="48" customHeight="1" s="84">
+    <row r="70" ht="48" customHeight="1" s="90">
       <c r="A70" s="36" t="inlineStr">
         <is>
           <t>Phase 6</t>
@@ -12918,7 +12912,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="48" customHeight="1" s="84">
+    <row r="71" ht="48" customHeight="1" s="90">
       <c r="A71" s="24" t="inlineStr">
         <is>
           <t>Phase 6</t>
@@ -13003,7 +12997,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="7.95" customHeight="1" s="84">
+    <row r="72" ht="7.95" customHeight="1" s="90">
       <c r="A72" s="24" t="inlineStr">
         <is>
           <t>Phase 6</t>
@@ -13086,7 +13080,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="105.6" customHeight="1" s="84">
+    <row r="73" ht="105.6" customHeight="1" s="90">
       <c r="A73" s="24" t="inlineStr">
         <is>
           <t>Phase 6</t>
@@ -13169,7 +13163,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="132" customHeight="1" s="84">
+    <row r="74" ht="132" customHeight="1" s="90">
       <c r="A74" s="24" t="inlineStr">
         <is>
           <t>Phase 6</t>
@@ -13252,7 +13246,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="79.2" customHeight="1" s="84">
+    <row r="75" ht="79.2" customHeight="1" s="90">
       <c r="A75" s="24" t="inlineStr">
         <is>
           <t>Phase 6</t>
@@ -13357,30 +13351,30 @@
   <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10" customWidth="1" style="84" min="1" max="1"/>
-    <col width="26" customWidth="1" style="84" min="2" max="2"/>
-    <col width="14" customWidth="1" style="84" min="3" max="3"/>
-    <col width="30" customWidth="1" style="84" min="4" max="4"/>
-    <col width="59.5546875" customWidth="1" style="84" min="5" max="5"/>
-    <col width="30" customWidth="1" style="84" min="6" max="6"/>
-    <col width="28" customWidth="1" style="84" min="7" max="7"/>
-    <col width="11" customWidth="1" style="84" min="8" max="8"/>
-    <col width="9" customWidth="1" style="84" min="9" max="9"/>
-    <col width="10" customWidth="1" style="84" min="10" max="10"/>
-    <col width="11" customWidth="1" style="84" min="11" max="12"/>
-    <col width="8" customWidth="1" style="84" min="13" max="13"/>
-    <col width="16" customWidth="1" style="84" min="14" max="14"/>
-    <col width="30" customWidth="1" style="84" min="15" max="15"/>
+    <col width="10" customWidth="1" style="90" min="1" max="1"/>
+    <col width="26" customWidth="1" style="90" min="2" max="2"/>
+    <col width="14" customWidth="1" style="90" min="3" max="3"/>
+    <col width="30" customWidth="1" style="90" min="4" max="4"/>
+    <col width="59.5546875" customWidth="1" style="90" min="5" max="5"/>
+    <col width="30" customWidth="1" style="90" min="6" max="6"/>
+    <col width="28" customWidth="1" style="90" min="7" max="7"/>
+    <col width="11" customWidth="1" style="90" min="8" max="8"/>
+    <col width="9" customWidth="1" style="90" min="9" max="9"/>
+    <col width="10" customWidth="1" style="90" min="10" max="10"/>
+    <col width="11" customWidth="1" style="90" min="11" max="12"/>
+    <col width="8" customWidth="1" style="90" min="13" max="13"/>
+    <col width="16" customWidth="1" style="90" min="14" max="14"/>
+    <col width="30" customWidth="1" style="90" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="84">
-      <c r="A1" s="103" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="90">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>CortexKitchen — Phase 6 (55 complete, grouped by feature branch — planned below, staging blocked at bottom)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.95" customHeight="1" s="84">
+    <row r="2" ht="19.95" customHeight="1" s="90">
       <c r="A2" s="40" t="inlineStr">
         <is>
           <t>Task ID</t>
@@ -13457,26 +13451,26 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="84">
-      <c r="A3" s="98" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="90">
+      <c r="A3" s="104" t="inlineStr">
         <is>
           <t>COMPLETED (incl. superseded, folded into the branch that delivered them) — 55 tasks</t>
         </is>
       </c>
-      <c r="B3" s="87" t="n"/>
-      <c r="C3" s="87" t="n"/>
-      <c r="D3" s="87" t="n"/>
-      <c r="E3" s="87" t="n"/>
-      <c r="F3" s="87" t="n"/>
-      <c r="G3" s="87" t="n"/>
-      <c r="H3" s="87" t="n"/>
-      <c r="I3" s="87" t="n"/>
-      <c r="J3" s="87" t="n"/>
-      <c r="K3" s="87" t="n"/>
-      <c r="L3" s="87" t="n"/>
-      <c r="M3" s="87" t="n"/>
-      <c r="N3" s="87" t="n"/>
-      <c r="O3" s="88" t="n"/>
+      <c r="B3" s="93" t="n"/>
+      <c r="C3" s="93" t="n"/>
+      <c r="D3" s="93" t="n"/>
+      <c r="E3" s="93" t="n"/>
+      <c r="F3" s="93" t="n"/>
+      <c r="G3" s="93" t="n"/>
+      <c r="H3" s="93" t="n"/>
+      <c r="I3" s="93" t="n"/>
+      <c r="J3" s="93" t="n"/>
+      <c r="K3" s="93" t="n"/>
+      <c r="L3" s="93" t="n"/>
+      <c r="M3" s="93" t="n"/>
+      <c r="N3" s="93" t="n"/>
+      <c r="O3" s="94" t="n"/>
     </row>
     <row r="4" ht="52.05" customFormat="1" customHeight="1" s="54">
       <c r="A4" s="57" t="inlineStr">
@@ -13697,7 +13691,7 @@
           <t>P6-S04</t>
         </is>
       </c>
-      <c r="B7" s="102" t="inlineStr">
+      <c r="B7" s="108" t="inlineStr">
         <is>
           <t>feature/swiggy-base-connector</t>
         </is>
@@ -13768,7 +13762,7 @@
           <t>P6-S07</t>
         </is>
       </c>
-      <c r="B8" s="100" t="n"/>
+      <c r="B8" s="106" t="n"/>
       <c r="C8" s="50" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -13835,7 +13829,7 @@
           <t>P6-S05</t>
         </is>
       </c>
-      <c r="B9" s="101" t="n"/>
+      <c r="B9" s="107" t="n"/>
       <c r="C9" s="50" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -13902,7 +13896,7 @@
           <t>P6-S06</t>
         </is>
       </c>
-      <c r="B10" s="102" t="inlineStr">
+      <c r="B10" s="108" t="inlineStr">
         <is>
           <t>feature/swiggy-sync-orders</t>
         </is>
@@ -13973,7 +13967,7 @@
           <t>P6-S08</t>
         </is>
       </c>
-      <c r="B11" s="101" t="n"/>
+      <c r="B11" s="107" t="n"/>
       <c r="C11" s="50" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -14111,7 +14105,7 @@
           <t>P6-S10</t>
         </is>
       </c>
-      <c r="B13" s="102" t="inlineStr">
+      <c r="B13" s="108" t="inlineStr">
         <is>
           <t>feature/swiggy-sync-feedback-reservations</t>
         </is>
@@ -14182,7 +14176,7 @@
           <t>P6-S11</t>
         </is>
       </c>
-      <c r="B14" s="101" t="n"/>
+      <c r="B14" s="107" t="n"/>
       <c r="C14" s="50" t="inlineStr">
         <is>
           <t>Integrations</t>
@@ -14249,7 +14243,7 @@
           <t>P6-S12</t>
         </is>
       </c>
-      <c r="B15" s="104" t="inlineStr">
+      <c r="B15" s="110" t="inlineStr">
         <is>
           <t>feature/swiggy-market-intel-enrichers</t>
         </is>
@@ -14320,7 +14314,7 @@
           <t>P6-S13</t>
         </is>
       </c>
-      <c r="B16" s="100" t="n"/>
+      <c r="B16" s="106" t="n"/>
       <c r="C16" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14385,7 +14379,7 @@
           <t>P6-S14</t>
         </is>
       </c>
-      <c r="B17" s="100" t="n"/>
+      <c r="B17" s="106" t="n"/>
       <c r="C17" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14467,7 +14461,7 @@
           <t>P6-S15</t>
         </is>
       </c>
-      <c r="B19" s="102" t="inlineStr">
+      <c r="B19" s="108" t="inlineStr">
         <is>
           <t>feature/swiggy-market-intel-node</t>
         </is>
@@ -14538,7 +14532,7 @@
           <t>P6-S16</t>
         </is>
       </c>
-      <c r="B20" s="100" t="n"/>
+      <c r="B20" s="106" t="n"/>
       <c r="C20" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14605,7 +14599,7 @@
           <t>P6-S17</t>
         </is>
       </c>
-      <c r="B21" s="100" t="n"/>
+      <c r="B21" s="106" t="n"/>
       <c r="C21" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14672,7 +14666,7 @@
           <t>P6-S18</t>
         </is>
       </c>
-      <c r="B22" s="101" t="n"/>
+      <c r="B22" s="107" t="n"/>
       <c r="C22" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -14827,7 +14821,7 @@
           <t>P6-F01</t>
         </is>
       </c>
-      <c r="B25" s="102" t="inlineStr">
+      <c r="B25" s="108" t="inlineStr">
         <is>
           <t>feature/swiggy-connectors-ui</t>
         </is>
@@ -14898,7 +14892,7 @@
           <t>P6-F02</t>
         </is>
       </c>
-      <c r="B26" s="100" t="n"/>
+      <c r="B26" s="106" t="n"/>
       <c r="C26" s="50" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -14965,7 +14959,7 @@
           <t>P6-F03</t>
         </is>
       </c>
-      <c r="B27" s="100" t="n"/>
+      <c r="B27" s="106" t="n"/>
       <c r="C27" s="50" t="inlineStr">
         <is>
           <t>Backend</t>
@@ -15016,7 +15010,7 @@
           <t>P6-F04</t>
         </is>
       </c>
-      <c r="B28" s="100" t="n"/>
+      <c r="B28" s="106" t="n"/>
       <c r="C28" s="50" t="inlineStr">
         <is>
           <t>Docs</t>
@@ -15067,7 +15061,7 @@
           <t>P6-F05</t>
         </is>
       </c>
-      <c r="B29" s="101" t="n"/>
+      <c r="B29" s="107" t="n"/>
       <c r="C29" s="50" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15206,7 +15200,7 @@
           <t>P6-S21</t>
         </is>
       </c>
-      <c r="B32" s="102" t="inlineStr">
+      <c r="B32" s="108" t="inlineStr">
         <is>
           <t>fix/swiggy-sse-market-intel</t>
         </is>
@@ -15277,7 +15271,7 @@
           <t>P6-S22</t>
         </is>
       </c>
-      <c r="B33" s="100" t="n"/>
+      <c r="B33" s="106" t="n"/>
       <c r="C33" s="50" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15344,7 +15338,7 @@
           <t>P6-S23</t>
         </is>
       </c>
-      <c r="B34" s="100" t="n"/>
+      <c r="B34" s="106" t="n"/>
       <c r="C34" s="50" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -15411,7 +15405,7 @@
           <t>P6-S24</t>
         </is>
       </c>
-      <c r="B35" s="100" t="n"/>
+      <c r="B35" s="106" t="n"/>
       <c r="C35" s="50" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -15478,7 +15472,7 @@
           <t>P6-S25</t>
         </is>
       </c>
-      <c r="B36" s="100" t="n"/>
+      <c r="B36" s="106" t="n"/>
       <c r="C36" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15545,7 +15539,7 @@
           <t>P6-S26</t>
         </is>
       </c>
-      <c r="B37" s="100" t="n"/>
+      <c r="B37" s="106" t="n"/>
       <c r="C37" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15612,7 +15606,7 @@
           <t>P6-S27</t>
         </is>
       </c>
-      <c r="B38" s="100" t="n"/>
+      <c r="B38" s="106" t="n"/>
       <c r="C38" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15679,7 +15673,7 @@
           <t>P6-S28</t>
         </is>
       </c>
-      <c r="B39" s="100" t="n"/>
+      <c r="B39" s="106" t="n"/>
       <c r="C39" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -15746,7 +15740,7 @@
           <t>P6-S29</t>
         </is>
       </c>
-      <c r="B40" s="100" t="n"/>
+      <c r="B40" s="106" t="n"/>
       <c r="C40" s="50" t="inlineStr">
         <is>
           <t>Security</t>
@@ -15805,7 +15799,7 @@
           <t>P6-S30</t>
         </is>
       </c>
-      <c r="B41" s="101" t="n"/>
+      <c r="B41" s="107" t="n"/>
       <c r="C41" s="50" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -15960,7 +15954,7 @@
           <t>P6-F09</t>
         </is>
       </c>
-      <c r="B44" s="99" t="inlineStr">
+      <c r="B44" s="105" t="inlineStr">
         <is>
           <t>feature/design-system-theming</t>
         </is>
@@ -16027,7 +16021,7 @@
           <t>P6-F10</t>
         </is>
       </c>
-      <c r="B45" s="100" t="n"/>
+      <c r="B45" s="106" t="n"/>
       <c r="C45" s="50" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -16094,7 +16088,7 @@
           <t>P6-F11</t>
         </is>
       </c>
-      <c r="B46" s="100" t="n"/>
+      <c r="B46" s="106" t="n"/>
       <c r="C46" s="50" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -16161,7 +16155,7 @@
           <t>P6-F18</t>
         </is>
       </c>
-      <c r="B47" s="100" t="n"/>
+      <c r="B47" s="106" t="n"/>
       <c r="C47" s="50" t="inlineStr">
         <is>
           <t>Backend</t>
@@ -16228,7 +16222,7 @@
           <t>P6-F19</t>
         </is>
       </c>
-      <c r="B48" s="100" t="n"/>
+      <c r="B48" s="106" t="n"/>
       <c r="C48" s="50" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -16295,7 +16289,7 @@
           <t>P6-S42</t>
         </is>
       </c>
-      <c r="B49" s="101" t="n"/>
+      <c r="B49" s="107" t="n"/>
       <c r="C49" s="50" t="inlineStr">
         <is>
           <t>Product</t>
@@ -16367,7 +16361,7 @@
           <t>P6-MI01</t>
         </is>
       </c>
-      <c r="B51" s="99" t="inlineStr">
+      <c r="B51" s="105" t="inlineStr">
         <is>
           <t>feature/swiggy-market-intel-extended</t>
         </is>
@@ -16422,7 +16416,7 @@
           <t>P6-MI02</t>
         </is>
       </c>
-      <c r="B52" s="100" t="n"/>
+      <c r="B52" s="106" t="n"/>
       <c r="C52" s="50" t="inlineStr">
         <is>
           <t>Infra</t>
@@ -16473,7 +16467,7 @@
           <t>P6-MI03</t>
         </is>
       </c>
-      <c r="B53" s="100" t="n"/>
+      <c r="B53" s="106" t="n"/>
       <c r="C53" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -16524,7 +16518,7 @@
           <t>P6-MI05</t>
         </is>
       </c>
-      <c r="B54" s="100" t="n"/>
+      <c r="B54" s="106" t="n"/>
       <c r="C54" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -16591,7 +16585,7 @@
           <t>P6-MI06</t>
         </is>
       </c>
-      <c r="B55" s="100" t="n"/>
+      <c r="B55" s="106" t="n"/>
       <c r="C55" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -16658,7 +16652,7 @@
           <t>P6-MI07</t>
         </is>
       </c>
-      <c r="B56" s="100" t="n"/>
+      <c r="B56" s="106" t="n"/>
       <c r="C56" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -16725,7 +16719,7 @@
           <t>P6-MI08</t>
         </is>
       </c>
-      <c r="B57" s="100" t="n"/>
+      <c r="B57" s="106" t="n"/>
       <c r="C57" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -16792,7 +16786,7 @@
           <t>P6-MI09</t>
         </is>
       </c>
-      <c r="B58" s="100" t="n"/>
+      <c r="B58" s="106" t="n"/>
       <c r="C58" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -16859,7 +16853,7 @@
           <t>P6-MI10</t>
         </is>
       </c>
-      <c r="B59" s="100" t="n"/>
+      <c r="B59" s="106" t="n"/>
       <c r="C59" s="50" t="inlineStr">
         <is>
           <t>Product</t>
@@ -16926,7 +16920,7 @@
           <t>P6-MI11</t>
         </is>
       </c>
-      <c r="B60" s="100" t="n"/>
+      <c r="B60" s="106" t="n"/>
       <c r="C60" s="50" t="inlineStr">
         <is>
           <t>Backend + Frontend</t>
@@ -16993,7 +16987,7 @@
           <t>P6-MI12</t>
         </is>
       </c>
-      <c r="B61" s="100" t="n"/>
+      <c r="B61" s="106" t="n"/>
       <c r="C61" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -17060,7 +17054,7 @@
           <t>P6-MI13</t>
         </is>
       </c>
-      <c r="B62" s="100" t="n"/>
+      <c r="B62" s="106" t="n"/>
       <c r="C62" s="50" t="inlineStr">
         <is>
           <t>Agents</t>
@@ -17123,7 +17117,7 @@
           <t>P6-MI14</t>
         </is>
       </c>
-      <c r="B63" s="101" t="n"/>
+      <c r="B63" s="107" t="n"/>
       <c r="C63" s="50" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -17212,29 +17206,29 @@
   <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10" customWidth="1" style="84" min="1" max="1"/>
-    <col width="26" customWidth="1" style="84" min="2" max="2"/>
-    <col width="14" customWidth="1" style="84" min="3" max="3"/>
-    <col width="30" customWidth="1" style="84" min="4" max="4"/>
-    <col width="46" customWidth="1" style="84" min="5" max="5"/>
-    <col width="30" customWidth="1" style="84" min="6" max="6"/>
-    <col width="24" customWidth="1" style="84" min="7" max="7"/>
-    <col width="11" customWidth="1" style="84" min="8" max="8"/>
-    <col width="9" customWidth="1" style="84" min="9" max="9"/>
-    <col width="10" customWidth="1" style="84" min="10" max="12"/>
-    <col width="8" customWidth="1" style="84" min="13" max="13"/>
-    <col width="16" customWidth="1" style="84" min="14" max="14"/>
-    <col width="32" customWidth="1" style="84" min="15" max="15"/>
+    <col width="10" customWidth="1" style="90" min="1" max="1"/>
+    <col width="26" customWidth="1" style="90" min="2" max="2"/>
+    <col width="14" customWidth="1" style="90" min="3" max="3"/>
+    <col width="30" customWidth="1" style="90" min="4" max="4"/>
+    <col width="46" customWidth="1" style="90" min="5" max="5"/>
+    <col width="30" customWidth="1" style="90" min="6" max="6"/>
+    <col width="24" customWidth="1" style="90" min="7" max="7"/>
+    <col width="11" customWidth="1" style="90" min="8" max="8"/>
+    <col width="9" customWidth="1" style="90" min="9" max="9"/>
+    <col width="10" customWidth="1" style="90" min="10" max="12"/>
+    <col width="8" customWidth="1" style="90" min="13" max="13"/>
+    <col width="16" customWidth="1" style="90" min="14" max="14"/>
+    <col width="32" customWidth="1" style="90" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="84">
-      <c r="A1" s="85" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="90">
+      <c r="A1" s="91" t="inlineStr">
         <is>
           <t>Phase 6A — Restaurant OS: compliance fixes + autonomous procurement + operator features</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.95" customHeight="1" s="84">
+    <row r="2" ht="19.95" customHeight="1" s="90">
       <c r="A2" s="61" t="inlineStr">
         <is>
           <t>Task ID</t>
@@ -17311,28 +17305,28 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="84">
-      <c r="A3" s="89" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="90">
+      <c r="A3" s="95" t="inlineStr">
         <is>
           <t>COMPLETED — 13 tasks done (Restaurant OS foundation)</t>
         </is>
       </c>
-      <c r="B3" s="87" t="n"/>
-      <c r="C3" s="87" t="n"/>
-      <c r="D3" s="87" t="n"/>
-      <c r="E3" s="87" t="n"/>
-      <c r="F3" s="87" t="n"/>
-      <c r="G3" s="87" t="n"/>
-      <c r="H3" s="87" t="n"/>
-      <c r="I3" s="87" t="n"/>
-      <c r="J3" s="87" t="n"/>
-      <c r="K3" s="87" t="n"/>
-      <c r="L3" s="87" t="n"/>
-      <c r="M3" s="87" t="n"/>
-      <c r="N3" s="87" t="n"/>
-      <c r="O3" s="88" t="n"/>
-    </row>
-    <row r="4" ht="52.05" customHeight="1" s="84">
+      <c r="B3" s="93" t="n"/>
+      <c r="C3" s="93" t="n"/>
+      <c r="D3" s="93" t="n"/>
+      <c r="E3" s="93" t="n"/>
+      <c r="F3" s="93" t="n"/>
+      <c r="G3" s="93" t="n"/>
+      <c r="H3" s="93" t="n"/>
+      <c r="I3" s="93" t="n"/>
+      <c r="J3" s="93" t="n"/>
+      <c r="K3" s="93" t="n"/>
+      <c r="L3" s="93" t="n"/>
+      <c r="M3" s="93" t="n"/>
+      <c r="N3" s="93" t="n"/>
+      <c r="O3" s="94" t="n"/>
+    </row>
+    <row r="4" ht="52.05" customHeight="1" s="90">
       <c r="A4" s="62" t="inlineStr">
         <is>
           <t>P6-A1</t>
@@ -17403,7 +17397,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52.05" customHeight="1" s="84">
+    <row r="5" ht="52.05" customHeight="1" s="90">
       <c r="A5" s="66" t="inlineStr">
         <is>
           <t>P6-A2</t>
@@ -17470,7 +17464,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="52.05" customHeight="1" s="84">
+    <row r="6" ht="52.05" customHeight="1" s="90">
       <c r="A6" s="62" t="inlineStr">
         <is>
           <t>P6-A3</t>
@@ -17537,7 +17531,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="52.05" customHeight="1" s="84">
+    <row r="7" ht="52.05" customHeight="1" s="90">
       <c r="A7" s="66" t="inlineStr">
         <is>
           <t>P6-A4</t>
@@ -17608,7 +17602,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="52.05" customHeight="1" s="84">
+    <row r="8" ht="52.05" customHeight="1" s="90">
       <c r="A8" s="62" t="inlineStr">
         <is>
           <t>P6-A6</t>
@@ -17679,7 +17673,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="52.05" customHeight="1" s="84">
+    <row r="9" ht="52.05" customHeight="1" s="90">
       <c r="A9" s="66" t="inlineStr">
         <is>
           <t>P6-A7</t>
@@ -17750,7 +17744,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="52.05" customHeight="1" s="84">
+    <row r="10" ht="52.05" customHeight="1" s="90">
       <c r="A10" s="62" t="inlineStr">
         <is>
           <t>P6-A8</t>
@@ -17821,7 +17815,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="52.05" customHeight="1" s="84">
+    <row r="11" ht="52.05" customHeight="1" s="90">
       <c r="A11" s="66" t="inlineStr">
         <is>
           <t>P6-A9</t>
@@ -17896,7 +17890,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="52.05" customHeight="1" s="84">
+    <row r="12" ht="52.05" customHeight="1" s="90">
       <c r="A12" s="62" t="inlineStr">
         <is>
           <t>P6-A10</t>
@@ -17963,7 +17957,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52.05" customHeight="1" s="84">
+    <row r="13" ht="52.05" customHeight="1" s="90">
       <c r="A13" s="66" t="inlineStr">
         <is>
           <t>P6-A11</t>
@@ -18038,7 +18032,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52.05" customHeight="1" s="84">
+    <row r="14" ht="52.05" customHeight="1" s="90">
       <c r="A14" s="62" t="inlineStr">
         <is>
           <t>P6-A12</t>
@@ -18109,7 +18103,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="52.05" customHeight="1" s="84">
+    <row r="15" ht="52.05" customHeight="1" s="90">
       <c r="A15" s="66" t="inlineStr">
         <is>
           <t>P6-A13</t>
@@ -18184,7 +18178,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="52.05" customHeight="1" s="84">
+    <row r="16" ht="52.05" customHeight="1" s="90">
       <c r="A16" s="62" t="inlineStr">
         <is>
           <t>P6-A18</t>
@@ -18255,29 +18249,29 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="7.95" customHeight="1" s="84"/>
-    <row r="18" ht="18" customHeight="1" s="84">
-      <c r="A18" s="86" t="inlineStr">
+    <row r="17" ht="7.95" customHeight="1" s="90"/>
+    <row r="18" ht="18" customHeight="1" s="90">
+      <c r="A18" s="92" t="inlineStr">
         <is>
           <t>COMPLIANCE — do immediately, non-negotiable</t>
         </is>
       </c>
-      <c r="B18" s="87" t="n"/>
-      <c r="C18" s="87" t="n"/>
-      <c r="D18" s="87" t="n"/>
-      <c r="E18" s="87" t="n"/>
-      <c r="F18" s="87" t="n"/>
-      <c r="G18" s="87" t="n"/>
-      <c r="H18" s="87" t="n"/>
-      <c r="I18" s="87" t="n"/>
-      <c r="J18" s="87" t="n"/>
-      <c r="K18" s="87" t="n"/>
-      <c r="L18" s="87" t="n"/>
-      <c r="M18" s="87" t="n"/>
-      <c r="N18" s="87" t="n"/>
-      <c r="O18" s="88" t="n"/>
-    </row>
-    <row r="19" ht="52.05" customHeight="1" s="84">
+      <c r="B18" s="93" t="n"/>
+      <c r="C18" s="93" t="n"/>
+      <c r="D18" s="93" t="n"/>
+      <c r="E18" s="93" t="n"/>
+      <c r="F18" s="93" t="n"/>
+      <c r="G18" s="93" t="n"/>
+      <c r="H18" s="93" t="n"/>
+      <c r="I18" s="93" t="n"/>
+      <c r="J18" s="93" t="n"/>
+      <c r="K18" s="93" t="n"/>
+      <c r="L18" s="93" t="n"/>
+      <c r="M18" s="93" t="n"/>
+      <c r="N18" s="93" t="n"/>
+      <c r="O18" s="94" t="n"/>
+    </row>
+    <row r="19" ht="52.05" customHeight="1" s="90">
       <c r="A19" s="76" t="inlineStr">
         <is>
           <t>P6-A19</t>
@@ -18340,7 +18334,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="52.05" customHeight="1" s="84">
+    <row r="20" ht="52.05" customHeight="1" s="90">
       <c r="A20" s="77" t="inlineStr">
         <is>
           <t>P6-A20</t>
@@ -18407,15 +18401,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="7.95" customHeight="1" s="84"/>
-    <row r="22" ht="18" customHeight="1" s="84">
-      <c r="A22" s="110" t="inlineStr">
+    <row r="21" ht="7.95" customHeight="1" s="90"/>
+    <row r="22" ht="18" customHeight="1" s="90">
+      <c r="A22" s="89" t="inlineStr">
         <is>
           <t>RESTAURANT OS — remaining planned tasks (no staging creds needed)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="52.05" customHeight="1" s="84">
+    <row r="23" ht="52.05" customHeight="1" s="90">
       <c r="A23" s="80" t="inlineStr">
         <is>
           <t>P6-A21</t>
@@ -18478,7 +18472,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="52.05" customHeight="1" s="84">
+    <row r="24" ht="52.05" customHeight="1" s="90">
       <c r="A24" s="80" t="inlineStr">
         <is>
           <t>P6-A22</t>
@@ -18541,7 +18535,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="52.05" customHeight="1" s="84">
+    <row r="25" ht="52.05" customHeight="1" s="90">
       <c r="A25" s="80" t="inlineStr">
         <is>
           <t>P6-A23</t>
@@ -18604,7 +18598,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="52.05" customHeight="1" s="84">
+    <row r="26" ht="52.05" customHeight="1" s="90">
       <c r="A26" s="80" t="inlineStr">
         <is>
           <t>P6-A24</t>
@@ -18671,7 +18665,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="52.05" customHeight="1" s="84">
+    <row r="27" ht="52.05" customHeight="1" s="90">
       <c r="A27" s="80" t="inlineStr">
         <is>
           <t>P6-A25</t>
@@ -18734,7 +18728,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="52.05" customHeight="1" s="84">
+    <row r="28" ht="52.05" customHeight="1" s="90">
       <c r="A28" s="80" t="inlineStr">
         <is>
           <t>P6-A26</t>
@@ -18801,13 +18795,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="52.05" customFormat="1" customHeight="1" s="110">
+    <row r="29" ht="52.05" customFormat="1" customHeight="1" s="89">
       <c r="A29" s="80" t="inlineStr">
         <is>
           <t>P6-A27</t>
         </is>
       </c>
-      <c r="B29" s="112" t="inlineStr">
+      <c r="B29" s="88" t="inlineStr">
         <is>
           <t>feature/kindred</t>
         </is>
@@ -18817,54 +18811,54 @@
           <t>Observability</t>
         </is>
       </c>
-      <c r="D29" s="108" t="inlineStr">
+      <c r="D29" s="85" t="inlineStr">
         <is>
           <t>Observability: Langfuse tracing + Kindred replay debugging endpoint</t>
         </is>
       </c>
-      <c r="E29" s="108" t="inlineStr">
+      <c r="E29" s="85" t="inlineStr">
         <is>
           <t>DONE on feature/kindred. Instruments the planning pipeline with Langfuse (langfuse.langchain.CallbackHandler attached to run_planning_scenario/stream_planning_scenario's RunnableConfig -- one span per LangGraph node per run, zero code change inside the nodes themselves) plus a new BaseLLMProvider._trace_generation() helper called from all 3 concrete providers (Groq/Gemini/Comet) right after record_usage(), so every individual LLM call shows up as its own Langfuse generation (real prompt/completion/token usage), not just which node ran. New settings: LANGFUSE_PUBLIC_KEY/SECRET_KEY/HOST/BASE_URL (SDK checks both host names, so both are supported), KINDRED_AGENT_ID, KINDRED_API_KEY (registered, currently unused -- no documented use case found). New POST /replay (app/api/routes/replay.py), mounted directly on the app in main.py at a bare root path (not under /api/v1) since that's Kindred's Configure Replay URL convention. Kindred replays at the level of one LLM generation, not a whole run -- confirmed from real request logs, which carry back exactly the [system, user] messages array captured for one observation. /replay reuses BaseLLMProvider.complete() directly (the same call path every node already uses) for that one call -- an initial version instead misrouted unrecognised input through ScenarioProfileService.derive_profile() and reran the full 11-node graph per replay (6+ LLM calls), which is both semantically wrong and is what burned a full Groq daily token quota (100k TPD) in 3 live replay clicks before the fix. All 5 Kindred replay metadata fields (kindred_replay_run_id/kindred_original_session_id/kindred_include_prior_context/kindred_turn_trace_id/is_replay) plus their 5 X-Kindred-* header equivalents are threaded onto the Langfuse trace via propagate_attributes(), not just the HTTP response, matching Kindred's own polling-by-trace-metadata model. session_id was originally f'org-{org_id}' (grouping every run from one org into one Langfuse session) -- found live to actively break Kindred's original&lt;-&gt;replay matching (one session had pooled 199 unrelated observations across many runs); changed to scope session_id to the individual run_id instead, which fixed the original/replay trace-tree structure lining up 1:1. ngrok (winget-installed 3.3.1) needed a manual `ngrok update` to 3.39.9 -- the Kindred-linked account requires &gt;=3.20.0. Fail-open throughout: every new code path no-ops when LANGFUSE_SECRET_KEY is unset, exactly like the existing LangSmith integration. KNOWN GAP, Kindred-side not ours: Kindred's own Reproducibility comparison view never renders the original/Reference output for the Agent Output step, even after the session fix gave it a matching trace structure -- directly verified via Langfuse's public API that the original data is fully present and correctly formatted in every case checked, so this is a gap in Kindred's own matching/rendering, not a data or formatting problem on our side. Full-graph replay ("turn 9"/root-span selection in Kindred, or true node re-execution with reconstructed state so a code change downstream could be caught) was scoped and deliberately not built -- would need LangGraph checkpointing that doesn't exist yet, and reopens real LLM cost per replay; explicit product decision to leave for a future task if it becomes a real recurring need.</t>
         </is>
       </c>
-      <c r="F29" s="108" t="inlineStr">
+      <c r="F29" s="85" t="inlineStr">
         <is>
           <t>feat: P6-A27 -- Langfuse tracing + Kindred replay endpoint</t>
         </is>
       </c>
-      <c r="G29" s="108" t="inlineStr">
+      <c r="G29" s="85" t="inlineStr">
         <is>
           <t>CLAUDE.md</t>
         </is>
       </c>
-      <c r="H29" s="109" t="inlineStr">
+      <c r="H29" s="86" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I29" s="107" t="inlineStr">
+      <c r="I29" s="84" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J29" s="107" t="inlineStr">
+      <c r="J29" s="84" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K29" s="107" t="n"/>
-      <c r="L29" s="107" t="n"/>
-      <c r="M29" s="107" t="n">
+      <c r="K29" s="84" t="n"/>
+      <c r="L29" s="84" t="n"/>
+      <c r="M29" s="84" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="108" t="n"/>
-      <c r="O29" s="108" t="inlineStr">
+      <c r="N29" s="85" t="n"/>
+      <c r="O29" s="85" t="inlineStr">
         <is>
           <t>VERIFIED: 544/544 backend tests pass (no new tests added -- Kindred's own setup prompt explicitly said not to add unrelated tests; existing suite confirms no regressions). Live end-to-end verification (not just unit tests): POST /replay smoke-tested repeatedly against the running local server, confirmed HTTP 200 + correct JSON shape (session_id/run_id/kindred_replay_run_id/output) every time. Cross-checked directly against Langfuse's public API (not just its UI) that resulting traces carry agent_id/session_id/kindred_replay_run_id/is_replay metadata correctly, and that every generation observation (original run's 8 LLM calls and every replay's 1 call) has complete input/output. ngrok tunnel verified reachable end-to-end (GET / through the public URL returned 200). Real Kindred replay runs executed against the live tunnel confirmed the fixed endpoint returns the correct single-step output fast (~1-9s) instead of the original bug's 20-130s full-pipeline reruns.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="52.05" customHeight="1" s="84">
+    <row r="30" ht="52.05" customHeight="1" s="90">
       <c r="A30" s="80" t="inlineStr">
         <is>
           <t>P6-A28</t>
@@ -18927,7 +18921,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="63" customHeight="1" s="84">
+    <row r="31" ht="63" customHeight="1" s="90">
       <c r="A31" s="80" t="inlineStr">
         <is>
           <t>P6-A29</t>
@@ -18990,7 +18984,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1" s="84">
+    <row r="32" ht="18" customHeight="1" s="90">
       <c r="A32" s="80" t="inlineStr">
         <is>
           <t>P6-A30</t>
@@ -19013,7 +19007,7 @@
       </c>
       <c r="E32" s="81" t="inlineStr">
         <is>
-          <t>Real-product IA decision, from a from-scratch v1 redesign discussion: a manager wants a fast overview (health score, KPIs, live intelligence) most of the time, and a smaller number of times wants to actually watch/inspect a plan being generated in depth -- two different jobs currently living on one route (/dashboard) via conditional rendering between TodayIdleState.tsx (idle) and the post-trigger success view. Splits the existing idle state (already has health score, net profit/margin, revenue trend, weather/holiday/market context strip via TodayContextStrip, and the scenario trigger flow) into a leaner /dashboard, and moves the existing success view (ForecastChart, AgentCard x4, CriticBanner, ActionQueuePanel) into a new /planning page that becomes the flagship experience. /planning gains two things that didn't exist before: a per-node observability strip (status/runtime/tokens/model/cost per node -- data already captured in node_traces/llm_usage inside run metadata, just never surfaced in the UI) and an explicit Evidence section listing which data sources fed the plan (Swiggy/weather/RSS/FSSAI/RAG -- already computed as market_intel_output/live_signals_text/rag_context, just never labelled as "evidence" in one place for the user). PDF/Excel export relocates here from Data/Run History (P6-A28) since it's about the current run, not historical browsing.</t>
+          <t>Real-product IA decision, from a from-scratch v1 redesign discussion: a manager wants a fast overview (health score, KPIs, live intelligence) most of the time, and a smaller number of times wants to actually watch/inspect a plan being generated in depth -- two different jobs currently living on one route (/dashboard) via conditional rendering between TodayIdleState.tsx (idle) and the post-trigger success view. Splits the existing idle state (already has health score, net profit/margin, revenue trend, weather/holiday/market context strip via TodayContextStrip, and the scenario trigger flow) into a leaner /dashboard, and moves the existing success view (ForecastChart, AgentCard x4, CriticBanner, ActionQueuePanel) into a new /planning page that becomes the flagship experience. /planning gains two things that didn't exist before: a per-node observability strip (status/runtime/tokens/model/cost per node -- data already captured in node_traces/llm_usage inside run metadata, just never surfaced in the UI) and an explicit Evidence section listing which data sources fed the plan (Swiggy/weather/RSS/FSSAI/RAG -- already computed as market_intel_output/live_signals_text/rag_context, just never labelled as "evidence" in one place for the user). PDF/Excel export relocates here from Data/Run History (P6-A28) since it's about the current run, not historical browsing. ACTUAL STATE (verified 2026-07-16): all acceptance criteria met. /dashboard is overview-only, /planning has the full trigger to node progress to plan to critic to export flow, ObservabilityStrip.tsx shows per-node status/duration/model/tokens/cost, EvidencePanel.tsx lists data sources, PDF/Excel export lives on /planning, scenario trigger flow unchanged.</t>
         </is>
       </c>
       <c r="F32" s="81" t="inlineStr">
@@ -19028,7 +19022,7 @@
       </c>
       <c r="H32" s="82" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I32" s="80" t="inlineStr">
@@ -19041,10 +19035,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K32" s="80" t="n"/>
-      <c r="L32" s="80" t="n"/>
+      <c r="K32" s="80" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="L32" s="80" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
       <c r="M32" s="80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
@@ -19057,7 +19059,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="52.05" customHeight="1" s="84">
+    <row r="33" ht="52.05" customHeight="1" s="90">
       <c r="A33" s="80" t="inlineStr">
         <is>
           <t>P6-A31</t>
@@ -19080,7 +19082,7 @@
       </c>
       <c r="E33" s="81" t="inlineStr">
         <is>
-          <t>The Action Queue (pending approvals) and Action Queue History (built in P6-A28, currently living inside the Data page) both relocate to a new dedicated /action-center page with its own primary-nav entry -- approving/rejecting real actions (restocks, WhatsApp vendor orders, pricing reviews) is a distinct daily job from either planning or historical data browsing, and deserves its own home rather than being a sub-section of something else. Reuses ActionQueuePanel and components/data/ActionQueueHistory.tsx (P6-A28) as-is, just relocated, plus adds status-filter tabs (pending/approved/executed/rejected/expired) instead of one combined feed. No backend change needed -- GET /api/v1/action-queue already supports an optional status filter.</t>
+          <t>The Action Queue (pending approvals) and Action Queue History (built in P6-A28, currently living inside the Data page) both relocate to a new dedicated /action-center page with its own primary-nav entry -- approving/rejecting real actions (restocks, WhatsApp vendor orders, pricing reviews) is a distinct daily job from either planning or historical data browsing, and deserves its own home rather than being a sub-section of something else. Reuses ActionQueuePanel and components/data/ActionQueueHistory.tsx (P6-A28) as-is, just relocated, plus adds status-filter tabs (pending/approved/executed/rejected/expired) instead of one combined feed. No backend change needed -- GET /api/v1/action-queue already supports an optional status filter. ACTUAL STATE (verified 2026-07-16): /action-center exists with its own Sidebar entry, shows pending approvals and full history, Action Queue content confirmed removed from /dashboard and /data. MISSING: no status-filter tabs (pending/approved/executed/rejected/expired) -- ActionQueueHistory.tsx returns every action newest-first with only a status badge per row, not filterable tabs.</t>
         </is>
       </c>
       <c r="F33" s="81" t="inlineStr">
@@ -19095,7 +19097,7 @@
       </c>
       <c r="H33" s="82" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I33" s="80" t="inlineStr">
@@ -19108,10 +19110,14 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K33" s="80" t="n"/>
+      <c r="K33" s="80" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="L33" s="80" t="n"/>
       <c r="M33" s="80" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N33" s="81" t="inlineStr">
         <is>
@@ -19124,7 +19130,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="52.05" customHeight="1" s="84">
+    <row r="34" ht="52.05" customHeight="1" s="90">
       <c r="A34" s="80" t="inlineStr">
         <is>
           <t>P6-A32</t>
@@ -19147,7 +19153,7 @@
       </c>
       <c r="E34" s="81" t="inlineStr">
         <is>
-          <t>New page, doesn't exist today in any form. Five sections per the v1 redesign: Business (revenue/orders/AOV/forecast accuracy, from business_analytics_service.py + the existing GET /business/performance endpoint -- already partially surfaced on the old Dashboard idle state, gets a proper historical/trend home here instead), Customers (ratings/complaints/sentiment/repeat, from complaint_intelligence + feedback data), Menu (top sellers/low performers/profitability -- this section IS the previously-separate Menu Engineering Matrix task: dish margin vs. order popularity, four quadrants Stars/Plowhorses/Puzzles/Dogs, from BusinessAnalyticsService's existing margin+popularity data, click-through to full dish margin detail), Operations (occupancy/service time/wait time/table turnover, from reservation + complaint data), Inventory (stock health/waste/supplier performance/food cost, from inventory + vendor data). Absorbs the standalone Menu Engineering Matrix task rather than building it in isolation, since it's genuinely a peer of the other 4 analytics sections, not a run-history concern. Depends on P6-A29 landing first -- otherwise every section visualizes the same permanently-frozen 3 ingredients/3 dishes no matter how good the charts are.</t>
+          <t>New page, doesn't exist today in any form. Five sections per the v1 redesign: Business (revenue/orders/AOV/forecast accuracy, from business_analytics_service.py + the existing GET /business/performance endpoint -- already partially surfaced on the old Dashboard idle state, gets a proper historical/trend home here instead), Customers (ratings/complaints/sentiment/repeat, from complaint_intelligence + feedback data), Menu (top sellers/low performers/profitability -- this section IS the previously-separate Menu Engineering Matrix task: dish margin vs. order popularity, four quadrants Stars/Plowhorses/Puzzles/Dogs, from BusinessAnalyticsService's existing margin+popularity data, click-through to full dish margin detail), Operations (occupancy/service time/wait time/table turnover, from reservation + complaint data), Inventory (stock health/waste/supplier performance/food cost, from inventory + vendor data). Absorbs the standalone Menu Engineering Matrix task rather than building it in isolation, since it's genuinely a peer of the other 4 analytics sections, not a run-history concern. Depends on P6-A29 landing first -- otherwise every section visualizes the same permanently-frozen 3 ingredients/3 dishes no matter how good the charts are. ACTUAL STATE (verified 2026-07-16): /analytics exists with real content (menu top/bottom sellers, channel split, peak hours, complaint themes, a market-intelligence teaser card) and a 7/14/30-day toggle, but that toggle only drives one card, not all sections. MISSING: the 5-section structure (Business/Customers/Menu/Operations/Inventory) does not exist as such, it is one flat page of cards; no Stars/Plowhorses/Puzzles/Dogs quadrant chart (the actual Menu Engineering Matrix); no click-through to dish margin detail; no Operations section; no Inventory section at all.</t>
         </is>
       </c>
       <c r="F34" s="81" t="inlineStr">
@@ -19162,7 +19168,7 @@
       </c>
       <c r="H34" s="82" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I34" s="80" t="inlineStr">
@@ -19175,10 +19181,14 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K34" s="80" t="n"/>
+      <c r="K34" s="80" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="L34" s="80" t="n"/>
       <c r="M34" s="80" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="N34" s="81" t="inlineStr">
         <is>
@@ -19191,7 +19201,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="7.95" customHeight="1" s="84">
+    <row r="35" ht="7.95" customHeight="1" s="90">
       <c r="A35" s="80" t="inlineStr">
         <is>
           <t>P6-A33</t>
@@ -19214,7 +19224,7 @@
       </c>
       <c r="E35" s="81" t="inlineStr">
         <is>
-          <t>New secondary-nav area (not a primary NavBar tab), for operational/technical concerns rather than daily manager workflows. Planning History and Data Health relocate here verbatim from the Data page built in P6-A28 (components/data/RunHistorySection.tsx, DataHealthSection.tsx -- reused as-is, just moved). Two genuinely new panels: Observability (per-run node_traces/llm_usage already captured in run metadata, plus Langfuse traces from P6-A27, surfaced as a real UI for the first time -- status/latency/errors per node/run) and AI Infrastructure (model/provider routing per node, token usage, cost breakdown -- same underlying llm_usage data sliced differently, plus which comet_tiered model tier served which node when tiered routing is active). Audit Trail is effectively the same data as Action Center's history (P6-A31) but framed as a compliance/audit view rather than an action-management view -- shared component, not a duplicate build. Integrations expands the existing /connectors page's Swiggy-only status view to also show Redis/Postgres/Qdrant/WhatsApp(Twilio)/RSS/Weather connectivity.</t>
+          <t>New secondary-nav area (not a primary NavBar tab), for operational/technical concerns rather than daily manager workflows. Planning History and Data Health relocate here verbatim from the Data page built in P6-A28 (components/data/RunHistorySection.tsx, DataHealthSection.tsx -- reused as-is, just moved). Two genuinely new panels: Observability (per-run node_traces/llm_usage already captured in run metadata, plus Langfuse traces from P6-A27, surfaced as a real UI for the first time -- status/latency/errors per node/run) and AI Infrastructure (model/provider routing per node, token usage, cost breakdown -- same underlying llm_usage data sliced differently, plus which comet_tiered model tier served which node when tiered routing is active). Audit Trail is effectively the same data as Action Center's history (P6-A31) but framed as a compliance/audit view rather than an action-management view -- shared component, not a duplicate build. Integrations expands the existing /connectors page's Swiggy-only status view to also show Redis/Postgres/Qdrant/WhatsApp(Twilio)/RSS/Weather connectivity. ACTUAL STATE (verified 2026-07-16): a genuine collapsible Admin secondary-nav grouping exists in Sidebar.tsx (ADMIN_LINKS: Market, Data, Connectors, Restaurant Profiles, Settings); /data does contain Planning History and Data Health sections. MISSING ENTIRELY: no Observability panel, no AI Infrastructure panel, no Audit Trail view anywhere in the codebase (the per-node cost/token/model data only exists today on /planning's ObservabilityStrip, not as a standalone admin surface); /connectors shows Swiggy status only, not Redis/Postgres/Qdrant/WhatsApp/RSS/Weather connectivity.</t>
         </is>
       </c>
       <c r="F35" s="81" t="inlineStr">
@@ -19229,7 +19239,7 @@
       </c>
       <c r="H35" s="82" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I35" s="80" t="inlineStr">
@@ -19242,10 +19252,14 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K35" s="80" t="n"/>
+      <c r="K35" s="80" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
       <c r="L35" s="80" t="n"/>
       <c r="M35" s="80" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N35" s="81" t="inlineStr">
         <is>
@@ -19258,7 +19272,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="118.8" customHeight="1" s="84">
+    <row r="36" ht="118.8" customHeight="1" s="90">
       <c r="A36" s="80" t="inlineStr">
         <is>
           <t>P6-A34</t>
@@ -19325,7 +19339,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="66" customHeight="1" s="84">
+    <row r="37" ht="66" customHeight="1" s="90">
       <c r="A37" s="80" t="inlineStr">
         <is>
           <t>P6-A35</t>
@@ -19392,7 +19406,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="145.2" customHeight="1" s="90">
       <c r="A38" s="80" t="inlineStr">
         <is>
           <t>P6-A36</t>
@@ -19456,7 +19470,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="107" t="inlineStr">
+      <c r="A39" s="84" t="inlineStr">
         <is>
           <t>P6-A37</t>
         </is>
@@ -19515,7 +19529,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="118.8" customHeight="1" s="84">
+    <row r="40" ht="118.8" customHeight="1" s="90">
       <c r="A40" s="80" t="inlineStr">
         <is>
           <t>P6-A38</t>
@@ -19578,7 +19592,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="52.8" customHeight="1" s="84">
+    <row r="41" ht="52.8" customHeight="1" s="90">
       <c r="A41" s="80" t="inlineStr">
         <is>
           <t>P6-A39</t>
@@ -19646,14 +19660,14 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="110" t="inlineStr">
+      <c r="A43" s="89" t="inlineStr">
         <is>
           <t>DOCS + SYNC — end of Phase 6A</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="111" t="inlineStr">
+    <row r="44" ht="118.8" customHeight="1" s="90">
+      <c r="A44" s="87" t="inlineStr">
         <is>
           <t>P6-A40</t>
         </is>
@@ -19719,8 +19733,8 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="111" t="inlineStr">
+    <row r="45" ht="52.8" customHeight="1" s="90">
+      <c r="A45" s="87" t="inlineStr">
         <is>
           <t>P6-A41</t>
         </is>
@@ -19807,23 +19821,23 @@
   <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10" customWidth="1" style="84" min="1" max="1"/>
-    <col width="26" customWidth="1" style="84" min="2" max="2"/>
-    <col width="14" customWidth="1" style="84" min="3" max="3"/>
-    <col width="30" customWidth="1" style="84" min="4" max="4"/>
-    <col width="46" customWidth="1" style="84" min="5" max="5"/>
-    <col width="30" customWidth="1" style="84" min="6" max="6"/>
-    <col width="24" customWidth="1" style="84" min="7" max="7"/>
-    <col width="11" customWidth="1" style="84" min="8" max="8"/>
-    <col width="9" customWidth="1" style="84" min="9" max="9"/>
-    <col width="10" customWidth="1" style="84" min="10" max="10"/>
-    <col width="8" customWidth="1" style="84" min="13" max="13"/>
-    <col width="16" customWidth="1" style="84" min="14" max="14"/>
-    <col width="32" customWidth="1" style="84" min="15" max="15"/>
+    <col width="10" customWidth="1" style="90" min="1" max="1"/>
+    <col width="26" customWidth="1" style="90" min="2" max="2"/>
+    <col width="14" customWidth="1" style="90" min="3" max="3"/>
+    <col width="30" customWidth="1" style="90" min="4" max="4"/>
+    <col width="46" customWidth="1" style="90" min="5" max="5"/>
+    <col width="30" customWidth="1" style="90" min="6" max="6"/>
+    <col width="24" customWidth="1" style="90" min="7" max="7"/>
+    <col width="11" customWidth="1" style="90" min="8" max="8"/>
+    <col width="9" customWidth="1" style="90" min="9" max="9"/>
+    <col width="10" customWidth="1" style="90" min="10" max="10"/>
+    <col width="8" customWidth="1" style="90" min="13" max="13"/>
+    <col width="16" customWidth="1" style="90" min="14" max="14"/>
+    <col width="32" customWidth="1" style="90" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1" s="84">
-      <c r="A1" s="113" t="inlineStr">
+    <row r="1" ht="15.6" customHeight="1" s="90">
+      <c r="A1" s="111" t="inlineStr">
         <is>
           <t>Phase 6B — Guest Concierge: consumer-facing event planning assistant (independent of Restaurant OS -- starts only after Phase 6A syncs to main)</t>
         </is>
@@ -20503,17 +20517,17 @@
   <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="40.77734375" customWidth="1" style="84" min="1" max="1"/>
-    <col width="29.88671875" customWidth="1" style="84" min="2" max="2"/>
-    <col width="48.77734375" customWidth="1" style="84" min="3" max="3"/>
-    <col width="6" customWidth="1" style="84" min="4" max="4"/>
-    <col width="36.21875" customWidth="1" style="84" min="6" max="6"/>
-    <col width="6" customWidth="1" style="84" min="7" max="7"/>
-    <col width="56" customWidth="1" style="84" min="8" max="8"/>
-    <col width="6" customWidth="1" style="84" min="9" max="10"/>
+    <col width="40.77734375" customWidth="1" style="90" min="1" max="1"/>
+    <col width="29.88671875" customWidth="1" style="90" min="2" max="2"/>
+    <col width="48.77734375" customWidth="1" style="90" min="3" max="3"/>
+    <col width="6" customWidth="1" style="90" min="4" max="4"/>
+    <col width="36.21875" customWidth="1" style="90" min="6" max="6"/>
+    <col width="6" customWidth="1" style="90" min="7" max="7"/>
+    <col width="56" customWidth="1" style="90" min="8" max="8"/>
+    <col width="6" customWidth="1" style="90" min="9" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="84">
+    <row r="1" ht="40.05" customHeight="1" s="90">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Task ID</t>
@@ -20591,7 +20605,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="106" t="inlineStr">
+      <c r="A2" s="112" t="inlineStr">
         <is>
           <t>BLOCKED -- needs Swiggy staging creds (write tools: checkout, book_table)</t>
         </is>
@@ -20947,7 +20961,7 @@
       <c r="O11" s="58" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="106" t="inlineStr">
+      <c r="A12" s="112" t="inlineStr">
         <is>
           <t>WHEN RECEIVED -- Sarvam AI access + AWS credits</t>
         </is>
@@ -21131,7 +21145,7 @@
       <c r="O17" s="58" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="106" t="inlineStr">
+      <c r="A18" s="112" t="inlineStr">
         <is>
           <t>-&gt; DEMO 2 / POTENTIAL DEMO | all above on main, staging write tools + Sarvam voice + AWS hosted -- record full product demo &lt;-</t>
         </is>
@@ -21155,7 +21169,7 @@
       <c r="O19" s="58" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="106" t="inlineStr">
+      <c r="A20" s="112" t="inlineStr">
         <is>
           <t>DOCS + PHASE 6 MILESTONE MERGE</t>
         </is>
@@ -21419,7 +21433,7 @@
       <c r="O27" s="58" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="106" t="inlineStr">
+      <c r="A28" s="112" t="inlineStr">
         <is>
           <t>PHASE 7 -- Production, CI/CD, Public Release</t>
         </is>
@@ -21863,7 +21877,7 @@
       <c r="O39" s="58" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="106" t="inlineStr">
+      <c r="A40" s="112" t="inlineStr">
         <is>
           <t>BLOCKED -- needs a real restaurant (not seeded/synthetic data)</t>
         </is>
@@ -21967,7 +21981,7 @@
       <c r="O43" s="58" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="106" t="inlineStr">
+      <c r="A44" s="112" t="inlineStr">
         <is>
           <t>DEPRIORITIZED FOR DEMO PREP (2026-07-08) -- not blocked on anything, just not demo-critical right now</t>
         </is>
@@ -22762,20 +22776,20 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="26" customWidth="1" style="84" min="1" max="1"/>
-    <col width="44" customWidth="1" style="84" min="2" max="2"/>
-    <col width="26" customWidth="1" style="84" min="3" max="3"/>
-    <col width="20" customWidth="1" style="84" min="4" max="4"/>
+    <col width="26" customWidth="1" style="90" min="1" max="1"/>
+    <col width="44" customWidth="1" style="90" min="2" max="2"/>
+    <col width="26" customWidth="1" style="90" min="3" max="3"/>
+    <col width="20" customWidth="1" style="90" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.95" customHeight="1" s="84">
-      <c r="A1" s="96" t="inlineStr">
+    <row r="1" ht="31.95" customHeight="1" s="90">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>CortexKitchen v2 — Documentation Strategy (Phase 6)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" s="84">
+    <row r="2" ht="18" customHeight="1" s="90">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Doc File</t>
@@ -22797,7 +22811,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1" s="84">
+    <row r="3" ht="36" customHeight="1" s="90">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>docs/CONNECTORS.md</t>
@@ -22819,7 +22833,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" s="84">
+    <row r="4" ht="36" customHeight="1" s="90">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>docs/SWIGGY_INTEGRATION.md</t>
@@ -22841,7 +22855,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" s="84">
+    <row r="5" ht="36" customHeight="1" s="90">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>docs/ACTION_QUEUE.md</t>
@@ -22863,7 +22877,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" s="84">
+    <row r="6" ht="36" customHeight="1" s="90">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>docs/DATA_SOURCES.md</t>
@@ -22885,7 +22899,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1" s="84">
+    <row r="7" ht="36" customHeight="1" s="90">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>docs/PRODUCT_MODES.md</t>
@@ -22907,7 +22921,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" s="84">
+    <row r="8" ht="36" customHeight="1" s="90">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>docs/ARCHITECTURE.md</t>
@@ -22929,7 +22943,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1" s="84">
+    <row r="9" ht="36" customHeight="1" s="90">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>docs/AGENTS.md</t>
@@ -22951,7 +22965,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1" s="84">
+    <row r="10" ht="36" customHeight="1" s="90">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>docs/APIS.md</t>
@@ -22973,7 +22987,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1" s="84">
+    <row r="11" ht="36" customHeight="1" s="90">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>docs/DATA_MODEL.md</t>
@@ -22995,7 +23009,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1" s="84">
+    <row r="12" ht="36" customHeight="1" s="90">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>docs/DECISIONS.md</t>
@@ -23017,7 +23031,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1" s="84">
+    <row r="13" ht="36" customHeight="1" s="90">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>docs/ROADMAP.md</t>
@@ -23039,7 +23053,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1" s="84">
+    <row r="14" ht="36" customHeight="1" s="90">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>docs/EVALUATION.md</t>
@@ -23061,7 +23075,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1" s="84">
+    <row r="15" ht="36" customHeight="1" s="90">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>README.md + docs/README.md</t>
@@ -23083,7 +23097,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" s="84">
+    <row r="16" ht="36" customHeight="1" s="90">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>CLAUDE.md</t>
@@ -23105,7 +23119,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1" s="84">
+    <row r="17" ht="36" customHeight="1" s="90">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Mintlify docs website</t>
@@ -23144,15 +23158,15 @@
   <dimension ref="A1:Z220"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="16" customWidth="1" style="84" min="1" max="1"/>
-    <col width="22" customWidth="1" style="84" min="2" max="2"/>
-    <col width="54" customWidth="1" style="84" min="3" max="3"/>
-    <col width="24" customWidth="1" style="84" min="4" max="4"/>
-    <col width="8.6640625" customWidth="1" style="84" min="5" max="26"/>
+    <col width="16" customWidth="1" style="90" min="1" max="1"/>
+    <col width="22" customWidth="1" style="90" min="2" max="2"/>
+    <col width="54" customWidth="1" style="90" min="3" max="3"/>
+    <col width="24" customWidth="1" style="90" min="4" max="4"/>
+    <col width="8.6640625" customWidth="1" style="90" min="5" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.95" customHeight="1" s="84">
-      <c r="A1" s="96" t="inlineStr">
+    <row r="1" ht="31.95" customHeight="1" s="90">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>CortexKitchen — Git Branching Rules</t>
         </is>
@@ -23180,7 +23194,7 @@
       <c r="Y1" s="1" t="n"/>
       <c r="Z1" s="1" t="n"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1" s="84">
+    <row r="2" ht="14.25" customHeight="1" s="90">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="1" t="n"/>
       <c r="C2" s="1" t="n"/>
@@ -23208,7 +23222,7 @@
       <c r="Y2" s="1" t="n"/>
       <c r="Z2" s="1" t="n"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1" s="84">
+    <row r="3" ht="14.25" customHeight="1" s="90">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Branch</t>
@@ -23252,7 +23266,7 @@
       <c r="Y3" s="1" t="n"/>
       <c r="Z3" s="1" t="n"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1" s="84">
+    <row r="4" ht="14.25" customHeight="1" s="90">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>main</t>
@@ -23296,7 +23310,7 @@
       <c r="Y4" s="1" t="n"/>
       <c r="Z4" s="1" t="n"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1" s="84">
+    <row r="5" ht="14.25" customHeight="1" s="90">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>dev</t>
@@ -23340,7 +23354,7 @@
       <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="1" t="n"/>
     </row>
-    <row r="6" ht="14.25" customHeight="1" s="84">
+    <row r="6" ht="14.25" customHeight="1" s="90">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>feature/...</t>
@@ -23384,7 +23398,7 @@
       <c r="Y6" s="1" t="n"/>
       <c r="Z6" s="1" t="n"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1" s="84">
+    <row r="7" ht="14.25" customHeight="1" s="90">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Local cleanup</t>
@@ -23428,7 +23442,7 @@
       <c r="Y7" s="1" t="n"/>
       <c r="Z7" s="1" t="n"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1" s="84">
+    <row r="8" ht="14.25" customHeight="1" s="90">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="1" t="n"/>
@@ -23456,7 +23470,7 @@
       <c r="Y8" s="1" t="n"/>
       <c r="Z8" s="1" t="n"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1" s="84">
+    <row r="9" ht="14.25" customHeight="1" s="90">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="1" t="n"/>
@@ -23484,7 +23498,7 @@
       <c r="Y9" s="1" t="n"/>
       <c r="Z9" s="1" t="n"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1" s="84">
+    <row r="10" ht="14.25" customHeight="1" s="90">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="1" t="n"/>
@@ -23512,7 +23526,7 @@
       <c r="Y10" s="1" t="n"/>
       <c r="Z10" s="1" t="n"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1" s="84">
+    <row r="11" ht="14.25" customHeight="1" s="90">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="1" t="n"/>
@@ -23540,7 +23554,7 @@
       <c r="Y11" s="1" t="n"/>
       <c r="Z11" s="1" t="n"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1" s="84">
+    <row r="12" ht="14.25" customHeight="1" s="90">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="1" t="n"/>
@@ -23568,7 +23582,7 @@
       <c r="Y12" s="1" t="n"/>
       <c r="Z12" s="1" t="n"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1" s="84">
+    <row r="13" ht="14.25" customHeight="1" s="90">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="1" t="n"/>
@@ -23596,7 +23610,7 @@
       <c r="Y13" s="1" t="n"/>
       <c r="Z13" s="1" t="n"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1" s="84">
+    <row r="14" ht="14.25" customHeight="1" s="90">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="1" t="n"/>
@@ -23624,7 +23638,7 @@
       <c r="Y14" s="1" t="n"/>
       <c r="Z14" s="1" t="n"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1" s="84">
+    <row r="15" ht="14.25" customHeight="1" s="90">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="1" t="n"/>
@@ -23652,7 +23666,7 @@
       <c r="Y15" s="1" t="n"/>
       <c r="Z15" s="1" t="n"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1" s="84">
+    <row r="16" ht="14.25" customHeight="1" s="90">
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="n"/>
@@ -23680,7 +23694,7 @@
       <c r="Y16" s="1" t="n"/>
       <c r="Z16" s="1" t="n"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1" s="84">
+    <row r="17" ht="14.25" customHeight="1" s="90">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="1" t="n"/>
@@ -23708,7 +23722,7 @@
       <c r="Y17" s="1" t="n"/>
       <c r="Z17" s="1" t="n"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1" s="84">
+    <row r="18" ht="14.25" customHeight="1" s="90">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>
@@ -23736,7 +23750,7 @@
       <c r="Y18" s="1" t="n"/>
       <c r="Z18" s="1" t="n"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1" s="84">
+    <row r="19" ht="14.25" customHeight="1" s="90">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="1" t="n"/>
@@ -23764,7 +23778,7 @@
       <c r="Y19" s="1" t="n"/>
       <c r="Z19" s="1" t="n"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1" s="84">
+    <row r="20" ht="14.25" customHeight="1" s="90">
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="1" t="n"/>
@@ -23792,7 +23806,7 @@
       <c r="Y20" s="1" t="n"/>
       <c r="Z20" s="1" t="n"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1" s="84">
+    <row r="21" ht="14.25" customHeight="1" s="90">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="1" t="n"/>
@@ -23820,7 +23834,7 @@
       <c r="Y21" s="1" t="n"/>
       <c r="Z21" s="1" t="n"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1" s="84">
+    <row r="22" ht="14.25" customHeight="1" s="90">
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="1" t="n"/>
@@ -23848,7 +23862,7 @@
       <c r="Y22" s="1" t="n"/>
       <c r="Z22" s="1" t="n"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1" s="84">
+    <row r="23" ht="14.25" customHeight="1" s="90">
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="1" t="n"/>
@@ -23876,7 +23890,7 @@
       <c r="Y23" s="1" t="n"/>
       <c r="Z23" s="1" t="n"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1" s="84">
+    <row r="24" ht="14.25" customHeight="1" s="90">
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="1" t="n"/>
@@ -23904,7 +23918,7 @@
       <c r="Y24" s="1" t="n"/>
       <c r="Z24" s="1" t="n"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1" s="84">
+    <row r="25" ht="14.25" customHeight="1" s="90">
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="1" t="n"/>
@@ -23932,7 +23946,7 @@
       <c r="Y25" s="1" t="n"/>
       <c r="Z25" s="1" t="n"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1" s="84">
+    <row r="26" ht="14.25" customHeight="1" s="90">
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="1" t="n"/>
@@ -23960,7 +23974,7 @@
       <c r="Y26" s="1" t="n"/>
       <c r="Z26" s="1" t="n"/>
     </row>
-    <row r="27" ht="14.25" customHeight="1" s="84">
+    <row r="27" ht="14.25" customHeight="1" s="90">
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="1" t="n"/>
@@ -23988,7 +24002,7 @@
       <c r="Y27" s="1" t="n"/>
       <c r="Z27" s="1" t="n"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1" s="84">
+    <row r="28" ht="14.25" customHeight="1" s="90">
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="1" t="n"/>
@@ -24016,7 +24030,7 @@
       <c r="Y28" s="1" t="n"/>
       <c r="Z28" s="1" t="n"/>
     </row>
-    <row r="29" ht="14.25" customHeight="1" s="84">
+    <row r="29" ht="14.25" customHeight="1" s="90">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="1" t="n"/>
@@ -24044,7 +24058,7 @@
       <c r="Y29" s="1" t="n"/>
       <c r="Z29" s="1" t="n"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1" s="84">
+    <row r="30" ht="14.25" customHeight="1" s="90">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="1" t="n"/>
@@ -24072,7 +24086,7 @@
       <c r="Y30" s="1" t="n"/>
       <c r="Z30" s="1" t="n"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1" s="84">
+    <row r="31" ht="14.25" customHeight="1" s="90">
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="1" t="n"/>
@@ -24100,7 +24114,7 @@
       <c r="Y31" s="1" t="n"/>
       <c r="Z31" s="1" t="n"/>
     </row>
-    <row r="32" ht="14.25" customHeight="1" s="84">
+    <row r="32" ht="14.25" customHeight="1" s="90">
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="1" t="n"/>
@@ -24128,7 +24142,7 @@
       <c r="Y32" s="1" t="n"/>
       <c r="Z32" s="1" t="n"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1" s="84">
+    <row r="33" ht="14.25" customHeight="1" s="90">
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="1" t="n"/>
@@ -24156,7 +24170,7 @@
       <c r="Y33" s="1" t="n"/>
       <c r="Z33" s="1" t="n"/>
     </row>
-    <row r="34" ht="14.25" customHeight="1" s="84">
+    <row r="34" ht="14.25" customHeight="1" s="90">
       <c r="A34" s="1" t="n"/>
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="1" t="n"/>
@@ -24184,7 +24198,7 @@
       <c r="Y34" s="1" t="n"/>
       <c r="Z34" s="1" t="n"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1" s="84">
+    <row r="35" ht="14.25" customHeight="1" s="90">
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="1" t="n"/>
@@ -24212,7 +24226,7 @@
       <c r="Y35" s="1" t="n"/>
       <c r="Z35" s="1" t="n"/>
     </row>
-    <row r="36" ht="14.25" customHeight="1" s="84">
+    <row r="36" ht="14.25" customHeight="1" s="90">
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="1" t="n"/>
@@ -24240,7 +24254,7 @@
       <c r="Y36" s="1" t="n"/>
       <c r="Z36" s="1" t="n"/>
     </row>
-    <row r="37" ht="14.25" customHeight="1" s="84">
+    <row r="37" ht="14.25" customHeight="1" s="90">
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="n"/>
@@ -24268,7 +24282,7 @@
       <c r="Y37" s="1" t="n"/>
       <c r="Z37" s="1" t="n"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1" s="84">
+    <row r="38" ht="14.25" customHeight="1" s="90">
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="1" t="n"/>
@@ -24296,7 +24310,7 @@
       <c r="Y38" s="1" t="n"/>
       <c r="Z38" s="1" t="n"/>
     </row>
-    <row r="39" ht="14.25" customHeight="1" s="84">
+    <row r="39" ht="14.25" customHeight="1" s="90">
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="1" t="n"/>
@@ -24324,7 +24338,7 @@
       <c r="Y39" s="1" t="n"/>
       <c r="Z39" s="1" t="n"/>
     </row>
-    <row r="40" ht="14.25" customHeight="1" s="84">
+    <row r="40" ht="14.25" customHeight="1" s="90">
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="1" t="n"/>
@@ -24352,7 +24366,7 @@
       <c r="Y40" s="1" t="n"/>
       <c r="Z40" s="1" t="n"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1" s="84">
+    <row r="41" ht="14.25" customHeight="1" s="90">
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="1" t="n"/>
@@ -24380,7 +24394,7 @@
       <c r="Y41" s="1" t="n"/>
       <c r="Z41" s="1" t="n"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1" s="84">
+    <row r="42" ht="14.25" customHeight="1" s="90">
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="1" t="n"/>
@@ -24408,7 +24422,7 @@
       <c r="Y42" s="1" t="n"/>
       <c r="Z42" s="1" t="n"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1" s="84">
+    <row r="43" ht="14.25" customHeight="1" s="90">
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="1" t="n"/>
@@ -24436,7 +24450,7 @@
       <c r="Y43" s="1" t="n"/>
       <c r="Z43" s="1" t="n"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1" s="84">
+    <row r="44" ht="14.25" customHeight="1" s="90">
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="1" t="n"/>
@@ -24464,7 +24478,7 @@
       <c r="Y44" s="1" t="n"/>
       <c r="Z44" s="1" t="n"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1" s="84">
+    <row r="45" ht="14.25" customHeight="1" s="90">
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="1" t="n"/>
@@ -24492,7 +24506,7 @@
       <c r="Y45" s="1" t="n"/>
       <c r="Z45" s="1" t="n"/>
     </row>
-    <row r="46" ht="14.25" customHeight="1" s="84">
+    <row r="46" ht="14.25" customHeight="1" s="90">
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="n"/>
       <c r="C46" s="1" t="n"/>
@@ -24520,7 +24534,7 @@
       <c r="Y46" s="1" t="n"/>
       <c r="Z46" s="1" t="n"/>
     </row>
-    <row r="47" ht="14.25" customHeight="1" s="84">
+    <row r="47" ht="14.25" customHeight="1" s="90">
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="n"/>
       <c r="C47" s="1" t="n"/>
@@ -24548,7 +24562,7 @@
       <c r="Y47" s="1" t="n"/>
       <c r="Z47" s="1" t="n"/>
     </row>
-    <row r="48" ht="14.25" customHeight="1" s="84">
+    <row r="48" ht="14.25" customHeight="1" s="90">
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="1" t="n"/>
       <c r="C48" s="1" t="n"/>
@@ -24576,7 +24590,7 @@
       <c r="Y48" s="1" t="n"/>
       <c r="Z48" s="1" t="n"/>
     </row>
-    <row r="49" ht="14.25" customHeight="1" s="84">
+    <row r="49" ht="14.25" customHeight="1" s="90">
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="n"/>
       <c r="C49" s="1" t="n"/>
@@ -24604,7 +24618,7 @@
       <c r="Y49" s="1" t="n"/>
       <c r="Z49" s="1" t="n"/>
     </row>
-    <row r="50" ht="14.25" customHeight="1" s="84">
+    <row r="50" ht="14.25" customHeight="1" s="90">
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="n"/>
       <c r="C50" s="1" t="n"/>
@@ -24632,7 +24646,7 @@
       <c r="Y50" s="1" t="n"/>
       <c r="Z50" s="1" t="n"/>
     </row>
-    <row r="51" ht="14.25" customHeight="1" s="84">
+    <row r="51" ht="14.25" customHeight="1" s="90">
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="n"/>
       <c r="C51" s="1" t="n"/>
@@ -24660,7 +24674,7 @@
       <c r="Y51" s="1" t="n"/>
       <c r="Z51" s="1" t="n"/>
     </row>
-    <row r="52" ht="14.25" customHeight="1" s="84">
+    <row r="52" ht="14.25" customHeight="1" s="90">
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="n"/>
       <c r="C52" s="1" t="n"/>
@@ -24688,7 +24702,7 @@
       <c r="Y52" s="1" t="n"/>
       <c r="Z52" s="1" t="n"/>
     </row>
-    <row r="53" ht="14.25" customHeight="1" s="84">
+    <row r="53" ht="14.25" customHeight="1" s="90">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="n"/>
       <c r="C53" s="1" t="n"/>
@@ -24716,7 +24730,7 @@
       <c r="Y53" s="1" t="n"/>
       <c r="Z53" s="1" t="n"/>
     </row>
-    <row r="54" ht="14.25" customHeight="1" s="84">
+    <row r="54" ht="14.25" customHeight="1" s="90">
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="n"/>
       <c r="C54" s="1" t="n"/>
@@ -24744,7 +24758,7 @@
       <c r="Y54" s="1" t="n"/>
       <c r="Z54" s="1" t="n"/>
     </row>
-    <row r="55" ht="14.25" customHeight="1" s="84">
+    <row r="55" ht="14.25" customHeight="1" s="90">
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="n"/>
       <c r="C55" s="1" t="n"/>
@@ -24772,7 +24786,7 @@
       <c r="Y55" s="1" t="n"/>
       <c r="Z55" s="1" t="n"/>
     </row>
-    <row r="56" ht="14.25" customHeight="1" s="84">
+    <row r="56" ht="14.25" customHeight="1" s="90">
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="n"/>
       <c r="C56" s="1" t="n"/>
@@ -24800,7 +24814,7 @@
       <c r="Y56" s="1" t="n"/>
       <c r="Z56" s="1" t="n"/>
     </row>
-    <row r="57" ht="14.25" customHeight="1" s="84">
+    <row r="57" ht="14.25" customHeight="1" s="90">
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="n"/>
       <c r="C57" s="1" t="n"/>
@@ -24828,7 +24842,7 @@
       <c r="Y57" s="1" t="n"/>
       <c r="Z57" s="1" t="n"/>
     </row>
-    <row r="58" ht="14.25" customHeight="1" s="84">
+    <row r="58" ht="14.25" customHeight="1" s="90">
       <c r="A58" s="1" t="n"/>
       <c r="B58" s="1" t="n"/>
       <c r="C58" s="1" t="n"/>
@@ -24856,7 +24870,7 @@
       <c r="Y58" s="1" t="n"/>
       <c r="Z58" s="1" t="n"/>
     </row>
-    <row r="59" ht="14.25" customHeight="1" s="84">
+    <row r="59" ht="14.25" customHeight="1" s="90">
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="n"/>
       <c r="C59" s="1" t="n"/>
@@ -24884,7 +24898,7 @@
       <c r="Y59" s="1" t="n"/>
       <c r="Z59" s="1" t="n"/>
     </row>
-    <row r="60" ht="14.25" customHeight="1" s="84">
+    <row r="60" ht="14.25" customHeight="1" s="90">
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="n"/>
       <c r="C60" s="1" t="n"/>
@@ -24912,7 +24926,7 @@
       <c r="Y60" s="1" t="n"/>
       <c r="Z60" s="1" t="n"/>
     </row>
-    <row r="61" ht="14.25" customHeight="1" s="84">
+    <row r="61" ht="14.25" customHeight="1" s="90">
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="n"/>
       <c r="C61" s="1" t="n"/>
@@ -24940,7 +24954,7 @@
       <c r="Y61" s="1" t="n"/>
       <c r="Z61" s="1" t="n"/>
     </row>
-    <row r="62" ht="14.25" customHeight="1" s="84">
+    <row r="62" ht="14.25" customHeight="1" s="90">
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="n"/>
       <c r="C62" s="1" t="n"/>
@@ -24968,7 +24982,7 @@
       <c r="Y62" s="1" t="n"/>
       <c r="Z62" s="1" t="n"/>
     </row>
-    <row r="63" ht="14.25" customHeight="1" s="84">
+    <row r="63" ht="14.25" customHeight="1" s="90">
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="n"/>
       <c r="C63" s="1" t="n"/>
@@ -24996,7 +25010,7 @@
       <c r="Y63" s="1" t="n"/>
       <c r="Z63" s="1" t="n"/>
     </row>
-    <row r="64" ht="14.25" customHeight="1" s="84">
+    <row r="64" ht="14.25" customHeight="1" s="90">
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="n"/>
       <c r="C64" s="1" t="n"/>
@@ -25024,7 +25038,7 @@
       <c r="Y64" s="1" t="n"/>
       <c r="Z64" s="1" t="n"/>
     </row>
-    <row r="65" ht="14.25" customHeight="1" s="84">
+    <row r="65" ht="14.25" customHeight="1" s="90">
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="n"/>
       <c r="C65" s="1" t="n"/>
@@ -25052,7 +25066,7 @@
       <c r="Y65" s="1" t="n"/>
       <c r="Z65" s="1" t="n"/>
     </row>
-    <row r="66" ht="14.25" customHeight="1" s="84">
+    <row r="66" ht="14.25" customHeight="1" s="90">
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="n"/>
       <c r="C66" s="1" t="n"/>
@@ -25080,7 +25094,7 @@
       <c r="Y66" s="1" t="n"/>
       <c r="Z66" s="1" t="n"/>
     </row>
-    <row r="67" ht="14.25" customHeight="1" s="84">
+    <row r="67" ht="14.25" customHeight="1" s="90">
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="n"/>
       <c r="C67" s="1" t="n"/>
@@ -25108,7 +25122,7 @@
       <c r="Y67" s="1" t="n"/>
       <c r="Z67" s="1" t="n"/>
     </row>
-    <row r="68" ht="14.25" customHeight="1" s="84">
+    <row r="68" ht="14.25" customHeight="1" s="90">
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="n"/>
       <c r="C68" s="1" t="n"/>
@@ -25136,7 +25150,7 @@
       <c r="Y68" s="1" t="n"/>
       <c r="Z68" s="1" t="n"/>
     </row>
-    <row r="69" ht="14.25" customHeight="1" s="84">
+    <row r="69" ht="14.25" customHeight="1" s="90">
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="n"/>
       <c r="C69" s="1" t="n"/>
@@ -25164,7 +25178,7 @@
       <c r="Y69" s="1" t="n"/>
       <c r="Z69" s="1" t="n"/>
     </row>
-    <row r="70" ht="14.25" customHeight="1" s="84">
+    <row r="70" ht="14.25" customHeight="1" s="90">
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="n"/>
       <c r="C70" s="1" t="n"/>
@@ -25192,7 +25206,7 @@
       <c r="Y70" s="1" t="n"/>
       <c r="Z70" s="1" t="n"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1" s="84">
+    <row r="71" ht="14.25" customHeight="1" s="90">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="n"/>
       <c r="C71" s="1" t="n"/>
@@ -25220,7 +25234,7 @@
       <c r="Y71" s="1" t="n"/>
       <c r="Z71" s="1" t="n"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1" s="84">
+    <row r="72" ht="14.25" customHeight="1" s="90">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="n"/>
       <c r="C72" s="1" t="n"/>
@@ -25248,7 +25262,7 @@
       <c r="Y72" s="1" t="n"/>
       <c r="Z72" s="1" t="n"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1" s="84">
+    <row r="73" ht="14.25" customHeight="1" s="90">
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="n"/>
       <c r="C73" s="1" t="n"/>
@@ -25276,7 +25290,7 @@
       <c r="Y73" s="1" t="n"/>
       <c r="Z73" s="1" t="n"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1" s="84">
+    <row r="74" ht="14.25" customHeight="1" s="90">
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="n"/>
       <c r="C74" s="1" t="n"/>
@@ -25304,7 +25318,7 @@
       <c r="Y74" s="1" t="n"/>
       <c r="Z74" s="1" t="n"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1" s="84">
+    <row r="75" ht="14.25" customHeight="1" s="90">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="n"/>
       <c r="C75" s="1" t="n"/>
@@ -25332,7 +25346,7 @@
       <c r="Y75" s="1" t="n"/>
       <c r="Z75" s="1" t="n"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1" s="84">
+    <row r="76" ht="14.25" customHeight="1" s="90">
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="n"/>
       <c r="C76" s="1" t="n"/>
@@ -25360,7 +25374,7 @@
       <c r="Y76" s="1" t="n"/>
       <c r="Z76" s="1" t="n"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1" s="84">
+    <row r="77" ht="14.25" customHeight="1" s="90">
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="n"/>
       <c r="C77" s="1" t="n"/>
@@ -25388,7 +25402,7 @@
       <c r="Y77" s="1" t="n"/>
       <c r="Z77" s="1" t="n"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1" s="84">
+    <row r="78" ht="14.25" customHeight="1" s="90">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="n"/>
       <c r="C78" s="1" t="n"/>
@@ -25416,7 +25430,7 @@
       <c r="Y78" s="1" t="n"/>
       <c r="Z78" s="1" t="n"/>
     </row>
-    <row r="79" ht="14.25" customHeight="1" s="84">
+    <row r="79" ht="14.25" customHeight="1" s="90">
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="n"/>
       <c r="C79" s="1" t="n"/>
@@ -25444,7 +25458,7 @@
       <c r="Y79" s="1" t="n"/>
       <c r="Z79" s="1" t="n"/>
     </row>
-    <row r="80" ht="14.25" customHeight="1" s="84">
+    <row r="80" ht="14.25" customHeight="1" s="90">
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="n"/>
       <c r="C80" s="1" t="n"/>
@@ -25472,7 +25486,7 @@
       <c r="Y80" s="1" t="n"/>
       <c r="Z80" s="1" t="n"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1" s="84">
+    <row r="81" ht="14.25" customHeight="1" s="90">
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="n"/>
       <c r="C81" s="1" t="n"/>
@@ -25500,7 +25514,7 @@
       <c r="Y81" s="1" t="n"/>
       <c r="Z81" s="1" t="n"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1" s="84">
+    <row r="82" ht="14.25" customHeight="1" s="90">
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="n"/>
       <c r="C82" s="1" t="n"/>
@@ -25528,7 +25542,7 @@
       <c r="Y82" s="1" t="n"/>
       <c r="Z82" s="1" t="n"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1" s="84">
+    <row r="83" ht="14.25" customHeight="1" s="90">
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="n"/>
       <c r="C83" s="1" t="n"/>
@@ -25556,7 +25570,7 @@
       <c r="Y83" s="1" t="n"/>
       <c r="Z83" s="1" t="n"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1" s="84">
+    <row r="84" ht="14.25" customHeight="1" s="90">
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="n"/>
       <c r="C84" s="1" t="n"/>
@@ -25584,7 +25598,7 @@
       <c r="Y84" s="1" t="n"/>
       <c r="Z84" s="1" t="n"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1" s="84">
+    <row r="85" ht="14.25" customHeight="1" s="90">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="n"/>
       <c r="C85" s="1" t="n"/>
@@ -25612,7 +25626,7 @@
       <c r="Y85" s="1" t="n"/>
       <c r="Z85" s="1" t="n"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1" s="84">
+    <row r="86" ht="14.25" customHeight="1" s="90">
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="n"/>
       <c r="C86" s="1" t="n"/>
@@ -25640,7 +25654,7 @@
       <c r="Y86" s="1" t="n"/>
       <c r="Z86" s="1" t="n"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1" s="84">
+    <row r="87" ht="14.25" customHeight="1" s="90">
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="n"/>
       <c r="C87" s="1" t="n"/>
@@ -25668,7 +25682,7 @@
       <c r="Y87" s="1" t="n"/>
       <c r="Z87" s="1" t="n"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1" s="84">
+    <row r="88" ht="14.25" customHeight="1" s="90">
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="n"/>
       <c r="C88" s="1" t="n"/>
@@ -25696,7 +25710,7 @@
       <c r="Y88" s="1" t="n"/>
       <c r="Z88" s="1" t="n"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1" s="84">
+    <row r="89" ht="14.25" customHeight="1" s="90">
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="n"/>
       <c r="C89" s="1" t="n"/>
@@ -25724,7 +25738,7 @@
       <c r="Y89" s="1" t="n"/>
       <c r="Z89" s="1" t="n"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1" s="84">
+    <row r="90" ht="14.25" customHeight="1" s="90">
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="n"/>
       <c r="C90" s="1" t="n"/>
@@ -25752,7 +25766,7 @@
       <c r="Y90" s="1" t="n"/>
       <c r="Z90" s="1" t="n"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1" s="84">
+    <row r="91" ht="14.25" customHeight="1" s="90">
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="n"/>
       <c r="C91" s="1" t="n"/>
@@ -25780,7 +25794,7 @@
       <c r="Y91" s="1" t="n"/>
       <c r="Z91" s="1" t="n"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1" s="84">
+    <row r="92" ht="14.25" customHeight="1" s="90">
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="n"/>
       <c r="C92" s="1" t="n"/>
@@ -25808,7 +25822,7 @@
       <c r="Y92" s="1" t="n"/>
       <c r="Z92" s="1" t="n"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1" s="84">
+    <row r="93" ht="14.25" customHeight="1" s="90">
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="n"/>
       <c r="C93" s="1" t="n"/>
@@ -25836,7 +25850,7 @@
       <c r="Y93" s="1" t="n"/>
       <c r="Z93" s="1" t="n"/>
     </row>
-    <row r="94" ht="14.25" customHeight="1" s="84">
+    <row r="94" ht="14.25" customHeight="1" s="90">
       <c r="A94" s="1" t="n"/>
       <c r="B94" s="1" t="n"/>
       <c r="C94" s="1" t="n"/>
@@ -25864,7 +25878,7 @@
       <c r="Y94" s="1" t="n"/>
       <c r="Z94" s="1" t="n"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1" s="84">
+    <row r="95" ht="14.25" customHeight="1" s="90">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="n"/>
       <c r="C95" s="1" t="n"/>
@@ -25892,7 +25906,7 @@
       <c r="Y95" s="1" t="n"/>
       <c r="Z95" s="1" t="n"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1" s="84">
+    <row r="96" ht="14.25" customHeight="1" s="90">
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="n"/>
       <c r="C96" s="1" t="n"/>
@@ -25920,7 +25934,7 @@
       <c r="Y96" s="1" t="n"/>
       <c r="Z96" s="1" t="n"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1" s="84">
+    <row r="97" ht="14.25" customHeight="1" s="90">
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="n"/>
       <c r="C97" s="1" t="n"/>
@@ -25948,7 +25962,7 @@
       <c r="Y97" s="1" t="n"/>
       <c r="Z97" s="1" t="n"/>
     </row>
-    <row r="98" ht="14.25" customHeight="1" s="84">
+    <row r="98" ht="14.25" customHeight="1" s="90">
       <c r="A98" s="1" t="n"/>
       <c r="B98" s="1" t="n"/>
       <c r="C98" s="1" t="n"/>
@@ -25976,7 +25990,7 @@
       <c r="Y98" s="1" t="n"/>
       <c r="Z98" s="1" t="n"/>
     </row>
-    <row r="99" ht="14.25" customHeight="1" s="84">
+    <row r="99" ht="14.25" customHeight="1" s="90">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="n"/>
       <c r="C99" s="1" t="n"/>
@@ -26004,7 +26018,7 @@
       <c r="Y99" s="1" t="n"/>
       <c r="Z99" s="1" t="n"/>
     </row>
-    <row r="100" ht="14.25" customHeight="1" s="84">
+    <row r="100" ht="14.25" customHeight="1" s="90">
       <c r="A100" s="1" t="n"/>
       <c r="B100" s="1" t="n"/>
       <c r="C100" s="1" t="n"/>
@@ -26032,7 +26046,7 @@
       <c r="Y100" s="1" t="n"/>
       <c r="Z100" s="1" t="n"/>
     </row>
-    <row r="101" ht="14.25" customHeight="1" s="84">
+    <row r="101" ht="14.25" customHeight="1" s="90">
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="n"/>
       <c r="C101" s="1" t="n"/>
@@ -26060,7 +26074,7 @@
       <c r="Y101" s="1" t="n"/>
       <c r="Z101" s="1" t="n"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1" s="84">
+    <row r="102" ht="14.25" customHeight="1" s="90">
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="n"/>
       <c r="C102" s="1" t="n"/>
@@ -26088,7 +26102,7 @@
       <c r="Y102" s="1" t="n"/>
       <c r="Z102" s="1" t="n"/>
     </row>
-    <row r="103" ht="14.25" customHeight="1" s="84">
+    <row r="103" ht="14.25" customHeight="1" s="90">
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="n"/>
       <c r="C103" s="1" t="n"/>
@@ -26116,7 +26130,7 @@
       <c r="Y103" s="1" t="n"/>
       <c r="Z103" s="1" t="n"/>
     </row>
-    <row r="104" ht="14.25" customHeight="1" s="84">
+    <row r="104" ht="14.25" customHeight="1" s="90">
       <c r="A104" s="1" t="n"/>
       <c r="B104" s="1" t="n"/>
       <c r="C104" s="1" t="n"/>
@@ -26144,7 +26158,7 @@
       <c r="Y104" s="1" t="n"/>
       <c r="Z104" s="1" t="n"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1" s="84">
+    <row r="105" ht="14.25" customHeight="1" s="90">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="n"/>
       <c r="C105" s="1" t="n"/>
@@ -26172,7 +26186,7 @@
       <c r="Y105" s="1" t="n"/>
       <c r="Z105" s="1" t="n"/>
     </row>
-    <row r="106" ht="14.25" customHeight="1" s="84">
+    <row r="106" ht="14.25" customHeight="1" s="90">
       <c r="A106" s="1" t="n"/>
       <c r="B106" s="1" t="n"/>
       <c r="C106" s="1" t="n"/>
@@ -26200,7 +26214,7 @@
       <c r="Y106" s="1" t="n"/>
       <c r="Z106" s="1" t="n"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1" s="84">
+    <row r="107" ht="14.25" customHeight="1" s="90">
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="n"/>
       <c r="C107" s="1" t="n"/>
@@ -26228,7 +26242,7 @@
       <c r="Y107" s="1" t="n"/>
       <c r="Z107" s="1" t="n"/>
     </row>
-    <row r="108" ht="14.25" customHeight="1" s="84">
+    <row r="108" ht="14.25" customHeight="1" s="90">
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="n"/>
       <c r="C108" s="1" t="n"/>
@@ -26256,7 +26270,7 @@
       <c r="Y108" s="1" t="n"/>
       <c r="Z108" s="1" t="n"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1" s="84">
+    <row r="109" ht="14.25" customHeight="1" s="90">
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="n"/>
       <c r="C109" s="1" t="n"/>
@@ -26284,7 +26298,7 @@
       <c r="Y109" s="1" t="n"/>
       <c r="Z109" s="1" t="n"/>
     </row>
-    <row r="110" ht="14.25" customHeight="1" s="84">
+    <row r="110" ht="14.25" customHeight="1" s="90">
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="n"/>
       <c r="C110" s="1" t="n"/>
@@ -26312,7 +26326,7 @@
       <c r="Y110" s="1" t="n"/>
       <c r="Z110" s="1" t="n"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1" s="84">
+    <row r="111" ht="14.25" customHeight="1" s="90">
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="n"/>
       <c r="C111" s="1" t="n"/>
@@ -26340,7 +26354,7 @@
       <c r="Y111" s="1" t="n"/>
       <c r="Z111" s="1" t="n"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1" s="84">
+    <row r="112" ht="14.25" customHeight="1" s="90">
       <c r="A112" s="1" t="n"/>
       <c r="B112" s="1" t="n"/>
       <c r="C112" s="1" t="n"/>
@@ -26368,7 +26382,7 @@
       <c r="Y112" s="1" t="n"/>
       <c r="Z112" s="1" t="n"/>
     </row>
-    <row r="113" ht="14.25" customHeight="1" s="84">
+    <row r="113" ht="14.25" customHeight="1" s="90">
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="n"/>
       <c r="C113" s="1" t="n"/>
@@ -26396,7 +26410,7 @@
       <c r="Y113" s="1" t="n"/>
       <c r="Z113" s="1" t="n"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1" s="84">
+    <row r="114" ht="14.25" customHeight="1" s="90">
       <c r="A114" s="1" t="n"/>
       <c r="B114" s="1" t="n"/>
       <c r="C114" s="1" t="n"/>
@@ -26424,7 +26438,7 @@
       <c r="Y114" s="1" t="n"/>
       <c r="Z114" s="1" t="n"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1" s="84">
+    <row r="115" ht="14.25" customHeight="1" s="90">
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="n"/>
       <c r="C115" s="1" t="n"/>
@@ -26452,7 +26466,7 @@
       <c r="Y115" s="1" t="n"/>
       <c r="Z115" s="1" t="n"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1" s="84">
+    <row r="116" ht="14.25" customHeight="1" s="90">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="n"/>
       <c r="C116" s="1" t="n"/>
@@ -26480,7 +26494,7 @@
       <c r="Y116" s="1" t="n"/>
       <c r="Z116" s="1" t="n"/>
     </row>
-    <row r="117" ht="14.25" customHeight="1" s="84">
+    <row r="117" ht="14.25" customHeight="1" s="90">
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="n"/>
       <c r="C117" s="1" t="n"/>
@@ -26508,7 +26522,7 @@
       <c r="Y117" s="1" t="n"/>
       <c r="Z117" s="1" t="n"/>
     </row>
-    <row r="118" ht="14.25" customHeight="1" s="84">
+    <row r="118" ht="14.25" customHeight="1" s="90">
       <c r="A118" s="1" t="n"/>
       <c r="B118" s="1" t="n"/>
       <c r="C118" s="1" t="n"/>
@@ -26536,7 +26550,7 @@
       <c r="Y118" s="1" t="n"/>
       <c r="Z118" s="1" t="n"/>
     </row>
-    <row r="119" ht="14.25" customHeight="1" s="84">
+    <row r="119" ht="14.25" customHeight="1" s="90">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="n"/>
       <c r="C119" s="1" t="n"/>
@@ -26564,7 +26578,7 @@
       <c r="Y119" s="1" t="n"/>
       <c r="Z119" s="1" t="n"/>
     </row>
-    <row r="120" ht="14.25" customHeight="1" s="84">
+    <row r="120" ht="14.25" customHeight="1" s="90">
       <c r="A120" s="1" t="n"/>
       <c r="B120" s="1" t="n"/>
       <c r="C120" s="1" t="n"/>
@@ -26592,7 +26606,7 @@
       <c r="Y120" s="1" t="n"/>
       <c r="Z120" s="1" t="n"/>
     </row>
-    <row r="121" ht="14.25" customHeight="1" s="84">
+    <row r="121" ht="14.25" customHeight="1" s="90">
       <c r="A121" s="1" t="n"/>
       <c r="B121" s="1" t="n"/>
       <c r="C121" s="1" t="n"/>
@@ -26620,7 +26634,7 @@
       <c r="Y121" s="1" t="n"/>
       <c r="Z121" s="1" t="n"/>
     </row>
-    <row r="122" ht="14.25" customHeight="1" s="84">
+    <row r="122" ht="14.25" customHeight="1" s="90">
       <c r="A122" s="1" t="n"/>
       <c r="B122" s="1" t="n"/>
       <c r="C122" s="1" t="n"/>
@@ -26648,7 +26662,7 @@
       <c r="Y122" s="1" t="n"/>
       <c r="Z122" s="1" t="n"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1" s="84">
+    <row r="123" ht="14.25" customHeight="1" s="90">
       <c r="A123" s="1" t="n"/>
       <c r="B123" s="1" t="n"/>
       <c r="C123" s="1" t="n"/>
@@ -26676,7 +26690,7 @@
       <c r="Y123" s="1" t="n"/>
       <c r="Z123" s="1" t="n"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1" s="84">
+    <row r="124" ht="14.25" customHeight="1" s="90">
       <c r="A124" s="1" t="n"/>
       <c r="B124" s="1" t="n"/>
       <c r="C124" s="1" t="n"/>
@@ -26704,7 +26718,7 @@
       <c r="Y124" s="1" t="n"/>
       <c r="Z124" s="1" t="n"/>
     </row>
-    <row r="125" ht="14.25" customHeight="1" s="84">
+    <row r="125" ht="14.25" customHeight="1" s="90">
       <c r="A125" s="1" t="n"/>
       <c r="B125" s="1" t="n"/>
       <c r="C125" s="1" t="n"/>
@@ -26732,7 +26746,7 @@
       <c r="Y125" s="1" t="n"/>
       <c r="Z125" s="1" t="n"/>
     </row>
-    <row r="126" ht="14.25" customHeight="1" s="84">
+    <row r="126" ht="14.25" customHeight="1" s="90">
       <c r="A126" s="1" t="n"/>
       <c r="B126" s="1" t="n"/>
       <c r="C126" s="1" t="n"/>
@@ -26760,7 +26774,7 @@
       <c r="Y126" s="1" t="n"/>
       <c r="Z126" s="1" t="n"/>
     </row>
-    <row r="127" ht="14.25" customHeight="1" s="84">
+    <row r="127" ht="14.25" customHeight="1" s="90">
       <c r="A127" s="1" t="n"/>
       <c r="B127" s="1" t="n"/>
       <c r="C127" s="1" t="n"/>
@@ -26788,7 +26802,7 @@
       <c r="Y127" s="1" t="n"/>
       <c r="Z127" s="1" t="n"/>
     </row>
-    <row r="128" ht="14.25" customHeight="1" s="84">
+    <row r="128" ht="14.25" customHeight="1" s="90">
       <c r="A128" s="1" t="n"/>
       <c r="B128" s="1" t="n"/>
       <c r="C128" s="1" t="n"/>
@@ -26816,7 +26830,7 @@
       <c r="Y128" s="1" t="n"/>
       <c r="Z128" s="1" t="n"/>
     </row>
-    <row r="129" ht="14.25" customHeight="1" s="84">
+    <row r="129" ht="14.25" customHeight="1" s="90">
       <c r="A129" s="1" t="n"/>
       <c r="B129" s="1" t="n"/>
       <c r="C129" s="1" t="n"/>
@@ -26844,7 +26858,7 @@
       <c r="Y129" s="1" t="n"/>
       <c r="Z129" s="1" t="n"/>
     </row>
-    <row r="130" ht="14.25" customHeight="1" s="84">
+    <row r="130" ht="14.25" customHeight="1" s="90">
       <c r="A130" s="1" t="n"/>
       <c r="B130" s="1" t="n"/>
       <c r="C130" s="1" t="n"/>
@@ -26872,7 +26886,7 @@
       <c r="Y130" s="1" t="n"/>
       <c r="Z130" s="1" t="n"/>
     </row>
-    <row r="131" ht="14.25" customHeight="1" s="84">
+    <row r="131" ht="14.25" customHeight="1" s="90">
       <c r="A131" s="1" t="n"/>
       <c r="B131" s="1" t="n"/>
       <c r="C131" s="1" t="n"/>
@@ -26900,7 +26914,7 @@
       <c r="Y131" s="1" t="n"/>
       <c r="Z131" s="1" t="n"/>
     </row>
-    <row r="132" ht="14.25" customHeight="1" s="84">
+    <row r="132" ht="14.25" customHeight="1" s="90">
       <c r="A132" s="1" t="n"/>
       <c r="B132" s="1" t="n"/>
       <c r="C132" s="1" t="n"/>
@@ -26928,7 +26942,7 @@
       <c r="Y132" s="1" t="n"/>
       <c r="Z132" s="1" t="n"/>
     </row>
-    <row r="133" ht="14.25" customHeight="1" s="84">
+    <row r="133" ht="14.25" customHeight="1" s="90">
       <c r="A133" s="1" t="n"/>
       <c r="B133" s="1" t="n"/>
       <c r="C133" s="1" t="n"/>
@@ -26956,7 +26970,7 @@
       <c r="Y133" s="1" t="n"/>
       <c r="Z133" s="1" t="n"/>
     </row>
-    <row r="134" ht="14.25" customHeight="1" s="84">
+    <row r="134" ht="14.25" customHeight="1" s="90">
       <c r="A134" s="1" t="n"/>
       <c r="B134" s="1" t="n"/>
       <c r="C134" s="1" t="n"/>
@@ -26984,7 +26998,7 @@
       <c r="Y134" s="1" t="n"/>
       <c r="Z134" s="1" t="n"/>
     </row>
-    <row r="135" ht="14.25" customHeight="1" s="84">
+    <row r="135" ht="14.25" customHeight="1" s="90">
       <c r="A135" s="1" t="n"/>
       <c r="B135" s="1" t="n"/>
       <c r="C135" s="1" t="n"/>
@@ -27012,7 +27026,7 @@
       <c r="Y135" s="1" t="n"/>
       <c r="Z135" s="1" t="n"/>
     </row>
-    <row r="136" ht="14.25" customHeight="1" s="84">
+    <row r="136" ht="14.25" customHeight="1" s="90">
       <c r="A136" s="1" t="n"/>
       <c r="B136" s="1" t="n"/>
       <c r="C136" s="1" t="n"/>
@@ -27040,7 +27054,7 @@
       <c r="Y136" s="1" t="n"/>
       <c r="Z136" s="1" t="n"/>
     </row>
-    <row r="137" ht="14.25" customHeight="1" s="84">
+    <row r="137" ht="14.25" customHeight="1" s="90">
       <c r="A137" s="1" t="n"/>
       <c r="B137" s="1" t="n"/>
       <c r="C137" s="1" t="n"/>
@@ -27068,7 +27082,7 @@
       <c r="Y137" s="1" t="n"/>
       <c r="Z137" s="1" t="n"/>
     </row>
-    <row r="138" ht="14.25" customHeight="1" s="84">
+    <row r="138" ht="14.25" customHeight="1" s="90">
       <c r="A138" s="1" t="n"/>
       <c r="B138" s="1" t="n"/>
       <c r="C138" s="1" t="n"/>
@@ -27096,7 +27110,7 @@
       <c r="Y138" s="1" t="n"/>
       <c r="Z138" s="1" t="n"/>
     </row>
-    <row r="139" ht="14.25" customHeight="1" s="84">
+    <row r="139" ht="14.25" customHeight="1" s="90">
       <c r="A139" s="1" t="n"/>
       <c r="B139" s="1" t="n"/>
       <c r="C139" s="1" t="n"/>
@@ -27124,7 +27138,7 @@
       <c r="Y139" s="1" t="n"/>
       <c r="Z139" s="1" t="n"/>
     </row>
-    <row r="140" ht="14.25" customHeight="1" s="84">
+    <row r="140" ht="14.25" customHeight="1" s="90">
       <c r="A140" s="1" t="n"/>
       <c r="B140" s="1" t="n"/>
       <c r="C140" s="1" t="n"/>
@@ -27152,7 +27166,7 @@
       <c r="Y140" s="1" t="n"/>
       <c r="Z140" s="1" t="n"/>
     </row>
-    <row r="141" ht="14.25" customHeight="1" s="84">
+    <row r="141" ht="14.25" customHeight="1" s="90">
       <c r="A141" s="1" t="n"/>
       <c r="B141" s="1" t="n"/>
       <c r="C141" s="1" t="n"/>
@@ -27180,7 +27194,7 @@
       <c r="Y141" s="1" t="n"/>
       <c r="Z141" s="1" t="n"/>
     </row>
-    <row r="142" ht="14.25" customHeight="1" s="84">
+    <row r="142" ht="14.25" customHeight="1" s="90">
       <c r="A142" s="1" t="n"/>
       <c r="B142" s="1" t="n"/>
       <c r="C142" s="1" t="n"/>
@@ -27208,7 +27222,7 @@
       <c r="Y142" s="1" t="n"/>
       <c r="Z142" s="1" t="n"/>
     </row>
-    <row r="143" ht="14.25" customHeight="1" s="84">
+    <row r="143" ht="14.25" customHeight="1" s="90">
       <c r="A143" s="1" t="n"/>
       <c r="B143" s="1" t="n"/>
       <c r="C143" s="1" t="n"/>
@@ -27236,7 +27250,7 @@
       <c r="Y143" s="1" t="n"/>
       <c r="Z143" s="1" t="n"/>
     </row>
-    <row r="144" ht="14.25" customHeight="1" s="84">
+    <row r="144" ht="14.25" customHeight="1" s="90">
       <c r="A144" s="1" t="n"/>
       <c r="B144" s="1" t="n"/>
       <c r="C144" s="1" t="n"/>
@@ -27264,7 +27278,7 @@
       <c r="Y144" s="1" t="n"/>
       <c r="Z144" s="1" t="n"/>
     </row>
-    <row r="145" ht="14.25" customHeight="1" s="84">
+    <row r="145" ht="14.25" customHeight="1" s="90">
       <c r="A145" s="1" t="n"/>
       <c r="B145" s="1" t="n"/>
       <c r="C145" s="1" t="n"/>
@@ -27292,7 +27306,7 @@
       <c r="Y145" s="1" t="n"/>
       <c r="Z145" s="1" t="n"/>
     </row>
-    <row r="146" ht="14.25" customHeight="1" s="84">
+    <row r="146" ht="14.25" customHeight="1" s="90">
       <c r="A146" s="1" t="n"/>
       <c r="B146" s="1" t="n"/>
       <c r="C146" s="1" t="n"/>
@@ -27320,7 +27334,7 @@
       <c r="Y146" s="1" t="n"/>
       <c r="Z146" s="1" t="n"/>
     </row>
-    <row r="147" ht="14.25" customHeight="1" s="84">
+    <row r="147" ht="14.25" customHeight="1" s="90">
       <c r="A147" s="1" t="n"/>
       <c r="B147" s="1" t="n"/>
       <c r="C147" s="1" t="n"/>
@@ -27348,7 +27362,7 @@
       <c r="Y147" s="1" t="n"/>
       <c r="Z147" s="1" t="n"/>
     </row>
-    <row r="148" ht="14.25" customHeight="1" s="84">
+    <row r="148" ht="14.25" customHeight="1" s="90">
       <c r="A148" s="1" t="n"/>
       <c r="B148" s="1" t="n"/>
       <c r="C148" s="1" t="n"/>
@@ -27376,7 +27390,7 @@
       <c r="Y148" s="1" t="n"/>
       <c r="Z148" s="1" t="n"/>
     </row>
-    <row r="149" ht="14.25" customHeight="1" s="84">
+    <row r="149" ht="14.25" customHeight="1" s="90">
       <c r="A149" s="1" t="n"/>
       <c r="B149" s="1" t="n"/>
       <c r="C149" s="1" t="n"/>
@@ -27404,7 +27418,7 @@
       <c r="Y149" s="1" t="n"/>
       <c r="Z149" s="1" t="n"/>
     </row>
-    <row r="150" ht="14.25" customHeight="1" s="84">
+    <row r="150" ht="14.25" customHeight="1" s="90">
       <c r="A150" s="1" t="n"/>
       <c r="B150" s="1" t="n"/>
       <c r="C150" s="1" t="n"/>
@@ -27432,7 +27446,7 @@
       <c r="Y150" s="1" t="n"/>
       <c r="Z150" s="1" t="n"/>
     </row>
-    <row r="151" ht="14.25" customHeight="1" s="84">
+    <row r="151" ht="14.25" customHeight="1" s="90">
       <c r="A151" s="1" t="n"/>
       <c r="B151" s="1" t="n"/>
       <c r="C151" s="1" t="n"/>
@@ -27460,7 +27474,7 @@
       <c r="Y151" s="1" t="n"/>
       <c r="Z151" s="1" t="n"/>
     </row>
-    <row r="152" ht="14.25" customHeight="1" s="84">
+    <row r="152" ht="14.25" customHeight="1" s="90">
       <c r="A152" s="1" t="n"/>
       <c r="B152" s="1" t="n"/>
       <c r="C152" s="1" t="n"/>
@@ -27488,7 +27502,7 @@
       <c r="Y152" s="1" t="n"/>
       <c r="Z152" s="1" t="n"/>
     </row>
-    <row r="153" ht="14.25" customHeight="1" s="84">
+    <row r="153" ht="14.25" customHeight="1" s="90">
       <c r="A153" s="1" t="n"/>
       <c r="B153" s="1" t="n"/>
       <c r="C153" s="1" t="n"/>
@@ -27516,7 +27530,7 @@
       <c r="Y153" s="1" t="n"/>
       <c r="Z153" s="1" t="n"/>
     </row>
-    <row r="154" ht="14.25" customHeight="1" s="84">
+    <row r="154" ht="14.25" customHeight="1" s="90">
       <c r="A154" s="1" t="n"/>
       <c r="B154" s="1" t="n"/>
       <c r="C154" s="1" t="n"/>
@@ -27544,7 +27558,7 @@
       <c r="Y154" s="1" t="n"/>
       <c r="Z154" s="1" t="n"/>
     </row>
-    <row r="155" ht="14.25" customHeight="1" s="84">
+    <row r="155" ht="14.25" customHeight="1" s="90">
       <c r="A155" s="1" t="n"/>
       <c r="B155" s="1" t="n"/>
       <c r="C155" s="1" t="n"/>
@@ -27572,7 +27586,7 @@
       <c r="Y155" s="1" t="n"/>
       <c r="Z155" s="1" t="n"/>
     </row>
-    <row r="156" ht="14.25" customHeight="1" s="84">
+    <row r="156" ht="14.25" customHeight="1" s="90">
       <c r="A156" s="1" t="n"/>
       <c r="B156" s="1" t="n"/>
       <c r="C156" s="1" t="n"/>
@@ -27600,7 +27614,7 @@
       <c r="Y156" s="1" t="n"/>
       <c r="Z156" s="1" t="n"/>
     </row>
-    <row r="157" ht="14.25" customHeight="1" s="84">
+    <row r="157" ht="14.25" customHeight="1" s="90">
       <c r="A157" s="1" t="n"/>
       <c r="B157" s="1" t="n"/>
       <c r="C157" s="1" t="n"/>
@@ -27628,7 +27642,7 @@
       <c r="Y157" s="1" t="n"/>
       <c r="Z157" s="1" t="n"/>
     </row>
-    <row r="158" ht="14.25" customHeight="1" s="84">
+    <row r="158" ht="14.25" customHeight="1" s="90">
       <c r="A158" s="1" t="n"/>
       <c r="B158" s="1" t="n"/>
       <c r="C158" s="1" t="n"/>
@@ -27656,7 +27670,7 @@
       <c r="Y158" s="1" t="n"/>
       <c r="Z158" s="1" t="n"/>
     </row>
-    <row r="159" ht="14.25" customHeight="1" s="84">
+    <row r="159" ht="14.25" customHeight="1" s="90">
       <c r="A159" s="1" t="n"/>
       <c r="B159" s="1" t="n"/>
       <c r="C159" s="1" t="n"/>
@@ -27684,7 +27698,7 @@
       <c r="Y159" s="1" t="n"/>
       <c r="Z159" s="1" t="n"/>
     </row>
-    <row r="160" ht="14.25" customHeight="1" s="84">
+    <row r="160" ht="14.25" customHeight="1" s="90">
       <c r="A160" s="1" t="n"/>
       <c r="B160" s="1" t="n"/>
       <c r="C160" s="1" t="n"/>
@@ -27712,7 +27726,7 @@
       <c r="Y160" s="1" t="n"/>
       <c r="Z160" s="1" t="n"/>
     </row>
-    <row r="161" ht="14.25" customHeight="1" s="84">
+    <row r="161" ht="14.25" customHeight="1" s="90">
       <c r="A161" s="1" t="n"/>
       <c r="B161" s="1" t="n"/>
       <c r="C161" s="1" t="n"/>
@@ -27740,7 +27754,7 @@
       <c r="Y161" s="1" t="n"/>
       <c r="Z161" s="1" t="n"/>
     </row>
-    <row r="162" ht="14.25" customHeight="1" s="84">
+    <row r="162" ht="14.25" customHeight="1" s="90">
       <c r="A162" s="1" t="n"/>
       <c r="B162" s="1" t="n"/>
       <c r="C162" s="1" t="n"/>
@@ -27768,7 +27782,7 @@
       <c r="Y162" s="1" t="n"/>
       <c r="Z162" s="1" t="n"/>
     </row>
-    <row r="163" ht="14.25" customHeight="1" s="84">
+    <row r="163" ht="14.25" customHeight="1" s="90">
       <c r="A163" s="1" t="n"/>
       <c r="B163" s="1" t="n"/>
       <c r="C163" s="1" t="n"/>
@@ -27796,7 +27810,7 @@
       <c r="Y163" s="1" t="n"/>
       <c r="Z163" s="1" t="n"/>
     </row>
-    <row r="164" ht="14.25" customHeight="1" s="84">
+    <row r="164" ht="14.25" customHeight="1" s="90">
       <c r="A164" s="1" t="n"/>
       <c r="B164" s="1" t="n"/>
       <c r="C164" s="1" t="n"/>
@@ -27824,7 +27838,7 @@
       <c r="Y164" s="1" t="n"/>
       <c r="Z164" s="1" t="n"/>
     </row>
-    <row r="165" ht="14.25" customHeight="1" s="84">
+    <row r="165" ht="14.25" customHeight="1" s="90">
       <c r="A165" s="1" t="n"/>
       <c r="B165" s="1" t="n"/>
       <c r="C165" s="1" t="n"/>
@@ -27852,7 +27866,7 @@
       <c r="Y165" s="1" t="n"/>
       <c r="Z165" s="1" t="n"/>
     </row>
-    <row r="166" ht="14.25" customHeight="1" s="84">
+    <row r="166" ht="14.25" customHeight="1" s="90">
       <c r="A166" s="1" t="n"/>
       <c r="B166" s="1" t="n"/>
       <c r="C166" s="1" t="n"/>
@@ -27880,7 +27894,7 @@
       <c r="Y166" s="1" t="n"/>
       <c r="Z166" s="1" t="n"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1" s="84">
+    <row r="167" ht="14.25" customHeight="1" s="90">
       <c r="A167" s="1" t="n"/>
       <c r="B167" s="1" t="n"/>
       <c r="C167" s="1" t="n"/>
@@ -27908,7 +27922,7 @@
       <c r="Y167" s="1" t="n"/>
       <c r="Z167" s="1" t="n"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1" s="84">
+    <row r="168" ht="14.25" customHeight="1" s="90">
       <c r="A168" s="1" t="n"/>
       <c r="B168" s="1" t="n"/>
       <c r="C168" s="1" t="n"/>
@@ -27936,7 +27950,7 @@
       <c r="Y168" s="1" t="n"/>
       <c r="Z168" s="1" t="n"/>
     </row>
-    <row r="169" ht="14.25" customHeight="1" s="84">
+    <row r="169" ht="14.25" customHeight="1" s="90">
       <c r="A169" s="1" t="n"/>
       <c r="B169" s="1" t="n"/>
       <c r="C169" s="1" t="n"/>
@@ -27964,7 +27978,7 @@
       <c r="Y169" s="1" t="n"/>
       <c r="Z169" s="1" t="n"/>
     </row>
-    <row r="170" ht="14.25" customHeight="1" s="84">
+    <row r="170" ht="14.25" customHeight="1" s="90">
       <c r="A170" s="1" t="n"/>
       <c r="B170" s="1" t="n"/>
       <c r="C170" s="1" t="n"/>
@@ -27992,7 +28006,7 @@
       <c r="Y170" s="1" t="n"/>
       <c r="Z170" s="1" t="n"/>
     </row>
-    <row r="171" ht="14.25" customHeight="1" s="84">
+    <row r="171" ht="14.25" customHeight="1" s="90">
       <c r="A171" s="1" t="n"/>
       <c r="B171" s="1" t="n"/>
       <c r="C171" s="1" t="n"/>
@@ -28020,7 +28034,7 @@
       <c r="Y171" s="1" t="n"/>
       <c r="Z171" s="1" t="n"/>
     </row>
-    <row r="172" ht="14.25" customHeight="1" s="84">
+    <row r="172" ht="14.25" customHeight="1" s="90">
       <c r="A172" s="1" t="n"/>
       <c r="B172" s="1" t="n"/>
       <c r="C172" s="1" t="n"/>
@@ -28048,7 +28062,7 @@
       <c r="Y172" s="1" t="n"/>
       <c r="Z172" s="1" t="n"/>
     </row>
-    <row r="173" ht="14.25" customHeight="1" s="84">
+    <row r="173" ht="14.25" customHeight="1" s="90">
       <c r="A173" s="1" t="n"/>
       <c r="B173" s="1" t="n"/>
       <c r="C173" s="1" t="n"/>
@@ -28076,7 +28090,7 @@
       <c r="Y173" s="1" t="n"/>
       <c r="Z173" s="1" t="n"/>
     </row>
-    <row r="174" ht="14.25" customHeight="1" s="84">
+    <row r="174" ht="14.25" customHeight="1" s="90">
       <c r="A174" s="1" t="n"/>
       <c r="B174" s="1" t="n"/>
       <c r="C174" s="1" t="n"/>
@@ -28104,7 +28118,7 @@
       <c r="Y174" s="1" t="n"/>
       <c r="Z174" s="1" t="n"/>
     </row>
-    <row r="175" ht="14.25" customHeight="1" s="84">
+    <row r="175" ht="14.25" customHeight="1" s="90">
       <c r="A175" s="1" t="n"/>
       <c r="B175" s="1" t="n"/>
       <c r="C175" s="1" t="n"/>
@@ -28132,7 +28146,7 @@
       <c r="Y175" s="1" t="n"/>
       <c r="Z175" s="1" t="n"/>
     </row>
-    <row r="176" ht="14.25" customHeight="1" s="84">
+    <row r="176" ht="14.25" customHeight="1" s="90">
       <c r="A176" s="1" t="n"/>
       <c r="B176" s="1" t="n"/>
       <c r="C176" s="1" t="n"/>
@@ -28160,7 +28174,7 @@
       <c r="Y176" s="1" t="n"/>
       <c r="Z176" s="1" t="n"/>
     </row>
-    <row r="177" ht="14.25" customHeight="1" s="84">
+    <row r="177" ht="14.25" customHeight="1" s="90">
       <c r="A177" s="1" t="n"/>
       <c r="B177" s="1" t="n"/>
       <c r="C177" s="1" t="n"/>
@@ -28188,7 +28202,7 @@
       <c r="Y177" s="1" t="n"/>
       <c r="Z177" s="1" t="n"/>
     </row>
-    <row r="178" ht="14.25" customHeight="1" s="84">
+    <row r="178" ht="14.25" customHeight="1" s="90">
       <c r="A178" s="1" t="n"/>
       <c r="B178" s="1" t="n"/>
       <c r="C178" s="1" t="n"/>
@@ -28216,7 +28230,7 @@
       <c r="Y178" s="1" t="n"/>
       <c r="Z178" s="1" t="n"/>
     </row>
-    <row r="179" ht="14.25" customHeight="1" s="84">
+    <row r="179" ht="14.25" customHeight="1" s="90">
       <c r="A179" s="1" t="n"/>
       <c r="B179" s="1" t="n"/>
       <c r="C179" s="1" t="n"/>
@@ -28244,7 +28258,7 @@
       <c r="Y179" s="1" t="n"/>
       <c r="Z179" s="1" t="n"/>
     </row>
-    <row r="180" ht="14.25" customHeight="1" s="84">
+    <row r="180" ht="14.25" customHeight="1" s="90">
       <c r="A180" s="1" t="n"/>
       <c r="B180" s="1" t="n"/>
       <c r="C180" s="1" t="n"/>
@@ -28272,7 +28286,7 @@
       <c r="Y180" s="1" t="n"/>
       <c r="Z180" s="1" t="n"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1" s="84">
+    <row r="181" ht="14.25" customHeight="1" s="90">
       <c r="A181" s="1" t="n"/>
       <c r="B181" s="1" t="n"/>
       <c r="C181" s="1" t="n"/>
@@ -28300,7 +28314,7 @@
       <c r="Y181" s="1" t="n"/>
       <c r="Z181" s="1" t="n"/>
     </row>
-    <row r="182" ht="14.25" customHeight="1" s="84">
+    <row r="182" ht="14.25" customHeight="1" s="90">
       <c r="A182" s="1" t="n"/>
       <c r="B182" s="1" t="n"/>
       <c r="C182" s="1" t="n"/>
@@ -28328,7 +28342,7 @@
       <c r="Y182" s="1" t="n"/>
       <c r="Z182" s="1" t="n"/>
     </row>
-    <row r="183" ht="14.25" customHeight="1" s="84">
+    <row r="183" ht="14.25" customHeight="1" s="90">
       <c r="A183" s="1" t="n"/>
       <c r="B183" s="1" t="n"/>
       <c r="C183" s="1" t="n"/>
@@ -28356,7 +28370,7 @@
       <c r="Y183" s="1" t="n"/>
       <c r="Z183" s="1" t="n"/>
     </row>
-    <row r="184" ht="14.25" customHeight="1" s="84">
+    <row r="184" ht="14.25" customHeight="1" s="90">
       <c r="A184" s="1" t="n"/>
       <c r="B184" s="1" t="n"/>
       <c r="C184" s="1" t="n"/>
@@ -28384,7 +28398,7 @@
       <c r="Y184" s="1" t="n"/>
       <c r="Z184" s="1" t="n"/>
     </row>
-    <row r="185" ht="14.25" customHeight="1" s="84">
+    <row r="185" ht="14.25" customHeight="1" s="90">
       <c r="A185" s="1" t="n"/>
       <c r="B185" s="1" t="n"/>
       <c r="C185" s="1" t="n"/>
@@ -28412,7 +28426,7 @@
       <c r="Y185" s="1" t="n"/>
       <c r="Z185" s="1" t="n"/>
     </row>
-    <row r="186" ht="14.25" customHeight="1" s="84">
+    <row r="186" ht="14.25" customHeight="1" s="90">
       <c r="A186" s="1" t="n"/>
       <c r="B186" s="1" t="n"/>
       <c r="C186" s="1" t="n"/>
@@ -28440,7 +28454,7 @@
       <c r="Y186" s="1" t="n"/>
       <c r="Z186" s="1" t="n"/>
     </row>
-    <row r="187" ht="14.25" customHeight="1" s="84">
+    <row r="187" ht="14.25" customHeight="1" s="90">
       <c r="A187" s="1" t="n"/>
       <c r="B187" s="1" t="n"/>
       <c r="C187" s="1" t="n"/>
@@ -28468,7 +28482,7 @@
       <c r="Y187" s="1" t="n"/>
       <c r="Z187" s="1" t="n"/>
     </row>
-    <row r="188" ht="14.25" customHeight="1" s="84">
+    <row r="188" ht="14.25" customHeight="1" s="90">
       <c r="A188" s="1" t="n"/>
       <c r="B188" s="1" t="n"/>
       <c r="C188" s="1" t="n"/>
@@ -28496,7 +28510,7 @@
       <c r="Y188" s="1" t="n"/>
       <c r="Z188" s="1" t="n"/>
     </row>
-    <row r="189" ht="14.25" customHeight="1" s="84">
+    <row r="189" ht="14.25" customHeight="1" s="90">
       <c r="A189" s="1" t="n"/>
       <c r="B189" s="1" t="n"/>
       <c r="C189" s="1" t="n"/>
@@ -28524,7 +28538,7 @@
       <c r="Y189" s="1" t="n"/>
       <c r="Z189" s="1" t="n"/>
     </row>
-    <row r="190" ht="14.25" customHeight="1" s="84">
+    <row r="190" ht="14.25" customHeight="1" s="90">
       <c r="A190" s="1" t="n"/>
       <c r="B190" s="1" t="n"/>
       <c r="C190" s="1" t="n"/>
@@ -28552,7 +28566,7 @@
       <c r="Y190" s="1" t="n"/>
       <c r="Z190" s="1" t="n"/>
     </row>
-    <row r="191" ht="14.25" customHeight="1" s="84">
+    <row r="191" ht="14.25" customHeight="1" s="90">
       <c r="A191" s="1" t="n"/>
       <c r="B191" s="1" t="n"/>
       <c r="C191" s="1" t="n"/>
@@ -28580,7 +28594,7 @@
       <c r="Y191" s="1" t="n"/>
       <c r="Z191" s="1" t="n"/>
     </row>
-    <row r="192" ht="14.25" customHeight="1" s="84">
+    <row r="192" ht="14.25" customHeight="1" s="90">
       <c r="A192" s="1" t="n"/>
       <c r="B192" s="1" t="n"/>
       <c r="C192" s="1" t="n"/>
@@ -28608,7 +28622,7 @@
       <c r="Y192" s="1" t="n"/>
       <c r="Z192" s="1" t="n"/>
     </row>
-    <row r="193" ht="14.25" customHeight="1" s="84">
+    <row r="193" ht="14.25" customHeight="1" s="90">
       <c r="A193" s="1" t="n"/>
       <c r="B193" s="1" t="n"/>
       <c r="C193" s="1" t="n"/>
@@ -28636,7 +28650,7 @@
       <c r="Y193" s="1" t="n"/>
       <c r="Z193" s="1" t="n"/>
     </row>
-    <row r="194" ht="14.25" customHeight="1" s="84">
+    <row r="194" ht="14.25" customHeight="1" s="90">
       <c r="A194" s="1" t="n"/>
       <c r="B194" s="1" t="n"/>
       <c r="C194" s="1" t="n"/>
@@ -28664,7 +28678,7 @@
       <c r="Y194" s="1" t="n"/>
       <c r="Z194" s="1" t="n"/>
     </row>
-    <row r="195" ht="14.25" customHeight="1" s="84">
+    <row r="195" ht="14.25" customHeight="1" s="90">
       <c r="A195" s="1" t="n"/>
       <c r="B195" s="1" t="n"/>
       <c r="C195" s="1" t="n"/>
@@ -28692,7 +28706,7 @@
       <c r="Y195" s="1" t="n"/>
       <c r="Z195" s="1" t="n"/>
     </row>
-    <row r="196" ht="14.25" customHeight="1" s="84">
+    <row r="196" ht="14.25" customHeight="1" s="90">
       <c r="A196" s="1" t="n"/>
       <c r="B196" s="1" t="n"/>
       <c r="C196" s="1" t="n"/>
@@ -28720,7 +28734,7 @@
       <c r="Y196" s="1" t="n"/>
       <c r="Z196" s="1" t="n"/>
     </row>
-    <row r="197" ht="14.25" customHeight="1" s="84">
+    <row r="197" ht="14.25" customHeight="1" s="90">
       <c r="A197" s="1" t="n"/>
       <c r="B197" s="1" t="n"/>
       <c r="C197" s="1" t="n"/>
@@ -28748,7 +28762,7 @@
       <c r="Y197" s="1" t="n"/>
       <c r="Z197" s="1" t="n"/>
     </row>
-    <row r="198" ht="14.25" customHeight="1" s="84">
+    <row r="198" ht="14.25" customHeight="1" s="90">
       <c r="A198" s="1" t="n"/>
       <c r="B198" s="1" t="n"/>
       <c r="C198" s="1" t="n"/>
@@ -28776,7 +28790,7 @@
       <c r="Y198" s="1" t="n"/>
       <c r="Z198" s="1" t="n"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1" s="84">
+    <row r="199" ht="14.25" customHeight="1" s="90">
       <c r="A199" s="1" t="n"/>
       <c r="B199" s="1" t="n"/>
       <c r="C199" s="1" t="n"/>
@@ -28804,7 +28818,7 @@
       <c r="Y199" s="1" t="n"/>
       <c r="Z199" s="1" t="n"/>
     </row>
-    <row r="200" ht="14.25" customHeight="1" s="84">
+    <row r="200" ht="14.25" customHeight="1" s="90">
       <c r="A200" s="1" t="n"/>
       <c r="B200" s="1" t="n"/>
       <c r="C200" s="1" t="n"/>
@@ -28832,7 +28846,7 @@
       <c r="Y200" s="1" t="n"/>
       <c r="Z200" s="1" t="n"/>
     </row>
-    <row r="201" ht="14.25" customHeight="1" s="84">
+    <row r="201" ht="14.25" customHeight="1" s="90">
       <c r="A201" s="1" t="n"/>
       <c r="B201" s="1" t="n"/>
       <c r="C201" s="1" t="n"/>
@@ -28860,7 +28874,7 @@
       <c r="Y201" s="1" t="n"/>
       <c r="Z201" s="1" t="n"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1" s="84">
+    <row r="202" ht="14.25" customHeight="1" s="90">
       <c r="A202" s="1" t="n"/>
       <c r="B202" s="1" t="n"/>
       <c r="C202" s="1" t="n"/>
@@ -28888,7 +28902,7 @@
       <c r="Y202" s="1" t="n"/>
       <c r="Z202" s="1" t="n"/>
     </row>
-    <row r="203" ht="14.25" customHeight="1" s="84">
+    <row r="203" ht="14.25" customHeight="1" s="90">
       <c r="A203" s="1" t="n"/>
       <c r="B203" s="1" t="n"/>
       <c r="C203" s="1" t="n"/>
@@ -28916,7 +28930,7 @@
       <c r="Y203" s="1" t="n"/>
       <c r="Z203" s="1" t="n"/>
     </row>
-    <row r="204" ht="14.25" customHeight="1" s="84">
+    <row r="204" ht="14.25" customHeight="1" s="90">
       <c r="A204" s="1" t="n"/>
       <c r="B204" s="1" t="n"/>
       <c r="C204" s="1" t="n"/>
@@ -28944,7 +28958,7 @@
       <c r="Y204" s="1" t="n"/>
       <c r="Z204" s="1" t="n"/>
     </row>
-    <row r="205" ht="14.25" customHeight="1" s="84">
+    <row r="205" ht="14.25" customHeight="1" s="90">
       <c r="A205" s="1" t="n"/>
       <c r="B205" s="1" t="n"/>
       <c r="C205" s="1" t="n"/>
@@ -28972,7 +28986,7 @@
       <c r="Y205" s="1" t="n"/>
       <c r="Z205" s="1" t="n"/>
     </row>
-    <row r="206" ht="14.25" customHeight="1" s="84">
+    <row r="206" ht="14.25" customHeight="1" s="90">
       <c r="A206" s="1" t="n"/>
       <c r="B206" s="1" t="n"/>
       <c r="C206" s="1" t="n"/>
@@ -29000,7 +29014,7 @@
       <c r="Y206" s="1" t="n"/>
       <c r="Z206" s="1" t="n"/>
     </row>
-    <row r="207" ht="14.25" customHeight="1" s="84">
+    <row r="207" ht="14.25" customHeight="1" s="90">
       <c r="A207" s="1" t="n"/>
       <c r="B207" s="1" t="n"/>
       <c r="C207" s="1" t="n"/>
@@ -29028,7 +29042,7 @@
       <c r="Y207" s="1" t="n"/>
       <c r="Z207" s="1" t="n"/>
     </row>
-    <row r="208" ht="14.25" customHeight="1" s="84">
+    <row r="208" ht="14.25" customHeight="1" s="90">
       <c r="A208" s="1" t="n"/>
       <c r="B208" s="1" t="n"/>
       <c r="C208" s="1" t="n"/>
@@ -29056,7 +29070,7 @@
       <c r="Y208" s="1" t="n"/>
       <c r="Z208" s="1" t="n"/>
     </row>
-    <row r="209" ht="14.25" customHeight="1" s="84">
+    <row r="209" ht="14.25" customHeight="1" s="90">
       <c r="A209" s="1" t="n"/>
       <c r="B209" s="1" t="n"/>
       <c r="C209" s="1" t="n"/>
@@ -29084,7 +29098,7 @@
       <c r="Y209" s="1" t="n"/>
       <c r="Z209" s="1" t="n"/>
     </row>
-    <row r="210" ht="14.25" customHeight="1" s="84">
+    <row r="210" ht="14.25" customHeight="1" s="90">
       <c r="A210" s="1" t="n"/>
       <c r="B210" s="1" t="n"/>
       <c r="C210" s="1" t="n"/>
@@ -29112,7 +29126,7 @@
       <c r="Y210" s="1" t="n"/>
       <c r="Z210" s="1" t="n"/>
     </row>
-    <row r="211" ht="14.25" customHeight="1" s="84">
+    <row r="211" ht="14.25" customHeight="1" s="90">
       <c r="A211" s="1" t="n"/>
       <c r="B211" s="1" t="n"/>
       <c r="C211" s="1" t="n"/>
@@ -29140,7 +29154,7 @@
       <c r="Y211" s="1" t="n"/>
       <c r="Z211" s="1" t="n"/>
     </row>
-    <row r="212" ht="14.25" customHeight="1" s="84">
+    <row r="212" ht="14.25" customHeight="1" s="90">
       <c r="A212" s="1" t="n"/>
       <c r="B212" s="1" t="n"/>
       <c r="C212" s="1" t="n"/>
@@ -29168,7 +29182,7 @@
       <c r="Y212" s="1" t="n"/>
       <c r="Z212" s="1" t="n"/>
     </row>
-    <row r="213" ht="14.25" customHeight="1" s="84">
+    <row r="213" ht="14.25" customHeight="1" s="90">
       <c r="A213" s="1" t="n"/>
       <c r="B213" s="1" t="n"/>
       <c r="C213" s="1" t="n"/>
@@ -29196,7 +29210,7 @@
       <c r="Y213" s="1" t="n"/>
       <c r="Z213" s="1" t="n"/>
     </row>
-    <row r="214" ht="14.25" customHeight="1" s="84">
+    <row r="214" ht="14.25" customHeight="1" s="90">
       <c r="A214" s="1" t="n"/>
       <c r="B214" s="1" t="n"/>
       <c r="C214" s="1" t="n"/>
@@ -29224,7 +29238,7 @@
       <c r="Y214" s="1" t="n"/>
       <c r="Z214" s="1" t="n"/>
     </row>
-    <row r="215" ht="14.25" customHeight="1" s="84">
+    <row r="215" ht="14.25" customHeight="1" s="90">
       <c r="A215" s="1" t="n"/>
       <c r="B215" s="1" t="n"/>
       <c r="C215" s="1" t="n"/>
@@ -29252,7 +29266,7 @@
       <c r="Y215" s="1" t="n"/>
       <c r="Z215" s="1" t="n"/>
     </row>
-    <row r="216" ht="14.25" customHeight="1" s="84">
+    <row r="216" ht="14.25" customHeight="1" s="90">
       <c r="A216" s="1" t="n"/>
       <c r="B216" s="1" t="n"/>
       <c r="C216" s="1" t="n"/>
@@ -29280,7 +29294,7 @@
       <c r="Y216" s="1" t="n"/>
       <c r="Z216" s="1" t="n"/>
     </row>
-    <row r="217" ht="14.25" customHeight="1" s="84">
+    <row r="217" ht="14.25" customHeight="1" s="90">
       <c r="A217" s="1" t="n"/>
       <c r="B217" s="1" t="n"/>
       <c r="C217" s="1" t="n"/>
@@ -29308,7 +29322,7 @@
       <c r="Y217" s="1" t="n"/>
       <c r="Z217" s="1" t="n"/>
     </row>
-    <row r="218" ht="14.25" customHeight="1" s="84">
+    <row r="218" ht="14.25" customHeight="1" s="90">
       <c r="A218" s="1" t="n"/>
       <c r="B218" s="1" t="n"/>
       <c r="C218" s="1" t="n"/>
@@ -29336,7 +29350,7 @@
       <c r="Y218" s="1" t="n"/>
       <c r="Z218" s="1" t="n"/>
     </row>
-    <row r="219" ht="14.25" customHeight="1" s="84">
+    <row r="219" ht="14.25" customHeight="1" s="90">
       <c r="A219" s="1" t="n"/>
       <c r="B219" s="1" t="n"/>
       <c r="C219" s="1" t="n"/>
@@ -29364,7 +29378,7 @@
       <c r="Y219" s="1" t="n"/>
       <c r="Z219" s="1" t="n"/>
     </row>
-    <row r="220" ht="14.25" customHeight="1" s="84">
+    <row r="220" ht="14.25" customHeight="1" s="90">
       <c r="A220" s="1" t="n"/>
       <c r="B220" s="1" t="n"/>
       <c r="C220" s="1" t="n"/>
@@ -29392,786 +29406,786 @@
       <c r="Y220" s="1" t="n"/>
       <c r="Z220" s="1" t="n"/>
     </row>
-    <row r="221" ht="14.25" customHeight="1" s="84"/>
-    <row r="222" ht="14.25" customHeight="1" s="84"/>
-    <row r="223" ht="14.25" customHeight="1" s="84"/>
-    <row r="224" ht="14.25" customHeight="1" s="84"/>
-    <row r="225" ht="14.25" customHeight="1" s="84"/>
-    <row r="226" ht="14.25" customHeight="1" s="84"/>
-    <row r="227" ht="14.25" customHeight="1" s="84"/>
-    <row r="228" ht="14.25" customHeight="1" s="84"/>
-    <row r="229" ht="14.25" customHeight="1" s="84"/>
-    <row r="230" ht="14.25" customHeight="1" s="84"/>
-    <row r="231" ht="14.25" customHeight="1" s="84"/>
-    <row r="232" ht="14.25" customHeight="1" s="84"/>
-    <row r="233" ht="14.25" customHeight="1" s="84"/>
-    <row r="234" ht="14.25" customHeight="1" s="84"/>
-    <row r="235" ht="14.25" customHeight="1" s="84"/>
-    <row r="236" ht="14.25" customHeight="1" s="84"/>
-    <row r="237" ht="14.25" customHeight="1" s="84"/>
-    <row r="238" ht="14.25" customHeight="1" s="84"/>
-    <row r="239" ht="14.25" customHeight="1" s="84"/>
-    <row r="240" ht="14.25" customHeight="1" s="84"/>
-    <row r="241" ht="14.25" customHeight="1" s="84"/>
-    <row r="242" ht="14.25" customHeight="1" s="84"/>
-    <row r="243" ht="14.25" customHeight="1" s="84"/>
-    <row r="244" ht="14.25" customHeight="1" s="84"/>
-    <row r="245" ht="14.25" customHeight="1" s="84"/>
-    <row r="246" ht="14.25" customHeight="1" s="84"/>
-    <row r="247" ht="14.25" customHeight="1" s="84"/>
-    <row r="248" ht="14.25" customHeight="1" s="84"/>
-    <row r="249" ht="14.25" customHeight="1" s="84"/>
-    <row r="250" ht="14.25" customHeight="1" s="84"/>
-    <row r="251" ht="14.25" customHeight="1" s="84"/>
-    <row r="252" ht="14.25" customHeight="1" s="84"/>
-    <row r="253" ht="14.25" customHeight="1" s="84"/>
-    <row r="254" ht="14.25" customHeight="1" s="84"/>
-    <row r="255" ht="14.25" customHeight="1" s="84"/>
-    <row r="256" ht="14.25" customHeight="1" s="84"/>
-    <row r="257" ht="14.25" customHeight="1" s="84"/>
-    <row r="258" ht="14.25" customHeight="1" s="84"/>
-    <row r="259" ht="14.25" customHeight="1" s="84"/>
-    <row r="260" ht="14.25" customHeight="1" s="84"/>
-    <row r="261" ht="14.25" customHeight="1" s="84"/>
-    <row r="262" ht="14.25" customHeight="1" s="84"/>
-    <row r="263" ht="14.25" customHeight="1" s="84"/>
-    <row r="264" ht="14.25" customHeight="1" s="84"/>
-    <row r="265" ht="14.25" customHeight="1" s="84"/>
-    <row r="266" ht="14.25" customHeight="1" s="84"/>
-    <row r="267" ht="14.25" customHeight="1" s="84"/>
-    <row r="268" ht="14.25" customHeight="1" s="84"/>
-    <row r="269" ht="14.25" customHeight="1" s="84"/>
-    <row r="270" ht="14.25" customHeight="1" s="84"/>
-    <row r="271" ht="14.25" customHeight="1" s="84"/>
-    <row r="272" ht="14.25" customHeight="1" s="84"/>
-    <row r="273" ht="14.25" customHeight="1" s="84"/>
-    <row r="274" ht="14.25" customHeight="1" s="84"/>
-    <row r="275" ht="14.25" customHeight="1" s="84"/>
-    <row r="276" ht="14.25" customHeight="1" s="84"/>
-    <row r="277" ht="14.25" customHeight="1" s="84"/>
-    <row r="278" ht="14.25" customHeight="1" s="84"/>
-    <row r="279" ht="14.25" customHeight="1" s="84"/>
-    <row r="280" ht="14.25" customHeight="1" s="84"/>
-    <row r="281" ht="14.25" customHeight="1" s="84"/>
-    <row r="282" ht="14.25" customHeight="1" s="84"/>
-    <row r="283" ht="14.25" customHeight="1" s="84"/>
-    <row r="284" ht="14.25" customHeight="1" s="84"/>
-    <row r="285" ht="14.25" customHeight="1" s="84"/>
-    <row r="286" ht="14.25" customHeight="1" s="84"/>
-    <row r="287" ht="14.25" customHeight="1" s="84"/>
-    <row r="288" ht="14.25" customHeight="1" s="84"/>
-    <row r="289" ht="14.25" customHeight="1" s="84"/>
-    <row r="290" ht="14.25" customHeight="1" s="84"/>
-    <row r="291" ht="14.25" customHeight="1" s="84"/>
-    <row r="292" ht="14.25" customHeight="1" s="84"/>
-    <row r="293" ht="14.25" customHeight="1" s="84"/>
-    <row r="294" ht="14.25" customHeight="1" s="84"/>
-    <row r="295" ht="14.25" customHeight="1" s="84"/>
-    <row r="296" ht="14.25" customHeight="1" s="84"/>
-    <row r="297" ht="14.25" customHeight="1" s="84"/>
-    <row r="298" ht="14.25" customHeight="1" s="84"/>
-    <row r="299" ht="14.25" customHeight="1" s="84"/>
-    <row r="300" ht="14.25" customHeight="1" s="84"/>
-    <row r="301" ht="14.25" customHeight="1" s="84"/>
-    <row r="302" ht="14.25" customHeight="1" s="84"/>
-    <row r="303" ht="14.25" customHeight="1" s="84"/>
-    <row r="304" ht="14.25" customHeight="1" s="84"/>
-    <row r="305" ht="14.25" customHeight="1" s="84"/>
-    <row r="306" ht="14.25" customHeight="1" s="84"/>
-    <row r="307" ht="14.25" customHeight="1" s="84"/>
-    <row r="308" ht="14.25" customHeight="1" s="84"/>
-    <row r="309" ht="14.25" customHeight="1" s="84"/>
-    <row r="310" ht="14.25" customHeight="1" s="84"/>
-    <row r="311" ht="14.25" customHeight="1" s="84"/>
-    <row r="312" ht="14.25" customHeight="1" s="84"/>
-    <row r="313" ht="14.25" customHeight="1" s="84"/>
-    <row r="314" ht="14.25" customHeight="1" s="84"/>
-    <row r="315" ht="14.25" customHeight="1" s="84"/>
-    <row r="316" ht="14.25" customHeight="1" s="84"/>
-    <row r="317" ht="14.25" customHeight="1" s="84"/>
-    <row r="318" ht="14.25" customHeight="1" s="84"/>
-    <row r="319" ht="14.25" customHeight="1" s="84"/>
-    <row r="320" ht="14.25" customHeight="1" s="84"/>
-    <row r="321" ht="14.25" customHeight="1" s="84"/>
-    <row r="322" ht="14.25" customHeight="1" s="84"/>
-    <row r="323" ht="14.25" customHeight="1" s="84"/>
-    <row r="324" ht="14.25" customHeight="1" s="84"/>
-    <row r="325" ht="14.25" customHeight="1" s="84"/>
-    <row r="326" ht="14.25" customHeight="1" s="84"/>
-    <row r="327" ht="14.25" customHeight="1" s="84"/>
-    <row r="328" ht="14.25" customHeight="1" s="84"/>
-    <row r="329" ht="14.25" customHeight="1" s="84"/>
-    <row r="330" ht="14.25" customHeight="1" s="84"/>
-    <row r="331" ht="14.25" customHeight="1" s="84"/>
-    <row r="332" ht="14.25" customHeight="1" s="84"/>
-    <row r="333" ht="14.25" customHeight="1" s="84"/>
-    <row r="334" ht="14.25" customHeight="1" s="84"/>
-    <row r="335" ht="14.25" customHeight="1" s="84"/>
-    <row r="336" ht="14.25" customHeight="1" s="84"/>
-    <row r="337" ht="14.25" customHeight="1" s="84"/>
-    <row r="338" ht="14.25" customHeight="1" s="84"/>
-    <row r="339" ht="14.25" customHeight="1" s="84"/>
-    <row r="340" ht="14.25" customHeight="1" s="84"/>
-    <row r="341" ht="14.25" customHeight="1" s="84"/>
-    <row r="342" ht="14.25" customHeight="1" s="84"/>
-    <row r="343" ht="14.25" customHeight="1" s="84"/>
-    <row r="344" ht="14.25" customHeight="1" s="84"/>
-    <row r="345" ht="14.25" customHeight="1" s="84"/>
-    <row r="346" ht="14.25" customHeight="1" s="84"/>
-    <row r="347" ht="14.25" customHeight="1" s="84"/>
-    <row r="348" ht="14.25" customHeight="1" s="84"/>
-    <row r="349" ht="14.25" customHeight="1" s="84"/>
-    <row r="350" ht="14.25" customHeight="1" s="84"/>
-    <row r="351" ht="14.25" customHeight="1" s="84"/>
-    <row r="352" ht="14.25" customHeight="1" s="84"/>
-    <row r="353" ht="14.25" customHeight="1" s="84"/>
-    <row r="354" ht="14.25" customHeight="1" s="84"/>
-    <row r="355" ht="14.25" customHeight="1" s="84"/>
-    <row r="356" ht="14.25" customHeight="1" s="84"/>
-    <row r="357" ht="14.25" customHeight="1" s="84"/>
-    <row r="358" ht="14.25" customHeight="1" s="84"/>
-    <row r="359" ht="14.25" customHeight="1" s="84"/>
-    <row r="360" ht="14.25" customHeight="1" s="84"/>
-    <row r="361" ht="14.25" customHeight="1" s="84"/>
-    <row r="362" ht="14.25" customHeight="1" s="84"/>
-    <row r="363" ht="14.25" customHeight="1" s="84"/>
-    <row r="364" ht="14.25" customHeight="1" s="84"/>
-    <row r="365" ht="14.25" customHeight="1" s="84"/>
-    <row r="366" ht="14.25" customHeight="1" s="84"/>
-    <row r="367" ht="14.25" customHeight="1" s="84"/>
-    <row r="368" ht="14.25" customHeight="1" s="84"/>
-    <row r="369" ht="14.25" customHeight="1" s="84"/>
-    <row r="370" ht="14.25" customHeight="1" s="84"/>
-    <row r="371" ht="14.25" customHeight="1" s="84"/>
-    <row r="372" ht="14.25" customHeight="1" s="84"/>
-    <row r="373" ht="14.25" customHeight="1" s="84"/>
-    <row r="374" ht="14.25" customHeight="1" s="84"/>
-    <row r="375" ht="14.25" customHeight="1" s="84"/>
-    <row r="376" ht="14.25" customHeight="1" s="84"/>
-    <row r="377" ht="14.25" customHeight="1" s="84"/>
-    <row r="378" ht="14.25" customHeight="1" s="84"/>
-    <row r="379" ht="14.25" customHeight="1" s="84"/>
-    <row r="380" ht="14.25" customHeight="1" s="84"/>
-    <row r="381" ht="14.25" customHeight="1" s="84"/>
-    <row r="382" ht="14.25" customHeight="1" s="84"/>
-    <row r="383" ht="14.25" customHeight="1" s="84"/>
-    <row r="384" ht="14.25" customHeight="1" s="84"/>
-    <row r="385" ht="14.25" customHeight="1" s="84"/>
-    <row r="386" ht="14.25" customHeight="1" s="84"/>
-    <row r="387" ht="14.25" customHeight="1" s="84"/>
-    <row r="388" ht="14.25" customHeight="1" s="84"/>
-    <row r="389" ht="14.25" customHeight="1" s="84"/>
-    <row r="390" ht="14.25" customHeight="1" s="84"/>
-    <row r="391" ht="14.25" customHeight="1" s="84"/>
-    <row r="392" ht="14.25" customHeight="1" s="84"/>
-    <row r="393" ht="14.25" customHeight="1" s="84"/>
-    <row r="394" ht="14.25" customHeight="1" s="84"/>
-    <row r="395" ht="14.25" customHeight="1" s="84"/>
-    <row r="396" ht="14.25" customHeight="1" s="84"/>
-    <row r="397" ht="14.25" customHeight="1" s="84"/>
-    <row r="398" ht="14.25" customHeight="1" s="84"/>
-    <row r="399" ht="14.25" customHeight="1" s="84"/>
-    <row r="400" ht="14.25" customHeight="1" s="84"/>
-    <row r="401" ht="14.25" customHeight="1" s="84"/>
-    <row r="402" ht="14.25" customHeight="1" s="84"/>
-    <row r="403" ht="14.25" customHeight="1" s="84"/>
-    <row r="404" ht="14.25" customHeight="1" s="84"/>
-    <row r="405" ht="14.25" customHeight="1" s="84"/>
-    <row r="406" ht="14.25" customHeight="1" s="84"/>
-    <row r="407" ht="14.25" customHeight="1" s="84"/>
-    <row r="408" ht="14.25" customHeight="1" s="84"/>
-    <row r="409" ht="14.25" customHeight="1" s="84"/>
-    <row r="410" ht="14.25" customHeight="1" s="84"/>
-    <row r="411" ht="14.25" customHeight="1" s="84"/>
-    <row r="412" ht="14.25" customHeight="1" s="84"/>
-    <row r="413" ht="14.25" customHeight="1" s="84"/>
-    <row r="414" ht="14.25" customHeight="1" s="84"/>
-    <row r="415" ht="14.25" customHeight="1" s="84"/>
-    <row r="416" ht="14.25" customHeight="1" s="84"/>
-    <row r="417" ht="14.25" customHeight="1" s="84"/>
-    <row r="418" ht="14.25" customHeight="1" s="84"/>
-    <row r="419" ht="14.25" customHeight="1" s="84"/>
-    <row r="420" ht="14.25" customHeight="1" s="84"/>
-    <row r="421" ht="14.25" customHeight="1" s="84"/>
-    <row r="422" ht="14.25" customHeight="1" s="84"/>
-    <row r="423" ht="14.25" customHeight="1" s="84"/>
-    <row r="424" ht="14.25" customHeight="1" s="84"/>
-    <row r="425" ht="14.25" customHeight="1" s="84"/>
-    <row r="426" ht="14.25" customHeight="1" s="84"/>
-    <row r="427" ht="14.25" customHeight="1" s="84"/>
-    <row r="428" ht="14.25" customHeight="1" s="84"/>
-    <row r="429" ht="14.25" customHeight="1" s="84"/>
-    <row r="430" ht="14.25" customHeight="1" s="84"/>
-    <row r="431" ht="14.25" customHeight="1" s="84"/>
-    <row r="432" ht="14.25" customHeight="1" s="84"/>
-    <row r="433" ht="14.25" customHeight="1" s="84"/>
-    <row r="434" ht="14.25" customHeight="1" s="84"/>
-    <row r="435" ht="14.25" customHeight="1" s="84"/>
-    <row r="436" ht="14.25" customHeight="1" s="84"/>
-    <row r="437" ht="14.25" customHeight="1" s="84"/>
-    <row r="438" ht="14.25" customHeight="1" s="84"/>
-    <row r="439" ht="14.25" customHeight="1" s="84"/>
-    <row r="440" ht="14.25" customHeight="1" s="84"/>
-    <row r="441" ht="14.25" customHeight="1" s="84"/>
-    <row r="442" ht="14.25" customHeight="1" s="84"/>
-    <row r="443" ht="14.25" customHeight="1" s="84"/>
-    <row r="444" ht="14.25" customHeight="1" s="84"/>
-    <row r="445" ht="14.25" customHeight="1" s="84"/>
-    <row r="446" ht="14.25" customHeight="1" s="84"/>
-    <row r="447" ht="14.25" customHeight="1" s="84"/>
-    <row r="448" ht="14.25" customHeight="1" s="84"/>
-    <row r="449" ht="14.25" customHeight="1" s="84"/>
-    <row r="450" ht="14.25" customHeight="1" s="84"/>
-    <row r="451" ht="14.25" customHeight="1" s="84"/>
-    <row r="452" ht="14.25" customHeight="1" s="84"/>
-    <row r="453" ht="14.25" customHeight="1" s="84"/>
-    <row r="454" ht="14.25" customHeight="1" s="84"/>
-    <row r="455" ht="14.25" customHeight="1" s="84"/>
-    <row r="456" ht="14.25" customHeight="1" s="84"/>
-    <row r="457" ht="14.25" customHeight="1" s="84"/>
-    <row r="458" ht="14.25" customHeight="1" s="84"/>
-    <row r="459" ht="14.25" customHeight="1" s="84"/>
-    <row r="460" ht="14.25" customHeight="1" s="84"/>
-    <row r="461" ht="14.25" customHeight="1" s="84"/>
-    <row r="462" ht="14.25" customHeight="1" s="84"/>
-    <row r="463" ht="14.25" customHeight="1" s="84"/>
-    <row r="464" ht="14.25" customHeight="1" s="84"/>
-    <row r="465" ht="14.25" customHeight="1" s="84"/>
-    <row r="466" ht="14.25" customHeight="1" s="84"/>
-    <row r="467" ht="14.25" customHeight="1" s="84"/>
-    <row r="468" ht="14.25" customHeight="1" s="84"/>
-    <row r="469" ht="14.25" customHeight="1" s="84"/>
-    <row r="470" ht="14.25" customHeight="1" s="84"/>
-    <row r="471" ht="14.25" customHeight="1" s="84"/>
-    <row r="472" ht="14.25" customHeight="1" s="84"/>
-    <row r="473" ht="14.25" customHeight="1" s="84"/>
-    <row r="474" ht="14.25" customHeight="1" s="84"/>
-    <row r="475" ht="14.25" customHeight="1" s="84"/>
-    <row r="476" ht="14.25" customHeight="1" s="84"/>
-    <row r="477" ht="14.25" customHeight="1" s="84"/>
-    <row r="478" ht="14.25" customHeight="1" s="84"/>
-    <row r="479" ht="14.25" customHeight="1" s="84"/>
-    <row r="480" ht="14.25" customHeight="1" s="84"/>
-    <row r="481" ht="14.25" customHeight="1" s="84"/>
-    <row r="482" ht="14.25" customHeight="1" s="84"/>
-    <row r="483" ht="14.25" customHeight="1" s="84"/>
-    <row r="484" ht="14.25" customHeight="1" s="84"/>
-    <row r="485" ht="14.25" customHeight="1" s="84"/>
-    <row r="486" ht="14.25" customHeight="1" s="84"/>
-    <row r="487" ht="14.25" customHeight="1" s="84"/>
-    <row r="488" ht="14.25" customHeight="1" s="84"/>
-    <row r="489" ht="14.25" customHeight="1" s="84"/>
-    <row r="490" ht="14.25" customHeight="1" s="84"/>
-    <row r="491" ht="14.25" customHeight="1" s="84"/>
-    <row r="492" ht="14.25" customHeight="1" s="84"/>
-    <row r="493" ht="14.25" customHeight="1" s="84"/>
-    <row r="494" ht="14.25" customHeight="1" s="84"/>
-    <row r="495" ht="14.25" customHeight="1" s="84"/>
-    <row r="496" ht="14.25" customHeight="1" s="84"/>
-    <row r="497" ht="14.25" customHeight="1" s="84"/>
-    <row r="498" ht="14.25" customHeight="1" s="84"/>
-    <row r="499" ht="14.25" customHeight="1" s="84"/>
-    <row r="500" ht="14.25" customHeight="1" s="84"/>
-    <row r="501" ht="14.25" customHeight="1" s="84"/>
-    <row r="502" ht="14.25" customHeight="1" s="84"/>
-    <row r="503" ht="14.25" customHeight="1" s="84"/>
-    <row r="504" ht="14.25" customHeight="1" s="84"/>
-    <row r="505" ht="14.25" customHeight="1" s="84"/>
-    <row r="506" ht="14.25" customHeight="1" s="84"/>
-    <row r="507" ht="14.25" customHeight="1" s="84"/>
-    <row r="508" ht="14.25" customHeight="1" s="84"/>
-    <row r="509" ht="14.25" customHeight="1" s="84"/>
-    <row r="510" ht="14.25" customHeight="1" s="84"/>
-    <row r="511" ht="14.25" customHeight="1" s="84"/>
-    <row r="512" ht="14.25" customHeight="1" s="84"/>
-    <row r="513" ht="14.25" customHeight="1" s="84"/>
-    <row r="514" ht="14.25" customHeight="1" s="84"/>
-    <row r="515" ht="14.25" customHeight="1" s="84"/>
-    <row r="516" ht="14.25" customHeight="1" s="84"/>
-    <row r="517" ht="14.25" customHeight="1" s="84"/>
-    <row r="518" ht="14.25" customHeight="1" s="84"/>
-    <row r="519" ht="14.25" customHeight="1" s="84"/>
-    <row r="520" ht="14.25" customHeight="1" s="84"/>
-    <row r="521" ht="14.25" customHeight="1" s="84"/>
-    <row r="522" ht="14.25" customHeight="1" s="84"/>
-    <row r="523" ht="14.25" customHeight="1" s="84"/>
-    <row r="524" ht="14.25" customHeight="1" s="84"/>
-    <row r="525" ht="14.25" customHeight="1" s="84"/>
-    <row r="526" ht="14.25" customHeight="1" s="84"/>
-    <row r="527" ht="14.25" customHeight="1" s="84"/>
-    <row r="528" ht="14.25" customHeight="1" s="84"/>
-    <row r="529" ht="14.25" customHeight="1" s="84"/>
-    <row r="530" ht="14.25" customHeight="1" s="84"/>
-    <row r="531" ht="14.25" customHeight="1" s="84"/>
-    <row r="532" ht="14.25" customHeight="1" s="84"/>
-    <row r="533" ht="14.25" customHeight="1" s="84"/>
-    <row r="534" ht="14.25" customHeight="1" s="84"/>
-    <row r="535" ht="14.25" customHeight="1" s="84"/>
-    <row r="536" ht="14.25" customHeight="1" s="84"/>
-    <row r="537" ht="14.25" customHeight="1" s="84"/>
-    <row r="538" ht="14.25" customHeight="1" s="84"/>
-    <row r="539" ht="14.25" customHeight="1" s="84"/>
-    <row r="540" ht="14.25" customHeight="1" s="84"/>
-    <row r="541" ht="14.25" customHeight="1" s="84"/>
-    <row r="542" ht="14.25" customHeight="1" s="84"/>
-    <row r="543" ht="14.25" customHeight="1" s="84"/>
-    <row r="544" ht="14.25" customHeight="1" s="84"/>
-    <row r="545" ht="14.25" customHeight="1" s="84"/>
-    <row r="546" ht="14.25" customHeight="1" s="84"/>
-    <row r="547" ht="14.25" customHeight="1" s="84"/>
-    <row r="548" ht="14.25" customHeight="1" s="84"/>
-    <row r="549" ht="14.25" customHeight="1" s="84"/>
-    <row r="550" ht="14.25" customHeight="1" s="84"/>
-    <row r="551" ht="14.25" customHeight="1" s="84"/>
-    <row r="552" ht="14.25" customHeight="1" s="84"/>
-    <row r="553" ht="14.25" customHeight="1" s="84"/>
-    <row r="554" ht="14.25" customHeight="1" s="84"/>
-    <row r="555" ht="14.25" customHeight="1" s="84"/>
-    <row r="556" ht="14.25" customHeight="1" s="84"/>
-    <row r="557" ht="14.25" customHeight="1" s="84"/>
-    <row r="558" ht="14.25" customHeight="1" s="84"/>
-    <row r="559" ht="14.25" customHeight="1" s="84"/>
-    <row r="560" ht="14.25" customHeight="1" s="84"/>
-    <row r="561" ht="14.25" customHeight="1" s="84"/>
-    <row r="562" ht="14.25" customHeight="1" s="84"/>
-    <row r="563" ht="14.25" customHeight="1" s="84"/>
-    <row r="564" ht="14.25" customHeight="1" s="84"/>
-    <row r="565" ht="14.25" customHeight="1" s="84"/>
-    <row r="566" ht="14.25" customHeight="1" s="84"/>
-    <row r="567" ht="14.25" customHeight="1" s="84"/>
-    <row r="568" ht="14.25" customHeight="1" s="84"/>
-    <row r="569" ht="14.25" customHeight="1" s="84"/>
-    <row r="570" ht="14.25" customHeight="1" s="84"/>
-    <row r="571" ht="14.25" customHeight="1" s="84"/>
-    <row r="572" ht="14.25" customHeight="1" s="84"/>
-    <row r="573" ht="14.25" customHeight="1" s="84"/>
-    <row r="574" ht="14.25" customHeight="1" s="84"/>
-    <row r="575" ht="14.25" customHeight="1" s="84"/>
-    <row r="576" ht="14.25" customHeight="1" s="84"/>
-    <row r="577" ht="14.25" customHeight="1" s="84"/>
-    <row r="578" ht="14.25" customHeight="1" s="84"/>
-    <row r="579" ht="14.25" customHeight="1" s="84"/>
-    <row r="580" ht="14.25" customHeight="1" s="84"/>
-    <row r="581" ht="14.25" customHeight="1" s="84"/>
-    <row r="582" ht="14.25" customHeight="1" s="84"/>
-    <row r="583" ht="14.25" customHeight="1" s="84"/>
-    <row r="584" ht="14.25" customHeight="1" s="84"/>
-    <row r="585" ht="14.25" customHeight="1" s="84"/>
-    <row r="586" ht="14.25" customHeight="1" s="84"/>
-    <row r="587" ht="14.25" customHeight="1" s="84"/>
-    <row r="588" ht="14.25" customHeight="1" s="84"/>
-    <row r="589" ht="14.25" customHeight="1" s="84"/>
-    <row r="590" ht="14.25" customHeight="1" s="84"/>
-    <row r="591" ht="14.25" customHeight="1" s="84"/>
-    <row r="592" ht="14.25" customHeight="1" s="84"/>
-    <row r="593" ht="14.25" customHeight="1" s="84"/>
-    <row r="594" ht="14.25" customHeight="1" s="84"/>
-    <row r="595" ht="14.25" customHeight="1" s="84"/>
-    <row r="596" ht="14.25" customHeight="1" s="84"/>
-    <row r="597" ht="14.25" customHeight="1" s="84"/>
-    <row r="598" ht="14.25" customHeight="1" s="84"/>
-    <row r="599" ht="14.25" customHeight="1" s="84"/>
-    <row r="600" ht="14.25" customHeight="1" s="84"/>
-    <row r="601" ht="14.25" customHeight="1" s="84"/>
-    <row r="602" ht="14.25" customHeight="1" s="84"/>
-    <row r="603" ht="14.25" customHeight="1" s="84"/>
-    <row r="604" ht="14.25" customHeight="1" s="84"/>
-    <row r="605" ht="14.25" customHeight="1" s="84"/>
-    <row r="606" ht="14.25" customHeight="1" s="84"/>
-    <row r="607" ht="14.25" customHeight="1" s="84"/>
-    <row r="608" ht="14.25" customHeight="1" s="84"/>
-    <row r="609" ht="14.25" customHeight="1" s="84"/>
-    <row r="610" ht="14.25" customHeight="1" s="84"/>
-    <row r="611" ht="14.25" customHeight="1" s="84"/>
-    <row r="612" ht="14.25" customHeight="1" s="84"/>
-    <row r="613" ht="14.25" customHeight="1" s="84"/>
-    <row r="614" ht="14.25" customHeight="1" s="84"/>
-    <row r="615" ht="14.25" customHeight="1" s="84"/>
-    <row r="616" ht="14.25" customHeight="1" s="84"/>
-    <row r="617" ht="14.25" customHeight="1" s="84"/>
-    <row r="618" ht="14.25" customHeight="1" s="84"/>
-    <row r="619" ht="14.25" customHeight="1" s="84"/>
-    <row r="620" ht="14.25" customHeight="1" s="84"/>
-    <row r="621" ht="14.25" customHeight="1" s="84"/>
-    <row r="622" ht="14.25" customHeight="1" s="84"/>
-    <row r="623" ht="14.25" customHeight="1" s="84"/>
-    <row r="624" ht="14.25" customHeight="1" s="84"/>
-    <row r="625" ht="14.25" customHeight="1" s="84"/>
-    <row r="626" ht="14.25" customHeight="1" s="84"/>
-    <row r="627" ht="14.25" customHeight="1" s="84"/>
-    <row r="628" ht="14.25" customHeight="1" s="84"/>
-    <row r="629" ht="14.25" customHeight="1" s="84"/>
-    <row r="630" ht="14.25" customHeight="1" s="84"/>
-    <row r="631" ht="14.25" customHeight="1" s="84"/>
-    <row r="632" ht="14.25" customHeight="1" s="84"/>
-    <row r="633" ht="14.25" customHeight="1" s="84"/>
-    <row r="634" ht="14.25" customHeight="1" s="84"/>
-    <row r="635" ht="14.25" customHeight="1" s="84"/>
-    <row r="636" ht="14.25" customHeight="1" s="84"/>
-    <row r="637" ht="14.25" customHeight="1" s="84"/>
-    <row r="638" ht="14.25" customHeight="1" s="84"/>
-    <row r="639" ht="14.25" customHeight="1" s="84"/>
-    <row r="640" ht="14.25" customHeight="1" s="84"/>
-    <row r="641" ht="14.25" customHeight="1" s="84"/>
-    <row r="642" ht="14.25" customHeight="1" s="84"/>
-    <row r="643" ht="14.25" customHeight="1" s="84"/>
-    <row r="644" ht="14.25" customHeight="1" s="84"/>
-    <row r="645" ht="14.25" customHeight="1" s="84"/>
-    <row r="646" ht="14.25" customHeight="1" s="84"/>
-    <row r="647" ht="14.25" customHeight="1" s="84"/>
-    <row r="648" ht="14.25" customHeight="1" s="84"/>
-    <row r="649" ht="14.25" customHeight="1" s="84"/>
-    <row r="650" ht="14.25" customHeight="1" s="84"/>
-    <row r="651" ht="14.25" customHeight="1" s="84"/>
-    <row r="652" ht="14.25" customHeight="1" s="84"/>
-    <row r="653" ht="14.25" customHeight="1" s="84"/>
-    <row r="654" ht="14.25" customHeight="1" s="84"/>
-    <row r="655" ht="14.25" customHeight="1" s="84"/>
-    <row r="656" ht="14.25" customHeight="1" s="84"/>
-    <row r="657" ht="14.25" customHeight="1" s="84"/>
-    <row r="658" ht="14.25" customHeight="1" s="84"/>
-    <row r="659" ht="14.25" customHeight="1" s="84"/>
-    <row r="660" ht="14.25" customHeight="1" s="84"/>
-    <row r="661" ht="14.25" customHeight="1" s="84"/>
-    <row r="662" ht="14.25" customHeight="1" s="84"/>
-    <row r="663" ht="14.25" customHeight="1" s="84"/>
-    <row r="664" ht="14.25" customHeight="1" s="84"/>
-    <row r="665" ht="14.25" customHeight="1" s="84"/>
-    <row r="666" ht="14.25" customHeight="1" s="84"/>
-    <row r="667" ht="14.25" customHeight="1" s="84"/>
-    <row r="668" ht="14.25" customHeight="1" s="84"/>
-    <row r="669" ht="14.25" customHeight="1" s="84"/>
-    <row r="670" ht="14.25" customHeight="1" s="84"/>
-    <row r="671" ht="14.25" customHeight="1" s="84"/>
-    <row r="672" ht="14.25" customHeight="1" s="84"/>
-    <row r="673" ht="14.25" customHeight="1" s="84"/>
-    <row r="674" ht="14.25" customHeight="1" s="84"/>
-    <row r="675" ht="14.25" customHeight="1" s="84"/>
-    <row r="676" ht="14.25" customHeight="1" s="84"/>
-    <row r="677" ht="14.25" customHeight="1" s="84"/>
-    <row r="678" ht="14.25" customHeight="1" s="84"/>
-    <row r="679" ht="14.25" customHeight="1" s="84"/>
-    <row r="680" ht="14.25" customHeight="1" s="84"/>
-    <row r="681" ht="14.25" customHeight="1" s="84"/>
-    <row r="682" ht="14.25" customHeight="1" s="84"/>
-    <row r="683" ht="14.25" customHeight="1" s="84"/>
-    <row r="684" ht="14.25" customHeight="1" s="84"/>
-    <row r="685" ht="14.25" customHeight="1" s="84"/>
-    <row r="686" ht="14.25" customHeight="1" s="84"/>
-    <row r="687" ht="14.25" customHeight="1" s="84"/>
-    <row r="688" ht="14.25" customHeight="1" s="84"/>
-    <row r="689" ht="14.25" customHeight="1" s="84"/>
-    <row r="690" ht="14.25" customHeight="1" s="84"/>
-    <row r="691" ht="14.25" customHeight="1" s="84"/>
-    <row r="692" ht="14.25" customHeight="1" s="84"/>
-    <row r="693" ht="14.25" customHeight="1" s="84"/>
-    <row r="694" ht="14.25" customHeight="1" s="84"/>
-    <row r="695" ht="14.25" customHeight="1" s="84"/>
-    <row r="696" ht="14.25" customHeight="1" s="84"/>
-    <row r="697" ht="14.25" customHeight="1" s="84"/>
-    <row r="698" ht="14.25" customHeight="1" s="84"/>
-    <row r="699" ht="14.25" customHeight="1" s="84"/>
-    <row r="700" ht="14.25" customHeight="1" s="84"/>
-    <row r="701" ht="14.25" customHeight="1" s="84"/>
-    <row r="702" ht="14.25" customHeight="1" s="84"/>
-    <row r="703" ht="14.25" customHeight="1" s="84"/>
-    <row r="704" ht="14.25" customHeight="1" s="84"/>
-    <row r="705" ht="14.25" customHeight="1" s="84"/>
-    <row r="706" ht="14.25" customHeight="1" s="84"/>
-    <row r="707" ht="14.25" customHeight="1" s="84"/>
-    <row r="708" ht="14.25" customHeight="1" s="84"/>
-    <row r="709" ht="14.25" customHeight="1" s="84"/>
-    <row r="710" ht="14.25" customHeight="1" s="84"/>
-    <row r="711" ht="14.25" customHeight="1" s="84"/>
-    <row r="712" ht="14.25" customHeight="1" s="84"/>
-    <row r="713" ht="14.25" customHeight="1" s="84"/>
-    <row r="714" ht="14.25" customHeight="1" s="84"/>
-    <row r="715" ht="14.25" customHeight="1" s="84"/>
-    <row r="716" ht="14.25" customHeight="1" s="84"/>
-    <row r="717" ht="14.25" customHeight="1" s="84"/>
-    <row r="718" ht="14.25" customHeight="1" s="84"/>
-    <row r="719" ht="14.25" customHeight="1" s="84"/>
-    <row r="720" ht="14.25" customHeight="1" s="84"/>
-    <row r="721" ht="14.25" customHeight="1" s="84"/>
-    <row r="722" ht="14.25" customHeight="1" s="84"/>
-    <row r="723" ht="14.25" customHeight="1" s="84"/>
-    <row r="724" ht="14.25" customHeight="1" s="84"/>
-    <row r="725" ht="14.25" customHeight="1" s="84"/>
-    <row r="726" ht="14.25" customHeight="1" s="84"/>
-    <row r="727" ht="14.25" customHeight="1" s="84"/>
-    <row r="728" ht="14.25" customHeight="1" s="84"/>
-    <row r="729" ht="14.25" customHeight="1" s="84"/>
-    <row r="730" ht="14.25" customHeight="1" s="84"/>
-    <row r="731" ht="14.25" customHeight="1" s="84"/>
-    <row r="732" ht="14.25" customHeight="1" s="84"/>
-    <row r="733" ht="14.25" customHeight="1" s="84"/>
-    <row r="734" ht="14.25" customHeight="1" s="84"/>
-    <row r="735" ht="14.25" customHeight="1" s="84"/>
-    <row r="736" ht="14.25" customHeight="1" s="84"/>
-    <row r="737" ht="14.25" customHeight="1" s="84"/>
-    <row r="738" ht="14.25" customHeight="1" s="84"/>
-    <row r="739" ht="14.25" customHeight="1" s="84"/>
-    <row r="740" ht="14.25" customHeight="1" s="84"/>
-    <row r="741" ht="14.25" customHeight="1" s="84"/>
-    <row r="742" ht="14.25" customHeight="1" s="84"/>
-    <row r="743" ht="14.25" customHeight="1" s="84"/>
-    <row r="744" ht="14.25" customHeight="1" s="84"/>
-    <row r="745" ht="14.25" customHeight="1" s="84"/>
-    <row r="746" ht="14.25" customHeight="1" s="84"/>
-    <row r="747" ht="14.25" customHeight="1" s="84"/>
-    <row r="748" ht="14.25" customHeight="1" s="84"/>
-    <row r="749" ht="14.25" customHeight="1" s="84"/>
-    <row r="750" ht="14.25" customHeight="1" s="84"/>
-    <row r="751" ht="14.25" customHeight="1" s="84"/>
-    <row r="752" ht="14.25" customHeight="1" s="84"/>
-    <row r="753" ht="14.25" customHeight="1" s="84"/>
-    <row r="754" ht="14.25" customHeight="1" s="84"/>
-    <row r="755" ht="14.25" customHeight="1" s="84"/>
-    <row r="756" ht="14.25" customHeight="1" s="84"/>
-    <row r="757" ht="14.25" customHeight="1" s="84"/>
-    <row r="758" ht="14.25" customHeight="1" s="84"/>
-    <row r="759" ht="14.25" customHeight="1" s="84"/>
-    <row r="760" ht="14.25" customHeight="1" s="84"/>
-    <row r="761" ht="14.25" customHeight="1" s="84"/>
-    <row r="762" ht="14.25" customHeight="1" s="84"/>
-    <row r="763" ht="14.25" customHeight="1" s="84"/>
-    <row r="764" ht="14.25" customHeight="1" s="84"/>
-    <row r="765" ht="14.25" customHeight="1" s="84"/>
-    <row r="766" ht="14.25" customHeight="1" s="84"/>
-    <row r="767" ht="14.25" customHeight="1" s="84"/>
-    <row r="768" ht="14.25" customHeight="1" s="84"/>
-    <row r="769" ht="14.25" customHeight="1" s="84"/>
-    <row r="770" ht="14.25" customHeight="1" s="84"/>
-    <row r="771" ht="14.25" customHeight="1" s="84"/>
-    <row r="772" ht="14.25" customHeight="1" s="84"/>
-    <row r="773" ht="14.25" customHeight="1" s="84"/>
-    <row r="774" ht="14.25" customHeight="1" s="84"/>
-    <row r="775" ht="14.25" customHeight="1" s="84"/>
-    <row r="776" ht="14.25" customHeight="1" s="84"/>
-    <row r="777" ht="14.25" customHeight="1" s="84"/>
-    <row r="778" ht="14.25" customHeight="1" s="84"/>
-    <row r="779" ht="14.25" customHeight="1" s="84"/>
-    <row r="780" ht="14.25" customHeight="1" s="84"/>
-    <row r="781" ht="14.25" customHeight="1" s="84"/>
-    <row r="782" ht="14.25" customHeight="1" s="84"/>
-    <row r="783" ht="14.25" customHeight="1" s="84"/>
-    <row r="784" ht="14.25" customHeight="1" s="84"/>
-    <row r="785" ht="14.25" customHeight="1" s="84"/>
-    <row r="786" ht="14.25" customHeight="1" s="84"/>
-    <row r="787" ht="14.25" customHeight="1" s="84"/>
-    <row r="788" ht="14.25" customHeight="1" s="84"/>
-    <row r="789" ht="14.25" customHeight="1" s="84"/>
-    <row r="790" ht="14.25" customHeight="1" s="84"/>
-    <row r="791" ht="14.25" customHeight="1" s="84"/>
-    <row r="792" ht="14.25" customHeight="1" s="84"/>
-    <row r="793" ht="14.25" customHeight="1" s="84"/>
-    <row r="794" ht="14.25" customHeight="1" s="84"/>
-    <row r="795" ht="14.25" customHeight="1" s="84"/>
-    <row r="796" ht="14.25" customHeight="1" s="84"/>
-    <row r="797" ht="14.25" customHeight="1" s="84"/>
-    <row r="798" ht="14.25" customHeight="1" s="84"/>
-    <row r="799" ht="14.25" customHeight="1" s="84"/>
-    <row r="800" ht="14.25" customHeight="1" s="84"/>
-    <row r="801" ht="14.25" customHeight="1" s="84"/>
-    <row r="802" ht="14.25" customHeight="1" s="84"/>
-    <row r="803" ht="14.25" customHeight="1" s="84"/>
-    <row r="804" ht="14.25" customHeight="1" s="84"/>
-    <row r="805" ht="14.25" customHeight="1" s="84"/>
-    <row r="806" ht="14.25" customHeight="1" s="84"/>
-    <row r="807" ht="14.25" customHeight="1" s="84"/>
-    <row r="808" ht="14.25" customHeight="1" s="84"/>
-    <row r="809" ht="14.25" customHeight="1" s="84"/>
-    <row r="810" ht="14.25" customHeight="1" s="84"/>
-    <row r="811" ht="14.25" customHeight="1" s="84"/>
-    <row r="812" ht="14.25" customHeight="1" s="84"/>
-    <row r="813" ht="14.25" customHeight="1" s="84"/>
-    <row r="814" ht="14.25" customHeight="1" s="84"/>
-    <row r="815" ht="14.25" customHeight="1" s="84"/>
-    <row r="816" ht="14.25" customHeight="1" s="84"/>
-    <row r="817" ht="14.25" customHeight="1" s="84"/>
-    <row r="818" ht="14.25" customHeight="1" s="84"/>
-    <row r="819" ht="14.25" customHeight="1" s="84"/>
-    <row r="820" ht="14.25" customHeight="1" s="84"/>
-    <row r="821" ht="14.25" customHeight="1" s="84"/>
-    <row r="822" ht="14.25" customHeight="1" s="84"/>
-    <row r="823" ht="14.25" customHeight="1" s="84"/>
-    <row r="824" ht="14.25" customHeight="1" s="84"/>
-    <row r="825" ht="14.25" customHeight="1" s="84"/>
-    <row r="826" ht="14.25" customHeight="1" s="84"/>
-    <row r="827" ht="14.25" customHeight="1" s="84"/>
-    <row r="828" ht="14.25" customHeight="1" s="84"/>
-    <row r="829" ht="14.25" customHeight="1" s="84"/>
-    <row r="830" ht="14.25" customHeight="1" s="84"/>
-    <row r="831" ht="14.25" customHeight="1" s="84"/>
-    <row r="832" ht="14.25" customHeight="1" s="84"/>
-    <row r="833" ht="14.25" customHeight="1" s="84"/>
-    <row r="834" ht="14.25" customHeight="1" s="84"/>
-    <row r="835" ht="14.25" customHeight="1" s="84"/>
-    <row r="836" ht="14.25" customHeight="1" s="84"/>
-    <row r="837" ht="14.25" customHeight="1" s="84"/>
-    <row r="838" ht="14.25" customHeight="1" s="84"/>
-    <row r="839" ht="14.25" customHeight="1" s="84"/>
-    <row r="840" ht="14.25" customHeight="1" s="84"/>
-    <row r="841" ht="14.25" customHeight="1" s="84"/>
-    <row r="842" ht="14.25" customHeight="1" s="84"/>
-    <row r="843" ht="14.25" customHeight="1" s="84"/>
-    <row r="844" ht="14.25" customHeight="1" s="84"/>
-    <row r="845" ht="14.25" customHeight="1" s="84"/>
-    <row r="846" ht="14.25" customHeight="1" s="84"/>
-    <row r="847" ht="14.25" customHeight="1" s="84"/>
-    <row r="848" ht="14.25" customHeight="1" s="84"/>
-    <row r="849" ht="14.25" customHeight="1" s="84"/>
-    <row r="850" ht="14.25" customHeight="1" s="84"/>
-    <row r="851" ht="14.25" customHeight="1" s="84"/>
-    <row r="852" ht="14.25" customHeight="1" s="84"/>
-    <row r="853" ht="14.25" customHeight="1" s="84"/>
-    <row r="854" ht="14.25" customHeight="1" s="84"/>
-    <row r="855" ht="14.25" customHeight="1" s="84"/>
-    <row r="856" ht="14.25" customHeight="1" s="84"/>
-    <row r="857" ht="14.25" customHeight="1" s="84"/>
-    <row r="858" ht="14.25" customHeight="1" s="84"/>
-    <row r="859" ht="14.25" customHeight="1" s="84"/>
-    <row r="860" ht="14.25" customHeight="1" s="84"/>
-    <row r="861" ht="14.25" customHeight="1" s="84"/>
-    <row r="862" ht="14.25" customHeight="1" s="84"/>
-    <row r="863" ht="14.25" customHeight="1" s="84"/>
-    <row r="864" ht="14.25" customHeight="1" s="84"/>
-    <row r="865" ht="14.25" customHeight="1" s="84"/>
-    <row r="866" ht="14.25" customHeight="1" s="84"/>
-    <row r="867" ht="14.25" customHeight="1" s="84"/>
-    <row r="868" ht="14.25" customHeight="1" s="84"/>
-    <row r="869" ht="14.25" customHeight="1" s="84"/>
-    <row r="870" ht="14.25" customHeight="1" s="84"/>
-    <row r="871" ht="14.25" customHeight="1" s="84"/>
-    <row r="872" ht="14.25" customHeight="1" s="84"/>
-    <row r="873" ht="14.25" customHeight="1" s="84"/>
-    <row r="874" ht="14.25" customHeight="1" s="84"/>
-    <row r="875" ht="14.25" customHeight="1" s="84"/>
-    <row r="876" ht="14.25" customHeight="1" s="84"/>
-    <row r="877" ht="14.25" customHeight="1" s="84"/>
-    <row r="878" ht="14.25" customHeight="1" s="84"/>
-    <row r="879" ht="14.25" customHeight="1" s="84"/>
-    <row r="880" ht="14.25" customHeight="1" s="84"/>
-    <row r="881" ht="14.25" customHeight="1" s="84"/>
-    <row r="882" ht="14.25" customHeight="1" s="84"/>
-    <row r="883" ht="14.25" customHeight="1" s="84"/>
-    <row r="884" ht="14.25" customHeight="1" s="84"/>
-    <row r="885" ht="14.25" customHeight="1" s="84"/>
-    <row r="886" ht="14.25" customHeight="1" s="84"/>
-    <row r="887" ht="14.25" customHeight="1" s="84"/>
-    <row r="888" ht="14.25" customHeight="1" s="84"/>
-    <row r="889" ht="14.25" customHeight="1" s="84"/>
-    <row r="890" ht="14.25" customHeight="1" s="84"/>
-    <row r="891" ht="14.25" customHeight="1" s="84"/>
-    <row r="892" ht="14.25" customHeight="1" s="84"/>
-    <row r="893" ht="14.25" customHeight="1" s="84"/>
-    <row r="894" ht="14.25" customHeight="1" s="84"/>
-    <row r="895" ht="14.25" customHeight="1" s="84"/>
-    <row r="896" ht="14.25" customHeight="1" s="84"/>
-    <row r="897" ht="14.25" customHeight="1" s="84"/>
-    <row r="898" ht="14.25" customHeight="1" s="84"/>
-    <row r="899" ht="14.25" customHeight="1" s="84"/>
-    <row r="900" ht="14.25" customHeight="1" s="84"/>
-    <row r="901" ht="14.25" customHeight="1" s="84"/>
-    <row r="902" ht="14.25" customHeight="1" s="84"/>
-    <row r="903" ht="14.25" customHeight="1" s="84"/>
-    <row r="904" ht="14.25" customHeight="1" s="84"/>
-    <row r="905" ht="14.25" customHeight="1" s="84"/>
-    <row r="906" ht="14.25" customHeight="1" s="84"/>
-    <row r="907" ht="14.25" customHeight="1" s="84"/>
-    <row r="908" ht="14.25" customHeight="1" s="84"/>
-    <row r="909" ht="14.25" customHeight="1" s="84"/>
-    <row r="910" ht="14.25" customHeight="1" s="84"/>
-    <row r="911" ht="14.25" customHeight="1" s="84"/>
-    <row r="912" ht="14.25" customHeight="1" s="84"/>
-    <row r="913" ht="14.25" customHeight="1" s="84"/>
-    <row r="914" ht="14.25" customHeight="1" s="84"/>
-    <row r="915" ht="14.25" customHeight="1" s="84"/>
-    <row r="916" ht="14.25" customHeight="1" s="84"/>
-    <row r="917" ht="14.25" customHeight="1" s="84"/>
-    <row r="918" ht="14.25" customHeight="1" s="84"/>
-    <row r="919" ht="14.25" customHeight="1" s="84"/>
-    <row r="920" ht="14.25" customHeight="1" s="84"/>
-    <row r="921" ht="14.25" customHeight="1" s="84"/>
-    <row r="922" ht="14.25" customHeight="1" s="84"/>
-    <row r="923" ht="14.25" customHeight="1" s="84"/>
-    <row r="924" ht="14.25" customHeight="1" s="84"/>
-    <row r="925" ht="14.25" customHeight="1" s="84"/>
-    <row r="926" ht="14.25" customHeight="1" s="84"/>
-    <row r="927" ht="14.25" customHeight="1" s="84"/>
-    <row r="928" ht="14.25" customHeight="1" s="84"/>
-    <row r="929" ht="14.25" customHeight="1" s="84"/>
-    <row r="930" ht="14.25" customHeight="1" s="84"/>
-    <row r="931" ht="14.25" customHeight="1" s="84"/>
-    <row r="932" ht="14.25" customHeight="1" s="84"/>
-    <row r="933" ht="14.25" customHeight="1" s="84"/>
-    <row r="934" ht="14.25" customHeight="1" s="84"/>
-    <row r="935" ht="14.25" customHeight="1" s="84"/>
-    <row r="936" ht="14.25" customHeight="1" s="84"/>
-    <row r="937" ht="14.25" customHeight="1" s="84"/>
-    <row r="938" ht="14.25" customHeight="1" s="84"/>
-    <row r="939" ht="14.25" customHeight="1" s="84"/>
-    <row r="940" ht="14.25" customHeight="1" s="84"/>
-    <row r="941" ht="14.25" customHeight="1" s="84"/>
-    <row r="942" ht="14.25" customHeight="1" s="84"/>
-    <row r="943" ht="14.25" customHeight="1" s="84"/>
-    <row r="944" ht="14.25" customHeight="1" s="84"/>
-    <row r="945" ht="14.25" customHeight="1" s="84"/>
-    <row r="946" ht="14.25" customHeight="1" s="84"/>
-    <row r="947" ht="14.25" customHeight="1" s="84"/>
-    <row r="948" ht="14.25" customHeight="1" s="84"/>
-    <row r="949" ht="14.25" customHeight="1" s="84"/>
-    <row r="950" ht="14.25" customHeight="1" s="84"/>
-    <row r="951" ht="14.25" customHeight="1" s="84"/>
-    <row r="952" ht="14.25" customHeight="1" s="84"/>
-    <row r="953" ht="14.25" customHeight="1" s="84"/>
-    <row r="954" ht="14.25" customHeight="1" s="84"/>
-    <row r="955" ht="14.25" customHeight="1" s="84"/>
-    <row r="956" ht="14.25" customHeight="1" s="84"/>
-    <row r="957" ht="14.25" customHeight="1" s="84"/>
-    <row r="958" ht="14.25" customHeight="1" s="84"/>
-    <row r="959" ht="14.25" customHeight="1" s="84"/>
-    <row r="960" ht="14.25" customHeight="1" s="84"/>
-    <row r="961" ht="14.25" customHeight="1" s="84"/>
-    <row r="962" ht="14.25" customHeight="1" s="84"/>
-    <row r="963" ht="14.25" customHeight="1" s="84"/>
-    <row r="964" ht="14.25" customHeight="1" s="84"/>
-    <row r="965" ht="14.25" customHeight="1" s="84"/>
-    <row r="966" ht="14.25" customHeight="1" s="84"/>
-    <row r="967" ht="14.25" customHeight="1" s="84"/>
-    <row r="968" ht="14.25" customHeight="1" s="84"/>
-    <row r="969" ht="14.25" customHeight="1" s="84"/>
-    <row r="970" ht="14.25" customHeight="1" s="84"/>
-    <row r="971" ht="14.25" customHeight="1" s="84"/>
-    <row r="972" ht="14.25" customHeight="1" s="84"/>
-    <row r="973" ht="14.25" customHeight="1" s="84"/>
-    <row r="974" ht="14.25" customHeight="1" s="84"/>
-    <row r="975" ht="14.25" customHeight="1" s="84"/>
-    <row r="976" ht="14.25" customHeight="1" s="84"/>
-    <row r="977" ht="14.25" customHeight="1" s="84"/>
-    <row r="978" ht="14.25" customHeight="1" s="84"/>
-    <row r="979" ht="14.25" customHeight="1" s="84"/>
-    <row r="980" ht="14.25" customHeight="1" s="84"/>
-    <row r="981" ht="14.25" customHeight="1" s="84"/>
-    <row r="982" ht="14.25" customHeight="1" s="84"/>
-    <row r="983" ht="14.25" customHeight="1" s="84"/>
-    <row r="984" ht="14.25" customHeight="1" s="84"/>
-    <row r="985" ht="14.25" customHeight="1" s="84"/>
-    <row r="986" ht="14.25" customHeight="1" s="84"/>
-    <row r="987" ht="14.25" customHeight="1" s="84"/>
-    <row r="988" ht="14.25" customHeight="1" s="84"/>
-    <row r="989" ht="14.25" customHeight="1" s="84"/>
-    <row r="990" ht="14.25" customHeight="1" s="84"/>
-    <row r="991" ht="14.25" customHeight="1" s="84"/>
-    <row r="992" ht="14.25" customHeight="1" s="84"/>
-    <row r="993" ht="14.25" customHeight="1" s="84"/>
-    <row r="994" ht="14.25" customHeight="1" s="84"/>
-    <row r="995" ht="14.25" customHeight="1" s="84"/>
-    <row r="996" ht="14.25" customHeight="1" s="84"/>
-    <row r="997" ht="14.25" customHeight="1" s="84"/>
-    <row r="998" ht="14.25" customHeight="1" s="84"/>
-    <row r="999" ht="14.25" customHeight="1" s="84"/>
-    <row r="1000" ht="14.25" customHeight="1" s="84"/>
+    <row r="221" ht="14.25" customHeight="1" s="90"/>
+    <row r="222" ht="14.25" customHeight="1" s="90"/>
+    <row r="223" ht="14.25" customHeight="1" s="90"/>
+    <row r="224" ht="14.25" customHeight="1" s="90"/>
+    <row r="225" ht="14.25" customHeight="1" s="90"/>
+    <row r="226" ht="14.25" customHeight="1" s="90"/>
+    <row r="227" ht="14.25" customHeight="1" s="90"/>
+    <row r="228" ht="14.25" customHeight="1" s="90"/>
+    <row r="229" ht="14.25" customHeight="1" s="90"/>
+    <row r="230" ht="14.25" customHeight="1" s="90"/>
+    <row r="231" ht="14.25" customHeight="1" s="90"/>
+    <row r="232" ht="14.25" customHeight="1" s="90"/>
+    <row r="233" ht="14.25" customHeight="1" s="90"/>
+    <row r="234" ht="14.25" customHeight="1" s="90"/>
+    <row r="235" ht="14.25" customHeight="1" s="90"/>
+    <row r="236" ht="14.25" customHeight="1" s="90"/>
+    <row r="237" ht="14.25" customHeight="1" s="90"/>
+    <row r="238" ht="14.25" customHeight="1" s="90"/>
+    <row r="239" ht="14.25" customHeight="1" s="90"/>
+    <row r="240" ht="14.25" customHeight="1" s="90"/>
+    <row r="241" ht="14.25" customHeight="1" s="90"/>
+    <row r="242" ht="14.25" customHeight="1" s="90"/>
+    <row r="243" ht="14.25" customHeight="1" s="90"/>
+    <row r="244" ht="14.25" customHeight="1" s="90"/>
+    <row r="245" ht="14.25" customHeight="1" s="90"/>
+    <row r="246" ht="14.25" customHeight="1" s="90"/>
+    <row r="247" ht="14.25" customHeight="1" s="90"/>
+    <row r="248" ht="14.25" customHeight="1" s="90"/>
+    <row r="249" ht="14.25" customHeight="1" s="90"/>
+    <row r="250" ht="14.25" customHeight="1" s="90"/>
+    <row r="251" ht="14.25" customHeight="1" s="90"/>
+    <row r="252" ht="14.25" customHeight="1" s="90"/>
+    <row r="253" ht="14.25" customHeight="1" s="90"/>
+    <row r="254" ht="14.25" customHeight="1" s="90"/>
+    <row r="255" ht="14.25" customHeight="1" s="90"/>
+    <row r="256" ht="14.25" customHeight="1" s="90"/>
+    <row r="257" ht="14.25" customHeight="1" s="90"/>
+    <row r="258" ht="14.25" customHeight="1" s="90"/>
+    <row r="259" ht="14.25" customHeight="1" s="90"/>
+    <row r="260" ht="14.25" customHeight="1" s="90"/>
+    <row r="261" ht="14.25" customHeight="1" s="90"/>
+    <row r="262" ht="14.25" customHeight="1" s="90"/>
+    <row r="263" ht="14.25" customHeight="1" s="90"/>
+    <row r="264" ht="14.25" customHeight="1" s="90"/>
+    <row r="265" ht="14.25" customHeight="1" s="90"/>
+    <row r="266" ht="14.25" customHeight="1" s="90"/>
+    <row r="267" ht="14.25" customHeight="1" s="90"/>
+    <row r="268" ht="14.25" customHeight="1" s="90"/>
+    <row r="269" ht="14.25" customHeight="1" s="90"/>
+    <row r="270" ht="14.25" customHeight="1" s="90"/>
+    <row r="271" ht="14.25" customHeight="1" s="90"/>
+    <row r="272" ht="14.25" customHeight="1" s="90"/>
+    <row r="273" ht="14.25" customHeight="1" s="90"/>
+    <row r="274" ht="14.25" customHeight="1" s="90"/>
+    <row r="275" ht="14.25" customHeight="1" s="90"/>
+    <row r="276" ht="14.25" customHeight="1" s="90"/>
+    <row r="277" ht="14.25" customHeight="1" s="90"/>
+    <row r="278" ht="14.25" customHeight="1" s="90"/>
+    <row r="279" ht="14.25" customHeight="1" s="90"/>
+    <row r="280" ht="14.25" customHeight="1" s="90"/>
+    <row r="281" ht="14.25" customHeight="1" s="90"/>
+    <row r="282" ht="14.25" customHeight="1" s="90"/>
+    <row r="283" ht="14.25" customHeight="1" s="90"/>
+    <row r="284" ht="14.25" customHeight="1" s="90"/>
+    <row r="285" ht="14.25" customHeight="1" s="90"/>
+    <row r="286" ht="14.25" customHeight="1" s="90"/>
+    <row r="287" ht="14.25" customHeight="1" s="90"/>
+    <row r="288" ht="14.25" customHeight="1" s="90"/>
+    <row r="289" ht="14.25" customHeight="1" s="90"/>
+    <row r="290" ht="14.25" customHeight="1" s="90"/>
+    <row r="291" ht="14.25" customHeight="1" s="90"/>
+    <row r="292" ht="14.25" customHeight="1" s="90"/>
+    <row r="293" ht="14.25" customHeight="1" s="90"/>
+    <row r="294" ht="14.25" customHeight="1" s="90"/>
+    <row r="295" ht="14.25" customHeight="1" s="90"/>
+    <row r="296" ht="14.25" customHeight="1" s="90"/>
+    <row r="297" ht="14.25" customHeight="1" s="90"/>
+    <row r="298" ht="14.25" customHeight="1" s="90"/>
+    <row r="299" ht="14.25" customHeight="1" s="90"/>
+    <row r="300" ht="14.25" customHeight="1" s="90"/>
+    <row r="301" ht="14.25" customHeight="1" s="90"/>
+    <row r="302" ht="14.25" customHeight="1" s="90"/>
+    <row r="303" ht="14.25" customHeight="1" s="90"/>
+    <row r="304" ht="14.25" customHeight="1" s="90"/>
+    <row r="305" ht="14.25" customHeight="1" s="90"/>
+    <row r="306" ht="14.25" customHeight="1" s="90"/>
+    <row r="307" ht="14.25" customHeight="1" s="90"/>
+    <row r="308" ht="14.25" customHeight="1" s="90"/>
+    <row r="309" ht="14.25" customHeight="1" s="90"/>
+    <row r="310" ht="14.25" customHeight="1" s="90"/>
+    <row r="311" ht="14.25" customHeight="1" s="90"/>
+    <row r="312" ht="14.25" customHeight="1" s="90"/>
+    <row r="313" ht="14.25" customHeight="1" s="90"/>
+    <row r="314" ht="14.25" customHeight="1" s="90"/>
+    <row r="315" ht="14.25" customHeight="1" s="90"/>
+    <row r="316" ht="14.25" customHeight="1" s="90"/>
+    <row r="317" ht="14.25" customHeight="1" s="90"/>
+    <row r="318" ht="14.25" customHeight="1" s="90"/>
+    <row r="319" ht="14.25" customHeight="1" s="90"/>
+    <row r="320" ht="14.25" customHeight="1" s="90"/>
+    <row r="321" ht="14.25" customHeight="1" s="90"/>
+    <row r="322" ht="14.25" customHeight="1" s="90"/>
+    <row r="323" ht="14.25" customHeight="1" s="90"/>
+    <row r="324" ht="14.25" customHeight="1" s="90"/>
+    <row r="325" ht="14.25" customHeight="1" s="90"/>
+    <row r="326" ht="14.25" customHeight="1" s="90"/>
+    <row r="327" ht="14.25" customHeight="1" s="90"/>
+    <row r="328" ht="14.25" customHeight="1" s="90"/>
+    <row r="329" ht="14.25" customHeight="1" s="90"/>
+    <row r="330" ht="14.25" customHeight="1" s="90"/>
+    <row r="331" ht="14.25" customHeight="1" s="90"/>
+    <row r="332" ht="14.25" customHeight="1" s="90"/>
+    <row r="333" ht="14.25" customHeight="1" s="90"/>
+    <row r="334" ht="14.25" customHeight="1" s="90"/>
+    <row r="335" ht="14.25" customHeight="1" s="90"/>
+    <row r="336" ht="14.25" customHeight="1" s="90"/>
+    <row r="337" ht="14.25" customHeight="1" s="90"/>
+    <row r="338" ht="14.25" customHeight="1" s="90"/>
+    <row r="339" ht="14.25" customHeight="1" s="90"/>
+    <row r="340" ht="14.25" customHeight="1" s="90"/>
+    <row r="341" ht="14.25" customHeight="1" s="90"/>
+    <row r="342" ht="14.25" customHeight="1" s="90"/>
+    <row r="343" ht="14.25" customHeight="1" s="90"/>
+    <row r="344" ht="14.25" customHeight="1" s="90"/>
+    <row r="345" ht="14.25" customHeight="1" s="90"/>
+    <row r="346" ht="14.25" customHeight="1" s="90"/>
+    <row r="347" ht="14.25" customHeight="1" s="90"/>
+    <row r="348" ht="14.25" customHeight="1" s="90"/>
+    <row r="349" ht="14.25" customHeight="1" s="90"/>
+    <row r="350" ht="14.25" customHeight="1" s="90"/>
+    <row r="351" ht="14.25" customHeight="1" s="90"/>
+    <row r="352" ht="14.25" customHeight="1" s="90"/>
+    <row r="353" ht="14.25" customHeight="1" s="90"/>
+    <row r="354" ht="14.25" customHeight="1" s="90"/>
+    <row r="355" ht="14.25" customHeight="1" s="90"/>
+    <row r="356" ht="14.25" customHeight="1" s="90"/>
+    <row r="357" ht="14.25" customHeight="1" s="90"/>
+    <row r="358" ht="14.25" customHeight="1" s="90"/>
+    <row r="359" ht="14.25" customHeight="1" s="90"/>
+    <row r="360" ht="14.25" customHeight="1" s="90"/>
+    <row r="361" ht="14.25" customHeight="1" s="90"/>
+    <row r="362" ht="14.25" customHeight="1" s="90"/>
+    <row r="363" ht="14.25" customHeight="1" s="90"/>
+    <row r="364" ht="14.25" customHeight="1" s="90"/>
+    <row r="365" ht="14.25" customHeight="1" s="90"/>
+    <row r="366" ht="14.25" customHeight="1" s="90"/>
+    <row r="367" ht="14.25" customHeight="1" s="90"/>
+    <row r="368" ht="14.25" customHeight="1" s="90"/>
+    <row r="369" ht="14.25" customHeight="1" s="90"/>
+    <row r="370" ht="14.25" customHeight="1" s="90"/>
+    <row r="371" ht="14.25" customHeight="1" s="90"/>
+    <row r="372" ht="14.25" customHeight="1" s="90"/>
+    <row r="373" ht="14.25" customHeight="1" s="90"/>
+    <row r="374" ht="14.25" customHeight="1" s="90"/>
+    <row r="375" ht="14.25" customHeight="1" s="90"/>
+    <row r="376" ht="14.25" customHeight="1" s="90"/>
+    <row r="377" ht="14.25" customHeight="1" s="90"/>
+    <row r="378" ht="14.25" customHeight="1" s="90"/>
+    <row r="379" ht="14.25" customHeight="1" s="90"/>
+    <row r="380" ht="14.25" customHeight="1" s="90"/>
+    <row r="381" ht="14.25" customHeight="1" s="90"/>
+    <row r="382" ht="14.25" customHeight="1" s="90"/>
+    <row r="383" ht="14.25" customHeight="1" s="90"/>
+    <row r="384" ht="14.25" customHeight="1" s="90"/>
+    <row r="385" ht="14.25" customHeight="1" s="90"/>
+    <row r="386" ht="14.25" customHeight="1" s="90"/>
+    <row r="387" ht="14.25" customHeight="1" s="90"/>
+    <row r="388" ht="14.25" customHeight="1" s="90"/>
+    <row r="389" ht="14.25" customHeight="1" s="90"/>
+    <row r="390" ht="14.25" customHeight="1" s="90"/>
+    <row r="391" ht="14.25" customHeight="1" s="90"/>
+    <row r="392" ht="14.25" customHeight="1" s="90"/>
+    <row r="393" ht="14.25" customHeight="1" s="90"/>
+    <row r="394" ht="14.25" customHeight="1" s="90"/>
+    <row r="395" ht="14.25" customHeight="1" s="90"/>
+    <row r="396" ht="14.25" customHeight="1" s="90"/>
+    <row r="397" ht="14.25" customHeight="1" s="90"/>
+    <row r="398" ht="14.25" customHeight="1" s="90"/>
+    <row r="399" ht="14.25" customHeight="1" s="90"/>
+    <row r="400" ht="14.25" customHeight="1" s="90"/>
+    <row r="401" ht="14.25" customHeight="1" s="90"/>
+    <row r="402" ht="14.25" customHeight="1" s="90"/>
+    <row r="403" ht="14.25" customHeight="1" s="90"/>
+    <row r="404" ht="14.25" customHeight="1" s="90"/>
+    <row r="405" ht="14.25" customHeight="1" s="90"/>
+    <row r="406" ht="14.25" customHeight="1" s="90"/>
+    <row r="407" ht="14.25" customHeight="1" s="90"/>
+    <row r="408" ht="14.25" customHeight="1" s="90"/>
+    <row r="409" ht="14.25" customHeight="1" s="90"/>
+    <row r="410" ht="14.25" customHeight="1" s="90"/>
+    <row r="411" ht="14.25" customHeight="1" s="90"/>
+    <row r="412" ht="14.25" customHeight="1" s="90"/>
+    <row r="413" ht="14.25" customHeight="1" s="90"/>
+    <row r="414" ht="14.25" customHeight="1" s="90"/>
+    <row r="415" ht="14.25" customHeight="1" s="90"/>
+    <row r="416" ht="14.25" customHeight="1" s="90"/>
+    <row r="417" ht="14.25" customHeight="1" s="90"/>
+    <row r="418" ht="14.25" customHeight="1" s="90"/>
+    <row r="419" ht="14.25" customHeight="1" s="90"/>
+    <row r="420" ht="14.25" customHeight="1" s="90"/>
+    <row r="421" ht="14.25" customHeight="1" s="90"/>
+    <row r="422" ht="14.25" customHeight="1" s="90"/>
+    <row r="423" ht="14.25" customHeight="1" s="90"/>
+    <row r="424" ht="14.25" customHeight="1" s="90"/>
+    <row r="425" ht="14.25" customHeight="1" s="90"/>
+    <row r="426" ht="14.25" customHeight="1" s="90"/>
+    <row r="427" ht="14.25" customHeight="1" s="90"/>
+    <row r="428" ht="14.25" customHeight="1" s="90"/>
+    <row r="429" ht="14.25" customHeight="1" s="90"/>
+    <row r="430" ht="14.25" customHeight="1" s="90"/>
+    <row r="431" ht="14.25" customHeight="1" s="90"/>
+    <row r="432" ht="14.25" customHeight="1" s="90"/>
+    <row r="433" ht="14.25" customHeight="1" s="90"/>
+    <row r="434" ht="14.25" customHeight="1" s="90"/>
+    <row r="435" ht="14.25" customHeight="1" s="90"/>
+    <row r="436" ht="14.25" customHeight="1" s="90"/>
+    <row r="437" ht="14.25" customHeight="1" s="90"/>
+    <row r="438" ht="14.25" customHeight="1" s="90"/>
+    <row r="439" ht="14.25" customHeight="1" s="90"/>
+    <row r="440" ht="14.25" customHeight="1" s="90"/>
+    <row r="441" ht="14.25" customHeight="1" s="90"/>
+    <row r="442" ht="14.25" customHeight="1" s="90"/>
+    <row r="443" ht="14.25" customHeight="1" s="90"/>
+    <row r="444" ht="14.25" customHeight="1" s="90"/>
+    <row r="445" ht="14.25" customHeight="1" s="90"/>
+    <row r="446" ht="14.25" customHeight="1" s="90"/>
+    <row r="447" ht="14.25" customHeight="1" s="90"/>
+    <row r="448" ht="14.25" customHeight="1" s="90"/>
+    <row r="449" ht="14.25" customHeight="1" s="90"/>
+    <row r="450" ht="14.25" customHeight="1" s="90"/>
+    <row r="451" ht="14.25" customHeight="1" s="90"/>
+    <row r="452" ht="14.25" customHeight="1" s="90"/>
+    <row r="453" ht="14.25" customHeight="1" s="90"/>
+    <row r="454" ht="14.25" customHeight="1" s="90"/>
+    <row r="455" ht="14.25" customHeight="1" s="90"/>
+    <row r="456" ht="14.25" customHeight="1" s="90"/>
+    <row r="457" ht="14.25" customHeight="1" s="90"/>
+    <row r="458" ht="14.25" customHeight="1" s="90"/>
+    <row r="459" ht="14.25" customHeight="1" s="90"/>
+    <row r="460" ht="14.25" customHeight="1" s="90"/>
+    <row r="461" ht="14.25" customHeight="1" s="90"/>
+    <row r="462" ht="14.25" customHeight="1" s="90"/>
+    <row r="463" ht="14.25" customHeight="1" s="90"/>
+    <row r="464" ht="14.25" customHeight="1" s="90"/>
+    <row r="465" ht="14.25" customHeight="1" s="90"/>
+    <row r="466" ht="14.25" customHeight="1" s="90"/>
+    <row r="467" ht="14.25" customHeight="1" s="90"/>
+    <row r="468" ht="14.25" customHeight="1" s="90"/>
+    <row r="469" ht="14.25" customHeight="1" s="90"/>
+    <row r="470" ht="14.25" customHeight="1" s="90"/>
+    <row r="471" ht="14.25" customHeight="1" s="90"/>
+    <row r="472" ht="14.25" customHeight="1" s="90"/>
+    <row r="473" ht="14.25" customHeight="1" s="90"/>
+    <row r="474" ht="14.25" customHeight="1" s="90"/>
+    <row r="475" ht="14.25" customHeight="1" s="90"/>
+    <row r="476" ht="14.25" customHeight="1" s="90"/>
+    <row r="477" ht="14.25" customHeight="1" s="90"/>
+    <row r="478" ht="14.25" customHeight="1" s="90"/>
+    <row r="479" ht="14.25" customHeight="1" s="90"/>
+    <row r="480" ht="14.25" customHeight="1" s="90"/>
+    <row r="481" ht="14.25" customHeight="1" s="90"/>
+    <row r="482" ht="14.25" customHeight="1" s="90"/>
+    <row r="483" ht="14.25" customHeight="1" s="90"/>
+    <row r="484" ht="14.25" customHeight="1" s="90"/>
+    <row r="485" ht="14.25" customHeight="1" s="90"/>
+    <row r="486" ht="14.25" customHeight="1" s="90"/>
+    <row r="487" ht="14.25" customHeight="1" s="90"/>
+    <row r="488" ht="14.25" customHeight="1" s="90"/>
+    <row r="489" ht="14.25" customHeight="1" s="90"/>
+    <row r="490" ht="14.25" customHeight="1" s="90"/>
+    <row r="491" ht="14.25" customHeight="1" s="90"/>
+    <row r="492" ht="14.25" customHeight="1" s="90"/>
+    <row r="493" ht="14.25" customHeight="1" s="90"/>
+    <row r="494" ht="14.25" customHeight="1" s="90"/>
+    <row r="495" ht="14.25" customHeight="1" s="90"/>
+    <row r="496" ht="14.25" customHeight="1" s="90"/>
+    <row r="497" ht="14.25" customHeight="1" s="90"/>
+    <row r="498" ht="14.25" customHeight="1" s="90"/>
+    <row r="499" ht="14.25" customHeight="1" s="90"/>
+    <row r="500" ht="14.25" customHeight="1" s="90"/>
+    <row r="501" ht="14.25" customHeight="1" s="90"/>
+    <row r="502" ht="14.25" customHeight="1" s="90"/>
+    <row r="503" ht="14.25" customHeight="1" s="90"/>
+    <row r="504" ht="14.25" customHeight="1" s="90"/>
+    <row r="505" ht="14.25" customHeight="1" s="90"/>
+    <row r="506" ht="14.25" customHeight="1" s="90"/>
+    <row r="507" ht="14.25" customHeight="1" s="90"/>
+    <row r="508" ht="14.25" customHeight="1" s="90"/>
+    <row r="509" ht="14.25" customHeight="1" s="90"/>
+    <row r="510" ht="14.25" customHeight="1" s="90"/>
+    <row r="511" ht="14.25" customHeight="1" s="90"/>
+    <row r="512" ht="14.25" customHeight="1" s="90"/>
+    <row r="513" ht="14.25" customHeight="1" s="90"/>
+    <row r="514" ht="14.25" customHeight="1" s="90"/>
+    <row r="515" ht="14.25" customHeight="1" s="90"/>
+    <row r="516" ht="14.25" customHeight="1" s="90"/>
+    <row r="517" ht="14.25" customHeight="1" s="90"/>
+    <row r="518" ht="14.25" customHeight="1" s="90"/>
+    <row r="519" ht="14.25" customHeight="1" s="90"/>
+    <row r="520" ht="14.25" customHeight="1" s="90"/>
+    <row r="521" ht="14.25" customHeight="1" s="90"/>
+    <row r="522" ht="14.25" customHeight="1" s="90"/>
+    <row r="523" ht="14.25" customHeight="1" s="90"/>
+    <row r="524" ht="14.25" customHeight="1" s="90"/>
+    <row r="525" ht="14.25" customHeight="1" s="90"/>
+    <row r="526" ht="14.25" customHeight="1" s="90"/>
+    <row r="527" ht="14.25" customHeight="1" s="90"/>
+    <row r="528" ht="14.25" customHeight="1" s="90"/>
+    <row r="529" ht="14.25" customHeight="1" s="90"/>
+    <row r="530" ht="14.25" customHeight="1" s="90"/>
+    <row r="531" ht="14.25" customHeight="1" s="90"/>
+    <row r="532" ht="14.25" customHeight="1" s="90"/>
+    <row r="533" ht="14.25" customHeight="1" s="90"/>
+    <row r="534" ht="14.25" customHeight="1" s="90"/>
+    <row r="535" ht="14.25" customHeight="1" s="90"/>
+    <row r="536" ht="14.25" customHeight="1" s="90"/>
+    <row r="537" ht="14.25" customHeight="1" s="90"/>
+    <row r="538" ht="14.25" customHeight="1" s="90"/>
+    <row r="539" ht="14.25" customHeight="1" s="90"/>
+    <row r="540" ht="14.25" customHeight="1" s="90"/>
+    <row r="541" ht="14.25" customHeight="1" s="90"/>
+    <row r="542" ht="14.25" customHeight="1" s="90"/>
+    <row r="543" ht="14.25" customHeight="1" s="90"/>
+    <row r="544" ht="14.25" customHeight="1" s="90"/>
+    <row r="545" ht="14.25" customHeight="1" s="90"/>
+    <row r="546" ht="14.25" customHeight="1" s="90"/>
+    <row r="547" ht="14.25" customHeight="1" s="90"/>
+    <row r="548" ht="14.25" customHeight="1" s="90"/>
+    <row r="549" ht="14.25" customHeight="1" s="90"/>
+    <row r="550" ht="14.25" customHeight="1" s="90"/>
+    <row r="551" ht="14.25" customHeight="1" s="90"/>
+    <row r="552" ht="14.25" customHeight="1" s="90"/>
+    <row r="553" ht="14.25" customHeight="1" s="90"/>
+    <row r="554" ht="14.25" customHeight="1" s="90"/>
+    <row r="555" ht="14.25" customHeight="1" s="90"/>
+    <row r="556" ht="14.25" customHeight="1" s="90"/>
+    <row r="557" ht="14.25" customHeight="1" s="90"/>
+    <row r="558" ht="14.25" customHeight="1" s="90"/>
+    <row r="559" ht="14.25" customHeight="1" s="90"/>
+    <row r="560" ht="14.25" customHeight="1" s="90"/>
+    <row r="561" ht="14.25" customHeight="1" s="90"/>
+    <row r="562" ht="14.25" customHeight="1" s="90"/>
+    <row r="563" ht="14.25" customHeight="1" s="90"/>
+    <row r="564" ht="14.25" customHeight="1" s="90"/>
+    <row r="565" ht="14.25" customHeight="1" s="90"/>
+    <row r="566" ht="14.25" customHeight="1" s="90"/>
+    <row r="567" ht="14.25" customHeight="1" s="90"/>
+    <row r="568" ht="14.25" customHeight="1" s="90"/>
+    <row r="569" ht="14.25" customHeight="1" s="90"/>
+    <row r="570" ht="14.25" customHeight="1" s="90"/>
+    <row r="571" ht="14.25" customHeight="1" s="90"/>
+    <row r="572" ht="14.25" customHeight="1" s="90"/>
+    <row r="573" ht="14.25" customHeight="1" s="90"/>
+    <row r="574" ht="14.25" customHeight="1" s="90"/>
+    <row r="575" ht="14.25" customHeight="1" s="90"/>
+    <row r="576" ht="14.25" customHeight="1" s="90"/>
+    <row r="577" ht="14.25" customHeight="1" s="90"/>
+    <row r="578" ht="14.25" customHeight="1" s="90"/>
+    <row r="579" ht="14.25" customHeight="1" s="90"/>
+    <row r="580" ht="14.25" customHeight="1" s="90"/>
+    <row r="581" ht="14.25" customHeight="1" s="90"/>
+    <row r="582" ht="14.25" customHeight="1" s="90"/>
+    <row r="583" ht="14.25" customHeight="1" s="90"/>
+    <row r="584" ht="14.25" customHeight="1" s="90"/>
+    <row r="585" ht="14.25" customHeight="1" s="90"/>
+    <row r="586" ht="14.25" customHeight="1" s="90"/>
+    <row r="587" ht="14.25" customHeight="1" s="90"/>
+    <row r="588" ht="14.25" customHeight="1" s="90"/>
+    <row r="589" ht="14.25" customHeight="1" s="90"/>
+    <row r="590" ht="14.25" customHeight="1" s="90"/>
+    <row r="591" ht="14.25" customHeight="1" s="90"/>
+    <row r="592" ht="14.25" customHeight="1" s="90"/>
+    <row r="593" ht="14.25" customHeight="1" s="90"/>
+    <row r="594" ht="14.25" customHeight="1" s="90"/>
+    <row r="595" ht="14.25" customHeight="1" s="90"/>
+    <row r="596" ht="14.25" customHeight="1" s="90"/>
+    <row r="597" ht="14.25" customHeight="1" s="90"/>
+    <row r="598" ht="14.25" customHeight="1" s="90"/>
+    <row r="599" ht="14.25" customHeight="1" s="90"/>
+    <row r="600" ht="14.25" customHeight="1" s="90"/>
+    <row r="601" ht="14.25" customHeight="1" s="90"/>
+    <row r="602" ht="14.25" customHeight="1" s="90"/>
+    <row r="603" ht="14.25" customHeight="1" s="90"/>
+    <row r="604" ht="14.25" customHeight="1" s="90"/>
+    <row r="605" ht="14.25" customHeight="1" s="90"/>
+    <row r="606" ht="14.25" customHeight="1" s="90"/>
+    <row r="607" ht="14.25" customHeight="1" s="90"/>
+    <row r="608" ht="14.25" customHeight="1" s="90"/>
+    <row r="609" ht="14.25" customHeight="1" s="90"/>
+    <row r="610" ht="14.25" customHeight="1" s="90"/>
+    <row r="611" ht="14.25" customHeight="1" s="90"/>
+    <row r="612" ht="14.25" customHeight="1" s="90"/>
+    <row r="613" ht="14.25" customHeight="1" s="90"/>
+    <row r="614" ht="14.25" customHeight="1" s="90"/>
+    <row r="615" ht="14.25" customHeight="1" s="90"/>
+    <row r="616" ht="14.25" customHeight="1" s="90"/>
+    <row r="617" ht="14.25" customHeight="1" s="90"/>
+    <row r="618" ht="14.25" customHeight="1" s="90"/>
+    <row r="619" ht="14.25" customHeight="1" s="90"/>
+    <row r="620" ht="14.25" customHeight="1" s="90"/>
+    <row r="621" ht="14.25" customHeight="1" s="90"/>
+    <row r="622" ht="14.25" customHeight="1" s="90"/>
+    <row r="623" ht="14.25" customHeight="1" s="90"/>
+    <row r="624" ht="14.25" customHeight="1" s="90"/>
+    <row r="625" ht="14.25" customHeight="1" s="90"/>
+    <row r="626" ht="14.25" customHeight="1" s="90"/>
+    <row r="627" ht="14.25" customHeight="1" s="90"/>
+    <row r="628" ht="14.25" customHeight="1" s="90"/>
+    <row r="629" ht="14.25" customHeight="1" s="90"/>
+    <row r="630" ht="14.25" customHeight="1" s="90"/>
+    <row r="631" ht="14.25" customHeight="1" s="90"/>
+    <row r="632" ht="14.25" customHeight="1" s="90"/>
+    <row r="633" ht="14.25" customHeight="1" s="90"/>
+    <row r="634" ht="14.25" customHeight="1" s="90"/>
+    <row r="635" ht="14.25" customHeight="1" s="90"/>
+    <row r="636" ht="14.25" customHeight="1" s="90"/>
+    <row r="637" ht="14.25" customHeight="1" s="90"/>
+    <row r="638" ht="14.25" customHeight="1" s="90"/>
+    <row r="639" ht="14.25" customHeight="1" s="90"/>
+    <row r="640" ht="14.25" customHeight="1" s="90"/>
+    <row r="641" ht="14.25" customHeight="1" s="90"/>
+    <row r="642" ht="14.25" customHeight="1" s="90"/>
+    <row r="643" ht="14.25" customHeight="1" s="90"/>
+    <row r="644" ht="14.25" customHeight="1" s="90"/>
+    <row r="645" ht="14.25" customHeight="1" s="90"/>
+    <row r="646" ht="14.25" customHeight="1" s="90"/>
+    <row r="647" ht="14.25" customHeight="1" s="90"/>
+    <row r="648" ht="14.25" customHeight="1" s="90"/>
+    <row r="649" ht="14.25" customHeight="1" s="90"/>
+    <row r="650" ht="14.25" customHeight="1" s="90"/>
+    <row r="651" ht="14.25" customHeight="1" s="90"/>
+    <row r="652" ht="14.25" customHeight="1" s="90"/>
+    <row r="653" ht="14.25" customHeight="1" s="90"/>
+    <row r="654" ht="14.25" customHeight="1" s="90"/>
+    <row r="655" ht="14.25" customHeight="1" s="90"/>
+    <row r="656" ht="14.25" customHeight="1" s="90"/>
+    <row r="657" ht="14.25" customHeight="1" s="90"/>
+    <row r="658" ht="14.25" customHeight="1" s="90"/>
+    <row r="659" ht="14.25" customHeight="1" s="90"/>
+    <row r="660" ht="14.25" customHeight="1" s="90"/>
+    <row r="661" ht="14.25" customHeight="1" s="90"/>
+    <row r="662" ht="14.25" customHeight="1" s="90"/>
+    <row r="663" ht="14.25" customHeight="1" s="90"/>
+    <row r="664" ht="14.25" customHeight="1" s="90"/>
+    <row r="665" ht="14.25" customHeight="1" s="90"/>
+    <row r="666" ht="14.25" customHeight="1" s="90"/>
+    <row r="667" ht="14.25" customHeight="1" s="90"/>
+    <row r="668" ht="14.25" customHeight="1" s="90"/>
+    <row r="669" ht="14.25" customHeight="1" s="90"/>
+    <row r="670" ht="14.25" customHeight="1" s="90"/>
+    <row r="671" ht="14.25" customHeight="1" s="90"/>
+    <row r="672" ht="14.25" customHeight="1" s="90"/>
+    <row r="673" ht="14.25" customHeight="1" s="90"/>
+    <row r="674" ht="14.25" customHeight="1" s="90"/>
+    <row r="675" ht="14.25" customHeight="1" s="90"/>
+    <row r="676" ht="14.25" customHeight="1" s="90"/>
+    <row r="677" ht="14.25" customHeight="1" s="90"/>
+    <row r="678" ht="14.25" customHeight="1" s="90"/>
+    <row r="679" ht="14.25" customHeight="1" s="90"/>
+    <row r="680" ht="14.25" customHeight="1" s="90"/>
+    <row r="681" ht="14.25" customHeight="1" s="90"/>
+    <row r="682" ht="14.25" customHeight="1" s="90"/>
+    <row r="683" ht="14.25" customHeight="1" s="90"/>
+    <row r="684" ht="14.25" customHeight="1" s="90"/>
+    <row r="685" ht="14.25" customHeight="1" s="90"/>
+    <row r="686" ht="14.25" customHeight="1" s="90"/>
+    <row r="687" ht="14.25" customHeight="1" s="90"/>
+    <row r="688" ht="14.25" customHeight="1" s="90"/>
+    <row r="689" ht="14.25" customHeight="1" s="90"/>
+    <row r="690" ht="14.25" customHeight="1" s="90"/>
+    <row r="691" ht="14.25" customHeight="1" s="90"/>
+    <row r="692" ht="14.25" customHeight="1" s="90"/>
+    <row r="693" ht="14.25" customHeight="1" s="90"/>
+    <row r="694" ht="14.25" customHeight="1" s="90"/>
+    <row r="695" ht="14.25" customHeight="1" s="90"/>
+    <row r="696" ht="14.25" customHeight="1" s="90"/>
+    <row r="697" ht="14.25" customHeight="1" s="90"/>
+    <row r="698" ht="14.25" customHeight="1" s="90"/>
+    <row r="699" ht="14.25" customHeight="1" s="90"/>
+    <row r="700" ht="14.25" customHeight="1" s="90"/>
+    <row r="701" ht="14.25" customHeight="1" s="90"/>
+    <row r="702" ht="14.25" customHeight="1" s="90"/>
+    <row r="703" ht="14.25" customHeight="1" s="90"/>
+    <row r="704" ht="14.25" customHeight="1" s="90"/>
+    <row r="705" ht="14.25" customHeight="1" s="90"/>
+    <row r="706" ht="14.25" customHeight="1" s="90"/>
+    <row r="707" ht="14.25" customHeight="1" s="90"/>
+    <row r="708" ht="14.25" customHeight="1" s="90"/>
+    <row r="709" ht="14.25" customHeight="1" s="90"/>
+    <row r="710" ht="14.25" customHeight="1" s="90"/>
+    <row r="711" ht="14.25" customHeight="1" s="90"/>
+    <row r="712" ht="14.25" customHeight="1" s="90"/>
+    <row r="713" ht="14.25" customHeight="1" s="90"/>
+    <row r="714" ht="14.25" customHeight="1" s="90"/>
+    <row r="715" ht="14.25" customHeight="1" s="90"/>
+    <row r="716" ht="14.25" customHeight="1" s="90"/>
+    <row r="717" ht="14.25" customHeight="1" s="90"/>
+    <row r="718" ht="14.25" customHeight="1" s="90"/>
+    <row r="719" ht="14.25" customHeight="1" s="90"/>
+    <row r="720" ht="14.25" customHeight="1" s="90"/>
+    <row r="721" ht="14.25" customHeight="1" s="90"/>
+    <row r="722" ht="14.25" customHeight="1" s="90"/>
+    <row r="723" ht="14.25" customHeight="1" s="90"/>
+    <row r="724" ht="14.25" customHeight="1" s="90"/>
+    <row r="725" ht="14.25" customHeight="1" s="90"/>
+    <row r="726" ht="14.25" customHeight="1" s="90"/>
+    <row r="727" ht="14.25" customHeight="1" s="90"/>
+    <row r="728" ht="14.25" customHeight="1" s="90"/>
+    <row r="729" ht="14.25" customHeight="1" s="90"/>
+    <row r="730" ht="14.25" customHeight="1" s="90"/>
+    <row r="731" ht="14.25" customHeight="1" s="90"/>
+    <row r="732" ht="14.25" customHeight="1" s="90"/>
+    <row r="733" ht="14.25" customHeight="1" s="90"/>
+    <row r="734" ht="14.25" customHeight="1" s="90"/>
+    <row r="735" ht="14.25" customHeight="1" s="90"/>
+    <row r="736" ht="14.25" customHeight="1" s="90"/>
+    <row r="737" ht="14.25" customHeight="1" s="90"/>
+    <row r="738" ht="14.25" customHeight="1" s="90"/>
+    <row r="739" ht="14.25" customHeight="1" s="90"/>
+    <row r="740" ht="14.25" customHeight="1" s="90"/>
+    <row r="741" ht="14.25" customHeight="1" s="90"/>
+    <row r="742" ht="14.25" customHeight="1" s="90"/>
+    <row r="743" ht="14.25" customHeight="1" s="90"/>
+    <row r="744" ht="14.25" customHeight="1" s="90"/>
+    <row r="745" ht="14.25" customHeight="1" s="90"/>
+    <row r="746" ht="14.25" customHeight="1" s="90"/>
+    <row r="747" ht="14.25" customHeight="1" s="90"/>
+    <row r="748" ht="14.25" customHeight="1" s="90"/>
+    <row r="749" ht="14.25" customHeight="1" s="90"/>
+    <row r="750" ht="14.25" customHeight="1" s="90"/>
+    <row r="751" ht="14.25" customHeight="1" s="90"/>
+    <row r="752" ht="14.25" customHeight="1" s="90"/>
+    <row r="753" ht="14.25" customHeight="1" s="90"/>
+    <row r="754" ht="14.25" customHeight="1" s="90"/>
+    <row r="755" ht="14.25" customHeight="1" s="90"/>
+    <row r="756" ht="14.25" customHeight="1" s="90"/>
+    <row r="757" ht="14.25" customHeight="1" s="90"/>
+    <row r="758" ht="14.25" customHeight="1" s="90"/>
+    <row r="759" ht="14.25" customHeight="1" s="90"/>
+    <row r="760" ht="14.25" customHeight="1" s="90"/>
+    <row r="761" ht="14.25" customHeight="1" s="90"/>
+    <row r="762" ht="14.25" customHeight="1" s="90"/>
+    <row r="763" ht="14.25" customHeight="1" s="90"/>
+    <row r="764" ht="14.25" customHeight="1" s="90"/>
+    <row r="765" ht="14.25" customHeight="1" s="90"/>
+    <row r="766" ht="14.25" customHeight="1" s="90"/>
+    <row r="767" ht="14.25" customHeight="1" s="90"/>
+    <row r="768" ht="14.25" customHeight="1" s="90"/>
+    <row r="769" ht="14.25" customHeight="1" s="90"/>
+    <row r="770" ht="14.25" customHeight="1" s="90"/>
+    <row r="771" ht="14.25" customHeight="1" s="90"/>
+    <row r="772" ht="14.25" customHeight="1" s="90"/>
+    <row r="773" ht="14.25" customHeight="1" s="90"/>
+    <row r="774" ht="14.25" customHeight="1" s="90"/>
+    <row r="775" ht="14.25" customHeight="1" s="90"/>
+    <row r="776" ht="14.25" customHeight="1" s="90"/>
+    <row r="777" ht="14.25" customHeight="1" s="90"/>
+    <row r="778" ht="14.25" customHeight="1" s="90"/>
+    <row r="779" ht="14.25" customHeight="1" s="90"/>
+    <row r="780" ht="14.25" customHeight="1" s="90"/>
+    <row r="781" ht="14.25" customHeight="1" s="90"/>
+    <row r="782" ht="14.25" customHeight="1" s="90"/>
+    <row r="783" ht="14.25" customHeight="1" s="90"/>
+    <row r="784" ht="14.25" customHeight="1" s="90"/>
+    <row r="785" ht="14.25" customHeight="1" s="90"/>
+    <row r="786" ht="14.25" customHeight="1" s="90"/>
+    <row r="787" ht="14.25" customHeight="1" s="90"/>
+    <row r="788" ht="14.25" customHeight="1" s="90"/>
+    <row r="789" ht="14.25" customHeight="1" s="90"/>
+    <row r="790" ht="14.25" customHeight="1" s="90"/>
+    <row r="791" ht="14.25" customHeight="1" s="90"/>
+    <row r="792" ht="14.25" customHeight="1" s="90"/>
+    <row r="793" ht="14.25" customHeight="1" s="90"/>
+    <row r="794" ht="14.25" customHeight="1" s="90"/>
+    <row r="795" ht="14.25" customHeight="1" s="90"/>
+    <row r="796" ht="14.25" customHeight="1" s="90"/>
+    <row r="797" ht="14.25" customHeight="1" s="90"/>
+    <row r="798" ht="14.25" customHeight="1" s="90"/>
+    <row r="799" ht="14.25" customHeight="1" s="90"/>
+    <row r="800" ht="14.25" customHeight="1" s="90"/>
+    <row r="801" ht="14.25" customHeight="1" s="90"/>
+    <row r="802" ht="14.25" customHeight="1" s="90"/>
+    <row r="803" ht="14.25" customHeight="1" s="90"/>
+    <row r="804" ht="14.25" customHeight="1" s="90"/>
+    <row r="805" ht="14.25" customHeight="1" s="90"/>
+    <row r="806" ht="14.25" customHeight="1" s="90"/>
+    <row r="807" ht="14.25" customHeight="1" s="90"/>
+    <row r="808" ht="14.25" customHeight="1" s="90"/>
+    <row r="809" ht="14.25" customHeight="1" s="90"/>
+    <row r="810" ht="14.25" customHeight="1" s="90"/>
+    <row r="811" ht="14.25" customHeight="1" s="90"/>
+    <row r="812" ht="14.25" customHeight="1" s="90"/>
+    <row r="813" ht="14.25" customHeight="1" s="90"/>
+    <row r="814" ht="14.25" customHeight="1" s="90"/>
+    <row r="815" ht="14.25" customHeight="1" s="90"/>
+    <row r="816" ht="14.25" customHeight="1" s="90"/>
+    <row r="817" ht="14.25" customHeight="1" s="90"/>
+    <row r="818" ht="14.25" customHeight="1" s="90"/>
+    <row r="819" ht="14.25" customHeight="1" s="90"/>
+    <row r="820" ht="14.25" customHeight="1" s="90"/>
+    <row r="821" ht="14.25" customHeight="1" s="90"/>
+    <row r="822" ht="14.25" customHeight="1" s="90"/>
+    <row r="823" ht="14.25" customHeight="1" s="90"/>
+    <row r="824" ht="14.25" customHeight="1" s="90"/>
+    <row r="825" ht="14.25" customHeight="1" s="90"/>
+    <row r="826" ht="14.25" customHeight="1" s="90"/>
+    <row r="827" ht="14.25" customHeight="1" s="90"/>
+    <row r="828" ht="14.25" customHeight="1" s="90"/>
+    <row r="829" ht="14.25" customHeight="1" s="90"/>
+    <row r="830" ht="14.25" customHeight="1" s="90"/>
+    <row r="831" ht="14.25" customHeight="1" s="90"/>
+    <row r="832" ht="14.25" customHeight="1" s="90"/>
+    <row r="833" ht="14.25" customHeight="1" s="90"/>
+    <row r="834" ht="14.25" customHeight="1" s="90"/>
+    <row r="835" ht="14.25" customHeight="1" s="90"/>
+    <row r="836" ht="14.25" customHeight="1" s="90"/>
+    <row r="837" ht="14.25" customHeight="1" s="90"/>
+    <row r="838" ht="14.25" customHeight="1" s="90"/>
+    <row r="839" ht="14.25" customHeight="1" s="90"/>
+    <row r="840" ht="14.25" customHeight="1" s="90"/>
+    <row r="841" ht="14.25" customHeight="1" s="90"/>
+    <row r="842" ht="14.25" customHeight="1" s="90"/>
+    <row r="843" ht="14.25" customHeight="1" s="90"/>
+    <row r="844" ht="14.25" customHeight="1" s="90"/>
+    <row r="845" ht="14.25" customHeight="1" s="90"/>
+    <row r="846" ht="14.25" customHeight="1" s="90"/>
+    <row r="847" ht="14.25" customHeight="1" s="90"/>
+    <row r="848" ht="14.25" customHeight="1" s="90"/>
+    <row r="849" ht="14.25" customHeight="1" s="90"/>
+    <row r="850" ht="14.25" customHeight="1" s="90"/>
+    <row r="851" ht="14.25" customHeight="1" s="90"/>
+    <row r="852" ht="14.25" customHeight="1" s="90"/>
+    <row r="853" ht="14.25" customHeight="1" s="90"/>
+    <row r="854" ht="14.25" customHeight="1" s="90"/>
+    <row r="855" ht="14.25" customHeight="1" s="90"/>
+    <row r="856" ht="14.25" customHeight="1" s="90"/>
+    <row r="857" ht="14.25" customHeight="1" s="90"/>
+    <row r="858" ht="14.25" customHeight="1" s="90"/>
+    <row r="859" ht="14.25" customHeight="1" s="90"/>
+    <row r="860" ht="14.25" customHeight="1" s="90"/>
+    <row r="861" ht="14.25" customHeight="1" s="90"/>
+    <row r="862" ht="14.25" customHeight="1" s="90"/>
+    <row r="863" ht="14.25" customHeight="1" s="90"/>
+    <row r="864" ht="14.25" customHeight="1" s="90"/>
+    <row r="865" ht="14.25" customHeight="1" s="90"/>
+    <row r="866" ht="14.25" customHeight="1" s="90"/>
+    <row r="867" ht="14.25" customHeight="1" s="90"/>
+    <row r="868" ht="14.25" customHeight="1" s="90"/>
+    <row r="869" ht="14.25" customHeight="1" s="90"/>
+    <row r="870" ht="14.25" customHeight="1" s="90"/>
+    <row r="871" ht="14.25" customHeight="1" s="90"/>
+    <row r="872" ht="14.25" customHeight="1" s="90"/>
+    <row r="873" ht="14.25" customHeight="1" s="90"/>
+    <row r="874" ht="14.25" customHeight="1" s="90"/>
+    <row r="875" ht="14.25" customHeight="1" s="90"/>
+    <row r="876" ht="14.25" customHeight="1" s="90"/>
+    <row r="877" ht="14.25" customHeight="1" s="90"/>
+    <row r="878" ht="14.25" customHeight="1" s="90"/>
+    <row r="879" ht="14.25" customHeight="1" s="90"/>
+    <row r="880" ht="14.25" customHeight="1" s="90"/>
+    <row r="881" ht="14.25" customHeight="1" s="90"/>
+    <row r="882" ht="14.25" customHeight="1" s="90"/>
+    <row r="883" ht="14.25" customHeight="1" s="90"/>
+    <row r="884" ht="14.25" customHeight="1" s="90"/>
+    <row r="885" ht="14.25" customHeight="1" s="90"/>
+    <row r="886" ht="14.25" customHeight="1" s="90"/>
+    <row r="887" ht="14.25" customHeight="1" s="90"/>
+    <row r="888" ht="14.25" customHeight="1" s="90"/>
+    <row r="889" ht="14.25" customHeight="1" s="90"/>
+    <row r="890" ht="14.25" customHeight="1" s="90"/>
+    <row r="891" ht="14.25" customHeight="1" s="90"/>
+    <row r="892" ht="14.25" customHeight="1" s="90"/>
+    <row r="893" ht="14.25" customHeight="1" s="90"/>
+    <row r="894" ht="14.25" customHeight="1" s="90"/>
+    <row r="895" ht="14.25" customHeight="1" s="90"/>
+    <row r="896" ht="14.25" customHeight="1" s="90"/>
+    <row r="897" ht="14.25" customHeight="1" s="90"/>
+    <row r="898" ht="14.25" customHeight="1" s="90"/>
+    <row r="899" ht="14.25" customHeight="1" s="90"/>
+    <row r="900" ht="14.25" customHeight="1" s="90"/>
+    <row r="901" ht="14.25" customHeight="1" s="90"/>
+    <row r="902" ht="14.25" customHeight="1" s="90"/>
+    <row r="903" ht="14.25" customHeight="1" s="90"/>
+    <row r="904" ht="14.25" customHeight="1" s="90"/>
+    <row r="905" ht="14.25" customHeight="1" s="90"/>
+    <row r="906" ht="14.25" customHeight="1" s="90"/>
+    <row r="907" ht="14.25" customHeight="1" s="90"/>
+    <row r="908" ht="14.25" customHeight="1" s="90"/>
+    <row r="909" ht="14.25" customHeight="1" s="90"/>
+    <row r="910" ht="14.25" customHeight="1" s="90"/>
+    <row r="911" ht="14.25" customHeight="1" s="90"/>
+    <row r="912" ht="14.25" customHeight="1" s="90"/>
+    <row r="913" ht="14.25" customHeight="1" s="90"/>
+    <row r="914" ht="14.25" customHeight="1" s="90"/>
+    <row r="915" ht="14.25" customHeight="1" s="90"/>
+    <row r="916" ht="14.25" customHeight="1" s="90"/>
+    <row r="917" ht="14.25" customHeight="1" s="90"/>
+    <row r="918" ht="14.25" customHeight="1" s="90"/>
+    <row r="919" ht="14.25" customHeight="1" s="90"/>
+    <row r="920" ht="14.25" customHeight="1" s="90"/>
+    <row r="921" ht="14.25" customHeight="1" s="90"/>
+    <row r="922" ht="14.25" customHeight="1" s="90"/>
+    <row r="923" ht="14.25" customHeight="1" s="90"/>
+    <row r="924" ht="14.25" customHeight="1" s="90"/>
+    <row r="925" ht="14.25" customHeight="1" s="90"/>
+    <row r="926" ht="14.25" customHeight="1" s="90"/>
+    <row r="927" ht="14.25" customHeight="1" s="90"/>
+    <row r="928" ht="14.25" customHeight="1" s="90"/>
+    <row r="929" ht="14.25" customHeight="1" s="90"/>
+    <row r="930" ht="14.25" customHeight="1" s="90"/>
+    <row r="931" ht="14.25" customHeight="1" s="90"/>
+    <row r="932" ht="14.25" customHeight="1" s="90"/>
+    <row r="933" ht="14.25" customHeight="1" s="90"/>
+    <row r="934" ht="14.25" customHeight="1" s="90"/>
+    <row r="935" ht="14.25" customHeight="1" s="90"/>
+    <row r="936" ht="14.25" customHeight="1" s="90"/>
+    <row r="937" ht="14.25" customHeight="1" s="90"/>
+    <row r="938" ht="14.25" customHeight="1" s="90"/>
+    <row r="939" ht="14.25" customHeight="1" s="90"/>
+    <row r="940" ht="14.25" customHeight="1" s="90"/>
+    <row r="941" ht="14.25" customHeight="1" s="90"/>
+    <row r="942" ht="14.25" customHeight="1" s="90"/>
+    <row r="943" ht="14.25" customHeight="1" s="90"/>
+    <row r="944" ht="14.25" customHeight="1" s="90"/>
+    <row r="945" ht="14.25" customHeight="1" s="90"/>
+    <row r="946" ht="14.25" customHeight="1" s="90"/>
+    <row r="947" ht="14.25" customHeight="1" s="90"/>
+    <row r="948" ht="14.25" customHeight="1" s="90"/>
+    <row r="949" ht="14.25" customHeight="1" s="90"/>
+    <row r="950" ht="14.25" customHeight="1" s="90"/>
+    <row r="951" ht="14.25" customHeight="1" s="90"/>
+    <row r="952" ht="14.25" customHeight="1" s="90"/>
+    <row r="953" ht="14.25" customHeight="1" s="90"/>
+    <row r="954" ht="14.25" customHeight="1" s="90"/>
+    <row r="955" ht="14.25" customHeight="1" s="90"/>
+    <row r="956" ht="14.25" customHeight="1" s="90"/>
+    <row r="957" ht="14.25" customHeight="1" s="90"/>
+    <row r="958" ht="14.25" customHeight="1" s="90"/>
+    <row r="959" ht="14.25" customHeight="1" s="90"/>
+    <row r="960" ht="14.25" customHeight="1" s="90"/>
+    <row r="961" ht="14.25" customHeight="1" s="90"/>
+    <row r="962" ht="14.25" customHeight="1" s="90"/>
+    <row r="963" ht="14.25" customHeight="1" s="90"/>
+    <row r="964" ht="14.25" customHeight="1" s="90"/>
+    <row r="965" ht="14.25" customHeight="1" s="90"/>
+    <row r="966" ht="14.25" customHeight="1" s="90"/>
+    <row r="967" ht="14.25" customHeight="1" s="90"/>
+    <row r="968" ht="14.25" customHeight="1" s="90"/>
+    <row r="969" ht="14.25" customHeight="1" s="90"/>
+    <row r="970" ht="14.25" customHeight="1" s="90"/>
+    <row r="971" ht="14.25" customHeight="1" s="90"/>
+    <row r="972" ht="14.25" customHeight="1" s="90"/>
+    <row r="973" ht="14.25" customHeight="1" s="90"/>
+    <row r="974" ht="14.25" customHeight="1" s="90"/>
+    <row r="975" ht="14.25" customHeight="1" s="90"/>
+    <row r="976" ht="14.25" customHeight="1" s="90"/>
+    <row r="977" ht="14.25" customHeight="1" s="90"/>
+    <row r="978" ht="14.25" customHeight="1" s="90"/>
+    <row r="979" ht="14.25" customHeight="1" s="90"/>
+    <row r="980" ht="14.25" customHeight="1" s="90"/>
+    <row r="981" ht="14.25" customHeight="1" s="90"/>
+    <row r="982" ht="14.25" customHeight="1" s="90"/>
+    <row r="983" ht="14.25" customHeight="1" s="90"/>
+    <row r="984" ht="14.25" customHeight="1" s="90"/>
+    <row r="985" ht="14.25" customHeight="1" s="90"/>
+    <row r="986" ht="14.25" customHeight="1" s="90"/>
+    <row r="987" ht="14.25" customHeight="1" s="90"/>
+    <row r="988" ht="14.25" customHeight="1" s="90"/>
+    <row r="989" ht="14.25" customHeight="1" s="90"/>
+    <row r="990" ht="14.25" customHeight="1" s="90"/>
+    <row r="991" ht="14.25" customHeight="1" s="90"/>
+    <row r="992" ht="14.25" customHeight="1" s="90"/>
+    <row r="993" ht="14.25" customHeight="1" s="90"/>
+    <row r="994" ht="14.25" customHeight="1" s="90"/>
+    <row r="995" ht="14.25" customHeight="1" s="90"/>
+    <row r="996" ht="14.25" customHeight="1" s="90"/>
+    <row r="997" ht="14.25" customHeight="1" s="90"/>
+    <row r="998" ht="14.25" customHeight="1" s="90"/>
+    <row r="999" ht="14.25" customHeight="1" s="90"/>
+    <row r="1000" ht="14.25" customHeight="1" s="90"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\cortexkitchen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE45B357-BC7A-4EBF-9C4A-856A3D816EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D201C1A-296E-4B54-9A50-042696BEA2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="1004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1003">
   <si>
     <t>Phase 6A — Restaurant OS: compliance fixes + autonomous procurement + operator features</t>
   </si>
@@ -744,9 +744,6 @@
   </si>
   <si>
     <t>End-to-end test/debug pass across every Phase 6A feature</t>
-  </si>
-  <si>
-    <t>Live, hands-on test of every feature shipped this milestone (P6-A1-A41) end-to-end against the running app, not just unit tests/typecheck -- fix bugs found, and expand capabilities wherever a real gap surfaces during testing (matching how OccupancyEnricher's live-testing bugs were caught during P6-A21-A24). Covers both backend flows and frontend pages in an actual browser session.</t>
   </si>
   <si>
     <t>fix: end-to-end hardening pass across Phase 6A</t>
@@ -3731,42 +3728,54 @@
     <xf numFmtId="0" fontId="26" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3775,31 +3784,19 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4029,33 +4026,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
-        <v>280</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
-      <c r="W1" s="95"/>
-      <c r="X1" s="95"/>
-      <c r="Y1" s="95"/>
+      <c r="A1" s="95" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
+      <c r="W1" s="96"/>
+      <c r="X1" s="96"/>
+      <c r="Y1" s="96"/>
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4088,10 +4085,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>281</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>282</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -4120,10 +4117,10 @@
     </row>
     <row r="4" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -4152,10 +4149,10 @@
     </row>
     <row r="5" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>285</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>286</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -4184,10 +4181,10 @@
     </row>
     <row r="6" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -4272,16 +4269,16 @@
     </row>
     <row r="9" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>290</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>291</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -4308,7 +4305,7 @@
     </row>
     <row r="10" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>23</v>
@@ -4317,7 +4314,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -4344,7 +4341,7 @@
     </row>
     <row r="11" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>23</v>
@@ -4353,7 +4350,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -4380,7 +4377,7 @@
     </row>
     <row r="12" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>23</v>
@@ -4389,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -4416,7 +4413,7 @@
     </row>
     <row r="13" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>23</v>
@@ -4425,7 +4422,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -4452,7 +4449,7 @@
     </row>
     <row r="14" spans="1:26" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>23</v>
@@ -4461,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -4488,7 +4485,7 @@
     </row>
     <row r="15" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>23</v>
@@ -4497,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -4524,16 +4521,16 @@
     </row>
     <row r="16" spans="1:26" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>304</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>305</v>
       </c>
       <c r="C16" s="15">
         <v>0.78129999999999999</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10194,7 +10191,7 @@
     </row>
     <row r="219" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B219" t="s">
         <v>203</v>
@@ -10203,7 +10200,7 @@
         <v>0</v>
       </c>
       <c r="D219" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="220" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -11017,53 +11014,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="98" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+    </row>
+    <row r="2" spans="1:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="103" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-    </row>
-    <row r="2" spans="1:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="99" t="s">
-        <v>310</v>
-      </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="93"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="90"/>
     </row>
     <row r="3" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>1</v>
@@ -11075,10 +11072,10 @@
         <v>4</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>312</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>313</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>8</v>
@@ -11096,63 +11093,63 @@
         <v>12</v>
       </c>
       <c r="M3" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>314</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>315</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="P3" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="Q3" s="5" t="s">
-        <v>317</v>
-      </c>
     </row>
     <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="98" t="s">
-        <v>292</v>
-      </c>
-      <c r="B4" s="92"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="92"/>
-      <c r="L4" s="92"/>
-      <c r="M4" s="92"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="92"/>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="93"/>
+      <c r="A4" s="102" t="s">
+        <v>291</v>
+      </c>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="90"/>
     </row>
     <row r="5" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="G5" s="17" t="s">
         <v>321</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>322</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>23</v>
@@ -11177,33 +11174,33 @@
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q5" s="17" t="s">
         <v>323</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B6" s="21">
         <v>2</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>325</v>
       </c>
-      <c r="D6" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="E6" s="22" t="s">
+      <c r="F6" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="G6" s="22" t="s">
         <v>327</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>328</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>23</v>
@@ -11227,36 +11224,36 @@
         <v>1</v>
       </c>
       <c r="O6" s="22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P6" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q6" s="22" t="s">
         <v>329</v>
-      </c>
-      <c r="Q6" s="22" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B7" s="16">
         <v>3</v>
       </c>
       <c r="C7" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="F7" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="G7" s="17" t="s">
         <v>333</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>334</v>
       </c>
       <c r="H7" s="18" t="s">
         <v>23</v>
@@ -11280,36 +11277,36 @@
         <v>1</v>
       </c>
       <c r="O7" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P7" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q7" s="17" t="s">
         <v>329</v>
-      </c>
-      <c r="Q7" s="17" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B8" s="21">
         <v>4</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="D8" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="E8" s="22" t="s">
+      <c r="F8" s="22" t="s">
         <v>336</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="G8" s="22" t="s">
         <v>337</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>338</v>
       </c>
       <c r="H8" s="18" t="s">
         <v>23</v>
@@ -11333,36 +11330,36 @@
         <v>1</v>
       </c>
       <c r="O8" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P8" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q8" s="22" t="s">
         <v>329</v>
-      </c>
-      <c r="Q8" s="22" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B9" s="16">
         <v>5</v>
       </c>
       <c r="C9" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="F9" s="17" t="s">
         <v>340</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="G9" s="17" t="s">
         <v>341</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>342</v>
       </c>
       <c r="H9" s="18" t="s">
         <v>23</v>
@@ -11377,66 +11374,66 @@
         <v>46096</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N9" s="20">
         <v>1</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P9" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q9" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="Q9" s="17" t="s">
-        <v>330</v>
-      </c>
     </row>
     <row r="10" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="98" t="s">
-        <v>294</v>
-      </c>
-      <c r="B10" s="92"/>
-      <c r="C10" s="92"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
-      <c r="L10" s="92"/>
-      <c r="M10" s="92"/>
-      <c r="N10" s="92"/>
-      <c r="O10" s="92"/>
-      <c r="P10" s="92"/>
-      <c r="Q10" s="93"/>
+      <c r="A10" s="102" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="89"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="89"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
+      <c r="M10" s="89"/>
+      <c r="N10" s="89"/>
+      <c r="O10" s="89"/>
+      <c r="P10" s="89"/>
+      <c r="Q10" s="90"/>
     </row>
     <row r="11" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B11" s="21">
         <v>7</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>49</v>
       </c>
       <c r="E11" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="F11" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="G11" s="22" t="s">
         <v>346</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>347</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>23</v>
@@ -11448,48 +11445,48 @@
         <v>25</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M11" s="21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N11" s="24">
         <v>1</v>
       </c>
       <c r="O11" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="P11" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="P11" s="22" t="s">
+      <c r="Q11" s="22" t="s">
         <v>349</v>
-      </c>
-      <c r="Q11" s="22" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B12" s="16">
         <v>8</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>59</v>
       </c>
       <c r="E12" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="F12" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="G12" s="17" t="s">
         <v>353</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>354</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>23</v>
@@ -11513,36 +11510,36 @@
         <v>1</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q12" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B13" s="21">
         <v>9</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>49</v>
       </c>
       <c r="E13" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>357</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="G13" s="22" t="s">
         <v>358</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>359</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>23</v>
@@ -11566,36 +11563,36 @@
         <v>1</v>
       </c>
       <c r="O13" s="22" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P13" s="22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B14" s="16">
         <v>10</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>183</v>
       </c>
       <c r="E14" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="F14" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="G14" s="17" t="s">
         <v>363</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>364</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>23</v>
@@ -11619,36 +11616,36 @@
         <v>1</v>
       </c>
       <c r="O14" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q14" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B15" s="21">
         <v>11</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D15" s="22" t="s">
         <v>49</v>
       </c>
       <c r="E15" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="F15" s="22" t="s">
         <v>367</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="G15" s="22" t="s">
         <v>368</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>369</v>
       </c>
       <c r="H15" s="18" t="s">
         <v>23</v>
@@ -11672,36 +11669,36 @@
         <v>1</v>
       </c>
       <c r="O15" s="22" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P15" s="22" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B16" s="16">
         <v>12</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>49</v>
       </c>
       <c r="E16" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="F16" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="G16" s="17" t="s">
         <v>373</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>374</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>23</v>
@@ -11725,36 +11722,36 @@
         <v>1</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q16" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B17" s="21">
         <v>13</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>375</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>376</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="22" t="s">
         <v>377</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="F17" s="22" t="s">
         <v>378</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="G17" s="22" t="s">
         <v>379</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>380</v>
       </c>
       <c r="H17" s="18" t="s">
         <v>23</v>
@@ -11778,36 +11775,36 @@
         <v>1</v>
       </c>
       <c r="O17" s="22" t="s">
+        <v>380</v>
+      </c>
+      <c r="P17" s="22" t="s">
         <v>381</v>
       </c>
-      <c r="P17" s="22" t="s">
-        <v>382</v>
-      </c>
       <c r="Q17" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B18" s="16">
         <v>14</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="F18" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="G18" s="17" t="s">
         <v>385</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>386</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>23</v>
@@ -11831,36 +11828,36 @@
         <v>1</v>
       </c>
       <c r="O18" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="P18" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="P18" s="17" t="s">
-        <v>388</v>
-      </c>
       <c r="Q18" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B19" s="21">
         <v>15</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>49</v>
       </c>
       <c r="E19" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="F19" s="22" t="s">
         <v>390</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="G19" s="22" t="s">
         <v>391</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>392</v>
       </c>
       <c r="H19" s="18" t="s">
         <v>23</v>
@@ -11884,36 +11881,36 @@
         <v>1</v>
       </c>
       <c r="O19" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="P19" s="22" t="s">
         <v>393</v>
       </c>
-      <c r="P19" s="22" t="s">
-        <v>394</v>
-      </c>
       <c r="Q19" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B20" s="16">
         <v>16</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>67</v>
       </c>
       <c r="E20" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="F20" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="G20" s="17" t="s">
         <v>397</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>398</v>
       </c>
       <c r="H20" s="18" t="s">
         <v>23</v>
@@ -11937,36 +11934,36 @@
         <v>1</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Q20" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B21" s="21">
         <v>17</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>400</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>401</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="F21" s="22" t="s">
         <v>402</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="G21" s="22" t="s">
         <v>403</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>404</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>23</v>
@@ -11990,36 +11987,36 @@
         <v>1</v>
       </c>
       <c r="O21" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="P21" s="22" t="s">
         <v>405</v>
       </c>
-      <c r="P21" s="22" t="s">
-        <v>406</v>
-      </c>
       <c r="Q21" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B22" s="16">
         <v>18</v>
       </c>
       <c r="C22" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="E22" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="E22" s="17" t="s">
+      <c r="F22" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="F22" s="17" t="s">
-        <v>409</v>
-      </c>
       <c r="G22" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>23</v>
@@ -12043,57 +12040,57 @@
         <v>1</v>
       </c>
       <c r="O22" s="17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P22" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q22" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="Q22" s="17" t="s">
-        <v>411</v>
-      </c>
     </row>
     <row r="23" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="97" t="s">
-        <v>296</v>
-      </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="92"/>
-      <c r="O23" s="92"/>
-      <c r="P23" s="92"/>
-      <c r="Q23" s="93"/>
+      <c r="A23" s="99" t="s">
+        <v>295</v>
+      </c>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="89"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="89"/>
+      <c r="N23" s="89"/>
+      <c r="O23" s="89"/>
+      <c r="P23" s="89"/>
+      <c r="Q23" s="90"/>
     </row>
     <row r="24" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B24" s="21">
         <v>19</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>413</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="F24" s="22" t="s">
         <v>414</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="G24" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>416</v>
       </c>
       <c r="H24" s="18" t="s">
         <v>23</v>
@@ -12117,36 +12114,36 @@
         <v>1</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="P24" s="22" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q24" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B25" s="25">
         <v>20</v>
       </c>
       <c r="C25" s="26" t="s">
+        <v>417</v>
+      </c>
+      <c r="D25" s="26" t="s">
         <v>418</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="E25" s="26" t="s">
         <v>419</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="F25" s="26" t="s">
         <v>420</v>
       </c>
-      <c r="F25" s="26" t="s">
+      <c r="G25" s="26" t="s">
         <v>421</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>422</v>
       </c>
       <c r="H25" s="18" t="s">
         <v>23</v>
@@ -12170,36 +12167,36 @@
         <v>1</v>
       </c>
       <c r="O25" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P25" s="26" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q25" s="26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B26" s="21">
         <v>21</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>423</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>425</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="F26" s="22" t="s">
         <v>426</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="G26" s="22" t="s">
         <v>427</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>428</v>
       </c>
       <c r="H26" s="18" t="s">
         <v>23</v>
@@ -12223,36 +12220,36 @@
         <v>1</v>
       </c>
       <c r="O26" s="22" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="P26" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q26" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B27" s="25">
         <v>22</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D27" s="26" t="s">
         <v>67</v>
       </c>
       <c r="E27" s="26" t="s">
+        <v>430</v>
+      </c>
+      <c r="F27" s="26" t="s">
         <v>431</v>
       </c>
-      <c r="F27" s="26" t="s">
+      <c r="G27" s="26" t="s">
         <v>432</v>
-      </c>
-      <c r="G27" s="26" t="s">
-        <v>433</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>23</v>
@@ -12276,36 +12273,36 @@
         <v>1</v>
       </c>
       <c r="O27" s="26" t="s">
+        <v>433</v>
+      </c>
+      <c r="P27" s="26" t="s">
         <v>434</v>
       </c>
-      <c r="P27" s="26" t="s">
+      <c r="Q27" s="26" t="s">
         <v>435</v>
-      </c>
-      <c r="Q27" s="26" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B28" s="21">
         <v>23</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="E28" s="22" t="s">
         <v>437</v>
       </c>
-      <c r="D28" s="22" t="s">
-        <v>401</v>
-      </c>
-      <c r="E28" s="22" t="s">
+      <c r="F28" s="22" t="s">
         <v>438</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="G28" s="22" t="s">
         <v>439</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>440</v>
       </c>
       <c r="H28" s="18" t="s">
         <v>23</v>
@@ -12329,36 +12326,36 @@
         <v>1</v>
       </c>
       <c r="O28" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="P28" s="22" t="s">
         <v>441</v>
       </c>
-      <c r="P28" s="22" t="s">
-        <v>442</v>
-      </c>
       <c r="Q28" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B29" s="25">
         <v>24</v>
       </c>
       <c r="C29" s="26" t="s">
+        <v>442</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E29" s="26" t="s">
         <v>443</v>
       </c>
-      <c r="D29" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="E29" s="26" t="s">
+      <c r="F29" s="26" t="s">
         <v>444</v>
       </c>
-      <c r="F29" s="26" t="s">
-        <v>445</v>
-      </c>
       <c r="G29" s="26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H29" s="18" t="s">
         <v>23</v>
@@ -12382,57 +12379,57 @@
         <v>1</v>
       </c>
       <c r="O29" s="26" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P29" s="26" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Q29" s="26" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="97" t="s">
-        <v>298</v>
-      </c>
-      <c r="B30" s="92"/>
-      <c r="C30" s="92"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="92"/>
-      <c r="G30" s="92"/>
-      <c r="H30" s="92"/>
-      <c r="I30" s="92"/>
-      <c r="J30" s="92"/>
-      <c r="K30" s="92"/>
-      <c r="L30" s="92"/>
-      <c r="M30" s="92"/>
-      <c r="N30" s="92"/>
-      <c r="O30" s="92"/>
-      <c r="P30" s="92"/>
-      <c r="Q30" s="93"/>
+      <c r="A30" s="99" t="s">
+        <v>297</v>
+      </c>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
+      <c r="L30" s="89"/>
+      <c r="M30" s="89"/>
+      <c r="N30" s="89"/>
+      <c r="O30" s="89"/>
+      <c r="P30" s="89"/>
+      <c r="Q30" s="90"/>
     </row>
     <row r="31" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B31" s="21">
         <v>25</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D31" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E31" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="F31" s="22" t="s">
         <v>448</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="G31" s="22" t="s">
         <v>449</v>
-      </c>
-      <c r="G31" s="22" t="s">
-        <v>450</v>
       </c>
       <c r="H31" s="18" t="s">
         <v>23</v>
@@ -12456,36 +12453,36 @@
         <v>1</v>
       </c>
       <c r="O31" s="22" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P31" s="22" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q31" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B32" s="25">
         <v>26</v>
       </c>
       <c r="C32" s="26" t="s">
+        <v>451</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>400</v>
+      </c>
+      <c r="E32" s="26" t="s">
         <v>452</v>
       </c>
-      <c r="D32" s="26" t="s">
-        <v>401</v>
-      </c>
-      <c r="E32" s="26" t="s">
+      <c r="F32" s="26" t="s">
         <v>453</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="G32" s="26" t="s">
         <v>454</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>455</v>
       </c>
       <c r="H32" s="18" t="s">
         <v>23</v>
@@ -12509,36 +12506,36 @@
         <v>1</v>
       </c>
       <c r="O32" s="26" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P32" s="26" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q32" s="26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B33" s="21">
         <v>27</v>
       </c>
       <c r="C33" s="22" t="s">
+        <v>456</v>
+      </c>
+      <c r="D33" s="22" t="s">
         <v>457</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="E33" s="22" t="s">
         <v>458</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="F33" s="22" t="s">
         <v>459</v>
       </c>
-      <c r="F33" s="22" t="s">
+      <c r="G33" s="22" t="s">
         <v>460</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>461</v>
       </c>
       <c r="H33" s="18" t="s">
         <v>23</v>
@@ -12562,36 +12559,36 @@
         <v>1</v>
       </c>
       <c r="O33" s="22" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P33" s="22" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q33" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B34" s="25">
         <v>28</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D34" s="26" t="s">
         <v>29</v>
       </c>
       <c r="E34" s="26" t="s">
+        <v>463</v>
+      </c>
+      <c r="F34" s="26" t="s">
         <v>464</v>
       </c>
-      <c r="F34" s="26" t="s">
+      <c r="G34" s="26" t="s">
         <v>465</v>
-      </c>
-      <c r="G34" s="26" t="s">
-        <v>466</v>
       </c>
       <c r="H34" s="18" t="s">
         <v>23</v>
@@ -12615,36 +12612,36 @@
         <v>1</v>
       </c>
       <c r="O34" s="26" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P34" s="26" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q34" s="26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B35" s="21">
         <v>29</v>
       </c>
       <c r="C35" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="E35" s="22" t="s">
         <v>468</v>
       </c>
-      <c r="D35" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="E35" s="22" t="s">
+      <c r="F35" s="22" t="s">
         <v>469</v>
       </c>
-      <c r="F35" s="22" t="s">
-        <v>470</v>
-      </c>
       <c r="G35" s="22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H35" s="18" t="s">
         <v>23</v>
@@ -12668,57 +12665,57 @@
         <v>1</v>
       </c>
       <c r="O35" s="22" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P35" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q35" s="22" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="100" t="s">
         <v>471</v>
       </c>
-      <c r="Q35" s="22" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="102" t="s">
-        <v>472</v>
-      </c>
-      <c r="B36" s="92"/>
-      <c r="C36" s="92"/>
-      <c r="D36" s="92"/>
-      <c r="E36" s="92"/>
-      <c r="F36" s="92"/>
-      <c r="G36" s="92"/>
-      <c r="H36" s="92"/>
-      <c r="I36" s="92"/>
-      <c r="J36" s="92"/>
-      <c r="K36" s="92"/>
-      <c r="L36" s="92"/>
-      <c r="M36" s="92"/>
-      <c r="N36" s="92"/>
-      <c r="O36" s="92"/>
-      <c r="P36" s="92"/>
-      <c r="Q36" s="93"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="89"/>
+      <c r="D36" s="89"/>
+      <c r="E36" s="89"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="89"/>
+      <c r="H36" s="89"/>
+      <c r="I36" s="89"/>
+      <c r="J36" s="89"/>
+      <c r="K36" s="89"/>
+      <c r="L36" s="89"/>
+      <c r="M36" s="89"/>
+      <c r="N36" s="89"/>
+      <c r="O36" s="89"/>
+      <c r="P36" s="89"/>
+      <c r="Q36" s="90"/>
     </row>
     <row r="37" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="29" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B37" s="29">
         <v>30</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D37" s="30" t="s">
         <v>183</v>
       </c>
       <c r="E37" s="30" t="s">
+        <v>473</v>
+      </c>
+      <c r="F37" s="30" t="s">
         <v>474</v>
       </c>
-      <c r="F37" s="30" t="s">
+      <c r="G37" s="30" t="s">
         <v>475</v>
-      </c>
-      <c r="G37" s="30" t="s">
-        <v>476</v>
       </c>
       <c r="H37" s="18" t="s">
         <v>23</v>
@@ -12742,36 +12739,36 @@
         <v>1</v>
       </c>
       <c r="O37" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="P37" s="30" t="s">
         <v>477</v>
       </c>
-      <c r="P37" s="30" t="s">
-        <v>478</v>
-      </c>
       <c r="Q37" s="30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B38" s="21">
         <v>31</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D38" s="22" t="s">
         <v>67</v>
       </c>
       <c r="E38" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="G38" s="22" t="s">
         <v>480</v>
-      </c>
-      <c r="F38" s="22" t="s">
-        <v>480</v>
-      </c>
-      <c r="G38" s="22" t="s">
-        <v>481</v>
       </c>
       <c r="H38" s="18" t="s">
         <v>23</v>
@@ -12795,36 +12792,36 @@
         <v>1</v>
       </c>
       <c r="O38" s="22" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P38" s="22" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q38" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="29" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B39" s="29">
         <v>31</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D39" s="30" t="s">
         <v>67</v>
       </c>
       <c r="E39" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="G39" s="30" t="s">
         <v>484</v>
-      </c>
-      <c r="F39" s="30" t="s">
-        <v>480</v>
-      </c>
-      <c r="G39" s="30" t="s">
-        <v>485</v>
       </c>
       <c r="H39" s="18" t="s">
         <v>23</v>
@@ -12848,57 +12845,57 @@
         <v>1</v>
       </c>
       <c r="O39" s="30" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P39" s="30" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q39" s="30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="96" t="s">
-        <v>300</v>
-      </c>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="92"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
-      <c r="M40" s="92"/>
-      <c r="N40" s="92"/>
-      <c r="O40" s="92"/>
-      <c r="P40" s="92"/>
-      <c r="Q40" s="93"/>
+      <c r="A40" s="101" t="s">
+        <v>299</v>
+      </c>
+      <c r="B40" s="89"/>
+      <c r="C40" s="89"/>
+      <c r="D40" s="89"/>
+      <c r="E40" s="89"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="89"/>
+      <c r="H40" s="89"/>
+      <c r="I40" s="89"/>
+      <c r="J40" s="89"/>
+      <c r="K40" s="89"/>
+      <c r="L40" s="89"/>
+      <c r="M40" s="89"/>
+      <c r="N40" s="89"/>
+      <c r="O40" s="89"/>
+      <c r="P40" s="89"/>
+      <c r="Q40" s="90"/>
     </row>
     <row r="41" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B41" s="21">
         <v>1</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D41" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E41" s="22" t="s">
+        <v>486</v>
+      </c>
+      <c r="F41" s="22" t="s">
         <v>487</v>
       </c>
-      <c r="F41" s="22" t="s">
+      <c r="G41" s="22" t="s">
         <v>488</v>
-      </c>
-      <c r="G41" s="22" t="s">
-        <v>489</v>
       </c>
       <c r="H41" s="18" t="s">
         <v>23</v>
@@ -12922,36 +12919,36 @@
         <v>1</v>
       </c>
       <c r="O41" s="22" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P41" s="22" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q41" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B42" s="16">
         <v>2</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D42" s="17" t="s">
         <v>169</v>
       </c>
       <c r="E42" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="F42" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="G42" s="17" t="s">
         <v>493</v>
-      </c>
-      <c r="G42" s="17" t="s">
-        <v>494</v>
       </c>
       <c r="H42" s="18" t="s">
         <v>23</v>
@@ -12975,36 +12972,36 @@
         <v>1</v>
       </c>
       <c r="O42" s="17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P42" s="17" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q42" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B43" s="21">
         <v>3</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E43" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="F43" s="22" t="s">
         <v>497</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="G43" s="22" t="s">
         <v>498</v>
-      </c>
-      <c r="G43" s="22" t="s">
-        <v>499</v>
       </c>
       <c r="H43" s="18" t="s">
         <v>23</v>
@@ -13028,36 +13025,36 @@
         <v>1</v>
       </c>
       <c r="O43" s="22" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P43" s="22" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q43" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B44" s="16">
         <v>4</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D44" s="17" t="s">
         <v>169</v>
       </c>
       <c r="E44" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="F44" s="17" t="s">
         <v>502</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="G44" s="17" t="s">
         <v>503</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>504</v>
       </c>
       <c r="H44" s="18" t="s">
         <v>23</v>
@@ -13081,36 +13078,36 @@
         <v>1</v>
       </c>
       <c r="O44" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P44" s="17" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="Q44" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B45" s="21">
         <v>5</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D45" s="22" t="s">
         <v>169</v>
       </c>
       <c r="E45" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="F45" s="22" t="s">
         <v>507</v>
       </c>
-      <c r="F45" s="22" t="s">
+      <c r="G45" s="22" t="s">
         <v>508</v>
-      </c>
-      <c r="G45" s="22" t="s">
-        <v>509</v>
       </c>
       <c r="H45" s="18" t="s">
         <v>23</v>
@@ -13134,36 +13131,36 @@
         <v>1</v>
       </c>
       <c r="O45" s="22" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="P45" s="22" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="Q45" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B46" s="16">
         <v>6</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D46" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E46" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="F46" s="17" t="s">
         <v>512</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="G46" s="17" t="s">
         <v>513</v>
-      </c>
-      <c r="G46" s="17" t="s">
-        <v>514</v>
       </c>
       <c r="H46" s="18" t="s">
         <v>23</v>
@@ -13187,36 +13184,36 @@
         <v>1</v>
       </c>
       <c r="O46" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P46" s="17" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Q46" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B47" s="21">
         <v>7</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D47" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E47" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="F47" s="22" t="s">
         <v>517</v>
       </c>
-      <c r="F47" s="22" t="s">
+      <c r="G47" s="22" t="s">
         <v>518</v>
-      </c>
-      <c r="G47" s="22" t="s">
-        <v>519</v>
       </c>
       <c r="H47" s="18" t="s">
         <v>23</v>
@@ -13240,36 +13237,36 @@
         <v>1</v>
       </c>
       <c r="O47" s="22" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P47" s="22" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="Q47" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B48" s="16">
         <v>8</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D48" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E48" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="F48" s="17" t="s">
         <v>522</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="G48" s="17" t="s">
         <v>523</v>
-      </c>
-      <c r="G48" s="17" t="s">
-        <v>524</v>
       </c>
       <c r="H48" s="18" t="s">
         <v>23</v>
@@ -13293,36 +13290,36 @@
         <v>1</v>
       </c>
       <c r="O48" s="17" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="P48" s="17" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="Q48" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B49" s="21">
         <v>9</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D49" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E49" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="F49" s="22" t="s">
         <v>527</v>
       </c>
-      <c r="F49" s="22" t="s">
+      <c r="G49" s="22" t="s">
         <v>528</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>529</v>
       </c>
       <c r="H49" s="18" t="s">
         <v>23</v>
@@ -13346,36 +13343,36 @@
         <v>1</v>
       </c>
       <c r="O49" s="22" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P49" s="22" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="Q49" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B50" s="16">
         <v>10</v>
       </c>
       <c r="C50" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="E50" s="17" t="s">
         <v>531</v>
       </c>
-      <c r="D50" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="E50" s="17" t="s">
+      <c r="F50" s="17" t="s">
         <v>532</v>
       </c>
-      <c r="F50" s="17" t="s">
+      <c r="G50" s="17" t="s">
         <v>533</v>
-      </c>
-      <c r="G50" s="17" t="s">
-        <v>534</v>
       </c>
       <c r="H50" s="18" t="s">
         <v>23</v>
@@ -13399,36 +13396,36 @@
         <v>1</v>
       </c>
       <c r="O50" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P50" s="17" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="Q50" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B51" s="21">
         <v>11</v>
       </c>
       <c r="C51" s="22" t="s">
+        <v>535</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="E51" s="22" t="s">
         <v>536</v>
       </c>
-      <c r="D51" s="22" t="s">
-        <v>401</v>
-      </c>
-      <c r="E51" s="22" t="s">
+      <c r="F51" s="22" t="s">
         <v>537</v>
       </c>
-      <c r="F51" s="22" t="s">
+      <c r="G51" s="22" t="s">
         <v>538</v>
-      </c>
-      <c r="G51" s="22" t="s">
-        <v>539</v>
       </c>
       <c r="H51" s="18" t="s">
         <v>23</v>
@@ -13452,36 +13449,36 @@
         <v>1</v>
       </c>
       <c r="O51" s="22" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P51" s="22" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Q51" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B52" s="16">
         <v>12</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D52" s="17" t="s">
         <v>59</v>
       </c>
       <c r="E52" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="F52" s="17" t="s">
         <v>542</v>
       </c>
-      <c r="F52" s="17" t="s">
+      <c r="G52" s="17" t="s">
         <v>543</v>
-      </c>
-      <c r="G52" s="17" t="s">
-        <v>544</v>
       </c>
       <c r="H52" s="18" t="s">
         <v>23</v>
@@ -13505,36 +13502,36 @@
         <v>1</v>
       </c>
       <c r="O52" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P52" s="17" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q52" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B53" s="21">
         <v>13</v>
       </c>
       <c r="C53" s="22" t="s">
+        <v>545</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="E53" s="22" t="s">
         <v>546</v>
       </c>
-      <c r="D53" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="E53" s="22" t="s">
+      <c r="F53" s="22" t="s">
         <v>547</v>
       </c>
-      <c r="F53" s="22" t="s">
-        <v>548</v>
-      </c>
       <c r="G53" s="22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H53" s="18" t="s">
         <v>23</v>
@@ -13558,57 +13555,57 @@
         <v>1</v>
       </c>
       <c r="O53" s="22" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P53" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="Q53" s="22" t="s">
         <v>549</v>
       </c>
-      <c r="Q53" s="22" t="s">
-        <v>550</v>
-      </c>
     </row>
     <row r="54" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="96" t="s">
-        <v>302</v>
-      </c>
-      <c r="B54" s="92"/>
-      <c r="C54" s="92"/>
-      <c r="D54" s="92"/>
-      <c r="E54" s="92"/>
-      <c r="F54" s="92"/>
-      <c r="G54" s="92"/>
-      <c r="H54" s="92"/>
-      <c r="I54" s="92"/>
-      <c r="J54" s="92"/>
-      <c r="K54" s="92"/>
-      <c r="L54" s="92"/>
-      <c r="M54" s="92"/>
-      <c r="N54" s="92"/>
-      <c r="O54" s="92"/>
-      <c r="P54" s="92"/>
-      <c r="Q54" s="93"/>
+      <c r="A54" s="101" t="s">
+        <v>301</v>
+      </c>
+      <c r="B54" s="89"/>
+      <c r="C54" s="89"/>
+      <c r="D54" s="89"/>
+      <c r="E54" s="89"/>
+      <c r="F54" s="89"/>
+      <c r="G54" s="89"/>
+      <c r="H54" s="89"/>
+      <c r="I54" s="89"/>
+      <c r="J54" s="89"/>
+      <c r="K54" s="89"/>
+      <c r="L54" s="89"/>
+      <c r="M54" s="89"/>
+      <c r="N54" s="89"/>
+      <c r="O54" s="89"/>
+      <c r="P54" s="89"/>
+      <c r="Q54" s="90"/>
     </row>
     <row r="55" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B55" s="16">
         <v>1</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D55" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E55" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="F55" s="17" t="s">
         <v>552</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="G55" s="17" t="s">
         <v>553</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>554</v>
       </c>
       <c r="H55" s="18" t="s">
         <v>23</v>
@@ -13626,36 +13623,36 @@
         <v>0</v>
       </c>
       <c r="O55" s="17" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="P55" s="17" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q55" s="17" t="s">
         <v>555</v>
-      </c>
-      <c r="Q55" s="17" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B56" s="21">
         <v>2</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D56" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E56" s="22" t="s">
+        <v>557</v>
+      </c>
+      <c r="F56" s="22" t="s">
         <v>558</v>
       </c>
-      <c r="F56" s="22" t="s">
+      <c r="G56" s="22" t="s">
         <v>559</v>
-      </c>
-      <c r="G56" s="22" t="s">
-        <v>560</v>
       </c>
       <c r="H56" s="18" t="s">
         <v>23</v>
@@ -13673,36 +13670,36 @@
         <v>0</v>
       </c>
       <c r="O56" s="22" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="P56" s="22" t="s">
+        <v>560</v>
+      </c>
+      <c r="Q56" s="22" t="s">
         <v>561</v>
-      </c>
-      <c r="Q56" s="22" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B57" s="16">
         <v>3</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D57" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E57" s="17" t="s">
+        <v>563</v>
+      </c>
+      <c r="F57" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="G57" s="17" t="s">
         <v>565</v>
-      </c>
-      <c r="G57" s="17" t="s">
-        <v>566</v>
       </c>
       <c r="H57" s="18" t="s">
         <v>23</v>
@@ -13720,36 +13717,36 @@
         <v>0</v>
       </c>
       <c r="O57" s="17" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="P57" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="Q57" s="17" t="s">
         <v>567</v>
-      </c>
-      <c r="Q57" s="17" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B58" s="21">
         <v>4</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D58" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E58" s="22" t="s">
+        <v>569</v>
+      </c>
+      <c r="F58" s="22" t="s">
         <v>570</v>
       </c>
-      <c r="F58" s="22" t="s">
+      <c r="G58" s="22" t="s">
         <v>571</v>
-      </c>
-      <c r="G58" s="22" t="s">
-        <v>572</v>
       </c>
       <c r="H58" s="18" t="s">
         <v>23</v>
@@ -13767,36 +13764,36 @@
         <v>0</v>
       </c>
       <c r="O58" s="22" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="P58" s="22" t="s">
+        <v>572</v>
+      </c>
+      <c r="Q58" s="22" t="s">
         <v>573</v>
-      </c>
-      <c r="Q58" s="22" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B59" s="16">
         <v>5</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D59" s="17" t="s">
         <v>59</v>
       </c>
       <c r="E59" s="17" t="s">
+        <v>575</v>
+      </c>
+      <c r="F59" s="17" t="s">
         <v>576</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="G59" s="17" t="s">
         <v>577</v>
-      </c>
-      <c r="G59" s="17" t="s">
-        <v>578</v>
       </c>
       <c r="H59" s="18" t="s">
         <v>23</v>
@@ -13814,36 +13811,36 @@
         <v>0</v>
       </c>
       <c r="O59" s="17" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="P59" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="Q59" s="17" t="s">
         <v>579</v>
-      </c>
-      <c r="Q59" s="17" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B60" s="21">
         <v>6</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D60" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E60" s="22" t="s">
+        <v>581</v>
+      </c>
+      <c r="F60" s="22" t="s">
         <v>582</v>
       </c>
-      <c r="F60" s="22" t="s">
+      <c r="G60" s="22" t="s">
         <v>583</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>584</v>
       </c>
       <c r="H60" s="18" t="s">
         <v>23</v>
@@ -13861,36 +13858,36 @@
         <v>0</v>
       </c>
       <c r="O60" s="22" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P60" s="22" t="s">
+        <v>584</v>
+      </c>
+      <c r="Q60" s="22" t="s">
         <v>585</v>
-      </c>
-      <c r="Q60" s="22" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B61" s="16">
         <v>7</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D61" s="17" t="s">
         <v>169</v>
       </c>
       <c r="E61" s="17" t="s">
+        <v>587</v>
+      </c>
+      <c r="F61" s="17" t="s">
         <v>588</v>
       </c>
-      <c r="F61" s="17" t="s">
+      <c r="G61" s="17" t="s">
         <v>589</v>
-      </c>
-      <c r="G61" s="17" t="s">
-        <v>590</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>23</v>
@@ -13908,36 +13905,36 @@
         <v>0</v>
       </c>
       <c r="O61" s="17" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P61" s="17" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q61" s="17" t="s">
         <v>591</v>
-      </c>
-      <c r="Q61" s="17" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B62" s="21">
         <v>8</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D62" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E62" s="22" t="s">
+        <v>593</v>
+      </c>
+      <c r="F62" s="22" t="s">
         <v>594</v>
       </c>
-      <c r="F62" s="22" t="s">
+      <c r="G62" s="22" t="s">
         <v>595</v>
-      </c>
-      <c r="G62" s="22" t="s">
-        <v>596</v>
       </c>
       <c r="H62" s="18" t="s">
         <v>23</v>
@@ -13955,36 +13952,36 @@
         <v>0</v>
       </c>
       <c r="O62" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P62" s="22" t="s">
+        <v>596</v>
+      </c>
+      <c r="Q62" s="22" t="s">
         <v>597</v>
-      </c>
-      <c r="Q62" s="22" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B63" s="16">
         <v>9</v>
       </c>
       <c r="C63" s="17" t="s">
+        <v>598</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="E63" s="17" t="s">
         <v>599</v>
       </c>
-      <c r="D63" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="E63" s="17" t="s">
+      <c r="F63" s="17" t="s">
         <v>600</v>
       </c>
-      <c r="F63" s="17" t="s">
+      <c r="G63" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="G63" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>23</v>
@@ -14002,36 +13999,36 @@
         <v>0</v>
       </c>
       <c r="O63" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P63" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="Q63" s="17" t="s">
         <v>603</v>
-      </c>
-      <c r="Q63" s="17" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B64" s="21">
         <v>10</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D64" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E64" s="22" t="s">
+        <v>605</v>
+      </c>
+      <c r="F64" s="22" t="s">
         <v>606</v>
       </c>
-      <c r="F64" s="22" t="s">
+      <c r="G64" s="22" t="s">
         <v>607</v>
-      </c>
-      <c r="G64" s="22" t="s">
-        <v>608</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>23</v>
@@ -14049,36 +14046,36 @@
         <v>0</v>
       </c>
       <c r="O64" s="22" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P64" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q64" s="22" t="s">
         <v>609</v>
-      </c>
-      <c r="Q64" s="22" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B65" s="16">
         <v>11</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D65" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E65" s="17" t="s">
+        <v>611</v>
+      </c>
+      <c r="F65" s="17" t="s">
         <v>612</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="G65" s="17" t="s">
         <v>613</v>
-      </c>
-      <c r="G65" s="17" t="s">
-        <v>614</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>23</v>
@@ -14096,36 +14093,36 @@
         <v>0</v>
       </c>
       <c r="O65" s="17" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="P65" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q65" s="17" t="s">
         <v>615</v>
-      </c>
-      <c r="Q65" s="17" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B66" s="21">
         <v>12</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D66" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E66" s="22" t="s">
+        <v>617</v>
+      </c>
+      <c r="F66" s="22" t="s">
         <v>618</v>
       </c>
-      <c r="F66" s="22" t="s">
+      <c r="G66" s="22" t="s">
         <v>619</v>
-      </c>
-      <c r="G66" s="22" t="s">
-        <v>620</v>
       </c>
       <c r="H66" s="18" t="s">
         <v>23</v>
@@ -14143,36 +14140,36 @@
         <v>0</v>
       </c>
       <c r="O66" s="22" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="P66" s="22" t="s">
+        <v>620</v>
+      </c>
+      <c r="Q66" s="22" t="s">
         <v>621</v>
-      </c>
-      <c r="Q66" s="22" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B67" s="16">
         <v>13</v>
       </c>
       <c r="C67" s="17" t="s">
+        <v>622</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="E67" s="17" t="s">
         <v>623</v>
       </c>
-      <c r="D67" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="E67" s="17" t="s">
+      <c r="F67" s="17" t="s">
         <v>624</v>
       </c>
-      <c r="F67" s="17" t="s">
-        <v>625</v>
-      </c>
       <c r="G67" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>23</v>
@@ -14190,57 +14187,57 @@
         <v>0</v>
       </c>
       <c r="O67" s="17" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="P67" s="17" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q67" s="17" t="s">
         <v>626</v>
       </c>
-      <c r="Q67" s="17" t="s">
-        <v>627</v>
-      </c>
     </row>
     <row r="68" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="100" t="s">
-        <v>304</v>
-      </c>
-      <c r="B68" s="92"/>
-      <c r="C68" s="92"/>
-      <c r="D68" s="92"/>
-      <c r="E68" s="92"/>
-      <c r="F68" s="92"/>
-      <c r="G68" s="92"/>
-      <c r="H68" s="92"/>
-      <c r="I68" s="92"/>
-      <c r="J68" s="92"/>
-      <c r="K68" s="92"/>
-      <c r="L68" s="92"/>
-      <c r="M68" s="92"/>
-      <c r="N68" s="92"/>
-      <c r="O68" s="92"/>
-      <c r="P68" s="92"/>
-      <c r="Q68" s="93"/>
+      <c r="A68" s="97" t="s">
+        <v>303</v>
+      </c>
+      <c r="B68" s="89"/>
+      <c r="C68" s="89"/>
+      <c r="D68" s="89"/>
+      <c r="E68" s="89"/>
+      <c r="F68" s="89"/>
+      <c r="G68" s="89"/>
+      <c r="H68" s="89"/>
+      <c r="I68" s="89"/>
+      <c r="J68" s="89"/>
+      <c r="K68" s="89"/>
+      <c r="L68" s="89"/>
+      <c r="M68" s="89"/>
+      <c r="N68" s="89"/>
+      <c r="O68" s="89"/>
+      <c r="P68" s="89"/>
+      <c r="Q68" s="90"/>
     </row>
     <row r="69" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B69" s="21">
         <v>0</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D69" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E69" s="22" t="s">
+        <v>628</v>
+      </c>
+      <c r="F69" s="22" t="s">
         <v>629</v>
       </c>
-      <c r="F69" s="22" t="s">
+      <c r="G69" s="22" t="s">
         <v>630</v>
-      </c>
-      <c r="G69" s="22" t="s">
-        <v>631</v>
       </c>
       <c r="H69" s="18" t="s">
         <v>23</v>
@@ -14249,7 +14246,7 @@
         <v>39</v>
       </c>
       <c r="J69" s="21" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K69" s="23">
         <v>46192</v>
@@ -14265,33 +14262,33 @@
       </c>
       <c r="O69" s="22"/>
       <c r="P69" s="22" t="s">
+        <v>632</v>
+      </c>
+      <c r="Q69" s="22" t="s">
         <v>633</v>
-      </c>
-      <c r="Q69" s="22" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="70" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="33" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B70" s="33">
         <v>0</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D70" s="34" t="s">
         <v>18</v>
       </c>
       <c r="E70" s="34" t="s">
+        <v>635</v>
+      </c>
+      <c r="F70" s="34" t="s">
         <v>636</v>
       </c>
-      <c r="F70" s="34" t="s">
+      <c r="G70" s="34" t="s">
         <v>637</v>
-      </c>
-      <c r="G70" s="34" t="s">
-        <v>638</v>
       </c>
       <c r="H70" s="18" t="s">
         <v>23</v>
@@ -14315,36 +14312,36 @@
         <v>1</v>
       </c>
       <c r="O70" s="34" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="P70" s="34" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="Q70" s="34" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B71" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="C71" s="22" t="s">
         <v>640</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>641</v>
       </c>
       <c r="D71" s="22" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="22" t="s">
+        <v>641</v>
+      </c>
+      <c r="F71" s="22" t="s">
         <v>642</v>
       </c>
-      <c r="F71" s="22" t="s">
+      <c r="G71" s="22" t="s">
         <v>643</v>
-      </c>
-      <c r="G71" s="22" t="s">
-        <v>644</v>
       </c>
       <c r="H71" s="18" t="s">
         <v>23</v>
@@ -14356,48 +14353,48 @@
         <v>25</v>
       </c>
       <c r="K71" s="21" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="L71" s="21" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="M71" s="21" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="N71" s="24">
         <v>1</v>
       </c>
       <c r="O71" s="22" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="P71" s="22" t="s">
+        <v>645</v>
+      </c>
+      <c r="Q71" s="22" t="s">
         <v>646</v>
-      </c>
-      <c r="Q71" s="22" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="72" spans="1:17" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B72" s="21">
         <v>1</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D72" s="22" t="s">
         <v>75</v>
       </c>
       <c r="E72" s="22" t="s">
+        <v>648</v>
+      </c>
+      <c r="F72" s="22" t="s">
         <v>649</v>
       </c>
-      <c r="F72" s="22" t="s">
+      <c r="G72" s="22" t="s">
         <v>650</v>
-      </c>
-      <c r="G72" s="22" t="s">
-        <v>651</v>
       </c>
       <c r="H72" s="18" t="s">
         <v>23</v>
@@ -14409,48 +14406,48 @@
         <v>25</v>
       </c>
       <c r="K72" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="L72" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="M72" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="N72" s="21">
         <v>1</v>
       </c>
       <c r="O72" s="22" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="P72" s="22" t="s">
+        <v>652</v>
+      </c>
+      <c r="Q72" s="22" t="s">
         <v>653</v>
-      </c>
-      <c r="Q72" s="22" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="105.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B73" s="21">
         <v>2</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D73" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E73" s="22" t="s">
+        <v>655</v>
+      </c>
+      <c r="F73" s="22" t="s">
         <v>656</v>
       </c>
-      <c r="F73" s="22" t="s">
-        <v>657</v>
-      </c>
       <c r="G73" s="22" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H73" s="18" t="s">
         <v>23</v>
@@ -14462,48 +14459,48 @@
         <v>25</v>
       </c>
       <c r="K73" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="L73" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="M73" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="N73" s="21">
         <v>1</v>
       </c>
       <c r="O73" s="22" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="P73" s="22" t="s">
+        <v>657</v>
+      </c>
+      <c r="Q73" s="22" t="s">
         <v>658</v>
-      </c>
-      <c r="Q73" s="22" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="74" spans="1:17" ht="132" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B74" s="21">
         <v>3</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D74" s="22" t="s">
         <v>75</v>
       </c>
       <c r="E74" s="22" t="s">
+        <v>660</v>
+      </c>
+      <c r="F74" s="22" t="s">
         <v>661</v>
       </c>
-      <c r="F74" s="22" t="s">
+      <c r="G74" s="22" t="s">
         <v>662</v>
-      </c>
-      <c r="G74" s="22" t="s">
-        <v>663</v>
       </c>
       <c r="H74" s="18" t="s">
         <v>23</v>
@@ -14515,48 +14512,48 @@
         <v>25</v>
       </c>
       <c r="K74" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="L74" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="M74" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="N74" s="21">
         <v>1</v>
       </c>
       <c r="O74" s="22" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="P74" s="22" t="s">
+        <v>663</v>
+      </c>
+      <c r="Q74" s="22" t="s">
         <v>664</v>
-      </c>
-      <c r="Q74" s="22" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B75" s="21">
         <v>4</v>
       </c>
       <c r="C75" s="22" t="s">
+        <v>665</v>
+      </c>
+      <c r="D75" s="22" t="s">
         <v>666</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="E75" s="22" t="s">
         <v>667</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="F75" s="22" t="s">
         <v>668</v>
       </c>
-      <c r="F75" s="22" t="s">
+      <c r="G75" s="22" t="s">
         <v>669</v>
-      </c>
-      <c r="G75" s="22" t="s">
-        <v>670</v>
       </c>
       <c r="H75" s="18" t="s">
         <v>23</v>
@@ -14568,23 +14565,23 @@
         <v>25</v>
       </c>
       <c r="K75" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="L75" s="21" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="M75" s="21"/>
       <c r="N75" s="21">
         <v>100</v>
       </c>
       <c r="O75" s="22" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="P75" s="22" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q75" t="s">
         <v>672</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -14626,23 +14623,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="105" t="s">
-        <v>674</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="95"/>
+      <c r="A1" s="107" t="s">
+        <v>673</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
     </row>
     <row r="2" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
@@ -14688,49 +14685,49 @@
         <v>14</v>
       </c>
       <c r="O2" s="37" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="107" t="s">
-        <v>675</v>
-      </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="92"/>
-      <c r="L3" s="92"/>
-      <c r="M3" s="92"/>
-      <c r="N3" s="92"/>
-      <c r="O3" s="93"/>
+      <c r="A3" s="106" t="s">
+        <v>674</v>
+      </c>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="90"/>
     </row>
     <row r="4" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="54" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C4" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E4" s="47" t="s">
+        <v>675</v>
+      </c>
+      <c r="F4" s="47" t="s">
         <v>676</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="G4" s="47" t="s">
         <v>677</v>
-      </c>
-      <c r="G4" s="47" t="s">
-        <v>678</v>
       </c>
       <c r="H4" s="48" t="s">
         <v>23</v>
@@ -14751,33 +14748,33 @@
         <v>1</v>
       </c>
       <c r="N4" s="47" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="O4" s="47" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="54" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C5" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E5" s="47" t="s">
+        <v>679</v>
+      </c>
+      <c r="F5" s="47" t="s">
         <v>680</v>
       </c>
-      <c r="F5" s="47" t="s">
+      <c r="G5" s="47" t="s">
         <v>681</v>
-      </c>
-      <c r="G5" s="47" t="s">
-        <v>682</v>
       </c>
       <c r="H5" s="48" t="s">
         <v>23</v>
@@ -14798,30 +14795,30 @@
         <v>1</v>
       </c>
       <c r="N5" s="47" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C6" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="47" t="s">
+        <v>683</v>
+      </c>
+      <c r="E6" s="47" t="s">
         <v>684</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="F6" s="47" t="s">
         <v>685</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>686</v>
       </c>
       <c r="G6" s="47" t="s">
         <v>33</v>
@@ -14845,33 +14842,33 @@
         <v>1</v>
       </c>
       <c r="N6" s="47" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
-        <v>648</v>
-      </c>
-      <c r="B7" s="104" t="s">
-        <v>651</v>
+        <v>647</v>
+      </c>
+      <c r="B7" s="105" t="s">
+        <v>650</v>
       </c>
       <c r="C7" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E7" s="47" t="s">
+        <v>687</v>
+      </c>
+      <c r="F7" s="47" t="s">
         <v>688</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="G7" s="47" t="s">
         <v>689</v>
-      </c>
-      <c r="G7" s="47" t="s">
-        <v>690</v>
       </c>
       <c r="H7" s="48" t="s">
         <v>23</v>
@@ -14892,31 +14889,31 @@
         <v>1</v>
       </c>
       <c r="N7" s="47" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="O7" s="47" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="54" t="s">
-        <v>692</v>
-      </c>
-      <c r="B8" s="90"/>
+        <v>691</v>
+      </c>
+      <c r="B8" s="85"/>
       <c r="C8" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D8" s="47" t="s">
+        <v>692</v>
+      </c>
+      <c r="E8" s="47" t="s">
         <v>693</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="F8" s="47" t="s">
         <v>694</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="G8" s="47" t="s">
         <v>695</v>
-      </c>
-      <c r="G8" s="47" t="s">
-        <v>696</v>
       </c>
       <c r="H8" s="48" t="s">
         <v>23</v>
@@ -14929,37 +14926,37 @@
       </c>
       <c r="K8" s="49"/>
       <c r="L8" s="49" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="M8" s="50">
         <v>1</v>
       </c>
       <c r="N8" s="47" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
-        <v>655</v>
-      </c>
-      <c r="B9" s="83"/>
+        <v>654</v>
+      </c>
+      <c r="B9" s="86"/>
       <c r="C9" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E9" s="47" t="s">
+        <v>698</v>
+      </c>
+      <c r="F9" s="47" t="s">
         <v>699</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="G9" s="47" t="s">
         <v>700</v>
-      </c>
-      <c r="G9" s="47" t="s">
-        <v>701</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>23</v>
@@ -14980,33 +14977,33 @@
         <v>1</v>
       </c>
       <c r="N9" s="47" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
-        <v>660</v>
-      </c>
-      <c r="B10" s="104" t="s">
-        <v>663</v>
+        <v>659</v>
+      </c>
+      <c r="B10" s="105" t="s">
+        <v>662</v>
       </c>
       <c r="C10" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D10" s="47" t="s">
+        <v>702</v>
+      </c>
+      <c r="E10" s="47" t="s">
         <v>703</v>
       </c>
-      <c r="E10" s="47" t="s">
+      <c r="F10" s="47" t="s">
         <v>704</v>
       </c>
-      <c r="F10" s="47" t="s">
+      <c r="G10" s="47" t="s">
         <v>705</v>
-      </c>
-      <c r="G10" s="47" t="s">
-        <v>706</v>
       </c>
       <c r="H10" s="48" t="s">
         <v>23</v>
@@ -15027,31 +15024,31 @@
         <v>1</v>
       </c>
       <c r="N10" s="47" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="54" t="s">
-        <v>708</v>
-      </c>
-      <c r="B11" s="83"/>
+        <v>707</v>
+      </c>
+      <c r="B11" s="86"/>
       <c r="C11" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D11" s="47" t="s">
+        <v>708</v>
+      </c>
+      <c r="E11" s="47" t="s">
         <v>709</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="F11" s="47" t="s">
         <v>710</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="G11" s="47" t="s">
         <v>711</v>
-      </c>
-      <c r="G11" s="47" t="s">
-        <v>712</v>
       </c>
       <c r="H11" s="48" t="s">
         <v>23</v>
@@ -15064,39 +15061,39 @@
       </c>
       <c r="K11" s="49"/>
       <c r="L11" s="49" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="M11" s="50">
         <v>1</v>
       </c>
       <c r="N11" s="47" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
+        <v>665</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>669</v>
+      </c>
+      <c r="C12" s="47" t="s">
         <v>666</v>
       </c>
-      <c r="B12" s="52" t="s">
-        <v>670</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>667</v>
-      </c>
       <c r="D12" s="47" t="s">
+        <v>713</v>
+      </c>
+      <c r="E12" s="47" t="s">
         <v>714</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="F12" s="47" t="s">
         <v>715</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="G12" s="47" t="s">
         <v>716</v>
-      </c>
-      <c r="G12" s="47" t="s">
-        <v>717</v>
       </c>
       <c r="H12" s="48" t="s">
         <v>23</v>
@@ -15117,33 +15114,33 @@
         <v>1</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="54" t="s">
+        <v>718</v>
+      </c>
+      <c r="B13" s="105" t="s">
         <v>719</v>
-      </c>
-      <c r="B13" s="104" t="s">
-        <v>720</v>
       </c>
       <c r="C13" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D13" s="47" t="s">
+        <v>720</v>
+      </c>
+      <c r="E13" s="47" t="s">
         <v>721</v>
       </c>
-      <c r="E13" s="47" t="s">
+      <c r="F13" s="47" t="s">
         <v>722</v>
       </c>
-      <c r="F13" s="47" t="s">
+      <c r="G13" s="47" t="s">
         <v>723</v>
-      </c>
-      <c r="G13" s="47" t="s">
-        <v>724</v>
       </c>
       <c r="H13" s="48" t="s">
         <v>23</v>
@@ -15164,31 +15161,31 @@
         <v>1</v>
       </c>
       <c r="N13" s="47" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="14" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="54" t="s">
-        <v>726</v>
-      </c>
-      <c r="B14" s="83"/>
+        <v>725</v>
+      </c>
+      <c r="B14" s="86"/>
       <c r="C14" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D14" s="47" t="s">
+        <v>726</v>
+      </c>
+      <c r="E14" s="47" t="s">
         <v>727</v>
       </c>
-      <c r="E14" s="47" t="s">
+      <c r="F14" s="47" t="s">
         <v>728</v>
       </c>
-      <c r="F14" s="47" t="s">
+      <c r="G14" s="47" t="s">
         <v>729</v>
-      </c>
-      <c r="G14" s="47" t="s">
-        <v>730</v>
       </c>
       <c r="H14" s="48" t="s">
         <v>23</v>
@@ -15209,33 +15206,33 @@
         <v>1</v>
       </c>
       <c r="N14" s="47" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="54" t="s">
+        <v>731</v>
+      </c>
+      <c r="B15" s="108" t="s">
         <v>732</v>
-      </c>
-      <c r="B15" s="106" t="s">
-        <v>733</v>
       </c>
       <c r="C15" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="47" t="s">
+        <v>733</v>
+      </c>
+      <c r="E15" s="47" t="s">
         <v>734</v>
       </c>
-      <c r="E15" s="47" t="s">
+      <c r="F15" s="47" t="s">
         <v>735</v>
       </c>
-      <c r="F15" s="47" t="s">
+      <c r="G15" s="47" t="s">
         <v>736</v>
-      </c>
-      <c r="G15" s="47" t="s">
-        <v>737</v>
       </c>
       <c r="H15" s="48" t="s">
         <v>23</v>
@@ -15256,31 +15253,31 @@
         <v>1</v>
       </c>
       <c r="N15" s="47" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="O15" s="47" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="54" t="s">
-        <v>739</v>
-      </c>
-      <c r="B16" s="90"/>
+        <v>738</v>
+      </c>
+      <c r="B16" s="85"/>
       <c r="C16" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E16" s="47" t="s">
         <v>740</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="F16" s="47" t="s">
         <v>741</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="G16" s="47" t="s">
         <v>742</v>
-      </c>
-      <c r="G16" s="47" t="s">
-        <v>743</v>
       </c>
       <c r="H16" s="48" t="s">
         <v>23</v>
@@ -15299,31 +15296,31 @@
         <v>1</v>
       </c>
       <c r="N16" s="47" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O16" s="47" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="54" t="s">
-        <v>745</v>
-      </c>
-      <c r="B17" s="90"/>
+        <v>744</v>
+      </c>
+      <c r="B17" s="85"/>
       <c r="C17" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="47" t="s">
+        <v>745</v>
+      </c>
+      <c r="E17" s="47" t="s">
         <v>746</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="F17" s="47" t="s">
         <v>747</v>
       </c>
-      <c r="F17" s="47" t="s">
+      <c r="G17" s="47" t="s">
         <v>748</v>
-      </c>
-      <c r="G17" s="47" t="s">
-        <v>749</v>
       </c>
       <c r="H17" s="48" t="s">
         <v>23</v>
@@ -15342,10 +15339,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="47" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O17" s="47" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="44" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -15367,25 +15364,25 @@
     </row>
     <row r="19" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="54" t="s">
+        <v>750</v>
+      </c>
+      <c r="B19" s="105" t="s">
         <v>751</v>
-      </c>
-      <c r="B19" s="104" t="s">
-        <v>752</v>
       </c>
       <c r="C19" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D19" s="47" t="s">
+        <v>752</v>
+      </c>
+      <c r="E19" s="47" t="s">
         <v>753</v>
       </c>
-      <c r="E19" s="47" t="s">
+      <c r="F19" s="47" t="s">
         <v>754</v>
       </c>
-      <c r="F19" s="47" t="s">
+      <c r="G19" s="47" t="s">
         <v>755</v>
-      </c>
-      <c r="G19" s="47" t="s">
-        <v>756</v>
       </c>
       <c r="H19" s="48" t="s">
         <v>23</v>
@@ -15406,31 +15403,31 @@
         <v>1</v>
       </c>
       <c r="N19" s="47" t="s">
+        <v>756</v>
+      </c>
+      <c r="O19" s="47" t="s">
         <v>757</v>
-      </c>
-      <c r="O19" s="47" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="54" t="s">
-        <v>759</v>
-      </c>
-      <c r="B20" s="90"/>
+        <v>758</v>
+      </c>
+      <c r="B20" s="85"/>
       <c r="C20" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="47" t="s">
+        <v>759</v>
+      </c>
+      <c r="E20" s="47" t="s">
         <v>760</v>
       </c>
-      <c r="E20" s="47" t="s">
+      <c r="F20" s="47" t="s">
         <v>761</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="G20" s="47" t="s">
         <v>762</v>
-      </c>
-      <c r="G20" s="47" t="s">
-        <v>763</v>
       </c>
       <c r="H20" s="48" t="s">
         <v>23</v>
@@ -15451,31 +15448,31 @@
         <v>1</v>
       </c>
       <c r="N20" s="47" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="O20" s="47" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="21" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="54" t="s">
-        <v>765</v>
-      </c>
-      <c r="B21" s="90"/>
+        <v>764</v>
+      </c>
+      <c r="B21" s="85"/>
       <c r="C21" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="47" t="s">
+        <v>765</v>
+      </c>
+      <c r="E21" s="47" t="s">
         <v>766</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="F21" s="47" t="s">
         <v>767</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="G21" s="47" t="s">
         <v>768</v>
-      </c>
-      <c r="G21" s="47" t="s">
-        <v>769</v>
       </c>
       <c r="H21" s="48" t="s">
         <v>23</v>
@@ -15496,31 +15493,31 @@
         <v>1</v>
       </c>
       <c r="N21" s="47" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="O21" s="47" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="22" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="54" t="s">
-        <v>771</v>
-      </c>
-      <c r="B22" s="83"/>
+        <v>770</v>
+      </c>
+      <c r="B22" s="86"/>
       <c r="C22" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="47" t="s">
+        <v>771</v>
+      </c>
+      <c r="E22" s="47" t="s">
         <v>772</v>
       </c>
-      <c r="E22" s="47" t="s">
+      <c r="F22" s="47" t="s">
         <v>773</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="G22" s="47" t="s">
         <v>774</v>
-      </c>
-      <c r="G22" s="47" t="s">
-        <v>775</v>
       </c>
       <c r="H22" s="48" t="s">
         <v>23</v>
@@ -15541,33 +15538,33 @@
         <v>1</v>
       </c>
       <c r="N22" s="47" t="s">
+        <v>775</v>
+      </c>
+      <c r="O22" s="47" t="s">
         <v>776</v>
-      </c>
-      <c r="O22" s="47" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="54" t="s">
+        <v>777</v>
+      </c>
+      <c r="B23" s="52" t="s">
         <v>778</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>779</v>
       </c>
       <c r="C23" s="47" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="47" t="s">
+        <v>779</v>
+      </c>
+      <c r="E23" s="47" t="s">
         <v>780</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="F23" s="47" t="s">
         <v>781</v>
       </c>
-      <c r="F23" s="47" t="s">
+      <c r="G23" s="47" t="s">
         <v>782</v>
-      </c>
-      <c r="G23" s="47" t="s">
-        <v>783</v>
       </c>
       <c r="H23" s="48" t="s">
         <v>23</v>
@@ -15588,10 +15585,10 @@
         <v>1</v>
       </c>
       <c r="N23" s="47" t="s">
+        <v>783</v>
+      </c>
+      <c r="O23" s="47" t="s">
         <v>784</v>
-      </c>
-      <c r="O23" s="47" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="44" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -15613,22 +15610,22 @@
     </row>
     <row r="25" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="54" t="s">
+        <v>785</v>
+      </c>
+      <c r="B25" s="105" t="s">
         <v>786</v>
-      </c>
-      <c r="B25" s="104" t="s">
-        <v>787</v>
       </c>
       <c r="C25" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D25" s="47" t="s">
+        <v>787</v>
+      </c>
+      <c r="E25" s="47" t="s">
         <v>788</v>
       </c>
-      <c r="E25" s="47" t="s">
+      <c r="F25" s="47" t="s">
         <v>789</v>
-      </c>
-      <c r="F25" s="47" t="s">
-        <v>790</v>
       </c>
       <c r="G25" s="47" t="s">
         <v>71</v>
@@ -15644,34 +15641,34 @@
       </c>
       <c r="K25" s="49"/>
       <c r="L25" s="49" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="M25" s="50">
         <v>0</v>
       </c>
       <c r="N25" s="47" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="O25" s="47" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="26" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="54" t="s">
-        <v>793</v>
-      </c>
-      <c r="B26" s="90"/>
+        <v>792</v>
+      </c>
+      <c r="B26" s="85"/>
       <c r="C26" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="47" t="s">
+        <v>793</v>
+      </c>
+      <c r="E26" s="47" t="s">
         <v>794</v>
       </c>
-      <c r="E26" s="47" t="s">
+      <c r="F26" s="47" t="s">
         <v>795</v>
-      </c>
-      <c r="F26" s="47" t="s">
-        <v>796</v>
       </c>
       <c r="G26" s="47" t="s">
         <v>71</v>
@@ -15687,34 +15684,34 @@
       </c>
       <c r="K26" s="49"/>
       <c r="L26" s="49" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="M26" s="50">
         <v>0</v>
       </c>
       <c r="N26" s="47" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="O26" s="47" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="27" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="54" t="s">
-        <v>798</v>
-      </c>
-      <c r="B27" s="90"/>
+        <v>797</v>
+      </c>
+      <c r="B27" s="85"/>
       <c r="C27" s="47" t="s">
         <v>49</v>
       </c>
       <c r="D27" s="47" t="s">
+        <v>798</v>
+      </c>
+      <c r="E27" s="47" t="s">
         <v>799</v>
       </c>
-      <c r="E27" s="47" t="s">
+      <c r="F27" s="47" t="s">
         <v>800</v>
-      </c>
-      <c r="F27" s="47" t="s">
-        <v>801</v>
       </c>
       <c r="G27" s="47" t="s">
         <v>112</v>
@@ -15736,23 +15733,23 @@
     </row>
     <row r="28" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="54" t="s">
+        <v>801</v>
+      </c>
+      <c r="B28" s="85"/>
+      <c r="C28" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="D28" s="47" t="s">
         <v>802</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="D28" s="47" t="s">
+      <c r="E28" s="47" t="s">
         <v>803</v>
       </c>
-      <c r="E28" s="47" t="s">
+      <c r="F28" s="47" t="s">
         <v>804</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="G28" s="47" t="s">
         <v>805</v>
-      </c>
-      <c r="G28" s="47" t="s">
-        <v>806</v>
       </c>
       <c r="H28" s="48" t="s">
         <v>23</v>
@@ -15771,20 +15768,20 @@
     </row>
     <row r="29" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="54" t="s">
-        <v>807</v>
-      </c>
-      <c r="B29" s="83"/>
+        <v>806</v>
+      </c>
+      <c r="B29" s="86"/>
       <c r="C29" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D29" s="47" t="s">
+        <v>807</v>
+      </c>
+      <c r="E29" s="47" t="s">
         <v>808</v>
       </c>
-      <c r="E29" s="47" t="s">
+      <c r="F29" s="47" t="s">
         <v>809</v>
-      </c>
-      <c r="F29" s="47" t="s">
-        <v>810</v>
       </c>
       <c r="G29" s="47" t="s">
         <v>71</v>
@@ -15800,39 +15797,39 @@
       </c>
       <c r="K29" s="49"/>
       <c r="L29" s="49" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="M29" s="50">
         <v>0</v>
       </c>
       <c r="N29" s="47" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="O29" s="47" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="30" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="54" t="s">
+        <v>811</v>
+      </c>
+      <c r="B30" s="47" t="s">
         <v>812</v>
-      </c>
-      <c r="B30" s="47" t="s">
-        <v>813</v>
       </c>
       <c r="C30" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="47" t="s">
+        <v>813</v>
+      </c>
+      <c r="E30" s="47" t="s">
         <v>814</v>
       </c>
-      <c r="E30" s="47" t="s">
+      <c r="F30" s="47" t="s">
         <v>815</v>
       </c>
-      <c r="F30" s="47" t="s">
+      <c r="G30" s="47" t="s">
         <v>816</v>
-      </c>
-      <c r="G30" s="47" t="s">
-        <v>817</v>
       </c>
       <c r="H30" s="48" t="s">
         <v>23</v>
@@ -15868,22 +15865,22 @@
     </row>
     <row r="32" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="54" t="s">
+        <v>817</v>
+      </c>
+      <c r="B32" s="105" t="s">
         <v>818</v>
       </c>
-      <c r="B32" s="104" t="s">
+      <c r="C32" s="47" t="s">
         <v>819</v>
       </c>
-      <c r="C32" s="47" t="s">
+      <c r="D32" s="47" t="s">
         <v>820</v>
       </c>
-      <c r="D32" s="47" t="s">
+      <c r="E32" s="47" t="s">
         <v>821</v>
       </c>
-      <c r="E32" s="47" t="s">
+      <c r="F32" s="47" t="s">
         <v>822</v>
-      </c>
-      <c r="F32" s="47" t="s">
-        <v>823</v>
       </c>
       <c r="G32" s="47" t="s">
         <v>112</v>
@@ -15907,31 +15904,31 @@
         <v>1</v>
       </c>
       <c r="N32" s="47" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="O32" s="47" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="33" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="54" t="s">
-        <v>825</v>
-      </c>
-      <c r="B33" s="90"/>
+        <v>824</v>
+      </c>
+      <c r="B33" s="85"/>
       <c r="C33" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D33" s="47" t="s">
+        <v>825</v>
+      </c>
+      <c r="E33" s="47" t="s">
         <v>826</v>
       </c>
-      <c r="E33" s="47" t="s">
+      <c r="F33" s="47" t="s">
         <v>827</v>
       </c>
-      <c r="F33" s="47" t="s">
+      <c r="G33" s="47" t="s">
         <v>828</v>
-      </c>
-      <c r="G33" s="47" t="s">
-        <v>829</v>
       </c>
       <c r="H33" s="48" t="s">
         <v>23</v>
@@ -15952,28 +15949,28 @@
         <v>1</v>
       </c>
       <c r="N33" s="47" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="O33" s="47" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="34" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="54" t="s">
-        <v>831</v>
-      </c>
-      <c r="B34" s="90"/>
+        <v>830</v>
+      </c>
+      <c r="B34" s="85"/>
       <c r="C34" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D34" s="47" t="s">
+        <v>831</v>
+      </c>
+      <c r="E34" s="47" t="s">
         <v>832</v>
       </c>
-      <c r="E34" s="47" t="s">
+      <c r="F34" s="47" t="s">
         <v>833</v>
-      </c>
-      <c r="F34" s="47" t="s">
-        <v>834</v>
       </c>
       <c r="G34" s="47" t="s">
         <v>112</v>
@@ -15997,28 +15994,28 @@
         <v>1</v>
       </c>
       <c r="N34" s="47" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="O34" s="47" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="54" t="s">
-        <v>836</v>
-      </c>
-      <c r="B35" s="90"/>
+        <v>835</v>
+      </c>
+      <c r="B35" s="85"/>
       <c r="C35" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D35" s="47" t="s">
+        <v>836</v>
+      </c>
+      <c r="E35" s="47" t="s">
         <v>837</v>
       </c>
-      <c r="E35" s="47" t="s">
+      <c r="F35" s="47" t="s">
         <v>838</v>
-      </c>
-      <c r="F35" s="47" t="s">
-        <v>839</v>
       </c>
       <c r="G35" s="47" t="s">
         <v>112</v>
@@ -16042,28 +16039,28 @@
         <v>1</v>
       </c>
       <c r="N35" s="47" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="O35" s="47" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="36" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="54" t="s">
-        <v>841</v>
-      </c>
-      <c r="B36" s="90"/>
+        <v>840</v>
+      </c>
+      <c r="B36" s="85"/>
       <c r="C36" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D36" s="47" t="s">
+        <v>841</v>
+      </c>
+      <c r="E36" s="47" t="s">
         <v>842</v>
       </c>
-      <c r="E36" s="47" t="s">
+      <c r="F36" s="47" t="s">
         <v>843</v>
-      </c>
-      <c r="F36" s="47" t="s">
-        <v>844</v>
       </c>
       <c r="G36" s="47" t="s">
         <v>112</v>
@@ -16087,28 +16084,28 @@
         <v>1</v>
       </c>
       <c r="N36" s="47" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O36" s="47" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="37" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="54" t="s">
-        <v>846</v>
-      </c>
-      <c r="B37" s="90"/>
+        <v>845</v>
+      </c>
+      <c r="B37" s="85"/>
       <c r="C37" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D37" s="47" t="s">
+        <v>846</v>
+      </c>
+      <c r="E37" s="47" t="s">
         <v>847</v>
       </c>
-      <c r="E37" s="47" t="s">
+      <c r="F37" s="47" t="s">
         <v>848</v>
-      </c>
-      <c r="F37" s="47" t="s">
-        <v>849</v>
       </c>
       <c r="G37" s="47" t="s">
         <v>112</v>
@@ -16132,28 +16129,28 @@
         <v>1</v>
       </c>
       <c r="N37" s="47" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="O37" s="47" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="38" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="54" t="s">
-        <v>851</v>
-      </c>
-      <c r="B38" s="90"/>
+        <v>850</v>
+      </c>
+      <c r="B38" s="85"/>
       <c r="C38" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D38" s="47" t="s">
+        <v>851</v>
+      </c>
+      <c r="E38" s="47" t="s">
         <v>852</v>
       </c>
-      <c r="E38" s="47" t="s">
+      <c r="F38" s="47" t="s">
         <v>853</v>
-      </c>
-      <c r="F38" s="47" t="s">
-        <v>854</v>
       </c>
       <c r="G38" s="47" t="s">
         <v>112</v>
@@ -16177,28 +16174,28 @@
         <v>1</v>
       </c>
       <c r="N38" s="47" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="O38" s="47" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="39" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="54" t="s">
-        <v>856</v>
-      </c>
-      <c r="B39" s="90"/>
+        <v>855</v>
+      </c>
+      <c r="B39" s="85"/>
       <c r="C39" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D39" s="47" t="s">
+        <v>856</v>
+      </c>
+      <c r="E39" s="47" t="s">
         <v>857</v>
       </c>
-      <c r="E39" s="47" t="s">
+      <c r="F39" s="47" t="s">
         <v>858</v>
-      </c>
-      <c r="F39" s="47" t="s">
-        <v>859</v>
       </c>
       <c r="G39" s="47" t="s">
         <v>112</v>
@@ -16222,28 +16219,28 @@
         <v>1</v>
       </c>
       <c r="N39" s="47" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="O39" s="47" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="40" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="54" t="s">
+        <v>860</v>
+      </c>
+      <c r="B40" s="85"/>
+      <c r="C40" s="47" t="s">
         <v>861</v>
       </c>
-      <c r="B40" s="90"/>
-      <c r="C40" s="47" t="s">
+      <c r="D40" s="47" t="s">
         <v>862</v>
       </c>
-      <c r="D40" s="47" t="s">
+      <c r="E40" s="47" t="s">
         <v>863</v>
       </c>
-      <c r="E40" s="47" t="s">
+      <c r="F40" s="47" t="s">
         <v>864</v>
-      </c>
-      <c r="F40" s="47" t="s">
-        <v>865</v>
       </c>
       <c r="G40" s="47" t="s">
         <v>112</v>
@@ -16271,20 +16268,20 @@
     </row>
     <row r="41" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="54" t="s">
-        <v>866</v>
-      </c>
-      <c r="B41" s="83"/>
+        <v>865</v>
+      </c>
+      <c r="B41" s="86"/>
       <c r="C41" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D41" s="47" t="s">
+        <v>866</v>
+      </c>
+      <c r="E41" s="47" t="s">
         <v>867</v>
       </c>
-      <c r="E41" s="47" t="s">
+      <c r="F41" s="47" t="s">
         <v>868</v>
-      </c>
-      <c r="F41" s="47" t="s">
-        <v>869</v>
       </c>
       <c r="G41" s="47" t="s">
         <v>112</v>
@@ -16308,30 +16305,30 @@
         <v>1</v>
       </c>
       <c r="N41" s="47" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="O41" s="47" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="54" t="s">
+        <v>870</v>
+      </c>
+      <c r="B42" s="52" t="s">
         <v>871</v>
-      </c>
-      <c r="B42" s="52" t="s">
-        <v>872</v>
       </c>
       <c r="C42" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D42" s="47" t="s">
+        <v>872</v>
+      </c>
+      <c r="E42" s="47" t="s">
         <v>873</v>
       </c>
-      <c r="E42" s="47" t="s">
+      <c r="F42" s="47" t="s">
         <v>874</v>
-      </c>
-      <c r="F42" s="47" t="s">
-        <v>875</v>
       </c>
       <c r="G42" s="47" t="s">
         <v>112</v>
@@ -16355,10 +16352,10 @@
         <v>1</v>
       </c>
       <c r="N42" s="47" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="O42" s="47" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="43" spans="1:15" s="44" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16380,22 +16377,22 @@
     </row>
     <row r="44" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="54" t="s">
+        <v>876</v>
+      </c>
+      <c r="B44" s="104" t="s">
         <v>877</v>
-      </c>
-      <c r="B44" s="103" t="s">
-        <v>878</v>
       </c>
       <c r="C44" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D44" s="47" t="s">
+        <v>878</v>
+      </c>
+      <c r="E44" s="47" t="s">
         <v>879</v>
       </c>
-      <c r="E44" s="47" t="s">
+      <c r="F44" s="47" t="s">
         <v>880</v>
-      </c>
-      <c r="F44" s="47" t="s">
-        <v>881</v>
       </c>
       <c r="G44" s="47" t="s">
         <v>71</v>
@@ -16420,25 +16417,25 @@
       </c>
       <c r="N44" s="47"/>
       <c r="O44" s="47" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="45" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="54" t="s">
-        <v>883</v>
-      </c>
-      <c r="B45" s="90"/>
+        <v>882</v>
+      </c>
+      <c r="B45" s="85"/>
       <c r="C45" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D45" s="47" t="s">
+        <v>883</v>
+      </c>
+      <c r="E45" s="47" t="s">
         <v>884</v>
       </c>
-      <c r="E45" s="47" t="s">
+      <c r="F45" s="47" t="s">
         <v>885</v>
-      </c>
-      <c r="F45" s="47" t="s">
-        <v>886</v>
       </c>
       <c r="G45" s="47" t="s">
         <v>71</v>
@@ -16462,31 +16459,31 @@
         <v>1</v>
       </c>
       <c r="N45" s="47" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="O45" s="47" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="54" t="s">
-        <v>888</v>
-      </c>
-      <c r="B46" s="90"/>
+        <v>887</v>
+      </c>
+      <c r="B46" s="85"/>
       <c r="C46" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D46" s="47" t="s">
+        <v>888</v>
+      </c>
+      <c r="E46" s="47" t="s">
         <v>889</v>
       </c>
-      <c r="E46" s="47" t="s">
+      <c r="F46" s="47" t="s">
         <v>890</v>
       </c>
-      <c r="F46" s="47" t="s">
+      <c r="G46" s="47" t="s">
         <v>891</v>
-      </c>
-      <c r="G46" s="47" t="s">
-        <v>892</v>
       </c>
       <c r="H46" s="48" t="s">
         <v>23</v>
@@ -16507,31 +16504,31 @@
         <v>1</v>
       </c>
       <c r="N46" s="47" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="O46" s="47" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="47" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="54" t="s">
-        <v>894</v>
-      </c>
-      <c r="B47" s="90"/>
+        <v>893</v>
+      </c>
+      <c r="B47" s="85"/>
       <c r="C47" s="47" t="s">
         <v>49</v>
       </c>
       <c r="D47" s="47" t="s">
+        <v>894</v>
+      </c>
+      <c r="E47" s="47" t="s">
         <v>895</v>
       </c>
-      <c r="E47" s="47" t="s">
+      <c r="F47" s="47" t="s">
         <v>896</v>
       </c>
-      <c r="F47" s="47" t="s">
+      <c r="G47" s="47" t="s">
         <v>897</v>
-      </c>
-      <c r="G47" s="47" t="s">
-        <v>898</v>
       </c>
       <c r="H47" s="48" t="s">
         <v>23</v>
@@ -16552,31 +16549,31 @@
         <v>1</v>
       </c>
       <c r="N47" s="47" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="O47" s="47" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="54" t="s">
-        <v>900</v>
-      </c>
-      <c r="B48" s="90"/>
+        <v>899</v>
+      </c>
+      <c r="B48" s="85"/>
       <c r="C48" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D48" s="47" t="s">
+        <v>900</v>
+      </c>
+      <c r="E48" s="47" t="s">
         <v>901</v>
       </c>
-      <c r="E48" s="47" t="s">
+      <c r="F48" s="47" t="s">
+        <v>890</v>
+      </c>
+      <c r="G48" s="47" t="s">
         <v>902</v>
-      </c>
-      <c r="F48" s="47" t="s">
-        <v>891</v>
-      </c>
-      <c r="G48" s="47" t="s">
-        <v>903</v>
       </c>
       <c r="H48" s="48" t="s">
         <v>23</v>
@@ -16597,34 +16594,34 @@
         <v>1</v>
       </c>
       <c r="N48" s="47" t="s">
+        <v>903</v>
+      </c>
+      <c r="O48" s="47" t="s">
         <v>904</v>
-      </c>
-      <c r="O48" s="47" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="51" customFormat="1" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="54" t="s">
-        <v>906</v>
-      </c>
-      <c r="B49" s="83"/>
+        <v>905</v>
+      </c>
+      <c r="B49" s="86"/>
       <c r="C49" s="47" t="s">
         <v>29</v>
       </c>
       <c r="D49" s="47" t="s">
+        <v>906</v>
+      </c>
+      <c r="E49" s="47" t="s">
         <v>907</v>
       </c>
-      <c r="E49" s="47" t="s">
+      <c r="F49" s="47" t="s">
         <v>908</v>
-      </c>
-      <c r="F49" s="47" t="s">
-        <v>909</v>
       </c>
       <c r="G49" s="47" t="s">
         <v>112</v>
       </c>
       <c r="H49" s="48" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="I49" s="46" t="s">
         <v>54</v>
@@ -16659,28 +16656,28 @@
     </row>
     <row r="51" spans="1:15" s="51" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="54" t="s">
+        <v>910</v>
+      </c>
+      <c r="B51" s="104" t="s">
         <v>911</v>
-      </c>
-      <c r="B51" s="103" t="s">
-        <v>912</v>
       </c>
       <c r="C51" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="47" t="s">
+        <v>912</v>
+      </c>
+      <c r="E51" s="47" t="s">
         <v>913</v>
       </c>
-      <c r="E51" s="47" t="s">
+      <c r="F51" s="47" t="s">
         <v>914</v>
       </c>
-      <c r="F51" s="47" t="s">
+      <c r="G51" s="47" t="s">
         <v>915</v>
       </c>
-      <c r="G51" s="47" t="s">
-        <v>916</v>
-      </c>
       <c r="H51" s="48" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="I51" s="46" t="s">
         <v>39</v>
@@ -16696,26 +16693,26 @@
     </row>
     <row r="52" spans="1:15" s="51" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="54" t="s">
-        <v>917</v>
-      </c>
-      <c r="B52" s="90"/>
+        <v>916</v>
+      </c>
+      <c r="B52" s="85"/>
       <c r="C52" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D52" s="47" t="s">
+        <v>917</v>
+      </c>
+      <c r="E52" s="47" t="s">
         <v>918</v>
       </c>
-      <c r="E52" s="47" t="s">
+      <c r="F52" s="47" t="s">
         <v>919</v>
       </c>
-      <c r="F52" s="47" t="s">
+      <c r="G52" s="47" t="s">
         <v>920</v>
       </c>
-      <c r="G52" s="47" t="s">
-        <v>921</v>
-      </c>
       <c r="H52" s="48" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="I52" s="46" t="s">
         <v>39</v>
@@ -16731,26 +16728,26 @@
     </row>
     <row r="53" spans="1:15" s="51" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="54" t="s">
-        <v>922</v>
-      </c>
-      <c r="B53" s="90"/>
+        <v>921</v>
+      </c>
+      <c r="B53" s="85"/>
       <c r="C53" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D53" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E53" s="47" t="s">
         <v>923</v>
       </c>
-      <c r="E53" s="47" t="s">
+      <c r="F53" s="47" t="s">
         <v>924</v>
       </c>
-      <c r="F53" s="47" t="s">
+      <c r="G53" s="47" t="s">
         <v>925</v>
       </c>
-      <c r="G53" s="47" t="s">
-        <v>926</v>
-      </c>
       <c r="H53" s="48" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="I53" s="46" t="s">
         <v>39</v>
@@ -16766,23 +16763,23 @@
     </row>
     <row r="54" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="54" t="s">
-        <v>927</v>
-      </c>
-      <c r="B54" s="90"/>
+        <v>926</v>
+      </c>
+      <c r="B54" s="85"/>
       <c r="C54" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D54" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="E54" s="47" t="s">
         <v>928</v>
       </c>
-      <c r="E54" s="47" t="s">
+      <c r="F54" s="47" t="s">
         <v>929</v>
       </c>
-      <c r="F54" s="47" t="s">
+      <c r="G54" s="47" t="s">
         <v>930</v>
-      </c>
-      <c r="G54" s="47" t="s">
-        <v>931</v>
       </c>
       <c r="H54" s="48" t="s">
         <v>23</v>
@@ -16803,31 +16800,31 @@
         <v>1</v>
       </c>
       <c r="N54" s="47" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="O54" s="47" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="55" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="54" t="s">
-        <v>933</v>
-      </c>
-      <c r="B55" s="90"/>
+        <v>932</v>
+      </c>
+      <c r="B55" s="85"/>
       <c r="C55" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D55" s="47" t="s">
+        <v>933</v>
+      </c>
+      <c r="E55" s="47" t="s">
         <v>934</v>
       </c>
-      <c r="E55" s="47" t="s">
+      <c r="F55" s="47" t="s">
         <v>935</v>
       </c>
-      <c r="F55" s="47" t="s">
-        <v>936</v>
-      </c>
       <c r="G55" s="47" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H55" s="48" t="s">
         <v>23</v>
@@ -16848,31 +16845,31 @@
         <v>1</v>
       </c>
       <c r="N55" s="47" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="O55" s="47" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="56" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="54" t="s">
-        <v>938</v>
-      </c>
-      <c r="B56" s="90"/>
+        <v>937</v>
+      </c>
+      <c r="B56" s="85"/>
       <c r="C56" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D56" s="47" t="s">
+        <v>938</v>
+      </c>
+      <c r="E56" s="47" t="s">
         <v>939</v>
       </c>
-      <c r="E56" s="47" t="s">
+      <c r="F56" s="47" t="s">
         <v>940</v>
       </c>
-      <c r="F56" s="47" t="s">
+      <c r="G56" s="47" t="s">
         <v>941</v>
-      </c>
-      <c r="G56" s="47" t="s">
-        <v>942</v>
       </c>
       <c r="H56" s="48" t="s">
         <v>23</v>
@@ -16893,28 +16890,28 @@
         <v>1</v>
       </c>
       <c r="N56" s="47" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="O56" s="47" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="57" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="54" t="s">
-        <v>944</v>
-      </c>
-      <c r="B57" s="90"/>
+        <v>943</v>
+      </c>
+      <c r="B57" s="85"/>
       <c r="C57" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D57" s="47" t="s">
+        <v>944</v>
+      </c>
+      <c r="E57" s="47" t="s">
         <v>945</v>
       </c>
-      <c r="E57" s="47" t="s">
+      <c r="F57" s="47" t="s">
         <v>946</v>
-      </c>
-      <c r="F57" s="47" t="s">
-        <v>947</v>
       </c>
       <c r="G57" s="47" t="s">
         <v>141</v>
@@ -16938,28 +16935,28 @@
         <v>1</v>
       </c>
       <c r="N57" s="47" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="O57" s="47" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="58" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="54" t="s">
-        <v>949</v>
-      </c>
-      <c r="B58" s="90"/>
+        <v>948</v>
+      </c>
+      <c r="B58" s="85"/>
       <c r="C58" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D58" s="47" t="s">
+        <v>949</v>
+      </c>
+      <c r="E58" s="47" t="s">
         <v>950</v>
       </c>
-      <c r="E58" s="47" t="s">
+      <c r="F58" s="47" t="s">
         <v>951</v>
-      </c>
-      <c r="F58" s="47" t="s">
-        <v>952</v>
       </c>
       <c r="G58" s="47" t="s">
         <v>33</v>
@@ -16983,31 +16980,31 @@
         <v>1</v>
       </c>
       <c r="N58" s="47" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="O58" s="47" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="59" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="54" t="s">
-        <v>954</v>
-      </c>
-      <c r="B59" s="90"/>
+        <v>953</v>
+      </c>
+      <c r="B59" s="85"/>
       <c r="C59" s="47" t="s">
         <v>29</v>
       </c>
       <c r="D59" s="47" t="s">
+        <v>954</v>
+      </c>
+      <c r="E59" s="47" t="s">
         <v>955</v>
       </c>
-      <c r="E59" s="47" t="s">
+      <c r="F59" s="47" t="s">
         <v>956</v>
       </c>
-      <c r="F59" s="47" t="s">
+      <c r="G59" s="47" t="s">
         <v>957</v>
-      </c>
-      <c r="G59" s="47" t="s">
-        <v>958</v>
       </c>
       <c r="H59" s="48" t="s">
         <v>23</v>
@@ -17028,31 +17025,31 @@
         <v>1</v>
       </c>
       <c r="N59" s="47" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="O59" s="47" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="60" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="54" t="s">
+        <v>959</v>
+      </c>
+      <c r="B60" s="85"/>
+      <c r="C60" s="47" t="s">
         <v>960</v>
       </c>
-      <c r="B60" s="90"/>
-      <c r="C60" s="47" t="s">
+      <c r="D60" s="47" t="s">
         <v>961</v>
       </c>
-      <c r="D60" s="47" t="s">
+      <c r="E60" s="47" t="s">
         <v>962</v>
       </c>
-      <c r="E60" s="47" t="s">
+      <c r="F60" s="47" t="s">
         <v>963</v>
       </c>
-      <c r="F60" s="47" t="s">
+      <c r="G60" s="47" t="s">
         <v>964</v>
-      </c>
-      <c r="G60" s="47" t="s">
-        <v>965</v>
       </c>
       <c r="H60" s="48" t="s">
         <v>23</v>
@@ -17073,31 +17070,31 @@
         <v>1</v>
       </c>
       <c r="N60" s="47" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="O60" s="47" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="61" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="54" t="s">
-        <v>967</v>
-      </c>
-      <c r="B61" s="90"/>
+        <v>966</v>
+      </c>
+      <c r="B61" s="85"/>
       <c r="C61" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D61" s="47" t="s">
+        <v>967</v>
+      </c>
+      <c r="E61" s="47" t="s">
         <v>968</v>
       </c>
-      <c r="E61" s="47" t="s">
+      <c r="F61" s="47" t="s">
         <v>969</v>
       </c>
-      <c r="F61" s="47" t="s">
-        <v>970</v>
-      </c>
       <c r="G61" s="47" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H61" s="48" t="s">
         <v>23</v>
@@ -17118,31 +17115,31 @@
         <v>1</v>
       </c>
       <c r="N61" s="47" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="O61" s="47" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="62" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="54" t="s">
-        <v>972</v>
-      </c>
-      <c r="B62" s="90"/>
+        <v>971</v>
+      </c>
+      <c r="B62" s="85"/>
       <c r="C62" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D62" s="47" t="s">
+        <v>972</v>
+      </c>
+      <c r="E62" s="47" t="s">
         <v>973</v>
       </c>
-      <c r="E62" s="47" t="s">
+      <c r="F62" s="47" t="s">
         <v>974</v>
       </c>
-      <c r="F62" s="47" t="s">
+      <c r="G62" s="47" t="s">
         <v>975</v>
-      </c>
-      <c r="G62" s="47" t="s">
-        <v>976</v>
       </c>
       <c r="H62" s="48" t="s">
         <v>23</v>
@@ -17164,25 +17161,25 @@
       </c>
       <c r="N62" s="47"/>
       <c r="O62" s="47" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="63" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="54" t="s">
-        <v>978</v>
-      </c>
-      <c r="B63" s="83"/>
+        <v>977</v>
+      </c>
+      <c r="B63" s="86"/>
       <c r="C63" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D63" s="47" t="s">
+        <v>978</v>
+      </c>
+      <c r="E63" s="47" t="s">
         <v>979</v>
       </c>
-      <c r="E63" s="47" t="s">
+      <c r="F63" s="47" t="s">
         <v>980</v>
-      </c>
-      <c r="F63" s="47" t="s">
-        <v>981</v>
       </c>
       <c r="G63" s="47" t="s">
         <v>71</v>
@@ -17206,14 +17203,18 @@
         <v>1</v>
       </c>
       <c r="N63" s="47" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="O63" s="47" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B32:B41"/>
+    <mergeCell ref="B7:B9"/>
     <mergeCell ref="B51:B63"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B19:B22"/>
@@ -17221,10 +17222,6 @@
     <mergeCell ref="B44:B49"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B25:B29"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B32:B41"/>
-    <mergeCell ref="B7:B9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
@@ -17254,23 +17251,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
     </row>
     <row r="2" spans="1:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="55" t="s">
@@ -17323,7 +17320,7 @@
       <c r="A3" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="84" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="56" t="s">
@@ -17368,7 +17365,7 @@
       <c r="A4" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="90"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="59" t="s">
         <v>29</v>
       </c>
@@ -17411,7 +17408,7 @@
       <c r="A5" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="90"/>
+      <c r="B5" s="85"/>
       <c r="C5" s="56" t="s">
         <v>29</v>
       </c>
@@ -17454,7 +17451,7 @@
       <c r="A6" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="83"/>
+      <c r="B6" s="86"/>
       <c r="C6" s="59" t="s">
         <v>18</v>
       </c>
@@ -17544,7 +17541,7 @@
       <c r="A8" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="87" t="s">
         <v>58</v>
       </c>
       <c r="C8" s="59" t="s">
@@ -17589,7 +17586,7 @@
       <c r="A9" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="83"/>
+      <c r="B9" s="86"/>
       <c r="C9" s="56" t="s">
         <v>67</v>
       </c>
@@ -17634,7 +17631,7 @@
       <c r="A10" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="82" t="s">
+      <c r="B10" s="87" t="s">
         <v>74</v>
       </c>
       <c r="C10" s="59" t="s">
@@ -17681,7 +17678,7 @@
       <c r="A11" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="83"/>
+      <c r="B11" s="86"/>
       <c r="C11" s="56" t="s">
         <v>59</v>
       </c>
@@ -17724,7 +17721,7 @@
       <c r="A12" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="82" t="s">
+      <c r="B12" s="87" t="s">
         <v>88</v>
       </c>
       <c r="C12" s="59" t="s">
@@ -17771,7 +17768,7 @@
       <c r="A13" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="B13" s="83"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="56" t="s">
         <v>29</v>
       </c>
@@ -17906,29 +17903,29 @@
     </row>
     <row r="16" spans="1:15" ht="52.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="88" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="92"/>
-      <c r="F17" s="92"/>
-      <c r="G17" s="92"/>
-      <c r="H17" s="92"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="92"/>
-      <c r="K17" s="92"/>
-      <c r="L17" s="92"/>
-      <c r="M17" s="92"/>
-      <c r="N17" s="92"/>
-      <c r="O17" s="93"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="90"/>
     </row>
     <row r="18" spans="1:15" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="93" t="s">
         <v>117</v>
       </c>
       <c r="C18" s="61" t="s">
@@ -17969,7 +17966,7 @@
       <c r="A19" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="B19" s="83"/>
+      <c r="B19" s="86"/>
       <c r="C19" s="64" t="s">
         <v>118</v>
       </c>
@@ -18013,7 +18010,7 @@
       <c r="A21" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="84" t="s">
+      <c r="B21" s="91" t="s">
         <v>131</v>
       </c>
       <c r="C21" s="68" t="s">
@@ -18054,7 +18051,7 @@
       <c r="A22" s="68" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="85"/>
+      <c r="B22" s="83"/>
       <c r="C22" s="68" t="s">
         <v>18</v>
       </c>
@@ -18093,7 +18090,7 @@
       <c r="A23" s="68" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="85"/>
+      <c r="B23" s="83"/>
       <c r="C23" s="68" t="s">
         <v>18</v>
       </c>
@@ -18132,7 +18129,7 @@
       <c r="A24" s="68" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="85"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="68" t="s">
         <v>18</v>
       </c>
@@ -18173,7 +18170,7 @@
       <c r="A25" s="68" t="s">
         <v>154</v>
       </c>
-      <c r="B25" s="85"/>
+      <c r="B25" s="83"/>
       <c r="C25" s="68" t="s">
         <v>29</v>
       </c>
@@ -18212,7 +18209,7 @@
       <c r="A26" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="85"/>
+      <c r="B26" s="83"/>
       <c r="C26" s="68" t="s">
         <v>67</v>
       </c>
@@ -18294,7 +18291,7 @@
       <c r="A28" s="68" t="s">
         <v>175</v>
       </c>
-      <c r="B28" s="84" t="s">
+      <c r="B28" s="91" t="s">
         <v>176</v>
       </c>
       <c r="C28" s="68" t="s">
@@ -18335,7 +18332,7 @@
       <c r="A29" s="68" t="s">
         <v>182</v>
       </c>
-      <c r="B29" s="85"/>
+      <c r="B29" s="83"/>
       <c r="C29" s="68" t="s">
         <v>183</v>
       </c>
@@ -18374,7 +18371,7 @@
       <c r="A30" s="68" t="s">
         <v>189</v>
       </c>
-      <c r="B30" s="85"/>
+      <c r="B30" s="83"/>
       <c r="C30" s="68" t="s">
         <v>67</v>
       </c>
@@ -18450,23 +18447,23 @@
       <c r="O32" s="72"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="87" t="s">
+      <c r="A33" s="82" t="s">
         <v>197</v>
       </c>
-      <c r="B33" s="85"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85"/>
-      <c r="F33" s="85"/>
-      <c r="G33" s="85"/>
-      <c r="H33" s="85"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="85"/>
-      <c r="K33" s="85"/>
-      <c r="L33" s="85"/>
-      <c r="M33" s="85"/>
-      <c r="N33" s="85"/>
-      <c r="O33" s="85"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
+      <c r="J33" s="83"/>
+      <c r="K33" s="83"/>
+      <c r="L33" s="83"/>
+      <c r="M33" s="83"/>
+      <c r="N33" s="83"/>
+      <c r="O33" s="83"/>
     </row>
     <row r="34" spans="1:15" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="70" t="s">
@@ -18549,7 +18546,7 @@
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="92" t="s">
         <v>205</v>
       </c>
       <c r="B36" t="s">
@@ -18559,10 +18556,10 @@
         <v>18</v>
       </c>
       <c r="D36" t="s">
+        <v>261</v>
+      </c>
+      <c r="E36" t="s">
         <v>262</v>
-      </c>
-      <c r="E36" t="s">
-        <v>263</v>
       </c>
       <c r="F36" t="s">
         <v>213</v>
@@ -18586,11 +18583,11 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="108"/>
+      <c r="A37" s="92"/>
       <c r="B37" t="s">
         <v>199</v>
       </c>
@@ -18598,10 +18595,10 @@
         <v>18</v>
       </c>
       <c r="D37" t="s">
+        <v>264</v>
+      </c>
+      <c r="E37" t="s">
         <v>265</v>
-      </c>
-      <c r="E37" t="s">
-        <v>266</v>
       </c>
       <c r="F37" t="s">
         <v>213</v>
@@ -18625,11 +18622,11 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="108"/>
+      <c r="A38" s="92"/>
       <c r="B38" t="s">
         <v>199</v>
       </c>
@@ -18637,10 +18634,10 @@
         <v>67</v>
       </c>
       <c r="D38" t="s">
+        <v>267</v>
+      </c>
+      <c r="E38" t="s">
         <v>268</v>
-      </c>
-      <c r="E38" t="s">
-        <v>269</v>
       </c>
       <c r="F38" t="s">
         <v>213</v>
@@ -18664,11 +18661,11 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="108"/>
+      <c r="A39" s="92"/>
       <c r="B39" t="s">
         <v>199</v>
       </c>
@@ -18676,10 +18673,10 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
+        <v>270</v>
+      </c>
+      <c r="E39" t="s">
         <v>271</v>
-      </c>
-      <c r="E39" t="s">
-        <v>272</v>
       </c>
       <c r="F39" t="s">
         <v>213</v>
@@ -18703,11 +18700,11 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="108"/>
+      <c r="A40" s="92"/>
       <c r="B40" t="s">
         <v>199</v>
       </c>
@@ -18715,10 +18712,10 @@
         <v>18</v>
       </c>
       <c r="D40" t="s">
+        <v>273</v>
+      </c>
+      <c r="E40" t="s">
         <v>274</v>
-      </c>
-      <c r="E40" t="s">
-        <v>275</v>
       </c>
       <c r="F40" t="s">
         <v>213</v>
@@ -18742,11 +18739,11 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="108"/>
+      <c r="A41" s="92"/>
       <c r="B41" t="s">
         <v>199</v>
       </c>
@@ -18754,10 +18751,10 @@
         <v>67</v>
       </c>
       <c r="D41" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" t="s">
         <v>277</v>
-      </c>
-      <c r="E41" t="s">
-        <v>278</v>
       </c>
       <c r="F41" t="s">
         <v>213</v>
@@ -18781,7 +18778,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="79" customFormat="1" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -18861,7 +18858,7 @@
     </row>
     <row r="45" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A45" s="81" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B45" s="81"/>
       <c r="C45" s="70"/>
@@ -18896,23 +18893,23 @@
       <c r="O46" s="70"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="82" t="s">
         <v>220</v>
       </c>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="85"/>
-      <c r="E47" s="85"/>
-      <c r="F47" s="85"/>
-      <c r="G47" s="85"/>
-      <c r="H47" s="85"/>
-      <c r="I47" s="85"/>
-      <c r="J47" s="85"/>
-      <c r="K47" s="85"/>
-      <c r="L47" s="85"/>
-      <c r="M47" s="85"/>
-      <c r="N47" s="85"/>
-      <c r="O47" s="85"/>
+      <c r="B47" s="83"/>
+      <c r="C47" s="83"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="83"/>
+      <c r="I47" s="83"/>
+      <c r="J47" s="83"/>
+      <c r="K47" s="83"/>
+      <c r="L47" s="83"/>
+      <c r="M47" s="83"/>
+      <c r="N47" s="83"/>
+      <c r="O47" s="83"/>
     </row>
     <row r="48" spans="1:15" ht="66" x14ac:dyDescent="0.3">
       <c r="A48" s="81" t="s">
@@ -19053,25 +19050,25 @@
       <c r="O51" s="70"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" s="87" t="s">
+      <c r="A52" s="82" t="s">
         <v>235</v>
       </c>
-      <c r="B52" s="85"/>
-      <c r="C52" s="85"/>
-      <c r="D52" s="85"/>
-      <c r="E52" s="85"/>
-      <c r="F52" s="85"/>
-      <c r="G52" s="85"/>
-      <c r="H52" s="85"/>
-      <c r="I52" s="85"/>
-      <c r="J52" s="85"/>
-      <c r="K52" s="85"/>
-      <c r="L52" s="85"/>
-      <c r="M52" s="85"/>
-      <c r="N52" s="85"/>
-      <c r="O52" s="85"/>
-    </row>
-    <row r="53" spans="1:15" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="B52" s="83"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="83"/>
+      <c r="J52" s="83"/>
+      <c r="K52" s="83"/>
+      <c r="L52" s="83"/>
+      <c r="M52" s="83"/>
+      <c r="N52" s="83"/>
+      <c r="O52" s="83"/>
+    </row>
+    <row r="53" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A53" s="81" t="s">
         <v>219</v>
       </c>
@@ -19084,11 +19081,9 @@
       <c r="D53" s="70" t="s">
         <v>239</v>
       </c>
-      <c r="E53" s="81" t="s">
+      <c r="E53" s="81"/>
+      <c r="F53" s="70" t="s">
         <v>240</v>
-      </c>
-      <c r="F53" s="70" t="s">
-        <v>241</v>
       </c>
       <c r="G53" s="70"/>
       <c r="H53" s="71" t="s">
@@ -19106,10 +19101,10 @@
         <v>0</v>
       </c>
       <c r="N53" s="70" t="s">
+        <v>241</v>
+      </c>
+      <c r="O53" s="70" t="s">
         <v>242</v>
-      </c>
-      <c r="O53" s="70" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
@@ -19130,45 +19125,45 @@
       <c r="O54" s="70"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="87" t="s">
-        <v>244</v>
-      </c>
-      <c r="B55" s="85"/>
-      <c r="C55" s="85"/>
-      <c r="D55" s="85"/>
-      <c r="E55" s="85"/>
-      <c r="F55" s="85"/>
-      <c r="G55" s="85"/>
-      <c r="H55" s="85"/>
-      <c r="I55" s="85"/>
-      <c r="J55" s="85"/>
-      <c r="K55" s="85"/>
-      <c r="L55" s="85"/>
-      <c r="M55" s="85"/>
-      <c r="N55" s="85"/>
-      <c r="O55" s="85"/>
+      <c r="A55" s="82" t="s">
+        <v>243</v>
+      </c>
+      <c r="B55" s="83"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="83"/>
+      <c r="E55" s="83"/>
+      <c r="F55" s="83"/>
+      <c r="G55" s="83"/>
+      <c r="H55" s="83"/>
+      <c r="I55" s="83"/>
+      <c r="J55" s="83"/>
+      <c r="K55" s="83"/>
+      <c r="L55" s="83"/>
+      <c r="M55" s="83"/>
+      <c r="N55" s="83"/>
+      <c r="O55" s="83"/>
     </row>
     <row r="56" spans="1:15" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A56" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="B56" s="81" t="s">
         <v>245</v>
       </c>
-      <c r="B56" s="81" t="s">
+      <c r="C56" s="70" t="s">
         <v>246</v>
       </c>
-      <c r="C56" s="70" t="s">
+      <c r="D56" s="70" t="s">
         <v>247</v>
       </c>
-      <c r="D56" s="70" t="s">
+      <c r="E56" s="81" t="s">
         <v>248</v>
       </c>
-      <c r="E56" s="81" t="s">
+      <c r="F56" s="70" t="s">
         <v>249</v>
       </c>
-      <c r="F56" s="70" t="s">
+      <c r="G56" s="70" t="s">
         <v>250</v>
-      </c>
-      <c r="G56" s="70" t="s">
-        <v>251</v>
       </c>
       <c r="H56" s="71" t="s">
         <v>203</v>
@@ -19188,30 +19183,30 @@
         <v>236</v>
       </c>
       <c r="O56" s="70" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="66" x14ac:dyDescent="0.3">
       <c r="A57" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="B57" s="81" t="s">
         <v>253</v>
       </c>
-      <c r="B57" s="81" t="s">
+      <c r="C57" s="70" t="s">
         <v>254</v>
       </c>
-      <c r="C57" s="70" t="s">
+      <c r="D57" s="70" t="s">
         <v>255</v>
       </c>
-      <c r="D57" s="70" t="s">
+      <c r="E57" s="81" t="s">
         <v>256</v>
       </c>
-      <c r="E57" s="81" t="s">
+      <c r="F57" s="70" t="s">
         <v>257</v>
       </c>
-      <c r="F57" s="70" t="s">
+      <c r="G57" s="70" t="s">
         <v>258</v>
-      </c>
-      <c r="G57" s="70" t="s">
-        <v>259</v>
       </c>
       <c r="H57" s="71" t="s">
         <v>203</v>
@@ -19228,14 +19223,15 @@
         <v>0</v>
       </c>
       <c r="N57" s="70" t="s">
+        <v>259</v>
+      </c>
+      <c r="O57" s="70" t="s">
         <v>260</v>
-      </c>
-      <c r="O57" s="70" t="s">
-        <v>261</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:O1"/>
     <mergeCell ref="A47:O47"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B8:B9"/>
@@ -19249,7 +19245,6 @@
     <mergeCell ref="B21:B26"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="A33:O33"/>
-    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19270,12 +19265,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
-        <v>983</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
+      <c r="A1" s="98" t="s">
+        <v>982</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -19329,16 +19324,16 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>984</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>985</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>986</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -19365,16 +19360,16 @@
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>987</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>988</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>989</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>990</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -19401,16 +19396,16 @@
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>992</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>993</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>994</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -19437,16 +19432,16 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>994</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>995</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>996</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>997</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>998</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -19473,16 +19468,16 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>999</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>1000</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>1001</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>1002</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\cortexkitchen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D201C1A-296E-4B54-9A50-042696BEA2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249336FE-9354-4772-B4D5-4C8B8C038652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="996">
   <si>
     <t>Phase 6A — Restaurant OS: compliance fixes + autonomous procurement + operator features</t>
   </si>
@@ -674,9 +674,6 @@
     <t>npx tsc --noEmit and npx eslint both clean on every touched file. Visual verification was via user-provided screenshots of the actual running app (not a live browser session driven by the agent -- browser tooling was declined this session) -- light mode only, confirmed across three iterative rounds of user feedback. Dark mode NOT verified this pass; flag for a follow-up check given the standing light-mode-parity requirement.</t>
   </si>
   <si>
-    <t>P6-A34</t>
-  </si>
-  <si>
     <t>P6-A35</t>
   </si>
   <si>
@@ -695,42 +692,24 @@
     <t>Automate golden dataset regeneration + RAGAS/DeepEval promotion pipeline</t>
   </si>
   <si>
-    <t>Automate turning the RAGAS/DeepEval candidate-dataset scripts' output into the actual golden eval fixtures (currently a manual promotion step), and automate golden dataset regeneration when seed data or scenarios change, instead of a one-off manual run.</t>
-  </si>
-  <si>
     <t>feat: automate golden dataset regeneration + eval promotion pipeline</t>
   </si>
   <si>
     <t>docs/EVALUATION.md</t>
   </si>
   <si>
-    <t>pipeline run regenerates fixtures without manual intervention; promoted fixtures pass existing RAGAS/DeepEval suites</t>
-  </si>
-  <si>
     <t>Make observability genuinely dynamic instead of manually checked</t>
   </si>
   <si>
-    <t>Current observability (Langfuse traces, per-node ObservabilityStrip, cost/token tracking) requires manually opening dashboards/traces to check health. Add automated checks/alerting so regressions surface proactively instead of requiring a manual look.</t>
-  </si>
-  <si>
     <t>feat: dynamic observability -- automated health checks instead of manual review</t>
   </si>
   <si>
-    <t>an induced regression (e.g. a broken node) is caught automatically, not just visible if someone happens to check</t>
-  </si>
-  <si>
     <t>CI pipeline hygiene: close current gaps</t>
   </si>
   <si>
-    <t>Pulled forward from the Phase 7 sheet's P7-24 audit. Confirm every service/model added across Phase 6A (Action Queue, workflow triggers, trust-ladder, WhatsApp vendor flow, Vendor/Supplier model, Menu Engineering Matrix, live-intelligence signals, Langfuse/Kindred) has test coverage and is included in the CI pipeline; expand RAGAS/DeepEval eval sets to cover agentic behaviors the existing eval sets predate (workflow-triggered actions, trust-ladder promotions, custom-profile scenario composition).</t>
-  </si>
-  <si>
     <t>chore: CI pipeline hygiene -- close Phase 6A test/CI/eval gaps</t>
   </si>
   <si>
-    <t>no new service/model lacks tests; CI includes every new test file; eval sets cover new agentic behaviors</t>
-  </si>
-  <si>
     <t>END-TO-END HARDENING -- priority 4</t>
   </si>
   <si>
@@ -3032,7 +3011,7 @@
     <t>Continue throughout project</t>
   </si>
   <si>
-    <t>guest concierge</t>
+    <t>p6-a34  guest concierge</t>
   </si>
 </sst>
 </file>
@@ -3728,11 +3707,14 @@
     <xf numFmtId="0" fontId="26" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3754,9 +3736,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3784,20 +3763,20 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4027,7 +4006,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="95" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -4085,10 +4064,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -4117,10 +4096,10 @@
     </row>
     <row r="4" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -4149,10 +4128,10 @@
     </row>
     <row r="5" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -4181,10 +4160,10 @@
     </row>
     <row r="6" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -4269,16 +4248,16 @@
     </row>
     <row r="9" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -4305,7 +4284,7 @@
     </row>
     <row r="10" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>23</v>
@@ -4314,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -4341,7 +4320,7 @@
     </row>
     <row r="11" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>23</v>
@@ -4350,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -4377,7 +4356,7 @@
     </row>
     <row r="12" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>23</v>
@@ -4386,7 +4365,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -4413,7 +4392,7 @@
     </row>
     <row r="13" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>23</v>
@@ -4422,7 +4401,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -4449,7 +4428,7 @@
     </row>
     <row r="14" spans="1:26" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>23</v>
@@ -4458,7 +4437,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -4485,7 +4464,7 @@
     </row>
     <row r="15" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>23</v>
@@ -4494,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -4521,16 +4500,16 @@
     </row>
     <row r="16" spans="1:26" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C16" s="15">
         <v>0.78129999999999999</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10191,7 +10170,7 @@
     </row>
     <row r="219" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B219" t="s">
         <v>203</v>
@@ -10200,7 +10179,7 @@
         <v>0</v>
       </c>
       <c r="D219" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="220" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -11015,7 +10994,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="98" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -11036,31 +11015,31 @@
     </row>
     <row r="2" spans="1:17" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="103" t="s">
-        <v>309</v>
-      </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="90"/>
+        <v>302</v>
+      </c>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
+      <c r="Q2" s="91"/>
     </row>
     <row r="3" spans="1:17" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>1</v>
@@ -11072,10 +11051,10 @@
         <v>4</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>8</v>
@@ -11093,63 +11072,63 @@
         <v>12</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="102" t="s">
-        <v>291</v>
-      </c>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="89"/>
-      <c r="P4" s="89"/>
-      <c r="Q4" s="90"/>
+        <v>284</v>
+      </c>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="90"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="91"/>
     </row>
     <row r="5" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>23</v>
@@ -11174,33 +11153,33 @@
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B6" s="21">
         <v>2</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>23</v>
@@ -11224,36 +11203,36 @@
         <v>1</v>
       </c>
       <c r="O6" s="22" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="P6" s="22" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="Q6" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B7" s="16">
         <v>3</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H7" s="18" t="s">
         <v>23</v>
@@ -11277,36 +11256,36 @@
         <v>1</v>
       </c>
       <c r="O7" s="17" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B8" s="21">
         <v>4</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H8" s="18" t="s">
         <v>23</v>
@@ -11330,36 +11309,36 @@
         <v>1</v>
       </c>
       <c r="O8" s="22" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="P8" s="22" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="Q8" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B9" s="16">
         <v>5</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="H9" s="18" t="s">
         <v>23</v>
@@ -11374,66 +11353,66 @@
         <v>46096</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="N9" s="20">
         <v>1</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="Q9" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="102" t="s">
-        <v>293</v>
-      </c>
-      <c r="B10" s="89"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="89"/>
-      <c r="J10" s="89"/>
-      <c r="K10" s="89"/>
-      <c r="L10" s="89"/>
-      <c r="M10" s="89"/>
-      <c r="N10" s="89"/>
-      <c r="O10" s="89"/>
-      <c r="P10" s="89"/>
-      <c r="Q10" s="90"/>
+        <v>286</v>
+      </c>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="90"/>
+      <c r="L10" s="90"/>
+      <c r="M10" s="90"/>
+      <c r="N10" s="90"/>
+      <c r="O10" s="90"/>
+      <c r="P10" s="90"/>
+      <c r="Q10" s="91"/>
     </row>
     <row r="11" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B11" s="21">
         <v>7</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>49</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>23</v>
@@ -11445,48 +11424,48 @@
         <v>25</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="M11" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="N11" s="24">
         <v>1</v>
       </c>
       <c r="O11" s="22" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="P11" s="22" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="Q11" s="22" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B12" s="16">
         <v>8</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>59</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>23</v>
@@ -11510,36 +11489,36 @@
         <v>1</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="Q12" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B13" s="21">
         <v>9</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>49</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>23</v>
@@ -11563,36 +11542,36 @@
         <v>1</v>
       </c>
       <c r="O13" s="22" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="P13" s="22" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B14" s="16">
         <v>10</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>183</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>23</v>
@@ -11616,36 +11595,36 @@
         <v>1</v>
       </c>
       <c r="O14" s="17" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="Q14" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B15" s="21">
         <v>11</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="D15" s="22" t="s">
         <v>49</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="H15" s="18" t="s">
         <v>23</v>
@@ -11669,36 +11648,36 @@
         <v>1</v>
       </c>
       <c r="O15" s="22" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="P15" s="22" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B16" s="16">
         <v>12</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>49</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>23</v>
@@ -11722,36 +11701,36 @@
         <v>1</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Q16" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B17" s="21">
         <v>13</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="H17" s="18" t="s">
         <v>23</v>
@@ -11775,36 +11754,36 @@
         <v>1</v>
       </c>
       <c r="O17" s="22" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="P17" s="22" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="Q17" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B18" s="16">
         <v>14</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>23</v>
@@ -11828,36 +11807,36 @@
         <v>1</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Q18" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B19" s="21">
         <v>15</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>49</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="H19" s="18" t="s">
         <v>23</v>
@@ -11881,36 +11860,36 @@
         <v>1</v>
       </c>
       <c r="O19" s="22" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="P19" s="22" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="Q19" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B20" s="16">
         <v>16</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>67</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="H20" s="18" t="s">
         <v>23</v>
@@ -11934,36 +11913,36 @@
         <v>1</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Q20" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B21" s="21">
         <v>17</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>23</v>
@@ -11987,36 +11966,36 @@
         <v>1</v>
       </c>
       <c r="O21" s="22" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="P21" s="22" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="Q21" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B22" s="16">
         <v>18</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>23</v>
@@ -12040,57 +12019,57 @@
         <v>1</v>
       </c>
       <c r="O22" s="17" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="Q22" s="17" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="99" t="s">
-        <v>295</v>
-      </c>
-      <c r="B23" s="89"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="89"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="89"/>
-      <c r="K23" s="89"/>
-      <c r="L23" s="89"/>
-      <c r="M23" s="89"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="89"/>
-      <c r="P23" s="89"/>
-      <c r="Q23" s="90"/>
+        <v>288</v>
+      </c>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="90"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="90"/>
+      <c r="O23" s="90"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="91"/>
     </row>
     <row r="24" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B24" s="21">
         <v>19</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="H24" s="18" t="s">
         <v>23</v>
@@ -12114,36 +12093,36 @@
         <v>1</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="P24" s="22" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="Q24" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B25" s="25">
         <v>20</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="H25" s="18" t="s">
         <v>23</v>
@@ -12167,36 +12146,36 @@
         <v>1</v>
       </c>
       <c r="O25" s="26" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="P25" s="26" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="Q25" s="26" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B26" s="21">
         <v>21</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="H26" s="18" t="s">
         <v>23</v>
@@ -12220,36 +12199,36 @@
         <v>1</v>
       </c>
       <c r="O26" s="22" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="P26" s="22" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="Q26" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B27" s="25">
         <v>22</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="D27" s="26" t="s">
         <v>67</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>23</v>
@@ -12273,36 +12252,36 @@
         <v>1</v>
       </c>
       <c r="O27" s="26" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="P27" s="26" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="Q27" s="26" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B28" s="21">
         <v>23</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="H28" s="18" t="s">
         <v>23</v>
@@ -12326,36 +12305,36 @@
         <v>1</v>
       </c>
       <c r="O28" s="22" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="P28" s="22" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="Q28" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B29" s="25">
         <v>24</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="H29" s="18" t="s">
         <v>23</v>
@@ -12379,57 +12358,57 @@
         <v>1</v>
       </c>
       <c r="O29" s="26" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="P29" s="26" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="Q29" s="26" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="99" t="s">
-        <v>297</v>
-      </c>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="89"/>
-      <c r="M30" s="89"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="89"/>
-      <c r="P30" s="89"/>
-      <c r="Q30" s="90"/>
+        <v>290</v>
+      </c>
+      <c r="B30" s="90"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="90"/>
+      <c r="O30" s="90"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="91"/>
     </row>
     <row r="31" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B31" s="21">
         <v>25</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="D31" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="H31" s="18" t="s">
         <v>23</v>
@@ -12453,36 +12432,36 @@
         <v>1</v>
       </c>
       <c r="O31" s="22" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="P31" s="22" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="Q31" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B32" s="25">
         <v>26</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="H32" s="18" t="s">
         <v>23</v>
@@ -12506,36 +12485,36 @@
         <v>1</v>
       </c>
       <c r="O32" s="26" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="P32" s="26" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="Q32" s="26" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B33" s="21">
         <v>27</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="H33" s="18" t="s">
         <v>23</v>
@@ -12559,36 +12538,36 @@
         <v>1</v>
       </c>
       <c r="O33" s="22" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="P33" s="22" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="Q33" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B34" s="25">
         <v>28</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="D34" s="26" t="s">
         <v>29</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="H34" s="18" t="s">
         <v>23</v>
@@ -12612,36 +12591,36 @@
         <v>1</v>
       </c>
       <c r="O34" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="P34" s="26" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="Q34" s="26" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B35" s="21">
         <v>29</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="H35" s="18" t="s">
         <v>23</v>
@@ -12665,57 +12644,57 @@
         <v>1</v>
       </c>
       <c r="O35" s="22" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="P35" s="22" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="Q35" s="22" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="100" t="s">
-        <v>471</v>
-      </c>
-      <c r="B36" s="89"/>
-      <c r="C36" s="89"/>
-      <c r="D36" s="89"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="89"/>
-      <c r="H36" s="89"/>
-      <c r="I36" s="89"/>
-      <c r="J36" s="89"/>
-      <c r="K36" s="89"/>
-      <c r="L36" s="89"/>
-      <c r="M36" s="89"/>
-      <c r="N36" s="89"/>
-      <c r="O36" s="89"/>
-      <c r="P36" s="89"/>
-      <c r="Q36" s="90"/>
+        <v>464</v>
+      </c>
+      <c r="B36" s="90"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="90"/>
+      <c r="F36" s="90"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="90"/>
+      <c r="I36" s="90"/>
+      <c r="J36" s="90"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="90"/>
+      <c r="M36" s="90"/>
+      <c r="N36" s="90"/>
+      <c r="O36" s="90"/>
+      <c r="P36" s="90"/>
+      <c r="Q36" s="91"/>
     </row>
     <row r="37" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="29" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B37" s="29">
         <v>30</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D37" s="30" t="s">
         <v>183</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="G37" s="30" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="H37" s="18" t="s">
         <v>23</v>
@@ -12739,36 +12718,36 @@
         <v>1</v>
       </c>
       <c r="O37" s="30" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="P37" s="30" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="Q37" s="30" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B38" s="21">
         <v>31</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="D38" s="22" t="s">
         <v>67</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="H38" s="18" t="s">
         <v>23</v>
@@ -12792,36 +12771,36 @@
         <v>1</v>
       </c>
       <c r="O38" s="22" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="P38" s="22" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="Q38" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="29" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B39" s="29">
         <v>31</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="D39" s="30" t="s">
         <v>67</v>
       </c>
       <c r="E39" s="30" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G39" s="30" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="H39" s="18" t="s">
         <v>23</v>
@@ -12845,57 +12824,57 @@
         <v>1</v>
       </c>
       <c r="O39" s="30" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="P39" s="30" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="Q39" s="30" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="101" t="s">
-        <v>299</v>
-      </c>
-      <c r="B40" s="89"/>
-      <c r="C40" s="89"/>
-      <c r="D40" s="89"/>
-      <c r="E40" s="89"/>
-      <c r="F40" s="89"/>
-      <c r="G40" s="89"/>
-      <c r="H40" s="89"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="89"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="89"/>
-      <c r="M40" s="89"/>
-      <c r="N40" s="89"/>
-      <c r="O40" s="89"/>
-      <c r="P40" s="89"/>
-      <c r="Q40" s="90"/>
+        <v>292</v>
+      </c>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="90"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="90"/>
+      <c r="O40" s="90"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="91"/>
     </row>
     <row r="41" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B41" s="21">
         <v>1</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="D41" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="H41" s="18" t="s">
         <v>23</v>
@@ -12919,36 +12898,36 @@
         <v>1</v>
       </c>
       <c r="O41" s="22" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="P41" s="22" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="Q41" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B42" s="16">
         <v>2</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="D42" s="17" t="s">
         <v>169</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H42" s="18" t="s">
         <v>23</v>
@@ -12972,36 +12951,36 @@
         <v>1</v>
       </c>
       <c r="O42" s="17" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="P42" s="17" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="Q42" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="21" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B43" s="21">
         <v>3</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="H43" s="18" t="s">
         <v>23</v>
@@ -13025,36 +13004,36 @@
         <v>1</v>
       </c>
       <c r="O43" s="22" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="P43" s="22" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="Q43" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B44" s="16">
         <v>4</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D44" s="17" t="s">
         <v>169</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="H44" s="18" t="s">
         <v>23</v>
@@ -13078,36 +13057,36 @@
         <v>1</v>
       </c>
       <c r="O44" s="17" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="P44" s="17" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="Q44" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="21" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B45" s="21">
         <v>5</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="D45" s="22" t="s">
         <v>169</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="H45" s="18" t="s">
         <v>23</v>
@@ -13131,36 +13110,36 @@
         <v>1</v>
       </c>
       <c r="O45" s="22" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="P45" s="22" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="Q45" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="16" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B46" s="16">
         <v>6</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="D46" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="H46" s="18" t="s">
         <v>23</v>
@@ -13184,36 +13163,36 @@
         <v>1</v>
       </c>
       <c r="O46" s="17" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="P46" s="17" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="Q46" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="21" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B47" s="21">
         <v>7</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="D47" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="H47" s="18" t="s">
         <v>23</v>
@@ -13237,36 +13216,36 @@
         <v>1</v>
       </c>
       <c r="O47" s="22" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="P47" s="22" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="Q47" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="16" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B48" s="16">
         <v>8</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="D48" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="H48" s="18" t="s">
         <v>23</v>
@@ -13290,36 +13269,36 @@
         <v>1</v>
       </c>
       <c r="O48" s="17" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="P48" s="17" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="Q48" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="21" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B49" s="21">
         <v>9</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="D49" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="H49" s="18" t="s">
         <v>23</v>
@@ -13343,36 +13322,36 @@
         <v>1</v>
       </c>
       <c r="O49" s="22" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="P49" s="22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="Q49" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="16" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B50" s="16">
         <v>10</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="H50" s="18" t="s">
         <v>23</v>
@@ -13396,36 +13375,36 @@
         <v>1</v>
       </c>
       <c r="O50" s="17" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="P50" s="17" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="Q50" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="21" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B51" s="21">
         <v>11</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="H51" s="18" t="s">
         <v>23</v>
@@ -13449,36 +13428,36 @@
         <v>1</v>
       </c>
       <c r="O51" s="22" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="P51" s="22" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="Q51" s="22" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="16" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B52" s="16">
         <v>12</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D52" s="17" t="s">
         <v>59</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="H52" s="18" t="s">
         <v>23</v>
@@ -13502,36 +13481,36 @@
         <v>1</v>
       </c>
       <c r="O52" s="17" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="P52" s="17" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="Q52" s="17" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="21" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B53" s="21">
         <v>13</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="H53" s="18" t="s">
         <v>23</v>
@@ -13555,57 +13534,57 @@
         <v>1</v>
       </c>
       <c r="O53" s="22" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="P53" s="22" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="Q53" s="22" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="101" t="s">
-        <v>301</v>
-      </c>
-      <c r="B54" s="89"/>
-      <c r="C54" s="89"/>
-      <c r="D54" s="89"/>
-      <c r="E54" s="89"/>
-      <c r="F54" s="89"/>
-      <c r="G54" s="89"/>
-      <c r="H54" s="89"/>
-      <c r="I54" s="89"/>
-      <c r="J54" s="89"/>
-      <c r="K54" s="89"/>
-      <c r="L54" s="89"/>
-      <c r="M54" s="89"/>
-      <c r="N54" s="89"/>
-      <c r="O54" s="89"/>
-      <c r="P54" s="89"/>
-      <c r="Q54" s="90"/>
+        <v>294</v>
+      </c>
+      <c r="B54" s="90"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="90"/>
+      <c r="E54" s="90"/>
+      <c r="F54" s="90"/>
+      <c r="G54" s="90"/>
+      <c r="H54" s="90"/>
+      <c r="I54" s="90"/>
+      <c r="J54" s="90"/>
+      <c r="K54" s="90"/>
+      <c r="L54" s="90"/>
+      <c r="M54" s="90"/>
+      <c r="N54" s="90"/>
+      <c r="O54" s="90"/>
+      <c r="P54" s="90"/>
+      <c r="Q54" s="91"/>
     </row>
     <row r="55" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B55" s="16">
         <v>1</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="D55" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="H55" s="18" t="s">
         <v>23</v>
@@ -13623,36 +13602,36 @@
         <v>0</v>
       </c>
       <c r="O55" s="17" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="P55" s="17" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="Q55" s="17" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="21" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B56" s="21">
         <v>2</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="D56" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="H56" s="18" t="s">
         <v>23</v>
@@ -13670,36 +13649,36 @@
         <v>0</v>
       </c>
       <c r="O56" s="22" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="P56" s="22" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="Q56" s="22" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="16" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B57" s="16">
         <v>3</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D57" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="F57" s="17" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="H57" s="18" t="s">
         <v>23</v>
@@ -13717,36 +13696,36 @@
         <v>0</v>
       </c>
       <c r="O57" s="17" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="P57" s="17" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="Q57" s="17" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="21" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B58" s="21">
         <v>4</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D58" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="H58" s="18" t="s">
         <v>23</v>
@@ -13764,36 +13743,36 @@
         <v>0</v>
       </c>
       <c r="O58" s="22" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="P58" s="22" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="Q58" s="22" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B59" s="16">
         <v>5</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="D59" s="17" t="s">
         <v>59</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="H59" s="18" t="s">
         <v>23</v>
@@ -13811,36 +13790,36 @@
         <v>0</v>
       </c>
       <c r="O59" s="17" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="P59" s="17" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="Q59" s="17" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="21" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B60" s="21">
         <v>6</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="D60" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="H60" s="18" t="s">
         <v>23</v>
@@ -13858,36 +13837,36 @@
         <v>0</v>
       </c>
       <c r="O60" s="22" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="P60" s="22" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="Q60" s="22" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="16" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B61" s="16">
         <v>7</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="D61" s="17" t="s">
         <v>169</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>23</v>
@@ -13905,36 +13884,36 @@
         <v>0</v>
       </c>
       <c r="O61" s="17" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="P61" s="17" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="Q61" s="17" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="21" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B62" s="21">
         <v>8</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="D62" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="G62" s="22" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="H62" s="18" t="s">
         <v>23</v>
@@ -13952,36 +13931,36 @@
         <v>0</v>
       </c>
       <c r="O62" s="22" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="P62" s="22" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="Q62" s="22" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B63" s="16">
         <v>9</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>23</v>
@@ -13999,36 +13978,36 @@
         <v>0</v>
       </c>
       <c r="O63" s="17" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="P63" s="17" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="Q63" s="17" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="21" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B64" s="21">
         <v>10</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="D64" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>23</v>
@@ -14046,36 +14025,36 @@
         <v>0</v>
       </c>
       <c r="O64" s="22" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="P64" s="22" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="Q64" s="22" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="16" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B65" s="16">
         <v>11</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="D65" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>23</v>
@@ -14093,36 +14072,36 @@
         <v>0</v>
       </c>
       <c r="O65" s="17" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="P65" s="17" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="Q65" s="17" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="21" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B66" s="21">
         <v>12</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="D66" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="H66" s="18" t="s">
         <v>23</v>
@@ -14140,36 +14119,36 @@
         <v>0</v>
       </c>
       <c r="O66" s="22" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="P66" s="22" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="Q66" s="22" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="16" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B67" s="16">
         <v>13</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>23</v>
@@ -14187,57 +14166,57 @@
         <v>0</v>
       </c>
       <c r="O67" s="17" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="P67" s="17" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="Q67" s="17" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
     </row>
     <row r="68" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="97" t="s">
-        <v>303</v>
-      </c>
-      <c r="B68" s="89"/>
-      <c r="C68" s="89"/>
-      <c r="D68" s="89"/>
-      <c r="E68" s="89"/>
-      <c r="F68" s="89"/>
-      <c r="G68" s="89"/>
-      <c r="H68" s="89"/>
-      <c r="I68" s="89"/>
-      <c r="J68" s="89"/>
-      <c r="K68" s="89"/>
-      <c r="L68" s="89"/>
-      <c r="M68" s="89"/>
-      <c r="N68" s="89"/>
-      <c r="O68" s="89"/>
-      <c r="P68" s="89"/>
-      <c r="Q68" s="90"/>
+        <v>296</v>
+      </c>
+      <c r="B68" s="90"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="90"/>
+      <c r="E68" s="90"/>
+      <c r="F68" s="90"/>
+      <c r="G68" s="90"/>
+      <c r="H68" s="90"/>
+      <c r="I68" s="90"/>
+      <c r="J68" s="90"/>
+      <c r="K68" s="90"/>
+      <c r="L68" s="90"/>
+      <c r="M68" s="90"/>
+      <c r="N68" s="90"/>
+      <c r="O68" s="90"/>
+      <c r="P68" s="90"/>
+      <c r="Q68" s="91"/>
     </row>
     <row r="69" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="21" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B69" s="21">
         <v>0</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="D69" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="H69" s="18" t="s">
         <v>23</v>
@@ -14246,7 +14225,7 @@
         <v>39</v>
       </c>
       <c r="J69" s="21" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="K69" s="23">
         <v>46192</v>
@@ -14262,33 +14241,33 @@
       </c>
       <c r="O69" s="22"/>
       <c r="P69" s="22" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="Q69" s="22" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
     </row>
     <row r="70" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="33" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B70" s="33">
         <v>0</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="D70" s="34" t="s">
         <v>18</v>
       </c>
       <c r="E70" s="34" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="F70" s="34" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="G70" s="34" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="H70" s="18" t="s">
         <v>23</v>
@@ -14312,36 +14291,36 @@
         <v>1</v>
       </c>
       <c r="O70" s="34" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="P70" s="34" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="Q70" s="34" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71" spans="1:17" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="21" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="D71" s="22" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="H71" s="18" t="s">
         <v>23</v>
@@ -14353,48 +14332,48 @@
         <v>25</v>
       </c>
       <c r="K71" s="21" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="L71" s="21" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="M71" s="21" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="N71" s="24">
         <v>1</v>
       </c>
       <c r="O71" s="22" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="P71" s="22" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="Q71" s="22" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
     </row>
     <row r="72" spans="1:17" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="21" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B72" s="21">
         <v>1</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="D72" s="22" t="s">
         <v>75</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="H72" s="18" t="s">
         <v>23</v>
@@ -14406,48 +14385,48 @@
         <v>25</v>
       </c>
       <c r="K72" s="21" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="L72" s="21" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="M72" s="21" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="N72" s="21">
         <v>1</v>
       </c>
       <c r="O72" s="22" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="Q72" s="22" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="105.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="21" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B73" s="21">
         <v>2</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="D73" s="22" t="s">
         <v>59</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="H73" s="18" t="s">
         <v>23</v>
@@ -14459,48 +14438,48 @@
         <v>25</v>
       </c>
       <c r="K73" s="21" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="L73" s="21" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="M73" s="21" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="N73" s="21">
         <v>1</v>
       </c>
       <c r="O73" s="22" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="P73" s="22" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="Q73" s="22" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
     </row>
     <row r="74" spans="1:17" ht="132" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="21" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B74" s="21">
         <v>3</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="D74" s="22" t="s">
         <v>75</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="F74" s="22" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="H74" s="18" t="s">
         <v>23</v>
@@ -14512,48 +14491,48 @@
         <v>25</v>
       </c>
       <c r="K74" s="21" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="L74" s="21" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="M74" s="21" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="N74" s="21">
         <v>1</v>
       </c>
       <c r="O74" s="22" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="P74" s="22" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="Q74" s="22" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="21" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B75" s="21">
         <v>4</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="D75" s="22" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="H75" s="18" t="s">
         <v>23</v>
@@ -14565,23 +14544,23 @@
         <v>25</v>
       </c>
       <c r="K75" s="21" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="L75" s="21" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="M75" s="21"/>
       <c r="N75" s="21">
         <v>100</v>
       </c>
       <c r="O75" s="22" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="P75" s="22" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="Q75" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -14623,8 +14602,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
-        <v>673</v>
+      <c r="A1" s="104" t="s">
+        <v>666</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -14685,49 +14664,49 @@
         <v>14</v>
       </c>
       <c r="O2" s="37" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="106" t="s">
-        <v>674</v>
-      </c>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="90"/>
+      <c r="A3" s="108" t="s">
+        <v>667</v>
+      </c>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="91"/>
     </row>
     <row r="4" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="54" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="C4" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="E4" s="47" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="F4" s="47" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="G4" s="47" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="H4" s="48" t="s">
         <v>23</v>
@@ -14748,33 +14727,33 @@
         <v>1</v>
       </c>
       <c r="N4" s="47" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="O4" s="47" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="54" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="C5" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="E5" s="47" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="G5" s="47" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="H5" s="48" t="s">
         <v>23</v>
@@ -14795,30 +14774,30 @@
         <v>1</v>
       </c>
       <c r="N5" s="47" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="C6" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="G6" s="47" t="s">
         <v>33</v>
@@ -14842,33 +14821,33 @@
         <v>1</v>
       </c>
       <c r="N6" s="47" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
-        <v>647</v>
-      </c>
-      <c r="B7" s="105" t="s">
-        <v>650</v>
+        <v>640</v>
+      </c>
+      <c r="B7" s="106" t="s">
+        <v>643</v>
       </c>
       <c r="C7" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="F7" s="47" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="G7" s="47" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="H7" s="48" t="s">
         <v>23</v>
@@ -14889,31 +14868,31 @@
         <v>1</v>
       </c>
       <c r="N7" s="47" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="O7" s="47" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="54" t="s">
-        <v>691</v>
-      </c>
-      <c r="B8" s="85"/>
+        <v>684</v>
+      </c>
+      <c r="B8" s="86"/>
       <c r="C8" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="G8" s="47" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="H8" s="48" t="s">
         <v>23</v>
@@ -14926,37 +14905,37 @@
       </c>
       <c r="K8" s="49"/>
       <c r="L8" s="49" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="M8" s="50">
         <v>1</v>
       </c>
       <c r="N8" s="47" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="O8" s="47" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
-        <v>654</v>
-      </c>
-      <c r="B9" s="86"/>
+        <v>647</v>
+      </c>
+      <c r="B9" s="87"/>
       <c r="C9" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="G9" s="47" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>23</v>
@@ -14977,33 +14956,33 @@
         <v>1</v>
       </c>
       <c r="N9" s="47" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="O9" s="47" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
-        <v>659</v>
-      </c>
-      <c r="B10" s="105" t="s">
-        <v>662</v>
+        <v>652</v>
+      </c>
+      <c r="B10" s="106" t="s">
+        <v>655</v>
       </c>
       <c r="C10" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="G10" s="47" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="H10" s="48" t="s">
         <v>23</v>
@@ -15024,31 +15003,31 @@
         <v>1</v>
       </c>
       <c r="N10" s="47" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="O10" s="47" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="54" t="s">
-        <v>707</v>
-      </c>
-      <c r="B11" s="86"/>
+        <v>700</v>
+      </c>
+      <c r="B11" s="87"/>
       <c r="C11" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="G11" s="47" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="H11" s="48" t="s">
         <v>23</v>
@@ -15061,39 +15040,39 @@
       </c>
       <c r="K11" s="49"/>
       <c r="L11" s="49" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="M11" s="50">
         <v>1</v>
       </c>
       <c r="N11" s="47" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="H12" s="48" t="s">
         <v>23</v>
@@ -15114,33 +15093,33 @@
         <v>1</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="54" t="s">
-        <v>718</v>
-      </c>
-      <c r="B13" s="105" t="s">
-        <v>719</v>
+        <v>711</v>
+      </c>
+      <c r="B13" s="106" t="s">
+        <v>712</v>
       </c>
       <c r="C13" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="F13" s="47" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="G13" s="47" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="H13" s="48" t="s">
         <v>23</v>
@@ -15161,31 +15140,31 @@
         <v>1</v>
       </c>
       <c r="N13" s="47" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
     </row>
     <row r="14" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="54" t="s">
-        <v>725</v>
-      </c>
-      <c r="B14" s="86"/>
+        <v>718</v>
+      </c>
+      <c r="B14" s="87"/>
       <c r="C14" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="H14" s="48" t="s">
         <v>23</v>
@@ -15206,33 +15185,33 @@
         <v>1</v>
       </c>
       <c r="N14" s="47" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="54" t="s">
-        <v>731</v>
-      </c>
-      <c r="B15" s="108" t="s">
-        <v>732</v>
+        <v>724</v>
+      </c>
+      <c r="B15" s="105" t="s">
+        <v>725</v>
       </c>
       <c r="C15" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="G15" s="47" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="H15" s="48" t="s">
         <v>23</v>
@@ -15253,31 +15232,31 @@
         <v>1</v>
       </c>
       <c r="N15" s="47" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="O15" s="47" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="54" t="s">
-        <v>738</v>
-      </c>
-      <c r="B16" s="85"/>
+        <v>731</v>
+      </c>
+      <c r="B16" s="86"/>
       <c r="C16" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="G16" s="47" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="H16" s="48" t="s">
         <v>23</v>
@@ -15296,31 +15275,31 @@
         <v>1</v>
       </c>
       <c r="N16" s="47" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="O16" s="47" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="54" t="s">
-        <v>744</v>
-      </c>
-      <c r="B17" s="85"/>
+        <v>737</v>
+      </c>
+      <c r="B17" s="86"/>
       <c r="C17" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="G17" s="47" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="H17" s="48" t="s">
         <v>23</v>
@@ -15339,10 +15318,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="47" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="O17" s="47" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="44" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -15364,25 +15343,25 @@
     </row>
     <row r="19" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="54" t="s">
-        <v>750</v>
-      </c>
-      <c r="B19" s="105" t="s">
-        <v>751</v>
+        <v>743</v>
+      </c>
+      <c r="B19" s="106" t="s">
+        <v>744</v>
       </c>
       <c r="C19" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D19" s="47" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="F19" s="47" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="G19" s="47" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="H19" s="48" t="s">
         <v>23</v>
@@ -15403,31 +15382,31 @@
         <v>1</v>
       </c>
       <c r="N19" s="47" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="O19" s="47" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="54" t="s">
-        <v>758</v>
-      </c>
-      <c r="B20" s="85"/>
+        <v>751</v>
+      </c>
+      <c r="B20" s="86"/>
       <c r="C20" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="47" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="F20" s="47" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="H20" s="48" t="s">
         <v>23</v>
@@ -15448,31 +15427,31 @@
         <v>1</v>
       </c>
       <c r="N20" s="47" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="O20" s="47" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
     </row>
     <row r="21" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="54" t="s">
-        <v>764</v>
-      </c>
-      <c r="B21" s="85"/>
+        <v>757</v>
+      </c>
+      <c r="B21" s="86"/>
       <c r="C21" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="F21" s="47" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="G21" s="47" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="H21" s="48" t="s">
         <v>23</v>
@@ -15493,31 +15472,31 @@
         <v>1</v>
       </c>
       <c r="N21" s="47" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="O21" s="47" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
     </row>
     <row r="22" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="54" t="s">
-        <v>770</v>
-      </c>
-      <c r="B22" s="86"/>
+        <v>763</v>
+      </c>
+      <c r="B22" s="87"/>
       <c r="C22" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="47" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="F22" s="47" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="G22" s="47" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="H22" s="48" t="s">
         <v>23</v>
@@ -15538,33 +15517,33 @@
         <v>1</v>
       </c>
       <c r="N22" s="47" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="O22" s="47" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="54" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="C23" s="47" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="F23" s="47" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="G23" s="47" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="H23" s="48" t="s">
         <v>23</v>
@@ -15585,10 +15564,10 @@
         <v>1</v>
       </c>
       <c r="N23" s="47" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="O23" s="47" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="44" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -15610,22 +15589,22 @@
     </row>
     <row r="25" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="54" t="s">
-        <v>785</v>
-      </c>
-      <c r="B25" s="105" t="s">
-        <v>786</v>
+        <v>778</v>
+      </c>
+      <c r="B25" s="106" t="s">
+        <v>779</v>
       </c>
       <c r="C25" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D25" s="47" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F25" s="47" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="G25" s="47" t="s">
         <v>71</v>
@@ -15641,34 +15620,34 @@
       </c>
       <c r="K25" s="49"/>
       <c r="L25" s="49" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="M25" s="50">
         <v>0</v>
       </c>
       <c r="N25" s="47" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="O25" s="47" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
     </row>
     <row r="26" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="54" t="s">
-        <v>792</v>
-      </c>
-      <c r="B26" s="85"/>
+        <v>785</v>
+      </c>
+      <c r="B26" s="86"/>
       <c r="C26" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="47" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="F26" s="47" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="G26" s="47" t="s">
         <v>71</v>
@@ -15684,34 +15663,34 @@
       </c>
       <c r="K26" s="49"/>
       <c r="L26" s="49" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="M26" s="50">
         <v>0</v>
       </c>
       <c r="N26" s="47" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="O26" s="47" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
     </row>
     <row r="27" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="54" t="s">
-        <v>797</v>
-      </c>
-      <c r="B27" s="85"/>
+        <v>790</v>
+      </c>
+      <c r="B27" s="86"/>
       <c r="C27" s="47" t="s">
         <v>49</v>
       </c>
       <c r="D27" s="47" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="G27" s="47" t="s">
         <v>112</v>
@@ -15733,23 +15712,23 @@
     </row>
     <row r="28" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="54" t="s">
-        <v>801</v>
-      </c>
-      <c r="B28" s="85"/>
+        <v>794</v>
+      </c>
+      <c r="B28" s="86"/>
       <c r="C28" s="47" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D28" s="47" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="G28" s="47" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="H28" s="48" t="s">
         <v>23</v>
@@ -15768,20 +15747,20 @@
     </row>
     <row r="29" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="54" t="s">
-        <v>806</v>
-      </c>
-      <c r="B29" s="86"/>
+        <v>799</v>
+      </c>
+      <c r="B29" s="87"/>
       <c r="C29" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D29" s="47" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="F29" s="47" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="G29" s="47" t="s">
         <v>71</v>
@@ -15797,39 +15776,39 @@
       </c>
       <c r="K29" s="49"/>
       <c r="L29" s="49" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="M29" s="50">
         <v>0</v>
       </c>
       <c r="N29" s="47" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="O29" s="47" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
     </row>
     <row r="30" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="54" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="C30" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="47" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="F30" s="47" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="G30" s="47" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="H30" s="48" t="s">
         <v>23</v>
@@ -15865,22 +15844,22 @@
     </row>
     <row r="32" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="54" t="s">
-        <v>817</v>
-      </c>
-      <c r="B32" s="105" t="s">
-        <v>818</v>
+        <v>810</v>
+      </c>
+      <c r="B32" s="106" t="s">
+        <v>811</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="F32" s="47" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="G32" s="47" t="s">
         <v>112</v>
@@ -15904,31 +15883,31 @@
         <v>1</v>
       </c>
       <c r="N32" s="47" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="O32" s="47" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
     </row>
     <row r="33" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="54" t="s">
-        <v>824</v>
-      </c>
-      <c r="B33" s="85"/>
+        <v>817</v>
+      </c>
+      <c r="B33" s="86"/>
       <c r="C33" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="E33" s="47" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="F33" s="47" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="G33" s="47" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="H33" s="48" t="s">
         <v>23</v>
@@ -15949,28 +15928,28 @@
         <v>1</v>
       </c>
       <c r="N33" s="47" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="O33" s="47" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
     </row>
     <row r="34" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="54" t="s">
-        <v>830</v>
-      </c>
-      <c r="B34" s="85"/>
+        <v>823</v>
+      </c>
+      <c r="B34" s="86"/>
       <c r="C34" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="F34" s="47" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="G34" s="47" t="s">
         <v>112</v>
@@ -15994,28 +15973,28 @@
         <v>1</v>
       </c>
       <c r="N34" s="47" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="O34" s="47" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="54" t="s">
-        <v>835</v>
-      </c>
-      <c r="B35" s="85"/>
+        <v>828</v>
+      </c>
+      <c r="B35" s="86"/>
       <c r="C35" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D35" s="47" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="F35" s="47" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="G35" s="47" t="s">
         <v>112</v>
@@ -16039,28 +16018,28 @@
         <v>1</v>
       </c>
       <c r="N35" s="47" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="O35" s="47" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
     </row>
     <row r="36" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="54" t="s">
-        <v>840</v>
-      </c>
-      <c r="B36" s="85"/>
+        <v>833</v>
+      </c>
+      <c r="B36" s="86"/>
       <c r="C36" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D36" s="47" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="F36" s="47" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="G36" s="47" t="s">
         <v>112</v>
@@ -16084,28 +16063,28 @@
         <v>1</v>
       </c>
       <c r="N36" s="47" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="O36" s="47" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
     </row>
     <row r="37" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="54" t="s">
-        <v>845</v>
-      </c>
-      <c r="B37" s="85"/>
+        <v>838</v>
+      </c>
+      <c r="B37" s="86"/>
       <c r="C37" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D37" s="47" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="F37" s="47" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="G37" s="47" t="s">
         <v>112</v>
@@ -16129,28 +16108,28 @@
         <v>1</v>
       </c>
       <c r="N37" s="47" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="O37" s="47" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
     </row>
     <row r="38" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="54" t="s">
-        <v>850</v>
-      </c>
-      <c r="B38" s="85"/>
+        <v>843</v>
+      </c>
+      <c r="B38" s="86"/>
       <c r="C38" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D38" s="47" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="F38" s="47" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="G38" s="47" t="s">
         <v>112</v>
@@ -16174,28 +16153,28 @@
         <v>1</v>
       </c>
       <c r="N38" s="47" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="O38" s="47" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
     </row>
     <row r="39" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="54" t="s">
-        <v>855</v>
-      </c>
-      <c r="B39" s="85"/>
+        <v>848</v>
+      </c>
+      <c r="B39" s="86"/>
       <c r="C39" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D39" s="47" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="F39" s="47" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="G39" s="47" t="s">
         <v>112</v>
@@ -16219,28 +16198,28 @@
         <v>1</v>
       </c>
       <c r="N39" s="47" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="O39" s="47" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
     </row>
     <row r="40" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="54" t="s">
-        <v>860</v>
-      </c>
-      <c r="B40" s="85"/>
+        <v>853</v>
+      </c>
+      <c r="B40" s="86"/>
       <c r="C40" s="47" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="D40" s="47" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="F40" s="47" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="G40" s="47" t="s">
         <v>112</v>
@@ -16268,20 +16247,20 @@
     </row>
     <row r="41" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="54" t="s">
-        <v>865</v>
-      </c>
-      <c r="B41" s="86"/>
+        <v>858</v>
+      </c>
+      <c r="B41" s="87"/>
       <c r="C41" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D41" s="47" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="F41" s="47" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="G41" s="47" t="s">
         <v>112</v>
@@ -16305,30 +16284,30 @@
         <v>1</v>
       </c>
       <c r="N41" s="47" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="O41" s="47" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="54" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="B42" s="52" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="C42" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D42" s="47" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="F42" s="47" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="G42" s="47" t="s">
         <v>112</v>
@@ -16352,10 +16331,10 @@
         <v>1</v>
       </c>
       <c r="N42" s="47" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="O42" s="47" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
     </row>
     <row r="43" spans="1:15" s="44" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -16377,22 +16356,22 @@
     </row>
     <row r="44" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="54" t="s">
-        <v>876</v>
-      </c>
-      <c r="B44" s="104" t="s">
-        <v>877</v>
+        <v>869</v>
+      </c>
+      <c r="B44" s="107" t="s">
+        <v>870</v>
       </c>
       <c r="C44" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D44" s="47" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="F44" s="47" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="G44" s="47" t="s">
         <v>71</v>
@@ -16417,25 +16396,25 @@
       </c>
       <c r="N44" s="47"/>
       <c r="O44" s="47" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
     </row>
     <row r="45" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="54" t="s">
-        <v>882</v>
-      </c>
-      <c r="B45" s="85"/>
+        <v>875</v>
+      </c>
+      <c r="B45" s="86"/>
       <c r="C45" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D45" s="47" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="F45" s="47" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="G45" s="47" t="s">
         <v>71</v>
@@ -16459,31 +16438,31 @@
         <v>1</v>
       </c>
       <c r="N45" s="47" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="O45" s="47" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="54" t="s">
-        <v>887</v>
-      </c>
-      <c r="B46" s="85"/>
+        <v>880</v>
+      </c>
+      <c r="B46" s="86"/>
       <c r="C46" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D46" s="47" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="F46" s="47" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="G46" s="47" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="H46" s="48" t="s">
         <v>23</v>
@@ -16504,31 +16483,31 @@
         <v>1</v>
       </c>
       <c r="N46" s="47" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="O46" s="47" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
     </row>
     <row r="47" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="54" t="s">
-        <v>893</v>
-      </c>
-      <c r="B47" s="85"/>
+        <v>886</v>
+      </c>
+      <c r="B47" s="86"/>
       <c r="C47" s="47" t="s">
         <v>49</v>
       </c>
       <c r="D47" s="47" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="F47" s="47" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="G47" s="47" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
       <c r="H47" s="48" t="s">
         <v>23</v>
@@ -16549,31 +16528,31 @@
         <v>1</v>
       </c>
       <c r="N47" s="47" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="O47" s="47" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
     </row>
     <row r="48" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="54" t="s">
-        <v>899</v>
-      </c>
-      <c r="B48" s="85"/>
+        <v>892</v>
+      </c>
+      <c r="B48" s="86"/>
       <c r="C48" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D48" s="47" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="E48" s="47" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="F48" s="47" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="G48" s="47" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="H48" s="48" t="s">
         <v>23</v>
@@ -16594,34 +16573,34 @@
         <v>1</v>
       </c>
       <c r="N48" s="47" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="O48" s="47" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="51" customFormat="1" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="54" t="s">
-        <v>905</v>
-      </c>
-      <c r="B49" s="86"/>
+        <v>898</v>
+      </c>
+      <c r="B49" s="87"/>
       <c r="C49" s="47" t="s">
         <v>29</v>
       </c>
       <c r="D49" s="47" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="E49" s="47" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="F49" s="47" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="G49" s="47" t="s">
         <v>112</v>
       </c>
       <c r="H49" s="48" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="I49" s="46" t="s">
         <v>54</v>
@@ -16656,28 +16635,28 @@
     </row>
     <row r="51" spans="1:15" s="51" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="54" t="s">
-        <v>910</v>
-      </c>
-      <c r="B51" s="104" t="s">
-        <v>911</v>
+        <v>903</v>
+      </c>
+      <c r="B51" s="107" t="s">
+        <v>904</v>
       </c>
       <c r="C51" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="47" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="E51" s="47" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="F51" s="47" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="G51" s="47" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="H51" s="48" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="I51" s="46" t="s">
         <v>39</v>
@@ -16693,26 +16672,26 @@
     </row>
     <row r="52" spans="1:15" s="51" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="54" t="s">
-        <v>916</v>
-      </c>
-      <c r="B52" s="85"/>
+        <v>909</v>
+      </c>
+      <c r="B52" s="86"/>
       <c r="C52" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D52" s="47" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="F52" s="47" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="G52" s="47" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="H52" s="48" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="I52" s="46" t="s">
         <v>39</v>
@@ -16728,26 +16707,26 @@
     </row>
     <row r="53" spans="1:15" s="51" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="54" t="s">
-        <v>921</v>
-      </c>
-      <c r="B53" s="85"/>
+        <v>914</v>
+      </c>
+      <c r="B53" s="86"/>
       <c r="C53" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D53" s="47" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="F53" s="47" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="G53" s="47" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="H53" s="48" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="I53" s="46" t="s">
         <v>39</v>
@@ -16763,23 +16742,23 @@
     </row>
     <row r="54" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="54" t="s">
-        <v>926</v>
-      </c>
-      <c r="B54" s="85"/>
+        <v>919</v>
+      </c>
+      <c r="B54" s="86"/>
       <c r="C54" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D54" s="47" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="F54" s="47" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="G54" s="47" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="H54" s="48" t="s">
         <v>23</v>
@@ -16800,31 +16779,31 @@
         <v>1</v>
       </c>
       <c r="N54" s="47" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="O54" s="47" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
     </row>
     <row r="55" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="54" t="s">
-        <v>932</v>
-      </c>
-      <c r="B55" s="85"/>
+        <v>925</v>
+      </c>
+      <c r="B55" s="86"/>
       <c r="C55" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D55" s="47" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
       <c r="E55" s="47" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
       <c r="F55" s="47" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
       <c r="G55" s="47" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="H55" s="48" t="s">
         <v>23</v>
@@ -16845,31 +16824,31 @@
         <v>1</v>
       </c>
       <c r="N55" s="47" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="O55" s="47" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
     </row>
     <row r="56" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="54" t="s">
-        <v>937</v>
-      </c>
-      <c r="B56" s="85"/>
+        <v>930</v>
+      </c>
+      <c r="B56" s="86"/>
       <c r="C56" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D56" s="47" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="E56" s="47" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="F56" s="47" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="G56" s="47" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="H56" s="48" t="s">
         <v>23</v>
@@ -16890,28 +16869,28 @@
         <v>1</v>
       </c>
       <c r="N56" s="47" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="O56" s="47" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
     </row>
     <row r="57" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="54" t="s">
-        <v>943</v>
-      </c>
-      <c r="B57" s="85"/>
+        <v>936</v>
+      </c>
+      <c r="B57" s="86"/>
       <c r="C57" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D57" s="47" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="E57" s="47" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="F57" s="47" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="G57" s="47" t="s">
         <v>141</v>
@@ -16935,28 +16914,28 @@
         <v>1</v>
       </c>
       <c r="N57" s="47" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
       <c r="O57" s="47" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
     </row>
     <row r="58" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="54" t="s">
-        <v>948</v>
-      </c>
-      <c r="B58" s="85"/>
+        <v>941</v>
+      </c>
+      <c r="B58" s="86"/>
       <c r="C58" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D58" s="47" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
       <c r="E58" s="47" t="s">
-        <v>950</v>
+        <v>943</v>
       </c>
       <c r="F58" s="47" t="s">
-        <v>951</v>
+        <v>944</v>
       </c>
       <c r="G58" s="47" t="s">
         <v>33</v>
@@ -16980,31 +16959,31 @@
         <v>1</v>
       </c>
       <c r="N58" s="47" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="O58" s="47" t="s">
-        <v>952</v>
+        <v>945</v>
       </c>
     </row>
     <row r="59" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="54" t="s">
-        <v>953</v>
-      </c>
-      <c r="B59" s="85"/>
+        <v>946</v>
+      </c>
+      <c r="B59" s="86"/>
       <c r="C59" s="47" t="s">
         <v>29</v>
       </c>
       <c r="D59" s="47" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="F59" s="47" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="G59" s="47" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="H59" s="48" t="s">
         <v>23</v>
@@ -17025,31 +17004,31 @@
         <v>1</v>
       </c>
       <c r="N59" s="47" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="O59" s="47" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
     </row>
     <row r="60" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="54" t="s">
-        <v>959</v>
-      </c>
-      <c r="B60" s="85"/>
+        <v>952</v>
+      </c>
+      <c r="B60" s="86"/>
       <c r="C60" s="47" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="D60" s="47" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="F60" s="47" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="G60" s="47" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="H60" s="48" t="s">
         <v>23</v>
@@ -17070,31 +17049,31 @@
         <v>1</v>
       </c>
       <c r="N60" s="47" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
       <c r="O60" s="47" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
     </row>
     <row r="61" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="54" t="s">
-        <v>966</v>
-      </c>
-      <c r="B61" s="85"/>
+        <v>959</v>
+      </c>
+      <c r="B61" s="86"/>
       <c r="C61" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D61" s="47" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="E61" s="47" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="F61" s="47" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="G61" s="47" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="H61" s="48" t="s">
         <v>23</v>
@@ -17115,31 +17094,31 @@
         <v>1</v>
       </c>
       <c r="N61" s="47" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="O61" s="47" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
     </row>
     <row r="62" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="54" t="s">
-        <v>971</v>
-      </c>
-      <c r="B62" s="85"/>
+        <v>964</v>
+      </c>
+      <c r="B62" s="86"/>
       <c r="C62" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D62" s="47" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="F62" s="47" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="G62" s="47" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="H62" s="48" t="s">
         <v>23</v>
@@ -17161,25 +17140,25 @@
       </c>
       <c r="N62" s="47"/>
       <c r="O62" s="47" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
     </row>
     <row r="63" spans="1:15" s="51" customFormat="1" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="54" t="s">
-        <v>977</v>
-      </c>
-      <c r="B63" s="86"/>
+        <v>970</v>
+      </c>
+      <c r="B63" s="87"/>
       <c r="C63" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D63" s="47" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="E63" s="47" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="F63" s="47" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="G63" s="47" t="s">
         <v>71</v>
@@ -17203,10 +17182,10 @@
         <v>1</v>
       </c>
       <c r="N63" s="47" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="O63" s="47" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
@@ -17251,7 +17230,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="83"/>
@@ -17320,7 +17299,7 @@
       <c r="A3" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="85" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="56" t="s">
@@ -17365,7 +17344,7 @@
       <c r="A4" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="85"/>
+      <c r="B4" s="86"/>
       <c r="C4" s="59" t="s">
         <v>29</v>
       </c>
@@ -17408,7 +17387,7 @@
       <c r="A5" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="85"/>
+      <c r="B5" s="86"/>
       <c r="C5" s="56" t="s">
         <v>29</v>
       </c>
@@ -17451,7 +17430,7 @@
       <c r="A6" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="86"/>
+      <c r="B6" s="87"/>
       <c r="C6" s="59" t="s">
         <v>18</v>
       </c>
@@ -17541,7 +17520,7 @@
       <c r="A8" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="87" t="s">
+      <c r="B8" s="88" t="s">
         <v>58</v>
       </c>
       <c r="C8" s="59" t="s">
@@ -17586,7 +17565,7 @@
       <c r="A9" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="86"/>
+      <c r="B9" s="87"/>
       <c r="C9" s="56" t="s">
         <v>67</v>
       </c>
@@ -17631,7 +17610,7 @@
       <c r="A10" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="88" t="s">
         <v>74</v>
       </c>
       <c r="C10" s="59" t="s">
@@ -17678,7 +17657,7 @@
       <c r="A11" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="86"/>
+      <c r="B11" s="87"/>
       <c r="C11" s="56" t="s">
         <v>59</v>
       </c>
@@ -17721,7 +17700,7 @@
       <c r="A12" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="87" t="s">
+      <c r="B12" s="88" t="s">
         <v>88</v>
       </c>
       <c r="C12" s="59" t="s">
@@ -17768,7 +17747,7 @@
       <c r="A13" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="B13" s="86"/>
+      <c r="B13" s="87"/>
       <c r="C13" s="56" t="s">
         <v>29</v>
       </c>
@@ -17903,29 +17882,29 @@
     </row>
     <row r="16" spans="1:15" ht="52.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="89" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="89"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="89"/>
-      <c r="K17" s="89"/>
-      <c r="L17" s="89"/>
-      <c r="M17" s="89"/>
-      <c r="N17" s="89"/>
-      <c r="O17" s="90"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="90"/>
+      <c r="N17" s="90"/>
+      <c r="O17" s="91"/>
     </row>
     <row r="18" spans="1:15" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="B18" s="93" t="s">
+      <c r="B18" s="94" t="s">
         <v>117</v>
       </c>
       <c r="C18" s="61" t="s">
@@ -17966,7 +17945,7 @@
       <c r="A19" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="B19" s="86"/>
+      <c r="B19" s="87"/>
       <c r="C19" s="64" t="s">
         <v>118</v>
       </c>
@@ -18010,7 +17989,7 @@
       <c r="A21" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="91" t="s">
+      <c r="B21" s="92" t="s">
         <v>131</v>
       </c>
       <c r="C21" s="68" t="s">
@@ -18291,7 +18270,7 @@
       <c r="A28" s="68" t="s">
         <v>175</v>
       </c>
-      <c r="B28" s="91" t="s">
+      <c r="B28" s="92" t="s">
         <v>176</v>
       </c>
       <c r="C28" s="68" t="s">
@@ -18447,7 +18426,7 @@
       <c r="O32" s="72"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="82" t="s">
+      <c r="A33" s="84" t="s">
         <v>197</v>
       </c>
       <c r="B33" s="83"/>
@@ -18546,7 +18525,7 @@
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="92" t="s">
+      <c r="A36" s="93" t="s">
         <v>205</v>
       </c>
       <c r="B36" t="s">
@@ -18556,10 +18535,10 @@
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E36" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="F36" t="s">
         <v>213</v>
@@ -18583,11 +18562,11 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="92"/>
+      <c r="A37" s="93"/>
       <c r="B37" t="s">
         <v>199</v>
       </c>
@@ -18595,10 +18574,10 @@
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E37" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="F37" t="s">
         <v>213</v>
@@ -18622,11 +18601,11 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="92"/>
+      <c r="A38" s="93"/>
       <c r="B38" t="s">
         <v>199</v>
       </c>
@@ -18634,10 +18613,10 @@
         <v>67</v>
       </c>
       <c r="D38" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E38" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="F38" t="s">
         <v>213</v>
@@ -18661,11 +18640,11 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="92"/>
+      <c r="A39" s="93"/>
       <c r="B39" t="s">
         <v>199</v>
       </c>
@@ -18673,10 +18652,10 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E39" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F39" t="s">
         <v>213</v>
@@ -18700,11 +18679,11 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="92"/>
+      <c r="A40" s="93"/>
       <c r="B40" t="s">
         <v>199</v>
       </c>
@@ -18712,10 +18691,10 @@
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E40" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F40" t="s">
         <v>213</v>
@@ -18739,11 +18718,11 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="92"/>
+      <c r="A41" s="93"/>
       <c r="B41" t="s">
         <v>199</v>
       </c>
@@ -18751,10 +18730,10 @@
         <v>67</v>
       </c>
       <c r="D41" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E41" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="F41" t="s">
         <v>213</v>
@@ -18778,7 +18757,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:15" s="79" customFormat="1" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -18856,9 +18835,9 @@
       <c r="N44" s="70"/>
       <c r="O44" s="70"/>
     </row>
-    <row r="45" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A45" s="81" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="B45" s="81"/>
       <c r="C45" s="70"/>
@@ -18893,8 +18872,8 @@
       <c r="O46" s="70"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" s="82" t="s">
-        <v>220</v>
+      <c r="A47" s="84" t="s">
+        <v>219</v>
       </c>
       <c r="B47" s="83"/>
       <c r="C47" s="83"/>
@@ -18911,27 +18890,25 @@
       <c r="N47" s="83"/>
       <c r="O47" s="83"/>
     </row>
-    <row r="48" spans="1:15" ht="66" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A48" s="81" t="s">
         <v>216</v>
       </c>
       <c r="B48" s="81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C48" s="70" t="s">
         <v>59</v>
       </c>
       <c r="D48" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="E48" s="81"/>
+      <c r="F48" s="70" t="s">
         <v>222</v>
       </c>
-      <c r="E48" s="81" t="s">
+      <c r="G48" s="70" t="s">
         <v>223</v>
-      </c>
-      <c r="F48" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="G48" s="70" t="s">
-        <v>225</v>
       </c>
       <c r="H48" s="71" t="s">
         <v>203</v>
@@ -18948,28 +18925,24 @@
         <v>0</v>
       </c>
       <c r="N48" s="70"/>
-      <c r="O48" s="70" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="66" x14ac:dyDescent="0.3">
+      <c r="O48" s="70"/>
+    </row>
+    <row r="49" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A49" s="81" t="s">
         <v>217</v>
       </c>
       <c r="B49" s="81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C49" s="70" t="s">
         <v>59</v>
       </c>
       <c r="D49" s="70" t="s">
-        <v>227</v>
-      </c>
-      <c r="E49" s="81" t="s">
-        <v>228</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="E49" s="81"/>
       <c r="F49" s="70" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G49" s="70" t="s">
         <v>92</v>
@@ -18989,28 +18962,24 @@
         <v>0</v>
       </c>
       <c r="N49" s="70"/>
-      <c r="O49" s="70" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="132" x14ac:dyDescent="0.3">
+      <c r="O49" s="70"/>
+    </row>
+    <row r="50" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A50" s="81" t="s">
         <v>218</v>
       </c>
       <c r="B50" s="81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C50" s="70" t="s">
         <v>59</v>
       </c>
       <c r="D50" s="70" t="s">
-        <v>231</v>
-      </c>
-      <c r="E50" s="81" t="s">
-        <v>232</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="E50" s="81"/>
       <c r="F50" s="70" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G50" s="70"/>
       <c r="H50" s="71" t="s">
@@ -19028,9 +18997,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="70"/>
-      <c r="O50" s="70" t="s">
-        <v>234</v>
-      </c>
+      <c r="O50" s="70"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="70"/>
@@ -19050,8 +19017,8 @@
       <c r="O51" s="70"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" s="82" t="s">
-        <v>235</v>
+      <c r="A52" s="84" t="s">
+        <v>228</v>
       </c>
       <c r="B52" s="83"/>
       <c r="C52" s="83"/>
@@ -19070,20 +19037,20 @@
     </row>
     <row r="53" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A53" s="81" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B53" s="81" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C53" s="70" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D53" s="70" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E53" s="81"/>
       <c r="F53" s="70" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="G53" s="70"/>
       <c r="H53" s="71" t="s">
@@ -19101,10 +19068,10 @@
         <v>0</v>
       </c>
       <c r="N53" s="70" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="O53" s="70" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
@@ -19125,8 +19092,8 @@
       <c r="O54" s="70"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="82" t="s">
-        <v>243</v>
+      <c r="A55" s="84" t="s">
+        <v>236</v>
       </c>
       <c r="B55" s="83"/>
       <c r="C55" s="83"/>
@@ -19145,25 +19112,25 @@
     </row>
     <row r="56" spans="1:15" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A56" s="70" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B56" s="81" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C56" s="70" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D56" s="70" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E56" s="81" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F56" s="70" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G56" s="70" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="H56" s="71" t="s">
         <v>203</v>
@@ -19180,33 +19147,33 @@
         <v>0</v>
       </c>
       <c r="N56" s="70" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="O56" s="70" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="66" x14ac:dyDescent="0.3">
       <c r="A57" s="70" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B57" s="81" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C57" s="70" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D57" s="70" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E57" s="81" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F57" s="70" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="G57" s="70" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="H57" s="71" t="s">
         <v>203</v>
@@ -19223,10 +19190,10 @@
         <v>0</v>
       </c>
       <c r="N57" s="70" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="O57" s="70" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -19266,7 +19233,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="98" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -19324,16 +19291,16 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -19360,16 +19327,16 @@
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -19396,16 +19363,16 @@
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -19432,16 +19399,16 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -19468,16 +19435,16 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -1136,12 +1136,15 @@
     <row r="3" ht="14.4" customHeight="1" s="96">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Current: Phase 6A (restaurant OS) -- compliance batch, live-intelligence signals, scenario overhaul, and the Dashboard/Planning/Action Center/Analytics/Data IA redesign are all DONE (P6-A1-A30). Of the UI redesign branch (feature/ui-redesign, P6-A31-A34), P6-A33 (AI Assistant page redesign) is now DONE -- P6-A31 (Action Center tabs), P6-A32 (Analytics 5-section + Menu Matrix), and P6-A34 (Admin panels + connector expansion) are still pending on this same branch. A single debugging session on this branch (2026-07-31) also surfaced and fixed five significant unplanned issues, tracked as P6-A45-A50: two live-intelligence data-integrity bugs (FSSAI site redesign silently broke ComplianceAlertsService; TrendsService was returning empty most days due to a redirect bug + a feed-fairness bug), a manual refresh control for all three live-signal surfaces, and two CRITICAL chat backend bugs -- the chat assistant was 100% broken (every message crashed) due to a DB-session lifecycle bug, and even once fixed, an unbounded Instamart tool result was blowing the Groq free-tier rate limit on ordinary questions. None of this was part of the original plan; all of it is now fixed and verified live against the running app, not just unit tests. Voice interface + chatbot capability expansion (feature/voice-and-chatbot-capabilities, P6-A35-A38), eval/observability/CI (P6-A39-A41), e2e hardening (P6-A42), and docs + sync to main (P6-A43-A44) remain fully ahead and untouched by this session -- Phase 6A is NOT close to done just because of this session's volume of work.</t>
+          <t>Current: Phase 6A (restaurant OS) -- compliance batch, live-intelligence signals, scenario overhaul, and the Dashboard/Planning/Action Center/Analytics/Data IA redesign are all DONE (P6-A1-A30). Of the UI redesign branch (feature/ui-redesign, P6-A31-A34): P6-A32's ComplianceAlertsService/TrendsService fixes + manual refresh control, and P6-A33 (AI Assistant page redesign) are DONE, along with five unplanned bug fixes surfaced during that same debugging session (live-intelligence data-integrity, a 100%-reproducible chat crash, a chat rate-limit failure mode). P6-A31 (Action Center tabs) and P6-A32 (Analytics 5-section + Menu Matrix) remain Planned.
+Last completed branch: feature/phase6b-guest-concierge (P6-A34), merged to dev 2026-08-03. Delivered Guest Concierge -- a no-auth ReAct agent over Swiggy's Food/Instamart/Dineout MCP servers (venue search + booking, food ordering, event-supplies sourcing), as a second, independent platform side with its own /concierge frontend. Same branch also shipped the two-sided homepage redesign, voice input (Whisper transcription) across Dashboard/Planning/chat/Concierge, Market Intelligence page reliability fixes (card-vanishing + a real SSR hydration bug), and a full rewrite of all 22 reference documentation files for accuracy.
+Guest Concierge required no separate Swiggy consent to build -- it is the Proposed Arrangement described in clause 1.1 of the signed Integration Agreement, not a gated feature. The earlier plan to gate it behind written consent under clause 2.1(v) (see row 4, now superseded) was a misreading of the agreement, corrected in docs/DECISIONS.md.
+Next recommended branch: P6-A31 (Action Center tabs) or P6-A32 (Analytics 5-section + Menu Matrix) to close out feature/ui-redesign, then eval/observability/CI automation, e2e hardening, and docs + sync to main.</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Phase 6A: 31 of 44 originally-planned tasks done (P6-A1-A30, A33), plus 6 unplanned fixes (P6-A45-A50) this session. Still pending on feature/ui-redesign: P6-A31, A32, A34. Then, in order: voice + chatbot capabilities branch (A35-A38), eval/observability/CI branch (A39-A41), e2e hardening (A42), docs + sync to main (A43-A44). Then Phase 6B.</t>
+          <t>Phase 6A sheet: 34 of 41 active tasks done. Phase 6 (legacy) sheet: 51 of 55 done, 4 superseded. Guest Concierge (P6-A34) delivered and merged to dev -- no longer gated on Swiggy consent. Still pending: P6-A31 (Action Center tabs), P6-A32 (Analytics 5-section + Menu Matrix), then eval/observability/CI, e2e hardening, and docs + sync to main.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1172,7 +1175,7 @@
     <row r="4" ht="14.4" customHeight="1" s="96">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Phase 6B: guest concierge -- 9 tasks (P6-B1-B9), gated on P6-B1 (Swiggy written consent, clause 2.1v) before any code.</t>
+          <t>Superseded: the original Phase 6B plan (guest concierge as 9 separately-scoped tasks, P6-B1-B9, gated on Swiggy written consent under clause 2.1(v)) never shipped as planned. Guest Concierge was instead delivered inside Phase 6A as P6-A34 (feature/phase6b-guest-concierge, merged to dev 2026-08-03) -- no separate consent was required, since it falls under clause 1.1's Proposed Arrangement. See docs/DECISIONS.md for the corrected compliance reasoning.</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1208,7 +1211,7 @@
     <row r="5" ht="14.4" customHeight="1" s="96">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Staging creds unlock: the real Instamart checkout() call (bulk-order option surfaced in P6-A38 already works up to approval as a peer option to WhatsApp; the final live checkout is what's still blocked) + Dineout book_table (P6-B5 Guest Concierge). Also P6-B7 Guest Concierge Instamart event supplies.</t>
+          <t>Staging creds unlock: the real Instamart checkout() call (bulk-order option already works up to approval as a peer option to WhatsApp; the final live checkout is what's still blocked) + Dineout book_table and Instamart checkout for Guest Concierge (implemented in ConciergeService as part of P6-A34, blocked on the same staging credentials).</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1244,7 +1247,7 @@
     <row r="6" ht="14.4" customHeight="1" s="96">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Compliance: P6-A19 (remove Zomato stub) + P6-A20 (anonymise market intel) -- DONE, merged to dev.</t>
+          <t>Compliance: P6-A19 (remove Zomato stub) + P6-A20 (anonymise market intel) -- DONE, merged to dev. Guest Concierge (P6-A34) confirmed compliant under clause 1.1 (Proposed Arrangement) -- no separate consent required; see docs/DECISIONS.md.</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -1641,11 +1644,11 @@
         </is>
       </c>
       <c r="C16" s="15" t="n">
-        <v>0.7813</v>
+        <v>0.91</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Swiggy-native restaurant OS: connector layer, fourteen-node LangGraph pipeline, Action Queue with approval gates + trust ladder + WhatsApp execution, financial scorecard, MCP server + in-app chatbot tool parity, live-intelligence signals, dynamic scenario composition, Langfuse/Kindred replay, Dashboard/Planning/Action Center/Analytics/Data page split. Next: eval/CI/observability automation, then a unified UI redesign round.</t>
+          <t>Swiggy-native restaurant OS: connector layer, fifteen-node LangGraph pipeline, Action Queue with approval gates + an informational trust-ladder badge + WhatsApp execution, financial scorecard, MCP server + in-app chatbot tool parity, live-intelligence signals, dynamic scenario composition, Langfuse/Kindred replay, Dashboard/Planning/Action Center/Analytics/Data page split, plus Guest Concierge -- a no-auth consumer event-planning agent over Swiggy Food/Instamart/Dineout, delivered as a second, independent platform side (P6-A34). Next: Action Center tabs (P6-A31), Analytics 5-section redesign (P6-A32), eval/CI/observability automation, e2e hardening, then docs + sync to main.</t>
         </is>
       </c>
     </row>

--- a/CortexKitchen_Progress_Tracker.xlsx
+++ b/CortexKitchen_Progress_Tracker.xlsx
@@ -1139,7 +1139,8 @@
           <t>Current: Phase 6A (restaurant OS) -- compliance batch, live-intelligence signals, scenario overhaul, and the Dashboard/Planning/Action Center/Analytics/Data IA redesign are all DONE (P6-A1-A30). Of the UI redesign branch (feature/ui-redesign, P6-A31-A34): P6-A32's ComplianceAlertsService/TrendsService fixes + manual refresh control, and P6-A33 (AI Assistant page redesign) are DONE, along with five unplanned bug fixes surfaced during that same debugging session (live-intelligence data-integrity, a 100%-reproducible chat crash, a chat rate-limit failure mode). P6-A31 (Action Center tabs) and P6-A32 (Analytics 5-section + Menu Matrix) remain Planned.
 Last completed branch: feature/phase6b-guest-concierge (P6-A34), merged to dev 2026-08-03. Delivered Guest Concierge -- a no-auth ReAct agent over Swiggy's Food/Instamart/Dineout MCP servers (venue search + booking, food ordering, event-supplies sourcing), as a second, independent platform side with its own /concierge frontend. Same branch also shipped the two-sided homepage redesign, voice input (Whisper transcription) across Dashboard/Planning/chat/Concierge, Market Intelligence page reliability fixes (card-vanishing + a real SSR hydration bug), and a full rewrite of all 22 reference documentation files for accuracy.
 Guest Concierge required no separate Swiggy consent to build -- it is the Proposed Arrangement described in clause 1.1 of the signed Integration Agreement, not a gated feature. The earlier plan to gate it behind written consent under clause 2.1(v) (see row 4, now superseded) was a misreading of the agreement, corrected in docs/DECISIONS.md.
-Next recommended branch: P6-A31 (Action Center tabs) or P6-A32 (Analytics 5-section + Menu Matrix) to close out feature/ui-redesign, then eval/observability/CI automation, e2e hardening, and docs + sync to main.</t>
+Next recommended branch: P6-A31 (Action Center tabs) or P6-A32 (Analytics 5-section + Menu Matrix) to close out feature/ui-redesign, then eval/observability/CI automation, e2e hardening, and docs + sync to main.
+Main sync: dev merged to main 2026-08-03 (364 files, +43,141/-6,043 lines) -- everything through Guest Concierge (P6-A34) is now on main. This went ahead of P6-A31/A32 (Action Center tabs, Analytics redesign) and the P6-A43 screenshot recapture, both still outstanding on dev.</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -20015,7 +20016,7 @@
       </c>
       <c r="E56" s="81" t="inlineStr">
         <is>
-          <t>Refresh CLAUDE.md and all docs/ files to match the fully implemented Phase 6A state (UI redesign, voice interface, chatbot capability expansion, eval/CI/observability work, e2e hardening) -- same standard as the prior 2026-07-06 docs rewrite (release-quality, matched to code, no stale content). Replace outdated screenshots across README/docs with current UI.</t>
+          <t>Documentation half of this task is done: all 22 markdown files in the repo audited, 16 rewritten for accuracy against the fully implemented Phase 6A state (Swiggy integration, live signals, IA redesign, Guest Concierge), internal task/decision IDs removed throughout. Screenshot half is NOT done -- the outdated screenshots/ directory was deleted rather than replaced; README now says "Screenshots coming soon" as an honest placeholder until a fresh set is captured against the redesigned UI.</t>
         </is>
       </c>
       <c r="F56" s="93" t="inlineStr">
@@ -20030,7 +20031,7 @@
       </c>
       <c r="H56" s="71" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I56" s="93" t="inlineStr">
@@ -20046,7 +20047,7 @@
       <c r="K56" s="93" t="n"/>
       <c r="L56" s="93" t="n"/>
       <c r="M56" s="93" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N56" s="93" t="inlineStr">
         <is>
@@ -20082,12 +20083,12 @@
       </c>
       <c r="E57" s="81" t="inlineStr">
         <is>
-          <t>Merge dev -&gt; main once P6-A31-A43 are all done and verified. Marks the close of this Phase 6A milestone. Phase 6B (Guest Concierge) starts only after this merge, and only once P6-B1 (Swiggy written consent) clears -- not before.</t>
+          <t>Merged dev to main via GitHub PR on 2026-08-03, ahead of the original planned sequence: P6-A31 (Action Center tabs) and P6-A32 (Analytics 5-section + Menu Matrix) are still Planned, and P6-A43's screenshot capture is still outstanding. The merge went ahead as a deliberate call to ship the Guest Concierge milestone now rather than wait on the remaining UI polish items. The note that Phase 6B (Guest Concierge) would start only after this merge and only once Swiggy written consent cleared was based on a misreading of the signed agreement -- Guest Concierge shipped as P6-A34, ahead of this merge, requiring no separate consent. 364 files changed, +43,141/-6,043 lines.</t>
         </is>
       </c>
       <c r="F57" s="93" t="inlineStr">
         <is>
-          <t>release: Phase 6A milestone -- dev to main sync</t>
+          <t>release: Swiggy-native platform, Guest Concierge, and full frontend redesign -- dev to main sync</t>
         </is>
       </c>
       <c r="G57" s="93" t="inlineStr">
@@ -20097,7 +20098,7 @@
       </c>
       <c r="H57" s="71" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I57" s="93" t="inlineStr">
@@ -20110,10 +20111,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="K57" s="93" t="n"/>
-      <c r="L57" s="93" t="n"/>
+      <c r="K57" s="93" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L57" s="93" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
       <c r="M57" s="93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" s="93" t="inlineStr">
         <is>
